--- a/reports/Micro250_stocks.xlsx
+++ b/reports/Micro250_stocks.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -537,7 +537,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>MTARTECH</t>
+          <t>TDPOWERSYS</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -546,37 +546,37 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>4905.1</v>
+        <v>1112.85</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>77.65000000000001</v>
+        <v>80.06</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>81.20999999999999</v>
+        <v>74.89</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>79.62</v>
+        <v>81.18000000000001</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>27.95</v>
+        <v>21.69</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>2960.44</v>
+        <v>763.35</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>2746.34</v>
+        <v>720.3</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>561245</v>
+        <v>1185525</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>15098</v>
+        <v>17384</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>STAR</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -585,37 +585,37 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>1033.05</v>
+        <v>1066.25</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>75.97</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>69.73</v>
+        <v>68.33</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>79.43000000000001</v>
+        <v>59.63</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>29.79</v>
+        <v>42.36</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>746.76</v>
+        <v>901.05</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>706.09</v>
+        <v>893.61</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>1071337</v>
+        <v>298669</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>16138</v>
+        <v>9828</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>IMFA</t>
+          <t>MTARTECH</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -624,37 +624,37 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>1558.5</v>
+        <v>5139.2</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>75.3</v>
+        <v>73.45</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>66.52</v>
+        <v>82.94</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>70.81</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>25.99</v>
+        <v>20.83</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>1211.13</v>
+        <v>3077.88</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>1156.77</v>
+        <v>2844.07</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>154561</v>
+        <v>559706</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>8409</v>
+        <v>15808</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>SHRIPISTON</t>
+          <t>MEDPLUS</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -663,37 +663,37 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>3710.1</v>
+        <v>903.65</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>71.06999999999999</v>
+        <v>67.02</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>67.67</v>
+        <v>62.92</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>73.88</v>
+        <v>58.41</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>22.99</v>
+        <v>21.58</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>2911.39</v>
+        <v>830.09</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>2819.28</v>
+        <v>824.33</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>122986</v>
+        <v>144845</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>16343</v>
+        <v>10844</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>STAR</t>
+          <t>ANURAS</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -702,37 +702,37 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1014.15</v>
+        <v>1341</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>70.02</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>62.88</v>
+        <v>63.37</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>57.79</v>
+        <v>69.64</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>52.97</v>
+        <v>27.53</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>893.95</v>
+        <v>1219.62</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>887.79</v>
+        <v>1183.7</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>273308</v>
+        <v>214656</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>9348</v>
+        <v>15267</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>IMFA</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -741,37 +741,37 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>246.69</v>
+        <v>1504.6</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>66.26000000000001</v>
+        <v>63.13</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>74.44</v>
+        <v>62.65</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>64.44</v>
+        <v>69.83</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>39.4</v>
+        <v>27.41</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>204.25</v>
+        <v>1226.82</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>201</v>
+        <v>1170.92</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>4817254</v>
+        <v>172943</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>9328</v>
+        <v>8118</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>PRIVISCL</t>
+          <t>SHRIPISTON</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -780,37 +780,37 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>3120</v>
+        <v>3478.7</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>65.77</v>
+        <v>57.64</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>61.05</v>
+        <v>60.48</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>67.31999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>39.47</v>
+        <v>30.78</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2798.22</v>
+        <v>2944.01</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2706.53</v>
+        <v>2847.39</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>100381</v>
+        <v>127033</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>12188</v>
+        <v>15324</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>AVANTIFEED</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -819,37 +819,37 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1466.2</v>
+        <v>242.04</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>65.73999999999999</v>
+        <v>57.5</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>73.06999999999999</v>
+        <v>70.67</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>76.7</v>
+        <v>63.6</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>24.03</v>
+        <v>37.25</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1006.82</v>
+        <v>206.45</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>951.75</v>
+        <v>202.79</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>945501</v>
+        <v>4248753</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>19976</v>
+        <v>9154</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>GAEL</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -858,37 +858,37 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>4176.6</v>
+        <v>151.37</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>65.16</v>
+        <v>57.44</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>67.34</v>
+        <v>63.73</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>74.3</v>
+        <v>60.79</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>24.24</v>
+        <v>39.85</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>3229.37</v>
+        <v>130.28</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>3045.5</v>
+        <v>127.81</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>115240</v>
+        <v>880858</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>12999</v>
+        <v>6943</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>CIEINDIA</t>
+          <t>ARVIND</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -897,37 +897,37 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>490.85</v>
+        <v>382.5</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>61.56</v>
+        <v>56.13</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>64.04000000000001</v>
+        <v>60.5</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>57.73</v>
+        <v>60.93</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>53.88</v>
+        <v>26.92</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>439.87</v>
+        <v>344.44</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>438.3</v>
+        <v>342.19</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>312668</v>
+        <v>384882</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>18621</v>
+        <v>10026</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ARVIND</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -936,148 +936,31 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>386.85</v>
+        <v>1113.8</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>61.53</v>
+        <v>48.02</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>61.99</v>
+        <v>61.66</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>61.41</v>
+        <v>67.22</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>25.53</v>
+        <v>24.26</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>342.05</v>
+        <v>963.46</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>340.22</v>
+        <v>935.13</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>384849</v>
+        <v>442084</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>10140</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>LUMAXTECH</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>1780</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>59.41</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>62.55</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>70.81999999999999</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>29.14</v>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>1442.3</v>
-      </c>
-      <c r="I13" s="4" t="n">
-        <v>1357.26</v>
-      </c>
-      <c r="J13" s="4" t="n">
-        <v>289912</v>
-      </c>
-      <c r="K13" s="4" t="n">
-        <v>12132</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>SANSERA</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>2322.2</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>58.28</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>67.33</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>70.47</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>23.89</v>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>1862.88</v>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>1776.42</v>
-      </c>
-      <c r="J14" s="4" t="n">
-        <v>215626</v>
-      </c>
-      <c r="K14" s="4" t="n">
-        <v>14496</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>GAEL</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>148.11</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>57.57</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>62.13</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>59.67</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>45.32</v>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>128.98</v>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>126.7</v>
-      </c>
-      <c r="J15" s="4" t="n">
-        <v>755700</v>
-      </c>
-      <c r="K15" s="4" t="n">
-        <v>6793</v>
+        <v>14778</v>
       </c>
     </row>
   </sheetData>
@@ -1093,9 +976,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1153,7 +1033,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>WEBELSOLAR</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -1162,22 +1042,22 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>1274.35</v>
+        <v>110.85</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>81.55</v>
+        <v>81.66</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>73.34</v>
+        <v>62.31</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>68.40000000000001</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>LUXIND</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -1186,22 +1066,22 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>1525.05</v>
+        <v>3060.7</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>80.23</v>
+        <v>81.27</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>70.45999999999999</v>
+        <v>60.54</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>53.63</v>
+        <v>52.85</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>TDPOWERSYS</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -1210,22 +1090,22 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>271.99</v>
+        <v>1112.85</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>79.43000000000001</v>
+        <v>80.06</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>84.29000000000001</v>
+        <v>74.89</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>77.34999999999999</v>
+        <v>81.18000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>WAAREERTL</t>
+          <t>AZAD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -1234,22 +1114,22 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1118</v>
+        <v>2090.2</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>79.31999999999999</v>
+        <v>79.43000000000001</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>63.89</v>
+        <v>70.58</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v/>
+        <v>63.76</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>AZAD</t>
+          <t>TIPSMUSIC</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -1258,22 +1138,22 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1920.7</v>
+        <v>665.15</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>79.09999999999999</v>
+        <v>77.55</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>65.05</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>60.74</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>VOLTAMP</t>
+          <t>STAR</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1282,22 +1162,22 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>10588.5</v>
+        <v>1066.25</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>78.84</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>69.31999999999999</v>
+        <v>68.33</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>60.7</v>
+        <v>59.63</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>MTARTECH</t>
+          <t>CEIGALL</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1306,22 +1186,22 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>4905.1</v>
+        <v>326.2</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>77.65000000000001</v>
+        <v>76.42</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>81.20999999999999</v>
+        <v>71.84</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>79.62</v>
+        <v>58.47</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>KIRLPNU</t>
+          <t>DYNAMATECH</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -1330,22 +1210,22 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1312</v>
+        <v>11829.5</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>77.18000000000001</v>
+        <v>74.81999999999999</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>62.97</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>57.41</v>
+        <v>71.66</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>PRSMJOHNSN</t>
+          <t>LUXIND</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1354,22 +1234,22 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>141.6</v>
+        <v>1654.1</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>76.91</v>
+        <v>74.7</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>42.39</v>
+        <v>74.95</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>49.29</v>
+        <v>56.21</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>VOLTAMP</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -1378,22 +1258,22 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1033.05</v>
+        <v>10768.5</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>75.97</v>
+        <v>74.31</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>69.73</v>
+        <v>72.95</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>79.43000000000001</v>
+        <v>61.27</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>GALLANTT</t>
+          <t>MTARTECH</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1402,22 +1282,22 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>872.2</v>
+        <v>5139.2</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>75.95999999999999</v>
+        <v>73.45</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>74.73999999999999</v>
+        <v>82.94</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>70.56999999999999</v>
+        <v>80.59999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>ABDL</t>
+          <t>EPIGRAL</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1426,22 +1306,22 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>578.3</v>
+        <v>1202.85</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>75.87</v>
+        <v>72.98999999999999</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>58.91</v>
+        <v>51.38</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>60.14</v>
+        <v>44.64</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>SHILPAMED</t>
+          <t>DIACABS</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1450,22 +1330,22 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>423.35</v>
+        <v>161.72</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>75.77</v>
+        <v>72.95</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>63.74</v>
+        <v>66.28</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>60.36</v>
+        <v>60.81</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>IMFA</t>
+          <t>KIRLPNU</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1474,22 +1354,22 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1558.5</v>
+        <v>1337.4</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>75.3</v>
+        <v>72.5</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>66.52</v>
+        <v>67.87</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>70.81</v>
+        <v>58.15</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>VSTIND</t>
+          <t>MANINFRA</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1498,22 +1378,22 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>265.25</v>
+        <v>113.53</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>75.06</v>
+        <v>72.42</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>61.24</v>
+        <v>49.22</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>48.48</v>
+        <v>42.54</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>STYRENIX</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1522,22 +1402,22 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>193.98</v>
+        <v>2331.4</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>74.93000000000001</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>63.63</v>
+        <v>60.41</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>62.02</v>
+        <v>54.98</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>BBL</t>
+          <t>PRUDENT</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1546,22 +1426,22 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>2796.1</v>
+        <v>2804.9</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>74.83</v>
+        <v>72.22</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>53.38</v>
+        <v>61.03</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>49.58</v>
+        <v>59.41</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>PNGJL</t>
+          <t>AHLUCONT</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1570,22 +1450,22 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>669.8</v>
+        <v>884.4</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>74.73999999999999</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>65.79000000000001</v>
+        <v>53.68</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>56.7</v>
+        <v>49.93</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>SKIPPER</t>
+          <t>INGERRAND</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1594,22 +1474,22 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>436.6</v>
+        <v>4216</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>74.63</v>
+        <v>71.53</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>55.21</v>
+        <v>63.63</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>53.75</v>
+        <v>59.42</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>ISGEC</t>
+          <t>BALAMINES</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1618,22 +1498,22 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1051.75</v>
+        <v>1250.6</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>74.13</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>64.98999999999999</v>
+        <v>56.4</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>52.88</v>
+        <v>41.88</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>PARAS</t>
+          <t>SHAILY</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1642,22 +1522,22 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>808.45</v>
+        <v>2503.1</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>74.04000000000001</v>
+        <v>71.03</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>62.48</v>
+        <v>60.02</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>53.02</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>WEBELSOLAR</t>
+          <t>ISGEC</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1666,22 +1546,22 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>90.59</v>
+        <v>1055.1</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>72.73999999999999</v>
+        <v>71.01000000000001</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>53.43</v>
+        <v>65.95999999999999</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>50.26</v>
+        <v>52.99</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>OSWALPUMPS</t>
+          <t>SKIPPER</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1690,22 +1570,22 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>424.1</v>
+        <v>454.15</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>72.3</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>47.49</v>
+        <v>58.67</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v/>
+        <v>55.23</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>SKYGOLD</t>
+          <t>NEOGEN</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1714,22 +1594,22 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>423.05</v>
+        <v>1634.5</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>71.75</v>
+        <v>70.44</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>67.05</v>
+        <v>62.45</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>64.91</v>
+        <v>53.22</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>EPIGRAL</t>
+          <t>PNGJL</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1738,22 +1618,22 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1168.5</v>
+        <v>666</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>71.72</v>
+        <v>70.33</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>51.27</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>43.74</v>
+        <v>56.28</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENT</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1762,22 +1642,22 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>66.34</v>
+        <v>1247.7</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>71.65000000000001</v>
+        <v>70.25</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>56.35</v>
+        <v>71.54000000000001</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>55.58</v>
+        <v>67.73</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>CEIGALL</t>
+          <t>LLOYDSENT</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1786,22 +1666,22 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>311.2</v>
+        <v>67.53</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>71.62</v>
+        <v>69.62</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>66.43000000000001</v>
+        <v>59.59</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>54.46</v>
+        <v>56.13</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>EMUDHRA</t>
+          <t>CYIENTDLM</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1810,22 +1690,22 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>515.6</v>
+        <v>373</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>71.45</v>
+        <v>69.54000000000001</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>45.26</v>
+        <v>51.75</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>42.87</v>
+        <v>40.19</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>INGERRAND</t>
+          <t>RATNAMANI</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1834,22 +1714,22 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>4110</v>
+        <v>2605.8</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>71.28</v>
+        <v>69.27</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>61.27</v>
+        <v>59.99</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>58.22</v>
+        <v>49.97</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>SWSOLAR</t>
+          <t>PRIVISCL</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1858,22 +1738,22 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>216.54</v>
+        <v>3232.6</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>71.09999999999999</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>45.7</v>
+        <v>63.82</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>40.49</v>
+        <v>68.59999999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>BELRISE</t>
+          <t>JSFB</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1882,22 +1762,22 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>217.01</v>
+        <v>459.35</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>71.06999999999999</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>69.55</v>
+        <v>63.1</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v/>
+        <v>51.47</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>SHRIPISTON</t>
+          <t>LLOYDSENGG</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1906,22 +1786,22 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>3710.1</v>
+        <v>57.43</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>71.06999999999999</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>67.67</v>
+        <v>57.4</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>73.88</v>
+        <v>50.01</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>UNIMECH</t>
+          <t>ANUP</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1930,22 +1810,22 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>969.55</v>
+        <v>2108.8</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>70.64</v>
+        <v>68.91</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>54.84</v>
+        <v>54.55</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>44.96</v>
+        <v>50.25</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>EIEL</t>
+          <t>ASTRAMICRO</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1954,22 +1834,22 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>208.2</v>
+        <v>1123.75</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>70.62</v>
+        <v>68.58</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>57.97</v>
+        <v>62.66</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>42.87</v>
+        <v>63.49</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>PRUDENT</t>
+          <t>BORORENEW</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1978,22 +1858,22 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>2733.2</v>
+        <v>511.25</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>70.36</v>
+        <v>68.44</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>59.59</v>
+        <v>52.03</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>58.48</v>
+        <v>50.08</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>SUNFLAG</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -2002,22 +1882,22 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>1118</v>
+        <v>287.1</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>70.20999999999999</v>
+        <v>68.36</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>61.38</v>
+        <v>62.53</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>62.77</v>
+        <v>57.62</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>SUNFLAG</t>
+          <t>KSL</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -2026,22 +1906,22 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>271.91</v>
+        <v>798.15</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>70.09999999999999</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>59.03</v>
+        <v>58.11</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>55.83</v>
+        <v>52.63</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>STAR</t>
+          <t>WABAG</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -2050,22 +1930,22 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>1014.15</v>
+        <v>1493.3</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>70.02</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>62.88</v>
+        <v>64.03</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>57.79</v>
+        <v>57.62</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENGG</t>
+          <t>STARCEMENT</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -2074,22 +1954,22 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>55.5</v>
+        <v>231.75</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>69.56999999999999</v>
+        <v>68.04000000000001</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>55.79</v>
+        <v>56.91</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>48.92</v>
+        <v>55.65</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>DIACABS</t>
+          <t>ABDL</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -2098,22 +1978,22 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>152.15</v>
+        <v>558.3</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>69.51000000000001</v>
+        <v>67.97</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>60.46</v>
+        <v>56.68</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>59.06</v>
+        <v>58.93</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>HGINFRA</t>
+          <t>HCC</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -2122,22 +2002,22 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>627.45</v>
+        <v>20.05</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>69</v>
+        <v>67.75</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>44.18</v>
+        <v>50.72</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>38.9</v>
+        <v>44.19</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>ANUP</t>
+          <t>UNIMECH</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -2146,22 +2026,22 @@
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>2038</v>
+        <v>994.9</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>68.8</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>51.62</v>
+        <v>56.74</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>49.09</v>
+        <v>46.29</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>POWERMECH</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -2170,22 +2050,22 @@
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>2373.6</v>
+        <v>266.45</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>68.66</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>54.54</v>
+        <v>84.62</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>50.22</v>
+        <v>76.87</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>RTNPOWER</t>
+          <t>GALLANTT</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -2194,22 +2074,22 @@
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>9.640000000000001</v>
+        <v>828.7</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>68.42</v>
+        <v>67.28</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>54.03</v>
+        <v>71.45999999999999</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>48.08</v>
+        <v>69.33</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>VMART</t>
+          <t>EMUDHRA</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -2218,22 +2098,22 @@
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>640.65</v>
+        <v>500.85</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>68.3</v>
+        <v>67.03</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>46.5</v>
+        <v>45.38</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>46.25</v>
+        <v>41.78</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GABRIEL</t>
+          <t>MEDPLUS</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -2242,22 +2122,22 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>1022.8</v>
+        <v>903.65</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>68.08</v>
+        <v>67.02</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>54.27</v>
+        <v>62.92</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>62.07</v>
+        <v>58.41</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>IMAGICAA</t>
+          <t>SANSERA</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -2266,22 +2146,22 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>48.96</v>
+        <v>2530.7</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>68.06</v>
+        <v>66.56999999999999</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>53</v>
+        <v>70.76000000000001</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>44.94</v>
+        <v>73.08</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>RTNINDIA</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -2290,22 +2170,22 @@
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>34.59</v>
+        <v>206.61</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>67.98999999999999</v>
+        <v>66.08</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>45.8</v>
+        <v>55.73</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>41.4</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>ALIVUS</t>
+          <t>PARADEEP</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -2314,22 +2194,22 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>1051.6</v>
+        <v>133.67</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>67.83</v>
+        <v>66.06</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>72.93000000000001</v>
+        <v>49.14</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>63.68</v>
+        <v>51.74</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>ASTRAMICRO</t>
+          <t>KSCL</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -2338,22 +2218,22 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>1081.55</v>
+        <v>937.15</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>67.77</v>
+        <v>65.72</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>60.73</v>
+        <v>52.27</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>62.06</v>
+        <v>50.26</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>AWFIS</t>
+          <t>SWSOLAR</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -2362,22 +2242,22 @@
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>355.3</v>
+        <v>213.31</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>67.45</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>43.55</v>
+        <v>52.65</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>35.48</v>
+        <v>40.12</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>BORORENEW</t>
+          <t>PRSMJOHNSN</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -2386,22 +2266,22 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>495.4</v>
+        <v>134.3</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>67.34999999999999</v>
+        <v>65.59</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>49.98</v>
+        <v>53.08</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>49</v>
+        <v>46.68</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>CMSINFO</t>
+          <t>POWERMECH</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -2410,22 +2290,22 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>317.3</v>
+        <v>2408.5</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>67.25</v>
+        <v>65.42</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>45.34</v>
+        <v>55.63</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>41.42</v>
+        <v>50.69</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>MARKSANS</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -2434,22 +2314,22 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>479.95</v>
+        <v>190.21</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>66.93000000000001</v>
+        <v>65.37</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>57.04</v>
+        <v>56.19</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>46.96</v>
+        <v>50.74</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>MIDHANI</t>
+          <t>INOXGREEN</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -2458,22 +2338,22 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>368.5</v>
+        <v>176.51</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>66.88</v>
+        <v>65.33</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>56.27</v>
+        <v>50.9</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>51.97</v>
+        <v>52.73</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>AHLUCONT</t>
+          <t>PARAS</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -2482,22 +2362,22 @@
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>835.6</v>
+        <v>800.55</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>66.83</v>
+        <v>65.3</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>48.84</v>
+        <v>61.45</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>48.01</v>
+        <v>52.71</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>STYRENIX</t>
+          <t>MIDHANI</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -2506,22 +2386,22 @@
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>2200.8</v>
+        <v>375.95</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>66.7</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>56.48</v>
+        <v>57.46</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>52.52</v>
+        <v>52.59</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>EPL</t>
+          <t>PNCINFRA</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -2530,22 +2410,22 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>236.45</v>
+        <v>217.26</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>66.48999999999999</v>
+        <v>65.14</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>60.49</v>
+        <v>46.52</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>56.63</v>
+        <v>40.43</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>NESCO</t>
+          <t>SHILPAMED</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -2554,22 +2434,22 @@
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>1197.4</v>
+        <v>413.9</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>66.34999999999999</v>
+        <v>65.05</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>54.09</v>
+        <v>64.31</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>57.6</v>
+        <v>59.51</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>KSL</t>
+          <t>AJAXENGG</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -2578,22 +2458,22 @@
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>753.35</v>
+        <v>527.75</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>66.26000000000001</v>
+        <v>64.95</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>52.67</v>
+        <v>49.64</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>50.94</v>
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>RATEGAIN</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -2602,22 +2482,22 @@
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>246.69</v>
+        <v>589.85</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>66.26000000000001</v>
+        <v>64.89</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>74.44</v>
+        <v>52.88</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>64.44</v>
+        <v>50.89</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>INDIAGLYCO</t>
+          <t>WELENT</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -2626,22 +2506,22 @@
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>976.7</v>
+        <v>505.35</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>66.22</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>56.16</v>
+        <v>54.62</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>60.13</v>
+        <v>54.64</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>OPTIEMUS</t>
+          <t>ANURAS</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -2650,22 +2530,22 @@
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>413</v>
+        <v>1341</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>66.19</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>45.46</v>
+        <v>63.37</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>46.8</v>
+        <v>69.64</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>CEMPRO</t>
+          <t>VSTIND</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -2674,22 +2554,22 @@
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>648.2</v>
+        <v>256.21</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>66.02</v>
+        <v>64.22</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>47.68</v>
+        <v>56.58</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v/>
+        <v>46.71</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>REFEX</t>
+          <t>KPIGREEN</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -2698,22 +2578,22 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>243.8</v>
+        <v>448.9</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>65.93000000000001</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>45.21</v>
+        <v>54.81</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>44.95</v>
+        <v>52.07</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>HCC</t>
+          <t>ETHOSLTD</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -2722,22 +2602,22 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>18.97</v>
+        <v>2639.7</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>65.84999999999999</v>
+        <v>63.58</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>47.77</v>
+        <v>53.41</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>43.06</v>
+        <v>52.32</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>TIPSMUSIC</t>
+          <t>SKYGOLD</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -2746,22 +2626,22 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>582.7</v>
+        <v>412.55</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>65.8</v>
+        <v>63.49</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>58.4</v>
+        <v>64.09</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>54.74</v>
+        <v>64.18000000000001</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>PRIVISCL</t>
+          <t>ALIVUS</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -2770,22 +2650,22 @@
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>3120</v>
+        <v>1050.05</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>65.77</v>
+        <v>63.18</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>61.05</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>67.31999999999999</v>
+        <v>63.55</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>AVANTIFEED</t>
+          <t>IMFA</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -2794,22 +2674,22 @@
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>1466.2</v>
+        <v>1504.6</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>65.73999999999999</v>
+        <v>63.13</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>73.06999999999999</v>
+        <v>62.65</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>76.7</v>
+        <v>69.83</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>MOIL</t>
+          <t>AWFIS</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -2818,22 +2698,22 @@
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>325.6</v>
+        <v>349.34</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>65.58</v>
+        <v>62.3</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>52.29</v>
+        <v>41.7</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>50.88</v>
+        <v>34.84</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>IONEXCHANG</t>
+          <t>EUREKAFORB</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -2842,22 +2722,22 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>399</v>
+        <v>510.05</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>65.53</v>
+        <v>62.01</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>56.32</v>
+        <v>47.81</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>45.75</v>
+        <v>45.66</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>KPIGREEN</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -2866,22 +2746,22 @@
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>442</v>
+        <v>183.65</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>65.53</v>
+        <v>62</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>54.7</v>
+        <v>62.66</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>51.61</v>
+        <v>59.45</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>JAIBALAJI</t>
+          <t>INDIASHLTR</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -2890,22 +2770,22 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>72.34999999999999</v>
+        <v>809.7</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>65.47</v>
+        <v>61.98</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>49.2</v>
+        <v>54.18</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>41.65</v>
+        <v>54.55</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>KSCL</t>
+          <t>PRINCEPIPE</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -2914,22 +2794,22 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>917.4</v>
+        <v>262.33</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>65.45</v>
+        <v>61.9</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>50.88</v>
+        <v>50.03</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>49.35</v>
+        <v>38.41</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>LXCHEM</t>
+          <t>JAIBALAJI</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -2938,22 +2818,22 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>141.49</v>
+        <v>71.53</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>65.38</v>
+        <v>61.77</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>46.06</v>
+        <v>48.49</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>37</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>TIMETECHNO</t>
+          <t>REFEX</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -2962,22 +2842,22 @@
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>195.77</v>
+        <v>247.71</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>65.25</v>
+        <v>61.75</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>53.52</v>
+        <v>46.1</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>54.92</v>
+        <v>45.37</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>SANDUMA</t>
+          <t>IIFLCAPS</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -2986,22 +2866,22 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>217.17</v>
+        <v>320.06</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>65.17</v>
+        <v>61.73</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>56.09</v>
+        <v>53.5</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>59.8</v>
+        <v>52.29</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>HGINFRA</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -3010,22 +2890,22 @@
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>4176.6</v>
+        <v>603.1</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>65.16</v>
+        <v>61.2</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>67.34</v>
+        <v>42.6</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>74.3</v>
+        <v>37.79</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>DHANUKA</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -3034,22 +2914,22 @@
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>480</v>
+        <v>1062.2</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>65.04000000000001</v>
+        <v>61.11</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>57.58</v>
+        <v>42.75</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>60.79</v>
+        <v>43.66</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>NETWORK18</t>
+          <t>ENTERO</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -3058,22 +2938,22 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>36.16</v>
+        <v>1250.1</v>
       </c>
       <c r="D81" s="4" t="n">
-        <v>65.02</v>
+        <v>61.03</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>44.02</v>
+        <v>58.26</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>38.52</v>
+        <v>55.35</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>ALLCARGO</t>
+          <t>LXCHEM</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -3082,22 +2962,22 @@
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>9.42</v>
+        <v>140.16</v>
       </c>
       <c r="D82" s="4" t="n">
-        <v>64.97</v>
+        <v>60.98</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>34.05</v>
+        <v>45.12</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>27.77</v>
+        <v>36.65</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>GANECOS</t>
+          <t>KRBL</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -3106,22 +2986,22 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>1051.55</v>
+        <v>359.9</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>64.94</v>
+        <v>60.93</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>56.25</v>
+        <v>52.54</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>46.51</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>EQUITASBNK</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -3130,22 +3010,22 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>272.8</v>
+        <v>65.22</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>64.84999999999999</v>
+        <v>60.9</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>54.09</v>
+        <v>55.03</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>54.01</v>
+        <v>49.57</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>TRANSRAILL</t>
+          <t>IONEXCHANG</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -3154,22 +3034,22 @@
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>578.55</v>
+        <v>397.35</v>
       </c>
       <c r="D85" s="4" t="n">
-        <v>64.78</v>
+        <v>60.7</v>
       </c>
       <c r="E85" s="4" t="n">
-        <v>52.2</v>
+        <v>55.26</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>50.21</v>
+        <v>45.58</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>FINEORG</t>
+          <t>RTNINDIA</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -3178,22 +3058,22 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>4844.1</v>
+        <v>34.25</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>64.7</v>
+        <v>60.67</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>60.82</v>
+        <v>45.01</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>53.26</v>
+        <v>41.18</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>GHCL</t>
+          <t>DBL</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -3202,22 +3082,22 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>509</v>
+        <v>455.05</v>
       </c>
       <c r="D87" s="4" t="n">
-        <v>64.47</v>
+        <v>60.52</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>48.88</v>
+        <v>51.28</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>46.63</v>
+        <v>51.64</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>CYIENTDLM</t>
+          <t>CEMPRO</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -3226,22 +3106,22 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>342.4</v>
+        <v>648.6</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>64.47</v>
+        <v>60.51</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>44.58</v>
+        <v>47.74</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>37.01</v>
+        <v/>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>JINDWORLD</t>
+          <t>INDIAGLYCO</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -3250,22 +3130,22 @@
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>26.33</v>
+        <v>963.25</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>64.41</v>
+        <v>60.49</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>45.45</v>
+        <v>54.88</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>36.25</v>
+        <v>59.68</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>WABAG</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -3274,22 +3154,22 @@
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>1414.7</v>
+        <v>270.09</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>64.37</v>
+        <v>60.45</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>57.71</v>
+        <v>52.96</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>55.74</v>
+        <v>53.57</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>PCJEWELLER</t>
+          <t>OSWALPUMPS</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -3298,22 +3178,22 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>9.75</v>
+        <v>399.75</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>64.3</v>
+        <v>60.32</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>45.9</v>
+        <v>43.45</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>48.87</v>
+        <v/>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>BAJAJELEC</t>
+          <t>GSFC</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -3322,22 +3202,22 @@
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>391.45</v>
+        <v>172.22</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>64.08</v>
+        <v>60.25</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>39.65</v>
+        <v>49.84</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>30.75</v>
+        <v>47.49</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>SURYAROSNI</t>
+          <t>TRANSRAILL</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -3346,22 +3226,22 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>240</v>
+        <v>576</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>64.02</v>
+        <v>60.24</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>48.65</v>
+        <v>51.41</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>47.63</v>
+        <v>50.01</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>NEOGEN</t>
+          <t>BELRISE</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -3370,22 +3250,22 @@
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>1487.4</v>
+        <v>212.76</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>63.76</v>
+        <v>60.09</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>58.26</v>
+        <v>68.62</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>50.26</v>
+        <v/>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>RAIN</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -3394,22 +3274,22 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>134.4</v>
+        <v>193.37</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>63.72</v>
+        <v>59.9</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>50.74</v>
+        <v>64.37</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>47.77</v>
+        <v>62.28</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>HERITGFOOD</t>
+          <t>WAAREERTL</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -3418,22 +3298,22 @@
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>355.7</v>
+        <v>1028.15</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>63.61</v>
+        <v>59.85</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>43.83</v>
+        <v>56.01</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>45.94</v>
+        <v/>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>GREAVESCOT</t>
+          <t>RBA</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -3442,22 +3322,22 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>159.67</v>
+        <v>63.43</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>63.48</v>
+        <v>59.71</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>46.91</v>
+        <v>45.49</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>46.35</v>
+        <v>36.91</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>RATNAMANI</t>
+          <t>EDELWEISS</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -3466,22 +3346,22 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>2479.9</v>
+        <v>119.07</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>63.48</v>
+        <v>59.63</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>54.97</v>
+        <v>57.95</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>47.4</v>
+        <v>58.79</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>ENTERO</t>
+          <t>FINEORG</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -3490,22 +3370,22 @@
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>1255.4</v>
+        <v>4851.5</v>
       </c>
       <c r="D99" s="4" t="n">
-        <v>63.36</v>
+        <v>59.58</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>60.88</v>
+        <v>59.33</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>55.59</v>
+        <v>53.32</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>INDIASHLTR</t>
+          <t>HERITGFOOD</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -3514,22 +3394,22 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>803.65</v>
+        <v>355.25</v>
       </c>
       <c r="D100" s="4" t="n">
-        <v>63.18</v>
+        <v>59.51</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>53.1</v>
+        <v>42.81</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>53.97</v>
+        <v>45.89</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>GOKEX</t>
+          <t>FDC</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -3538,22 +3418,22 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>723.65</v>
+        <v>366.15</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>63.09</v>
+        <v>59.45</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>50.99</v>
+        <v>45.53</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>48.81</v>
+        <v>44.24</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>TSFINV</t>
+          <t>IFBIND</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -3562,22 +3442,22 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>418.4</v>
+        <v>1148.55</v>
       </c>
       <c r="D102" s="4" t="n">
-        <v>63.05</v>
+        <v>59.38</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>38.7</v>
+        <v>42.33</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v/>
+        <v>46.05</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>AURIONPRO</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -3586,22 +3466,22 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>930.45</v>
+        <v>468.45</v>
       </c>
       <c r="D103" s="4" t="n">
-        <v>62.96</v>
+        <v>59.25</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>43.99</v>
+        <v>51.63</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>44.56</v>
+        <v>45.81</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>ZYDUSWELL</t>
+          <t>POLYPLEX</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -3610,22 +3490,22 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>500</v>
+        <v>889.65</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>62.93</v>
+        <v>59.18</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>63.91</v>
+        <v>51.37</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>62.18</v>
+        <v>43.57</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>GSFC</t>
+          <t>TANLA</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -3634,22 +3514,22 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>172</v>
+        <v>485.8</v>
       </c>
       <c r="D105" s="4" t="n">
-        <v>62.73</v>
+        <v>58.73</v>
       </c>
       <c r="E105" s="4" t="n">
-        <v>51.06</v>
+        <v>47.1</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>47.44</v>
+        <v>41.74</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>PGIL</t>
+          <t>MOIL</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -3658,22 +3538,22 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>1637.2</v>
+        <v>319.1</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>62.6</v>
+        <v>58.65</v>
       </c>
       <c r="E106" s="4" t="n">
-        <v>55.97</v>
+        <v>50.24</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>62.51</v>
+        <v>50.08</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>JKPAPER</t>
+          <t>SHARDACROP</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -3682,22 +3562,22 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>371.95</v>
+        <v>1109.65</v>
       </c>
       <c r="D107" s="4" t="n">
-        <v>62.49</v>
+        <v>58.61</v>
       </c>
       <c r="E107" s="4" t="n">
-        <v>57.53</v>
+        <v>59.04</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>51.39</v>
+        <v>61.12</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>SUBROS</t>
+          <t>BAJAJELEC</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -3706,22 +3586,22 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>779.65</v>
+        <v>388.6</v>
       </c>
       <c r="D108" s="4" t="n">
-        <v>62.38</v>
+        <v>58.54</v>
       </c>
       <c r="E108" s="4" t="n">
-        <v>49.46</v>
+        <v>39.09</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>52.74</v>
+        <v>30.46</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>EDELWEISS</t>
+          <t>RTNPOWER</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -3730,22 +3610,22 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>118.46</v>
+        <v>9.48</v>
       </c>
       <c r="D109" s="4" t="n">
-        <v>62.35</v>
+        <v>58.35</v>
       </c>
       <c r="E109" s="4" t="n">
-        <v>57.94</v>
+        <v>51.09</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>58.61</v>
+        <v>47.59</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>MANORAMA</t>
+          <t>VESUVIUS</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -3754,22 +3634,22 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>1417.3</v>
+        <v>499.95</v>
       </c>
       <c r="D110" s="4" t="n">
-        <v>62.27</v>
+        <v>58.32</v>
       </c>
       <c r="E110" s="4" t="n">
-        <v>55.85</v>
+        <v>53.18</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>62.38</v>
+        <v>55.44</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>JKIL</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -3778,22 +3658,22 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>1198.1</v>
+        <v>515.25</v>
       </c>
       <c r="D111" s="4" t="n">
-        <v>62.21</v>
+        <v>58.31</v>
       </c>
       <c r="E111" s="4" t="n">
-        <v>69.93000000000001</v>
+        <v>44</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>70.70999999999999</v>
+        <v>43.37</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>KANSAINER</t>
+          <t>SURYAROSNI</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -3802,22 +3682,22 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>200.8</v>
+        <v>235.58</v>
       </c>
       <c r="D112" s="4" t="n">
-        <v>62.04</v>
+        <v>58.26</v>
       </c>
       <c r="E112" s="4" t="n">
-        <v>46.11</v>
+        <v>47.35</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>38.67</v>
+        <v>47.06</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>EQUITASBNK</t>
+          <t>AVANTIFEED</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -3826,22 +3706,22 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>64.79000000000001</v>
+        <v>1421.1</v>
       </c>
       <c r="D113" s="4" t="n">
-        <v>62.02</v>
+        <v>58.23</v>
       </c>
       <c r="E113" s="4" t="n">
-        <v>55.61</v>
+        <v>69.08</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>49.33</v>
+        <v>75.91</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>ASHOKA</t>
+          <t>MAXESTATES</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -3850,22 +3730,22 @@
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>136.4</v>
+        <v>393</v>
       </c>
       <c r="D114" s="4" t="n">
-        <v>61.99</v>
+        <v>58.21</v>
       </c>
       <c r="E114" s="4" t="n">
-        <v>44.52</v>
+        <v>46.94</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>44.08</v>
+        <v>47.15</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>MSTCLTD</t>
+          <t>OPTIEMUS</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -3874,22 +3754,22 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>462.65</v>
+        <v>402.9</v>
       </c>
       <c r="D115" s="4" t="n">
-        <v>61.89</v>
+        <v>58.11</v>
       </c>
       <c r="E115" s="4" t="n">
-        <v>52.55</v>
+        <v>43.93</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>47.56</v>
+        <v>46.21</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>YATHARTH</t>
+          <t>VMART</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -3898,22 +3778,22 @@
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>750.05</v>
+        <v>617.35</v>
       </c>
       <c r="D116" s="4" t="n">
-        <v>61.79</v>
+        <v>58.1</v>
       </c>
       <c r="E116" s="4" t="n">
-        <v>59.64</v>
+        <v>46.95</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>60.16</v>
+        <v>44.98</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>MEDPLUS</t>
+          <t>TVSSCS</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -3922,22 +3802,22 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>877.4</v>
+        <v>114.35</v>
       </c>
       <c r="D117" s="4" t="n">
-        <v>61.78</v>
+        <v>58.08</v>
       </c>
       <c r="E117" s="4" t="n">
-        <v>59.18</v>
+        <v>51.36</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>56.54</v>
+        <v>41.27</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>TEAMLEASE</t>
+          <t>JKPAPER</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -3946,22 +3826,22 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>1270.7</v>
+        <v>371.7</v>
       </c>
       <c r="D118" s="4" t="n">
-        <v>61.66</v>
+        <v>57.93</v>
       </c>
       <c r="E118" s="4" t="n">
-        <v>34.68</v>
+        <v>56.4</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>32.8</v>
+        <v>51.37</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>RATEGAIN</t>
+          <t>MANORAMA</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -3970,22 +3850,22 @@
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>573.3</v>
+        <v>1411.1</v>
       </c>
       <c r="D119" s="4" t="n">
-        <v>61.59</v>
+        <v>57.92</v>
       </c>
       <c r="E119" s="4" t="n">
-        <v>52.03</v>
+        <v>55.37</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>49.91</v>
+        <v>62.21</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>CIEINDIA</t>
+          <t>SUNTECK</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -3994,22 +3874,22 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>490.85</v>
+        <v>350.65</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>61.56</v>
+        <v>57.79</v>
       </c>
       <c r="E120" s="4" t="n">
-        <v>64.04000000000001</v>
+        <v>45.14</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>57.73</v>
+        <v>43.97</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>ARVIND</t>
+          <t>SAMHI</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -4018,22 +3898,22 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>386.85</v>
+        <v>162.33</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>61.53</v>
+        <v>57.72</v>
       </c>
       <c r="E121" s="4" t="n">
-        <v>61.99</v>
+        <v>45.96</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>61.41</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>ICIL</t>
+          <t>SHRIPISTON</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -4042,22 +3922,22 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>276.39</v>
+        <v>3478.7</v>
       </c>
       <c r="D122" s="4" t="n">
-        <v>61.53</v>
+        <v>57.64</v>
       </c>
       <c r="E122" s="4" t="n">
-        <v>52.15</v>
+        <v>60.48</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>49.9</v>
+        <v>71.75</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>EMIL</t>
+          <t>ZYDUSWELL</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -4066,22 +3946,22 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>103.85</v>
+        <v>490.85</v>
       </c>
       <c r="D123" s="4" t="n">
-        <v>61.48</v>
+        <v>57.62</v>
       </c>
       <c r="E123" s="4" t="n">
-        <v>48.25</v>
+        <v>61.72</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>42.47</v>
+        <v>61.37</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>SPARC</t>
+          <t>TARC</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -4090,22 +3970,22 @@
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>147.11</v>
+        <v>137.41</v>
       </c>
       <c r="D124" s="4" t="n">
-        <v>61.47</v>
+        <v>57.52</v>
       </c>
       <c r="E124" s="4" t="n">
-        <v>58.74</v>
+        <v>45.99</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>45.1</v>
+        <v>47.85</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>TANLA</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -4114,22 +3994,22 @@
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>484.35</v>
+        <v>242.04</v>
       </c>
       <c r="D125" s="4" t="n">
-        <v>61.42</v>
+        <v>57.5</v>
       </c>
       <c r="E125" s="4" t="n">
-        <v>48.02</v>
+        <v>70.67</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>41.65</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>PURVA</t>
+          <t>GAEL</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -4138,22 +4018,22 @@
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>220.65</v>
+        <v>151.37</v>
       </c>
       <c r="D126" s="4" t="n">
-        <v>61.36</v>
+        <v>57.44</v>
       </c>
       <c r="E126" s="4" t="n">
-        <v>50.19</v>
+        <v>63.73</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>45.86</v>
+        <v>60.79</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>KRBL</t>
+          <t>NESCO</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -4162,22 +4042,22 @@
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>347.65</v>
+        <v>1168.6</v>
       </c>
       <c r="D127" s="4" t="n">
-        <v>61.3</v>
+        <v>57.37</v>
       </c>
       <c r="E127" s="4" t="n">
         <v>50.54</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>51.52</v>
+        <v>56.4</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>VESUVIUS</t>
+          <t>BOSCH-HCIL</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -4186,22 +4066,22 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>506.25</v>
+        <v>1366.7</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>61.24</v>
+        <v>57.29</v>
       </c>
       <c r="E128" s="4" t="n">
-        <v>53.11</v>
+        <v>50</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>56.04</v>
+        <v/>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>STARCEMENT</t>
+          <t>SANDUMA</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -4210,22 +4090,22 @@
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>220.64</v>
+        <v>209.35</v>
       </c>
       <c r="D129" s="4" t="n">
-        <v>61.23</v>
+        <v>57.17</v>
       </c>
       <c r="E129" s="4" t="n">
-        <v>51.41</v>
+        <v>52.83</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>53.06</v>
+        <v>58.54</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>WELENT</t>
+          <t>SHAREINDIA</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -4234,22 +4114,22 @@
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>486</v>
+        <v>144.82</v>
       </c>
       <c r="D130" s="4" t="n">
-        <v>61.19</v>
+        <v>57.09</v>
       </c>
       <c r="E130" s="4" t="n">
-        <v>50.32</v>
+        <v>48.1</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>53.16</v>
+        <v>41.44</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>SHAREINDIA</t>
+          <t>IMAGICAA</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -4258,22 +4138,22 @@
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>145.12</v>
+        <v>46.92</v>
       </c>
       <c r="D131" s="4" t="n">
-        <v>61.17</v>
+        <v>57.04</v>
       </c>
       <c r="E131" s="4" t="n">
-        <v>49.19</v>
+        <v>48.29</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>41.5</v>
+        <v>43.35</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>SHARDACROP</t>
+          <t>ADVENZYMES</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -4282,22 +4162,22 @@
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>1101.25</v>
+        <v>299.05</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>60.87</v>
+        <v>57.03</v>
       </c>
       <c r="E132" s="4" t="n">
-        <v>58.95</v>
+        <v>50.82</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>60.92</v>
+        <v>46.96</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>PRICOLLTD</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -4306,22 +4186,22 @@
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>192</v>
+        <v>594.65</v>
       </c>
       <c r="D133" s="4" t="n">
-        <v>60.85</v>
+        <v>57.03</v>
       </c>
       <c r="E133" s="4" t="n">
-        <v>62.66</v>
+        <v>54.73</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>62.03</v>
+        <v>59.46</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>PARADEEP</t>
+          <t>V2RETAIL</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -4330,22 +4210,22 @@
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>124.52</v>
+        <v>203.06</v>
       </c>
       <c r="D134" s="4" t="n">
-        <v>60.85</v>
+        <v>56.91</v>
       </c>
       <c r="E134" s="4" t="n">
-        <v>43.37</v>
+        <v>50.64</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>49.66</v>
+        <v>62.26</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>PNCINFRA</t>
+          <t>RENUKA</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -4354,22 +4234,22 @@
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>203.68</v>
+        <v>27.83</v>
       </c>
       <c r="D135" s="4" t="n">
-        <v>60.84</v>
+        <v>56.9</v>
       </c>
       <c r="E135" s="4" t="n">
-        <v>40.06</v>
+        <v>54.76</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>38.25</v>
+        <v>41.65</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>ANURAS</t>
+          <t>GRWRHITECH</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -4378,22 +4258,22 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>1316.2</v>
+        <v>4035.9</v>
       </c>
       <c r="D136" s="4" t="n">
-        <v>60.83</v>
+        <v>56.84</v>
       </c>
       <c r="E136" s="4" t="n">
-        <v>58.02</v>
+        <v>56.92</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>68.72</v>
+        <v>56.13</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>IIFLCAPS</t>
+          <t>GANESHHOU</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -4402,22 +4282,22 @@
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>308.79</v>
+        <v>644.8</v>
       </c>
       <c r="D137" s="4" t="n">
-        <v>60.81</v>
+        <v>56.79</v>
       </c>
       <c r="E137" s="4" t="n">
-        <v>52.1</v>
+        <v>39.76</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>50.89</v>
+        <v/>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>GATEWAY</t>
+          <t>ZAGGLE</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -4426,22 +4306,22 @@
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>59</v>
+        <v>256.26</v>
       </c>
       <c r="D138" s="4" t="n">
-        <v>60.66</v>
+        <v>56.73</v>
       </c>
       <c r="E138" s="4" t="n">
-        <v>53.62</v>
+        <v>42.07</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>43.57</v>
+        <v>43.89</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>DBL</t>
+          <t>MASTEK</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -4450,22 +4330,22 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>452.2</v>
+        <v>1700.1</v>
       </c>
       <c r="D139" s="4" t="n">
-        <v>60.37</v>
+        <v>56.46</v>
       </c>
       <c r="E139" s="4" t="n">
-        <v>51.64</v>
+        <v>41.86</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>51.33</v>
+        <v>40.85</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>ADVENZYMES</t>
+          <t>GHCL</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -4474,22 +4354,22 @@
         </is>
       </c>
       <c r="C140" s="4" t="n">
-        <v>302.65</v>
+        <v>495.65</v>
       </c>
       <c r="D140" s="4" t="n">
-        <v>60.33</v>
+        <v>56.43</v>
       </c>
       <c r="E140" s="4" t="n">
-        <v>53.83</v>
+        <v>44.98</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>47.53</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>TARC</t>
+          <t>ASHOKA</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -4498,22 +4378,22 @@
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>138.93</v>
+        <v>133.05</v>
       </c>
       <c r="D141" s="4" t="n">
-        <v>60.28</v>
+        <v>56.35</v>
       </c>
       <c r="E141" s="4" t="n">
-        <v>44.84</v>
+        <v>41.96</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>48.17</v>
+        <v>43.47</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>TVSSCS</t>
+          <t>INDIGOPNTS</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -4522,22 +4402,22 @@
         </is>
       </c>
       <c r="C142" s="4" t="n">
-        <v>114.01</v>
+        <v>860.05</v>
       </c>
       <c r="D142" s="4" t="n">
-        <v>60.19</v>
+        <v>56.19</v>
       </c>
       <c r="E142" s="4" t="n">
-        <v>52.19</v>
+        <v>39.98</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>41.14</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>TEXRAIL</t>
+          <t>THYROCARE</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -4546,22 +4426,22 @@
         </is>
       </c>
       <c r="C143" s="4" t="n">
-        <v>104.7</v>
+        <v>395.1</v>
       </c>
       <c r="D143" s="4" t="n">
-        <v>60.18</v>
+        <v>56.15</v>
       </c>
       <c r="E143" s="4" t="n">
-        <v>43.5</v>
+        <v>48.83</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>42.55</v>
+        <v>56.3</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>SAMHI</t>
+          <t>ARVIND</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -4570,22 +4450,22 @@
         </is>
       </c>
       <c r="C144" s="4" t="n">
-        <v>163.47</v>
+        <v>382.5</v>
       </c>
       <c r="D144" s="4" t="n">
-        <v>60.16</v>
+        <v>56.13</v>
       </c>
       <c r="E144" s="4" t="n">
-        <v>46.36</v>
+        <v>60.5</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>46.39</v>
+        <v>60.93</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>INNOVACAP</t>
+          <t>PATELENG</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -4594,22 +4474,22 @@
         </is>
       </c>
       <c r="C145" s="4" t="n">
-        <v>733.75</v>
+        <v>27.7</v>
       </c>
       <c r="D145" s="4" t="n">
-        <v>60.16</v>
+        <v>56</v>
       </c>
       <c r="E145" s="4" t="n">
-        <v>52.84</v>
+        <v>44.62</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>49.81</v>
+        <v>37.81</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>HIKAL</t>
+          <t>EMIL</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -4618,22 +4498,22 @@
         </is>
       </c>
       <c r="C146" s="4" t="n">
-        <v>189.28</v>
+        <v>103.31</v>
       </c>
       <c r="D146" s="4" t="n">
-        <v>60.15</v>
+        <v>55.96</v>
       </c>
       <c r="E146" s="4" t="n">
-        <v>43.36</v>
+        <v>46.68</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>37.06</v>
+        <v>42.31</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>JKLAKSHMI</t>
+          <t>GOKEX</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -4642,22 +4522,22 @@
         </is>
       </c>
       <c r="C147" s="4" t="n">
-        <v>669.15</v>
+        <v>709.05</v>
       </c>
       <c r="D147" s="4" t="n">
-        <v>60.13</v>
+        <v>55.93</v>
       </c>
       <c r="E147" s="4" t="n">
-        <v>43.29</v>
+        <v>49.63</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>44.35</v>
+        <v>48.27</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>CIGNITITEC</t>
+          <t>EPL</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -4666,22 +4546,22 @@
         </is>
       </c>
       <c r="C148" s="4" t="n">
-        <v>1277.7</v>
+        <v>225.84</v>
       </c>
       <c r="D148" s="4" t="n">
-        <v>60.09</v>
+        <v>55.78</v>
       </c>
       <c r="E148" s="4" t="n">
-        <v>43.08</v>
+        <v>56.51</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>47.27</v>
+        <v>54.49</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>FIEMIND</t>
+          <t>GREENPANEL</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -4690,22 +4570,22 @@
         </is>
       </c>
       <c r="C149" s="4" t="n">
-        <v>2250.5</v>
+        <v>208.87</v>
       </c>
       <c r="D149" s="4" t="n">
-        <v>59.99</v>
+        <v>55.78</v>
       </c>
       <c r="E149" s="4" t="n">
-        <v>58.03</v>
+        <v>44.13</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>66.68000000000001</v>
+        <v>39.91</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>GREENPANEL</t>
+          <t>PURVA</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -4714,22 +4594,22 @@
         </is>
       </c>
       <c r="C150" s="4" t="n">
-        <v>211.98</v>
+        <v>214.26</v>
       </c>
       <c r="D150" s="4" t="n">
-        <v>59.98</v>
+        <v>55.76</v>
       </c>
       <c r="E150" s="4" t="n">
-        <v>46.03</v>
+        <v>47.16</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>40.44</v>
+        <v>44.94</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>BIRLACORPN</t>
+          <t>ALLCARGO</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -4738,22 +4618,22 @@
         </is>
       </c>
       <c r="C151" s="4" t="n">
-        <v>969.35</v>
+        <v>9</v>
       </c>
       <c r="D151" s="4" t="n">
-        <v>59.96</v>
+        <v>55.76</v>
       </c>
       <c r="E151" s="4" t="n">
-        <v>45.73</v>
+        <v>32.7</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>41.99</v>
+        <v>27.27</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>RENUKA</t>
+          <t>KANSAINER</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -4762,22 +4642,22 @@
         </is>
       </c>
       <c r="C152" s="4" t="n">
-        <v>27.63</v>
+        <v>197.15</v>
       </c>
       <c r="D152" s="4" t="n">
-        <v>59.69</v>
+        <v>55.64</v>
       </c>
       <c r="E152" s="4" t="n">
-        <v>56.35</v>
+        <v>43.53</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>41.31</v>
+        <v>37.6</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>BANCOINDIA</t>
+          <t>GABRIEL</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -4786,22 +4666,22 @@
         </is>
       </c>
       <c r="C153" s="4" t="n">
-        <v>618.15</v>
+        <v>973</v>
       </c>
       <c r="D153" s="4" t="n">
-        <v>59.67</v>
+        <v>55.53</v>
       </c>
       <c r="E153" s="4" t="n">
-        <v>51.62</v>
+        <v>51</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>57.29</v>
+        <v>60.5</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>PATELENG</t>
+          <t>GREAVESCOT</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -4810,22 +4690,22 @@
         </is>
       </c>
       <c r="C154" s="4" t="n">
-        <v>27.9</v>
+        <v>154.81</v>
       </c>
       <c r="D154" s="4" t="n">
-        <v>59.67</v>
+        <v>55.48</v>
       </c>
       <c r="E154" s="4" t="n">
-        <v>46.54</v>
+        <v>44.2</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>38.08</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>SHAKTIPUMP</t>
+          <t>GANECOS</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -4834,22 +4714,22 @@
         </is>
       </c>
       <c r="C155" s="4" t="n">
-        <v>558.25</v>
+        <v>1008.5</v>
       </c>
       <c r="D155" s="4" t="n">
-        <v>59.58</v>
+        <v>55.46</v>
       </c>
       <c r="E155" s="4" t="n">
-        <v>43.2</v>
+        <v>53.41</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>46.49</v>
+        <v>45.32</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>AGI</t>
+          <t>BANCOINDIA</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -4858,22 +4738,22 @@
         </is>
       </c>
       <c r="C156" s="4" t="n">
-        <v>575.55</v>
+        <v>606.8</v>
       </c>
       <c r="D156" s="4" t="n">
-        <v>59.51</v>
+        <v>55.37</v>
       </c>
       <c r="E156" s="4" t="n">
-        <v>41.77</v>
+        <v>49.57</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>43.25</v>
+        <v>56.79</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>BLACKBUCK</t>
+          <t>SUDARSCHEM</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -4882,22 +4762,22 @@
         </is>
       </c>
       <c r="C157" s="4" t="n">
-        <v>616.5</v>
+        <v>869.55</v>
       </c>
       <c r="D157" s="4" t="n">
-        <v>59.51</v>
+        <v>55.28</v>
       </c>
       <c r="E157" s="4" t="n">
-        <v>53.26</v>
+        <v>41.82</v>
       </c>
       <c r="F157" s="4" t="n">
-        <v>60.61</v>
+        <v>46.83</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>LUMAXTECH</t>
+          <t>AARTIDRUGS</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -4906,16 +4786,16 @@
         </is>
       </c>
       <c r="C158" s="4" t="n">
-        <v>1780</v>
+        <v>366.7</v>
       </c>
       <c r="D158" s="4" t="n">
-        <v>59.41</v>
+        <v>55.24</v>
       </c>
       <c r="E158" s="4" t="n">
-        <v>62.55</v>
+        <v>43.47</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v>70.81999999999999</v>
+        <v>43.14</v>
       </c>
     </row>
     <row r="159">
@@ -4930,22 +4810,22 @@
         </is>
       </c>
       <c r="C159" s="4" t="n">
-        <v>4658.7</v>
+        <v>4595.3</v>
       </c>
       <c r="D159" s="4" t="n">
-        <v>59.36</v>
+        <v>55.11</v>
       </c>
       <c r="E159" s="4" t="n">
-        <v>55.72</v>
+        <v>52.32</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>48.12</v>
+        <v>46.92</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>FDC</t>
+          <t>INNOVACAP</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -4954,22 +4834,22 @@
         </is>
       </c>
       <c r="C160" s="4" t="n">
-        <v>360.2</v>
+        <v>721.15</v>
       </c>
       <c r="D160" s="4" t="n">
-        <v>59.14</v>
+        <v>55.03</v>
       </c>
       <c r="E160" s="4" t="n">
-        <v>42.75</v>
+        <v>49.29</v>
       </c>
       <c r="F160" s="4" t="n">
-        <v>43.34</v>
+        <v>48.81</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>DYNAMATECH</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -4978,22 +4858,22 @@
         </is>
       </c>
       <c r="C161" s="4" t="n">
-        <v>10287</v>
+        <v>603.3</v>
       </c>
       <c r="D161" s="4" t="n">
-        <v>59.13</v>
+        <v>54.96</v>
       </c>
       <c r="E161" s="4" t="n">
-        <v>59.48</v>
+        <v>52.76</v>
       </c>
       <c r="F161" s="4" t="n">
-        <v>66.81999999999999</v>
+        <v>49.48</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>SENCO</t>
+          <t>ACUTAAS</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -5002,22 +4882,22 @@
         </is>
       </c>
       <c r="C162" s="4" t="n">
-        <v>327.95</v>
+        <v>2395</v>
       </c>
       <c r="D162" s="4" t="n">
-        <v>59.02</v>
+        <v>54.95</v>
       </c>
       <c r="E162" s="4" t="n">
-        <v>51.64</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>47.75</v>
+        <v/>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>SHARDAMOTR</t>
+          <t>LMW</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -5026,22 +4906,22 @@
         </is>
       </c>
       <c r="C163" s="4" t="n">
-        <v>867</v>
+        <v>14288</v>
       </c>
       <c r="D163" s="4" t="n">
-        <v>58.99</v>
+        <v>54.86</v>
       </c>
       <c r="E163" s="4" t="n">
-        <v>47.4</v>
+        <v>48.55</v>
       </c>
       <c r="F163" s="4" t="n">
-        <v>43.39</v>
+        <v>48.84</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>ARVINDFASN</t>
+          <t>SUPRIYA</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -5050,22 +4930,22 @@
         </is>
       </c>
       <c r="C164" s="4" t="n">
-        <v>466.05</v>
+        <v>642.85</v>
       </c>
       <c r="D164" s="4" t="n">
-        <v>58.99</v>
+        <v>54.79</v>
       </c>
       <c r="E164" s="4" t="n">
-        <v>51.85</v>
+        <v>44.3</v>
       </c>
       <c r="F164" s="4" t="n">
-        <v>50.88</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>PRINCEPIPE</t>
+          <t>TEXRAIL</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -5074,22 +4954,22 @@
         </is>
       </c>
       <c r="C165" s="4" t="n">
-        <v>253.57</v>
+        <v>102.28</v>
       </c>
       <c r="D165" s="4" t="n">
-        <v>58.82</v>
+        <v>54.69</v>
       </c>
       <c r="E165" s="4" t="n">
-        <v>47.4</v>
+        <v>41.33</v>
       </c>
       <c r="F165" s="4" t="n">
-        <v>37.33</v>
+        <v>41.96</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>MASTEK</t>
+          <t>HCG</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -5098,22 +4978,22 @@
         </is>
       </c>
       <c r="C166" s="4" t="n">
-        <v>1690</v>
+        <v>569.35</v>
       </c>
       <c r="D166" s="4" t="n">
-        <v>58.77</v>
+        <v>54.58</v>
       </c>
       <c r="E166" s="4" t="n">
-        <v>43.88</v>
+        <v>42.09</v>
       </c>
       <c r="F166" s="4" t="n">
-        <v>40.62</v>
+        <v>54.26</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>BALAMINES</t>
+          <t>SHAKTIPUMP</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -5122,22 +5002,22 @@
         </is>
       </c>
       <c r="C167" s="4" t="n">
-        <v>1131.1</v>
+        <v>545.25</v>
       </c>
       <c r="D167" s="4" t="n">
-        <v>58.74</v>
+        <v>54.41</v>
       </c>
       <c r="E167" s="4" t="n">
-        <v>47.09</v>
+        <v>40.31</v>
       </c>
       <c r="F167" s="4" t="n">
-        <v>38.49</v>
+        <v>45.81</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>JKIL</t>
+          <t>VIYASH</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -5146,22 +5026,22 @@
         </is>
       </c>
       <c r="C168" s="4" t="n">
-        <v>512.7</v>
+        <v>207.15</v>
       </c>
       <c r="D168" s="4" t="n">
-        <v>58.67</v>
+        <v>54.36</v>
       </c>
       <c r="E168" s="4" t="n">
-        <v>44.66</v>
+        <v>57.65</v>
       </c>
       <c r="F168" s="4" t="n">
-        <v>43.13</v>
+        <v/>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>IFBIND</t>
+          <t>RAIN</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -5170,22 +5050,22 @@
         </is>
       </c>
       <c r="C169" s="4" t="n">
-        <v>1103.05</v>
+        <v>128.2</v>
       </c>
       <c r="D169" s="4" t="n">
-        <v>58.57</v>
+        <v>54.26</v>
       </c>
       <c r="E169" s="4" t="n">
-        <v>39.88</v>
+        <v>48.66</v>
       </c>
       <c r="F169" s="4" t="n">
-        <v>45.11</v>
+        <v>46.33</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>BOSCH-HCIL</t>
+          <t>DODLA</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -5194,22 +5074,22 @@
         </is>
       </c>
       <c r="C170" s="4" t="n">
-        <v>1353.5</v>
+        <v>1092.9</v>
       </c>
       <c r="D170" s="4" t="n">
-        <v>58.4</v>
+        <v>54.21</v>
       </c>
       <c r="E170" s="4" t="n">
-        <v>48.31</v>
+        <v>42.79</v>
       </c>
       <c r="F170" s="4" t="n">
-        <v/>
+        <v>49.42</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>AARTIDRUGS</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -5218,22 +5098,22 @@
         </is>
       </c>
       <c r="C171" s="4" t="n">
-        <v>369</v>
+        <v>455.65</v>
       </c>
       <c r="D171" s="4" t="n">
-        <v>58.35</v>
+        <v>54.09</v>
       </c>
       <c r="E171" s="4" t="n">
-        <v>45.17</v>
+        <v>53.51</v>
       </c>
       <c r="F171" s="4" t="n">
-        <v>43.41</v>
+        <v>59.07</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>SYMPHONY</t>
+          <t>ORCHPHARMA</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -5242,22 +5122,22 @@
         </is>
       </c>
       <c r="C172" s="4" t="n">
-        <v>812.6</v>
+        <v>566.85</v>
       </c>
       <c r="D172" s="4" t="n">
-        <v>58.32</v>
+        <v>54.07</v>
       </c>
       <c r="E172" s="4" t="n">
-        <v>45.72</v>
+        <v>38.59</v>
       </c>
       <c r="F172" s="4" t="n">
-        <v>42.01</v>
+        <v>41.67</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>PARKHOTELS</t>
+          <t>AARTIPHARM</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -5266,22 +5146,22 @@
         </is>
       </c>
       <c r="C173" s="4" t="n">
-        <v>120.2</v>
+        <v>692.95</v>
       </c>
       <c r="D173" s="4" t="n">
-        <v>58.29</v>
+        <v>54.05</v>
       </c>
       <c r="E173" s="4" t="n">
-        <v>45.27</v>
+        <v>45.92</v>
       </c>
       <c r="F173" s="4" t="n">
-        <v>38.22</v>
+        <v>51.23</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>SANSERA</t>
+          <t>PCJEWELLER</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -5290,22 +5170,22 @@
         </is>
       </c>
       <c r="C174" s="4" t="n">
-        <v>2322.2</v>
+        <v>9.35</v>
       </c>
       <c r="D174" s="4" t="n">
-        <v>58.28</v>
+        <v>53.95</v>
       </c>
       <c r="E174" s="4" t="n">
-        <v>67.33</v>
+        <v>44.38</v>
       </c>
       <c r="F174" s="4" t="n">
-        <v>70.47</v>
+        <v>47.82</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>ZAGGLE</t>
+          <t>NFL</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -5314,22 +5194,22 @@
         </is>
       </c>
       <c r="C175" s="4" t="n">
-        <v>255.69</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="D175" s="4" t="n">
-        <v>58.25</v>
+        <v>53.87</v>
       </c>
       <c r="E175" s="4" t="n">
-        <v>43.09</v>
+        <v>42.83</v>
       </c>
       <c r="F175" s="4" t="n">
-        <v>43.83</v>
+        <v>44.69</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>RELAXO</t>
+          <t>AGI</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -5338,22 +5218,22 @@
         </is>
       </c>
       <c r="C176" s="4" t="n">
-        <v>307.99</v>
+        <v>556.2</v>
       </c>
       <c r="D176" s="4" t="n">
-        <v>57.63</v>
+        <v>53.86</v>
       </c>
       <c r="E176" s="4" t="n">
-        <v>37.99</v>
+        <v>38.38</v>
       </c>
       <c r="F176" s="4" t="n">
-        <v>28.66</v>
+        <v>42.22</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>VAIBHAVGBL</t>
+          <t>JINDWORLD</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -5362,22 +5242,22 @@
         </is>
       </c>
       <c r="C177" s="4" t="n">
-        <v>220.81</v>
+        <v>24.64</v>
       </c>
       <c r="D177" s="4" t="n">
-        <v>57.58</v>
+        <v>53.85</v>
       </c>
       <c r="E177" s="4" t="n">
-        <v>50.65</v>
+        <v>41.72</v>
       </c>
       <c r="F177" s="4" t="n">
-        <v>44.4</v>
+        <v>34.87</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>GAEL</t>
+          <t>SPARC</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -5386,22 +5266,22 @@
         </is>
       </c>
       <c r="C178" s="4" t="n">
-        <v>148.11</v>
+        <v>139.28</v>
       </c>
       <c r="D178" s="4" t="n">
-        <v>57.57</v>
+        <v>53.68</v>
       </c>
       <c r="E178" s="4" t="n">
-        <v>62.13</v>
+        <v>52.84</v>
       </c>
       <c r="F178" s="4" t="n">
-        <v>59.67</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>GARFIBRES</t>
+          <t>TSFINV</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -5410,22 +5290,22 @@
         </is>
       </c>
       <c r="C179" s="4" t="n">
-        <v>640.3</v>
+        <v>397.85</v>
       </c>
       <c r="D179" s="4" t="n">
-        <v>57.56</v>
+        <v>53.57</v>
       </c>
       <c r="E179" s="4" t="n">
-        <v>45.71</v>
+        <v>37.3</v>
       </c>
       <c r="F179" s="4" t="n">
-        <v>41.76</v>
+        <v/>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>QUESS</t>
+          <t>CELLO</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -5434,22 +5314,22 @@
         </is>
       </c>
       <c r="C180" s="4" t="n">
-        <v>194.45</v>
+        <v>427.45</v>
       </c>
       <c r="D180" s="4" t="n">
-        <v>57.55</v>
+        <v>53.56</v>
       </c>
       <c r="E180" s="4" t="n">
-        <v>41.45</v>
+        <v>36.21</v>
       </c>
       <c r="F180" s="4" t="n">
-        <v>31.19</v>
+        <v>32.99</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>NFL</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -5458,22 +5338,22 @@
         </is>
       </c>
       <c r="C181" s="4" t="n">
-        <v>76.48</v>
+        <v>1040.65</v>
       </c>
       <c r="D181" s="4" t="n">
-        <v>57.52</v>
+        <v>53.49</v>
       </c>
       <c r="E181" s="4" t="n">
-        <v>45.07</v>
+        <v>55.01</v>
       </c>
       <c r="F181" s="4" t="n">
-        <v>45.01</v>
+        <v>60.36</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>INOXGREEN</t>
+          <t>SYMPHONY</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -5482,22 +5362,22 @@
         </is>
       </c>
       <c r="C182" s="4" t="n">
-        <v>162.18</v>
+        <v>794.7</v>
       </c>
       <c r="D182" s="4" t="n">
-        <v>57.42</v>
+        <v>53.37</v>
       </c>
       <c r="E182" s="4" t="n">
-        <v>45.9</v>
+        <v>43.87</v>
       </c>
       <c r="F182" s="4" t="n">
-        <v>50.75</v>
+        <v>41.08</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>PRICOLLTD</t>
+          <t>EASEMYTRIP</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -5506,22 +5386,22 @@
         </is>
       </c>
       <c r="C183" s="4" t="n">
-        <v>582.05</v>
+        <v>7.62</v>
       </c>
       <c r="D183" s="4" t="n">
-        <v>57.32</v>
+        <v>53.26</v>
       </c>
       <c r="E183" s="4" t="n">
-        <v>53.58</v>
+        <v>49.32</v>
       </c>
       <c r="F183" s="4" t="n">
-        <v>58.65</v>
+        <v>36.92</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>SOUTHBANK</t>
+          <t>SUBROS</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -5530,22 +5410,22 @@
         </is>
       </c>
       <c r="C184" s="4" t="n">
-        <v>39.43</v>
+        <v>753.45</v>
       </c>
       <c r="D184" s="4" t="n">
-        <v>57.32</v>
+        <v>53.24</v>
       </c>
       <c r="E184" s="4" t="n">
-        <v>53.5</v>
+        <v>46.18</v>
       </c>
       <c r="F184" s="4" t="n">
-        <v>63.94</v>
+        <v>51.62</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>POLYPLEX</t>
+          <t>DCAL</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -5554,22 +5434,22 @@
         </is>
       </c>
       <c r="C185" s="4" t="n">
-        <v>873</v>
+        <v>169.01</v>
       </c>
       <c r="D185" s="4" t="n">
-        <v>57.3</v>
+        <v>53.2</v>
       </c>
       <c r="E185" s="4" t="n">
-        <v>50.61</v>
+        <v>38.11</v>
       </c>
       <c r="F185" s="4" t="n">
-        <v>42.75</v>
+        <v>44.33</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>ROUTE</t>
+          <t>PARKHOTELS</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -5578,22 +5458,22 @@
         </is>
       </c>
       <c r="C186" s="4" t="n">
-        <v>505.95</v>
+        <v>119.04</v>
       </c>
       <c r="D186" s="4" t="n">
-        <v>57.16</v>
+        <v>53.07</v>
       </c>
       <c r="E186" s="4" t="n">
-        <v>34.83</v>
+        <v>43.28</v>
       </c>
       <c r="F186" s="4" t="n">
-        <v>28.15</v>
+        <v>37.7</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>EASEMYTRIP</t>
+          <t>LUMAXTECH</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -5602,22 +5482,22 @@
         </is>
       </c>
       <c r="C187" s="4" t="n">
-        <v>7.78</v>
+        <v>1727</v>
       </c>
       <c r="D187" s="4" t="n">
-        <v>57.01</v>
+        <v>53</v>
       </c>
       <c r="E187" s="4" t="n">
-        <v>50.8</v>
+        <v>59.23</v>
       </c>
       <c r="F187" s="4" t="n">
-        <v>37.48</v>
+        <v>70.02</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>ORIENTCEM</t>
+          <t>SHARDAMOTR</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -5626,22 +5506,22 @@
         </is>
       </c>
       <c r="C188" s="4" t="n">
-        <v>145.45</v>
+        <v>845</v>
       </c>
       <c r="D188" s="4" t="n">
-        <v>56.9</v>
+        <v>53</v>
       </c>
       <c r="E188" s="4" t="n">
-        <v>36.34</v>
+        <v>45.27</v>
       </c>
       <c r="F188" s="4" t="n">
-        <v>36.92</v>
+        <v>42.67</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>RALLIS</t>
+          <t>NETWORK18</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -5650,22 +5530,22 @@
         </is>
       </c>
       <c r="C189" s="4" t="n">
-        <v>261.83</v>
+        <v>34.2</v>
       </c>
       <c r="D189" s="4" t="n">
-        <v>56.82</v>
+        <v>52.92</v>
       </c>
       <c r="E189" s="4" t="n">
-        <v>50.89</v>
+        <v>40.01</v>
       </c>
       <c r="F189" s="4" t="n">
-        <v>48.48</v>
+        <v>37.05</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>VARROC</t>
+          <t>ORIENTCEM</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -5674,22 +5554,22 @@
         </is>
       </c>
       <c r="C190" s="4" t="n">
-        <v>532.75</v>
+        <v>143.57</v>
       </c>
       <c r="D190" s="4" t="n">
-        <v>56.57</v>
+        <v>52.88</v>
       </c>
       <c r="E190" s="4" t="n">
-        <v>47.08</v>
+        <v>35.78</v>
       </c>
       <c r="F190" s="4" t="n">
-        <v>50.59</v>
+        <v>36.52</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>VIYASH</t>
+          <t>GULFOILLUB</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -5698,22 +5578,22 @@
         </is>
       </c>
       <c r="C191" s="4" t="n">
-        <v>207.75</v>
+        <v>969.5</v>
       </c>
       <c r="D191" s="4" t="n">
-        <v>56.55</v>
+        <v>52.55</v>
       </c>
       <c r="E191" s="4" t="n">
-        <v/>
+        <v>39.97</v>
       </c>
       <c r="F191" s="4" t="n">
-        <v/>
+        <v>47.67</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>AJAXENGG</t>
+          <t>ICIL</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -5722,22 +5602,22 @@
         </is>
       </c>
       <c r="C192" s="4" t="n">
-        <v>490</v>
+        <v>263.29</v>
       </c>
       <c r="D192" s="4" t="n">
-        <v>56.45</v>
+        <v>52.5</v>
       </c>
       <c r="E192" s="4" t="n">
-        <v>42.53</v>
+        <v>49.18</v>
       </c>
       <c r="F192" s="4" t="n">
-        <v/>
+        <v>48.18</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>RBA</t>
+          <t>TIMETECHNO</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -5746,22 +5626,22 @@
         </is>
       </c>
       <c r="C193" s="4" t="n">
-        <v>62.7</v>
+        <v>184.11</v>
       </c>
       <c r="D193" s="4" t="n">
-        <v>56.36</v>
+        <v>52.5</v>
       </c>
       <c r="E193" s="4" t="n">
-        <v>45.11</v>
+        <v>48.37</v>
       </c>
       <c r="F193" s="4" t="n">
-        <v>36.24</v>
+        <v>52.56</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>GMMPFAUDLR</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -5770,22 +5650,22 @@
         </is>
       </c>
       <c r="C194" s="4" t="n">
-        <v>605.75</v>
+        <v>908.6</v>
       </c>
       <c r="D194" s="4" t="n">
-        <v>56.33</v>
+        <v>52.46</v>
       </c>
       <c r="E194" s="4" t="n">
-        <v>53.4</v>
+        <v>40.43</v>
       </c>
       <c r="F194" s="4" t="n">
-        <v>49.71</v>
+        <v>41.16</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>GATEWAY</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -5794,22 +5674,22 @@
         </is>
       </c>
       <c r="C195" s="4" t="n">
-        <v>177.5</v>
+        <v>57.03</v>
       </c>
       <c r="D195" s="4" t="n">
-        <v>56.18</v>
+        <v>52.37</v>
       </c>
       <c r="E195" s="4" t="n">
-        <v>49.8</v>
+        <v>48.81</v>
       </c>
       <c r="F195" s="4" t="n">
-        <v>48.48</v>
+        <v>41.56</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>ELECTCAST</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -5818,22 +5698,22 @@
         </is>
       </c>
       <c r="C196" s="4" t="n">
-        <v>106.7</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="D196" s="4" t="n">
-        <v>56.16</v>
+        <v>52.21</v>
       </c>
       <c r="E196" s="4" t="n">
-        <v>42.86</v>
+        <v>49.47</v>
       </c>
       <c r="F196" s="4" t="n">
-        <v>40.79</v>
+        <v>43.08</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>DATAMATICS</t>
+          <t>RELAXO</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -5842,22 +5722,22 @@
         </is>
       </c>
       <c r="C197" s="4" t="n">
-        <v>740.9</v>
+        <v>301.19</v>
       </c>
       <c r="D197" s="4" t="n">
-        <v>56.14</v>
+        <v>52.14</v>
       </c>
       <c r="E197" s="4" t="n">
-        <v>49.1</v>
+        <v>36.56</v>
       </c>
       <c r="F197" s="4" t="n">
-        <v>52.74</v>
+        <v>27.77</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>SUPRIYA</t>
+          <t>ROUTE</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -5866,22 +5746,22 @@
         </is>
       </c>
       <c r="C198" s="4" t="n">
-        <v>638.05</v>
+        <v>497.6</v>
       </c>
       <c r="D198" s="4" t="n">
-        <v>56.09</v>
+        <v>52.05</v>
       </c>
       <c r="E198" s="4" t="n">
-        <v>43.23</v>
+        <v>33.07</v>
       </c>
       <c r="F198" s="4" t="n">
-        <v>52.44</v>
+        <v>27.59</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>SFL</t>
+          <t>YATHARTH</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -5890,22 +5770,22 @@
         </is>
       </c>
       <c r="C199" s="4" t="n">
-        <v>541.8</v>
+        <v>718.3</v>
       </c>
       <c r="D199" s="4" t="n">
-        <v>55.98</v>
+        <v>51.84</v>
       </c>
       <c r="E199" s="4" t="n">
-        <v>44.72</v>
+        <v>54.34</v>
       </c>
       <c r="F199" s="4" t="n">
-        <v>37.57</v>
+        <v>58.71</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>BALUFORGE</t>
+          <t>VAIBHAVGBL</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -5914,22 +5794,22 @@
         </is>
       </c>
       <c r="C200" s="4" t="n">
-        <v>477.15</v>
+        <v>215.03</v>
       </c>
       <c r="D200" s="4" t="n">
-        <v>55.81</v>
+        <v>51.69</v>
       </c>
       <c r="E200" s="4" t="n">
-        <v>46.43</v>
+        <v>47.58</v>
       </c>
       <c r="F200" s="4" t="n">
-        <v>47.39</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>MAXESTATES</t>
+          <t>FIEMIND</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -5938,22 +5818,22 @@
         </is>
       </c>
       <c r="C201" s="4" t="n">
-        <v>383.4</v>
+        <v>2175</v>
       </c>
       <c r="D201" s="4" t="n">
-        <v>55.78</v>
+        <v>51.51</v>
       </c>
       <c r="E201" s="4" t="n">
-        <v>45.94</v>
+        <v>52.85</v>
       </c>
       <c r="F201" s="4" t="n">
-        <v>46.27</v>
+        <v>65.19</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>SOUTHBANK</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -5962,22 +5842,22 @@
         </is>
       </c>
       <c r="C202" s="4" t="n">
-        <v>439</v>
+        <v>38.63</v>
       </c>
       <c r="D202" s="4" t="n">
-        <v>55.76</v>
+        <v>51.45</v>
       </c>
       <c r="E202" s="4" t="n">
-        <v>46.95</v>
+        <v>52.67</v>
       </c>
       <c r="F202" s="4" t="n">
-        <v>51.63</v>
+        <v>63.11</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>GMRP&amp;UI</t>
+          <t>SENCO</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -5986,22 +5866,22 @@
         </is>
       </c>
       <c r="C203" s="4" t="n">
-        <v>108.29</v>
+        <v>318.1</v>
       </c>
       <c r="D203" s="4" t="n">
-        <v>55.76</v>
+        <v>51.24</v>
       </c>
       <c r="E203" s="4" t="n">
-        <v>50.86</v>
+        <v>49.36</v>
       </c>
       <c r="F203" s="4" t="n">
-        <v>53.76</v>
+        <v>46.79</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>DCAL</t>
+          <t>RALLIS</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -6010,22 +5890,22 @@
         </is>
       </c>
       <c r="C204" s="4" t="n">
-        <v>171.22</v>
+        <v>256.47</v>
       </c>
       <c r="D204" s="4" t="n">
-        <v>55.75</v>
+        <v>51.15</v>
       </c>
       <c r="E204" s="4" t="n">
-        <v>37.94</v>
+        <v>47.25</v>
       </c>
       <c r="F204" s="4" t="n">
-        <v>44.65</v>
+        <v>47.73</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>LMW</t>
+          <t>HIKAL</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -6034,22 +5914,22 @@
         </is>
       </c>
       <c r="C205" s="4" t="n">
-        <v>14221</v>
+        <v>181.1</v>
       </c>
       <c r="D205" s="4" t="n">
-        <v>55.7</v>
+        <v>51.03</v>
       </c>
       <c r="E205" s="4" t="n">
-        <v>49</v>
+        <v>40.27</v>
       </c>
       <c r="F205" s="4" t="n">
-        <v>48.62</v>
+        <v>35.61</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>GANESHHOU</t>
+          <t>GMRP&amp;UI</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -6058,22 +5938,22 @@
         </is>
       </c>
       <c r="C206" s="4" t="n">
-        <v>635.2</v>
+        <v>106</v>
       </c>
       <c r="D206" s="4" t="n">
-        <v>55.67</v>
+        <v>50.91</v>
       </c>
       <c r="E206" s="4" t="n">
-        <v>38.87</v>
+        <v>48.26</v>
       </c>
       <c r="F206" s="4" t="n">
-        <v/>
+        <v>53.04</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>ETHOSLTD</t>
+          <t>BLACKBUCK</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -6082,22 +5962,22 @@
         </is>
       </c>
       <c r="C207" s="4" t="n">
-        <v>2407.8</v>
+        <v>597.25</v>
       </c>
       <c r="D207" s="4" t="n">
-        <v>55.51</v>
+        <v>50.91</v>
       </c>
       <c r="E207" s="4" t="n">
-        <v>45.54</v>
+        <v>49.9</v>
       </c>
       <c r="F207" s="4" t="n">
-        <v>48.74</v>
+        <v>58.58</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>JSFB</t>
+          <t>QUESS</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -6106,22 +5986,22 @@
         </is>
       </c>
       <c r="C208" s="4" t="n">
-        <v>391.1</v>
+        <v>190.14</v>
       </c>
       <c r="D208" s="4" t="n">
-        <v>55.44</v>
+        <v>50.73</v>
       </c>
       <c r="E208" s="4" t="n">
-        <v>47.28</v>
+        <v>38.46</v>
       </c>
       <c r="F208" s="4" t="n">
-        <v>43.08</v>
+        <v>30.54</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>GRWRHITECH</t>
+          <t>ARVINDFASN</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -6130,22 +6010,22 @@
         </is>
       </c>
       <c r="C209" s="4" t="n">
-        <v>3910</v>
+        <v>449.75</v>
       </c>
       <c r="D209" s="4" t="n">
-        <v>54.89</v>
+        <v>50.72</v>
       </c>
       <c r="E209" s="4" t="n">
-        <v>56.15</v>
+        <v>47.92</v>
       </c>
       <c r="F209" s="4" t="n">
-        <v>55.39</v>
+        <v>49.14</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>HEMIPROP</t>
+          <t>JKLAKSHMI</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -6154,22 +6034,22 @@
         </is>
       </c>
       <c r="C210" s="4" t="n">
-        <v>132.26</v>
+        <v>640.1</v>
       </c>
       <c r="D210" s="4" t="n">
-        <v>54.83</v>
+        <v>50.61</v>
       </c>
       <c r="E210" s="4" t="n">
-        <v>48.13</v>
+        <v>39.4</v>
       </c>
       <c r="F210" s="4" t="n">
-        <v>47.09</v>
+        <v>42.48</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>ACUTAAS</t>
+          <t>CMSINFO</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -6178,22 +6058,22 @@
         </is>
       </c>
       <c r="C211" s="4" t="n">
-        <v>2370.5</v>
+        <v>302.15</v>
       </c>
       <c r="D211" s="4" t="n">
-        <v>54.72</v>
+        <v>50.61</v>
       </c>
       <c r="E211" s="4" t="n">
-        <v>63.24</v>
+        <v>40.61</v>
       </c>
       <c r="F211" s="4" t="n">
-        <v/>
+        <v>39.05</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>SUDARSCHEM</t>
+          <t>BECTORFOOD</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -6202,22 +6082,22 @@
         </is>
       </c>
       <c r="C212" s="4" t="n">
-        <v>846.55</v>
+        <v>194.55</v>
       </c>
       <c r="D212" s="4" t="n">
-        <v>54.6</v>
+        <v>50.28</v>
       </c>
       <c r="E212" s="4" t="n">
-        <v>42.23</v>
+        <v>35.81</v>
       </c>
       <c r="F212" s="4" t="n">
-        <v>45.84</v>
+        <v>40.61</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>THYROCARE</t>
+          <t>MSTCLTD</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -6226,22 +6106,22 @@
         </is>
       </c>
       <c r="C213" s="4" t="n">
-        <v>391</v>
+        <v>433.4</v>
       </c>
       <c r="D213" s="4" t="n">
-        <v>54.52</v>
+        <v>50.15</v>
       </c>
       <c r="E213" s="4" t="n">
-        <v>47.33</v>
+        <v>45.71</v>
       </c>
       <c r="F213" s="4" t="n">
-        <v>55.94</v>
+        <v>45.56</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>PGIL</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -6250,22 +6130,22 @@
         </is>
       </c>
       <c r="C214" s="4" t="n">
-        <v>688.5</v>
+        <v>1543.7</v>
       </c>
       <c r="D214" s="4" t="n">
-        <v>54.33</v>
+        <v>50.07</v>
       </c>
       <c r="E214" s="4" t="n">
-        <v>46.5</v>
+        <v>51.4</v>
       </c>
       <c r="F214" s="4" t="n">
-        <v>50.97</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>CSBBANK</t>
+          <t>GARFIBRES</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -6274,22 +6154,22 @@
         </is>
       </c>
       <c r="C215" s="4" t="n">
-        <v>396.35</v>
+        <v>627.1</v>
       </c>
       <c r="D215" s="4" t="n">
-        <v>54.24</v>
+        <v>49.9</v>
       </c>
       <c r="E215" s="4" t="n">
-        <v>50.63</v>
+        <v>42.78</v>
       </c>
       <c r="F215" s="4" t="n">
-        <v>54.36</v>
+        <v>40.28</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>GPPL</t>
+          <t>BALUFORGE</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -6298,22 +6178,22 @@
         </is>
       </c>
       <c r="C216" s="4" t="n">
-        <v>158.6</v>
+        <v>460.1</v>
       </c>
       <c r="D216" s="4" t="n">
-        <v>54.11</v>
+        <v>49.78</v>
       </c>
       <c r="E216" s="4" t="n">
-        <v>48.31</v>
+        <v>43.21</v>
       </c>
       <c r="F216" s="4" t="n">
-        <v>51.59</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>UJJIVANSFB</t>
+          <t>VARROC</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -6322,22 +6202,22 @@
         </is>
       </c>
       <c r="C217" s="4" t="n">
-        <v>58.24</v>
+        <v>512.25</v>
       </c>
       <c r="D217" s="4" t="n">
-        <v>53.98</v>
+        <v>49.16</v>
       </c>
       <c r="E217" s="4" t="n">
-        <v>56.57</v>
+        <v>41.78</v>
       </c>
       <c r="F217" s="4" t="n">
-        <v>59.41</v>
+        <v>48.88</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>SANOFI</t>
+          <t>TEAMLEASE</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -6346,22 +6226,22 @@
         </is>
       </c>
       <c r="C218" s="4" t="n">
-        <v>3550.8</v>
+        <v>1208.6</v>
       </c>
       <c r="D218" s="4" t="n">
-        <v>53.59</v>
+        <v>49.11</v>
       </c>
       <c r="E218" s="4" t="n">
-        <v>32.67</v>
+        <v>33.02</v>
       </c>
       <c r="F218" s="4" t="n">
-        <v>32.59</v>
+        <v>30.96</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>GMMPFAUDLR</t>
+          <t>UJJIVANSFB</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -6370,22 +6250,22 @@
         </is>
       </c>
       <c r="C219" s="4" t="n">
-        <v>910.45</v>
+        <v>56.79</v>
       </c>
       <c r="D219" s="4" t="n">
-        <v>53.46</v>
+        <v>48.94</v>
       </c>
       <c r="E219" s="4" t="n">
-        <v>42.47</v>
+        <v>52.86</v>
       </c>
       <c r="F219" s="4" t="n">
-        <v>41.23</v>
+        <v>58.48</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>JAMNAAUTO</t>
+          <t>RELIGARE</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -6394,22 +6274,22 @@
         </is>
       </c>
       <c r="C220" s="4" t="n">
-        <v>126.49</v>
+        <v>220.48</v>
       </c>
       <c r="D220" s="4" t="n">
-        <v>53.43</v>
+        <v>48.81</v>
       </c>
       <c r="E220" s="4" t="n">
-        <v>56.16</v>
+        <v>43.47</v>
       </c>
       <c r="F220" s="4" t="n">
-        <v>56.43</v>
+        <v>48.34</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>CELLO</t>
+          <t>WESTLIFE</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -6418,22 +6298,22 @@
         </is>
       </c>
       <c r="C221" s="4" t="n">
-        <v>426.8</v>
+        <v>462.75</v>
       </c>
       <c r="D221" s="4" t="n">
-        <v>53.39</v>
+        <v>48.67</v>
       </c>
       <c r="E221" s="4" t="n">
-        <v>36.87</v>
+        <v>36.01</v>
       </c>
       <c r="F221" s="4" t="n">
-        <v>32.91</v>
+        <v>30.66</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>HCG</t>
+          <t>JAMNAAUTO</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -6442,22 +6322,22 @@
         </is>
       </c>
       <c r="C222" s="4" t="n">
-        <v>562.7</v>
+        <v>122.99</v>
       </c>
       <c r="D222" s="4" t="n">
-        <v>53.31</v>
+        <v>48.65</v>
       </c>
       <c r="E222" s="4" t="n">
-        <v>40.9</v>
+        <v>52.05</v>
       </c>
       <c r="F222" s="4" t="n">
-        <v>53.65</v>
+        <v>55.43</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>GULFOILLUB</t>
+          <t>GPPL</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -6466,22 +6346,22 @@
         </is>
       </c>
       <c r="C223" s="4" t="n">
-        <v>965.25</v>
+        <v>154.56</v>
       </c>
       <c r="D223" s="4" t="n">
-        <v>53.12</v>
+        <v>48.65</v>
       </c>
       <c r="E223" s="4" t="n">
-        <v>40.1</v>
+        <v>44.37</v>
       </c>
       <c r="F223" s="4" t="n">
-        <v>47.45</v>
+        <v>50.47</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>ORCHPHARMA</t>
+          <t>CSBBANK</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -6490,22 +6370,22 @@
         </is>
       </c>
       <c r="C224" s="4" t="n">
-        <v>562.95</v>
+        <v>382.65</v>
       </c>
       <c r="D224" s="4" t="n">
-        <v>53.02</v>
+        <v>48.47</v>
       </c>
       <c r="E224" s="4" t="n">
-        <v>38.83</v>
+        <v>47.37</v>
       </c>
       <c r="F224" s="4" t="n">
-        <v>41.52</v>
+        <v>52.8</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>INDIGOPNTS</t>
+          <t>DATAMATICS</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -6514,22 +6394,22 @@
         </is>
       </c>
       <c r="C225" s="4" t="n">
-        <v>829.8</v>
+        <v>707.4</v>
       </c>
       <c r="D225" s="4" t="n">
-        <v>52.92</v>
+        <v>48.2</v>
       </c>
       <c r="E225" s="4" t="n">
-        <v>37.56</v>
+        <v>44.76</v>
       </c>
       <c r="F225" s="4" t="n">
-        <v>38.63</v>
+        <v>51.25</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>ELECTCAST</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -6538,22 +6418,22 @@
         </is>
       </c>
       <c r="C226" s="4" t="n">
-        <v>79.54000000000001</v>
+        <v>1113.8</v>
       </c>
       <c r="D226" s="4" t="n">
-        <v>52.66</v>
+        <v>48.02</v>
       </c>
       <c r="E226" s="4" t="n">
-        <v>51.03</v>
+        <v>61.66</v>
       </c>
       <c r="F226" s="4" t="n">
-        <v>43.17</v>
+        <v>67.22</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>MANINFRA</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -6562,22 +6442,22 @@
         </is>
       </c>
       <c r="C227" s="4" t="n">
-        <v>95.75</v>
+        <v>428.65</v>
       </c>
       <c r="D227" s="4" t="n">
-        <v>52.19</v>
+        <v>47.78</v>
       </c>
       <c r="E227" s="4" t="n">
-        <v>35.83</v>
+        <v>44.96</v>
       </c>
       <c r="F227" s="4" t="n">
-        <v>37.49</v>
+        <v>50.34</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>DODLA</t>
+          <t>SFL</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -6586,22 +6466,22 @@
         </is>
       </c>
       <c r="C228" s="4" t="n">
-        <v>1070.9</v>
+        <v>523.25</v>
       </c>
       <c r="D228" s="4" t="n">
-        <v>51.92</v>
+        <v>47.74</v>
       </c>
       <c r="E228" s="4" t="n">
-        <v>42.6</v>
+        <v>40.49</v>
       </c>
       <c r="F228" s="4" t="n">
-        <v>48.51</v>
+        <v>36.24</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>GRINFRA</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -6610,22 +6490,22 @@
         </is>
       </c>
       <c r="C229" s="4" t="n">
-        <v>883</v>
+        <v>3799.3</v>
       </c>
       <c r="D229" s="4" t="n">
-        <v>51.76</v>
+        <v>47.64</v>
       </c>
       <c r="E229" s="4" t="n">
-        <v>39.58</v>
+        <v>58.02</v>
       </c>
       <c r="F229" s="4" t="n">
-        <v>37.86</v>
+        <v>71.59999999999999</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>DHANUKA</t>
+          <t>KITEX</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -6634,22 +6514,22 @@
         </is>
       </c>
       <c r="C230" s="4" t="n">
-        <v>1006.35</v>
+        <v>163.63</v>
       </c>
       <c r="D230" s="4" t="n">
-        <v>51.65</v>
+        <v>47.34</v>
       </c>
       <c r="E230" s="4" t="n">
-        <v>36.21</v>
+        <v>43.64</v>
       </c>
       <c r="F230" s="4" t="n">
-        <v>41.71</v>
+        <v>49.47</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>KITEX</t>
+          <t>CIEINDIA</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -6658,22 +6538,22 @@
         </is>
       </c>
       <c r="C231" s="4" t="n">
-        <v>168</v>
+        <v>457.2</v>
       </c>
       <c r="D231" s="4" t="n">
-        <v>51.63</v>
+        <v>46.94</v>
       </c>
       <c r="E231" s="4" t="n">
-        <v>46.38</v>
+        <v>55.55</v>
       </c>
       <c r="F231" s="4" t="n">
-        <v>50.13</v>
+        <v>54.57</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>RELIGARE</t>
+          <t>BIRLACORPN</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -6682,22 +6562,22 @@
         </is>
       </c>
       <c r="C232" s="4" t="n">
-        <v>223.29</v>
+        <v>907.9</v>
       </c>
       <c r="D232" s="4" t="n">
-        <v>51.55</v>
+        <v>46.88</v>
       </c>
       <c r="E232" s="4" t="n">
-        <v>44.92</v>
+        <v>40.6</v>
       </c>
       <c r="F232" s="4" t="n">
-        <v>48.93</v>
+        <v>38.75</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>TEGA</t>
+          <t>GRINFRA</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -6706,22 +6586,22 @@
         </is>
       </c>
       <c r="C233" s="4" t="n">
-        <v>1725.6</v>
+        <v>866.45</v>
       </c>
       <c r="D233" s="4" t="n">
-        <v>51.1</v>
+        <v>46.72</v>
       </c>
       <c r="E233" s="4" t="n">
-        <v>46.65</v>
+        <v>36.11</v>
       </c>
       <c r="F233" s="4" t="n">
-        <v>54.53</v>
+        <v>37.03</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>IXIGO</t>
+          <t>JISLJALEQS</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -6730,22 +6610,22 @@
         </is>
       </c>
       <c r="C234" s="4" t="n">
-        <v>176.16</v>
+        <v>31.36</v>
       </c>
       <c r="D234" s="4" t="n">
-        <v>51.04</v>
+        <v>46.3</v>
       </c>
       <c r="E234" s="4" t="n">
-        <v>41.21</v>
+        <v>33.87</v>
       </c>
       <c r="F234" s="4" t="n">
-        <v>44.87</v>
+        <v>35.82</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>JISLJALEQS</t>
+          <t>HEMIPROP</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -6754,22 +6634,22 @@
         </is>
       </c>
       <c r="C235" s="4" t="n">
-        <v>32.4</v>
+        <v>125.49</v>
       </c>
       <c r="D235" s="4" t="n">
-        <v>50.96</v>
+        <v>46.22</v>
       </c>
       <c r="E235" s="4" t="n">
-        <v>36.58</v>
+        <v>44.13</v>
       </c>
       <c r="F235" s="4" t="n">
-        <v>36.83</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>CARTRADE</t>
+          <t>TEGA</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -6778,22 +6658,22 @@
         </is>
       </c>
       <c r="C236" s="4" t="n">
-        <v>1820.5</v>
+        <v>1680.1</v>
       </c>
       <c r="D236" s="4" t="n">
-        <v>50.94</v>
+        <v>45.82</v>
       </c>
       <c r="E236" s="4" t="n">
-        <v>40.89</v>
+        <v>42.79</v>
       </c>
       <c r="F236" s="4" t="n">
-        <v>51.09</v>
+        <v>53.19</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>CCAVENUE</t>
+          <t>SANOFI</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -6802,22 +6682,22 @@
         </is>
       </c>
       <c r="C237" s="4" t="n">
-        <v>15.08</v>
+        <v>3427.6</v>
       </c>
       <c r="D237" s="4" t="n">
-        <v>50.6</v>
+        <v>45.67</v>
       </c>
       <c r="E237" s="4" t="n">
-        <v/>
+        <v>30.76</v>
       </c>
       <c r="F237" s="4" t="n">
-        <v/>
+        <v>31.54</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>EUREKAFORB</t>
+          <t>AURIONPRO</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -6826,22 +6706,22 @@
         </is>
       </c>
       <c r="C238" s="4" t="n">
-        <v>473.95</v>
+        <v>831.45</v>
       </c>
       <c r="D238" s="4" t="n">
-        <v>50.04</v>
+        <v>45.1</v>
       </c>
       <c r="E238" s="4" t="n">
-        <v>41.74</v>
+        <v>37.8</v>
       </c>
       <c r="F238" s="4" t="n">
-        <v>41.66</v>
+        <v>41.03</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>JUSTDIAL</t>
+          <t>EMBDL</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
@@ -6850,22 +6730,22 @@
         </is>
       </c>
       <c r="C239" s="4" t="n">
-        <v>547.25</v>
+        <v>47.7</v>
       </c>
       <c r="D239" s="4" t="n">
-        <v>49.85</v>
+        <v>44.95</v>
       </c>
       <c r="E239" s="4" t="n">
-        <v>34.68</v>
+        <v>34.64</v>
       </c>
       <c r="F239" s="4" t="n">
-        <v>36.19</v>
+        <v>31.34</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>V2RETAIL</t>
+          <t>KNRCON</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -6874,22 +6754,22 @@
         </is>
       </c>
       <c r="C240" s="4" t="n">
-        <v>193.75</v>
+        <v>117.93</v>
       </c>
       <c r="D240" s="4" t="n">
-        <v>49.17</v>
+        <v>44.4</v>
       </c>
       <c r="E240" s="4" t="n">
-        <v>45.82</v>
+        <v>35.56</v>
       </c>
       <c r="F240" s="4" t="n">
-        <v>60.35</v>
+        <v>31.76</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>KNRCON</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
@@ -6898,22 +6778,22 @@
         </is>
       </c>
       <c r="C241" s="4" t="n">
-        <v>121.32</v>
+        <v>97.13</v>
       </c>
       <c r="D241" s="4" t="n">
-        <v>49</v>
+        <v>43.76</v>
       </c>
       <c r="E241" s="4" t="n">
-        <v>37.8</v>
+        <v>36.77</v>
       </c>
       <c r="F241" s="4" t="n">
-        <v>32.61</v>
+        <v>37.97</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>SUNTECK</t>
+          <t>RAYMONDLSL</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -6922,22 +6802,22 @@
         </is>
       </c>
       <c r="C242" s="4" t="n">
-        <v>323.65</v>
+        <v>779.7</v>
       </c>
       <c r="D242" s="4" t="n">
-        <v>48.79</v>
+        <v>43.71</v>
       </c>
       <c r="E242" s="4" t="n">
-        <v>41.12</v>
+        <v>36.76</v>
       </c>
       <c r="F242" s="4" t="n">
-        <v>41.06</v>
+        <v>21.97</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>BECTORFOOD</t>
+          <t>IXIGO</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -6946,22 +6826,22 @@
         </is>
       </c>
       <c r="C243" s="4" t="n">
-        <v>190.38</v>
+        <v>166.7</v>
       </c>
       <c r="D243" s="4" t="n">
-        <v>48.69</v>
+        <v>43.04</v>
       </c>
       <c r="E243" s="4" t="n">
-        <v>34.19</v>
+        <v>38.2</v>
       </c>
       <c r="F243" s="4" t="n">
-        <v>39.67</v>
+        <v>42.61</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>WESTLIFE</t>
+          <t>JUSTDIAL</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -6970,22 +6850,22 @@
         </is>
       </c>
       <c r="C244" s="4" t="n">
-        <v>458.15</v>
+        <v>527.4</v>
       </c>
       <c r="D244" s="4" t="n">
-        <v>48.05</v>
+        <v>42.69</v>
       </c>
       <c r="E244" s="4" t="n">
-        <v>36.27</v>
+        <v>32.42</v>
       </c>
       <c r="F244" s="4" t="n">
-        <v>30.39</v>
+        <v>34.79</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>RAYMONDLSL</t>
+          <t>VINATIORGA</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
@@ -6994,22 +6874,22 @@
         </is>
       </c>
       <c r="C245" s="4" t="n">
-        <v>796.9</v>
+        <v>1280.6</v>
       </c>
       <c r="D245" s="4" t="n">
-        <v>47.36</v>
+        <v>42.44</v>
       </c>
       <c r="E245" s="4" t="n">
-        <v>38.15</v>
+        <v>28.15</v>
       </c>
       <c r="F245" s="4" t="n">
-        <v>23.11</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>SAFARI</t>
+          <t>CARTRADE</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -7018,22 +6898,22 @@
         </is>
       </c>
       <c r="C246" s="4" t="n">
-        <v>1550</v>
+        <v>1694.3</v>
       </c>
       <c r="D246" s="4" t="n">
-        <v>46.25</v>
+        <v>41.76</v>
       </c>
       <c r="E246" s="4" t="n">
-        <v>35.36</v>
+        <v>36.97</v>
       </c>
       <c r="F246" s="4" t="n">
-        <v>41.14</v>
+        <v>48.84</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>EMBDL</t>
+          <t>MAHLIFE</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
@@ -7042,22 +6922,22 @@
         </is>
       </c>
       <c r="C247" s="4" t="n">
-        <v>47.7</v>
+        <v>317.9</v>
       </c>
       <c r="D247" s="4" t="n">
-        <v>44.95</v>
+        <v>41.27</v>
       </c>
       <c r="E247" s="4" t="n">
-        <v>36.19</v>
+        <v>37.6</v>
       </c>
       <c r="F247" s="4" t="n">
-        <v>31.34</v>
+        <v>39.79</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>VIPIND</t>
+          <t>CIGNITITEC</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -7066,22 +6946,22 @@
         </is>
       </c>
       <c r="C248" s="4" t="n">
-        <v>320.2</v>
+        <v>1136.2</v>
       </c>
       <c r="D248" s="4" t="n">
-        <v>44.59</v>
+        <v>39.67</v>
       </c>
       <c r="E248" s="4" t="n">
-        <v>36.88</v>
+        <v>36.18</v>
       </c>
       <c r="F248" s="4" t="n">
-        <v>37.84</v>
+        <v>43.17</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>MAHLIFE</t>
+          <t>CCAVENUE</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
@@ -7090,22 +6970,22 @@
         </is>
       </c>
       <c r="C249" s="4" t="n">
-        <v>318.8</v>
+        <v>13.98</v>
       </c>
       <c r="D249" s="4" t="n">
-        <v>40.9</v>
+        <v>39.25</v>
       </c>
       <c r="E249" s="4" t="n">
-        <v>39.34</v>
+        <v/>
       </c>
       <c r="F249" s="4" t="n">
-        <v>39.92</v>
+        <v/>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>VINATIORGA</t>
+          <t>SAFARI</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
@@ -7114,22 +6994,22 @@
         </is>
       </c>
       <c r="C250" s="4" t="n">
-        <v>1275</v>
+        <v>1470</v>
       </c>
       <c r="D250" s="4" t="n">
-        <v>40.12</v>
+        <v>38.7</v>
       </c>
       <c r="E250" s="4" t="n">
-        <v>28.81</v>
+        <v>31.94</v>
       </c>
       <c r="F250" s="4" t="n">
-        <v>34.66</v>
+        <v>39.07</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>SHAILY</t>
+          <t>VIPIND</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
@@ -7138,16 +7018,16 @@
         </is>
       </c>
       <c r="C251" s="4" t="n">
-        <v>1876.8</v>
+        <v>299.3</v>
       </c>
       <c r="D251" s="4" t="n">
-        <v>38.29</v>
+        <v>34.16</v>
       </c>
       <c r="E251" s="4" t="n">
-        <v>42.9</v>
+        <v>32.61</v>
       </c>
       <c r="F251" s="4" t="n">
-        <v>55.95</v>
+        <v>34.9</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Micro250_stocks.xlsx
+++ b/reports/Micro250_stocks.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -537,7 +537,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>MTARTECH</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -546,37 +546,37 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>1112.85</v>
+        <v>6457.1</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>80.06</v>
+        <v>85.84999999999999</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>74.89</v>
+        <v>88.94</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>81.18000000000001</v>
+        <v>84.72</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>21.69</v>
+        <v>24.19</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>763.35</v>
+        <v>3213.18</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>720.3</v>
+        <v>2955.17</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>1185525</v>
+        <v>690324</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>17384</v>
+        <v>20547</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>STAR</t>
+          <t>PRIVISCL</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -585,37 +585,37 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>1066.25</v>
+        <v>3360.1</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>77.09999999999999</v>
+        <v>75.44</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>68.33</v>
+        <v>66.92</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>59.63</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>42.36</v>
+        <v>22.84</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>901.05</v>
+        <v>2843.94</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>893.61</v>
+        <v>2749.55</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>298669</v>
+        <v>104134</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>9828</v>
+        <v>13104</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>MTARTECH</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -624,37 +624,37 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>5139.2</v>
+        <v>268.61</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>73.45</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>82.94</v>
+        <v>78.16</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>80.59999999999999</v>
+        <v>67.91</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>20.83</v>
+        <v>27.2</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>3077.88</v>
+        <v>209.44</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>2844.07</v>
+        <v>205.24</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>559706</v>
+        <v>3838377</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>15808</v>
+        <v>10152</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>MEDPLUS</t>
+          <t>SKYGOLD</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -663,37 +663,37 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>903.65</v>
+        <v>453.9</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>67.02</v>
+        <v>72.2</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>62.92</v>
+        <v>69.42</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>58.41</v>
+        <v>66.89</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>21.58</v>
+        <v>20.79</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>830.09</v>
+        <v>349.23</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>824.33</v>
+        <v>342.51</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>144845</v>
+        <v>895727</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>10844</v>
+        <v>7002</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>ANURAS</t>
+          <t>ARVIND</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -702,37 +702,37 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1341</v>
+        <v>398.55</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>64.79000000000001</v>
+        <v>64.39</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>63.37</v>
+        <v>63.78</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>69.64</v>
+        <v>62.66</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>27.53</v>
+        <v>28.47</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1219.62</v>
+        <v>347.02</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>1183.7</v>
+        <v>344.27</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>214656</v>
+        <v>331319</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>15267</v>
+        <v>10415</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>IMFA</t>
+          <t>GAEL</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -741,37 +741,37 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1504.6</v>
+        <v>155.75</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>63.13</v>
+        <v>61.08</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>62.65</v>
+        <v>65.78</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>69.83</v>
+        <v>62.2</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>27.41</v>
+        <v>40.8</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1226.82</v>
+        <v>131.43</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1170.92</v>
+        <v>128.76</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>172943</v>
+        <v>926648</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>8118</v>
+        <v>7132</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>SHRIPISTON</t>
+          <t>ANURAS</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -780,37 +780,37 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>3478.7</v>
+        <v>1343.8</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>57.64</v>
+        <v>61.04</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>60.48</v>
+        <v>63.5</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>71.75</v>
+        <v>69.73999999999999</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>30.78</v>
+        <v>21.03</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2944.01</v>
+        <v>1224.86</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2847.39</v>
+        <v>1189.05</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>127033</v>
+        <v>218109</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>15324</v>
+        <v>15283</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>STAR</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -819,37 +819,37 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>242.04</v>
+        <v>1036.8</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>57.5</v>
+        <v>60.13</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>70.67</v>
+        <v>63.91</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>63.6</v>
+        <v>58.61</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>37.25</v>
+        <v>27.69</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>206.45</v>
+        <v>909.3200000000001</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>202.79</v>
+        <v>900.24</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>4248753</v>
+        <v>303173</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>9154</v>
+        <v>9562</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>GAEL</t>
+          <t>SHRIPISTON</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -858,37 +858,37 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>151.37</v>
+        <v>3491.1</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>57.44</v>
+        <v>56.42</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>63.73</v>
+        <v>60.9</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>60.79</v>
+        <v>71.87</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>39.85</v>
+        <v>34.66</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>130.28</v>
+        <v>2972.56</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>127.81</v>
+        <v>2872.39</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>880858</v>
+        <v>129049</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>6943</v>
+        <v>15431</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ARVIND</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -897,37 +897,37 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>382.5</v>
+        <v>1171.8</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>56.13</v>
+        <v>56.29</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>60.5</v>
+        <v>65.67</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>60.93</v>
+        <v>69.7</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>26.92</v>
+        <v>42.72</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>344.44</v>
+        <v>973.97</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>342.19</v>
+        <v>944.1</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>384882</v>
+        <v>417200</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>10026</v>
+        <v>15582</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>IMFA</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -936,31 +936,70 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1113.8</v>
+        <v>1502.6</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>48.02</v>
+        <v>55.61</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>61.66</v>
+        <v>62.35</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>67.22</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>24.26</v>
+        <v>24.69</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>963.46</v>
+        <v>1245.08</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>935.13</v>
+        <v>1187.11</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>442084</v>
+        <v>224153</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>14778</v>
+        <v>8093</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>THANGAMAYL</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>3955.8</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>53.51</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>60.22</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>72.79000000000001</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>36.94</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>3301.64</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>3114.43</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>110315</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>12284</v>
       </c>
     </row>
   </sheetData>
@@ -976,6 +1015,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1033,7 +1073,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>WEBELSOLAR</t>
+          <t>MTARTECH</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -1042,22 +1082,22 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>110.85</v>
+        <v>6457.1</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>81.66</v>
+        <v>85.84999999999999</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>62.31</v>
+        <v>88.94</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>54.9</v>
+        <v>84.72</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>BBL</t>
+          <t>CEMPRO</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -1066,22 +1106,22 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>3060.7</v>
+        <v>815.25</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>81.27</v>
+        <v>80.61</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>60.54</v>
+        <v>67.3</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>52.85</v>
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>VOLTAMP</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -1090,22 +1130,22 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>1112.85</v>
+        <v>11742</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>80.06</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>74.89</v>
+        <v>77.28</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>81.18000000000001</v>
+        <v>64.09</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>AZAD</t>
+          <t>KIRLPNU</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -1114,22 +1154,22 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>2090.2</v>
+        <v>1503.3</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>79.43000000000001</v>
+        <v>79.34</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>70.58</v>
+        <v>75.17</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>63.76</v>
+        <v>62.41</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>TIPSMUSIC</t>
+          <t>TDPOWERSYS</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -1138,22 +1178,22 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>665.15</v>
+        <v>1152.7</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>77.55</v>
+        <v>78.83</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>67.98999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>60.3</v>
+        <v>81.95</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>STAR</t>
+          <t>INGERRAND</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1162,22 +1202,22 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1066.25</v>
+        <v>4417.7</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>77.09999999999999</v>
+        <v>78.69</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>68.33</v>
+        <v>67.45999999999999</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>59.63</v>
+        <v>61.53</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>CEIGALL</t>
+          <t>MANINFRA</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1186,22 +1226,22 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>326.2</v>
+        <v>120.35</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>76.42</v>
+        <v>77.15000000000001</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>71.84</v>
+        <v>53.45</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>58.47</v>
+        <v>44.27</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>DYNAMATECH</t>
+          <t>CEIGALL</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -1210,22 +1250,22 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>11829.5</v>
+        <v>338.6</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>74.81999999999999</v>
+        <v>76.01000000000001</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>66.98999999999999</v>
+        <v>73.70999999999999</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>71.66</v>
+        <v>61.28</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>LUXIND</t>
+          <t>ADVENZYMES</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1234,22 +1274,22 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1654.1</v>
+        <v>347.7</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>74.7</v>
+        <v>75.69</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>74.95</v>
+        <v>63.27</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>56.21</v>
+        <v>53.81</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>VOLTAMP</t>
+          <t>PRIVISCL</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -1258,22 +1298,22 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>10768.5</v>
+        <v>3360.1</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>74.31</v>
+        <v>75.44</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>72.95</v>
+        <v>66.92</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>61.27</v>
+        <v>69.93000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>MTARTECH</t>
+          <t>AZAD</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1282,22 +1322,22 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>5139.2</v>
+        <v>2164.9</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>73.45</v>
+        <v>74.93000000000001</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>82.94</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>80.59999999999999</v>
+        <v>64.95</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>EPIGRAL</t>
+          <t>KSL</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1306,22 +1346,22 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1202.85</v>
+        <v>849.7</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>72.98999999999999</v>
+        <v>74.88</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>51.38</v>
+        <v>63.03</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>44.64</v>
+        <v>54.43</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>DIACABS</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1330,22 +1370,22 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>161.72</v>
+        <v>207.7</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>72.95</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>66.28</v>
+        <v>73.22</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>60.81</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>KIRLPNU</t>
+          <t>BALAMINES</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1354,22 +1394,22 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1337.4</v>
+        <v>1333.65</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>72.5</v>
+        <v>73.72</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>67.87</v>
+        <v>61.99</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>58.15</v>
+        <v>44.02</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>MANINFRA</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1378,22 +1418,22 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>113.53</v>
+        <v>3096.8</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>72.42</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>49.22</v>
+        <v>61.8</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>42.54</v>
+        <v>53.27</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>STYRENIX</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1402,22 +1442,22 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2331.4</v>
+        <v>268.61</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>72.31999999999999</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>60.41</v>
+        <v>78.16</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>54.98</v>
+        <v>67.91</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>PRUDENT</t>
+          <t>HCC</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1426,22 +1466,22 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>2804.9</v>
+        <v>22.04</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>72.22</v>
+        <v>73.22</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>61.03</v>
+        <v>56.37</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>59.41</v>
+        <v>46.16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>AHLUCONT</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1450,22 +1490,22 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>884.4</v>
+        <v>294.8</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>72.06999999999999</v>
+        <v>72.66</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>53.68</v>
+        <v>87.06999999999999</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>49.93</v>
+        <v>79.12</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>INGERRAND</t>
+          <t>EMIL</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1474,22 +1514,22 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>4216</v>
+        <v>124.34</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>71.53</v>
+        <v>72.48999999999999</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>63.63</v>
+        <v>62.21</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>59.42</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>BALAMINES</t>
+          <t>SKYGOLD</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1498,22 +1538,22 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1250.6</v>
+        <v>453.9</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>71.20999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>56.4</v>
+        <v>69.42</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>41.88</v>
+        <v>66.89</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>SHAILY</t>
+          <t>INDIAGLYCO</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1522,22 +1562,22 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2503.1</v>
+        <v>1042.05</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>71.03</v>
+        <v>71.95</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>60.02</v>
+        <v>61.75</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>66.7</v>
+        <v>62.17</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>ISGEC</t>
+          <t>SKIPPER</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1546,22 +1586,22 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1055.1</v>
+        <v>478.45</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>71.01000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>65.95999999999999</v>
+        <v>62.01</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>52.99</v>
+        <v>57.14</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>SKIPPER</t>
+          <t>CYIENTDLM</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1570,22 +1610,22 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>454.15</v>
+        <v>393.1</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>70.59999999999999</v>
+        <v>70.73</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>58.67</v>
+        <v>55.95</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>55.23</v>
+        <v>42.11</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>NEOGEN</t>
+          <t>ISGEC</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1594,22 +1634,22 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1634.5</v>
+        <v>1088.95</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>70.44</v>
+        <v>70.62</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>62.45</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>53.22</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>PNGJL</t>
+          <t>AHLUCONT</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1618,22 +1658,22 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>666</v>
+        <v>891</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>70.33</v>
+        <v>70.31</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>65.34999999999999</v>
+        <v>54.56</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>56.28</v>
+        <v>50.18</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>SHAILY</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1642,22 +1682,22 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1247.7</v>
+        <v>2532.6</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>70.25</v>
+        <v>69.34</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>71.54000000000001</v>
+        <v>60.68</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>67.73</v>
+        <v>67.04000000000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENT</t>
+          <t>EPIGRAL</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1666,22 +1706,22 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>67.53</v>
+        <v>1215.65</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>69.62</v>
+        <v>69.23</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>59.59</v>
+        <v>51.02</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>56.13</v>
+        <v>44.96</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>CYIENTDLM</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1690,22 +1730,22 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>373</v>
+        <v>1295.35</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>69.54000000000001</v>
+        <v>69.11</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>51.75</v>
+        <v>73.13</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>40.19</v>
+        <v>68.92</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>RATNAMANI</t>
+          <t>BALUFORGE</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1714,22 +1754,22 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2605.8</v>
+        <v>541.4</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>69.27</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>59.99</v>
+        <v>54.25</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>49.97</v>
+        <v>50.81</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>PRIVISCL</t>
+          <t>WEBELSOLAR</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1738,22 +1778,22 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>3232.6</v>
+        <v>110.66</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>69.18000000000001</v>
+        <v>68.78</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>63.82</v>
+        <v>61.94</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>68.59999999999999</v>
+        <v>54.86</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>JSFB</t>
+          <t>SUNFLAG</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1762,22 +1802,22 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>459.35</v>
+        <v>292.61</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>68.95999999999999</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>63.1</v>
+        <v>63.25</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>51.47</v>
+        <v>58.23</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENGG</t>
+          <t>YATHARTH</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1786,22 +1826,22 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>57.43</v>
+        <v>820</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>68.95999999999999</v>
+        <v>68.36</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>57.4</v>
+        <v>63.75</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>50.01</v>
+        <v>63.04</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>ANUP</t>
+          <t>KSCL</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1810,22 +1850,22 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2108.8</v>
+        <v>965.35</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>68.91</v>
+        <v>68.33</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>54.55</v>
+        <v>55.57</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>50.25</v>
+        <v>51.51</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>ASTRAMICRO</t>
+          <t>NEOGEN</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1834,22 +1874,22 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1123.75</v>
+        <v>1637.5</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>68.58</v>
+        <v>68.3</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>62.66</v>
+        <v>62.21</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>63.49</v>
+        <v>53.27</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>BORORENEW</t>
+          <t>PRUDENT</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1858,22 +1898,22 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>511.25</v>
+        <v>2826.1</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>68.44</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>52.03</v>
+        <v>61.72</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>50.08</v>
+        <v>59.68</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>SUNFLAG</t>
+          <t>GREENPANEL</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1882,22 +1922,22 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>287.1</v>
+        <v>228.91</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>68.36</v>
+        <v>67.92</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>62.53</v>
+        <v>51.76</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>57.62</v>
+        <v>43.12</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>KSL</t>
+          <t>TIPSMUSIC</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -1906,22 +1946,22 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>798.15</v>
+        <v>649.7</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>68.34999999999999</v>
+        <v>67.78</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>58.11</v>
+        <v>64.22</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>52.63</v>
+        <v>59.36</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>WABAG</t>
+          <t>RATNAMANI</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1930,22 +1970,22 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>1493.3</v>
+        <v>2645</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>68.20999999999999</v>
+        <v>67.67</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>64.03</v>
+        <v>61.28</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>57.62</v>
+        <v>50.72</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>STARCEMENT</t>
+          <t>GALLANTT</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -1954,22 +1994,22 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>231.75</v>
+        <v>861.85</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>68.04000000000001</v>
+        <v>67.56</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>56.91</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>55.65</v>
+        <v>70.29000000000001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>ABDL</t>
+          <t>ORCHPHARMA</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -1978,22 +2018,22 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>558.3</v>
+        <v>625.75</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>67.97</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>56.68</v>
+        <v>46.52</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>58.93</v>
+        <v>43.87</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>HCC</t>
+          <t>RBA</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -2002,22 +2042,22 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>20.05</v>
+        <v>65.36</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>67.75</v>
+        <v>67.25</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>50.72</v>
+        <v>50.54</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>44.19</v>
+        <v>38.61</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>UNIMECH</t>
+          <t>REFEX</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -2026,22 +2066,22 @@
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>994.9</v>
+        <v>263.86</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>67.70999999999999</v>
+        <v>67.23999999999999</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>56.74</v>
+        <v>50.62</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>46.29</v>
+        <v>47.06</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>WABAG</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -2050,22 +2090,22 @@
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>266.45</v>
+        <v>1509.6</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>67.34999999999999</v>
+        <v>67.14</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>84.62</v>
+        <v>64.67</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>76.87</v>
+        <v>57.99</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>GALLANTT</t>
+          <t>LLOYDSENGG</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -2074,22 +2114,22 @@
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>828.7</v>
+        <v>57.77</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>67.28</v>
+        <v>66.89</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>71.45999999999999</v>
+        <v>57.58</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>69.33</v>
+        <v>50.2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>EMUDHRA</t>
+          <t>POWERMECH</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -2098,22 +2138,22 @@
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>500.85</v>
+        <v>2481.8</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>67.03</v>
+        <v>66.84</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>45.38</v>
+        <v>58.56</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>41.78</v>
+        <v>51.65</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>MEDPLUS</t>
+          <t>LLOYDSENT</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -2122,22 +2162,22 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>903.65</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>67.02</v>
+        <v>66.63</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>62.92</v>
+        <v>59.96</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>58.41</v>
+        <v>56.57</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>SANSERA</t>
+          <t>MANORAMA</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -2146,22 +2186,22 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>2530.7</v>
+        <v>1509</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>66.56999999999999</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>70.76000000000001</v>
+        <v>59.81</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>73.08</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>EIEL</t>
+          <t>POLYPLEX</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -2170,22 +2210,22 @@
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>206.61</v>
+        <v>946.2</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>66.08</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>55.73</v>
+        <v>58.06</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>42.5</v>
+        <v>46.18</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>PARADEEP</t>
+          <t>SURYAROSNI</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -2194,22 +2234,22 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>133.67</v>
+        <v>250.12</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>66.06</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>49.14</v>
+        <v>52.94</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>51.74</v>
+        <v>48.89</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>KSCL</t>
+          <t>MIDHANI</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -2218,22 +2258,22 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>937.15</v>
+        <v>389.9</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>65.72</v>
+        <v>66.17</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>52.27</v>
+        <v>60.16</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>50.26</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>SWSOLAR</t>
+          <t>RATEGAIN</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -2242,22 +2282,22 @@
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>213.31</v>
+        <v>602.6</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>65.70999999999999</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>52.65</v>
+        <v>54.99</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>40.12</v>
+        <v>51.62</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>PRSMJOHNSN</t>
+          <t>JAIBALAJI</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -2266,22 +2306,22 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>134.3</v>
+        <v>78.29000000000001</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>65.59</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>53.08</v>
+        <v>53.82</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>46.68</v>
+        <v>43.37</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>POWERMECH</t>
+          <t>AARTIPHARM</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -2290,22 +2330,22 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>2408.5</v>
+        <v>740.25</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>65.42</v>
+        <v>64.84</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>55.63</v>
+        <v>52.98</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>50.69</v>
+        <v>53.92</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>ALLCARGO</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -2314,22 +2354,22 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>190.21</v>
+        <v>9.68</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>65.37</v>
+        <v>64.81</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>56.19</v>
+        <v>35.79</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>50.74</v>
+        <v>28.07</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>INOXGREEN</t>
+          <t>RTNPOWER</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -2338,22 +2378,22 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>176.51</v>
+        <v>10.12</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>65.33</v>
+        <v>64.77</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>50.9</v>
+        <v>56.93</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>52.73</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>PARAS</t>
+          <t>RENUKA</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -2362,22 +2402,22 @@
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>800.55</v>
+        <v>29.21</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>65.3</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>61.45</v>
+        <v>60.01</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>52.71</v>
+        <v>43.87</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>MIDHANI</t>
+          <t>ARVIND</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -2386,22 +2426,22 @@
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>375.95</v>
+        <v>398.55</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>65.26000000000001</v>
+        <v>64.39</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>57.46</v>
+        <v>63.78</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>52.59</v>
+        <v>62.66</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>PNCINFRA</t>
+          <t>INOXGREEN</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -2410,22 +2450,22 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>217.26</v>
+        <v>180.73</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>65.14</v>
+        <v>64.39</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>46.52</v>
+        <v>52.11</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>40.43</v>
+        <v>53.28</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>SHILPAMED</t>
+          <t>ASTRAMICRO</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -2434,22 +2474,22 @@
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>413.9</v>
+        <v>1125.2</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>65.05</v>
+        <v>64.36</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>64.31</v>
+        <v>63.07</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>59.51</v>
+        <v>63.54</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>AJAXENGG</t>
+          <t>ACUTAAS</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -2458,13 +2498,13 @@
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>527.75</v>
+        <v>2594.1</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>64.95</v>
+        <v>64.33</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>49.64</v>
+        <v>68.26000000000001</v>
       </c>
       <c r="F61" s="4" t="n">
         <v/>
@@ -2473,7 +2513,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>RATEGAIN</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -2482,22 +2522,22 @@
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>589.85</v>
+        <v>211.94</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>64.89</v>
+        <v>64.31</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>52.88</v>
+        <v>57.35</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>50.89</v>
+        <v>43.72</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>WELENT</t>
+          <t>VSTIND</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -2506,22 +2546,22 @@
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>505.35</v>
+        <v>258.37</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>64.84999999999999</v>
+        <v>64.17</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>54.62</v>
+        <v>57.62</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>54.64</v>
+        <v>47.14</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>ANURAS</t>
+          <t>NESCO</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -2530,22 +2570,22 @@
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>1341</v>
+        <v>1227.7</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>64.79000000000001</v>
+        <v>64.13</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>63.37</v>
+        <v>55.69</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>69.64</v>
+        <v>58.79</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>VSTIND</t>
+          <t>GRINFRA</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -2554,22 +2594,22 @@
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>256.21</v>
+        <v>937.2</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>64.22</v>
+        <v>64.05</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>56.58</v>
+        <v>45.12</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>46.71</v>
+        <v>40.45</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>KPIGREEN</t>
+          <t>AGI</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -2578,22 +2618,22 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>448.9</v>
+        <v>634</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>64.09999999999999</v>
+        <v>63.83</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>54.81</v>
+        <v>50.04</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>52.07</v>
+        <v>46.13</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>ETHOSLTD</t>
+          <t>WELENT</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -2602,22 +2642,22 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>2639.7</v>
+        <v>523.25</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>63.58</v>
+        <v>63.73</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>53.41</v>
+        <v>58.13</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>52.32</v>
+        <v>55.92</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>SKYGOLD</t>
+          <t>INNOVACAP</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -2626,22 +2666,22 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>412.55</v>
+        <v>752.05</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>63.49</v>
+        <v>63.69</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>64.09</v>
+        <v>53.85</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>64.18000000000001</v>
+        <v>51.19</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>ALIVUS</t>
+          <t>SUPRIYA</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -2650,22 +2690,22 @@
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>1050.05</v>
+        <v>694.9</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>63.18</v>
+        <v>63.61</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>67.73999999999999</v>
+        <v>55.54</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>63.55</v>
+        <v>55.9</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>IMFA</t>
+          <t>EQUITASBNK</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -2674,22 +2714,22 @@
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>1504.6</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>63.13</v>
+        <v>63.09</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>62.65</v>
+        <v>57.05</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>69.83</v>
+        <v>50.47</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>AWFIS</t>
+          <t>VESUVIUS</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -2698,22 +2738,22 @@
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>349.34</v>
+        <v>519.1</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>62.3</v>
+        <v>63.06</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>41.7</v>
+        <v>56.51</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>34.84</v>
+        <v>57.23</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>EUREKAFORB</t>
+          <t>ZYDUSWELL</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -2722,22 +2762,22 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>510.05</v>
+        <v>508.55</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>62.01</v>
+        <v>62.94</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>47.81</v>
+        <v>64.48</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>45.66</v>
+        <v>62.91</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>DIACABS</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -2746,22 +2786,22 @@
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>183.65</v>
+        <v>157.8</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>62</v>
+        <v>62.94</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>62.66</v>
+        <v>62.43</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>59.45</v>
+        <v>60.11</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>INDIASHLTR</t>
+          <t>RTNINDIA</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -2770,22 +2810,22 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>809.7</v>
+        <v>35.52</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>61.98</v>
+        <v>62.93</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>54.18</v>
+        <v>47.9</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>54.55</v>
+        <v>42</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>PRINCEPIPE</t>
+          <t>STYRENIX</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -2794,22 +2834,22 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>262.33</v>
+        <v>2260.9</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>61.9</v>
+        <v>62.79</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>50.03</v>
+        <v>56.82</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>38.41</v>
+        <v>53.68</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>JAIBALAJI</t>
+          <t>PRSMJOHNSN</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -2818,22 +2858,22 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>71.53</v>
+        <v>133.84</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>61.77</v>
+        <v>62.63</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>48.49</v>
+        <v>52.73</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>41.4</v>
+        <v>46.51</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>REFEX</t>
+          <t>DHANUKA</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -2842,22 +2882,22 @@
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>247.71</v>
+        <v>1079.65</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>61.75</v>
+        <v>62.62</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>46.1</v>
+        <v>45.04</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>45.37</v>
+        <v>44.25</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>IIFLCAPS</t>
+          <t>DYNAMATECH</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -2866,22 +2906,22 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>320.06</v>
+        <v>11568</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>61.73</v>
+        <v>62.54</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>53.5</v>
+        <v>66.2</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>52.29</v>
+        <v>70.94</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>HGINFRA</t>
+          <t>SANOFICONR</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -2890,22 +2930,22 @@
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>603.1</v>
+        <v>4763.9</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>61.2</v>
+        <v>62.44</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>42.6</v>
+        <v>56.12</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>37.79</v>
+        <v>49.99</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>DHANUKA</t>
+          <t>TRANSRAILL</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -2914,22 +2954,22 @@
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>1062.2</v>
+        <v>598.95</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>61.11</v>
+        <v>62.43</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>42.75</v>
+        <v>54.35</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>43.66</v>
+        <v>51.75</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>ENTERO</t>
+          <t>OSWALPUMPS</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -2938,22 +2978,22 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>1250.1</v>
+        <v>412.35</v>
       </c>
       <c r="D81" s="4" t="n">
-        <v>61.03</v>
+        <v>62.33</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>58.26</v>
+        <v>45.17</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>55.35</v>
+        <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>LXCHEM</t>
+          <t>GREAVESCOT</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -2962,22 +3002,22 @@
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>140.16</v>
+        <v>165.18</v>
       </c>
       <c r="D82" s="4" t="n">
-        <v>60.98</v>
+        <v>62.3</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>45.12</v>
+        <v>49.34</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>36.65</v>
+        <v>47.39</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>KRBL</t>
+          <t>GABRIEL</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -2986,22 +3026,22 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>359.9</v>
+        <v>1025.6</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>60.93</v>
+        <v>62.3</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>52.54</v>
+        <v>54.69</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>52.78</v>
+        <v>62.16</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>EQUITASBNK</t>
+          <t>PARAS</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -3010,22 +3050,22 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>65.22</v>
+        <v>794.25</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>60.9</v>
+        <v>61.87</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>55.03</v>
+        <v>60.63</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>49.57</v>
+        <v>52.46</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>IONEXCHANG</t>
+          <t>JSFB</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -3034,22 +3074,22 @@
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>397.35</v>
+        <v>458.15</v>
       </c>
       <c r="D85" s="4" t="n">
-        <v>60.7</v>
+        <v>61.77</v>
       </c>
       <c r="E85" s="4" t="n">
-        <v>55.26</v>
+        <v>62.11</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>45.58</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>RTNINDIA</t>
+          <t>BAJAJELEC</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -3058,22 +3098,22 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>34.25</v>
+        <v>396.1</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>60.67</v>
+        <v>61.68</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>45.01</v>
+        <v>41.69</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>41.18</v>
+        <v>31.22</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>DBL</t>
+          <t>AWFIS</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -3082,22 +3122,22 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>455.05</v>
+        <v>351.42</v>
       </c>
       <c r="D87" s="4" t="n">
-        <v>60.52</v>
+        <v>61.67</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>51.28</v>
+        <v>42.04</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>51.64</v>
+        <v>35.07</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>CEMPRO</t>
+          <t>SANSERA</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -3106,22 +3146,22 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>648.6</v>
+        <v>2513.6</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>60.51</v>
+        <v>61.54</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>47.74</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v/>
+        <v>72.89</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>INDIAGLYCO</t>
+          <t>DCAL</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -3130,22 +3170,22 @@
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>963.25</v>
+        <v>183.18</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>60.49</v>
+        <v>61.43</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>54.88</v>
+        <v>44.5</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>59.68</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>BORORENEW</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -3154,22 +3194,22 @@
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>270.09</v>
+        <v>501.5</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>60.45</v>
+        <v>61.39</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>52.96</v>
+        <v>50.67</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>53.57</v>
+        <v>49.42</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>OSWALPUMPS</t>
+          <t>DBL</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -3178,22 +3218,22 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>399.75</v>
+        <v>464.8</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>60.32</v>
+        <v>61.31</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>43.45</v>
+        <v>52.42</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v/>
+        <v>52.67</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>GSFC</t>
+          <t>GAEL</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -3202,22 +3242,22 @@
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>172.22</v>
+        <v>155.75</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>60.25</v>
+        <v>61.08</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>49.84</v>
+        <v>65.78</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>47.49</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>TRANSRAILL</t>
+          <t>ANURAS</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -3226,22 +3266,22 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>576</v>
+        <v>1343.8</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>60.24</v>
+        <v>61.04</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>51.41</v>
+        <v>63.5</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>50.01</v>
+        <v>69.73999999999999</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>BELRISE</t>
+          <t>STARCEMENT</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -3250,22 +3290,22 @@
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>212.76</v>
+        <v>230.29</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>60.09</v>
+        <v>60.86</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>68.62</v>
+        <v>55.65</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v/>
+        <v>55.33</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>AJAXENGG</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -3274,22 +3314,22 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>193.37</v>
+        <v>524.05</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>59.9</v>
+        <v>60.82</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>64.37</v>
+        <v>48.41</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>62.28</v>
+        <v/>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>WAAREERTL</t>
+          <t>KRBL</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -3298,22 +3338,22 @@
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>1028.15</v>
+        <v>367.15</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>59.85</v>
+        <v>60.77</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>56.01</v>
+        <v>54</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v/>
+        <v>53.5</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>RBA</t>
+          <t>SUDARSCHEM</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -3322,22 +3362,22 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>63.43</v>
+        <v>914.35</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>59.71</v>
+        <v>60.46</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>45.49</v>
+        <v>47.92</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>36.91</v>
+        <v>48.66</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>EDELWEISS</t>
+          <t>KPIGREEN</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -3346,22 +3386,22 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>119.07</v>
+        <v>447.95</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>59.63</v>
+        <v>60.38</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>57.95</v>
+        <v>53.92</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>58.79</v>
+        <v>52</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>FINEORG</t>
+          <t>OPTIEMUS</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -3370,22 +3410,22 @@
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>4851.5</v>
+        <v>415.8</v>
       </c>
       <c r="D99" s="4" t="n">
-        <v>59.58</v>
+        <v>60.29</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>59.33</v>
+        <v>46.54</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>53.32</v>
+        <v>46.96</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>HERITGFOOD</t>
+          <t>LXCHEM</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -3394,22 +3434,22 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>355.25</v>
+        <v>144.34</v>
       </c>
       <c r="D100" s="4" t="n">
-        <v>59.51</v>
+        <v>60.27</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>42.81</v>
+        <v>47.87</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>45.89</v>
+        <v>37.73</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>FDC</t>
+          <t>PNGJL</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -3418,22 +3458,22 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>366.15</v>
+        <v>653.75</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>59.45</v>
+        <v>60.25</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>45.53</v>
+        <v>61.17</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>44.24</v>
+        <v>54.86</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>IFBIND</t>
+          <t>STAR</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -3442,22 +3482,22 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>1148.55</v>
+        <v>1036.8</v>
       </c>
       <c r="D102" s="4" t="n">
-        <v>59.38</v>
+        <v>60.13</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>42.33</v>
+        <v>63.91</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>46.05</v>
+        <v>58.61</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>SYMPHONY</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -3466,22 +3506,22 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>468.45</v>
+        <v>846.8</v>
       </c>
       <c r="D103" s="4" t="n">
-        <v>59.25</v>
+        <v>60.1</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>51.63</v>
+        <v>50.31</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>45.81</v>
+        <v>43.7</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>POLYPLEX</t>
+          <t>JKIL</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -3490,22 +3530,22 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>889.65</v>
+        <v>519.9</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>59.18</v>
+        <v>60.03</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>51.37</v>
+        <v>44.83</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>43.57</v>
+        <v>43.81</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>TANLA</t>
+          <t>PNCINFRA</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -3514,22 +3554,22 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>485.8</v>
+        <v>213.87</v>
       </c>
       <c r="D105" s="4" t="n">
-        <v>58.73</v>
+        <v>60</v>
       </c>
       <c r="E105" s="4" t="n">
-        <v>47.1</v>
+        <v>44.95</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>41.74</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>MOIL</t>
+          <t>SWSOLAR</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -3538,22 +3578,22 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>319.1</v>
+        <v>208.34</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>58.65</v>
+        <v>59.98</v>
       </c>
       <c r="E106" s="4" t="n">
-        <v>50.24</v>
+        <v>50.94</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>50.08</v>
+        <v>39.55</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>SHARDACROP</t>
+          <t>ROUTE</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -3562,22 +3602,22 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>1109.65</v>
+        <v>527.15</v>
       </c>
       <c r="D107" s="4" t="n">
-        <v>58.61</v>
+        <v>59.75</v>
       </c>
       <c r="E107" s="4" t="n">
-        <v>59.04</v>
+        <v>39.18</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>61.12</v>
+        <v>29.51</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>BAJAJELEC</t>
+          <t>EMUDHRA</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -3586,22 +3626,22 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>388.6</v>
+        <v>489.4</v>
       </c>
       <c r="D108" s="4" t="n">
-        <v>58.54</v>
+        <v>59.71</v>
       </c>
       <c r="E108" s="4" t="n">
-        <v>39.09</v>
+        <v>43.06</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>30.46</v>
+        <v>40.9</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>RTNPOWER</t>
+          <t>TIMETECHNO</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -3610,22 +3650,22 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>9.48</v>
+        <v>193.01</v>
       </c>
       <c r="D109" s="4" t="n">
-        <v>58.35</v>
+        <v>59.6</v>
       </c>
       <c r="E109" s="4" t="n">
-        <v>51.09</v>
+        <v>52.77</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>47.59</v>
+        <v>54.38</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>VESUVIUS</t>
+          <t>SHILPAMED</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -3634,22 +3674,22 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>499.95</v>
+        <v>406.65</v>
       </c>
       <c r="D110" s="4" t="n">
-        <v>58.32</v>
+        <v>59.42</v>
       </c>
       <c r="E110" s="4" t="n">
-        <v>53.18</v>
+        <v>63.06</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>55.44</v>
+        <v>58.83</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>JKIL</t>
+          <t>UNIMECH</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -3658,22 +3698,22 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>515.25</v>
+        <v>1002.4</v>
       </c>
       <c r="D111" s="4" t="n">
-        <v>58.31</v>
+        <v>59.27</v>
       </c>
       <c r="E111" s="4" t="n">
-        <v>44</v>
+        <v>57.28</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>43.37</v>
+        <v>46.67</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>SURYAROSNI</t>
+          <t>INDIASHLTR</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -3682,22 +3722,22 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>235.58</v>
+        <v>809.6</v>
       </c>
       <c r="D112" s="4" t="n">
-        <v>58.26</v>
+        <v>59.06</v>
       </c>
       <c r="E112" s="4" t="n">
-        <v>47.35</v>
+        <v>54.43</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>47.06</v>
+        <v>54.54</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>AVANTIFEED</t>
+          <t>ANUP</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -3706,22 +3746,22 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>1421.1</v>
+        <v>2062.2</v>
       </c>
       <c r="D113" s="4" t="n">
-        <v>58.23</v>
+        <v>59.02</v>
       </c>
       <c r="E113" s="4" t="n">
-        <v>69.08</v>
+        <v>52.05</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>75.91</v>
+        <v>49.49</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>MAXESTATES</t>
+          <t>ICIL</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -3730,22 +3770,22 @@
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>393</v>
+        <v>277.36</v>
       </c>
       <c r="D114" s="4" t="n">
-        <v>58.21</v>
+        <v>58.96</v>
       </c>
       <c r="E114" s="4" t="n">
-        <v>46.94</v>
+        <v>52.97</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>47.15</v>
+        <v>50.02</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>OPTIEMUS</t>
+          <t>GANESHHOU</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -3754,22 +3794,22 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>402.9</v>
+        <v>665.55</v>
       </c>
       <c r="D115" s="4" t="n">
-        <v>58.11</v>
+        <v>58.72</v>
       </c>
       <c r="E115" s="4" t="n">
-        <v>43.93</v>
+        <v>42.92</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>46.21</v>
+        <v/>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>VMART</t>
+          <t>HERITGFOOD</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -3778,22 +3818,22 @@
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>617.35</v>
+        <v>358.15</v>
       </c>
       <c r="D116" s="4" t="n">
-        <v>58.1</v>
+        <v>58.68</v>
       </c>
       <c r="E116" s="4" t="n">
-        <v>46.95</v>
+        <v>43.99</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>44.98</v>
+        <v>46.21</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>TVSSCS</t>
+          <t>GANECOS</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -3802,22 +3842,22 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>114.35</v>
+        <v>1049.55</v>
       </c>
       <c r="D117" s="4" t="n">
-        <v>58.08</v>
+        <v>58.62</v>
       </c>
       <c r="E117" s="4" t="n">
-        <v>51.36</v>
+        <v>55.55</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>41.27</v>
+        <v>46.46</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>JKPAPER</t>
+          <t>NFL</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -3826,22 +3866,22 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>371.7</v>
+        <v>77.91</v>
       </c>
       <c r="D118" s="4" t="n">
-        <v>57.93</v>
+        <v>58.62</v>
       </c>
       <c r="E118" s="4" t="n">
-        <v>56.4</v>
+        <v>47.1</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>51.37</v>
+        <v>45.65</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>MANORAMA</t>
+          <t>GHCL</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -3850,22 +3890,22 @@
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>1411.1</v>
+        <v>506.8</v>
       </c>
       <c r="D119" s="4" t="n">
-        <v>57.92</v>
+        <v>58.26</v>
       </c>
       <c r="E119" s="4" t="n">
-        <v>55.37</v>
+        <v>47.66</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>62.21</v>
+        <v>46.45</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>SUNTECK</t>
+          <t>RALLIS</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -3874,22 +3914,22 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>350.65</v>
+        <v>265.91</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>57.79</v>
+        <v>58.24</v>
       </c>
       <c r="E120" s="4" t="n">
-        <v>45.14</v>
+        <v>50.09</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>43.97</v>
+        <v>49.04</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>SAMHI</t>
+          <t>AARTIDRUGS</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -3898,22 +3938,22 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>162.33</v>
+        <v>376.3</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>57.72</v>
+        <v>58.22</v>
       </c>
       <c r="E121" s="4" t="n">
-        <v>45.96</v>
+        <v>46.89</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>46.11</v>
+        <v>44.24</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>SHRIPISTON</t>
+          <t>SHAKTIPUMP</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -3922,22 +3962,22 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>3478.7</v>
+        <v>564.3</v>
       </c>
       <c r="D122" s="4" t="n">
-        <v>57.64</v>
+        <v>58.21</v>
       </c>
       <c r="E122" s="4" t="n">
-        <v>60.48</v>
+        <v>43.41</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>71.75</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>ZYDUSWELL</t>
+          <t>BELRISE</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -3946,22 +3986,22 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>490.85</v>
+        <v>212.72</v>
       </c>
       <c r="D123" s="4" t="n">
-        <v>57.62</v>
+        <v>58.11</v>
       </c>
       <c r="E123" s="4" t="n">
-        <v>61.72</v>
+        <v>68.86</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>61.37</v>
+        <v/>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>TARC</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -3970,22 +4010,22 @@
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>137.41</v>
+        <v>469.3</v>
       </c>
       <c r="D124" s="4" t="n">
-        <v>57.52</v>
+        <v>58.11</v>
       </c>
       <c r="E124" s="4" t="n">
-        <v>45.99</v>
+        <v>52.46</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>47.85</v>
+        <v>45.89</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>SUBROS</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -3994,22 +4034,22 @@
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>242.04</v>
+        <v>778.55</v>
       </c>
       <c r="D125" s="4" t="n">
-        <v>57.5</v>
+        <v>57.96</v>
       </c>
       <c r="E125" s="4" t="n">
-        <v>70.67</v>
+        <v>48.54</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>63.6</v>
+        <v>52.69</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>GAEL</t>
+          <t>IONEXCHANG</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -4018,22 +4058,22 @@
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>151.37</v>
+        <v>396.4</v>
       </c>
       <c r="D126" s="4" t="n">
-        <v>57.44</v>
+        <v>57.8</v>
       </c>
       <c r="E126" s="4" t="n">
-        <v>63.73</v>
+        <v>55.44</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>60.79</v>
+        <v>45.49</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>NESCO</t>
+          <t>JINDWORLD</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -4042,22 +4082,22 @@
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>1168.6</v>
+        <v>25.9</v>
       </c>
       <c r="D127" s="4" t="n">
-        <v>57.37</v>
+        <v>57.75</v>
       </c>
       <c r="E127" s="4" t="n">
-        <v>50.54</v>
+        <v>45.25</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>56.4</v>
+        <v>35.9</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>BOSCH-HCIL</t>
+          <t>PATELENG</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -4066,22 +4106,22 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>1366.7</v>
+        <v>28.38</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>57.29</v>
+        <v>57.69</v>
       </c>
       <c r="E128" s="4" t="n">
-        <v>50</v>
+        <v>46.55</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v/>
+        <v>38.74</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>SANDUMA</t>
+          <t>HIKAL</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -4090,22 +4130,22 @@
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>209.35</v>
+        <v>189.25</v>
       </c>
       <c r="D129" s="4" t="n">
-        <v>57.17</v>
+        <v>57.49</v>
       </c>
       <c r="E129" s="4" t="n">
-        <v>52.83</v>
+        <v>43.14</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>58.54</v>
+        <v>37.06</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>SHAREINDIA</t>
+          <t>TEXRAIL</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -4114,22 +4154,22 @@
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>144.82</v>
+        <v>105.47</v>
       </c>
       <c r="D130" s="4" t="n">
-        <v>57.09</v>
+        <v>57.4</v>
       </c>
       <c r="E130" s="4" t="n">
-        <v>48.1</v>
+        <v>44.23</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>41.44</v>
+        <v>42.73</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>IMAGICAA</t>
+          <t>TANLA</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -4138,22 +4178,22 @@
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>46.92</v>
+        <v>511.95</v>
       </c>
       <c r="D131" s="4" t="n">
-        <v>57.04</v>
+        <v>57.33</v>
       </c>
       <c r="E131" s="4" t="n">
-        <v>48.29</v>
+        <v>52.76</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>43.35</v>
+        <v>43.42</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>ADVENZYMES</t>
+          <t>FDC</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -4162,22 +4202,22 @@
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>299.05</v>
+        <v>364.45</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>57.03</v>
+        <v>57.3</v>
       </c>
       <c r="E132" s="4" t="n">
-        <v>50.82</v>
+        <v>46.17</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>46.96</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>PRICOLLTD</t>
+          <t>BANCOINDIA</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -4186,22 +4226,22 @@
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>594.65</v>
+        <v>618.55</v>
       </c>
       <c r="D133" s="4" t="n">
-        <v>57.03</v>
+        <v>57.16</v>
       </c>
       <c r="E133" s="4" t="n">
-        <v>54.73</v>
+        <v>50.39</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>59.46</v>
+        <v>57.31</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>V2RETAIL</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -4210,22 +4250,22 @@
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>203.06</v>
+        <v>464.1</v>
       </c>
       <c r="D134" s="4" t="n">
-        <v>56.91</v>
+        <v>56.87</v>
       </c>
       <c r="E134" s="4" t="n">
-        <v>50.64</v>
+        <v>55.71</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>62.26</v>
+        <v>59.68</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>RENUKA</t>
+          <t>HGINFRA</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -4234,22 +4274,22 @@
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>27.83</v>
+        <v>595</v>
       </c>
       <c r="D135" s="4" t="n">
-        <v>56.9</v>
+        <v>56.83</v>
       </c>
       <c r="E135" s="4" t="n">
-        <v>54.76</v>
+        <v>41.96</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>41.65</v>
+        <v>37.41</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>GRWRHITECH</t>
+          <t>BOSCH-HCIL</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -4258,22 +4298,22 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>4035.9</v>
+        <v>1390.6</v>
       </c>
       <c r="D136" s="4" t="n">
-        <v>56.84</v>
+        <v>56.79</v>
       </c>
       <c r="E136" s="4" t="n">
-        <v>56.92</v>
+        <v>51.92</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>56.13</v>
+        <v/>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>GANESHHOU</t>
+          <t>ABDL</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -4282,22 +4322,22 @@
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>644.8</v>
+        <v>531.8</v>
       </c>
       <c r="D137" s="4" t="n">
-        <v>56.79</v>
+        <v>56.74</v>
       </c>
       <c r="E137" s="4" t="n">
-        <v>39.76</v>
+        <v>53.23</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v/>
+        <v>57.2</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>ZAGGLE</t>
+          <t>TVSSCS</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -4306,22 +4346,22 @@
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>256.26</v>
+        <v>114.51</v>
       </c>
       <c r="D138" s="4" t="n">
-        <v>56.73</v>
+        <v>56.61</v>
       </c>
       <c r="E138" s="4" t="n">
-        <v>42.07</v>
+        <v>51.45</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>43.89</v>
+        <v>41.32</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>MASTEK</t>
+          <t>EASEMYTRIP</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -4330,22 +4370,22 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>1700.1</v>
+        <v>7.86</v>
       </c>
       <c r="D139" s="4" t="n">
-        <v>56.46</v>
+        <v>56.59</v>
       </c>
       <c r="E139" s="4" t="n">
-        <v>41.86</v>
+        <v>51.53</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>40.85</v>
+        <v>37.76</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>GHCL</t>
+          <t>SHRIPISTON</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -4354,22 +4394,22 @@
         </is>
       </c>
       <c r="C140" s="4" t="n">
-        <v>495.65</v>
+        <v>3491.1</v>
       </c>
       <c r="D140" s="4" t="n">
-        <v>56.43</v>
+        <v>56.42</v>
       </c>
       <c r="E140" s="4" t="n">
-        <v>44.98</v>
+        <v>60.9</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>45.5</v>
+        <v>71.87</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>ASHOKA</t>
+          <t>VARROC</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -4378,22 +4418,22 @@
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>133.05</v>
+        <v>533.8</v>
       </c>
       <c r="D141" s="4" t="n">
-        <v>56.35</v>
+        <v>56.32</v>
       </c>
       <c r="E141" s="4" t="n">
-        <v>41.96</v>
+        <v>46.05</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>43.47</v>
+        <v>50.67</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>INDIGOPNTS</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -4402,22 +4442,22 @@
         </is>
       </c>
       <c r="C142" s="4" t="n">
-        <v>860.05</v>
+        <v>1171.8</v>
       </c>
       <c r="D142" s="4" t="n">
-        <v>56.19</v>
+        <v>56.29</v>
       </c>
       <c r="E142" s="4" t="n">
-        <v>39.98</v>
+        <v>65.67</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>39.78</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>THYROCARE</t>
+          <t>IIFLCAPS</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -4426,22 +4466,22 @@
         </is>
       </c>
       <c r="C143" s="4" t="n">
-        <v>395.1</v>
+        <v>312.33</v>
       </c>
       <c r="D143" s="4" t="n">
-        <v>56.15</v>
+        <v>56.28</v>
       </c>
       <c r="E143" s="4" t="n">
-        <v>48.83</v>
+        <v>51.88</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>56.3</v>
+        <v>51.34</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>ARVIND</t>
+          <t>ASHOKA</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -4450,22 +4490,22 @@
         </is>
       </c>
       <c r="C144" s="4" t="n">
-        <v>382.5</v>
+        <v>134.25</v>
       </c>
       <c r="D144" s="4" t="n">
-        <v>56.13</v>
+        <v>56.21</v>
       </c>
       <c r="E144" s="4" t="n">
-        <v>60.5</v>
+        <v>42.49</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>60.93</v>
+        <v>43.69</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>PATELENG</t>
+          <t>IFBIND</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -4474,22 +4514,22 @@
         </is>
       </c>
       <c r="C145" s="4" t="n">
-        <v>27.7</v>
+        <v>1142.85</v>
       </c>
       <c r="D145" s="4" t="n">
-        <v>56</v>
+        <v>56.16</v>
       </c>
       <c r="E145" s="4" t="n">
-        <v>44.62</v>
+        <v>41.42</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>37.81</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>EMIL</t>
+          <t>LMW</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -4498,22 +4538,22 @@
         </is>
       </c>
       <c r="C146" s="4" t="n">
-        <v>103.31</v>
+        <v>14562</v>
       </c>
       <c r="D146" s="4" t="n">
-        <v>55.96</v>
+        <v>56.13</v>
       </c>
       <c r="E146" s="4" t="n">
-        <v>46.68</v>
+        <v>49.7</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>42.31</v>
+        <v>49.76</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>GOKEX</t>
+          <t>ALIVUS</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -4522,22 +4562,22 @@
         </is>
       </c>
       <c r="C147" s="4" t="n">
-        <v>709.05</v>
+        <v>1038.15</v>
       </c>
       <c r="D147" s="4" t="n">
-        <v>55.93</v>
+        <v>56.12</v>
       </c>
       <c r="E147" s="4" t="n">
-        <v>49.63</v>
+        <v>61.73</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>48.27</v>
+        <v>62.54</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>EPL</t>
+          <t>MARKSANS</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -4546,22 +4586,22 @@
         </is>
       </c>
       <c r="C148" s="4" t="n">
-        <v>225.84</v>
+        <v>184.63</v>
       </c>
       <c r="D148" s="4" t="n">
-        <v>55.78</v>
+        <v>56.07</v>
       </c>
       <c r="E148" s="4" t="n">
-        <v>56.51</v>
+        <v>52.76</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>54.49</v>
+        <v>49.77</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>GREENPANEL</t>
+          <t>WAAREERTL</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -4570,22 +4610,22 @@
         </is>
       </c>
       <c r="C149" s="4" t="n">
-        <v>208.87</v>
+        <v>1017.6</v>
       </c>
       <c r="D149" s="4" t="n">
-        <v>55.78</v>
+        <v>55.98</v>
       </c>
       <c r="E149" s="4" t="n">
-        <v>44.13</v>
+        <v>55.25</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>39.91</v>
+        <v/>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>PURVA</t>
+          <t>QUESS</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -4594,22 +4634,22 @@
         </is>
       </c>
       <c r="C150" s="4" t="n">
-        <v>214.26</v>
+        <v>197.68</v>
       </c>
       <c r="D150" s="4" t="n">
-        <v>55.76</v>
+        <v>55.94</v>
       </c>
       <c r="E150" s="4" t="n">
-        <v>47.16</v>
+        <v>42.8</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>44.94</v>
+        <v>31.67</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>ALLCARGO</t>
+          <t>THYROCARE</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -4618,22 +4658,22 @@
         </is>
       </c>
       <c r="C151" s="4" t="n">
-        <v>9</v>
+        <v>400.3</v>
       </c>
       <c r="D151" s="4" t="n">
-        <v>55.76</v>
+        <v>55.92</v>
       </c>
       <c r="E151" s="4" t="n">
-        <v>32.7</v>
+        <v>50.07</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>27.27</v>
+        <v>56.75</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>KANSAINER</t>
+          <t>PARADEEP</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -4642,22 +4682,22 @@
         </is>
       </c>
       <c r="C152" s="4" t="n">
-        <v>197.15</v>
+        <v>128.96</v>
       </c>
       <c r="D152" s="4" t="n">
-        <v>55.64</v>
+        <v>55.87</v>
       </c>
       <c r="E152" s="4" t="n">
-        <v>43.53</v>
+        <v>46.66</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>37.6</v>
+        <v>50.69</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>GABRIEL</t>
+          <t>SHARDAMOTR</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -4666,22 +4706,22 @@
         </is>
       </c>
       <c r="C153" s="4" t="n">
-        <v>973</v>
+        <v>863.75</v>
       </c>
       <c r="D153" s="4" t="n">
-        <v>55.53</v>
+        <v>55.7</v>
       </c>
       <c r="E153" s="4" t="n">
-        <v>51</v>
+        <v>46.88</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>60.5</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>GREAVESCOT</t>
+          <t>PRINCEPIPE</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -4690,22 +4730,22 @@
         </is>
       </c>
       <c r="C154" s="4" t="n">
-        <v>154.81</v>
+        <v>259.39</v>
       </c>
       <c r="D154" s="4" t="n">
-        <v>55.48</v>
+        <v>55.7</v>
       </c>
       <c r="E154" s="4" t="n">
-        <v>44.2</v>
+        <v>48.5</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>45.4</v>
+        <v>38.05</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>GANECOS</t>
+          <t>SANDUMA</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -4714,22 +4754,22 @@
         </is>
       </c>
       <c r="C155" s="4" t="n">
-        <v>1008.5</v>
+        <v>210.61</v>
       </c>
       <c r="D155" s="4" t="n">
-        <v>55.46</v>
+        <v>55.62</v>
       </c>
       <c r="E155" s="4" t="n">
-        <v>53.41</v>
+        <v>53.13</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>45.32</v>
+        <v>58.75</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>BANCOINDIA</t>
+          <t>IMFA</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -4738,22 +4778,22 @@
         </is>
       </c>
       <c r="C156" s="4" t="n">
-        <v>606.8</v>
+        <v>1502.6</v>
       </c>
       <c r="D156" s="4" t="n">
-        <v>55.37</v>
+        <v>55.61</v>
       </c>
       <c r="E156" s="4" t="n">
-        <v>49.57</v>
+        <v>62.35</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>56.79</v>
+        <v>69.79000000000001</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>SUDARSCHEM</t>
+          <t>GSFC</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -4762,22 +4802,22 @@
         </is>
       </c>
       <c r="C157" s="4" t="n">
-        <v>869.55</v>
+        <v>170.39</v>
       </c>
       <c r="D157" s="4" t="n">
-        <v>55.28</v>
+        <v>55.39</v>
       </c>
       <c r="E157" s="4" t="n">
-        <v>41.82</v>
+        <v>48.94</v>
       </c>
       <c r="F157" s="4" t="n">
-        <v>46.83</v>
+        <v>47.02</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>AARTIDRUGS</t>
+          <t>MAXESTATES</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -4786,22 +4826,22 @@
         </is>
       </c>
       <c r="C158" s="4" t="n">
-        <v>366.7</v>
+        <v>391.3</v>
       </c>
       <c r="D158" s="4" t="n">
-        <v>55.24</v>
+        <v>55.07</v>
       </c>
       <c r="E158" s="4" t="n">
-        <v>43.47</v>
+        <v>46.33</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v>43.14</v>
+        <v>47</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>SANOFICONR</t>
+          <t>EUREKAFORB</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -4810,22 +4850,22 @@
         </is>
       </c>
       <c r="C159" s="4" t="n">
-        <v>4595.3</v>
+        <v>498.65</v>
       </c>
       <c r="D159" s="4" t="n">
-        <v>55.11</v>
+        <v>54.96</v>
       </c>
       <c r="E159" s="4" t="n">
-        <v>52.32</v>
+        <v>46.86</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>46.92</v>
+        <v>44.46</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>INNOVACAP</t>
+          <t>HCG</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -4834,22 +4874,22 @@
         </is>
       </c>
       <c r="C160" s="4" t="n">
-        <v>721.15</v>
+        <v>572.55</v>
       </c>
       <c r="D160" s="4" t="n">
-        <v>55.03</v>
+        <v>54.94</v>
       </c>
       <c r="E160" s="4" t="n">
-        <v>49.29</v>
+        <v>44.35</v>
       </c>
       <c r="F160" s="4" t="n">
-        <v>48.81</v>
+        <v>54.54</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>EPL</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -4858,22 +4898,22 @@
         </is>
       </c>
       <c r="C161" s="4" t="n">
-        <v>603.3</v>
+        <v>226.13</v>
       </c>
       <c r="D161" s="4" t="n">
-        <v>54.96</v>
+        <v>54.9</v>
       </c>
       <c r="E161" s="4" t="n">
-        <v>52.76</v>
+        <v>57.1</v>
       </c>
       <c r="F161" s="4" t="n">
-        <v>49.48</v>
+        <v>54.55</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>ACUTAAS</t>
+          <t>PURVA</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -4882,22 +4922,22 @@
         </is>
       </c>
       <c r="C162" s="4" t="n">
-        <v>2395</v>
+        <v>214.37</v>
       </c>
       <c r="D162" s="4" t="n">
-        <v>54.95</v>
+        <v>54.82</v>
       </c>
       <c r="E162" s="4" t="n">
-        <v>64.01000000000001</v>
+        <v>47.06</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v/>
+        <v>44.95</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>LMW</t>
+          <t>MASTEK</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -4906,22 +4946,22 @@
         </is>
       </c>
       <c r="C163" s="4" t="n">
-        <v>14288</v>
+        <v>1694.2</v>
       </c>
       <c r="D163" s="4" t="n">
-        <v>54.86</v>
+        <v>54.8</v>
       </c>
       <c r="E163" s="4" t="n">
-        <v>48.55</v>
+        <v>42.16</v>
       </c>
       <c r="F163" s="4" t="n">
-        <v>48.84</v>
+        <v>40.72</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>SUPRIYA</t>
+          <t>SPARC</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -4930,22 +4970,22 @@
         </is>
       </c>
       <c r="C164" s="4" t="n">
-        <v>642.85</v>
+        <v>143.04</v>
       </c>
       <c r="D164" s="4" t="n">
-        <v>54.79</v>
+        <v>54.76</v>
       </c>
       <c r="E164" s="4" t="n">
-        <v>44.3</v>
+        <v>54.65</v>
       </c>
       <c r="F164" s="4" t="n">
-        <v>52.75</v>
+        <v>44.17</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>TEXRAIL</t>
+          <t>INDIGOPNTS</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -4954,22 +4994,22 @@
         </is>
       </c>
       <c r="C165" s="4" t="n">
-        <v>102.28</v>
+        <v>860.2</v>
       </c>
       <c r="D165" s="4" t="n">
-        <v>54.69</v>
+        <v>54.63</v>
       </c>
       <c r="E165" s="4" t="n">
-        <v>41.33</v>
+        <v>40.2</v>
       </c>
       <c r="F165" s="4" t="n">
-        <v>41.96</v>
+        <v>39.79</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>HCG</t>
+          <t>PARKHOTELS</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -4978,22 +5018,22 @@
         </is>
       </c>
       <c r="C166" s="4" t="n">
-        <v>569.35</v>
+        <v>121.73</v>
       </c>
       <c r="D166" s="4" t="n">
         <v>54.58</v>
       </c>
       <c r="E166" s="4" t="n">
-        <v>42.09</v>
+        <v>47.6</v>
       </c>
       <c r="F166" s="4" t="n">
-        <v>54.26</v>
+        <v>38.89</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>SHAKTIPUMP</t>
+          <t>SOUTHBANK</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -5002,22 +5042,22 @@
         </is>
       </c>
       <c r="C167" s="4" t="n">
-        <v>545.25</v>
+        <v>39.46</v>
       </c>
       <c r="D167" s="4" t="n">
-        <v>54.41</v>
+        <v>54.58</v>
       </c>
       <c r="E167" s="4" t="n">
-        <v>40.31</v>
+        <v>55.02</v>
       </c>
       <c r="F167" s="4" t="n">
-        <v>45.81</v>
+        <v>63.97</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>VIYASH</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -5026,22 +5066,22 @@
         </is>
       </c>
       <c r="C168" s="4" t="n">
-        <v>207.15</v>
+        <v>607.3</v>
       </c>
       <c r="D168" s="4" t="n">
-        <v>54.36</v>
+        <v>54.55</v>
       </c>
       <c r="E168" s="4" t="n">
-        <v>57.65</v>
+        <v>53.06</v>
       </c>
       <c r="F168" s="4" t="n">
-        <v/>
+        <v>49.85</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>RAIN</t>
+          <t>VMART</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -5050,22 +5090,22 @@
         </is>
       </c>
       <c r="C169" s="4" t="n">
-        <v>128.2</v>
+        <v>616.45</v>
       </c>
       <c r="D169" s="4" t="n">
-        <v>54.26</v>
+        <v>54.48</v>
       </c>
       <c r="E169" s="4" t="n">
-        <v>48.66</v>
+        <v>47.1</v>
       </c>
       <c r="F169" s="4" t="n">
-        <v>46.33</v>
+        <v>44.93</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>DODLA</t>
+          <t>LUXIND</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -5074,22 +5114,22 @@
         </is>
       </c>
       <c r="C170" s="4" t="n">
-        <v>1092.9</v>
+        <v>1398.2</v>
       </c>
       <c r="D170" s="4" t="n">
-        <v>54.21</v>
+        <v>54.41</v>
       </c>
       <c r="E170" s="4" t="n">
-        <v>42.79</v>
+        <v>60.4</v>
       </c>
       <c r="F170" s="4" t="n">
-        <v>49.42</v>
+        <v>50.78</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -5098,22 +5138,22 @@
         </is>
       </c>
       <c r="C171" s="4" t="n">
-        <v>455.65</v>
+        <v>1057.25</v>
       </c>
       <c r="D171" s="4" t="n">
-        <v>54.09</v>
+        <v>54.4</v>
       </c>
       <c r="E171" s="4" t="n">
-        <v>53.51</v>
+        <v>56.4</v>
       </c>
       <c r="F171" s="4" t="n">
-        <v>59.07</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>ORCHPHARMA</t>
+          <t>GRWRHITECH</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -5122,22 +5162,22 @@
         </is>
       </c>
       <c r="C172" s="4" t="n">
-        <v>566.85</v>
+        <v>3999</v>
       </c>
       <c r="D172" s="4" t="n">
-        <v>54.07</v>
+        <v>54.38</v>
       </c>
       <c r="E172" s="4" t="n">
-        <v>38.59</v>
+        <v>56.17</v>
       </c>
       <c r="F172" s="4" t="n">
-        <v>41.67</v>
+        <v>55.92</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>KANSAINER</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -5146,22 +5186,22 @@
         </is>
       </c>
       <c r="C173" s="4" t="n">
-        <v>692.95</v>
+        <v>197.19</v>
       </c>
       <c r="D173" s="4" t="n">
-        <v>54.05</v>
+        <v>54.32</v>
       </c>
       <c r="E173" s="4" t="n">
-        <v>45.92</v>
+        <v>43.03</v>
       </c>
       <c r="F173" s="4" t="n">
-        <v>51.23</v>
+        <v>37.61</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>PCJEWELLER</t>
+          <t>DATAMATICS</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -5170,22 +5210,22 @@
         </is>
       </c>
       <c r="C174" s="4" t="n">
-        <v>9.35</v>
+        <v>732.8</v>
       </c>
       <c r="D174" s="4" t="n">
-        <v>53.95</v>
+        <v>54.27</v>
       </c>
       <c r="E174" s="4" t="n">
-        <v>44.38</v>
+        <v>48.36</v>
       </c>
       <c r="F174" s="4" t="n">
-        <v>47.82</v>
+        <v>52.39</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>NFL</t>
+          <t>ELECTCAST</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -5194,22 +5234,22 @@
         </is>
       </c>
       <c r="C175" s="4" t="n">
-        <v>75.76000000000001</v>
+        <v>81.98999999999999</v>
       </c>
       <c r="D175" s="4" t="n">
-        <v>53.87</v>
+        <v>54.22</v>
       </c>
       <c r="E175" s="4" t="n">
-        <v>42.83</v>
+        <v>52.29</v>
       </c>
       <c r="F175" s="4" t="n">
-        <v>44.69</v>
+        <v>44.07</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>AGI</t>
+          <t>GULFOILLUB</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -5218,22 +5258,22 @@
         </is>
       </c>
       <c r="C176" s="4" t="n">
-        <v>556.2</v>
+        <v>983.3</v>
       </c>
       <c r="D176" s="4" t="n">
-        <v>53.86</v>
+        <v>54.22</v>
       </c>
       <c r="E176" s="4" t="n">
-        <v>38.38</v>
+        <v>42.47</v>
       </c>
       <c r="F176" s="4" t="n">
-        <v>42.22</v>
+        <v>48.37</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>JINDWORLD</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -5242,22 +5282,22 @@
         </is>
       </c>
       <c r="C177" s="4" t="n">
-        <v>24.64</v>
+        <v>263.56</v>
       </c>
       <c r="D177" s="4" t="n">
-        <v>53.85</v>
+        <v>54.19</v>
       </c>
       <c r="E177" s="4" t="n">
-        <v>41.72</v>
+        <v>50.66</v>
       </c>
       <c r="F177" s="4" t="n">
-        <v>34.87</v>
+        <v>52.49</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>SPARC</t>
+          <t>TSFINV</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -5266,22 +5306,22 @@
         </is>
       </c>
       <c r="C178" s="4" t="n">
-        <v>139.28</v>
+        <v>402.95</v>
       </c>
       <c r="D178" s="4" t="n">
-        <v>53.68</v>
+        <v>54.17</v>
       </c>
       <c r="E178" s="4" t="n">
-        <v>52.84</v>
+        <v>39.83</v>
       </c>
       <c r="F178" s="4" t="n">
-        <v>43.28</v>
+        <v/>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>TSFINV</t>
+          <t>GOKEX</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -5290,22 +5330,22 @@
         </is>
       </c>
       <c r="C179" s="4" t="n">
-        <v>397.85</v>
+        <v>703.7</v>
       </c>
       <c r="D179" s="4" t="n">
-        <v>53.57</v>
+        <v>54</v>
       </c>
       <c r="E179" s="4" t="n">
-        <v>37.3</v>
+        <v>49.5</v>
       </c>
       <c r="F179" s="4" t="n">
-        <v/>
+        <v>48.07</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>CELLO</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -5314,22 +5354,22 @@
         </is>
       </c>
       <c r="C180" s="4" t="n">
-        <v>427.45</v>
+        <v>439.95</v>
       </c>
       <c r="D180" s="4" t="n">
-        <v>53.56</v>
+        <v>53.68</v>
       </c>
       <c r="E180" s="4" t="n">
-        <v>36.21</v>
+        <v>48.53</v>
       </c>
       <c r="F180" s="4" t="n">
-        <v>32.99</v>
+        <v>51.75</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -5338,22 +5378,22 @@
         </is>
       </c>
       <c r="C181" s="4" t="n">
-        <v>1040.65</v>
+        <v>3955.8</v>
       </c>
       <c r="D181" s="4" t="n">
-        <v>53.49</v>
+        <v>53.51</v>
       </c>
       <c r="E181" s="4" t="n">
-        <v>55.01</v>
+        <v>60.22</v>
       </c>
       <c r="F181" s="4" t="n">
-        <v>60.36</v>
+        <v>72.79000000000001</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>SYMPHONY</t>
+          <t>AVANTIFEED</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -5362,22 +5402,22 @@
         </is>
       </c>
       <c r="C182" s="4" t="n">
-        <v>794.7</v>
+        <v>1380.7</v>
       </c>
       <c r="D182" s="4" t="n">
-        <v>53.37</v>
+        <v>53.29</v>
       </c>
       <c r="E182" s="4" t="n">
-        <v>43.87</v>
+        <v>65.95</v>
       </c>
       <c r="F182" s="4" t="n">
-        <v>41.08</v>
+        <v>75.14</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>EASEMYTRIP</t>
+          <t>PCJEWELLER</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -5386,22 +5426,22 @@
         </is>
       </c>
       <c r="C183" s="4" t="n">
-        <v>7.62</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="D183" s="4" t="n">
-        <v>53.26</v>
+        <v>53.22</v>
       </c>
       <c r="E183" s="4" t="n">
-        <v>49.32</v>
+        <v>44.72</v>
       </c>
       <c r="F183" s="4" t="n">
-        <v>36.92</v>
+        <v>47.87</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>SUBROS</t>
+          <t>DODLA</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -5410,22 +5450,22 @@
         </is>
       </c>
       <c r="C184" s="4" t="n">
-        <v>753.45</v>
+        <v>1099.9</v>
       </c>
       <c r="D184" s="4" t="n">
-        <v>53.24</v>
+        <v>53.19</v>
       </c>
       <c r="E184" s="4" t="n">
-        <v>46.18</v>
+        <v>42.36</v>
       </c>
       <c r="F184" s="4" t="n">
-        <v>51.62</v>
+        <v>49.7</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>DCAL</t>
+          <t>MAHLIFE</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -5434,22 +5474,22 @@
         </is>
       </c>
       <c r="C185" s="4" t="n">
-        <v>169.01</v>
+        <v>340.5</v>
       </c>
       <c r="D185" s="4" t="n">
-        <v>53.2</v>
+        <v>53.14</v>
       </c>
       <c r="E185" s="4" t="n">
-        <v>38.11</v>
+        <v>45.27</v>
       </c>
       <c r="F185" s="4" t="n">
-        <v>44.33</v>
+        <v>42.99</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>PARKHOTELS</t>
+          <t>WESTLIFE</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -5458,22 +5498,22 @@
         </is>
       </c>
       <c r="C186" s="4" t="n">
-        <v>119.04</v>
+        <v>475.85</v>
       </c>
       <c r="D186" s="4" t="n">
-        <v>53.07</v>
+        <v>53.11</v>
       </c>
       <c r="E186" s="4" t="n">
-        <v>43.28</v>
+        <v>40.07</v>
       </c>
       <c r="F186" s="4" t="n">
-        <v>37.7</v>
+        <v>31.45</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>LUMAXTECH</t>
+          <t>CIEINDIA</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -5482,22 +5522,22 @@
         </is>
       </c>
       <c r="C187" s="4" t="n">
-        <v>1727</v>
+        <v>473.75</v>
       </c>
       <c r="D187" s="4" t="n">
-        <v>53</v>
+        <v>53.08</v>
       </c>
       <c r="E187" s="4" t="n">
-        <v>59.23</v>
+        <v>58.85</v>
       </c>
       <c r="F187" s="4" t="n">
-        <v>70.02</v>
+        <v>55.79</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>SHARDAMOTR</t>
+          <t>GATEWAY</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -5506,16 +5546,16 @@
         </is>
       </c>
       <c r="C188" s="4" t="n">
-        <v>845</v>
+        <v>57.37</v>
       </c>
       <c r="D188" s="4" t="n">
-        <v>53</v>
+        <v>52.86</v>
       </c>
       <c r="E188" s="4" t="n">
-        <v>45.27</v>
+        <v>50.18</v>
       </c>
       <c r="F188" s="4" t="n">
-        <v>42.67</v>
+        <v>41.91</v>
       </c>
     </row>
     <row r="189">
@@ -5530,22 +5570,22 @@
         </is>
       </c>
       <c r="C189" s="4" t="n">
-        <v>34.2</v>
+        <v>34.43</v>
       </c>
       <c r="D189" s="4" t="n">
-        <v>52.92</v>
+        <v>52.68</v>
       </c>
       <c r="E189" s="4" t="n">
-        <v>40.01</v>
+        <v>40.63</v>
       </c>
       <c r="F189" s="4" t="n">
-        <v>37.05</v>
+        <v>37.23</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>ORIENTCEM</t>
+          <t>TEAMLEASE</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -5554,22 +5594,22 @@
         </is>
       </c>
       <c r="C190" s="4" t="n">
-        <v>143.57</v>
+        <v>1232.3</v>
       </c>
       <c r="D190" s="4" t="n">
-        <v>52.88</v>
+        <v>52.64</v>
       </c>
       <c r="E190" s="4" t="n">
-        <v>35.78</v>
+        <v>35.33</v>
       </c>
       <c r="F190" s="4" t="n">
-        <v>36.52</v>
+        <v>31.67</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>GULFOILLUB</t>
+          <t>ENTERO</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -5578,22 +5618,22 @@
         </is>
       </c>
       <c r="C191" s="4" t="n">
-        <v>969.5</v>
+        <v>1216.4</v>
       </c>
       <c r="D191" s="4" t="n">
-        <v>52.55</v>
+        <v>52.57</v>
       </c>
       <c r="E191" s="4" t="n">
-        <v>39.97</v>
+        <v>54.46</v>
       </c>
       <c r="F191" s="4" t="n">
-        <v>47.67</v>
+        <v>53.52</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>ICIL</t>
+          <t>KNRCON</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -5602,22 +5642,22 @@
         </is>
       </c>
       <c r="C192" s="4" t="n">
-        <v>263.29</v>
+        <v>125.13</v>
       </c>
       <c r="D192" s="4" t="n">
-        <v>52.5</v>
+        <v>52.47</v>
       </c>
       <c r="E192" s="4" t="n">
-        <v>49.18</v>
+        <v>40.54</v>
       </c>
       <c r="F192" s="4" t="n">
-        <v>48.18</v>
+        <v>33.53</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>TIMETECHNO</t>
+          <t>VAIBHAVGBL</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -5626,22 +5666,22 @@
         </is>
       </c>
       <c r="C193" s="4" t="n">
-        <v>184.11</v>
+        <v>217.18</v>
       </c>
       <c r="D193" s="4" t="n">
-        <v>52.5</v>
+        <v>52.43</v>
       </c>
       <c r="E193" s="4" t="n">
-        <v>48.37</v>
+        <v>48.73</v>
       </c>
       <c r="F193" s="4" t="n">
-        <v>52.56</v>
+        <v>43.84</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>GMMPFAUDLR</t>
+          <t>MEDPLUS</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -5650,22 +5690,22 @@
         </is>
       </c>
       <c r="C194" s="4" t="n">
-        <v>908.6</v>
+        <v>872.15</v>
       </c>
       <c r="D194" s="4" t="n">
-        <v>52.46</v>
+        <v>52.4</v>
       </c>
       <c r="E194" s="4" t="n">
-        <v>40.43</v>
+        <v>57.29</v>
       </c>
       <c r="F194" s="4" t="n">
-        <v>41.16</v>
+        <v>56.14</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>GATEWAY</t>
+          <t>JKPAPER</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -5674,22 +5714,22 @@
         </is>
       </c>
       <c r="C195" s="4" t="n">
-        <v>57.03</v>
+        <v>360.25</v>
       </c>
       <c r="D195" s="4" t="n">
-        <v>52.37</v>
+        <v>51.65</v>
       </c>
       <c r="E195" s="4" t="n">
-        <v>48.81</v>
+        <v>52.2</v>
       </c>
       <c r="F195" s="4" t="n">
-        <v>41.56</v>
+        <v>50.08</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>ELECTCAST</t>
+          <t>FIEMIND</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -5698,22 +5738,22 @@
         </is>
       </c>
       <c r="C196" s="4" t="n">
-        <v>79.29000000000001</v>
+        <v>2182.7</v>
       </c>
       <c r="D196" s="4" t="n">
-        <v>52.21</v>
+        <v>51.64</v>
       </c>
       <c r="E196" s="4" t="n">
-        <v>49.47</v>
+        <v>52.93</v>
       </c>
       <c r="F196" s="4" t="n">
-        <v>43.08</v>
+        <v>65.34999999999999</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>RELAXO</t>
+          <t>AURIONPRO</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -5722,22 +5762,22 @@
         </is>
       </c>
       <c r="C197" s="4" t="n">
-        <v>301.19</v>
+        <v>869.9</v>
       </c>
       <c r="D197" s="4" t="n">
-        <v>52.14</v>
+        <v>51.54</v>
       </c>
       <c r="E197" s="4" t="n">
-        <v>36.56</v>
+        <v>41.76</v>
       </c>
       <c r="F197" s="4" t="n">
-        <v>27.77</v>
+        <v>42.45</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>ROUTE</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -5746,22 +5786,22 @@
         </is>
       </c>
       <c r="C198" s="4" t="n">
-        <v>497.6</v>
+        <v>186.76</v>
       </c>
       <c r="D198" s="4" t="n">
-        <v>52.05</v>
+        <v>51.54</v>
       </c>
       <c r="E198" s="4" t="n">
-        <v>33.07</v>
+        <v>59.11</v>
       </c>
       <c r="F198" s="4" t="n">
-        <v>27.59</v>
+        <v>61.05</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>YATHARTH</t>
+          <t>ORIENTCEM</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -5770,22 +5810,22 @@
         </is>
       </c>
       <c r="C199" s="4" t="n">
-        <v>718.3</v>
+        <v>143.8</v>
       </c>
       <c r="D199" s="4" t="n">
-        <v>51.84</v>
+        <v>51.37</v>
       </c>
       <c r="E199" s="4" t="n">
-        <v>54.34</v>
+        <v>36.53</v>
       </c>
       <c r="F199" s="4" t="n">
-        <v>58.71</v>
+        <v>36.57</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>VAIBHAVGBL</t>
+          <t>GMMPFAUDLR</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -5794,22 +5834,22 @@
         </is>
       </c>
       <c r="C200" s="4" t="n">
-        <v>215.03</v>
+        <v>905.55</v>
       </c>
       <c r="D200" s="4" t="n">
-        <v>51.69</v>
+        <v>51.33</v>
       </c>
       <c r="E200" s="4" t="n">
-        <v>47.58</v>
+        <v>39.88</v>
       </c>
       <c r="F200" s="4" t="n">
-        <v>43.5</v>
+        <v>41.05</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>FIEMIND</t>
+          <t>SUNTECK</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -5818,22 +5858,22 @@
         </is>
       </c>
       <c r="C201" s="4" t="n">
-        <v>2175</v>
+        <v>340.25</v>
       </c>
       <c r="D201" s="4" t="n">
-        <v>51.51</v>
+        <v>51.32</v>
       </c>
       <c r="E201" s="4" t="n">
-        <v>52.85</v>
+        <v>43.28</v>
       </c>
       <c r="F201" s="4" t="n">
-        <v>65.19</v>
+        <v>42.89</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>SOUTHBANK</t>
+          <t>BECTORFOOD</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -5842,22 +5882,22 @@
         </is>
       </c>
       <c r="C202" s="4" t="n">
-        <v>38.63</v>
+        <v>196.21</v>
       </c>
       <c r="D202" s="4" t="n">
-        <v>51.45</v>
+        <v>51.16</v>
       </c>
       <c r="E202" s="4" t="n">
-        <v>52.67</v>
+        <v>36.63</v>
       </c>
       <c r="F202" s="4" t="n">
-        <v>63.11</v>
+        <v>40.98</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>SENCO</t>
+          <t>GMRP&amp;UI</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -5866,22 +5906,22 @@
         </is>
       </c>
       <c r="C203" s="4" t="n">
-        <v>318.1</v>
+        <v>106.55</v>
       </c>
       <c r="D203" s="4" t="n">
-        <v>51.24</v>
+        <v>51.1</v>
       </c>
       <c r="E203" s="4" t="n">
-        <v>49.36</v>
+        <v>48.4</v>
       </c>
       <c r="F203" s="4" t="n">
-        <v>46.79</v>
+        <v>53.22</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>RALLIS</t>
+          <t>VINATIORGA</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -5890,22 +5930,22 @@
         </is>
       </c>
       <c r="C204" s="4" t="n">
-        <v>256.47</v>
+        <v>1322.3</v>
       </c>
       <c r="D204" s="4" t="n">
-        <v>51.15</v>
+        <v>50.99</v>
       </c>
       <c r="E204" s="4" t="n">
-        <v>47.25</v>
+        <v>34.74</v>
       </c>
       <c r="F204" s="4" t="n">
-        <v>47.73</v>
+        <v>35.94</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>HIKAL</t>
+          <t>JKLAKSHMI</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -5914,22 +5954,22 @@
         </is>
       </c>
       <c r="C205" s="4" t="n">
-        <v>181.1</v>
+        <v>645.1</v>
       </c>
       <c r="D205" s="4" t="n">
-        <v>51.03</v>
+        <v>50.84</v>
       </c>
       <c r="E205" s="4" t="n">
-        <v>40.27</v>
+        <v>40.41</v>
       </c>
       <c r="F205" s="4" t="n">
-        <v>35.61</v>
+        <v>42.81</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>GMRP&amp;UI</t>
+          <t>JISLJALEQS</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -5938,22 +5978,22 @@
         </is>
       </c>
       <c r="C206" s="4" t="n">
-        <v>106</v>
+        <v>32.52</v>
       </c>
       <c r="D206" s="4" t="n">
-        <v>50.91</v>
+        <v>50.83</v>
       </c>
       <c r="E206" s="4" t="n">
-        <v>48.26</v>
+        <v>37.43</v>
       </c>
       <c r="F206" s="4" t="n">
-        <v>53.04</v>
+        <v>36.94</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>BLACKBUCK</t>
+          <t>V2RETAIL</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -5962,22 +6002,22 @@
         </is>
       </c>
       <c r="C207" s="4" t="n">
-        <v>597.25</v>
+        <v>198.65</v>
       </c>
       <c r="D207" s="4" t="n">
-        <v>50.91</v>
+        <v>50.81</v>
       </c>
       <c r="E207" s="4" t="n">
-        <v>49.9</v>
+        <v>47.61</v>
       </c>
       <c r="F207" s="4" t="n">
-        <v>58.58</v>
+        <v>61.38</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>QUESS</t>
+          <t>TARC</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -5986,22 +6026,22 @@
         </is>
       </c>
       <c r="C208" s="4" t="n">
-        <v>190.14</v>
+        <v>132.71</v>
       </c>
       <c r="D208" s="4" t="n">
-        <v>50.73</v>
+        <v>50.61</v>
       </c>
       <c r="E208" s="4" t="n">
-        <v>38.46</v>
+        <v>44.11</v>
       </c>
       <c r="F208" s="4" t="n">
-        <v>30.54</v>
+        <v>46.84</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>ARVINDFASN</t>
+          <t>SHARDACROP</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -6010,22 +6050,22 @@
         </is>
       </c>
       <c r="C209" s="4" t="n">
-        <v>449.75</v>
+        <v>1072.75</v>
       </c>
       <c r="D209" s="4" t="n">
-        <v>50.72</v>
+        <v>50.39</v>
       </c>
       <c r="E209" s="4" t="n">
-        <v>47.92</v>
+        <v>56.33</v>
       </c>
       <c r="F209" s="4" t="n">
-        <v>49.14</v>
+        <v>60.22</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>JKLAKSHMI</t>
+          <t>GPPL</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -6034,22 +6074,22 @@
         </is>
       </c>
       <c r="C210" s="4" t="n">
-        <v>640.1</v>
+        <v>156.05</v>
       </c>
       <c r="D210" s="4" t="n">
-        <v>50.61</v>
+        <v>50.12</v>
       </c>
       <c r="E210" s="4" t="n">
-        <v>39.4</v>
+        <v>45.17</v>
       </c>
       <c r="F210" s="4" t="n">
-        <v>42.48</v>
+        <v>50.89</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>CMSINFO</t>
+          <t>IMAGICAA</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -6058,22 +6098,22 @@
         </is>
       </c>
       <c r="C211" s="4" t="n">
-        <v>302.15</v>
+        <v>45.48</v>
       </c>
       <c r="D211" s="4" t="n">
-        <v>50.61</v>
+        <v>50.08</v>
       </c>
       <c r="E211" s="4" t="n">
-        <v>40.61</v>
+        <v>45.65</v>
       </c>
       <c r="F211" s="4" t="n">
-        <v>39.05</v>
+        <v>42.16</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>BECTORFOOD</t>
+          <t>RAIN</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -6082,22 +6122,22 @@
         </is>
       </c>
       <c r="C212" s="4" t="n">
-        <v>194.55</v>
+        <v>126.2</v>
       </c>
       <c r="D212" s="4" t="n">
-        <v>50.28</v>
+        <v>49.78</v>
       </c>
       <c r="E212" s="4" t="n">
-        <v>35.81</v>
+        <v>47.56</v>
       </c>
       <c r="F212" s="4" t="n">
-        <v>40.61</v>
+        <v>45.85</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>MSTCLTD</t>
+          <t>MOIL</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -6106,22 +6146,22 @@
         </is>
       </c>
       <c r="C213" s="4" t="n">
-        <v>433.4</v>
+        <v>310.9</v>
       </c>
       <c r="D213" s="4" t="n">
-        <v>50.15</v>
+        <v>49.52</v>
       </c>
       <c r="E213" s="4" t="n">
-        <v>45.71</v>
+        <v>48.16</v>
       </c>
       <c r="F213" s="4" t="n">
-        <v>45.56</v>
+        <v>49.04</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>PGIL</t>
+          <t>HEMIPROP</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -6130,22 +6170,22 @@
         </is>
       </c>
       <c r="C214" s="4" t="n">
-        <v>1543.7</v>
+        <v>128.12</v>
       </c>
       <c r="D214" s="4" t="n">
-        <v>50.07</v>
+        <v>49.44</v>
       </c>
       <c r="E214" s="4" t="n">
-        <v>51.4</v>
+        <v>46.23</v>
       </c>
       <c r="F214" s="4" t="n">
-        <v>60.52</v>
+        <v>45.89</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>GARFIBRES</t>
+          <t>VIYASH</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -6154,22 +6194,22 @@
         </is>
       </c>
       <c r="C215" s="4" t="n">
-        <v>627.1</v>
+        <v>203.74</v>
       </c>
       <c r="D215" s="4" t="n">
-        <v>49.9</v>
+        <v>49.43</v>
       </c>
       <c r="E215" s="4" t="n">
-        <v>42.78</v>
+        <v>55.08</v>
       </c>
       <c r="F215" s="4" t="n">
-        <v>40.28</v>
+        <v/>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>BALUFORGE</t>
+          <t>UJJIVANSFB</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -6178,22 +6218,22 @@
         </is>
       </c>
       <c r="C216" s="4" t="n">
-        <v>460.1</v>
+        <v>56.88</v>
       </c>
       <c r="D216" s="4" t="n">
-        <v>49.78</v>
+        <v>49.41</v>
       </c>
       <c r="E216" s="4" t="n">
-        <v>43.21</v>
+        <v>53.63</v>
       </c>
       <c r="F216" s="4" t="n">
-        <v>46.4</v>
+        <v>58.54</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>VARROC</t>
+          <t>MSTCLTD</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -6202,22 +6242,22 @@
         </is>
       </c>
       <c r="C217" s="4" t="n">
-        <v>512.25</v>
+        <v>433.15</v>
       </c>
       <c r="D217" s="4" t="n">
-        <v>49.16</v>
+        <v>49.35</v>
       </c>
       <c r="E217" s="4" t="n">
-        <v>41.78</v>
+        <v>45.94</v>
       </c>
       <c r="F217" s="4" t="n">
-        <v>48.88</v>
+        <v>45.54</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>TEAMLEASE</t>
+          <t>RELAXO</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -6226,22 +6266,22 @@
         </is>
       </c>
       <c r="C218" s="4" t="n">
-        <v>1208.6</v>
+        <v>298.09</v>
       </c>
       <c r="D218" s="4" t="n">
-        <v>49.11</v>
+        <v>49.28</v>
       </c>
       <c r="E218" s="4" t="n">
-        <v>33.02</v>
+        <v>36.39</v>
       </c>
       <c r="F218" s="4" t="n">
-        <v>30.96</v>
+        <v>27.35</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>UJJIVANSFB</t>
+          <t>RELIGARE</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -6250,22 +6290,22 @@
         </is>
       </c>
       <c r="C219" s="4" t="n">
-        <v>56.79</v>
+        <v>221.64</v>
       </c>
       <c r="D219" s="4" t="n">
-        <v>48.94</v>
+        <v>49.25</v>
       </c>
       <c r="E219" s="4" t="n">
-        <v>52.86</v>
+        <v>43.48</v>
       </c>
       <c r="F219" s="4" t="n">
-        <v>58.48</v>
+        <v>48.59</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>RELIGARE</t>
+          <t>SAMHI</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -6274,22 +6314,22 @@
         </is>
       </c>
       <c r="C220" s="4" t="n">
-        <v>220.48</v>
+        <v>156.27</v>
       </c>
       <c r="D220" s="4" t="n">
-        <v>48.81</v>
+        <v>49.15</v>
       </c>
       <c r="E220" s="4" t="n">
-        <v>43.47</v>
+        <v>42.7</v>
       </c>
       <c r="F220" s="4" t="n">
-        <v>48.34</v>
+        <v>44.58</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>WESTLIFE</t>
+          <t>FINEORG</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -6298,22 +6338,22 @@
         </is>
       </c>
       <c r="C221" s="4" t="n">
-        <v>462.75</v>
+        <v>4628.1</v>
       </c>
       <c r="D221" s="4" t="n">
-        <v>48.67</v>
+        <v>49.07</v>
       </c>
       <c r="E221" s="4" t="n">
-        <v>36.01</v>
+        <v>53.51</v>
       </c>
       <c r="F221" s="4" t="n">
-        <v>30.66</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>JAMNAAUTO</t>
+          <t>PGIL</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -6322,22 +6362,22 @@
         </is>
       </c>
       <c r="C222" s="4" t="n">
-        <v>122.99</v>
+        <v>1535.8</v>
       </c>
       <c r="D222" s="4" t="n">
-        <v>48.65</v>
+        <v>48.78</v>
       </c>
       <c r="E222" s="4" t="n">
-        <v>52.05</v>
+        <v>51.33</v>
       </c>
       <c r="F222" s="4" t="n">
-        <v>55.43</v>
+        <v>60.34</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>GPPL</t>
+          <t>KITEX</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -6346,22 +6386,22 @@
         </is>
       </c>
       <c r="C223" s="4" t="n">
-        <v>154.56</v>
+        <v>164.49</v>
       </c>
       <c r="D223" s="4" t="n">
-        <v>48.65</v>
+        <v>48.13</v>
       </c>
       <c r="E223" s="4" t="n">
-        <v>44.37</v>
+        <v>43.8</v>
       </c>
       <c r="F223" s="4" t="n">
-        <v>50.47</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>CSBBANK</t>
+          <t>PRICOLLTD</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -6370,22 +6410,22 @@
         </is>
       </c>
       <c r="C224" s="4" t="n">
-        <v>382.65</v>
+        <v>572.75</v>
       </c>
       <c r="D224" s="4" t="n">
-        <v>48.47</v>
+        <v>48</v>
       </c>
       <c r="E224" s="4" t="n">
-        <v>47.37</v>
+        <v>50.93</v>
       </c>
       <c r="F224" s="4" t="n">
-        <v>52.8</v>
+        <v>58.04</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>DATAMATICS</t>
+          <t>ARVINDFASN</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -6394,22 +6434,22 @@
         </is>
       </c>
       <c r="C225" s="4" t="n">
-        <v>707.4</v>
+        <v>443.15</v>
       </c>
       <c r="D225" s="4" t="n">
-        <v>48.2</v>
+        <v>47.98</v>
       </c>
       <c r="E225" s="4" t="n">
-        <v>44.76</v>
+        <v>47.28</v>
       </c>
       <c r="F225" s="4" t="n">
-        <v>51.25</v>
+        <v>48.39</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>ETHOSLTD</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -6418,22 +6458,22 @@
         </is>
       </c>
       <c r="C226" s="4" t="n">
-        <v>1113.8</v>
+        <v>2401.8</v>
       </c>
       <c r="D226" s="4" t="n">
-        <v>48.02</v>
+        <v>47.81</v>
       </c>
       <c r="E226" s="4" t="n">
-        <v>61.66</v>
+        <v>46.28</v>
       </c>
       <c r="F226" s="4" t="n">
-        <v>67.22</v>
+        <v>48.64</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>SENCO</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -6442,22 +6482,22 @@
         </is>
       </c>
       <c r="C227" s="4" t="n">
-        <v>428.65</v>
+        <v>313.1</v>
       </c>
       <c r="D227" s="4" t="n">
-        <v>47.78</v>
+        <v>47.74</v>
       </c>
       <c r="E227" s="4" t="n">
-        <v>44.96</v>
+        <v>48.05</v>
       </c>
       <c r="F227" s="4" t="n">
-        <v>50.34</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>SFL</t>
+          <t>EDELWEISS</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -6466,22 +6506,22 @@
         </is>
       </c>
       <c r="C228" s="4" t="n">
-        <v>523.25</v>
+        <v>114.25</v>
       </c>
       <c r="D228" s="4" t="n">
-        <v>47.74</v>
+        <v>47.64</v>
       </c>
       <c r="E228" s="4" t="n">
-        <v>40.49</v>
+        <v>53.01</v>
       </c>
       <c r="F228" s="4" t="n">
-        <v>36.24</v>
+        <v>57.29</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>CELLO</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -6490,22 +6530,22 @@
         </is>
       </c>
       <c r="C229" s="4" t="n">
-        <v>3799.3</v>
+        <v>417.5</v>
       </c>
       <c r="D229" s="4" t="n">
         <v>47.64</v>
       </c>
       <c r="E229" s="4" t="n">
-        <v>58.02</v>
+        <v>34.92</v>
       </c>
       <c r="F229" s="4" t="n">
-        <v>71.59999999999999</v>
+        <v>31.86</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>KITEX</t>
+          <t>CSBBANK</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -6514,22 +6554,22 @@
         </is>
       </c>
       <c r="C230" s="4" t="n">
-        <v>163.63</v>
+        <v>381.95</v>
       </c>
       <c r="D230" s="4" t="n">
-        <v>47.34</v>
+        <v>47.62</v>
       </c>
       <c r="E230" s="4" t="n">
-        <v>43.64</v>
+        <v>48.07</v>
       </c>
       <c r="F230" s="4" t="n">
-        <v>49.47</v>
+        <v>52.71</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>CIEINDIA</t>
+          <t>ZAGGLE</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -6538,16 +6578,16 @@
         </is>
       </c>
       <c r="C231" s="4" t="n">
-        <v>457.2</v>
+        <v>240.76</v>
       </c>
       <c r="D231" s="4" t="n">
-        <v>46.94</v>
+        <v>47.21</v>
       </c>
       <c r="E231" s="4" t="n">
-        <v>55.55</v>
+        <v>38.81</v>
       </c>
       <c r="F231" s="4" t="n">
-        <v>54.57</v>
+        <v>42.32</v>
       </c>
     </row>
     <row r="232">
@@ -6562,22 +6602,22 @@
         </is>
       </c>
       <c r="C232" s="4" t="n">
-        <v>907.9</v>
+        <v>909.5</v>
       </c>
       <c r="D232" s="4" t="n">
-        <v>46.88</v>
+        <v>47.14</v>
       </c>
       <c r="E232" s="4" t="n">
-        <v>40.6</v>
+        <v>41.65</v>
       </c>
       <c r="F232" s="4" t="n">
-        <v>38.75</v>
+        <v>38.83</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>GRINFRA</t>
+          <t>RAYMONDLSL</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -6586,22 +6626,22 @@
         </is>
       </c>
       <c r="C233" s="4" t="n">
-        <v>866.45</v>
+        <v>794.2</v>
       </c>
       <c r="D233" s="4" t="n">
-        <v>46.72</v>
+        <v>46.93</v>
       </c>
       <c r="E233" s="4" t="n">
-        <v>36.11</v>
+        <v>38.59</v>
       </c>
       <c r="F233" s="4" t="n">
-        <v>37.03</v>
+        <v>22.93</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>JISLJALEQS</t>
+          <t>SHAREINDIA</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -6610,22 +6650,22 @@
         </is>
       </c>
       <c r="C234" s="4" t="n">
-        <v>31.36</v>
+        <v>137.45</v>
       </c>
       <c r="D234" s="4" t="n">
-        <v>46.3</v>
+        <v>46.88</v>
       </c>
       <c r="E234" s="4" t="n">
-        <v>33.87</v>
+        <v>43.72</v>
       </c>
       <c r="F234" s="4" t="n">
-        <v>35.82</v>
+        <v>39.99</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>HEMIPROP</t>
+          <t>JAMNAAUTO</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -6634,22 +6674,22 @@
         </is>
       </c>
       <c r="C235" s="4" t="n">
-        <v>125.49</v>
+        <v>121.56</v>
       </c>
       <c r="D235" s="4" t="n">
-        <v>46.22</v>
+        <v>46.54</v>
       </c>
       <c r="E235" s="4" t="n">
-        <v>44.13</v>
+        <v>51.09</v>
       </c>
       <c r="F235" s="4" t="n">
-        <v>45.11</v>
+        <v>55.01</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>TEGA</t>
+          <t>CIGNITITEC</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -6658,22 +6698,22 @@
         </is>
       </c>
       <c r="C236" s="4" t="n">
-        <v>1680.1</v>
+        <v>1182.2</v>
       </c>
       <c r="D236" s="4" t="n">
-        <v>45.82</v>
+        <v>46.35</v>
       </c>
       <c r="E236" s="4" t="n">
-        <v>42.79</v>
+        <v>39.34</v>
       </c>
       <c r="F236" s="4" t="n">
-        <v>53.19</v>
+        <v>44.57</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>SANOFI</t>
+          <t>GARFIBRES</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -6682,22 +6722,22 @@
         </is>
       </c>
       <c r="C237" s="4" t="n">
-        <v>3427.6</v>
+        <v>614.75</v>
       </c>
       <c r="D237" s="4" t="n">
-        <v>45.67</v>
+        <v>45.12</v>
       </c>
       <c r="E237" s="4" t="n">
-        <v>30.76</v>
+        <v>41</v>
       </c>
       <c r="F237" s="4" t="n">
-        <v>31.54</v>
+        <v>38.83</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>AURIONPRO</t>
+          <t>TEGA</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -6706,22 +6746,22 @@
         </is>
       </c>
       <c r="C238" s="4" t="n">
-        <v>831.45</v>
+        <v>1663.4</v>
       </c>
       <c r="D238" s="4" t="n">
-        <v>45.1</v>
+        <v>44.62</v>
       </c>
       <c r="E238" s="4" t="n">
-        <v>37.8</v>
+        <v>42.63</v>
       </c>
       <c r="F238" s="4" t="n">
-        <v>41.03</v>
+        <v>52.68</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>EMBDL</t>
+          <t>IXIGO</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
@@ -6730,22 +6770,22 @@
         </is>
       </c>
       <c r="C239" s="4" t="n">
-        <v>47.7</v>
+        <v>168.08</v>
       </c>
       <c r="D239" s="4" t="n">
-        <v>44.95</v>
+        <v>44.45</v>
       </c>
       <c r="E239" s="4" t="n">
-        <v>34.64</v>
+        <v>38.09</v>
       </c>
       <c r="F239" s="4" t="n">
-        <v>31.34</v>
+        <v>42.92</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>KNRCON</t>
+          <t>SANOFI</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -6754,22 +6794,22 @@
         </is>
       </c>
       <c r="C240" s="4" t="n">
-        <v>117.93</v>
+        <v>3407.2</v>
       </c>
       <c r="D240" s="4" t="n">
-        <v>44.4</v>
+        <v>44.06</v>
       </c>
       <c r="E240" s="4" t="n">
-        <v>35.56</v>
+        <v>30.98</v>
       </c>
       <c r="F240" s="4" t="n">
-        <v>31.76</v>
+        <v>30.61</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>LUMAXTECH</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
@@ -6778,22 +6818,22 @@
         </is>
       </c>
       <c r="C241" s="4" t="n">
-        <v>97.13</v>
+        <v>1621.4</v>
       </c>
       <c r="D241" s="4" t="n">
-        <v>43.76</v>
+        <v>43.87</v>
       </c>
       <c r="E241" s="4" t="n">
-        <v>36.77</v>
+        <v>54.72</v>
       </c>
       <c r="F241" s="4" t="n">
-        <v>37.97</v>
+        <v>68.29000000000001</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>RAYMONDLSL</t>
+          <t>SFL</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -6802,22 +6842,22 @@
         </is>
       </c>
       <c r="C242" s="4" t="n">
-        <v>779.7</v>
+        <v>509.05</v>
       </c>
       <c r="D242" s="4" t="n">
-        <v>43.71</v>
+        <v>43.66</v>
       </c>
       <c r="E242" s="4" t="n">
-        <v>36.76</v>
+        <v>38.68</v>
       </c>
       <c r="F242" s="4" t="n">
-        <v>21.97</v>
+        <v>35.18</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>IXIGO</t>
+          <t>JUSTDIAL</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -6826,22 +6866,22 @@
         </is>
       </c>
       <c r="C243" s="4" t="n">
-        <v>166.7</v>
+        <v>525.95</v>
       </c>
       <c r="D243" s="4" t="n">
-        <v>43.04</v>
+        <v>42.6</v>
       </c>
       <c r="E243" s="4" t="n">
-        <v>38.2</v>
+        <v>33.18</v>
       </c>
       <c r="F243" s="4" t="n">
-        <v>42.61</v>
+        <v>34.68</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>JUSTDIAL</t>
+          <t>EMBDL</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -6850,22 +6890,22 @@
         </is>
       </c>
       <c r="C244" s="4" t="n">
-        <v>527.4</v>
+        <v>46.28</v>
       </c>
       <c r="D244" s="4" t="n">
-        <v>42.69</v>
+        <v>42.52</v>
       </c>
       <c r="E244" s="4" t="n">
-        <v>32.42</v>
+        <v>33.76</v>
       </c>
       <c r="F244" s="4" t="n">
-        <v>34.79</v>
+        <v>30.65</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>VINATIORGA</t>
+          <t>CMSINFO</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
@@ -6874,22 +6914,22 @@
         </is>
       </c>
       <c r="C245" s="4" t="n">
-        <v>1280.6</v>
+        <v>290.35</v>
       </c>
       <c r="D245" s="4" t="n">
-        <v>42.44</v>
+        <v>41.93</v>
       </c>
       <c r="E245" s="4" t="n">
-        <v>28.15</v>
+        <v>37.28</v>
       </c>
       <c r="F245" s="4" t="n">
-        <v>34.8</v>
+        <v>37.06</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>CARTRADE</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -6898,22 +6938,22 @@
         </is>
       </c>
       <c r="C246" s="4" t="n">
-        <v>1694.3</v>
+        <v>93.55</v>
       </c>
       <c r="D246" s="4" t="n">
-        <v>41.76</v>
+        <v>40.16</v>
       </c>
       <c r="E246" s="4" t="n">
-        <v>36.97</v>
+        <v>35.34</v>
       </c>
       <c r="F246" s="4" t="n">
-        <v>48.84</v>
+        <v>36.84</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>MAHLIFE</t>
+          <t>BLACKBUCK</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
@@ -6922,22 +6962,22 @@
         </is>
       </c>
       <c r="C247" s="4" t="n">
-        <v>317.9</v>
+        <v>548.05</v>
       </c>
       <c r="D247" s="4" t="n">
-        <v>41.27</v>
+        <v>38.41</v>
       </c>
       <c r="E247" s="4" t="n">
-        <v>37.6</v>
+        <v>44.24</v>
       </c>
       <c r="F247" s="4" t="n">
-        <v>39.79</v>
+        <v>51.95</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>CIGNITITEC</t>
+          <t>CCAVENUE</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -6946,22 +6986,22 @@
         </is>
       </c>
       <c r="C248" s="4" t="n">
-        <v>1136.2</v>
+        <v>13.74</v>
       </c>
       <c r="D248" s="4" t="n">
-        <v>39.67</v>
+        <v>37.5</v>
       </c>
       <c r="E248" s="4" t="n">
-        <v>36.18</v>
+        <v/>
       </c>
       <c r="F248" s="4" t="n">
-        <v>43.17</v>
+        <v/>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>CCAVENUE</t>
+          <t>CARTRADE</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
@@ -6970,22 +7010,22 @@
         </is>
       </c>
       <c r="C249" s="4" t="n">
-        <v>13.98</v>
+        <v>1623.4</v>
       </c>
       <c r="D249" s="4" t="n">
-        <v>39.25</v>
+        <v>37.31</v>
       </c>
       <c r="E249" s="4" t="n">
-        <v/>
+        <v>35.4</v>
       </c>
       <c r="F249" s="4" t="n">
-        <v/>
+        <v>47.54</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>SAFARI</t>
+          <t>VIPIND</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
@@ -6994,22 +7034,22 @@
         </is>
       </c>
       <c r="C250" s="4" t="n">
-        <v>1470</v>
+        <v>296.25</v>
       </c>
       <c r="D250" s="4" t="n">
-        <v>38.7</v>
+        <v>33.89</v>
       </c>
       <c r="E250" s="4" t="n">
-        <v>31.94</v>
+        <v>31.71</v>
       </c>
       <c r="F250" s="4" t="n">
-        <v>39.07</v>
+        <v>34.65</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>VIPIND</t>
+          <t>SAFARI</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
@@ -7018,16 +7058,16 @@
         </is>
       </c>
       <c r="C251" s="4" t="n">
-        <v>299.3</v>
+        <v>1412.5</v>
       </c>
       <c r="D251" s="4" t="n">
-        <v>34.16</v>
+        <v>33.58</v>
       </c>
       <c r="E251" s="4" t="n">
-        <v>32.61</v>
+        <v>30.09</v>
       </c>
       <c r="F251" s="4" t="n">
-        <v>34.9</v>
+        <v>37.7</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Micro250_stocks.xlsx
+++ b/reports/Micro250_stocks.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -537,7 +537,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>MTARTECH</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -546,31 +546,31 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>6457.1</v>
+        <v>375.95</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>85.84999999999999</v>
+        <v>85.47</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>88.94</v>
+        <v>91.27</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>84.72</v>
+        <v>83.93000000000001</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>24.19</v>
+        <v>21.74</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>3213.18</v>
+        <v>172.4</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>2955.17</v>
+        <v>159.23</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>690324</v>
+        <v>7017711</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>20547</v>
+        <v>18351</v>
       </c>
     </row>
     <row r="3">
@@ -585,37 +585,37 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>3360.1</v>
+        <v>3487.9</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>75.44</v>
+        <v>80.56999999999999</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>66.92</v>
+        <v>69.94</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>69.93000000000001</v>
+        <v>71.25</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>22.84</v>
+        <v>20.85</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>2843.94</v>
+        <v>2887.47</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>2749.55</v>
+        <v>2787.18</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>104134</v>
+        <v>107278</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>13104</v>
+        <v>13625</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -624,37 +624,37 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>268.61</v>
+        <v>1387</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>73.31999999999999</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>78.16</v>
+        <v>70.56</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>67.91</v>
+        <v>69.79000000000001</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>27.2</v>
+        <v>33.21</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>209.44</v>
+        <v>982.39</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>205.24</v>
+        <v>960.4</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>3838377</v>
+        <v>447675</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>10152</v>
+        <v>9260</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>SKYGOLD</t>
+          <t>STAR</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -663,37 +663,37 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>453.9</v>
+        <v>1156.9</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>72.2</v>
+        <v>76.48</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>69.42</v>
+        <v>71.95</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>66.89</v>
+        <v>62.76</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>20.79</v>
+        <v>24.9</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>349.23</v>
+        <v>922.98</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>342.51</v>
+        <v>910.72</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>895727</v>
+        <v>296780</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>7002</v>
+        <v>10663</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>ARVIND</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -702,37 +702,37 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>398.55</v>
+        <v>222.81</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>64.39</v>
+        <v>75.29000000000001</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>63.78</v>
+        <v>76.62</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>62.66</v>
+        <v>67.91</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>28.47</v>
+        <v>20.16</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>347.02</v>
+        <v>171.96</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>344.27</v>
+        <v>170.35</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>331319</v>
+        <v>2326753</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>10415</v>
+        <v>6595</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>GAEL</t>
+          <t>GRWRHITECH</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -741,37 +741,37 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>155.75</v>
+        <v>5290.3</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>61.08</v>
+        <v>75.12</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>65.78</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>62.2</v>
+        <v>62.81</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>40.8</v>
+        <v>21.6</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>131.43</v>
+        <v>3754.51</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>128.76</v>
+        <v>3699.67</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>926648</v>
+        <v>136256</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>7132</v>
+        <v>12291</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ANURAS</t>
+          <t>SANDUMA</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -780,37 +780,37 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1343.8</v>
+        <v>241.11</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>61.04</v>
+        <v>74.12</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>63.5</v>
+        <v>61.78</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>69.73999999999999</v>
+        <v>63.51</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>21.03</v>
+        <v>49.55</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1224.86</v>
+        <v>201.29</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1189.05</v>
+        <v>197.02</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>218109</v>
+        <v>2467898</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>15283</v>
+        <v>11720</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>STAR</t>
+          <t>GAEL</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -819,37 +819,37 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1036.8</v>
+        <v>166.46</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>60.13</v>
+        <v>70.16</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>63.91</v>
+        <v>70.54000000000001</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>58.61</v>
+        <v>65.48</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>27.69</v>
+        <v>27.38</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>909.3200000000001</v>
+        <v>133.55</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>900.24</v>
+        <v>130.46</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>303173</v>
+        <v>1031500</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>9562</v>
+        <v>7635</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>SHRIPISTON</t>
+          <t>ARVIND</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -858,37 +858,37 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>3491.1</v>
+        <v>435</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>56.42</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>60.9</v>
+        <v>70.47</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>71.87</v>
+        <v>66.31</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>34.66</v>
+        <v>25.25</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2972.56</v>
+        <v>351.98</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2872.39</v>
+        <v>348.4</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>129049</v>
+        <v>765911</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>15431</v>
+        <v>11402</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>ANURAS</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -897,37 +897,37 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1171.8</v>
+        <v>1372.1</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>56.29</v>
+        <v>66.05</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>65.67</v>
+        <v>66.28</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>69.7</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>42.72</v>
+        <v>23.21</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>973.97</v>
+        <v>1233.63</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>944.1</v>
+        <v>1197.24</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>417200</v>
+        <v>283910</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>15582</v>
+        <v>15621</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>IMFA</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -936,37 +936,37 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1502.6</v>
+        <v>4246.7</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>55.61</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>62.35</v>
+        <v>64.13</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>69.79000000000001</v>
+        <v>74.89</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>24.69</v>
+        <v>27.26</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1245.08</v>
+        <v>3359.94</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1187.11</v>
+        <v>3168.9</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>224153</v>
+        <v>108481</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>8093</v>
+        <v>13200</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>GALLANTT</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -975,31 +975,343 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>3955.8</v>
+        <v>869.25</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>53.51</v>
+        <v>64.81</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>60.22</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>72.79000000000001</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>36.94</v>
+        <v>21.05</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>3301.64</v>
+        <v>628.92</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>3114.43</v>
+        <v>605.46</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>110315</v>
+        <v>6022576</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>12284</v>
+        <v>20973</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>UJJIVANSFB</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>61.35</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>62.08</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>35.12</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>55.18</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>15758015</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>12133</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>ASTRAMICRO</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>1147.4</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>62.94</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>64.25</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>55.42</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>993.35</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>981.02</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>444790</v>
+      </c>
+      <c r="K15" s="4" t="n">
+        <v>10894</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>EDELWEISS</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>125.14</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>62.36</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>60.97</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>60.77</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>37.97</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>111.48</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>110.17</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>5445843</v>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>11845</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>SANSERA</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>2519.8</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>59.41</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>70.02</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>72.95999999999999</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>20.77</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>1974.93</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>1873.51</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>235693</v>
+      </c>
+      <c r="K17" s="4" t="n">
+        <v>15706</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>IMFA</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>1548.1</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>59.03</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>64.31999999999999</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>70.69</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>32.81</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>1262.33</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>1203.32</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>263287</v>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>8353</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>AETHER</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>1213.4</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>58.39</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>68.01000000000001</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>71.38</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>992.71</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>960.01</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>402172</v>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>16099</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>AVANTIFEED</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>1435.2</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>58.35</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>76.23999999999999</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>27.93</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>1074.76</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>1011.23</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>1107422</v>
+      </c>
+      <c r="K20" s="4" t="n">
+        <v>19554</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>KTKBANK</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>259.35</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>57.57</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>71.33</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>65.02</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>22.79</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>213.89</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>208.77</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>3266548</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>9808</v>
       </c>
     </row>
   </sheetData>
@@ -1016,6 +1328,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1073,7 +1393,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>MTARTECH</t>
+          <t>SUNFLAG</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -1082,22 +1402,22 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>6457.1</v>
+        <v>415.85</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>85.84999999999999</v>
+        <v>88.93000000000001</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>88.94</v>
+        <v>80.28</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>84.72</v>
+        <v>69.03</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>CEMPRO</t>
+          <t>SKYGOLD</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -1106,22 +1426,22 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>815.25</v>
+        <v>541.25</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>80.61</v>
+        <v>85.62</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>67.3</v>
+        <v>77.51000000000001</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v/>
+        <v>71.75</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>VOLTAMP</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -1130,22 +1450,22 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>11742</v>
+        <v>375.95</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>80.59999999999999</v>
+        <v>85.47</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>77.28</v>
+        <v>91.27</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>64.09</v>
+        <v>83.93000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KIRLPNU</t>
+          <t>MANINFRA</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -1154,22 +1474,22 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1503.3</v>
+        <v>134.73</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>79.34</v>
+        <v>85.31</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>75.17</v>
+        <v>60.91</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>62.41</v>
+        <v>47.83</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>CEIGALL</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -1178,22 +1498,22 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1152.7</v>
+        <v>376.8</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>78.83</v>
+        <v>83.51000000000001</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>76.7</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>81.95</v>
+        <v>68.39</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>INGERRAND</t>
+          <t>THYROCARE</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1202,22 +1522,22 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4417.7</v>
+        <v>486.5</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>78.69</v>
+        <v>81.78</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>67.45999999999999</v>
+        <v>65.83</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>61.53</v>
+        <v>63.49</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>MANINFRA</t>
+          <t>INDIAGLYCO</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1226,22 +1546,22 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>120.35</v>
+        <v>1150.4</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>77.15000000000001</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>53.45</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>44.27</v>
+        <v>65.34</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>CEIGALL</t>
+          <t>PRIVISCL</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -1250,22 +1570,22 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>338.6</v>
+        <v>3487.9</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>76.01000000000001</v>
+        <v>80.56999999999999</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>73.70999999999999</v>
+        <v>69.94</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>61.28</v>
+        <v>71.25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ADVENZYMES</t>
+          <t>AZAD</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1274,22 +1594,22 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>347.7</v>
+        <v>2315.6</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>75.69</v>
+        <v>80.38</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>63.27</v>
+        <v>75.81999999999999</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>53.81</v>
+        <v>67.27</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>PRIVISCL</t>
+          <t>CYIENTDLM</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -1298,22 +1618,22 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>3360.1</v>
+        <v>432.9</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>75.44</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>66.92</v>
+        <v>62.19</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>69.93000000000001</v>
+        <v>45.82</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>AZAD</t>
+          <t>ORCHPHARMA</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1322,22 +1642,22 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2164.9</v>
+        <v>703.45</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>74.93000000000001</v>
+        <v>79.37</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>72.79000000000001</v>
+        <v>55.39</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>64.95</v>
+        <v>46.72</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>KSL</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1346,22 +1666,22 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>849.7</v>
+        <v>1387</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>74.88</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>63.03</v>
+        <v>70.56</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>54.43</v>
+        <v>69.79000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>CEMPRO</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1370,22 +1690,22 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>207.7</v>
+        <v>956.15</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>74.84999999999999</v>
+        <v>78.42</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>73.22</v>
+        <v>75.61</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>64.95999999999999</v>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>BALAMINES</t>
+          <t>INNOVACAP</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1394,22 +1714,22 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1333.65</v>
+        <v>875.75</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>73.72</v>
+        <v>78.34</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>61.99</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>44.02</v>
+        <v>59.31</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>BBL</t>
+          <t>PNGJL</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1418,22 +1738,22 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>3096.8</v>
+        <v>727.9</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>73.40000000000001</v>
+        <v>77.43000000000001</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>61.8</v>
+        <v>71.53</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>53.27</v>
+        <v>62.73</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>RATNAMANI</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1442,22 +1762,22 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>268.61</v>
+        <v>2869.4</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>73.31999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>78.16</v>
+        <v>67.56</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>67.91</v>
+        <v>54.89</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>HCC</t>
+          <t>RBA</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1466,22 +1786,22 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>22.04</v>
+        <v>68.09</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>73.22</v>
+        <v>77.22</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>56.37</v>
+        <v>55.69</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>46.16</v>
+        <v>41.03</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>STAR</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1490,22 +1810,22 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>294.8</v>
+        <v>1156.9</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>72.66</v>
+        <v>76.48</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>87.06999999999999</v>
+        <v>71.95</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>79.12</v>
+        <v>62.76</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>EMIL</t>
+          <t>INGERRAND</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1514,22 +1834,22 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>124.34</v>
+        <v>4575.3</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>72.48999999999999</v>
+        <v>76.45</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>62.21</v>
+        <v>69.92</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>47.8</v>
+        <v>63.14</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>SKYGOLD</t>
+          <t>BALAMINES</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1538,22 +1858,22 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>453.9</v>
+        <v>1487.2</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>72.2</v>
+        <v>76.38</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>69.42</v>
+        <v>69.36</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>66.89</v>
+        <v>47.84</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>INDIAGLYCO</t>
+          <t>TDPOWERSYS</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1562,22 +1882,22 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1042.05</v>
+        <v>1219.6</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>71.95</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>61.75</v>
+        <v>78.66</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>62.17</v>
+        <v>83.19</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>SKIPPER</t>
+          <t>NEOGEN</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1586,22 +1906,22 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>478.45</v>
+        <v>1772.4</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>71.09999999999999</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>62.01</v>
+        <v>66.79000000000001</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>57.14</v>
+        <v>55.86</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>CYIENTDLM</t>
+          <t>MIDHANI</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1610,22 +1930,22 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>393.1</v>
+        <v>421.25</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>70.73</v>
+        <v>75.73999999999999</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>55.95</v>
+        <v>65.13</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>42.11</v>
+        <v>56.18</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>ISGEC</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1634,22 +1954,22 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1088.95</v>
+        <v>222.81</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>70.62</v>
+        <v>75.29000000000001</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>67.73999999999999</v>
+        <v>76.62</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>54.1</v>
+        <v>67.91</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>AHLUCONT</t>
+          <t>ADVENZYMES</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1658,22 +1978,22 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>891</v>
+        <v>357.25</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>70.31</v>
+        <v>75.23</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>54.56</v>
+        <v>65.48</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>50.18</v>
+        <v>55.04</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>SHAILY</t>
+          <t>GABRIEL</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1682,22 +2002,22 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2532.6</v>
+        <v>1131.9</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>69.34</v>
+        <v>75.14</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>60.68</v>
+        <v>61.16</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>67.04000000000001</v>
+        <v>65.34</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>EPIGRAL</t>
+          <t>GRWRHITECH</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1706,22 +2026,22 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1215.65</v>
+        <v>5290.3</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>69.23</v>
+        <v>75.12</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>51.02</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>44.96</v>
+        <v>62.81</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>YATHARTH</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1730,22 +2050,22 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1295.35</v>
+        <v>862.2</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>69.11</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>73.13</v>
+        <v>66.81</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>68.92</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>BALUFORGE</t>
+          <t>LXCHEM</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1754,22 +2074,22 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>541.4</v>
+        <v>164.84</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>68.81999999999999</v>
+        <v>74.48999999999999</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>54.25</v>
+        <v>57.73</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>50.81</v>
+        <v>42.89</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>WEBELSOLAR</t>
+          <t>SHAILY</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1778,22 +2098,22 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>110.66</v>
+        <v>2679.2</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>68.78</v>
+        <v>74.18000000000001</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>61.94</v>
+        <v>63.59</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>54.86</v>
+        <v>68.79000000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>SUNFLAG</t>
+          <t>SANDUMA</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1802,22 +2122,22 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>292.61</v>
+        <v>241.11</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>68.51000000000001</v>
+        <v>74.12</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>63.25</v>
+        <v>61.78</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>58.23</v>
+        <v>63.51</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>YATHARTH</t>
+          <t>HEMIPROP</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1826,22 +2146,22 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>820</v>
+        <v>154.21</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>68.36</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>63.75</v>
+        <v>60.17</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>63.04</v>
+        <v>53.09</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>KSCL</t>
+          <t>INDIGOPNTS</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1850,22 +2170,22 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>965.35</v>
+        <v>974.15</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>68.33</v>
+        <v>73.94</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>55.57</v>
+        <v>51.29</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>51.51</v>
+        <v>44.05</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>NEOGEN</t>
+          <t>MTARTECH</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1874,22 +2194,22 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1637.5</v>
+        <v>6470</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>68.3</v>
+        <v>73.83</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>62.21</v>
+        <v>88.38</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>53.27</v>
+        <v>84.75</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>PRUDENT</t>
+          <t>QUESS</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1898,22 +2218,22 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>2826.1</v>
+        <v>223.59</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>68.01000000000001</v>
+        <v>73.56</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>61.72</v>
+        <v>56.52</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>59.68</v>
+        <v>35.95</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GREENPANEL</t>
+          <t>BORORENEW</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1922,22 +2242,22 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>228.91</v>
+        <v>561.75</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>67.92</v>
+        <v>73.38</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>51.76</v>
+        <v>58.86</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>43.12</v>
+        <v>53.49</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>TIPSMUSIC</t>
+          <t>KIRLPNU</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -1946,22 +2266,22 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>649.7</v>
+        <v>1560.2</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>67.78</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>64.22</v>
+        <v>77.64</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>59.36</v>
+        <v>63.77</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>RATNAMANI</t>
+          <t>SPARC</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1970,22 +2290,22 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>2645</v>
+        <v>173.09</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>67.67</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>61.28</v>
+        <v>67.41</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>50.72</v>
+        <v>50.81</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GALLANTT</t>
+          <t>IIFLCAPS</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -1994,22 +2314,22 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>861.85</v>
+        <v>356.3</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>67.56</v>
+        <v>72.7</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>72.81999999999999</v>
+        <v>60.22</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>70.29000000000001</v>
+        <v>56.64</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>ORCHPHARMA</t>
+          <t>LLOYDSENGG</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -2018,22 +2338,22 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>625.75</v>
+        <v>62.87</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>67.54000000000001</v>
+        <v>72.41</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>46.52</v>
+        <v>62.82</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>43.87</v>
+        <v>53.03</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>RBA</t>
+          <t>EMBDL</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -2042,22 +2362,22 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>65.36</v>
+        <v>69.98</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>67.25</v>
+        <v>72.39</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>50.54</v>
+        <v>54.54</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>38.61</v>
+        <v>41.33</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>REFEX</t>
+          <t>RATEGAIN</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -2066,22 +2386,22 @@
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>263.86</v>
+        <v>634.75</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>67.23999999999999</v>
+        <v>71.97</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>50.62</v>
+        <v>58.89</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>47.06</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>WABAG</t>
+          <t>SENCO</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -2090,22 +2410,22 @@
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>1509.6</v>
+        <v>365.4</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>67.14</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>64.67</v>
+        <v>60.5</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>57.99</v>
+        <v>51.47</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENGG</t>
+          <t>AWFIS</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -2114,22 +2434,22 @@
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>57.77</v>
+        <v>379.15</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>66.89</v>
+        <v>71.47</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>57.58</v>
+        <v>47.57</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>50.2</v>
+        <v>38.13</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>POWERMECH</t>
+          <t>KANSAINER</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -2138,22 +2458,22 @@
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>2481.8</v>
+        <v>220.35</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>66.84</v>
+        <v>71.23999999999999</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>58.56</v>
+        <v>54.93</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>51.65</v>
+        <v>44.28</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENT</t>
+          <t>ALIVUS</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -2162,22 +2482,22 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>68.51000000000001</v>
+        <v>1121.3</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>66.63</v>
+        <v>71.17</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>59.96</v>
+        <v>73.56999999999999</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>56.57</v>
+        <v>69.01000000000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>MANORAMA</t>
+          <t>PARAS</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -2186,22 +2506,22 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>1509</v>
+        <v>866.6</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>66.59999999999999</v>
+        <v>71.06</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>59.81</v>
+        <v>66.05</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>64.7</v>
+        <v>55.37</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>POLYPLEX</t>
+          <t>EPIGRAL</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -2210,22 +2530,22 @@
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>946.2</v>
+        <v>1327.1</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>66.54000000000001</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>58.06</v>
+        <v>58.76</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>46.18</v>
+        <v>47.84</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>SURYAROSNI</t>
+          <t>OPTIEMUS</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -2234,22 +2554,22 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>250.12</v>
+        <v>462.5</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>66.40000000000001</v>
+        <v>70.94</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>52.94</v>
+        <v>53.69</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>48.89</v>
+        <v>49.71</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>MIDHANI</t>
+          <t>POWERMECH</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -2258,22 +2578,22 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>389.9</v>
+        <v>2605.8</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>66.17</v>
+        <v>70.78</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>60.16</v>
+        <v>61.9</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>53.7</v>
+        <v>53.32</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>RATEGAIN</t>
+          <t>HIKAL</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -2282,22 +2602,22 @@
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>602.6</v>
+        <v>210.75</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>65.90000000000001</v>
+        <v>70.73999999999999</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>54.99</v>
+        <v>51.13</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>51.62</v>
+        <v>40.83</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>JAIBALAJI</t>
+          <t>LLOYDSENT</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -2306,22 +2626,22 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>78.29000000000001</v>
+        <v>71.64</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>65.59999999999999</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>53.82</v>
+        <v>62.76</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>43.37</v>
+        <v>58.02</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>DYNAMATECH</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -2330,22 +2650,22 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>740.25</v>
+        <v>12530</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>64.84</v>
+        <v>70.64</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>52.98</v>
+        <v>68.88</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>53.92</v>
+        <v>73.59</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>ALLCARGO</t>
+          <t>ABDL</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -2354,22 +2674,22 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>9.68</v>
+        <v>591.3</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>64.81</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>35.79</v>
+        <v>59.39</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>28.07</v>
+        <v>61.15</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>RTNPOWER</t>
+          <t>EQUITASBNK</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -2378,22 +2698,22 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>10.12</v>
+        <v>72.45</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>64.77</v>
+        <v>70.25</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>56.93</v>
+        <v>63.4</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>49.5</v>
+        <v>53.56</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>RENUKA</t>
+          <t>TEAMLEASE</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -2402,22 +2722,22 @@
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>29.21</v>
+        <v>1354.1</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>64.76000000000001</v>
+        <v>70.22</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>60.01</v>
+        <v>47.05</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>43.87</v>
+        <v>35.38</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>ARVIND</t>
+          <t>GAEL</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -2426,22 +2746,22 @@
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>398.55</v>
+        <v>166.46</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>64.39</v>
+        <v>70.16</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>63.78</v>
+        <v>70.54000000000001</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>62.66</v>
+        <v>65.48</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>INOXGREEN</t>
+          <t>HCC</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -2450,22 +2770,22 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>180.73</v>
+        <v>23.3</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>64.39</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>52.11</v>
+        <v>59.32</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>53.28</v>
+        <v>47.43</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>ASTRAMICRO</t>
+          <t>KSCL</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -2474,22 +2794,22 @@
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>1125.2</v>
+        <v>992.6</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>64.36</v>
+        <v>69.8</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>63.07</v>
+        <v>57.62</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>63.54</v>
+        <v>52.75</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>ACUTAAS</t>
+          <t>JAIBALAJI</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -2498,22 +2818,22 @@
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>2594.1</v>
+        <v>83.53</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>64.33</v>
+        <v>69.77</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>68.26000000000001</v>
+        <v>57.11</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v/>
+        <v>44.92</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>EIEL</t>
+          <t>DATAMATICS</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -2522,22 +2842,22 @@
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>211.94</v>
+        <v>818.4</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>64.31</v>
+        <v>69.77</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>57.35</v>
+        <v>56.74</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>43.72</v>
+        <v>56.1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>VSTIND</t>
+          <t>AJAXENGG</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -2546,22 +2866,22 @@
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>258.37</v>
+        <v>555</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>64.17</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>57.62</v>
+        <v>54.26</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>47.14</v>
+        <v>46.89</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>NESCO</t>
+          <t>ICIL</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -2570,22 +2890,22 @@
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>1227.7</v>
+        <v>306</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>64.13</v>
+        <v>69.55</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>55.69</v>
+        <v>58.31</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>58.79</v>
+        <v>53.64</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>GRINFRA</t>
+          <t>NESCO</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -2594,22 +2914,22 @@
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>937.2</v>
+        <v>1311.3</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>64.05</v>
+        <v>69.54000000000001</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>45.12</v>
+        <v>60.9</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>40.45</v>
+        <v>61.96</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>AGI</t>
+          <t>ARVIND</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -2618,22 +2938,22 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>634</v>
+        <v>435</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>63.83</v>
+        <v>69.48999999999999</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>50.04</v>
+        <v>70.47</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>46.13</v>
+        <v>66.31</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>WELENT</t>
+          <t>ACUTAAS</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -2642,22 +2962,22 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>523.25</v>
+        <v>2734.3</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>63.73</v>
+        <v>69.39</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>58.13</v>
+        <v>70.92</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>55.92</v>
+        <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>INNOVACAP</t>
+          <t>RAIN</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -2666,22 +2986,22 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>752.05</v>
+        <v>143.82</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>63.69</v>
+        <v>69.08</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>53.85</v>
+        <v>56.21</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>51.19</v>
+        <v>50.09</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>SUPRIYA</t>
+          <t>SHILPAMED</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -2690,22 +3010,22 @@
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>694.9</v>
+        <v>437</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>63.61</v>
+        <v>68.88</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>55.54</v>
+        <v>67.22</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>55.9</v>
+        <v>61.73</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>EQUITASBNK</t>
+          <t>TEXRAIL</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -2714,22 +3034,22 @@
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>66.84999999999999</v>
+        <v>114.97</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>63.09</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>57.05</v>
+        <v>50.84</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>50.47</v>
+        <v>45.09</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>VESUVIUS</t>
+          <t>V2RETAIL</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -2738,22 +3058,22 @@
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>519.1</v>
+        <v>219.64</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>63.06</v>
+        <v>68.36</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>56.51</v>
+        <v>57.65</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>57.23</v>
+        <v>65.51000000000001</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>ZYDUSWELL</t>
+          <t>VSTIND</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -2762,22 +3082,22 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>508.55</v>
+        <v>264.4</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>62.94</v>
+        <v>68.06999999999999</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>64.48</v>
+        <v>59.88</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>62.91</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>DIACABS</t>
+          <t>MANORAMA</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -2786,22 +3106,22 @@
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>157.8</v>
+        <v>1576.2</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>62.94</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>62.43</v>
+        <v>63.98</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>60.11</v>
+        <v>66.34</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>RTNINDIA</t>
+          <t>DIACABS</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -2810,22 +3130,22 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>35.52</v>
+        <v>172.85</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>62.93</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>47.9</v>
+        <v>69.23999999999999</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>42</v>
+        <v>62.84</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>STYRENIX</t>
+          <t>PNCINFRA</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -2834,22 +3154,22 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>2260.9</v>
+        <v>224.69</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>62.79</v>
+        <v>67.8</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>56.82</v>
+        <v>49.92</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>53.68</v>
+        <v>41.68</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>PRSMJOHNSN</t>
+          <t>GANESHHOU</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -2858,22 +3178,22 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>133.84</v>
+        <v>714.35</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>62.63</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>52.73</v>
+        <v>52.2</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>46.51</v>
+        <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>DHANUKA</t>
+          <t>KSL</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -2882,22 +3202,22 @@
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>1079.65</v>
+        <v>862.5</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>62.62</v>
+        <v>67.68000000000001</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>45.04</v>
+        <v>63.8</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>44.25</v>
+        <v>54.89</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>DYNAMATECH</t>
+          <t>TVSSCS</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -2906,22 +3226,22 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>11568</v>
+        <v>125.29</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>62.54</v>
+        <v>67.58</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>66.2</v>
+        <v>57.75</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>70.94</v>
+        <v>45.21</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>SANOFICONR</t>
+          <t>GRINFRA</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -2930,22 +3250,22 @@
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>4763.9</v>
+        <v>979.9</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>62.44</v>
+        <v>67.51000000000001</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>56.12</v>
+        <v>50.74</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>49.99</v>
+        <v>42.48</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>TRANSRAILL</t>
+          <t>INOXGREEN</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -2954,22 +3274,22 @@
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>598.95</v>
+        <v>190.61</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>62.43</v>
+        <v>67.43000000000001</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>54.35</v>
+        <v>55.75</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>51.75</v>
+        <v>54.61</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>OSWALPUMPS</t>
+          <t>SURYAROSNI</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -2978,22 +3298,22 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>412.35</v>
+        <v>266</v>
       </c>
       <c r="D81" s="4" t="n">
-        <v>62.33</v>
+        <v>67.23</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>45.17</v>
+        <v>57.28</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v/>
+        <v>50.9</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>GREAVESCOT</t>
+          <t>BALUFORGE</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -3002,22 +3322,22 @@
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>165.18</v>
+        <v>550.05</v>
       </c>
       <c r="D82" s="4" t="n">
-        <v>62.3</v>
+        <v>66.81</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>49.34</v>
+        <v>54.95</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>47.39</v>
+        <v>51.27</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>GABRIEL</t>
+          <t>VMART</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -3026,22 +3346,22 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>1025.6</v>
+        <v>677.8</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>62.3</v>
+        <v>66.58</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>54.69</v>
+        <v>55.51</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>62.16</v>
+        <v>48.38</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>PARAS</t>
+          <t>FDC</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -3050,22 +3370,22 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>794.25</v>
+        <v>380.2</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>61.87</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>60.63</v>
+        <v>50.64</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>52.46</v>
+        <v>46.44</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>JSFB</t>
+          <t>CIGNITITEC</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -3074,22 +3394,22 @@
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>458.15</v>
+        <v>1360</v>
       </c>
       <c r="D85" s="4" t="n">
-        <v>61.77</v>
+        <v>66.41</v>
       </c>
       <c r="E85" s="4" t="n">
-        <v>62.11</v>
+        <v>49.18</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>51.35</v>
+        <v>49.72</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>BAJAJELEC</t>
+          <t>STYRENIX</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -3098,22 +3418,22 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>396.1</v>
+        <v>2334.3</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>61.68</v>
+        <v>66.31999999999999</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>41.69</v>
+        <v>59.53</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>31.22</v>
+        <v>55.13</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>AWFIS</t>
+          <t>ANURAS</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -3122,22 +3442,22 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>351.42</v>
+        <v>1372.1</v>
       </c>
       <c r="D87" s="4" t="n">
-        <v>61.67</v>
+        <v>66.05</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>42.04</v>
+        <v>66.28</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>35.07</v>
+        <v>70.79000000000001</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>SANSERA</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -3146,22 +3466,22 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>2513.6</v>
+        <v>496.15</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>61.54</v>
+        <v>65.98999999999999</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>70.56999999999999</v>
+        <v>57.68</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>72.89</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>DCAL</t>
+          <t>SFL</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -3170,22 +3490,22 @@
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>183.18</v>
+        <v>580.85</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>61.43</v>
+        <v>65.95999999999999</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>44.5</v>
+        <v>52.59</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>46.3</v>
+        <v>40.55</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>BORORENEW</t>
+          <t>ISGEC</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -3194,22 +3514,22 @@
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>501.5</v>
+        <v>1075.1</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>61.39</v>
+        <v>65.73</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>50.67</v>
+        <v>66.31</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>49.42</v>
+        <v>53.54</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>DBL</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -3218,22 +3538,22 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>464.8</v>
+        <v>4246.7</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>61.31</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>52.42</v>
+        <v>64.13</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>52.67</v>
+        <v>74.89</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>GAEL</t>
+          <t>WEBELSOLAR</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -3242,22 +3562,22 @@
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>155.75</v>
+        <v>114.94</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>61.08</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>65.78</v>
+        <v>63.93</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>62.2</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>ANURAS</t>
+          <t>ALLCARGO</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -3266,22 +3586,22 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>1343.8</v>
+        <v>9.81</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>61.04</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>63.5</v>
+        <v>36.67</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>69.73999999999999</v>
+        <v>28.24</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>STARCEMENT</t>
+          <t>CARTRADE</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -3290,22 +3610,22 @@
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>230.29</v>
+        <v>1954.9</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>60.86</v>
+        <v>65.48</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>55.65</v>
+        <v>46.84</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>55.33</v>
+        <v>53.61</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>AJAXENGG</t>
+          <t>SUPRIYA</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -3314,22 +3634,22 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>524.05</v>
+        <v>706.7</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>60.82</v>
+        <v>65.23</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>48.41</v>
+        <v>57.23</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v/>
+        <v>56.61</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>KRBL</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -3338,22 +3658,22 @@
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>367.15</v>
+        <v>217.18</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>60.77</v>
+        <v>65.23</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>54</v>
+        <v>58.66</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>53.5</v>
+        <v>44.95</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>SUDARSCHEM</t>
+          <t>TANLA</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -3362,22 +3682,22 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>914.35</v>
+        <v>564.8</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>60.46</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>47.92</v>
+        <v>60.87</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>48.66</v>
+        <v>47.12</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>KPIGREEN</t>
+          <t>EMUDHRA</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -3386,22 +3706,22 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>447.95</v>
+        <v>519.45</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>60.38</v>
+        <v>65</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>53.92</v>
+        <v>49.48</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>52</v>
+        <v>43.31</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>OPTIEMUS</t>
+          <t>KPIGREEN</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -3410,22 +3730,22 @@
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>415.8</v>
+        <v>476.2</v>
       </c>
       <c r="D99" s="4" t="n">
-        <v>60.29</v>
+        <v>64.83</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>46.54</v>
+        <v>59.25</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>46.96</v>
+        <v>53.91</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>LXCHEM</t>
+          <t>GALLANTT</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -3434,22 +3754,22 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>144.34</v>
+        <v>869.25</v>
       </c>
       <c r="D100" s="4" t="n">
-        <v>60.27</v>
+        <v>64.81</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>47.87</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>37.73</v>
+        <v>70.51000000000001</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>PNGJL</t>
+          <t>ELECTCAST</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -3458,22 +3778,22 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>653.75</v>
+        <v>92.29000000000001</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>60.25</v>
+        <v>64.8</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>61.17</v>
+        <v>61.44</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>54.86</v>
+        <v>47.79</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>STAR</t>
+          <t>VAIBHAVGBL</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -3482,22 +3802,22 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>1036.8</v>
+        <v>235.08</v>
       </c>
       <c r="D102" s="4" t="n">
-        <v>60.13</v>
+        <v>64.78</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>63.91</v>
+        <v>54.86</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>58.61</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>SYMPHONY</t>
+          <t>TIPSMUSIC</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -3506,22 +3826,22 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>846.8</v>
+        <v>648.35</v>
       </c>
       <c r="D103" s="4" t="n">
-        <v>60.1</v>
+        <v>64.72</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>50.31</v>
+        <v>64.59</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>43.7</v>
+        <v>59.23</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>JKIL</t>
+          <t>INDIASHLTR</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -3530,22 +3850,22 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>519.9</v>
+        <v>836.3</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>60.03</v>
+        <v>64.61</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>44.83</v>
+        <v>58.72</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>43.81</v>
+        <v>57.13</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>PNCINFRA</t>
+          <t>PRICOLLTD</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -3554,22 +3874,22 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>213.87</v>
+        <v>622.25</v>
       </c>
       <c r="D105" s="4" t="n">
-        <v>60</v>
+        <v>64.55</v>
       </c>
       <c r="E105" s="4" t="n">
-        <v>44.95</v>
+        <v>58.02</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>39.9</v>
+        <v>61.34</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>SWSOLAR</t>
+          <t>WESTLIFE</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -3578,22 +3898,22 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>208.34</v>
+        <v>505.2</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>59.98</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="E106" s="4" t="n">
-        <v>50.94</v>
+        <v>47.45</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>39.55</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>ROUTE</t>
+          <t>DHANUKA</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -3602,22 +3922,22 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>527.15</v>
+        <v>1100</v>
       </c>
       <c r="D107" s="4" t="n">
-        <v>59.75</v>
+        <v>64.48</v>
       </c>
       <c r="E107" s="4" t="n">
-        <v>39.18</v>
+        <v>47.13</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>29.51</v>
+        <v>44.97</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>EMUDHRA</t>
+          <t>HGINFRA</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -3626,22 +3946,22 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>489.4</v>
+        <v>626.65</v>
       </c>
       <c r="D108" s="4" t="n">
-        <v>59.71</v>
+        <v>64.45</v>
       </c>
       <c r="E108" s="4" t="n">
-        <v>43.06</v>
+        <v>45.76</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>40.9</v>
+        <v>38.97</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>TIMETECHNO</t>
+          <t>DBL</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -3650,22 +3970,22 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>193.01</v>
+        <v>478.75</v>
       </c>
       <c r="D109" s="4" t="n">
-        <v>59.6</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="E109" s="4" t="n">
-        <v>52.77</v>
+        <v>55.55</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>54.38</v>
+        <v>54.17</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>SHILPAMED</t>
+          <t>SHARDAMOTR</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -3674,22 +3994,22 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>406.65</v>
+        <v>909.55</v>
       </c>
       <c r="D110" s="4" t="n">
-        <v>59.42</v>
+        <v>64.27</v>
       </c>
       <c r="E110" s="4" t="n">
-        <v>63.06</v>
+        <v>51.88</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>58.83</v>
+        <v>44.84</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>UNIMECH</t>
+          <t>ZYDUSWELL</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -3698,22 +4018,22 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>1002.4</v>
+        <v>517.5</v>
       </c>
       <c r="D111" s="4" t="n">
-        <v>59.27</v>
+        <v>64.17</v>
       </c>
       <c r="E111" s="4" t="n">
-        <v>57.28</v>
+        <v>65.83</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>46.67</v>
+        <v>63.7</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>INDIASHLTR</t>
+          <t>EPL</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -3722,22 +4042,22 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>809.6</v>
+        <v>238.76</v>
       </c>
       <c r="D112" s="4" t="n">
-        <v>59.06</v>
+        <v>64.03</v>
       </c>
       <c r="E112" s="4" t="n">
-        <v>54.43</v>
+        <v>61.43</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>54.54</v>
+        <v>57.25</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>ANUP</t>
+          <t>GREAVESCOT</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -3746,22 +4066,22 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>2062.2</v>
+        <v>171.36</v>
       </c>
       <c r="D113" s="4" t="n">
-        <v>59.02</v>
+        <v>63.91</v>
       </c>
       <c r="E113" s="4" t="n">
-        <v>52.05</v>
+        <v>51.96</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>49.49</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>ICIL</t>
+          <t>UJJIVANSFB</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -3770,22 +4090,22 @@
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>277.36</v>
+        <v>62.4</v>
       </c>
       <c r="D114" s="4" t="n">
-        <v>58.96</v>
+        <v>63.9</v>
       </c>
       <c r="E114" s="4" t="n">
-        <v>52.97</v>
+        <v>61.35</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>50.02</v>
+        <v>62.08</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>GANESHHOU</t>
+          <t>SWSOLAR</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -3794,22 +4114,22 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>665.55</v>
+        <v>217.26</v>
       </c>
       <c r="D115" s="4" t="n">
-        <v>58.72</v>
+        <v>63.82</v>
       </c>
       <c r="E115" s="4" t="n">
-        <v>42.92</v>
+        <v>53.9</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v/>
+        <v>40.65</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>HERITGFOOD</t>
+          <t>ANUP</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -3818,22 +4138,22 @@
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>358.15</v>
+        <v>2161.9</v>
       </c>
       <c r="D116" s="4" t="n">
-        <v>58.68</v>
+        <v>63.76</v>
       </c>
       <c r="E116" s="4" t="n">
-        <v>43.99</v>
+        <v>56.12</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>46.21</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>GANECOS</t>
+          <t>POLYPLEX</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -3842,22 +4162,22 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>1049.55</v>
+        <v>950.1</v>
       </c>
       <c r="D117" s="4" t="n">
-        <v>58.62</v>
+        <v>63.69</v>
       </c>
       <c r="E117" s="4" t="n">
-        <v>55.55</v>
+        <v>58.35</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>46.46</v>
+        <v>46.36</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>NFL</t>
+          <t>REFEX</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -3866,22 +4186,22 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>77.91</v>
+        <v>263</v>
       </c>
       <c r="D118" s="4" t="n">
-        <v>58.62</v>
+        <v>63.55</v>
       </c>
       <c r="E118" s="4" t="n">
-        <v>47.1</v>
+        <v>50.59</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>45.65</v>
+        <v>46.97</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>GHCL</t>
+          <t>RTNINDIA</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -3890,22 +4210,22 @@
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>506.8</v>
+        <v>37.79</v>
       </c>
       <c r="D119" s="4" t="n">
-        <v>58.26</v>
+        <v>63.54</v>
       </c>
       <c r="E119" s="4" t="n">
-        <v>47.66</v>
+        <v>52.11</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>46.45</v>
+        <v>43.52</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>RALLIS</t>
+          <t>VINATIORGA</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -3914,22 +4234,22 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>265.91</v>
+        <v>1395.1</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>58.24</v>
+        <v>63.47</v>
       </c>
       <c r="E120" s="4" t="n">
-        <v>50.09</v>
+        <v>43.57</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>49.04</v>
+        <v>39.64</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>AARTIDRUGS</t>
+          <t>ASTRAMICRO</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -3938,22 +4258,22 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>376.3</v>
+        <v>1147.4</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>58.22</v>
+        <v>62.94</v>
       </c>
       <c r="E121" s="4" t="n">
-        <v>46.89</v>
+        <v>64.25</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>44.24</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>SHAKTIPUMP</t>
+          <t>IONEXCHANG</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -3962,22 +4282,22 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>564.3</v>
+        <v>419.25</v>
       </c>
       <c r="D122" s="4" t="n">
-        <v>58.21</v>
+        <v>62.91</v>
       </c>
       <c r="E122" s="4" t="n">
-        <v>43.41</v>
+        <v>60.68</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>46.8</v>
+        <v>47.86</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>BELRISE</t>
+          <t>LUXIND</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -3986,22 +4306,22 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>212.72</v>
+        <v>1563.1</v>
       </c>
       <c r="D123" s="4" t="n">
-        <v>58.11</v>
+        <v>62.89</v>
       </c>
       <c r="E123" s="4" t="n">
-        <v>68.86</v>
+        <v>64.87</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v/>
+        <v>54.68</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -4010,22 +4330,22 @@
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>469.3</v>
+        <v>1300.2</v>
       </c>
       <c r="D124" s="4" t="n">
-        <v>58.11</v>
+        <v>62.88</v>
       </c>
       <c r="E124" s="4" t="n">
-        <v>52.46</v>
+        <v>73.23</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>45.89</v>
+        <v>69.04000000000001</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>SUBROS</t>
+          <t>MARKSANS</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -4034,22 +4354,22 @@
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>778.55</v>
+        <v>197.76</v>
       </c>
       <c r="D125" s="4" t="n">
-        <v>57.96</v>
+        <v>62.58</v>
       </c>
       <c r="E125" s="4" t="n">
-        <v>48.54</v>
+        <v>59.26</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>52.69</v>
+        <v>52.16</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>IONEXCHANG</t>
+          <t>BIRLACORPN</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -4058,22 +4378,22 @@
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>396.4</v>
+        <v>995</v>
       </c>
       <c r="D126" s="4" t="n">
-        <v>57.8</v>
+        <v>62.54</v>
       </c>
       <c r="E126" s="4" t="n">
-        <v>55.44</v>
+        <v>49.05</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>45.49</v>
+        <v>43.56</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>JINDWORLD</t>
+          <t>BOSCH-HCIL</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -4082,22 +4402,22 @@
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>25.9</v>
+        <v>1447.7</v>
       </c>
       <c r="D127" s="4" t="n">
-        <v>57.75</v>
+        <v>62.39</v>
       </c>
       <c r="E127" s="4" t="n">
-        <v>45.25</v>
+        <v>56.63</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>35.9</v>
+        <v/>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>PATELENG</t>
+          <t>STARCEMENT</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -4106,22 +4426,22 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>28.38</v>
+        <v>236.45</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>57.69</v>
+        <v>62.36</v>
       </c>
       <c r="E128" s="4" t="n">
-        <v>46.55</v>
+        <v>59.29</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>38.74</v>
+        <v>56.76</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>HIKAL</t>
+          <t>EDELWEISS</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -4130,22 +4450,22 @@
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>189.25</v>
+        <v>125.14</v>
       </c>
       <c r="D129" s="4" t="n">
-        <v>57.49</v>
+        <v>62.36</v>
       </c>
       <c r="E129" s="4" t="n">
-        <v>43.14</v>
+        <v>60.97</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>37.06</v>
+        <v>60.77</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>TEXRAIL</t>
+          <t>SUDARSCHEM</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -4154,22 +4474,22 @@
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>105.47</v>
+        <v>947.35</v>
       </c>
       <c r="D130" s="4" t="n">
-        <v>57.4</v>
+        <v>62.16</v>
       </c>
       <c r="E130" s="4" t="n">
-        <v>44.23</v>
+        <v>51.45</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>42.73</v>
+        <v>50.03</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>TANLA</t>
+          <t>EMIL</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -4178,22 +4498,22 @@
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>511.95</v>
+        <v>119.23</v>
       </c>
       <c r="D131" s="4" t="n">
-        <v>57.33</v>
+        <v>62.04</v>
       </c>
       <c r="E131" s="4" t="n">
-        <v>52.76</v>
+        <v>57.58</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>43.42</v>
+        <v>46.64</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>FDC</t>
+          <t>SUBROS</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -4202,22 +4522,22 @@
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>364.45</v>
+        <v>800.35</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>57.3</v>
+        <v>61.9</v>
       </c>
       <c r="E132" s="4" t="n">
-        <v>46.17</v>
+        <v>51.03</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>43.99</v>
+        <v>53.66</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>BANCOINDIA</t>
+          <t>VIYASH</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -4226,22 +4546,22 @@
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>618.55</v>
+        <v>219.6</v>
       </c>
       <c r="D133" s="4" t="n">
-        <v>57.16</v>
+        <v>61.82</v>
       </c>
       <c r="E133" s="4" t="n">
-        <v>50.39</v>
+        <v>65.23</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>57.31</v>
+        <v/>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>BELRISE</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -4250,22 +4570,22 @@
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>464.1</v>
+        <v>222.39</v>
       </c>
       <c r="D134" s="4" t="n">
-        <v>56.87</v>
+        <v>61.8</v>
       </c>
       <c r="E134" s="4" t="n">
-        <v>55.71</v>
+        <v>71.76000000000001</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>59.68</v>
+        <v/>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>HGINFRA</t>
+          <t>PARKHOTELS</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -4274,22 +4594,22 @@
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>595</v>
+        <v>129.73</v>
       </c>
       <c r="D135" s="4" t="n">
-        <v>56.83</v>
+        <v>61.8</v>
       </c>
       <c r="E135" s="4" t="n">
-        <v>41.96</v>
+        <v>52.9</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>37.41</v>
+        <v>42.4</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>BOSCH-HCIL</t>
+          <t>GATEWAY</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -4298,22 +4618,22 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>1390.6</v>
+        <v>59.96</v>
       </c>
       <c r="D136" s="4" t="n">
-        <v>56.79</v>
+        <v>61.58</v>
       </c>
       <c r="E136" s="4" t="n">
-        <v>51.92</v>
+        <v>54.81</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v/>
+        <v>44.68</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>ABDL</t>
+          <t>VARROC</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -4322,22 +4642,22 @@
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>531.8</v>
+        <v>559.85</v>
       </c>
       <c r="D137" s="4" t="n">
-        <v>56.74</v>
+        <v>61.55</v>
       </c>
       <c r="E137" s="4" t="n">
-        <v>53.23</v>
+        <v>52.4</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>57.2</v>
+        <v>52.83</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>TVSSCS</t>
+          <t>HCG</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -4346,22 +4666,22 @@
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>114.51</v>
+        <v>603.8</v>
       </c>
       <c r="D138" s="4" t="n">
-        <v>56.61</v>
+        <v>61.48</v>
       </c>
       <c r="E138" s="4" t="n">
-        <v>51.45</v>
+        <v>51.69</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>41.32</v>
+        <v>57.37</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>EASEMYTRIP</t>
+          <t>PRUDENT</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -4370,22 +4690,22 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>7.86</v>
+        <v>2829.1</v>
       </c>
       <c r="D139" s="4" t="n">
-        <v>56.59</v>
+        <v>61.45</v>
       </c>
       <c r="E139" s="4" t="n">
-        <v>51.53</v>
+        <v>61.7</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>37.76</v>
+        <v>59.72</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>SHRIPISTON</t>
+          <t>KRBL</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -4394,22 +4714,22 @@
         </is>
       </c>
       <c r="C140" s="4" t="n">
-        <v>3491.1</v>
+        <v>373.15</v>
       </c>
       <c r="D140" s="4" t="n">
-        <v>56.42</v>
+        <v>61.35</v>
       </c>
       <c r="E140" s="4" t="n">
-        <v>60.9</v>
+        <v>55.54</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>71.87</v>
+        <v>54.11</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>VARROC</t>
+          <t>UNIMECH</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -4418,22 +4738,22 @@
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>533.8</v>
+        <v>1043.9</v>
       </c>
       <c r="D141" s="4" t="n">
-        <v>56.32</v>
+        <v>61.33</v>
       </c>
       <c r="E141" s="4" t="n">
-        <v>46.05</v>
+        <v>60.35</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>50.67</v>
+        <v>48.84</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>JINDWORLD</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -4442,22 +4762,22 @@
         </is>
       </c>
       <c r="C142" s="4" t="n">
-        <v>1171.8</v>
+        <v>26.83</v>
       </c>
       <c r="D142" s="4" t="n">
-        <v>56.29</v>
+        <v>61.3</v>
       </c>
       <c r="E142" s="4" t="n">
-        <v>65.67</v>
+        <v>47.04</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>69.7</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>IIFLCAPS</t>
+          <t>DCAL</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -4466,22 +4786,22 @@
         </is>
       </c>
       <c r="C143" s="4" t="n">
-        <v>312.33</v>
+        <v>187.25</v>
       </c>
       <c r="D143" s="4" t="n">
-        <v>56.28</v>
+        <v>61.18</v>
       </c>
       <c r="E143" s="4" t="n">
-        <v>51.88</v>
+        <v>45.92</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>51.34</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>ASHOKA</t>
+          <t>WELENT</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -4490,22 +4810,22 @@
         </is>
       </c>
       <c r="C144" s="4" t="n">
-        <v>134.25</v>
+        <v>522.2</v>
       </c>
       <c r="D144" s="4" t="n">
-        <v>56.21</v>
+        <v>61</v>
       </c>
       <c r="E144" s="4" t="n">
-        <v>42.49</v>
+        <v>57.61</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>43.69</v>
+        <v>55.82</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>IFBIND</t>
+          <t>BANCOINDIA</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -4514,22 +4834,22 @@
         </is>
       </c>
       <c r="C145" s="4" t="n">
-        <v>1142.85</v>
+        <v>636.25</v>
       </c>
       <c r="D145" s="4" t="n">
-        <v>56.16</v>
+        <v>60.92</v>
       </c>
       <c r="E145" s="4" t="n">
-        <v>41.42</v>
+        <v>52.98</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>45.94</v>
+        <v>58.12</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>LMW</t>
+          <t>ROUTE</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -4538,22 +4858,22 @@
         </is>
       </c>
       <c r="C146" s="4" t="n">
-        <v>14562</v>
+        <v>552.5</v>
       </c>
       <c r="D146" s="4" t="n">
-        <v>56.13</v>
+        <v>60.86</v>
       </c>
       <c r="E146" s="4" t="n">
-        <v>49.7</v>
+        <v>44.11</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>49.76</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>ALIVUS</t>
+          <t>JAMNAAUTO</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -4562,22 +4882,22 @@
         </is>
       </c>
       <c r="C147" s="4" t="n">
-        <v>1038.15</v>
+        <v>131.65</v>
       </c>
       <c r="D147" s="4" t="n">
-        <v>56.12</v>
+        <v>60.81</v>
       </c>
       <c r="E147" s="4" t="n">
-        <v>61.73</v>
+        <v>57.43</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>62.54</v>
+        <v>58.02</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>GSFC</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -4586,22 +4906,22 @@
         </is>
       </c>
       <c r="C148" s="4" t="n">
-        <v>184.63</v>
+        <v>175.95</v>
       </c>
       <c r="D148" s="4" t="n">
-        <v>56.07</v>
+        <v>60.8</v>
       </c>
       <c r="E148" s="4" t="n">
-        <v>52.76</v>
+        <v>52.46</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>49.77</v>
+        <v>48.54</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>WAAREERTL</t>
+          <t>BAJAJELEC</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -4610,22 +4930,22 @@
         </is>
       </c>
       <c r="C149" s="4" t="n">
-        <v>1017.6</v>
+        <v>405.95</v>
       </c>
       <c r="D149" s="4" t="n">
-        <v>55.98</v>
+        <v>60.78</v>
       </c>
       <c r="E149" s="4" t="n">
-        <v>55.25</v>
+        <v>44.58</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v/>
+        <v>32.27</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>QUESS</t>
+          <t>SHRIPISTON</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -4634,22 +4954,22 @@
         </is>
       </c>
       <c r="C150" s="4" t="n">
-        <v>197.68</v>
+        <v>3604.4</v>
       </c>
       <c r="D150" s="4" t="n">
-        <v>55.94</v>
+        <v>60.7</v>
       </c>
       <c r="E150" s="4" t="n">
-        <v>42.8</v>
+        <v>62.71</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>31.67</v>
+        <v>73.02</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>THYROCARE</t>
+          <t>LMW</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -4658,22 +4978,22 @@
         </is>
       </c>
       <c r="C151" s="4" t="n">
-        <v>400.3</v>
+        <v>14972</v>
       </c>
       <c r="D151" s="4" t="n">
-        <v>55.92</v>
+        <v>60.59</v>
       </c>
       <c r="E151" s="4" t="n">
-        <v>50.07</v>
+        <v>53.89</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>56.75</v>
+        <v>51.17</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>PARADEEP</t>
+          <t>AGI</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -4682,22 +5002,22 @@
         </is>
       </c>
       <c r="C152" s="4" t="n">
-        <v>128.96</v>
+        <v>629.2</v>
       </c>
       <c r="D152" s="4" t="n">
-        <v>55.87</v>
+        <v>60.5</v>
       </c>
       <c r="E152" s="4" t="n">
-        <v>46.66</v>
+        <v>49.52</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>50.69</v>
+        <v>45.93</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>SHARDAMOTR</t>
+          <t>AARTIPHARM</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -4706,22 +5026,22 @@
         </is>
       </c>
       <c r="C153" s="4" t="n">
-        <v>863.75</v>
+        <v>766.2</v>
       </c>
       <c r="D153" s="4" t="n">
-        <v>55.7</v>
+        <v>60.45</v>
       </c>
       <c r="E153" s="4" t="n">
-        <v>46.88</v>
+        <v>55.27</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>43.28</v>
+        <v>55.38</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>PRINCEPIPE</t>
+          <t>GREENPANEL</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -4730,22 +5050,22 @@
         </is>
       </c>
       <c r="C154" s="4" t="n">
-        <v>259.39</v>
+        <v>225.44</v>
       </c>
       <c r="D154" s="4" t="n">
-        <v>55.7</v>
+        <v>60.36</v>
       </c>
       <c r="E154" s="4" t="n">
-        <v>48.5</v>
+        <v>50.42</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>38.05</v>
+        <v>42.7</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>SANDUMA</t>
+          <t>SKIPPER</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -4754,22 +5074,22 @@
         </is>
       </c>
       <c r="C155" s="4" t="n">
-        <v>210.61</v>
+        <v>466.2</v>
       </c>
       <c r="D155" s="4" t="n">
-        <v>55.62</v>
+        <v>59.87</v>
       </c>
       <c r="E155" s="4" t="n">
-        <v>53.13</v>
+        <v>59.47</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>58.75</v>
+        <v>55.85</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>IMFA</t>
+          <t>NFL</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -4778,22 +5098,22 @@
         </is>
       </c>
       <c r="C156" s="4" t="n">
-        <v>1502.6</v>
+        <v>78.63</v>
       </c>
       <c r="D156" s="4" t="n">
-        <v>55.61</v>
+        <v>59.83</v>
       </c>
       <c r="E156" s="4" t="n">
-        <v>62.35</v>
+        <v>47.78</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>69.79000000000001</v>
+        <v>45.98</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>GSFC</t>
+          <t>GANECOS</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -4802,22 +5122,22 @@
         </is>
       </c>
       <c r="C157" s="4" t="n">
-        <v>170.39</v>
+        <v>1063.6</v>
       </c>
       <c r="D157" s="4" t="n">
-        <v>55.39</v>
+        <v>59.62</v>
       </c>
       <c r="E157" s="4" t="n">
-        <v>48.94</v>
+        <v>56.36</v>
       </c>
       <c r="F157" s="4" t="n">
-        <v>47.02</v>
+        <v>46.86</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>MAXESTATES</t>
+          <t>JKPAPER</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -4826,22 +5146,22 @@
         </is>
       </c>
       <c r="C158" s="4" t="n">
-        <v>391.3</v>
+        <v>379</v>
       </c>
       <c r="D158" s="4" t="n">
-        <v>55.07</v>
+        <v>59.57</v>
       </c>
       <c r="E158" s="4" t="n">
-        <v>46.33</v>
+        <v>57.74</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v>47</v>
+        <v>52.31</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>EUREKAFORB</t>
+          <t>TSFINV</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -4850,22 +5170,22 @@
         </is>
       </c>
       <c r="C159" s="4" t="n">
-        <v>498.65</v>
+        <v>421</v>
       </c>
       <c r="D159" s="4" t="n">
-        <v>54.96</v>
+        <v>59.47</v>
       </c>
       <c r="E159" s="4" t="n">
-        <v>46.86</v>
+        <v>44.34</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>44.46</v>
+        <v/>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>HCG</t>
+          <t>SANOFICONR</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -4874,22 +5194,22 @@
         </is>
       </c>
       <c r="C160" s="4" t="n">
-        <v>572.55</v>
+        <v>4767.7</v>
       </c>
       <c r="D160" s="4" t="n">
-        <v>54.94</v>
+        <v>59.44</v>
       </c>
       <c r="E160" s="4" t="n">
-        <v>44.35</v>
+        <v>56.29</v>
       </c>
       <c r="F160" s="4" t="n">
-        <v>54.54</v>
+        <v>50.06</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>EPL</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -4898,22 +5218,22 @@
         </is>
       </c>
       <c r="C161" s="4" t="n">
-        <v>226.13</v>
+        <v>456.15</v>
       </c>
       <c r="D161" s="4" t="n">
-        <v>54.9</v>
+        <v>59.44</v>
       </c>
       <c r="E161" s="4" t="n">
-        <v>57.1</v>
+        <v>52.61</v>
       </c>
       <c r="F161" s="4" t="n">
-        <v>54.55</v>
+        <v>53.76</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>PURVA</t>
+          <t>SANSERA</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -4922,22 +5242,22 @@
         </is>
       </c>
       <c r="C162" s="4" t="n">
-        <v>214.37</v>
+        <v>2519.8</v>
       </c>
       <c r="D162" s="4" t="n">
-        <v>54.82</v>
+        <v>59.41</v>
       </c>
       <c r="E162" s="4" t="n">
-        <v>47.06</v>
+        <v>70.02</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>44.95</v>
+        <v>72.95999999999999</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>MASTEK</t>
+          <t>JISLJALEQS</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -4946,22 +5266,22 @@
         </is>
       </c>
       <c r="C163" s="4" t="n">
-        <v>1694.2</v>
+        <v>35.06</v>
       </c>
       <c r="D163" s="4" t="n">
-        <v>54.8</v>
+        <v>59.37</v>
       </c>
       <c r="E163" s="4" t="n">
-        <v>42.16</v>
+        <v>44.33</v>
       </c>
       <c r="F163" s="4" t="n">
-        <v>40.72</v>
+        <v>39.42</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>SPARC</t>
+          <t>GOKEX</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -4970,22 +5290,22 @@
         </is>
       </c>
       <c r="C164" s="4" t="n">
-        <v>143.04</v>
+        <v>732.45</v>
       </c>
       <c r="D164" s="4" t="n">
-        <v>54.76</v>
+        <v>59.29</v>
       </c>
       <c r="E164" s="4" t="n">
-        <v>54.65</v>
+        <v>51.64</v>
       </c>
       <c r="F164" s="4" t="n">
-        <v>44.17</v>
+        <v>49.21</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>INDIGOPNTS</t>
+          <t>RTNPOWER</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -4994,22 +5314,22 @@
         </is>
       </c>
       <c r="C165" s="4" t="n">
-        <v>860.2</v>
+        <v>10.02</v>
       </c>
       <c r="D165" s="4" t="n">
-        <v>54.63</v>
+        <v>59.28</v>
       </c>
       <c r="E165" s="4" t="n">
-        <v>40.2</v>
+        <v>55.62</v>
       </c>
       <c r="F165" s="4" t="n">
-        <v>39.79</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>PARKHOTELS</t>
+          <t>WABAG</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -5018,22 +5338,22 @@
         </is>
       </c>
       <c r="C166" s="4" t="n">
-        <v>121.73</v>
+        <v>1478</v>
       </c>
       <c r="D166" s="4" t="n">
-        <v>54.58</v>
+        <v>59.21</v>
       </c>
       <c r="E166" s="4" t="n">
-        <v>47.6</v>
+        <v>61.74</v>
       </c>
       <c r="F166" s="4" t="n">
-        <v>38.89</v>
+        <v>56.95</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>SOUTHBANK</t>
+          <t>MAXESTATES</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -5042,22 +5362,22 @@
         </is>
       </c>
       <c r="C167" s="4" t="n">
-        <v>39.46</v>
+        <v>408.05</v>
       </c>
       <c r="D167" s="4" t="n">
-        <v>54.58</v>
+        <v>59.2</v>
       </c>
       <c r="E167" s="4" t="n">
-        <v>55.02</v>
+        <v>50.58</v>
       </c>
       <c r="F167" s="4" t="n">
-        <v>63.97</v>
+        <v>48.59</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>RALLIS</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -5066,22 +5386,22 @@
         </is>
       </c>
       <c r="C168" s="4" t="n">
-        <v>607.3</v>
+        <v>267.95</v>
       </c>
       <c r="D168" s="4" t="n">
-        <v>54.55</v>
+        <v>59.11</v>
       </c>
       <c r="E168" s="4" t="n">
-        <v>53.06</v>
+        <v>51.05</v>
       </c>
       <c r="F168" s="4" t="n">
-        <v>49.85</v>
+        <v>49.34</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>VMART</t>
+          <t>HERITGFOOD</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -5090,22 +5410,22 @@
         </is>
       </c>
       <c r="C169" s="4" t="n">
-        <v>616.45</v>
+        <v>362.6</v>
       </c>
       <c r="D169" s="4" t="n">
-        <v>54.48</v>
+        <v>59.07</v>
       </c>
       <c r="E169" s="4" t="n">
-        <v>47.1</v>
+        <v>45.14</v>
       </c>
       <c r="F169" s="4" t="n">
-        <v>44.93</v>
+        <v>46.71</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>LUXIND</t>
+          <t>IMFA</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -5114,22 +5434,22 @@
         </is>
       </c>
       <c r="C170" s="4" t="n">
-        <v>1398.2</v>
+        <v>1548.1</v>
       </c>
       <c r="D170" s="4" t="n">
-        <v>54.41</v>
+        <v>59.03</v>
       </c>
       <c r="E170" s="4" t="n">
-        <v>60.4</v>
+        <v>64.31999999999999</v>
       </c>
       <c r="F170" s="4" t="n">
-        <v>50.78</v>
+        <v>70.69</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>EUREKAFORB</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -5138,22 +5458,22 @@
         </is>
       </c>
       <c r="C171" s="4" t="n">
-        <v>1057.25</v>
+        <v>513.4</v>
       </c>
       <c r="D171" s="4" t="n">
-        <v>54.4</v>
+        <v>58.89</v>
       </c>
       <c r="E171" s="4" t="n">
-        <v>56.4</v>
+        <v>48.82</v>
       </c>
       <c r="F171" s="4" t="n">
-        <v>60.9</v>
+        <v>46.12</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>GRWRHITECH</t>
+          <t>FIEMIND</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -5162,22 +5482,22 @@
         </is>
       </c>
       <c r="C172" s="4" t="n">
-        <v>3999</v>
+        <v>2267</v>
       </c>
       <c r="D172" s="4" t="n">
-        <v>54.38</v>
+        <v>58.84</v>
       </c>
       <c r="E172" s="4" t="n">
-        <v>56.17</v>
+        <v>57.62</v>
       </c>
       <c r="F172" s="4" t="n">
-        <v>55.92</v>
+        <v>67.11</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>KANSAINER</t>
+          <t>PATELENG</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -5186,22 +5506,22 @@
         </is>
       </c>
       <c r="C173" s="4" t="n">
-        <v>197.19</v>
+        <v>28.82</v>
       </c>
       <c r="D173" s="4" t="n">
-        <v>54.32</v>
+        <v>58.76</v>
       </c>
       <c r="E173" s="4" t="n">
-        <v>43.03</v>
+        <v>48</v>
       </c>
       <c r="F173" s="4" t="n">
-        <v>37.61</v>
+        <v>39.38</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>DATAMATICS</t>
+          <t>KNRCON</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -5210,22 +5530,22 @@
         </is>
       </c>
       <c r="C174" s="4" t="n">
-        <v>732.8</v>
+        <v>131.94</v>
       </c>
       <c r="D174" s="4" t="n">
-        <v>54.27</v>
+        <v>58.76</v>
       </c>
       <c r="E174" s="4" t="n">
-        <v>48.36</v>
+        <v>44.21</v>
       </c>
       <c r="F174" s="4" t="n">
-        <v>52.39</v>
+        <v>35.24</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>ELECTCAST</t>
+          <t>SHAREINDIA</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -5234,22 +5554,22 @@
         </is>
       </c>
       <c r="C175" s="4" t="n">
-        <v>81.98999999999999</v>
+        <v>147.5</v>
       </c>
       <c r="D175" s="4" t="n">
-        <v>54.22</v>
+        <v>58.62</v>
       </c>
       <c r="E175" s="4" t="n">
-        <v>52.29</v>
+        <v>50.15</v>
       </c>
       <c r="F175" s="4" t="n">
-        <v>44.07</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>GULFOILLUB</t>
+          <t>MSTCLTD</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -5258,22 +5578,22 @@
         </is>
       </c>
       <c r="C176" s="4" t="n">
-        <v>983.3</v>
+        <v>455.9</v>
       </c>
       <c r="D176" s="4" t="n">
-        <v>54.22</v>
+        <v>58.49</v>
       </c>
       <c r="E176" s="4" t="n">
-        <v>42.47</v>
+        <v>50.15</v>
       </c>
       <c r="F176" s="4" t="n">
-        <v>48.37</v>
+        <v>47.23</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -5282,22 +5602,22 @@
         </is>
       </c>
       <c r="C177" s="4" t="n">
-        <v>263.56</v>
+        <v>1213.4</v>
       </c>
       <c r="D177" s="4" t="n">
-        <v>54.19</v>
+        <v>58.39</v>
       </c>
       <c r="E177" s="4" t="n">
-        <v>50.66</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="F177" s="4" t="n">
-        <v>52.49</v>
+        <v>71.38</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>TSFINV</t>
+          <t>AVANTIFEED</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -5306,22 +5626,22 @@
         </is>
       </c>
       <c r="C178" s="4" t="n">
-        <v>402.95</v>
+        <v>1435.2</v>
       </c>
       <c r="D178" s="4" t="n">
-        <v>54.17</v>
+        <v>58.35</v>
       </c>
       <c r="E178" s="4" t="n">
-        <v>39.83</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="F178" s="4" t="n">
-        <v/>
+        <v>76.23999999999999</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>GOKEX</t>
+          <t>AARTIDRUGS</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -5330,22 +5650,22 @@
         </is>
       </c>
       <c r="C179" s="4" t="n">
-        <v>703.7</v>
+        <v>387.9</v>
       </c>
       <c r="D179" s="4" t="n">
-        <v>54</v>
+        <v>58.29</v>
       </c>
       <c r="E179" s="4" t="n">
-        <v>49.5</v>
+        <v>50.33</v>
       </c>
       <c r="F179" s="4" t="n">
-        <v>48.07</v>
+        <v>45.61</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>PGIL</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -5354,22 +5674,22 @@
         </is>
       </c>
       <c r="C180" s="4" t="n">
-        <v>439.95</v>
+        <v>1604.7</v>
       </c>
       <c r="D180" s="4" t="n">
-        <v>53.68</v>
+        <v>58.17</v>
       </c>
       <c r="E180" s="4" t="n">
-        <v>48.53</v>
+        <v>54.05</v>
       </c>
       <c r="F180" s="4" t="n">
-        <v>51.75</v>
+        <v>61.95</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>IFBIND</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -5378,22 +5698,22 @@
         </is>
       </c>
       <c r="C181" s="4" t="n">
-        <v>3955.8</v>
+        <v>1188.6</v>
       </c>
       <c r="D181" s="4" t="n">
-        <v>53.51</v>
+        <v>58.16</v>
       </c>
       <c r="E181" s="4" t="n">
-        <v>60.22</v>
+        <v>45.62</v>
       </c>
       <c r="F181" s="4" t="n">
-        <v>72.79000000000001</v>
+        <v>46.93</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>AVANTIFEED</t>
+          <t>JSFB</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -5402,22 +5722,22 @@
         </is>
       </c>
       <c r="C182" s="4" t="n">
-        <v>1380.7</v>
+        <v>455.05</v>
       </c>
       <c r="D182" s="4" t="n">
-        <v>53.29</v>
+        <v>57.69</v>
       </c>
       <c r="E182" s="4" t="n">
-        <v>65.95</v>
+        <v>61.77</v>
       </c>
       <c r="F182" s="4" t="n">
-        <v>75.14</v>
+        <v>50.98</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>PCJEWELLER</t>
+          <t>EASEMYTRIP</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -5426,22 +5746,22 @@
         </is>
       </c>
       <c r="C183" s="4" t="n">
-        <v>9.369999999999999</v>
+        <v>7.96</v>
       </c>
       <c r="D183" s="4" t="n">
-        <v>53.22</v>
+        <v>57.67</v>
       </c>
       <c r="E183" s="4" t="n">
-        <v>44.72</v>
+        <v>51.95</v>
       </c>
       <c r="F183" s="4" t="n">
-        <v>47.87</v>
+        <v>38.12</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>DODLA</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -5450,22 +5770,22 @@
         </is>
       </c>
       <c r="C184" s="4" t="n">
-        <v>1099.9</v>
+        <v>259.35</v>
       </c>
       <c r="D184" s="4" t="n">
-        <v>53.19</v>
+        <v>57.57</v>
       </c>
       <c r="E184" s="4" t="n">
-        <v>42.36</v>
+        <v>71.33</v>
       </c>
       <c r="F184" s="4" t="n">
-        <v>49.7</v>
+        <v>65.02</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>MAHLIFE</t>
+          <t>ASHOKA</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -5474,22 +5794,22 @@
         </is>
       </c>
       <c r="C185" s="4" t="n">
-        <v>340.5</v>
+        <v>137.21</v>
       </c>
       <c r="D185" s="4" t="n">
-        <v>53.14</v>
+        <v>57.5</v>
       </c>
       <c r="E185" s="4" t="n">
-        <v>45.27</v>
+        <v>44.57</v>
       </c>
       <c r="F185" s="4" t="n">
-        <v>42.99</v>
+        <v>44.26</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>WESTLIFE</t>
+          <t>SOUTHBANK</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -5498,22 +5818,22 @@
         </is>
       </c>
       <c r="C186" s="4" t="n">
-        <v>475.85</v>
+        <v>40.91</v>
       </c>
       <c r="D186" s="4" t="n">
-        <v>53.11</v>
+        <v>57.2</v>
       </c>
       <c r="E186" s="4" t="n">
-        <v>40.07</v>
+        <v>58.22</v>
       </c>
       <c r="F186" s="4" t="n">
-        <v>31.45</v>
+        <v>65.48</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>CIEINDIA</t>
+          <t>OSWALPUMPS</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -5522,22 +5842,22 @@
         </is>
       </c>
       <c r="C187" s="4" t="n">
-        <v>473.75</v>
+        <v>410.6</v>
       </c>
       <c r="D187" s="4" t="n">
-        <v>53.08</v>
+        <v>57.15</v>
       </c>
       <c r="E187" s="4" t="n">
-        <v>58.85</v>
+        <v>45.14</v>
       </c>
       <c r="F187" s="4" t="n">
-        <v>55.79</v>
+        <v/>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>GATEWAY</t>
+          <t>ZAGGLE</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -5546,22 +5866,22 @@
         </is>
       </c>
       <c r="C188" s="4" t="n">
-        <v>57.37</v>
+        <v>259.11</v>
       </c>
       <c r="D188" s="4" t="n">
-        <v>52.86</v>
+        <v>57.11</v>
       </c>
       <c r="E188" s="4" t="n">
-        <v>50.18</v>
+        <v>44.35</v>
       </c>
       <c r="F188" s="4" t="n">
-        <v>41.91</v>
+        <v>44.31</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>NETWORK18</t>
+          <t>AURIONPRO</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -5570,22 +5890,22 @@
         </is>
       </c>
       <c r="C189" s="4" t="n">
-        <v>34.43</v>
+        <v>896.05</v>
       </c>
       <c r="D189" s="4" t="n">
-        <v>52.68</v>
+        <v>56.67</v>
       </c>
       <c r="E189" s="4" t="n">
-        <v>40.63</v>
+        <v>44</v>
       </c>
       <c r="F189" s="4" t="n">
-        <v>37.23</v>
+        <v>43.45</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>TEAMLEASE</t>
+          <t>RELAXO</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -5594,22 +5914,22 @@
         </is>
       </c>
       <c r="C190" s="4" t="n">
-        <v>1232.3</v>
+        <v>308.85</v>
       </c>
       <c r="D190" s="4" t="n">
-        <v>52.64</v>
+        <v>56.61</v>
       </c>
       <c r="E190" s="4" t="n">
-        <v>35.33</v>
+        <v>39.54</v>
       </c>
       <c r="F190" s="4" t="n">
-        <v>31.67</v>
+        <v>28.88</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>ENTERO</t>
+          <t>BECTORFOOD</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -5618,22 +5938,22 @@
         </is>
       </c>
       <c r="C191" s="4" t="n">
-        <v>1216.4</v>
+        <v>202.39</v>
       </c>
       <c r="D191" s="4" t="n">
-        <v>52.57</v>
+        <v>56.58</v>
       </c>
       <c r="E191" s="4" t="n">
-        <v>54.46</v>
+        <v>41.34</v>
       </c>
       <c r="F191" s="4" t="n">
-        <v>53.52</v>
+        <v>42.4</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>KNRCON</t>
+          <t>GULFOILLUB</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -5642,22 +5962,22 @@
         </is>
       </c>
       <c r="C192" s="4" t="n">
-        <v>125.13</v>
+        <v>1000.8</v>
       </c>
       <c r="D192" s="4" t="n">
-        <v>52.47</v>
+        <v>56.38</v>
       </c>
       <c r="E192" s="4" t="n">
-        <v>40.54</v>
+        <v>44.48</v>
       </c>
       <c r="F192" s="4" t="n">
-        <v>33.53</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>VAIBHAVGBL</t>
+          <t>DODLA</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -5666,22 +5986,22 @@
         </is>
       </c>
       <c r="C193" s="4" t="n">
-        <v>217.18</v>
+        <v>1127.3</v>
       </c>
       <c r="D193" s="4" t="n">
-        <v>52.43</v>
+        <v>56.35</v>
       </c>
       <c r="E193" s="4" t="n">
-        <v>48.73</v>
+        <v>47.7</v>
       </c>
       <c r="F193" s="4" t="n">
-        <v>43.84</v>
+        <v>50.85</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>MEDPLUS</t>
+          <t>JKLAKSHMI</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -5690,22 +6010,22 @@
         </is>
       </c>
       <c r="C194" s="4" t="n">
-        <v>872.15</v>
+        <v>664.4</v>
       </c>
       <c r="D194" s="4" t="n">
-        <v>52.4</v>
+        <v>56.15</v>
       </c>
       <c r="E194" s="4" t="n">
-        <v>57.29</v>
+        <v>43.59</v>
       </c>
       <c r="F194" s="4" t="n">
-        <v>56.14</v>
+        <v>44.14</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>JKPAPER</t>
+          <t>LUMAXTECH</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -5714,22 +6034,22 @@
         </is>
       </c>
       <c r="C195" s="4" t="n">
-        <v>360.25</v>
+        <v>1736.1</v>
       </c>
       <c r="D195" s="4" t="n">
-        <v>51.65</v>
+        <v>56.13</v>
       </c>
       <c r="E195" s="4" t="n">
-        <v>52.2</v>
+        <v>58.37</v>
       </c>
       <c r="F195" s="4" t="n">
-        <v>50.08</v>
+        <v>70.3</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>FIEMIND</t>
+          <t>PURVA</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -5738,22 +6058,22 @@
         </is>
       </c>
       <c r="C196" s="4" t="n">
-        <v>2182.7</v>
+        <v>218.73</v>
       </c>
       <c r="D196" s="4" t="n">
-        <v>51.64</v>
+        <v>56.08</v>
       </c>
       <c r="E196" s="4" t="n">
-        <v>52.93</v>
+        <v>48.63</v>
       </c>
       <c r="F196" s="4" t="n">
-        <v>65.34999999999999</v>
+        <v>45.63</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>AURIONPRO</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -5762,22 +6082,22 @@
         </is>
       </c>
       <c r="C197" s="4" t="n">
-        <v>869.9</v>
+        <v>268.6</v>
       </c>
       <c r="D197" s="4" t="n">
-        <v>51.54</v>
+        <v>55.88</v>
       </c>
       <c r="E197" s="4" t="n">
-        <v>41.76</v>
+        <v>52.38</v>
       </c>
       <c r="F197" s="4" t="n">
-        <v>42.45</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>SHARDACROP</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -5786,22 +6106,22 @@
         </is>
       </c>
       <c r="C198" s="4" t="n">
-        <v>186.76</v>
+        <v>1122.4</v>
       </c>
       <c r="D198" s="4" t="n">
-        <v>51.54</v>
+        <v>55.8</v>
       </c>
       <c r="E198" s="4" t="n">
-        <v>59.11</v>
+        <v>59.05</v>
       </c>
       <c r="F198" s="4" t="n">
-        <v>61.05</v>
+        <v>61.51</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>ORIENTCEM</t>
+          <t>WAAREERTL</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -5810,22 +6130,22 @@
         </is>
       </c>
       <c r="C199" s="4" t="n">
-        <v>143.8</v>
+        <v>1028.3</v>
       </c>
       <c r="D199" s="4" t="n">
-        <v>51.37</v>
+        <v>55.73</v>
       </c>
       <c r="E199" s="4" t="n">
-        <v>36.53</v>
+        <v>55.89</v>
       </c>
       <c r="F199" s="4" t="n">
-        <v>36.57</v>
+        <v/>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>GMMPFAUDLR</t>
+          <t>KITEX</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -5834,22 +6154,22 @@
         </is>
       </c>
       <c r="C200" s="4" t="n">
-        <v>905.55</v>
+        <v>171.08</v>
       </c>
       <c r="D200" s="4" t="n">
-        <v>51.33</v>
+        <v>55.23</v>
       </c>
       <c r="E200" s="4" t="n">
-        <v>39.88</v>
+        <v>46.87</v>
       </c>
       <c r="F200" s="4" t="n">
-        <v>41.05</v>
+        <v>50.66</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>SUNTECK</t>
+          <t>PCJEWELLER</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -5858,22 +6178,22 @@
         </is>
       </c>
       <c r="C201" s="4" t="n">
-        <v>340.25</v>
+        <v>9.5</v>
       </c>
       <c r="D201" s="4" t="n">
-        <v>51.32</v>
+        <v>55.18</v>
       </c>
       <c r="E201" s="4" t="n">
-        <v>43.28</v>
+        <v>45.73</v>
       </c>
       <c r="F201" s="4" t="n">
-        <v>42.89</v>
+        <v>48.24</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>BECTORFOOD</t>
+          <t>IMAGICAA</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -5882,22 +6202,22 @@
         </is>
       </c>
       <c r="C202" s="4" t="n">
-        <v>196.21</v>
+        <v>46.85</v>
       </c>
       <c r="D202" s="4" t="n">
-        <v>51.16</v>
+        <v>54.99</v>
       </c>
       <c r="E202" s="4" t="n">
-        <v>36.63</v>
+        <v>48.5</v>
       </c>
       <c r="F202" s="4" t="n">
-        <v>40.98</v>
+        <v>43.38</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>GMRP&amp;UI</t>
+          <t>PRSMJOHNSN</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -5906,22 +6226,22 @@
         </is>
       </c>
       <c r="C203" s="4" t="n">
-        <v>106.55</v>
+        <v>131.85</v>
       </c>
       <c r="D203" s="4" t="n">
-        <v>51.1</v>
+        <v>54.86</v>
       </c>
       <c r="E203" s="4" t="n">
-        <v>48.4</v>
+        <v>50.2</v>
       </c>
       <c r="F203" s="4" t="n">
-        <v>53.22</v>
+        <v>45.81</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>VINATIORGA</t>
+          <t>GHCL</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -5930,22 +6250,22 @@
         </is>
       </c>
       <c r="C204" s="4" t="n">
-        <v>1322.3</v>
+        <v>510.9</v>
       </c>
       <c r="D204" s="4" t="n">
-        <v>50.99</v>
+        <v>54.82</v>
       </c>
       <c r="E204" s="4" t="n">
-        <v>34.74</v>
+        <v>48.75</v>
       </c>
       <c r="F204" s="4" t="n">
-        <v>35.94</v>
+        <v>46.82</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>JKLAKSHMI</t>
+          <t>PRINCEPIPE</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -5954,22 +6274,22 @@
         </is>
       </c>
       <c r="C205" s="4" t="n">
-        <v>645.1</v>
+        <v>259.65</v>
       </c>
       <c r="D205" s="4" t="n">
-        <v>50.84</v>
+        <v>54.11</v>
       </c>
       <c r="E205" s="4" t="n">
-        <v>40.41</v>
+        <v>49.08</v>
       </c>
       <c r="F205" s="4" t="n">
-        <v>42.81</v>
+        <v>38.08</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>JISLJALEQS</t>
+          <t>ARVINDFASN</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -5978,22 +6298,22 @@
         </is>
       </c>
       <c r="C206" s="4" t="n">
-        <v>32.52</v>
+        <v>460.05</v>
       </c>
       <c r="D206" s="4" t="n">
-        <v>50.83</v>
+        <v>54.11</v>
       </c>
       <c r="E206" s="4" t="n">
-        <v>37.43</v>
+        <v>49.99</v>
       </c>
       <c r="F206" s="4" t="n">
-        <v>36.94</v>
+        <v>50.39</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>V2RETAIL</t>
+          <t>AHLUCONT</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -6002,16 +6322,16 @@
         </is>
       </c>
       <c r="C207" s="4" t="n">
-        <v>198.65</v>
+        <v>847.55</v>
       </c>
       <c r="D207" s="4" t="n">
-        <v>50.81</v>
+        <v>53.96</v>
       </c>
       <c r="E207" s="4" t="n">
-        <v>47.61</v>
+        <v>49.65</v>
       </c>
       <c r="F207" s="4" t="n">
-        <v>61.38</v>
+        <v>48.47</v>
       </c>
     </row>
     <row r="208">
@@ -6026,22 +6346,22 @@
         </is>
       </c>
       <c r="C208" s="4" t="n">
-        <v>132.71</v>
+        <v>136.69</v>
       </c>
       <c r="D208" s="4" t="n">
-        <v>50.61</v>
+        <v>53.95</v>
       </c>
       <c r="E208" s="4" t="n">
-        <v>44.11</v>
+        <v>46.16</v>
       </c>
       <c r="F208" s="4" t="n">
-        <v>46.84</v>
+        <v>47.76</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>SHARDACROP</t>
+          <t>GPPL</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -6050,22 +6370,22 @@
         </is>
       </c>
       <c r="C209" s="4" t="n">
-        <v>1072.75</v>
+        <v>158.9</v>
       </c>
       <c r="D209" s="4" t="n">
-        <v>50.39</v>
+        <v>53.41</v>
       </c>
       <c r="E209" s="4" t="n">
-        <v>56.33</v>
+        <v>47.67</v>
       </c>
       <c r="F209" s="4" t="n">
-        <v>60.22</v>
+        <v>51.73</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>GPPL</t>
+          <t>JKIL</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -6074,22 +6394,22 @@
         </is>
       </c>
       <c r="C210" s="4" t="n">
-        <v>156.05</v>
+        <v>511.65</v>
       </c>
       <c r="D210" s="4" t="n">
-        <v>50.12</v>
+        <v>53.36</v>
       </c>
       <c r="E210" s="4" t="n">
-        <v>45.17</v>
+        <v>43.5</v>
       </c>
       <c r="F210" s="4" t="n">
-        <v>50.89</v>
+        <v>43.17</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>IMAGICAA</t>
+          <t>MASTEK</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -6098,22 +6418,22 @@
         </is>
       </c>
       <c r="C211" s="4" t="n">
-        <v>45.48</v>
+        <v>1683.1</v>
       </c>
       <c r="D211" s="4" t="n">
-        <v>50.08</v>
+        <v>53.14</v>
       </c>
       <c r="E211" s="4" t="n">
-        <v>45.65</v>
+        <v>41.06</v>
       </c>
       <c r="F211" s="4" t="n">
-        <v>42.16</v>
+        <v>40.53</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>RAIN</t>
+          <t>SUNTECK</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -6122,22 +6442,22 @@
         </is>
       </c>
       <c r="C212" s="4" t="n">
-        <v>126.2</v>
+        <v>345</v>
       </c>
       <c r="D212" s="4" t="n">
-        <v>49.78</v>
+        <v>52.98</v>
       </c>
       <c r="E212" s="4" t="n">
-        <v>47.56</v>
+        <v>44.37</v>
       </c>
       <c r="F212" s="4" t="n">
-        <v>45.85</v>
+        <v>43.43</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>MOIL</t>
+          <t>GARFIBRES</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -6146,22 +6466,22 @@
         </is>
       </c>
       <c r="C213" s="4" t="n">
-        <v>310.9</v>
+        <v>641.15</v>
       </c>
       <c r="D213" s="4" t="n">
-        <v>49.52</v>
+        <v>52.97</v>
       </c>
       <c r="E213" s="4" t="n">
-        <v>48.16</v>
+        <v>46.22</v>
       </c>
       <c r="F213" s="4" t="n">
-        <v>49.04</v>
+        <v>42.07</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>HEMIPROP</t>
+          <t>TIMETECHNO</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -6170,22 +6490,22 @@
         </is>
       </c>
       <c r="C214" s="4" t="n">
-        <v>128.12</v>
+        <v>187.08</v>
       </c>
       <c r="D214" s="4" t="n">
-        <v>49.44</v>
+        <v>52.84</v>
       </c>
       <c r="E214" s="4" t="n">
-        <v>46.23</v>
+        <v>49.58</v>
       </c>
       <c r="F214" s="4" t="n">
-        <v>45.89</v>
+        <v>52.92</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>VIYASH</t>
+          <t>GMRP&amp;UI</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -6194,22 +6514,22 @@
         </is>
       </c>
       <c r="C215" s="4" t="n">
-        <v>203.74</v>
+        <v>108.29</v>
       </c>
       <c r="D215" s="4" t="n">
-        <v>49.43</v>
+        <v>52.69</v>
       </c>
       <c r="E215" s="4" t="n">
-        <v>55.08</v>
+        <v>49.94</v>
       </c>
       <c r="F215" s="4" t="n">
-        <v/>
+        <v>53.8</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>UJJIVANSFB</t>
+          <t>JUSTDIAL</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -6218,22 +6538,22 @@
         </is>
       </c>
       <c r="C216" s="4" t="n">
-        <v>56.88</v>
+        <v>544.75</v>
       </c>
       <c r="D216" s="4" t="n">
-        <v>49.41</v>
+        <v>52.64</v>
       </c>
       <c r="E216" s="4" t="n">
-        <v>53.63</v>
+        <v>36.31</v>
       </c>
       <c r="F216" s="4" t="n">
-        <v>58.54</v>
+        <v>36.12</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>MSTCLTD</t>
+          <t>MEDPLUS</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -6242,22 +6562,22 @@
         </is>
       </c>
       <c r="C217" s="4" t="n">
-        <v>433.15</v>
+        <v>874.7</v>
       </c>
       <c r="D217" s="4" t="n">
-        <v>49.35</v>
+        <v>52.52</v>
       </c>
       <c r="E217" s="4" t="n">
-        <v>45.94</v>
+        <v>56.57</v>
       </c>
       <c r="F217" s="4" t="n">
-        <v>45.54</v>
+        <v>56.35</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>RELAXO</t>
+          <t>MOIL</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -6266,22 +6586,22 @@
         </is>
       </c>
       <c r="C218" s="4" t="n">
-        <v>298.09</v>
+        <v>315.35</v>
       </c>
       <c r="D218" s="4" t="n">
-        <v>49.28</v>
+        <v>52.34</v>
       </c>
       <c r="E218" s="4" t="n">
-        <v>36.39</v>
+        <v>49.46</v>
       </c>
       <c r="F218" s="4" t="n">
-        <v>27.35</v>
+        <v>49.65</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>RELIGARE</t>
+          <t>VESUVIUS</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -6290,22 +6610,22 @@
         </is>
       </c>
       <c r="C219" s="4" t="n">
-        <v>221.64</v>
+        <v>506.1</v>
       </c>
       <c r="D219" s="4" t="n">
-        <v>49.25</v>
+        <v>52.25</v>
       </c>
       <c r="E219" s="4" t="n">
-        <v>43.48</v>
+        <v>54.19</v>
       </c>
       <c r="F219" s="4" t="n">
-        <v>48.59</v>
+        <v>55.78</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>SAMHI</t>
+          <t>ENTERO</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -6314,22 +6634,22 @@
         </is>
       </c>
       <c r="C220" s="4" t="n">
-        <v>156.27</v>
+        <v>1224.6</v>
       </c>
       <c r="D220" s="4" t="n">
-        <v>49.15</v>
+        <v>52.24</v>
       </c>
       <c r="E220" s="4" t="n">
-        <v>42.7</v>
+        <v>55.79</v>
       </c>
       <c r="F220" s="4" t="n">
-        <v>44.58</v>
+        <v>53.92</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>FINEORG</t>
+          <t>CIEINDIA</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -6338,22 +6658,22 @@
         </is>
       </c>
       <c r="C221" s="4" t="n">
-        <v>4628.1</v>
+        <v>474.85</v>
       </c>
       <c r="D221" s="4" t="n">
-        <v>49.07</v>
+        <v>52.23</v>
       </c>
       <c r="E221" s="4" t="n">
-        <v>53.51</v>
+        <v>59.04</v>
       </c>
       <c r="F221" s="4" t="n">
-        <v>51.35</v>
+        <v>56.78</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>PGIL</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -6362,22 +6682,22 @@
         </is>
       </c>
       <c r="C222" s="4" t="n">
-        <v>1535.8</v>
+        <v>459.65</v>
       </c>
       <c r="D222" s="4" t="n">
-        <v>48.78</v>
+        <v>52.18</v>
       </c>
       <c r="E222" s="4" t="n">
-        <v>51.33</v>
+        <v>54.19</v>
       </c>
       <c r="F222" s="4" t="n">
-        <v>60.34</v>
+        <v>59.18</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>KITEX</t>
+          <t>CELLO</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -6386,22 +6706,22 @@
         </is>
       </c>
       <c r="C223" s="4" t="n">
-        <v>164.49</v>
+        <v>423.65</v>
       </c>
       <c r="D223" s="4" t="n">
-        <v>48.13</v>
+        <v>51.92</v>
       </c>
       <c r="E223" s="4" t="n">
-        <v>43.8</v>
+        <v>36.48</v>
       </c>
       <c r="F223" s="4" t="n">
-        <v>49.6</v>
+        <v>32.61</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>PRICOLLTD</t>
+          <t>NETWORK18</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -6410,22 +6730,22 @@
         </is>
       </c>
       <c r="C224" s="4" t="n">
-        <v>572.75</v>
+        <v>34.42</v>
       </c>
       <c r="D224" s="4" t="n">
-        <v>48</v>
+        <v>51.9</v>
       </c>
       <c r="E224" s="4" t="n">
-        <v>50.93</v>
+        <v>40.61</v>
       </c>
       <c r="F224" s="4" t="n">
-        <v>58.04</v>
+        <v>37.22</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>ARVINDFASN</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -6434,22 +6754,22 @@
         </is>
       </c>
       <c r="C225" s="4" t="n">
-        <v>443.15</v>
+        <v>608.25</v>
       </c>
       <c r="D225" s="4" t="n">
-        <v>47.98</v>
+        <v>51.69</v>
       </c>
       <c r="E225" s="4" t="n">
-        <v>47.28</v>
+        <v>53.65</v>
       </c>
       <c r="F225" s="4" t="n">
-        <v>48.39</v>
+        <v>49.95</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>ETHOSLTD</t>
+          <t>SAFARI</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -6458,22 +6778,22 @@
         </is>
       </c>
       <c r="C226" s="4" t="n">
-        <v>2401.8</v>
+        <v>1524.4</v>
       </c>
       <c r="D226" s="4" t="n">
-        <v>47.81</v>
+        <v>50.98</v>
       </c>
       <c r="E226" s="4" t="n">
-        <v>46.28</v>
+        <v>37.21</v>
       </c>
       <c r="F226" s="4" t="n">
-        <v>48.64</v>
+        <v>40.86</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>SENCO</t>
+          <t>FINEORG</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -6482,22 +6802,22 @@
         </is>
       </c>
       <c r="C227" s="4" t="n">
-        <v>313.1</v>
+        <v>4653.9</v>
       </c>
       <c r="D227" s="4" t="n">
-        <v>47.74</v>
+        <v>50.66</v>
       </c>
       <c r="E227" s="4" t="n">
-        <v>48.05</v>
+        <v>54.2</v>
       </c>
       <c r="F227" s="4" t="n">
-        <v>46.28</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>EDELWEISS</t>
+          <t>RELIGARE</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -6506,22 +6826,22 @@
         </is>
       </c>
       <c r="C228" s="4" t="n">
-        <v>114.25</v>
+        <v>223</v>
       </c>
       <c r="D228" s="4" t="n">
-        <v>47.64</v>
+        <v>50.64</v>
       </c>
       <c r="E228" s="4" t="n">
-        <v>53.01</v>
+        <v>45.18</v>
       </c>
       <c r="F228" s="4" t="n">
-        <v>57.29</v>
+        <v>48.89</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>CELLO</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -6530,22 +6850,22 @@
         </is>
       </c>
       <c r="C229" s="4" t="n">
-        <v>417.5</v>
+        <v>2793.1</v>
       </c>
       <c r="D229" s="4" t="n">
-        <v>47.64</v>
+        <v>50.34</v>
       </c>
       <c r="E229" s="4" t="n">
-        <v>34.92</v>
+        <v>52.27</v>
       </c>
       <c r="F229" s="4" t="n">
-        <v>31.86</v>
+        <v>49.34</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>CSBBANK</t>
+          <t>SHAKTIPUMP</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -6554,22 +6874,22 @@
         </is>
       </c>
       <c r="C230" s="4" t="n">
-        <v>381.95</v>
+        <v>550.05</v>
       </c>
       <c r="D230" s="4" t="n">
-        <v>47.62</v>
+        <v>50.32</v>
       </c>
       <c r="E230" s="4" t="n">
-        <v>48.07</v>
+        <v>41.52</v>
       </c>
       <c r="F230" s="4" t="n">
-        <v>52.71</v>
+        <v>46.12</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>ZAGGLE</t>
+          <t>SAMHI</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -6578,22 +6898,22 @@
         </is>
       </c>
       <c r="C231" s="4" t="n">
-        <v>240.76</v>
+        <v>157.46</v>
       </c>
       <c r="D231" s="4" t="n">
-        <v>47.21</v>
+        <v>49.88</v>
       </c>
       <c r="E231" s="4" t="n">
-        <v>38.81</v>
+        <v>43.64</v>
       </c>
       <c r="F231" s="4" t="n">
-        <v>42.32</v>
+        <v>44.91</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>BIRLACORPN</t>
+          <t>MAHLIFE</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -6602,22 +6922,22 @@
         </is>
       </c>
       <c r="C232" s="4" t="n">
-        <v>909.5</v>
+        <v>334.7</v>
       </c>
       <c r="D232" s="4" t="n">
-        <v>47.14</v>
+        <v>49.55</v>
       </c>
       <c r="E232" s="4" t="n">
-        <v>41.65</v>
+        <v>44.1</v>
       </c>
       <c r="F232" s="4" t="n">
-        <v>38.83</v>
+        <v>42.37</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>RAYMONDLSL</t>
+          <t>TRANSRAILL</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -6626,22 +6946,22 @@
         </is>
       </c>
       <c r="C233" s="4" t="n">
-        <v>794.2</v>
+        <v>566.8</v>
       </c>
       <c r="D233" s="4" t="n">
-        <v>46.93</v>
+        <v>49.43</v>
       </c>
       <c r="E233" s="4" t="n">
-        <v>38.59</v>
+        <v>49.72</v>
       </c>
       <c r="F233" s="4" t="n">
-        <v>22.93</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>SHAREINDIA</t>
+          <t>BLACKBUCK</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -6650,22 +6970,22 @@
         </is>
       </c>
       <c r="C234" s="4" t="n">
-        <v>137.45</v>
+        <v>579.1</v>
       </c>
       <c r="D234" s="4" t="n">
-        <v>46.88</v>
+        <v>49.24</v>
       </c>
       <c r="E234" s="4" t="n">
-        <v>43.72</v>
+        <v>48.23</v>
       </c>
       <c r="F234" s="4" t="n">
-        <v>39.99</v>
+        <v>55.82</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>JAMNAAUTO</t>
+          <t>PARADEEP</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -6674,22 +6994,22 @@
         </is>
       </c>
       <c r="C235" s="4" t="n">
-        <v>121.56</v>
+        <v>124.88</v>
       </c>
       <c r="D235" s="4" t="n">
-        <v>46.54</v>
+        <v>49.15</v>
       </c>
       <c r="E235" s="4" t="n">
-        <v>51.09</v>
+        <v>44.4</v>
       </c>
       <c r="F235" s="4" t="n">
-        <v>55.01</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>CIGNITITEC</t>
+          <t>ETHOSLTD</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -6698,22 +7018,22 @@
         </is>
       </c>
       <c r="C236" s="4" t="n">
-        <v>1182.2</v>
+        <v>2404.6</v>
       </c>
       <c r="D236" s="4" t="n">
-        <v>46.35</v>
+        <v>48.62</v>
       </c>
       <c r="E236" s="4" t="n">
-        <v>39.34</v>
+        <v>46.42</v>
       </c>
       <c r="F236" s="4" t="n">
-        <v>44.57</v>
+        <v>48.69</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>GARFIBRES</t>
+          <t>ORIENTCEM</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -6722,22 +7042,22 @@
         </is>
       </c>
       <c r="C237" s="4" t="n">
-        <v>614.75</v>
+        <v>141.47</v>
       </c>
       <c r="D237" s="4" t="n">
-        <v>45.12</v>
+        <v>48</v>
       </c>
       <c r="E237" s="4" t="n">
-        <v>41</v>
+        <v>34.86</v>
       </c>
       <c r="F237" s="4" t="n">
-        <v>38.83</v>
+        <v>36.26</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>TEGA</t>
+          <t>VIPIND</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -6746,22 +7066,22 @@
         </is>
       </c>
       <c r="C238" s="4" t="n">
-        <v>1663.4</v>
+        <v>309</v>
       </c>
       <c r="D238" s="4" t="n">
-        <v>44.62</v>
+        <v>47.76</v>
       </c>
       <c r="E238" s="4" t="n">
-        <v>42.63</v>
+        <v>37.07</v>
       </c>
       <c r="F238" s="4" t="n">
-        <v>52.68</v>
+        <v>36.71</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>IXIGO</t>
+          <t>RENUKA</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
@@ -6770,22 +7090,22 @@
         </is>
       </c>
       <c r="C239" s="4" t="n">
-        <v>168.08</v>
+        <v>27.59</v>
       </c>
       <c r="D239" s="4" t="n">
-        <v>44.45</v>
+        <v>47.72</v>
       </c>
       <c r="E239" s="4" t="n">
-        <v>38.09</v>
+        <v>52.45</v>
       </c>
       <c r="F239" s="4" t="n">
-        <v>42.92</v>
+        <v>41.85</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>SANOFI</t>
+          <t>SYMPHONY</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -6794,22 +7114,22 @@
         </is>
       </c>
       <c r="C240" s="4" t="n">
-        <v>3407.2</v>
+        <v>794.3</v>
       </c>
       <c r="D240" s="4" t="n">
-        <v>44.06</v>
+        <v>47.08</v>
       </c>
       <c r="E240" s="4" t="n">
-        <v>30.98</v>
+        <v>44.7</v>
       </c>
       <c r="F240" s="4" t="n">
-        <v>30.61</v>
+        <v>41.69</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>LUMAXTECH</t>
+          <t>GMMPFAUDLR</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
@@ -6818,22 +7138,22 @@
         </is>
       </c>
       <c r="C241" s="4" t="n">
-        <v>1621.4</v>
+        <v>894.1</v>
       </c>
       <c r="D241" s="4" t="n">
-        <v>43.87</v>
+        <v>46.92</v>
       </c>
       <c r="E241" s="4" t="n">
-        <v>54.72</v>
+        <v>38.97</v>
       </c>
       <c r="F241" s="4" t="n">
-        <v>68.29000000000001</v>
+        <v>40.73</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>SFL</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -6842,22 +7162,22 @@
         </is>
       </c>
       <c r="C242" s="4" t="n">
-        <v>509.05</v>
+        <v>96.76000000000001</v>
       </c>
       <c r="D242" s="4" t="n">
-        <v>43.66</v>
+        <v>46.9</v>
       </c>
       <c r="E242" s="4" t="n">
-        <v>38.68</v>
+        <v>37.67</v>
       </c>
       <c r="F242" s="4" t="n">
-        <v>35.18</v>
+        <v>37.93</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>JUSTDIAL</t>
+          <t>TEGA</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -6866,22 +7186,22 @@
         </is>
       </c>
       <c r="C243" s="4" t="n">
-        <v>525.95</v>
+        <v>1662</v>
       </c>
       <c r="D243" s="4" t="n">
-        <v>42.6</v>
+        <v>46.52</v>
       </c>
       <c r="E243" s="4" t="n">
-        <v>33.18</v>
+        <v>41.62</v>
       </c>
       <c r="F243" s="4" t="n">
-        <v>34.68</v>
+        <v>52.63</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>EMBDL</t>
+          <t>IXIGO</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -6890,22 +7210,22 @@
         </is>
       </c>
       <c r="C244" s="4" t="n">
-        <v>46.28</v>
+        <v>168.38</v>
       </c>
       <c r="D244" s="4" t="n">
-        <v>42.52</v>
+        <v>46.09</v>
       </c>
       <c r="E244" s="4" t="n">
-        <v>33.76</v>
+        <v>38.87</v>
       </c>
       <c r="F244" s="4" t="n">
-        <v>30.65</v>
+        <v>43.01</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>CMSINFO</t>
+          <t>RAYMONDLSL</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
@@ -6914,22 +7234,22 @@
         </is>
       </c>
       <c r="C245" s="4" t="n">
-        <v>290.35</v>
+        <v>788.65</v>
       </c>
       <c r="D245" s="4" t="n">
-        <v>41.93</v>
+        <v>45.95</v>
       </c>
       <c r="E245" s="4" t="n">
-        <v>37.28</v>
+        <v>37.87</v>
       </c>
       <c r="F245" s="4" t="n">
-        <v>37.06</v>
+        <v>22.82</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -6938,22 +7258,22 @@
         </is>
       </c>
       <c r="C246" s="4" t="n">
-        <v>93.55</v>
+        <v>180.84</v>
       </c>
       <c r="D246" s="4" t="n">
-        <v>40.16</v>
+        <v>45.77</v>
       </c>
       <c r="E246" s="4" t="n">
-        <v>35.34</v>
+        <v>54.48</v>
       </c>
       <c r="F246" s="4" t="n">
-        <v>36.84</v>
+        <v>59.18</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>BLACKBUCK</t>
+          <t>CMSINFO</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
@@ -6962,22 +7282,22 @@
         </is>
       </c>
       <c r="C247" s="4" t="n">
-        <v>548.05</v>
+        <v>289.6</v>
       </c>
       <c r="D247" s="4" t="n">
-        <v>38.41</v>
+        <v>43.36</v>
       </c>
       <c r="E247" s="4" t="n">
-        <v>44.24</v>
+        <v>37.28</v>
       </c>
       <c r="F247" s="4" t="n">
-        <v>51.95</v>
+        <v>36.98</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>CCAVENUE</t>
+          <t>VOLTAMP</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -6986,22 +7306,22 @@
         </is>
       </c>
       <c r="C248" s="4" t="n">
-        <v>13.74</v>
+        <v>9535</v>
       </c>
       <c r="D248" s="4" t="n">
-        <v>37.5</v>
+        <v>42.75</v>
       </c>
       <c r="E248" s="4" t="n">
-        <v/>
+        <v>55.11</v>
       </c>
       <c r="F248" s="4" t="n">
-        <v/>
+        <v>54.42</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>CARTRADE</t>
+          <t>CSBBANK</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
@@ -7010,22 +7330,22 @@
         </is>
       </c>
       <c r="C249" s="4" t="n">
-        <v>1623.4</v>
+        <v>365.05</v>
       </c>
       <c r="D249" s="4" t="n">
-        <v>37.31</v>
+        <v>42.5</v>
       </c>
       <c r="E249" s="4" t="n">
-        <v>35.4</v>
+        <v>44.01</v>
       </c>
       <c r="F249" s="4" t="n">
-        <v>47.54</v>
+        <v>50.41</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>VIPIND</t>
+          <t>CCAVENUE</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
@@ -7034,22 +7354,22 @@
         </is>
       </c>
       <c r="C250" s="4" t="n">
-        <v>296.25</v>
+        <v>13.95</v>
       </c>
       <c r="D250" s="4" t="n">
-        <v>33.89</v>
+        <v>41.92</v>
       </c>
       <c r="E250" s="4" t="n">
-        <v>31.71</v>
+        <v>37.56</v>
       </c>
       <c r="F250" s="4" t="n">
-        <v>34.65</v>
+        <v/>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>SAFARI</t>
+          <t>SANOFI</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
@@ -7058,16 +7378,16 @@
         </is>
       </c>
       <c r="C251" s="4" t="n">
-        <v>1412.5</v>
+        <v>3330.6</v>
       </c>
       <c r="D251" s="4" t="n">
-        <v>33.58</v>
+        <v>35.79</v>
       </c>
       <c r="E251" s="4" t="n">
-        <v>30.09</v>
+        <v>29.37</v>
       </c>
       <c r="F251" s="4" t="n">
-        <v>37.7</v>
+        <v>30.4</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Micro250_stocks.xlsx
+++ b/reports/Micro250_stocks.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -546,37 +546,37 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>375.95</v>
+        <v>419.8</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>85.47</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>91.27</v>
+        <v>92.67</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>83.93000000000001</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>21.74</v>
+        <v>21.31</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>172.4</v>
+        <v>187.62</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>159.23</v>
+        <v>171.38</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>7017711</v>
+        <v>7152897</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>18351</v>
+        <v>20492</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>PRIVISCL</t>
+          <t>ARVIND</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -585,37 +585,37 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>3487.9</v>
+        <v>451.1</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>80.56999999999999</v>
+        <v>72.55</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>69.94</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>71.25</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>20.85</v>
+        <v>23.84</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>2887.47</v>
+        <v>357.86</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>2787.18</v>
+        <v>353.04</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>107278</v>
+        <v>866094</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>13625</v>
+        <v>11824</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>MEDPLUS</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -624,37 +624,37 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>1387</v>
+        <v>951</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>78.98999999999999</v>
+        <v>72.19</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>70.56</v>
+        <v>66.56</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>69.79000000000001</v>
+        <v>61.77</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>33.21</v>
+        <v>31.7</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>982.39</v>
+        <v>839.39</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>960.4</v>
+        <v>832.33</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>447675</v>
+        <v>137673</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>9260</v>
+        <v>11412</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>STAR</t>
+          <t>GRWRHITECH</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -663,37 +663,37 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1156.9</v>
+        <v>5403.4</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>76.48</v>
+        <v>69.81</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>71.95</v>
+        <v>72.05</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>62.76</v>
+        <v>63.31</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>24.9</v>
+        <v>25.12</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>922.98</v>
+        <v>3851.83</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>910.72</v>
+        <v>3776.45</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>296780</v>
+        <v>139260</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>10663</v>
+        <v>12553</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>SUNFLAG</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -702,37 +702,37 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>222.81</v>
+        <v>373.45</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>75.29000000000001</v>
+        <v>66</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>76.62</v>
+        <v>68.7</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>67.91</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>20.16</v>
+        <v>26.29</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>171.96</v>
+        <v>269.14</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>170.35</v>
+        <v>265.85</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>2326753</v>
+        <v>1426600</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>6595</v>
+        <v>6730</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>GRWRHITECH</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -741,37 +741,37 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>5290.3</v>
+        <v>211.13</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>75.12</v>
+        <v>59.63</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>71.15000000000001</v>
+        <v>68.06999999999999</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>62.81</v>
+        <v>65.68000000000001</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>21.6</v>
+        <v>30.9</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>3754.51</v>
+        <v>174.34</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3699.67</v>
+        <v>172.23</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>136256</v>
+        <v>2365831</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>12291</v>
+        <v>6250</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>SANDUMA</t>
+          <t>CEIGALL</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -780,37 +780,37 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>241.11</v>
+        <v>345.4</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>74.12</v>
+        <v>57.44</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>61.78</v>
+        <v>66.31999999999999</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>63.51</v>
+        <v>62.77</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>49.55</v>
+        <v>20.02</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>201.29</v>
+        <v>287.82</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>197.02</v>
+        <v>285.12</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>2467898</v>
+        <v>677116</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>11720</v>
+        <v>6017</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>GAEL</t>
+          <t>SANSERA</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -819,37 +819,37 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>166.46</v>
+        <v>2385</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>70.16</v>
+        <v>47.3</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>70.54000000000001</v>
+        <v>62.86</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>65.48</v>
+        <v>68.81</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>27.38</v>
+        <v>33.48</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>133.55</v>
+        <v>2002.82</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>130.46</v>
+        <v>1899.66</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1031500</v>
+        <v>221004</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>7635</v>
+        <v>14866</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ARVIND</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -858,37 +858,37 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>435</v>
+        <v>246.1</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>69.48999999999999</v>
+        <v>45.81</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>70.47</v>
+        <v>62.82</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>66.31</v>
+        <v>61.29</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>25.25</v>
+        <v>34.06</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>351.98</v>
+        <v>216.09</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>348.4</v>
+        <v>210.71</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>765911</v>
+        <v>2967112</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>11402</v>
+        <v>9307</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ANURAS</t>
+          <t>AVANTIFEED</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -897,421 +897,31 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1372.1</v>
+        <v>1323.2</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>66.05</v>
+        <v>45.34</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>66.28</v>
+        <v>60.18</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>70.79000000000001</v>
+        <v>71.66</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>23.21</v>
+        <v>37.83</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1233.63</v>
+        <v>1092.59</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1197.24</v>
+        <v>1027.75</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>283910</v>
+        <v>1086347</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>15621</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>THANGAMAYL</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>4246.7</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>65.68000000000001</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>64.13</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>74.89</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>27.26</v>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>3359.94</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>3168.9</v>
-      </c>
-      <c r="J12" s="4" t="n">
-        <v>108481</v>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>13200</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>GALLANTT</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>869.25</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>64.81</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>73.54000000000001</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>70.51000000000001</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>21.05</v>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>628.92</v>
-      </c>
-      <c r="I13" s="4" t="n">
-        <v>605.46</v>
-      </c>
-      <c r="J13" s="4" t="n">
-        <v>6022576</v>
-      </c>
-      <c r="K13" s="4" t="n">
-        <v>20973</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>UJJIVANSFB</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>62.4</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>63.9</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>61.35</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>62.08</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>35.12</v>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>55.18</v>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>53.7</v>
-      </c>
-      <c r="J14" s="4" t="n">
-        <v>15758015</v>
-      </c>
-      <c r="K14" s="4" t="n">
-        <v>12133</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>ASTRAMICRO</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>1147.4</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>62.94</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>64.25</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>64.3</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>55.42</v>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>993.35</v>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>981.02</v>
-      </c>
-      <c r="J15" s="4" t="n">
-        <v>444790</v>
-      </c>
-      <c r="K15" s="4" t="n">
-        <v>10894</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>EDELWEISS</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>125.14</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>62.36</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>60.97</v>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>60.77</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>37.97</v>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>111.48</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>110.17</v>
-      </c>
-      <c r="J16" s="4" t="n">
-        <v>5445843</v>
-      </c>
-      <c r="K16" s="4" t="n">
-        <v>11845</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>SANSERA</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>2519.8</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>59.41</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>70.02</v>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v>72.95999999999999</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>20.77</v>
-      </c>
-      <c r="H17" s="4" t="n">
-        <v>1974.93</v>
-      </c>
-      <c r="I17" s="4" t="n">
-        <v>1873.51</v>
-      </c>
-      <c r="J17" s="4" t="n">
-        <v>235693</v>
-      </c>
-      <c r="K17" s="4" t="n">
-        <v>15706</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>IMFA</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>1548.1</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>59.03</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>64.31999999999999</v>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>70.69</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>32.81</v>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>1262.33</v>
-      </c>
-      <c r="I18" s="4" t="n">
-        <v>1203.32</v>
-      </c>
-      <c r="J18" s="4" t="n">
-        <v>263287</v>
-      </c>
-      <c r="K18" s="4" t="n">
-        <v>8353</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>AETHER</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>1213.4</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>58.39</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>68.01000000000001</v>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>71.38</v>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="H19" s="4" t="n">
-        <v>992.71</v>
-      </c>
-      <c r="I19" s="4" t="n">
-        <v>960.01</v>
-      </c>
-      <c r="J19" s="4" t="n">
-        <v>402172</v>
-      </c>
-      <c r="K19" s="4" t="n">
-        <v>16099</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>AVANTIFEED</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>1435.2</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>58.35</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>68.09999999999999</v>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>76.23999999999999</v>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>27.93</v>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>1074.76</v>
-      </c>
-      <c r="I20" s="4" t="n">
-        <v>1011.23</v>
-      </c>
-      <c r="J20" s="4" t="n">
-        <v>1107422</v>
-      </c>
-      <c r="K20" s="4" t="n">
-        <v>19554</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>KTKBANK</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>259.35</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>57.57</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>71.33</v>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>65.02</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>22.79</v>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>213.89</v>
-      </c>
-      <c r="I21" s="4" t="n">
-        <v>208.77</v>
-      </c>
-      <c r="J21" s="4" t="n">
-        <v>3266548</v>
-      </c>
-      <c r="K21" s="4" t="n">
-        <v>9808</v>
+        <v>18028</v>
       </c>
     </row>
   </sheetData>
@@ -1326,16 +936,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1393,7 +993,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SUNFLAG</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -1402,22 +1002,22 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>415.85</v>
+        <v>419.8</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>88.93000000000001</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>80.28</v>
+        <v>92.67</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>69.03</v>
+        <v>85.70999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>SKYGOLD</t>
+          <t>LLOYDSENGG</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -1426,22 +1026,22 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>541.25</v>
+        <v>70.59</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>85.62</v>
+        <v>77.31</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>77.51000000000001</v>
+        <v>68.89</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>71.75</v>
+        <v>56.76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>TDPOWERSYS</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -1450,22 +1050,22 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>375.95</v>
+        <v>1311.3</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>85.47</v>
+        <v>77.02</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>91.27</v>
+        <v>81.33</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>83.93000000000001</v>
+        <v>84.64</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>MANINFRA</t>
+          <t>DIACABS</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -1474,22 +1074,22 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>134.73</v>
+        <v>196.45</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>85.31</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>60.91</v>
+        <v>76.03</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>47.83</v>
+        <v>66.45</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>CEIGALL</t>
+          <t>BALAMINES</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -1498,22 +1098,22 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>376.8</v>
+        <v>1706.2</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>83.51000000000001</v>
+        <v>75.65000000000001</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>81.01000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>68.39</v>
+        <v>52.47</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>THYROCARE</t>
+          <t>SHAILY</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1522,22 +1122,22 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>486.5</v>
+        <v>2768.3</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>81.78</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>65.83</v>
+        <v>65.29000000000001</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>63.49</v>
+        <v>69.76000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>INDIAGLYCO</t>
+          <t>SHILPAMED</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1546,22 +1146,22 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>1150.4</v>
+        <v>478.4</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>81.26000000000001</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>68.68000000000001</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>65.34</v>
+        <v>65.09</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>PRIVISCL</t>
+          <t>STAR</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -1570,22 +1170,22 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>3487.9</v>
+        <v>1153.7</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>80.56999999999999</v>
+        <v>73.43000000000001</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>69.94</v>
+        <v>71.48999999999999</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>71.25</v>
+        <v>62.66</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AZAD</t>
+          <t>ARVIND</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1594,22 +1194,22 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2315.6</v>
+        <v>451.1</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>80.38</v>
+        <v>72.55</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>75.81999999999999</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>67.27</v>
+        <v>67.70999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>CYIENTDLM</t>
+          <t>MEDPLUS</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -1618,16 +1218,16 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>432.9</v>
+        <v>951</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>79.59999999999999</v>
+        <v>72.19</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>62.19</v>
+        <v>66.56</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>45.82</v>
+        <v>61.77</v>
       </c>
     </row>
     <row r="12">
@@ -1642,22 +1242,22 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>703.45</v>
+        <v>712.6</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>79.37</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>55.39</v>
+        <v>56.28</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>46.72</v>
+        <v>47.04</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1666,22 +1266,22 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1387</v>
+        <v>299.95</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>78.98999999999999</v>
+        <v>71.68000000000001</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>70.56</v>
+        <v>61.38</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>69.79000000000001</v>
+        <v>58.33</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>CEMPRO</t>
+          <t>MTARTECH</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1690,22 +1290,22 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>956.15</v>
+        <v>7234</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>78.42</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>75.61</v>
+        <v>90.42</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v/>
+        <v>86.54000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>INNOVACAP</t>
+          <t>GRWRHITECH</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1714,22 +1314,22 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>875.75</v>
+        <v>5403.4</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>78.34</v>
+        <v>69.81</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>67.54000000000001</v>
+        <v>72.05</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>59.31</v>
+        <v>63.31</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>PNGJL</t>
+          <t>REFEX</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1738,22 +1338,22 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>727.9</v>
+        <v>277.8</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>77.43000000000001</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>71.53</v>
+        <v>54.8</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>62.73</v>
+        <v>48.53</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>RATNAMANI</t>
+          <t>INDIGOPNTS</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1762,22 +1362,22 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2869.4</v>
+        <v>985.3</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>77.40000000000001</v>
+        <v>68.62</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>67.56</v>
+        <v>52.24</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>54.89</v>
+        <v>44.43</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>RBA</t>
+          <t>RAIN</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1786,22 +1386,22 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>68.09</v>
+        <v>156.99</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>77.22</v>
+        <v>68.43000000000001</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>55.69</v>
+        <v>61.3</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>41.03</v>
+        <v>52.85</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>STAR</t>
+          <t>KANSAINER</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1810,22 +1410,22 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1156.9</v>
+        <v>222.07</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>76.48</v>
+        <v>68.42</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>71.95</v>
+        <v>55.64</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>62.76</v>
+        <v>44.71</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>INGERRAND</t>
+          <t>HCG</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1834,22 +1434,22 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>4575.3</v>
+        <v>637.2</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>76.45</v>
+        <v>68.28</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>69.92</v>
+        <v>58.85</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>63.14</v>
+        <v>60.02</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>BALAMINES</t>
+          <t>RBA</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1858,22 +1458,22 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1487.2</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>76.38</v>
+        <v>67.91</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>69.36</v>
+        <v>54.83</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>47.84</v>
+        <v>40.73</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>INNOVACAP</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1882,22 +1482,22 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1219.6</v>
+        <v>858.3</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>76.09999999999999</v>
+        <v>67.64</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>78.66</v>
+        <v>64.67</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>83.19</v>
+        <v>58.34</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>NEOGEN</t>
+          <t>TEAMLEASE</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1906,22 +1506,22 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1772.4</v>
+        <v>1364.6</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>75.93000000000001</v>
+        <v>67.33</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>66.79000000000001</v>
+        <v>47.91</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>55.86</v>
+        <v>35.68</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>MIDHANI</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1930,22 +1530,22 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>421.25</v>
+        <v>1323.1</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>75.73999999999999</v>
+        <v>66.87</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>65.13</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>56.18</v>
+        <v>68.40000000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>MARKSANS</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1954,22 +1554,22 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>222.81</v>
+        <v>207.45</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>75.29000000000001</v>
+        <v>66.68000000000001</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>76.62</v>
+        <v>63.39</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>67.91</v>
+        <v>53.77</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>ADVENZYMES</t>
+          <t>CYIENTDLM</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1978,22 +1578,22 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>357.25</v>
+        <v>416.25</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>75.23</v>
+        <v>66.25</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>65.48</v>
+        <v>58.32</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>55.04</v>
+        <v>44.33</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GABRIEL</t>
+          <t>SUNFLAG</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -2002,22 +1602,22 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1131.9</v>
+        <v>373.45</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>75.14</v>
+        <v>66</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>61.16</v>
+        <v>68.7</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>65.34</v>
+        <v>66.01000000000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>GRWRHITECH</t>
+          <t>SFL</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -2026,22 +1626,22 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>5290.3</v>
+        <v>604.95</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>75.12</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>71.15000000000001</v>
+        <v>56.27</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>62.81</v>
+        <v>42.16</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>YATHARTH</t>
+          <t>V2RETAIL</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -2050,22 +1650,22 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>862.2</v>
+        <v>228.24</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>74.56999999999999</v>
+        <v>65.38</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>66.81</v>
+        <v>60.72</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>64.7</v>
+        <v>66.95999999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>LXCHEM</t>
+          <t>ANURAS</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -2074,22 +1674,22 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>164.84</v>
+        <v>1376</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>74.48999999999999</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>57.73</v>
+        <v>66.64</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>42.89</v>
+        <v>70.93000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>SHAILY</t>
+          <t>CEMPRO</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -2098,22 +1698,22 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2679.2</v>
+        <v>899.55</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>74.18000000000001</v>
+        <v>65.06</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>63.59</v>
+        <v>68.12</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>68.79000000000001</v>
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>SANDUMA</t>
+          <t>KIRLPNU</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -2122,22 +1722,22 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>241.11</v>
+        <v>1541.4</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>74.12</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>61.78</v>
+        <v>75.44</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>63.51</v>
+        <v>63.33</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>HEMIPROP</t>
+          <t>THYROCARE</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -2146,22 +1746,22 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>154.21</v>
+        <v>462.15</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>73.98999999999999</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>60.17</v>
+        <v>60.08</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>53.09</v>
+        <v>61.81</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>INDIGOPNTS</t>
+          <t>JSFB</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -2170,22 +1770,22 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>974.15</v>
+        <v>490.85</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>73.94</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>51.29</v>
+        <v>67.97</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>44.05</v>
+        <v>54.79</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MTARTECH</t>
+          <t>EMBDL</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -2194,22 +1794,22 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>6470</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>73.83</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>88.38</v>
+        <v>54.7</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>84.75</v>
+        <v>41.43</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>QUESS</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -2218,22 +1818,22 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>223.59</v>
+        <v>514.35</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>73.56</v>
+        <v>64.77</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>56.52</v>
+        <v>61.13</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>35.95</v>
+        <v>50.45</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>BORORENEW</t>
+          <t>ADVENZYMES</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -2242,22 +1842,22 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>561.75</v>
+        <v>363.75</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>73.38</v>
+        <v>64.48</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>58.86</v>
+        <v>66.75</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>53.49</v>
+        <v>55.84</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>KIRLPNU</t>
+          <t>GABRIEL</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -2266,22 +1866,22 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>1560.2</v>
+        <v>1091</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>73.18000000000001</v>
+        <v>63.57</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>77.64</v>
+        <v>57.76</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>63.77</v>
+        <v>64.18000000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>SPARC</t>
+          <t>DCAL</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -2290,22 +1890,22 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>173.09</v>
+        <v>194.25</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>73.06999999999999</v>
+        <v>63.33</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>67.41</v>
+        <v>48.75</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>50.81</v>
+        <v>47.86</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>IIFLCAPS</t>
+          <t>LLOYDSENT</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -2314,22 +1914,22 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>356.3</v>
+        <v>70.5</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>72.7</v>
+        <v>63.21</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>60.22</v>
+        <v>61.3</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>56.64</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENGG</t>
+          <t>PGIL</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -2338,22 +1938,22 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>62.87</v>
+        <v>1671.6</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>72.41</v>
+        <v>62.86</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>62.82</v>
+        <v>56.82</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>53.03</v>
+        <v>63.4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>EMBDL</t>
+          <t>ISGEC</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -2362,22 +1962,22 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>69.98</v>
+        <v>1085.7</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>72.39</v>
+        <v>62.6</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>54.54</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>41.33</v>
+        <v>53.96</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>RATEGAIN</t>
+          <t>STYRENIX</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -2386,22 +1986,22 @@
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>634.75</v>
+        <v>2344.8</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>71.97</v>
+        <v>62.45</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>58.89</v>
+        <v>59.91</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>53.5</v>
+        <v>55.33</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>SENCO</t>
+          <t>IIFLCAPS</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -2410,22 +2010,22 @@
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>365.4</v>
+        <v>342.95</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>71.51000000000001</v>
+        <v>62.3</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>60.5</v>
+        <v>56.91</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>51.47</v>
+        <v>55.16</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>AWFIS</t>
+          <t>ACUTAAS</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -2434,22 +2034,22 @@
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>379.15</v>
+        <v>2731</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>71.47</v>
+        <v>61.54</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>47.57</v>
+        <v>70.77</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>38.13</v>
+        <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>KANSAINER</t>
+          <t>GAEL</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -2458,22 +2058,22 @@
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>220.35</v>
+        <v>162.79</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>71.23999999999999</v>
+        <v>61.44</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>54.93</v>
+        <v>67.17</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>44.28</v>
+        <v>64.42</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>ALIVUS</t>
+          <t>HEMIPROP</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -2482,22 +2082,22 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>1121.3</v>
+        <v>148.97</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>71.17</v>
+        <v>61.31</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>73.56999999999999</v>
+        <v>56.94</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>69.01000000000001</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>PARAS</t>
+          <t>GMRP&amp;UI</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -2506,22 +2106,22 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>866.6</v>
+        <v>113.9</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>71.06</v>
+        <v>61.23</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>66.05</v>
+        <v>53.95</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>55.37</v>
+        <v>55.58</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>EPIGRAL</t>
+          <t>TIPSMUSIC</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -2530,22 +2130,22 @@
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>1327.1</v>
+        <v>646.65</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>70.98999999999999</v>
+        <v>60.98</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>58.76</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>47.84</v>
+        <v>59.06</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>OPTIEMUS</t>
+          <t>VSTIND</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -2554,22 +2154,22 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>462.5</v>
+        <v>260.2</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>70.94</v>
+        <v>60.82</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>53.69</v>
+        <v>57.42</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>49.71</v>
+        <v>47.53</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>POWERMECH</t>
+          <t>SPARC</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -2578,22 +2178,22 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>2605.8</v>
+        <v>163.65</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>70.78</v>
+        <v>60.78</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>61.9</v>
+        <v>61.64</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>53.32</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>HIKAL</t>
+          <t>PRUDENT</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -2602,22 +2202,22 @@
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>210.75</v>
+        <v>2832.3</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>70.73999999999999</v>
+        <v>60.58</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>51.13</v>
+        <v>61.8</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>40.83</v>
+        <v>59.77</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENT</t>
+          <t>BIRLACORPN</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -2626,22 +2226,22 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>71.64</v>
+        <v>1018.65</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>70.65000000000001</v>
+        <v>60.56</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>62.76</v>
+        <v>51.09</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>58.02</v>
+        <v>44.74</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>DYNAMATECH</t>
+          <t>EMIL</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -2650,22 +2250,22 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>12530</v>
+        <v>119.89</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>70.64</v>
+        <v>60.44</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>68.88</v>
+        <v>57.98</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>73.59</v>
+        <v>46.78</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>ABDL</t>
+          <t>INGERRAND</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -2674,22 +2274,22 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>591.3</v>
+        <v>4398.7</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>70.34999999999999</v>
+        <v>60.06</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>59.39</v>
+        <v>63.83</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>61.15</v>
+        <v>61.21</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>EQUITASBNK</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -2698,22 +2298,22 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>72.45</v>
+        <v>211.13</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>70.25</v>
+        <v>59.63</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>63.4</v>
+        <v>68.06999999999999</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>53.56</v>
+        <v>65.68000000000001</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>TEAMLEASE</t>
+          <t>VARROC</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -2722,22 +2322,22 @@
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>1354.1</v>
+        <v>557.85</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>70.22</v>
+        <v>59.39</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>47.05</v>
+        <v>51.96</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>35.38</v>
+        <v>52.67</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>GAEL</t>
+          <t>MIDHANI</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -2746,22 +2346,22 @@
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>166.46</v>
+        <v>408.05</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>70.16</v>
+        <v>59.35</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>70.54000000000001</v>
+        <v>61.56</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>65.48</v>
+        <v>55.17</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>HCC</t>
+          <t>VIYASH</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -2770,22 +2370,22 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>23.3</v>
+        <v>224.54</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>69.84999999999999</v>
+        <v>59.07</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>59.32</v>
+        <v>67.87</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>47.43</v>
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>KSCL</t>
+          <t>SANOFICONR</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -2794,22 +2394,22 @@
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>992.6</v>
+        <v>4868.4</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>69.8</v>
+        <v>58.69</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>57.62</v>
+        <v>58.62</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>52.75</v>
+        <v>51.84</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>JAIBALAJI</t>
+          <t>RATEGAIN</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -2818,22 +2418,22 @@
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>83.53</v>
+        <v>625.35</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>69.77</v>
+        <v>58.56</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>57.11</v>
+        <v>57.21</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>44.92</v>
+        <v>52.97</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>DATAMATICS</t>
+          <t>INDIASHLTR</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -2842,22 +2442,22 @@
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>818.4</v>
+        <v>826.55</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>69.77</v>
+        <v>58.35</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>56.74</v>
+        <v>56.51</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>56.1</v>
+        <v>56.22</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>AJAXENGG</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -2866,22 +2466,22 @@
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>555</v>
+        <v>458.95</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>69.59999999999999</v>
+        <v>58.26</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>54.26</v>
+        <v>53.35</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>46.89</v>
+        <v>54.09</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>ICIL</t>
+          <t>PRICOLLTD</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -2890,22 +2490,22 @@
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>306</v>
+        <v>614.7</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>69.55</v>
+        <v>58.01</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>58.31</v>
+        <v>56.68</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>53.64</v>
+        <v>60.87</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>NESCO</t>
+          <t>TEXRAIL</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -2914,22 +2514,22 @@
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>1311.3</v>
+        <v>116.23</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>69.54000000000001</v>
+        <v>57.83</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>60.9</v>
+        <v>51.69</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>61.96</v>
+        <v>45.39</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>ARVIND</t>
+          <t>DHANUKA</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -2938,22 +2538,22 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>435</v>
+        <v>1083.5</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>69.48999999999999</v>
+        <v>57.81</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>70.47</v>
+        <v>45.44</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>66.31</v>
+        <v>44.39</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>ACUTAAS</t>
+          <t>ICIL</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -2962,22 +2562,22 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>2734.3</v>
+        <v>290.2</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>69.39</v>
+        <v>57.64</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>70.92</v>
+        <v>54.33</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v/>
+        <v>51.71</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>RAIN</t>
+          <t>CEIGALL</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -2986,22 +2586,22 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>143.82</v>
+        <v>345.4</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>69.08</v>
+        <v>57.44</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>56.21</v>
+        <v>66.31999999999999</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>50.09</v>
+        <v>62.77</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>SHILPAMED</t>
+          <t>GANESHHOU</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -3010,22 +2610,22 @@
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>437</v>
+        <v>685.5</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>68.88</v>
+        <v>57.35</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>67.22</v>
+        <v>47.7</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>61.73</v>
+        <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>TEXRAIL</t>
+          <t>JKPAPER</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -3034,22 +2634,22 @@
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>114.97</v>
+        <v>381.65</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>68.70999999999999</v>
+        <v>57.35</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>50.84</v>
+        <v>58.46</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>45.09</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>V2RETAIL</t>
+          <t>YATHARTH</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -3058,22 +2658,22 @@
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>219.64</v>
+        <v>815.6</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>68.36</v>
+        <v>57.24</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>57.65</v>
+        <v>60.72</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>65.51000000000001</v>
+        <v>62.73</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>VSTIND</t>
+          <t>NEOGEN</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -3082,22 +2682,22 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>264.4</v>
+        <v>1664.8</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>68.06999999999999</v>
+        <v>57.09</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>59.88</v>
+        <v>60.87</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>48.4</v>
+        <v>53.82</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>MANORAMA</t>
+          <t>PNCINFRA</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -3106,22 +2706,22 @@
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>1576.2</v>
+        <v>217.64</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>68.01000000000001</v>
+        <v>57.07</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>63.98</v>
+        <v>47.11</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>66.34</v>
+        <v>40.53</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>DIACABS</t>
+          <t>LXCHEM</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -3130,22 +2730,22 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>172.85</v>
+        <v>152.49</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>67.84999999999999</v>
+        <v>56.66</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>69.23999999999999</v>
+        <v>51.3</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>62.84</v>
+        <v>39.89</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>PNCINFRA</t>
+          <t>ABDL</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -3154,22 +2754,22 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>224.69</v>
+        <v>555.35</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>67.8</v>
+        <v>56.22</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>49.92</v>
+        <v>54.55</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>41.68</v>
+        <v>58.85</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>GANESHHOU</t>
+          <t>SKIPPER</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -3178,22 +2778,22 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>714.35</v>
+        <v>460.2</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>67.70999999999999</v>
+        <v>56.22</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>52.2</v>
+        <v>58.07</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v/>
+        <v>55.24</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>KSL</t>
+          <t>HIKAL</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -3202,22 +2802,22 @@
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>862.5</v>
+        <v>201.46</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>67.68000000000001</v>
+        <v>56.08</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>63.8</v>
+        <v>48.12</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>54.89</v>
+        <v>39.26</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>TVSSCS</t>
+          <t>CMSINFO</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -3226,22 +2826,22 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>125.29</v>
+        <v>302.95</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>67.58</v>
+        <v>55.94</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>57.75</v>
+        <v>43.02</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>45.21</v>
+        <v>39.33</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>GRINFRA</t>
+          <t>MAXESTATES</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -3250,22 +2850,22 @@
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>979.9</v>
+        <v>404.9</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>67.51000000000001</v>
+        <v>55.91</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>50.74</v>
+        <v>49.83</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>42.48</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>INOXGREEN</t>
+          <t>SANDUMA</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -3274,22 +2874,22 @@
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>190.61</v>
+        <v>224.24</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>67.43000000000001</v>
+        <v>55.74</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>55.75</v>
+        <v>55.72</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>54.61</v>
+        <v>61.02</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>SURYAROSNI</t>
+          <t>SUPRIYA</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -3298,22 +2898,22 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>266</v>
+        <v>688.55</v>
       </c>
       <c r="D81" s="4" t="n">
-        <v>67.23</v>
+        <v>55.58</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>57.28</v>
+        <v>53.22</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>50.9</v>
+        <v>55.41</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>BALUFORGE</t>
+          <t>AZAD</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -3322,16 +2922,16 @@
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>550.05</v>
+        <v>2098.2</v>
       </c>
       <c r="D82" s="4" t="n">
-        <v>66.81</v>
+        <v>54.96</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>54.95</v>
+        <v>63.73</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>51.27</v>
+        <v>62.96</v>
       </c>
     </row>
     <row r="83">
@@ -3346,22 +2946,22 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>677.8</v>
+        <v>641.2</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>66.58</v>
+        <v>54.28</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>55.51</v>
+        <v>50.24</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>48.38</v>
+        <v>46.38</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>FDC</t>
+          <t>ASTRAMICRO</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -3370,22 +2970,22 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>380.2</v>
+        <v>1106.6</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>66.51000000000001</v>
+        <v>54.28</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>50.64</v>
+        <v>59.53</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>46.44</v>
+        <v>62.42</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>CIGNITITEC</t>
+          <t>KNRCON</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -3394,22 +2994,22 @@
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>1360</v>
+        <v>129.56</v>
       </c>
       <c r="D85" s="4" t="n">
-        <v>66.41</v>
+        <v>54.24</v>
       </c>
       <c r="E85" s="4" t="n">
-        <v>49.18</v>
+        <v>43.11</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>49.72</v>
+        <v>34.65</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>STYRENIX</t>
+          <t>GREAVESCOT</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -3418,22 +3018,22 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>2334.3</v>
+        <v>165.76</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>66.31999999999999</v>
+        <v>54.2</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>59.53</v>
+        <v>49.34</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>55.13</v>
+        <v>47.51</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>ANURAS</t>
+          <t>POWERMECH</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -3442,22 +3042,22 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>1372.1</v>
+        <v>2441</v>
       </c>
       <c r="D87" s="4" t="n">
-        <v>66.05</v>
+        <v>54.11</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>66.28</v>
+        <v>54.75</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>70.79000000000001</v>
+        <v>51.06</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>KSL</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -3466,22 +3066,22 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>496.15</v>
+        <v>814.05</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>65.98999999999999</v>
+        <v>53.95</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>57.68</v>
+        <v>57.13</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>48.7</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>SFL</t>
+          <t>EUREKAFORB</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -3490,22 +3090,22 @@
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>580.85</v>
+        <v>511.8</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>65.95999999999999</v>
+        <v>53.93</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>52.59</v>
+        <v>48.5</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>40.55</v>
+        <v>45.95</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>ISGEC</t>
+          <t>EQUITASBNK</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -3514,22 +3114,22 @@
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>1075.1</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>65.73</v>
+        <v>53.87</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>66.31</v>
+        <v>56.28</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>53.54</v>
+        <v>51.12</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>HCC</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -3538,22 +3138,22 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>4246.7</v>
+        <v>21.41</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>65.68000000000001</v>
+        <v>53.81</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>64.13</v>
+        <v>53.24</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>74.89</v>
+        <v>45.61</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>WEBELSOLAR</t>
+          <t>WELENT</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -3562,22 +3162,22 @@
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>114.94</v>
+        <v>510.75</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>65.56999999999999</v>
+        <v>53.72</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>63.93</v>
+        <v>54.71</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>55.8</v>
+        <v>54.76</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>ALLCARGO</t>
+          <t>ZYDUSWELL</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -3586,22 +3186,22 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>9.81</v>
+        <v>502.15</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>65.51000000000001</v>
+        <v>53.71</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>36.67</v>
+        <v>61.53</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>28.24</v>
+        <v>61.95</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>CARTRADE</t>
+          <t>AJAXENGG</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -3610,22 +3210,22 @@
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>1954.9</v>
+        <v>526.45</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>65.48</v>
+        <v>53.68</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>46.84</v>
+        <v>49.22</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>53.61</v>
+        <v>43.33</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>SUPRIYA</t>
+          <t>SENCO</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -3634,22 +3234,22 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>706.7</v>
+        <v>334.7</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>65.23</v>
+        <v>53.25</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>57.23</v>
+        <v>52.51</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>56.61</v>
+        <v>48.55</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>EIEL</t>
+          <t>EASEMYTRIP</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -3658,22 +3258,22 @@
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>217.18</v>
+        <v>7.91</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>65.23</v>
+        <v>53.14</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>58.66</v>
+        <v>51.5</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>44.95</v>
+        <v>37.94</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>TANLA</t>
+          <t>LMW</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -3682,22 +3282,22 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>564.8</v>
+        <v>14561</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>65.01000000000001</v>
+        <v>53.1</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>60.87</v>
+        <v>50.4</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>47.12</v>
+        <v>49.76</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>EMUDHRA</t>
+          <t>NESCO</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -3706,22 +3306,22 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>519.45</v>
+        <v>1230.4</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>65</v>
+        <v>53.06</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>49.48</v>
+        <v>53.81</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>43.31</v>
+        <v>58.9</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>KPIGREEN</t>
+          <t>SHARDAMOTR</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -3730,22 +3330,22 @@
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>476.2</v>
+        <v>873.4</v>
       </c>
       <c r="D99" s="4" t="n">
-        <v>64.83</v>
+        <v>53</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>59.25</v>
+        <v>48.29</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>53.91</v>
+        <v>43.62</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>GALLANTT</t>
+          <t>EPIGRAL</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -3754,22 +3354,22 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>869.25</v>
+        <v>1216.4</v>
       </c>
       <c r="D100" s="4" t="n">
-        <v>64.81</v>
+        <v>52.82</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>73.54000000000001</v>
+        <v>51.24</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>70.51000000000001</v>
+        <v>44.98</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>ELECTCAST</t>
+          <t>RATNAMANI</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -3778,22 +3378,22 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>92.29000000000001</v>
+        <v>2693.4</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>64.8</v>
+        <v>52.8</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>61.44</v>
+        <v>59.39</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>47.79</v>
+        <v>51.69</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>VAIBHAVGBL</t>
+          <t>RALLIS</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -3802,22 +3402,22 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>235.08</v>
+        <v>263.7</v>
       </c>
       <c r="D102" s="4" t="n">
-        <v>64.78</v>
+        <v>52.77</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>54.86</v>
+        <v>49.54</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>46.7</v>
+        <v>48.73</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>TIPSMUSIC</t>
+          <t>CARTRADE</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -3826,22 +3426,22 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>648.35</v>
+        <v>1824.8</v>
       </c>
       <c r="D103" s="4" t="n">
-        <v>64.72</v>
+        <v>52.72</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>64.59</v>
+        <v>43.57</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>59.23</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>INDIASHLTR</t>
+          <t>HGINFRA</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -3850,22 +3450,22 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>836.3</v>
+        <v>604.2</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>64.61</v>
+        <v>52.47</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>58.72</v>
+        <v>43.54</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>57.13</v>
+        <v>37.87</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>PRICOLLTD</t>
+          <t>JINDWORLD</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -3874,22 +3474,22 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>622.25</v>
+        <v>26.53</v>
       </c>
       <c r="D105" s="4" t="n">
-        <v>64.55</v>
+        <v>52.39</v>
       </c>
       <c r="E105" s="4" t="n">
-        <v>58.02</v>
+        <v>46.39</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>61.34</v>
+        <v>36.44</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>WESTLIFE</t>
+          <t>CIGNITITEC</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -3898,22 +3498,22 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>505.2</v>
+        <v>1260.3</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>64.54000000000001</v>
+        <v>52.32</v>
       </c>
       <c r="E106" s="4" t="n">
-        <v>47.45</v>
+        <v>44.74</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>35.5</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>DHANUKA</t>
+          <t>GRINFRA</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -3922,22 +3522,22 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>1100</v>
+        <v>934.9</v>
       </c>
       <c r="D107" s="4" t="n">
-        <v>64.48</v>
+        <v>52.09</v>
       </c>
       <c r="E107" s="4" t="n">
-        <v>47.13</v>
+        <v>46.03</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>44.97</v>
+        <v>40.37</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>HGINFRA</t>
+          <t>SKYGOLD</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -3946,22 +3546,22 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>626.65</v>
+        <v>446.2</v>
       </c>
       <c r="D108" s="4" t="n">
-        <v>64.45</v>
+        <v>52.08</v>
       </c>
       <c r="E108" s="4" t="n">
-        <v>45.76</v>
+        <v>59.43</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>38.97</v>
+        <v>65.89</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>DBL</t>
+          <t>MANINFRA</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -3970,22 +3570,22 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>478.75</v>
+        <v>117.58</v>
       </c>
       <c r="D109" s="4" t="n">
-        <v>64.40000000000001</v>
+        <v>51.98</v>
       </c>
       <c r="E109" s="4" t="n">
-        <v>55.55</v>
+        <v>50.54</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>54.17</v>
+        <v>43.69</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>SHARDAMOTR</t>
+          <t>IMFA</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -3994,22 +3594,22 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>909.55</v>
+        <v>1476.5</v>
       </c>
       <c r="D110" s="4" t="n">
-        <v>64.27</v>
+        <v>51.78</v>
       </c>
       <c r="E110" s="4" t="n">
-        <v>51.88</v>
+        <v>59.48</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>44.84</v>
+        <v>68.58</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>ZYDUSWELL</t>
+          <t>WEBELSOLAR</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -4018,22 +3618,22 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>517.5</v>
+        <v>103.44</v>
       </c>
       <c r="D111" s="4" t="n">
-        <v>64.17</v>
+        <v>51.55</v>
       </c>
       <c r="E111" s="4" t="n">
-        <v>65.83</v>
+        <v>56.39</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>63.7</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>EPL</t>
+          <t>OPTIEMUS</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -4042,22 +3642,22 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>238.76</v>
+        <v>415.5</v>
       </c>
       <c r="D112" s="4" t="n">
-        <v>64.03</v>
+        <v>51.51</v>
       </c>
       <c r="E112" s="4" t="n">
-        <v>61.43</v>
+        <v>46.68</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>57.25</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>GREAVESCOT</t>
+          <t>BAJAJELEC</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -4066,22 +3666,22 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>171.36</v>
+        <v>393.1</v>
       </c>
       <c r="D113" s="4" t="n">
-        <v>63.91</v>
+        <v>51.5</v>
       </c>
       <c r="E113" s="4" t="n">
-        <v>51.96</v>
+        <v>41.5</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>48.6</v>
+        <v>31.07</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>UJJIVANSFB</t>
+          <t>INOXGREEN</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -4090,22 +3690,22 @@
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>62.4</v>
+        <v>177.64</v>
       </c>
       <c r="D114" s="4" t="n">
-        <v>63.9</v>
+        <v>51.46</v>
       </c>
       <c r="E114" s="4" t="n">
-        <v>61.35</v>
+        <v>50.68</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>62.08</v>
+        <v>52.79</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>SWSOLAR</t>
+          <t>PURVA</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -4114,22 +3714,22 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>217.26</v>
+        <v>213.11</v>
       </c>
       <c r="D115" s="4" t="n">
-        <v>63.82</v>
+        <v>51.22</v>
       </c>
       <c r="E115" s="4" t="n">
-        <v>53.9</v>
+        <v>46.86</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>40.65</v>
+        <v>44.79</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>ANUP</t>
+          <t>FDC</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -4138,22 +3738,22 @@
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>2161.9</v>
+        <v>366.15</v>
       </c>
       <c r="D116" s="4" t="n">
-        <v>63.76</v>
+        <v>51.21</v>
       </c>
       <c r="E116" s="4" t="n">
-        <v>56.12</v>
+        <v>46.11</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>51.2</v>
+        <v>44.26</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>POLYPLEX</t>
+          <t>QUESS</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -4162,22 +3762,22 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>950.1</v>
+        <v>202.97</v>
       </c>
       <c r="D117" s="4" t="n">
-        <v>63.69</v>
+        <v>50.72</v>
       </c>
       <c r="E117" s="4" t="n">
-        <v>58.35</v>
+        <v>47.72</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>46.36</v>
+        <v>32.91</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>REFEX</t>
+          <t>GSFC</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -4186,22 +3786,22 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>263</v>
+        <v>170</v>
       </c>
       <c r="D118" s="4" t="n">
-        <v>63.55</v>
+        <v>50.65</v>
       </c>
       <c r="E118" s="4" t="n">
-        <v>50.59</v>
+        <v>48.29</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>46.97</v>
+        <v>46.92</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>RTNINDIA</t>
+          <t>BANCOINDIA</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -4210,22 +3810,22 @@
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>37.79</v>
+        <v>608.35</v>
       </c>
       <c r="D119" s="4" t="n">
-        <v>63.54</v>
+        <v>50.53</v>
       </c>
       <c r="E119" s="4" t="n">
-        <v>52.11</v>
+        <v>49.47</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>43.52</v>
+        <v>56.67</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>VINATIORGA</t>
+          <t>BOSCH-HCIL</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -4234,22 +3834,22 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>1395.1</v>
+        <v>1385.7</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>63.47</v>
+        <v>50.28</v>
       </c>
       <c r="E120" s="4" t="n">
-        <v>43.57</v>
+        <v>50.94</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>39.64</v>
+        <v/>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>ASTRAMICRO</t>
+          <t>JKLAKSHMI</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -4258,22 +3858,22 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>1147.4</v>
+        <v>653.7</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>62.94</v>
+        <v>50.22</v>
       </c>
       <c r="E121" s="4" t="n">
-        <v>64.25</v>
+        <v>42.18</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>64.3</v>
+        <v>43.41</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>IONEXCHANG</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -4282,22 +3882,22 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>419.25</v>
+        <v>183.55</v>
       </c>
       <c r="D122" s="4" t="n">
-        <v>62.91</v>
+        <v>50.19</v>
       </c>
       <c r="E122" s="4" t="n">
-        <v>60.68</v>
+        <v>56.11</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>47.86</v>
+        <v>60.02</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>LUXIND</t>
+          <t>GANECOS</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -4306,22 +3906,22 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>1563.1</v>
+        <v>1016.9</v>
       </c>
       <c r="D123" s="4" t="n">
-        <v>62.89</v>
+        <v>50.15</v>
       </c>
       <c r="E123" s="4" t="n">
-        <v>64.87</v>
+        <v>53.12</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>54.68</v>
+        <v>45.64</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>GMMPFAUDLR</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -4330,22 +3930,22 @@
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>1300.2</v>
+        <v>896.5</v>
       </c>
       <c r="D124" s="4" t="n">
-        <v>62.88</v>
+        <v>50.12</v>
       </c>
       <c r="E124" s="4" t="n">
-        <v>73.23</v>
+        <v>39.36</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>69.04000000000001</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>INDIAGLYCO</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -4354,22 +3954,22 @@
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>197.76</v>
+        <v>1019.3</v>
       </c>
       <c r="D125" s="4" t="n">
-        <v>62.58</v>
+        <v>50.05</v>
       </c>
       <c r="E125" s="4" t="n">
-        <v>59.26</v>
+        <v>55.48</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>52.16</v>
+        <v>61</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>BIRLACORPN</t>
+          <t>DATAMATICS</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -4378,22 +3978,22 @@
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>995</v>
+        <v>741.8</v>
       </c>
       <c r="D126" s="4" t="n">
-        <v>62.54</v>
+        <v>50.04</v>
       </c>
       <c r="E126" s="4" t="n">
-        <v>49.05</v>
+        <v>48.75</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>43.56</v>
+        <v>52.81</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>BOSCH-HCIL</t>
+          <t>POLYPLEX</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -4402,22 +4002,22 @@
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>1447.7</v>
+        <v>899.15</v>
       </c>
       <c r="D127" s="4" t="n">
-        <v>62.39</v>
+        <v>49.7</v>
       </c>
       <c r="E127" s="4" t="n">
-        <v>56.63</v>
+        <v>51.2</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v/>
+        <v>44.34</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>STARCEMENT</t>
+          <t>JAIBALAJI</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -4426,22 +4026,22 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>236.45</v>
+        <v>76.58</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>62.36</v>
+        <v>49.63</v>
       </c>
       <c r="E128" s="4" t="n">
-        <v>59.29</v>
+        <v>51.51</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>56.76</v>
+        <v>42.98</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>EDELWEISS</t>
+          <t>PRINCEPIPE</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -4450,22 +4050,22 @@
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>125.14</v>
+        <v>251.8</v>
       </c>
       <c r="D129" s="4" t="n">
-        <v>62.36</v>
+        <v>49.56</v>
       </c>
       <c r="E129" s="4" t="n">
-        <v>60.97</v>
+        <v>46.09</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>60.77</v>
+        <v>37.44</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>SUDARSCHEM</t>
+          <t>FINEORG</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -4474,22 +4074,22 @@
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>947.35</v>
+        <v>4631.3</v>
       </c>
       <c r="D130" s="4" t="n">
-        <v>62.16</v>
+        <v>49.49</v>
       </c>
       <c r="E130" s="4" t="n">
-        <v>51.45</v>
+        <v>53.6</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>50.03</v>
+        <v>51.38</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>EMIL</t>
+          <t>SURYAROSNI</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -4498,22 +4098,22 @@
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>119.23</v>
+        <v>242.85</v>
       </c>
       <c r="D131" s="4" t="n">
-        <v>62.04</v>
+        <v>49.39</v>
       </c>
       <c r="E131" s="4" t="n">
-        <v>57.58</v>
+        <v>49.38</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>46.64</v>
+        <v>48</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>SUBROS</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -4522,22 +4122,22 @@
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>800.35</v>
+        <v>1172.6</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>61.9</v>
+        <v>49.35</v>
       </c>
       <c r="E132" s="4" t="n">
-        <v>51.03</v>
+        <v>62.82</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>53.66</v>
+        <v>62.55</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>VIYASH</t>
+          <t>TVSSCS</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -4546,22 +4146,22 @@
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>219.6</v>
+        <v>113.32</v>
       </c>
       <c r="D133" s="4" t="n">
-        <v>61.82</v>
+        <v>49.29</v>
       </c>
       <c r="E133" s="4" t="n">
-        <v>65.23</v>
+        <v>50</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v/>
+        <v>41</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>BELRISE</t>
+          <t>GARFIBRES</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -4570,22 +4170,22 @@
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>222.39</v>
+        <v>628.45</v>
       </c>
       <c r="D134" s="4" t="n">
-        <v>61.8</v>
+        <v>49.25</v>
       </c>
       <c r="E134" s="4" t="n">
-        <v>71.76000000000001</v>
+        <v>44.18</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v/>
+        <v>40.56</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>PARKHOTELS</t>
+          <t>BELRISE</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -4594,22 +4194,22 @@
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>129.73</v>
+        <v>209.46</v>
       </c>
       <c r="D135" s="4" t="n">
-        <v>61.8</v>
+        <v>49.1</v>
       </c>
       <c r="E135" s="4" t="n">
-        <v>52.9</v>
+        <v>62.65</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>42.4</v>
+        <v/>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>GATEWAY</t>
+          <t>GOKEX</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -4618,22 +4218,22 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>59.96</v>
+        <v>687.7</v>
       </c>
       <c r="D136" s="4" t="n">
-        <v>61.58</v>
+        <v>49</v>
       </c>
       <c r="E136" s="4" t="n">
-        <v>54.81</v>
+        <v>47.79</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>44.68</v>
+        <v>47.48</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>VARROC</t>
+          <t>RELIGARE</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -4642,22 +4242,22 @@
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>559.85</v>
+        <v>221.93</v>
       </c>
       <c r="D137" s="4" t="n">
-        <v>61.55</v>
+        <v>48.6</v>
       </c>
       <c r="E137" s="4" t="n">
-        <v>52.4</v>
+        <v>44.54</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>52.83</v>
+        <v>48.65</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>HCG</t>
+          <t>VINATIORGA</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -4666,22 +4266,22 @@
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>603.8</v>
+        <v>1322.8</v>
       </c>
       <c r="D138" s="4" t="n">
-        <v>61.48</v>
+        <v>48.34</v>
       </c>
       <c r="E138" s="4" t="n">
-        <v>51.69</v>
+        <v>37.89</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>57.37</v>
+        <v>35.97</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>PRUDENT</t>
+          <t>AARTIPHARM</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -4690,22 +4290,22 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>2829.1</v>
+        <v>711.75</v>
       </c>
       <c r="D139" s="4" t="n">
-        <v>61.45</v>
+        <v>48.19</v>
       </c>
       <c r="E139" s="4" t="n">
-        <v>61.7</v>
+        <v>48.27</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>59.72</v>
+        <v>52.06</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>KRBL</t>
+          <t>LUXIND</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -4714,22 +4314,22 @@
         </is>
       </c>
       <c r="C140" s="4" t="n">
-        <v>373.15</v>
+        <v>1367.1</v>
       </c>
       <c r="D140" s="4" t="n">
-        <v>61.35</v>
+        <v>47.93</v>
       </c>
       <c r="E140" s="4" t="n">
-        <v>55.54</v>
+        <v>56.13</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>54.11</v>
+        <v>49.97</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>UNIMECH</t>
+          <t>IONEXCHANG</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -4738,22 +4338,22 @@
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>1043.9</v>
+        <v>390.15</v>
       </c>
       <c r="D141" s="4" t="n">
-        <v>61.33</v>
+        <v>47.8</v>
       </c>
       <c r="E141" s="4" t="n">
-        <v>60.35</v>
+        <v>51.67</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>48.84</v>
+        <v>44.93</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>JINDWORLD</t>
+          <t>MOIL</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -4762,22 +4362,22 @@
         </is>
       </c>
       <c r="C142" s="4" t="n">
-        <v>26.83</v>
+        <v>306.95</v>
       </c>
       <c r="D142" s="4" t="n">
-        <v>61.3</v>
+        <v>47.76</v>
       </c>
       <c r="E142" s="4" t="n">
-        <v>47.04</v>
+        <v>47.38</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>36.7</v>
+        <v>48.52</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>DCAL</t>
+          <t>ANUP</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -4786,22 +4386,22 @@
         </is>
       </c>
       <c r="C143" s="4" t="n">
-        <v>187.25</v>
+        <v>1966.5</v>
       </c>
       <c r="D143" s="4" t="n">
-        <v>61.18</v>
+        <v>47.49</v>
       </c>
       <c r="E143" s="4" t="n">
-        <v>45.92</v>
+        <v>48.69</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>46.88</v>
+        <v>47.88</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>WELENT</t>
+          <t>SUDARSCHEM</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -4810,22 +4410,22 @@
         </is>
       </c>
       <c r="C144" s="4" t="n">
-        <v>522.2</v>
+        <v>868.6</v>
       </c>
       <c r="D144" s="4" t="n">
-        <v>61</v>
+        <v>47.47</v>
       </c>
       <c r="E144" s="4" t="n">
-        <v>57.61</v>
+        <v>43.3</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>55.82</v>
+        <v>46.89</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>BANCOINDIA</t>
+          <t>RTNINDIA</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -4834,22 +4434,22 @@
         </is>
       </c>
       <c r="C145" s="4" t="n">
-        <v>636.25</v>
+        <v>33.9</v>
       </c>
       <c r="D145" s="4" t="n">
-        <v>60.92</v>
+        <v>47.46</v>
       </c>
       <c r="E145" s="4" t="n">
-        <v>52.98</v>
+        <v>45.04</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>58.12</v>
+        <v>41.21</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>ROUTE</t>
+          <t>ENTERO</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -4858,22 +4458,22 @@
         </is>
       </c>
       <c r="C146" s="4" t="n">
-        <v>552.5</v>
+        <v>1192.3</v>
       </c>
       <c r="D146" s="4" t="n">
-        <v>60.86</v>
+        <v>47.42</v>
       </c>
       <c r="E146" s="4" t="n">
-        <v>44.11</v>
+        <v>52.73</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>31.2</v>
+        <v>52.17</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>JAMNAAUTO</t>
+          <t>UNIMECH</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -4882,22 +4482,22 @@
         </is>
       </c>
       <c r="C147" s="4" t="n">
-        <v>131.65</v>
+        <v>941.2</v>
       </c>
       <c r="D147" s="4" t="n">
-        <v>60.81</v>
+        <v>47.31</v>
       </c>
       <c r="E147" s="4" t="n">
-        <v>57.43</v>
+        <v>50.7</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>58.02</v>
+        <v>43.93</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>GSFC</t>
+          <t>SANSERA</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -4906,22 +4506,22 @@
         </is>
       </c>
       <c r="C148" s="4" t="n">
-        <v>175.95</v>
+        <v>2385</v>
       </c>
       <c r="D148" s="4" t="n">
-        <v>60.8</v>
+        <v>47.3</v>
       </c>
       <c r="E148" s="4" t="n">
-        <v>52.46</v>
+        <v>62.86</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>48.54</v>
+        <v>68.81</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>BAJAJELEC</t>
+          <t>SWSOLAR</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -4930,22 +4530,22 @@
         </is>
       </c>
       <c r="C149" s="4" t="n">
-        <v>405.95</v>
+        <v>199.78</v>
       </c>
       <c r="D149" s="4" t="n">
-        <v>60.78</v>
+        <v>47.2</v>
       </c>
       <c r="E149" s="4" t="n">
-        <v>44.58</v>
+        <v>47.66</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>32.27</v>
+        <v>38.85</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>SHRIPISTON</t>
+          <t>TANLA</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -4954,22 +4554,22 @@
         </is>
       </c>
       <c r="C150" s="4" t="n">
-        <v>3604.4</v>
+        <v>497.5</v>
       </c>
       <c r="D150" s="4" t="n">
-        <v>60.7</v>
+        <v>47.15</v>
       </c>
       <c r="E150" s="4" t="n">
-        <v>62.71</v>
+        <v>49.55</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>73.02</v>
+        <v>42.97</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>LMW</t>
+          <t>BORORENEW</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -4978,22 +4578,22 @@
         </is>
       </c>
       <c r="C151" s="4" t="n">
-        <v>14972</v>
+        <v>500.2</v>
       </c>
       <c r="D151" s="4" t="n">
-        <v>60.59</v>
+        <v>47.13</v>
       </c>
       <c r="E151" s="4" t="n">
-        <v>53.89</v>
+        <v>49.58</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>51.17</v>
+        <v>49.33</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>AGI</t>
+          <t>AARTIDRUGS</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -5002,22 +4602,22 @@
         </is>
       </c>
       <c r="C152" s="4" t="n">
-        <v>629.2</v>
+        <v>367.75</v>
       </c>
       <c r="D152" s="4" t="n">
-        <v>60.5</v>
+        <v>47.07</v>
       </c>
       <c r="E152" s="4" t="n">
-        <v>49.52</v>
+        <v>44.6</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>45.93</v>
+        <v>43.44</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>ALIVUS</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -5026,22 +4626,22 @@
         </is>
       </c>
       <c r="C153" s="4" t="n">
-        <v>766.2</v>
+        <v>1044.6</v>
       </c>
       <c r="D153" s="4" t="n">
-        <v>60.45</v>
+        <v>47.06</v>
       </c>
       <c r="E153" s="4" t="n">
-        <v>55.27</v>
+        <v>58.89</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>55.38</v>
+        <v>63.13</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>GREENPANEL</t>
+          <t>SOUTHBANK</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -5050,22 +4650,22 @@
         </is>
       </c>
       <c r="C154" s="4" t="n">
-        <v>225.44</v>
+        <v>38.83</v>
       </c>
       <c r="D154" s="4" t="n">
-        <v>60.36</v>
+        <v>47.04</v>
       </c>
       <c r="E154" s="4" t="n">
-        <v>50.42</v>
+        <v>52.06</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>42.7</v>
+        <v>62.78</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>SKIPPER</t>
+          <t>WESTLIFE</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -5074,22 +4674,22 @@
         </is>
       </c>
       <c r="C155" s="4" t="n">
-        <v>466.2</v>
+        <v>473.2</v>
       </c>
       <c r="D155" s="4" t="n">
-        <v>59.87</v>
+        <v>47.03</v>
       </c>
       <c r="E155" s="4" t="n">
-        <v>59.47</v>
+        <v>41.32</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>55.85</v>
+        <v>31.28</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>NFL</t>
+          <t>SHRIPISTON</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -5098,22 +4698,22 @@
         </is>
       </c>
       <c r="C156" s="4" t="n">
-        <v>78.63</v>
+        <v>3385.6</v>
       </c>
       <c r="D156" s="4" t="n">
-        <v>59.83</v>
+        <v>47.03</v>
       </c>
       <c r="E156" s="4" t="n">
-        <v>47.78</v>
+        <v>56.67</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>45.98</v>
+        <v>69.11</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>GANECOS</t>
+          <t>AGI</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -5122,22 +4722,22 @@
         </is>
       </c>
       <c r="C157" s="4" t="n">
-        <v>1063.6</v>
+        <v>579.5</v>
       </c>
       <c r="D157" s="4" t="n">
-        <v>59.62</v>
+        <v>46.99</v>
       </c>
       <c r="E157" s="4" t="n">
-        <v>56.36</v>
+        <v>43.45</v>
       </c>
       <c r="F157" s="4" t="n">
-        <v>46.86</v>
+        <v>43.89</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>JKPAPER</t>
+          <t>OSWALPUMPS</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -5146,22 +4746,22 @@
         </is>
       </c>
       <c r="C158" s="4" t="n">
-        <v>379</v>
+        <v>385.05</v>
       </c>
       <c r="D158" s="4" t="n">
-        <v>59.57</v>
+        <v>46.93</v>
       </c>
       <c r="E158" s="4" t="n">
-        <v>57.74</v>
+        <v>41.82</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v>52.31</v>
+        <v/>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>TSFINV</t>
+          <t>VIPIND</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -5170,22 +4770,22 @@
         </is>
       </c>
       <c r="C159" s="4" t="n">
-        <v>421</v>
+        <v>302.55</v>
       </c>
       <c r="D159" s="4" t="n">
-        <v>59.47</v>
+        <v>46.78</v>
       </c>
       <c r="E159" s="4" t="n">
-        <v>44.34</v>
+        <v>35.63</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v/>
+        <v>35.69</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>SANOFICONR</t>
+          <t>LUMAXTECH</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -5194,22 +4794,22 @@
         </is>
       </c>
       <c r="C160" s="4" t="n">
-        <v>4767.7</v>
+        <v>1636.1</v>
       </c>
       <c r="D160" s="4" t="n">
-        <v>59.44</v>
+        <v>46.75</v>
       </c>
       <c r="E160" s="4" t="n">
-        <v>56.29</v>
+        <v>53.96</v>
       </c>
       <c r="F160" s="4" t="n">
-        <v>50.06</v>
+        <v>68.56</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>ELECTCAST</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -5218,22 +4818,22 @@
         </is>
       </c>
       <c r="C161" s="4" t="n">
-        <v>456.15</v>
+        <v>81.95999999999999</v>
       </c>
       <c r="D161" s="4" t="n">
-        <v>59.44</v>
+        <v>46.74</v>
       </c>
       <c r="E161" s="4" t="n">
-        <v>52.61</v>
+        <v>50.96</v>
       </c>
       <c r="F161" s="4" t="n">
-        <v>53.76</v>
+        <v>44.06</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>SANSERA</t>
+          <t>SYMPHONY</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -5242,22 +4842,22 @@
         </is>
       </c>
       <c r="C162" s="4" t="n">
-        <v>2519.8</v>
+        <v>784.1</v>
       </c>
       <c r="D162" s="4" t="n">
-        <v>59.41</v>
+        <v>46.62</v>
       </c>
       <c r="E162" s="4" t="n">
-        <v>70.02</v>
+        <v>43.73</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>72.95999999999999</v>
+        <v>41.32</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>JISLJALEQS</t>
+          <t>FIEMIND</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -5266,22 +4866,22 @@
         </is>
       </c>
       <c r="C163" s="4" t="n">
-        <v>35.06</v>
+        <v>2168.2</v>
       </c>
       <c r="D163" s="4" t="n">
-        <v>59.37</v>
+        <v>46.62</v>
       </c>
       <c r="E163" s="4" t="n">
-        <v>44.33</v>
+        <v>51.55</v>
       </c>
       <c r="F163" s="4" t="n">
-        <v>39.42</v>
+        <v>64.75</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>GOKEX</t>
+          <t>IFBIND</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -5290,22 +4890,22 @@
         </is>
       </c>
       <c r="C164" s="4" t="n">
-        <v>732.45</v>
+        <v>1113.1</v>
       </c>
       <c r="D164" s="4" t="n">
-        <v>59.29</v>
+        <v>46.42</v>
       </c>
       <c r="E164" s="4" t="n">
-        <v>51.64</v>
+        <v>41.07</v>
       </c>
       <c r="F164" s="4" t="n">
-        <v>49.21</v>
+        <v>45.39</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>RTNPOWER</t>
+          <t>KSCL</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -5314,22 +4914,22 @@
         </is>
       </c>
       <c r="C165" s="4" t="n">
-        <v>10.02</v>
+        <v>918.35</v>
       </c>
       <c r="D165" s="4" t="n">
-        <v>59.28</v>
+        <v>46.32</v>
       </c>
       <c r="E165" s="4" t="n">
-        <v>55.62</v>
+        <v>49.34</v>
       </c>
       <c r="F165" s="4" t="n">
-        <v>49.2</v>
+        <v>49.29</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>WABAG</t>
+          <t>SHAREINDIA</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -5338,22 +4938,22 @@
         </is>
       </c>
       <c r="C166" s="4" t="n">
-        <v>1478</v>
+        <v>138.49</v>
       </c>
       <c r="D166" s="4" t="n">
-        <v>59.21</v>
+        <v>46.21</v>
       </c>
       <c r="E166" s="4" t="n">
-        <v>61.74</v>
+        <v>45.46</v>
       </c>
       <c r="F166" s="4" t="n">
-        <v>56.95</v>
+        <v>40.22</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>MAXESTATES</t>
+          <t>IXIGO</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -5362,22 +4962,22 @@
         </is>
       </c>
       <c r="C167" s="4" t="n">
-        <v>408.05</v>
+        <v>165.62</v>
       </c>
       <c r="D167" s="4" t="n">
-        <v>59.2</v>
+        <v>46.16</v>
       </c>
       <c r="E167" s="4" t="n">
-        <v>50.58</v>
+        <v>38.09</v>
       </c>
       <c r="F167" s="4" t="n">
-        <v>48.59</v>
+        <v>42.34</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>RALLIS</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -5386,22 +4986,22 @@
         </is>
       </c>
       <c r="C168" s="4" t="n">
-        <v>267.95</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="D168" s="4" t="n">
-        <v>59.11</v>
+        <v>46.12</v>
       </c>
       <c r="E168" s="4" t="n">
-        <v>51.05</v>
+        <v>36.78</v>
       </c>
       <c r="F168" s="4" t="n">
-        <v>49.34</v>
+        <v>37.25</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>HERITGFOOD</t>
+          <t>CIEINDIA</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -5410,22 +5010,22 @@
         </is>
       </c>
       <c r="C169" s="4" t="n">
-        <v>362.6</v>
+        <v>460.75</v>
       </c>
       <c r="D169" s="4" t="n">
-        <v>59.07</v>
+        <v>46.11</v>
       </c>
       <c r="E169" s="4" t="n">
-        <v>45.14</v>
+        <v>54.82</v>
       </c>
       <c r="F169" s="4" t="n">
-        <v>46.71</v>
+        <v>54.78</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>IMFA</t>
+          <t>TSFINV</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -5434,22 +5034,22 @@
         </is>
       </c>
       <c r="C170" s="4" t="n">
-        <v>1548.1</v>
+        <v>391.7</v>
       </c>
       <c r="D170" s="4" t="n">
-        <v>59.03</v>
+        <v>46</v>
       </c>
       <c r="E170" s="4" t="n">
-        <v>64.31999999999999</v>
+        <v>38.38</v>
       </c>
       <c r="F170" s="4" t="n">
-        <v>70.69</v>
+        <v/>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>EUREKAFORB</t>
+          <t>MAHLIFE</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -5458,22 +5058,22 @@
         </is>
       </c>
       <c r="C171" s="4" t="n">
-        <v>513.4</v>
+        <v>326.45</v>
       </c>
       <c r="D171" s="4" t="n">
-        <v>58.89</v>
+        <v>45.94</v>
       </c>
       <c r="E171" s="4" t="n">
-        <v>48.82</v>
+        <v>41.89</v>
       </c>
       <c r="F171" s="4" t="n">
-        <v>46.12</v>
+        <v>41.51</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>FIEMIND</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -5482,22 +5082,22 @@
         </is>
       </c>
       <c r="C172" s="4" t="n">
-        <v>2267</v>
+        <v>246.1</v>
       </c>
       <c r="D172" s="4" t="n">
-        <v>58.84</v>
+        <v>45.81</v>
       </c>
       <c r="E172" s="4" t="n">
-        <v>57.62</v>
+        <v>62.82</v>
       </c>
       <c r="F172" s="4" t="n">
-        <v>67.11</v>
+        <v>61.29</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>PATELENG</t>
+          <t>SUBROS</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -5506,22 +5106,22 @@
         </is>
       </c>
       <c r="C173" s="4" t="n">
-        <v>28.82</v>
+        <v>748.1</v>
       </c>
       <c r="D173" s="4" t="n">
-        <v>58.76</v>
+        <v>45.68</v>
       </c>
       <c r="E173" s="4" t="n">
-        <v>48</v>
+        <v>45.87</v>
       </c>
       <c r="F173" s="4" t="n">
-        <v>39.38</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>KNRCON</t>
+          <t>DYNAMATECH</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -5530,22 +5130,22 @@
         </is>
       </c>
       <c r="C174" s="4" t="n">
-        <v>131.94</v>
+        <v>10736</v>
       </c>
       <c r="D174" s="4" t="n">
-        <v>58.76</v>
+        <v>45.61</v>
       </c>
       <c r="E174" s="4" t="n">
-        <v>44.21</v>
+        <v>55.74</v>
       </c>
       <c r="F174" s="4" t="n">
-        <v>35.24</v>
+        <v>65.27</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>SHAREINDIA</t>
+          <t>VAIBHAVGBL</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -5554,22 +5154,22 @@
         </is>
       </c>
       <c r="C175" s="4" t="n">
-        <v>147.5</v>
+        <v>213.49</v>
       </c>
       <c r="D175" s="4" t="n">
-        <v>58.62</v>
+        <v>45.6</v>
       </c>
       <c r="E175" s="4" t="n">
-        <v>50.15</v>
+        <v>47.2</v>
       </c>
       <c r="F175" s="4" t="n">
-        <v>42.1</v>
+        <v>43.36</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>MSTCLTD</t>
+          <t>PRSMJOHNSN</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -5578,22 +5178,22 @@
         </is>
       </c>
       <c r="C176" s="4" t="n">
-        <v>455.9</v>
+        <v>127.34</v>
       </c>
       <c r="D176" s="4" t="n">
-        <v>58.49</v>
+        <v>45.54</v>
       </c>
       <c r="E176" s="4" t="n">
-        <v>50.15</v>
+        <v>45.26</v>
       </c>
       <c r="F176" s="4" t="n">
-        <v>47.23</v>
+        <v>44.31</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>RAYMONDLSL</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -5602,22 +5202,22 @@
         </is>
       </c>
       <c r="C177" s="4" t="n">
-        <v>1213.4</v>
+        <v>779.6</v>
       </c>
       <c r="D177" s="4" t="n">
-        <v>58.39</v>
+        <v>45.47</v>
       </c>
       <c r="E177" s="4" t="n">
-        <v>68.01000000000001</v>
+        <v>37.25</v>
       </c>
       <c r="F177" s="4" t="n">
-        <v>71.38</v>
+        <v>22.63</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>AVANTIFEED</t>
+          <t>EMUDHRA</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -5626,22 +5226,22 @@
         </is>
       </c>
       <c r="C178" s="4" t="n">
-        <v>1435.2</v>
+        <v>470.55</v>
       </c>
       <c r="D178" s="4" t="n">
-        <v>58.35</v>
+        <v>45.42</v>
       </c>
       <c r="E178" s="4" t="n">
-        <v>68.09999999999999</v>
+        <v>41.71</v>
       </c>
       <c r="F178" s="4" t="n">
-        <v>76.23999999999999</v>
+        <v>39.84</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>AARTIDRUGS</t>
+          <t>ASHOKA</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -5650,22 +5250,22 @@
         </is>
       </c>
       <c r="C179" s="4" t="n">
-        <v>387.9</v>
+        <v>128.09</v>
       </c>
       <c r="D179" s="4" t="n">
-        <v>58.29</v>
+        <v>45.41</v>
       </c>
       <c r="E179" s="4" t="n">
-        <v>50.33</v>
+        <v>40.21</v>
       </c>
       <c r="F179" s="4" t="n">
-        <v>45.61</v>
+        <v>42.78</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>PGIL</t>
+          <t>ARVINDFASN</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -5674,22 +5274,22 @@
         </is>
       </c>
       <c r="C180" s="4" t="n">
-        <v>1604.7</v>
+        <v>433.4</v>
       </c>
       <c r="D180" s="4" t="n">
-        <v>58.17</v>
+        <v>45.37</v>
       </c>
       <c r="E180" s="4" t="n">
-        <v>54.05</v>
+        <v>45.39</v>
       </c>
       <c r="F180" s="4" t="n">
-        <v>61.95</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>IFBIND</t>
+          <t>AVANTIFEED</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -5698,22 +5298,22 @@
         </is>
       </c>
       <c r="C181" s="4" t="n">
-        <v>1188.6</v>
+        <v>1323.2</v>
       </c>
       <c r="D181" s="4" t="n">
-        <v>58.16</v>
+        <v>45.34</v>
       </c>
       <c r="E181" s="4" t="n">
-        <v>45.62</v>
+        <v>60.18</v>
       </c>
       <c r="F181" s="4" t="n">
-        <v>46.93</v>
+        <v>71.66</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>JSFB</t>
+          <t>GATEWAY</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -5722,22 +5322,22 @@
         </is>
       </c>
       <c r="C182" s="4" t="n">
-        <v>455.05</v>
+        <v>56.58</v>
       </c>
       <c r="D182" s="4" t="n">
-        <v>57.69</v>
+        <v>45.32</v>
       </c>
       <c r="E182" s="4" t="n">
-        <v>61.77</v>
+        <v>47.8</v>
       </c>
       <c r="F182" s="4" t="n">
-        <v>50.98</v>
+        <v>41.28</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>EASEMYTRIP</t>
+          <t>PARAS</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -5746,22 +5346,22 @@
         </is>
       </c>
       <c r="C183" s="4" t="n">
-        <v>7.96</v>
+        <v>753.4</v>
       </c>
       <c r="D183" s="4" t="n">
-        <v>57.67</v>
+        <v>45.13</v>
       </c>
       <c r="E183" s="4" t="n">
-        <v>51.95</v>
+        <v>53.67</v>
       </c>
       <c r="F183" s="4" t="n">
-        <v>38.12</v>
+        <v>50.6</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>ROUTE</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -5770,22 +5370,22 @@
         </is>
       </c>
       <c r="C184" s="4" t="n">
-        <v>259.35</v>
+        <v>503.55</v>
       </c>
       <c r="D184" s="4" t="n">
-        <v>57.57</v>
+        <v>45.08</v>
       </c>
       <c r="E184" s="4" t="n">
-        <v>71.33</v>
+        <v>37.87</v>
       </c>
       <c r="F184" s="4" t="n">
-        <v>65.02</v>
+        <v>28.86</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>ASHOKA</t>
+          <t>WABAG</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -5794,22 +5394,22 @@
         </is>
       </c>
       <c r="C185" s="4" t="n">
-        <v>137.21</v>
+        <v>1386.1</v>
       </c>
       <c r="D185" s="4" t="n">
-        <v>57.5</v>
+        <v>45.01</v>
       </c>
       <c r="E185" s="4" t="n">
-        <v>44.57</v>
+        <v>53.53</v>
       </c>
       <c r="F185" s="4" t="n">
-        <v>44.26</v>
+        <v>54.13</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>SOUTHBANK</t>
+          <t>TARC</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -5818,22 +5418,22 @@
         </is>
       </c>
       <c r="C186" s="4" t="n">
-        <v>40.91</v>
+        <v>130.35</v>
       </c>
       <c r="D186" s="4" t="n">
-        <v>57.2</v>
+        <v>44.9</v>
       </c>
       <c r="E186" s="4" t="n">
-        <v>58.22</v>
+        <v>42.79</v>
       </c>
       <c r="F186" s="4" t="n">
-        <v>65.48</v>
+        <v>46.35</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>OSWALPUMPS</t>
+          <t>TIMETECHNO</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -5842,22 +5442,22 @@
         </is>
       </c>
       <c r="C187" s="4" t="n">
-        <v>410.6</v>
+        <v>178.12</v>
       </c>
       <c r="D187" s="4" t="n">
-        <v>57.15</v>
+        <v>44.79</v>
       </c>
       <c r="E187" s="4" t="n">
-        <v>45.14</v>
+        <v>45.75</v>
       </c>
       <c r="F187" s="4" t="n">
-        <v/>
+        <v>50.86</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>ZAGGLE</t>
+          <t>RTNPOWER</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -5866,22 +5466,22 @@
         </is>
       </c>
       <c r="C188" s="4" t="n">
-        <v>259.11</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="D188" s="4" t="n">
-        <v>57.11</v>
+        <v>44.42</v>
       </c>
       <c r="E188" s="4" t="n">
-        <v>44.35</v>
+        <v>48.33</v>
       </c>
       <c r="F188" s="4" t="n">
-        <v>44.31</v>
+        <v>47.08</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>AURIONPRO</t>
+          <t>SAFARI</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -5890,22 +5490,22 @@
         </is>
       </c>
       <c r="C189" s="4" t="n">
-        <v>896.05</v>
+        <v>1458.1</v>
       </c>
       <c r="D189" s="4" t="n">
-        <v>56.67</v>
+        <v>44.41</v>
       </c>
       <c r="E189" s="4" t="n">
-        <v>44</v>
+        <v>34.98</v>
       </c>
       <c r="F189" s="4" t="n">
-        <v>43.45</v>
+        <v>39.03</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>RELAXO</t>
+          <t>EDELWEISS</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -5914,22 +5514,22 @@
         </is>
       </c>
       <c r="C190" s="4" t="n">
-        <v>308.85</v>
+        <v>113.39</v>
       </c>
       <c r="D190" s="4" t="n">
-        <v>56.61</v>
+        <v>44.37</v>
       </c>
       <c r="E190" s="4" t="n">
-        <v>39.54</v>
+        <v>51.14</v>
       </c>
       <c r="F190" s="4" t="n">
-        <v>28.88</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>BECTORFOOD</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -5938,22 +5538,22 @@
         </is>
       </c>
       <c r="C191" s="4" t="n">
-        <v>202.39</v>
+        <v>193.3</v>
       </c>
       <c r="D191" s="4" t="n">
-        <v>56.58</v>
+        <v>44.3</v>
       </c>
       <c r="E191" s="4" t="n">
-        <v>41.34</v>
+        <v>50.26</v>
       </c>
       <c r="F191" s="4" t="n">
-        <v>42.4</v>
+        <v>40.48</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>GULFOILLUB</t>
+          <t>KRBL</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -5962,22 +5562,22 @@
         </is>
       </c>
       <c r="C192" s="4" t="n">
-        <v>1000.8</v>
+        <v>338.85</v>
       </c>
       <c r="D192" s="4" t="n">
-        <v>56.38</v>
+        <v>44.2</v>
       </c>
       <c r="E192" s="4" t="n">
-        <v>44.48</v>
+        <v>46.93</v>
       </c>
       <c r="F192" s="4" t="n">
-        <v>49.3</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>DODLA</t>
+          <t>NFL</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -5986,22 +5586,22 @@
         </is>
       </c>
       <c r="C193" s="4" t="n">
-        <v>1127.3</v>
+        <v>74.39</v>
       </c>
       <c r="D193" s="4" t="n">
-        <v>56.35</v>
+        <v>44.08</v>
       </c>
       <c r="E193" s="4" t="n">
-        <v>47.7</v>
+        <v>41.71</v>
       </c>
       <c r="F193" s="4" t="n">
-        <v>50.85</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>JKLAKSHMI</t>
+          <t>GULFOILLUB</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -6010,22 +5610,22 @@
         </is>
       </c>
       <c r="C194" s="4" t="n">
-        <v>664.4</v>
+        <v>942.25</v>
       </c>
       <c r="D194" s="4" t="n">
-        <v>56.15</v>
+        <v>43.97</v>
       </c>
       <c r="E194" s="4" t="n">
-        <v>43.59</v>
+        <v>38.46</v>
       </c>
       <c r="F194" s="4" t="n">
-        <v>44.14</v>
+        <v>46.38</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>LUMAXTECH</t>
+          <t>PARKHOTELS</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -6034,22 +5634,22 @@
         </is>
       </c>
       <c r="C195" s="4" t="n">
-        <v>1736.1</v>
+        <v>119.09</v>
       </c>
       <c r="D195" s="4" t="n">
-        <v>56.13</v>
+        <v>43.85</v>
       </c>
       <c r="E195" s="4" t="n">
-        <v>58.37</v>
+        <v>44.64</v>
       </c>
       <c r="F195" s="4" t="n">
-        <v>70.3</v>
+        <v>38.12</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>PURVA</t>
+          <t>VOLTAMP</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -6058,22 +5658,22 @@
         </is>
       </c>
       <c r="C196" s="4" t="n">
-        <v>218.73</v>
+        <v>9501</v>
       </c>
       <c r="D196" s="4" t="n">
-        <v>56.08</v>
+        <v>43.82</v>
       </c>
       <c r="E196" s="4" t="n">
-        <v>48.63</v>
+        <v>54.85</v>
       </c>
       <c r="F196" s="4" t="n">
-        <v>45.63</v>
+        <v>54.3</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>MSTCLTD</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -6082,22 +5682,22 @@
         </is>
       </c>
       <c r="C197" s="4" t="n">
-        <v>268.6</v>
+        <v>422.25</v>
       </c>
       <c r="D197" s="4" t="n">
-        <v>55.88</v>
+        <v>43.55</v>
       </c>
       <c r="E197" s="4" t="n">
-        <v>52.38</v>
+        <v>44.33</v>
       </c>
       <c r="F197" s="4" t="n">
-        <v>53.4</v>
+        <v>44.85</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>SHARDACROP</t>
+          <t>JKIL</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -6106,22 +5706,22 @@
         </is>
       </c>
       <c r="C198" s="4" t="n">
-        <v>1122.4</v>
+        <v>493.8</v>
       </c>
       <c r="D198" s="4" t="n">
-        <v>55.8</v>
+        <v>43.44</v>
       </c>
       <c r="E198" s="4" t="n">
-        <v>59.05</v>
+        <v>40.33</v>
       </c>
       <c r="F198" s="4" t="n">
-        <v>61.51</v>
+        <v>41.84</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>WAAREERTL</t>
+          <t>SUNTECK</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -6130,22 +5730,22 @@
         </is>
       </c>
       <c r="C199" s="4" t="n">
-        <v>1028.3</v>
+        <v>318</v>
       </c>
       <c r="D199" s="4" t="n">
-        <v>55.73</v>
+        <v>43.35</v>
       </c>
       <c r="E199" s="4" t="n">
-        <v>55.89</v>
+        <v>39.38</v>
       </c>
       <c r="F199" s="4" t="n">
-        <v/>
+        <v>41.05</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>KITEX</t>
+          <t>PARADEEP</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -6154,22 +5754,22 @@
         </is>
       </c>
       <c r="C200" s="4" t="n">
-        <v>171.08</v>
+        <v>120.46</v>
       </c>
       <c r="D200" s="4" t="n">
-        <v>55.23</v>
+        <v>43.28</v>
       </c>
       <c r="E200" s="4" t="n">
-        <v>46.87</v>
+        <v>42.1</v>
       </c>
       <c r="F200" s="4" t="n">
-        <v>50.66</v>
+        <v>48.64</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>PCJEWELLER</t>
+          <t>CSBBANK</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -6178,22 +5778,22 @@
         </is>
       </c>
       <c r="C201" s="4" t="n">
-        <v>9.5</v>
+        <v>358.65</v>
       </c>
       <c r="D201" s="4" t="n">
-        <v>55.18</v>
+        <v>43.18</v>
       </c>
       <c r="E201" s="4" t="n">
-        <v>45.73</v>
+        <v>42.81</v>
       </c>
       <c r="F201" s="4" t="n">
-        <v>48.24</v>
+        <v>49.59</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>IMAGICAA</t>
+          <t>JISLJALEQS</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -6202,22 +5802,22 @@
         </is>
       </c>
       <c r="C202" s="4" t="n">
-        <v>46.85</v>
+        <v>31.12</v>
       </c>
       <c r="D202" s="4" t="n">
-        <v>54.99</v>
+        <v>43.1</v>
       </c>
       <c r="E202" s="4" t="n">
-        <v>48.5</v>
+        <v>37.39</v>
       </c>
       <c r="F202" s="4" t="n">
-        <v>43.38</v>
+        <v>36.12</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>PRSMJOHNSN</t>
+          <t>BALUFORGE</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -6226,22 +5826,22 @@
         </is>
       </c>
       <c r="C203" s="4" t="n">
-        <v>131.85</v>
+        <v>478.15</v>
       </c>
       <c r="D203" s="4" t="n">
-        <v>54.86</v>
+        <v>43</v>
       </c>
       <c r="E203" s="4" t="n">
-        <v>50.2</v>
+        <v>46.17</v>
       </c>
       <c r="F203" s="4" t="n">
-        <v>45.81</v>
+        <v>47.53</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>GHCL</t>
+          <t>VESUVIUS</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -6250,22 +5850,22 @@
         </is>
       </c>
       <c r="C204" s="4" t="n">
-        <v>510.9</v>
+        <v>477.85</v>
       </c>
       <c r="D204" s="4" t="n">
-        <v>54.82</v>
+        <v>42.96</v>
       </c>
       <c r="E204" s="4" t="n">
-        <v>48.75</v>
+        <v>47.54</v>
       </c>
       <c r="F204" s="4" t="n">
-        <v>46.82</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>PRINCEPIPE</t>
+          <t>KPIGREEN</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -6274,22 +5874,22 @@
         </is>
       </c>
       <c r="C205" s="4" t="n">
-        <v>259.65</v>
+        <v>420.6</v>
       </c>
       <c r="D205" s="4" t="n">
-        <v>54.11</v>
+        <v>42.95</v>
       </c>
       <c r="E205" s="4" t="n">
-        <v>49.08</v>
+        <v>48.7</v>
       </c>
       <c r="F205" s="4" t="n">
-        <v>38.08</v>
+        <v>50</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>ARVINDFASN</t>
+          <t>RELAXO</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -6298,22 +5898,22 @@
         </is>
       </c>
       <c r="C206" s="4" t="n">
-        <v>460.05</v>
+        <v>288.4</v>
       </c>
       <c r="D206" s="4" t="n">
-        <v>54.11</v>
+        <v>42.91</v>
       </c>
       <c r="E206" s="4" t="n">
-        <v>49.99</v>
+        <v>35.5</v>
       </c>
       <c r="F206" s="4" t="n">
-        <v>50.39</v>
+        <v>26.83</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>AHLUCONT</t>
+          <t>ETHOSLTD</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -6322,22 +5922,22 @@
         </is>
       </c>
       <c r="C207" s="4" t="n">
-        <v>847.55</v>
+        <v>2318.2</v>
       </c>
       <c r="D207" s="4" t="n">
-        <v>53.96</v>
+        <v>42.89</v>
       </c>
       <c r="E207" s="4" t="n">
-        <v>49.65</v>
+        <v>43.97</v>
       </c>
       <c r="F207" s="4" t="n">
-        <v>48.47</v>
+        <v>47.26</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>TARC</t>
+          <t>ORIENTCEM</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -6346,22 +5946,22 @@
         </is>
       </c>
       <c r="C208" s="4" t="n">
-        <v>136.69</v>
+        <v>136.45</v>
       </c>
       <c r="D208" s="4" t="n">
-        <v>53.95</v>
+        <v>42.73</v>
       </c>
       <c r="E208" s="4" t="n">
-        <v>46.16</v>
+        <v>32.55</v>
       </c>
       <c r="F208" s="4" t="n">
-        <v>47.76</v>
+        <v>35.61</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>GPPL</t>
+          <t>GALLANTT</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -6370,22 +5970,22 @@
         </is>
       </c>
       <c r="C209" s="4" t="n">
-        <v>158.9</v>
+        <v>744.9</v>
       </c>
       <c r="D209" s="4" t="n">
-        <v>53.41</v>
+        <v>42.58</v>
       </c>
       <c r="E209" s="4" t="n">
-        <v>47.67</v>
+        <v>58.59</v>
       </c>
       <c r="F209" s="4" t="n">
-        <v>51.73</v>
+        <v>62.86</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>JKIL</t>
+          <t>DBL</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -6394,22 +5994,22 @@
         </is>
       </c>
       <c r="C210" s="4" t="n">
-        <v>511.65</v>
+        <v>441.5</v>
       </c>
       <c r="D210" s="4" t="n">
-        <v>53.36</v>
+        <v>42.11</v>
       </c>
       <c r="E210" s="4" t="n">
-        <v>43.5</v>
+        <v>48.18</v>
       </c>
       <c r="F210" s="4" t="n">
-        <v>43.17</v>
+        <v>49.93</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>MASTEK</t>
+          <t>WAAREERTL</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -6418,22 +6018,22 @@
         </is>
       </c>
       <c r="C211" s="4" t="n">
-        <v>1683.1</v>
+        <v>942.4</v>
       </c>
       <c r="D211" s="4" t="n">
-        <v>53.14</v>
+        <v>42.06</v>
       </c>
       <c r="E211" s="4" t="n">
-        <v>41.06</v>
+        <v>48.79</v>
       </c>
       <c r="F211" s="4" t="n">
-        <v>40.53</v>
+        <v/>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>SUNTECK</t>
+          <t>UJJIVANSFB</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -6442,22 +6042,22 @@
         </is>
       </c>
       <c r="C212" s="4" t="n">
-        <v>345</v>
+        <v>55.83</v>
       </c>
       <c r="D212" s="4" t="n">
-        <v>52.98</v>
+        <v>41.93</v>
       </c>
       <c r="E212" s="4" t="n">
-        <v>44.37</v>
+        <v>49.98</v>
       </c>
       <c r="F212" s="4" t="n">
-        <v>43.43</v>
+        <v>57.51</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>GARFIBRES</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -6466,22 +6066,22 @@
         </is>
       </c>
       <c r="C213" s="4" t="n">
-        <v>641.15</v>
+        <v>1111.5</v>
       </c>
       <c r="D213" s="4" t="n">
-        <v>52.97</v>
+        <v>41.81</v>
       </c>
       <c r="E213" s="4" t="n">
-        <v>46.22</v>
+        <v>57.13</v>
       </c>
       <c r="F213" s="4" t="n">
-        <v>42.07</v>
+        <v>64.26000000000001</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>TIMETECHNO</t>
+          <t>EPL</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -6490,22 +6090,22 @@
         </is>
       </c>
       <c r="C214" s="4" t="n">
-        <v>187.08</v>
+        <v>215.29</v>
       </c>
       <c r="D214" s="4" t="n">
-        <v>52.84</v>
+        <v>41.71</v>
       </c>
       <c r="E214" s="4" t="n">
-        <v>49.58</v>
+        <v>50.28</v>
       </c>
       <c r="F214" s="4" t="n">
-        <v>52.92</v>
+        <v>51.75</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>GMRP&amp;UI</t>
+          <t>PRIVISCL</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -6514,22 +6114,22 @@
         </is>
       </c>
       <c r="C215" s="4" t="n">
-        <v>108.29</v>
+        <v>3091.8</v>
       </c>
       <c r="D215" s="4" t="n">
-        <v>52.69</v>
+        <v>41.64</v>
       </c>
       <c r="E215" s="4" t="n">
-        <v>49.94</v>
+        <v>54.08</v>
       </c>
       <c r="F215" s="4" t="n">
-        <v>53.8</v>
+        <v>63.79</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>JUSTDIAL</t>
+          <t>GHCL</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -6538,22 +6138,22 @@
         </is>
       </c>
       <c r="C216" s="4" t="n">
-        <v>544.75</v>
+        <v>472.65</v>
       </c>
       <c r="D216" s="4" t="n">
-        <v>52.64</v>
+        <v>41.28</v>
       </c>
       <c r="E216" s="4" t="n">
-        <v>36.31</v>
+        <v>40.8</v>
       </c>
       <c r="F216" s="4" t="n">
-        <v>36.12</v>
+        <v>43.92</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>MEDPLUS</t>
+          <t>GPPL</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -6562,22 +6162,22 @@
         </is>
       </c>
       <c r="C217" s="4" t="n">
-        <v>874.7</v>
+        <v>151.05</v>
       </c>
       <c r="D217" s="4" t="n">
-        <v>52.52</v>
+        <v>41.24</v>
       </c>
       <c r="E217" s="4" t="n">
-        <v>56.57</v>
+        <v>42.63</v>
       </c>
       <c r="F217" s="4" t="n">
-        <v>56.35</v>
+        <v>49.38</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>MOIL</t>
+          <t>ALLCARGO</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -6586,22 +6186,22 @@
         </is>
       </c>
       <c r="C218" s="4" t="n">
-        <v>315.35</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D218" s="4" t="n">
-        <v>52.34</v>
+        <v>41.19</v>
       </c>
       <c r="E218" s="4" t="n">
-        <v>49.46</v>
+        <v>33.82</v>
       </c>
       <c r="F218" s="4" t="n">
-        <v>49.65</v>
+        <v>27.65</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>VESUVIUS</t>
+          <t>PATELENG</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -6610,22 +6210,22 @@
         </is>
       </c>
       <c r="C219" s="4" t="n">
-        <v>506.1</v>
+        <v>26.26</v>
       </c>
       <c r="D219" s="4" t="n">
-        <v>52.25</v>
+        <v>41.19</v>
       </c>
       <c r="E219" s="4" t="n">
-        <v>54.19</v>
+        <v>41.49</v>
       </c>
       <c r="F219" s="4" t="n">
-        <v>55.78</v>
+        <v>36.88</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>ENTERO</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -6634,22 +6234,22 @@
         </is>
       </c>
       <c r="C220" s="4" t="n">
-        <v>1224.6</v>
+        <v>2563.8</v>
       </c>
       <c r="D220" s="4" t="n">
-        <v>52.24</v>
+        <v>41.1</v>
       </c>
       <c r="E220" s="4" t="n">
-        <v>55.79</v>
+        <v>46.69</v>
       </c>
       <c r="F220" s="4" t="n">
-        <v>53.92</v>
+        <v>46.73</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>CIEINDIA</t>
+          <t>HERITGFOOD</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -6658,22 +6258,22 @@
         </is>
       </c>
       <c r="C221" s="4" t="n">
-        <v>474.85</v>
+        <v>330.45</v>
       </c>
       <c r="D221" s="4" t="n">
-        <v>52.23</v>
+        <v>40.63</v>
       </c>
       <c r="E221" s="4" t="n">
-        <v>59.04</v>
+        <v>37.7</v>
       </c>
       <c r="F221" s="4" t="n">
-        <v>56.78</v>
+        <v>43.61</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>NETWORK18</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -6682,22 +6282,22 @@
         </is>
       </c>
       <c r="C222" s="4" t="n">
-        <v>459.65</v>
+        <v>32.22</v>
       </c>
       <c r="D222" s="4" t="n">
-        <v>52.18</v>
+        <v>40.59</v>
       </c>
       <c r="E222" s="4" t="n">
-        <v>54.19</v>
+        <v>36.43</v>
       </c>
       <c r="F222" s="4" t="n">
-        <v>59.18</v>
+        <v>36.18</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>CELLO</t>
+          <t>SHAKTIPUMP</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -6706,22 +6306,22 @@
         </is>
       </c>
       <c r="C223" s="4" t="n">
-        <v>423.65</v>
+        <v>508.6</v>
       </c>
       <c r="D223" s="4" t="n">
-        <v>51.92</v>
+        <v>40.56</v>
       </c>
       <c r="E223" s="4" t="n">
-        <v>36.48</v>
+        <v>37.34</v>
       </c>
       <c r="F223" s="4" t="n">
-        <v>32.61</v>
+        <v>44.26</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>NETWORK18</t>
+          <t>AWFIS</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -6730,22 +6330,22 @@
         </is>
       </c>
       <c r="C224" s="4" t="n">
-        <v>34.42</v>
+        <v>317.9</v>
       </c>
       <c r="D224" s="4" t="n">
-        <v>51.9</v>
+        <v>40.51</v>
       </c>
       <c r="E224" s="4" t="n">
-        <v>40.61</v>
+        <v>38.87</v>
       </c>
       <c r="F224" s="4" t="n">
-        <v>37.22</v>
+        <v>33.09</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -6754,22 +6354,22 @@
         </is>
       </c>
       <c r="C225" s="4" t="n">
-        <v>608.25</v>
+        <v>431.45</v>
       </c>
       <c r="D225" s="4" t="n">
-        <v>51.69</v>
+        <v>40.34</v>
       </c>
       <c r="E225" s="4" t="n">
-        <v>53.65</v>
+        <v>46.63</v>
       </c>
       <c r="F225" s="4" t="n">
-        <v>49.95</v>
+        <v>56.16</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>SAFARI</t>
+          <t>JUSTDIAL</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -6778,22 +6378,22 @@
         </is>
       </c>
       <c r="C226" s="4" t="n">
-        <v>1524.4</v>
+        <v>521.35</v>
       </c>
       <c r="D226" s="4" t="n">
-        <v>50.98</v>
+        <v>40.22</v>
       </c>
       <c r="E226" s="4" t="n">
-        <v>37.21</v>
+        <v>33.63</v>
       </c>
       <c r="F226" s="4" t="n">
-        <v>40.86</v>
+        <v>34.49</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>FINEORG</t>
+          <t>DODLA</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -6802,22 +6402,22 @@
         </is>
       </c>
       <c r="C227" s="4" t="n">
-        <v>4653.9</v>
+        <v>1025.6</v>
       </c>
       <c r="D227" s="4" t="n">
-        <v>50.66</v>
+        <v>40.1</v>
       </c>
       <c r="E227" s="4" t="n">
-        <v>54.2</v>
+        <v>37.35</v>
       </c>
       <c r="F227" s="4" t="n">
-        <v>51.6</v>
+        <v>46.72</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>RELIGARE</t>
+          <t>STARCEMENT</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -6826,22 +6426,22 @@
         </is>
       </c>
       <c r="C228" s="4" t="n">
-        <v>223</v>
+        <v>215.12</v>
       </c>
       <c r="D228" s="4" t="n">
-        <v>50.64</v>
+        <v>39.93</v>
       </c>
       <c r="E228" s="4" t="n">
-        <v>45.18</v>
+        <v>45.94</v>
       </c>
       <c r="F228" s="4" t="n">
-        <v>48.89</v>
+        <v>51.15</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>BBL</t>
+          <t>JAMNAAUTO</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -6850,22 +6450,22 @@
         </is>
       </c>
       <c r="C229" s="4" t="n">
-        <v>2793.1</v>
+        <v>116.19</v>
       </c>
       <c r="D229" s="4" t="n">
-        <v>50.34</v>
+        <v>39.53</v>
       </c>
       <c r="E229" s="4" t="n">
-        <v>52.27</v>
+        <v>47.23</v>
       </c>
       <c r="F229" s="4" t="n">
-        <v>49.34</v>
+        <v>52.98</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>SHAKTIPUMP</t>
+          <t>SHARDACROP</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -6874,22 +6474,22 @@
         </is>
       </c>
       <c r="C230" s="4" t="n">
-        <v>550.05</v>
+        <v>969</v>
       </c>
       <c r="D230" s="4" t="n">
-        <v>50.32</v>
+        <v>39.53</v>
       </c>
       <c r="E230" s="4" t="n">
-        <v>41.52</v>
+        <v>48.87</v>
       </c>
       <c r="F230" s="4" t="n">
-        <v>46.12</v>
+        <v>56.29</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>SAMHI</t>
+          <t>KITEX</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -6898,22 +6498,22 @@
         </is>
       </c>
       <c r="C231" s="4" t="n">
-        <v>157.46</v>
+        <v>156.75</v>
       </c>
       <c r="D231" s="4" t="n">
-        <v>49.88</v>
+        <v>39.41</v>
       </c>
       <c r="E231" s="4" t="n">
-        <v>43.64</v>
+        <v>41.86</v>
       </c>
       <c r="F231" s="4" t="n">
-        <v>44.91</v>
+        <v>48.38</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>MAHLIFE</t>
+          <t>TEGA</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -6922,22 +6522,22 @@
         </is>
       </c>
       <c r="C232" s="4" t="n">
-        <v>334.7</v>
+        <v>1585.3</v>
       </c>
       <c r="D232" s="4" t="n">
-        <v>49.55</v>
+        <v>39.34</v>
       </c>
       <c r="E232" s="4" t="n">
-        <v>44.1</v>
+        <v>36.73</v>
       </c>
       <c r="F232" s="4" t="n">
-        <v>42.37</v>
+        <v>49.94</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>TRANSRAILL</t>
+          <t>GREENPANEL</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -6946,22 +6546,22 @@
         </is>
       </c>
       <c r="C233" s="4" t="n">
-        <v>566.8</v>
+        <v>202.67</v>
       </c>
       <c r="D233" s="4" t="n">
-        <v>49.43</v>
+        <v>39.31</v>
       </c>
       <c r="E233" s="4" t="n">
-        <v>49.72</v>
+        <v>42.95</v>
       </c>
       <c r="F233" s="4" t="n">
-        <v>49.17</v>
+        <v>40.1</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>BLACKBUCK</t>
+          <t>IMAGICAA</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -6970,22 +6570,22 @@
         </is>
       </c>
       <c r="C234" s="4" t="n">
-        <v>579.1</v>
+        <v>43.22</v>
       </c>
       <c r="D234" s="4" t="n">
-        <v>49.24</v>
+        <v>39.24</v>
       </c>
       <c r="E234" s="4" t="n">
-        <v>48.23</v>
+        <v>42.7</v>
       </c>
       <c r="F234" s="4" t="n">
-        <v>55.82</v>
+        <v>40.73</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>PARADEEP</t>
+          <t>SAMHI</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -6994,22 +6594,22 @@
         </is>
       </c>
       <c r="C235" s="4" t="n">
-        <v>124.88</v>
+        <v>146.59</v>
       </c>
       <c r="D235" s="4" t="n">
-        <v>49.15</v>
+        <v>38.74</v>
       </c>
       <c r="E235" s="4" t="n">
-        <v>44.4</v>
+        <v>38.29</v>
       </c>
       <c r="F235" s="4" t="n">
-        <v>49.69</v>
+        <v>42.51</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>ETHOSLTD</t>
+          <t>AHLUCONT</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -7018,22 +6618,22 @@
         </is>
       </c>
       <c r="C236" s="4" t="n">
-        <v>2404.6</v>
+        <v>794.3</v>
       </c>
       <c r="D236" s="4" t="n">
-        <v>48.62</v>
+        <v>38.67</v>
       </c>
       <c r="E236" s="4" t="n">
-        <v>46.42</v>
+        <v>44.61</v>
       </c>
       <c r="F236" s="4" t="n">
-        <v>48.69</v>
+        <v>46.52</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>ORIENTCEM</t>
+          <t>MASTEK</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -7042,22 +6642,22 @@
         </is>
       </c>
       <c r="C237" s="4" t="n">
-        <v>141.47</v>
+        <v>1549.9</v>
       </c>
       <c r="D237" s="4" t="n">
-        <v>48</v>
+        <v>38.37</v>
       </c>
       <c r="E237" s="4" t="n">
-        <v>34.86</v>
+        <v>35.27</v>
       </c>
       <c r="F237" s="4" t="n">
-        <v>36.26</v>
+        <v>38.48</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>VIPIND</t>
+          <t>CCAVENUE</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -7066,22 +6666,22 @@
         </is>
       </c>
       <c r="C238" s="4" t="n">
-        <v>309</v>
+        <v>13.68</v>
       </c>
       <c r="D238" s="4" t="n">
-        <v>47.76</v>
+        <v>38.2</v>
       </c>
       <c r="E238" s="4" t="n">
-        <v>37.07</v>
+        <v>36.05</v>
       </c>
       <c r="F238" s="4" t="n">
-        <v>36.71</v>
+        <v/>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>RENUKA</t>
+          <t>BLACKBUCK</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
@@ -7090,22 +6690,22 @@
         </is>
       </c>
       <c r="C239" s="4" t="n">
-        <v>27.59</v>
+        <v>530.7</v>
       </c>
       <c r="D239" s="4" t="n">
-        <v>47.72</v>
+        <v>37.89</v>
       </c>
       <c r="E239" s="4" t="n">
-        <v>52.45</v>
+        <v>43.06</v>
       </c>
       <c r="F239" s="4" t="n">
-        <v>41.85</v>
+        <v>49.53</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>SYMPHONY</t>
+          <t>MANORAMA</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -7114,22 +6714,22 @@
         </is>
       </c>
       <c r="C240" s="4" t="n">
-        <v>794.3</v>
+        <v>1305.6</v>
       </c>
       <c r="D240" s="4" t="n">
-        <v>47.08</v>
+        <v>37.78</v>
       </c>
       <c r="E240" s="4" t="n">
-        <v>44.7</v>
+        <v>47.2</v>
       </c>
       <c r="F240" s="4" t="n">
-        <v>41.69</v>
+        <v>56.39</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>GMMPFAUDLR</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
@@ -7138,22 +6738,22 @@
         </is>
       </c>
       <c r="C241" s="4" t="n">
-        <v>894.1</v>
+        <v>3594.2</v>
       </c>
       <c r="D241" s="4" t="n">
-        <v>46.92</v>
+        <v>37.77</v>
       </c>
       <c r="E241" s="4" t="n">
-        <v>38.97</v>
+        <v>51.95</v>
       </c>
       <c r="F241" s="4" t="n">
-        <v>40.73</v>
+        <v>65.93000000000001</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>ZAGGLE</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -7162,22 +6762,22 @@
         </is>
       </c>
       <c r="C242" s="4" t="n">
-        <v>96.76000000000001</v>
+        <v>210.62</v>
       </c>
       <c r="D242" s="4" t="n">
-        <v>46.9</v>
+        <v>37.45</v>
       </c>
       <c r="E242" s="4" t="n">
-        <v>37.67</v>
+        <v>35.21</v>
       </c>
       <c r="F242" s="4" t="n">
-        <v>37.93</v>
+        <v>39.98</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>TEGA</t>
+          <t>BECTORFOOD</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -7186,22 +6786,22 @@
         </is>
       </c>
       <c r="C243" s="4" t="n">
-        <v>1662</v>
+        <v>181.83</v>
       </c>
       <c r="D243" s="4" t="n">
-        <v>46.52</v>
+        <v>36.85</v>
       </c>
       <c r="E243" s="4" t="n">
-        <v>41.62</v>
+        <v>33.15</v>
       </c>
       <c r="F243" s="4" t="n">
-        <v>52.63</v>
+        <v>38.74</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>IXIGO</t>
+          <t>CELLO</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -7210,22 +6810,22 @@
         </is>
       </c>
       <c r="C244" s="4" t="n">
-        <v>168.38</v>
+        <v>397</v>
       </c>
       <c r="D244" s="4" t="n">
-        <v>46.09</v>
+        <v>36.49</v>
       </c>
       <c r="E244" s="4" t="n">
-        <v>38.87</v>
+        <v>32.14</v>
       </c>
       <c r="F244" s="4" t="n">
-        <v>43.01</v>
+        <v>30.71</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>RAYMONDLSL</t>
+          <t>PNGJL</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
@@ -7234,22 +6834,22 @@
         </is>
       </c>
       <c r="C245" s="4" t="n">
-        <v>788.65</v>
+        <v>573.9</v>
       </c>
       <c r="D245" s="4" t="n">
-        <v>45.95</v>
+        <v>35.02</v>
       </c>
       <c r="E245" s="4" t="n">
-        <v>37.87</v>
+        <v>45.82</v>
       </c>
       <c r="F245" s="4" t="n">
-        <v>22.82</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>TRANSRAILL</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -7258,22 +6858,22 @@
         </is>
       </c>
       <c r="C246" s="4" t="n">
-        <v>180.84</v>
+        <v>513.35</v>
       </c>
       <c r="D246" s="4" t="n">
-        <v>45.77</v>
+        <v>34.46</v>
       </c>
       <c r="E246" s="4" t="n">
-        <v>54.48</v>
+        <v>42.95</v>
       </c>
       <c r="F246" s="4" t="n">
-        <v>59.18</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>CMSINFO</t>
+          <t>AURIONPRO</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
@@ -7282,22 +6882,22 @@
         </is>
       </c>
       <c r="C247" s="4" t="n">
-        <v>289.6</v>
+        <v>750.9</v>
       </c>
       <c r="D247" s="4" t="n">
-        <v>43.36</v>
+        <v>33.56</v>
       </c>
       <c r="E247" s="4" t="n">
-        <v>37.28</v>
+        <v>35.15</v>
       </c>
       <c r="F247" s="4" t="n">
-        <v>36.98</v>
+        <v>39.29</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>VOLTAMP</t>
+          <t>PCJEWELLER</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -7306,22 +6906,22 @@
         </is>
       </c>
       <c r="C248" s="4" t="n">
-        <v>9535</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="D248" s="4" t="n">
-        <v>42.75</v>
+        <v>33.03</v>
       </c>
       <c r="E248" s="4" t="n">
-        <v>55.11</v>
+        <v>38.07</v>
       </c>
       <c r="F248" s="4" t="n">
-        <v>54.42</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>CSBBANK</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
@@ -7330,22 +6930,22 @@
         </is>
       </c>
       <c r="C249" s="4" t="n">
-        <v>365.05</v>
+        <v>537.4</v>
       </c>
       <c r="D249" s="4" t="n">
-        <v>42.5</v>
+        <v>31.47</v>
       </c>
       <c r="E249" s="4" t="n">
-        <v>44.01</v>
+        <v>40.98</v>
       </c>
       <c r="F249" s="4" t="n">
-        <v>50.41</v>
+        <v>43.77</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>CCAVENUE</t>
+          <t>RENUKA</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
@@ -7354,16 +6954,16 @@
         </is>
       </c>
       <c r="C250" s="4" t="n">
-        <v>13.95</v>
+        <v>24.2</v>
       </c>
       <c r="D250" s="4" t="n">
-        <v>41.92</v>
+        <v>29.63</v>
       </c>
       <c r="E250" s="4" t="n">
-        <v>37.56</v>
+        <v>41.16</v>
       </c>
       <c r="F250" s="4" t="n">
-        <v/>
+        <v>38.18</v>
       </c>
     </row>
     <row r="251">
@@ -7378,16 +6978,16 @@
         </is>
       </c>
       <c r="C251" s="4" t="n">
-        <v>3330.6</v>
+        <v>3217.9</v>
       </c>
       <c r="D251" s="4" t="n">
-        <v>35.79</v>
+        <v>28.34</v>
       </c>
       <c r="E251" s="4" t="n">
-        <v>29.37</v>
+        <v>27.02</v>
       </c>
       <c r="F251" s="4" t="n">
-        <v>30.4</v>
+        <v>29.66</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Micro250_stocks.xlsx
+++ b/reports/Micro250_stocks.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -546,37 +546,37 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>419.8</v>
+        <v>441.15</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>87.54000000000001</v>
+        <v>81.41</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>92.67</v>
+        <v>93.23</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>85.70999999999999</v>
+        <v>86.44</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>21.31</v>
+        <v>34.82</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>187.62</v>
+        <v>202.48</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>171.38</v>
+        <v>183.44</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>7152897</v>
+        <v>6428792</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>20492</v>
+        <v>21536</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ARVIND</t>
+          <t>SANSERA</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -585,37 +585,37 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>451.1</v>
+        <v>2853.8</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>72.55</v>
+        <v>75.38</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>72.79000000000001</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>67.70999999999999</v>
+        <v>76.56</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>23.84</v>
+        <v>37.62</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>357.86</v>
+        <v>2041.39</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>353.04</v>
+        <v>1933.92</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>866094</v>
+        <v>340211</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>11824</v>
+        <v>17788</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>MEDPLUS</t>
+          <t>ARVIND</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -624,37 +624,37 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>951</v>
+        <v>480.35</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>72.19</v>
+        <v>73.67</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>66.56</v>
+        <v>76.41</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>61.77</v>
+        <v>69.97</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>31.7</v>
+        <v>21.12</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>839.39</v>
+        <v>365.95</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>832.33</v>
+        <v>359.38</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>137673</v>
+        <v>1126904</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>11412</v>
+        <v>12591</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>GRWRHITECH</t>
+          <t>MTARTECH</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -663,37 +663,37 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>5403.4</v>
+        <v>8075.5</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>69.81</v>
+        <v>73.51000000000001</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>72.05</v>
+        <v>92.06999999999999</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>63.31</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>25.12</v>
+        <v>32.3</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>3851.83</v>
+        <v>3923.62</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>3776.45</v>
+        <v>3540.42</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>139260</v>
+        <v>1522731</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>12553</v>
+        <v>24840</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>SUNFLAG</t>
+          <t>STAR</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -702,37 +702,37 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>373.45</v>
+        <v>1153.2</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>66</v>
+        <v>68.55</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>68.7</v>
+        <v>71.41</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>66.01000000000001</v>
+        <v>62.64</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>26.29</v>
+        <v>29.14</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>269.14</v>
+        <v>951.6900000000001</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>265.85</v>
+        <v>934.16</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1426600</v>
+        <v>373720</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>6730</v>
+        <v>10629</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>YATHARTH</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -741,37 +741,37 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>211.13</v>
+        <v>862.15</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>59.63</v>
+        <v>65.48</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>68.06999999999999</v>
+        <v>64.23</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>65.68000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>30.9</v>
+        <v>21.82</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>174.34</v>
+        <v>714.45</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>172.23</v>
+        <v>697.35</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2365831</v>
+        <v>483591</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>6250</v>
+        <v>8307</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>CEIGALL</t>
+          <t>V2RETAIL</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -780,37 +780,37 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>345.4</v>
+        <v>233.33</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>57.44</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>66.31999999999999</v>
+        <v>62.46</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>62.77</v>
+        <v>67.76000000000001</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>20.02</v>
+        <v>20.37</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>287.82</v>
+        <v>205.07</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>285.12</v>
+        <v>201.52</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>677116</v>
+        <v>1414573</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>6017</v>
+        <v>8508</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>SANSERA</t>
+          <t>SUNFLAG</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -819,37 +819,37 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>2385</v>
+        <v>377.25</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>47.3</v>
+        <v>63.6</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>62.86</v>
+        <v>69.13</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>68.81</v>
+        <v>66.3</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>33.48</v>
+        <v>33.76</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>2002.82</v>
+        <v>275.12</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1899.66</v>
+        <v>270.66</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>221004</v>
+        <v>1425999</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>14866</v>
+        <v>6799</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>ASTRAMICRO</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -858,37 +858,37 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>246.1</v>
+        <v>1174.9</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>45.81</v>
+        <v>63.59</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>62.82</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>61.29</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>34.06</v>
+        <v>50.64</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>216.09</v>
+        <v>1010.23</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>210.71</v>
+        <v>995.7</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>2967112</v>
+        <v>379596</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>9307</v>
+        <v>11155</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AVANTIFEED</t>
+          <t>GRWRHITECH</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -897,31 +897,265 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1323.2</v>
+        <v>5353.4</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>45.34</v>
+        <v>63.2</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>60.18</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>71.66</v>
+        <v>63.09</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>37.83</v>
+        <v>26.89</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1092.59</v>
+        <v>3957.29</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1027.75</v>
+        <v>3859.81</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1086347</v>
+        <v>151828</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>18028</v>
+        <v>12437</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>SHAILY</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>2695.2</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>62.01</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>68.97</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>36.77</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>2223.36</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>2159.04</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>531436</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>12397</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>GAEL</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>163.44</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>59.61</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>67.45999999999999</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>64.62</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>23.66</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>137.34</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>133.61</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>1170635</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>7497</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>ANURAS</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>1366.1</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>58.96</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>64.75</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>70.58</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>1250.4</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>1213.33</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>338416</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>15553</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>KTKBANK</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>264.5</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>58.93</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>68.45</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>25.51</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>218.8</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>213</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>3249038</v>
+      </c>
+      <c r="K15" s="4" t="n">
+        <v>10003</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>CEIGALL</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>343.55</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>55.77</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>65.56999999999999</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>62.38</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>28.17</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>290.58</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>287.34</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>734013</v>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>5985</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>AZAD</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>2039.6</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>51.51</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>60.91</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>61.32</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>26.67</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>1743.05</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>1709.9</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>584364</v>
+      </c>
+      <c r="K17" s="4" t="n">
+        <v>13172</v>
       </c>
     </row>
   </sheetData>
@@ -936,6 +1170,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1002,22 +1242,22 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>419.8</v>
+        <v>441.15</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>87.54000000000001</v>
+        <v>81.41</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>92.67</v>
+        <v>93.23</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>85.70999999999999</v>
+        <v>86.44</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENGG</t>
+          <t>SPARC</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -1026,22 +1266,22 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>70.59</v>
+        <v>209.77</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>77.31</v>
+        <v>77.76000000000001</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>68.89</v>
+        <v>73.56</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>56.76</v>
+        <v>57.05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>SANSERA</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -1050,22 +1290,22 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>1311.3</v>
+        <v>2853.8</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>77.02</v>
+        <v>75.38</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>81.33</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>84.64</v>
+        <v>76.56</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>DIACABS</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -1074,16 +1314,16 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>196.45</v>
+        <v>1473</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>76.31999999999999</v>
+        <v>74.83</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>76.03</v>
+        <v>70.77</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>66.45</v>
+        <v>71.48</v>
       </c>
     </row>
     <row r="6">
@@ -1098,22 +1338,22 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1706.2</v>
+        <v>1822.5</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>75.65000000000001</v>
+        <v>74.77</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>76.5</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>52.47</v>
+        <v>54.61</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>SHAILY</t>
+          <t>SHILPAMED</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1122,22 +1362,22 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>2768.3</v>
+        <v>490.25</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>74.84999999999999</v>
+        <v>74.42</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>65.29000000000001</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>69.76000000000001</v>
+        <v>65.94</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>SHILPAMED</t>
+          <t>ARVIND</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1146,22 +1386,22 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>478.4</v>
+        <v>480.35</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>74.15000000000001</v>
+        <v>73.67</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>72.68000000000001</v>
+        <v>76.41</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>65.09</v>
+        <v>69.97</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>STAR</t>
+          <t>MTARTECH</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -1170,22 +1410,22 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1153.7</v>
+        <v>8075.5</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>73.43000000000001</v>
+        <v>73.51000000000001</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>71.48999999999999</v>
+        <v>92.06999999999999</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>62.66</v>
+        <v>88.06999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ARVIND</t>
+          <t>SUPRIYA</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1194,22 +1434,22 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>451.1</v>
+        <v>774.1</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>72.55</v>
+        <v>73.36</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>72.79000000000001</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>67.70999999999999</v>
+        <v>60.24</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>MEDPLUS</t>
+          <t>RATEGAIN</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -1218,22 +1458,22 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>951</v>
+        <v>714.45</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>72.19</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>66.56</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>61.77</v>
+        <v>57.58</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ORCHPHARMA</t>
+          <t>LLOYDSENGG</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1242,22 +1482,22 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>712.6</v>
+        <v>69.37</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>71.90000000000001</v>
+        <v>70.42</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>56.28</v>
+        <v>67.03</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>47.04</v>
+        <v>56.21</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>DIACABS</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1266,22 +1506,22 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>299.95</v>
+        <v>193.5</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>71.68000000000001</v>
+        <v>69.73</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>61.38</v>
+        <v>73.84</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>58.33</v>
+        <v>66.04000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>MTARTECH</t>
+          <t>TIPSMUSIC</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1290,22 +1530,22 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>7234</v>
+        <v>681.05</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>71.20999999999999</v>
+        <v>69.67</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>90.42</v>
+        <v>68.23</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>86.54000000000001</v>
+        <v>61.35</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>GRWRHITECH</t>
+          <t>SFL</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1314,22 +1554,22 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>5403.4</v>
+        <v>638.5</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>69.81</v>
+        <v>69.53</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>72.05</v>
+        <v>60.82</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>63.31</v>
+        <v>44.26</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>REFEX</t>
+          <t>ENTERO</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1338,22 +1578,22 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>277.8</v>
+        <v>1354.4</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>68.65000000000001</v>
+        <v>69.33</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>54.8</v>
+        <v>63.53</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>48.53</v>
+        <v>59.51</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>INDIGOPNTS</t>
+          <t>STAR</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1362,22 +1602,22 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>985.3</v>
+        <v>1153.2</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>68.62</v>
+        <v>68.55</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>52.24</v>
+        <v>71.41</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>44.43</v>
+        <v>62.64</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>RAIN</t>
+          <t>SUDARSCHEM</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1386,22 +1626,22 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>156.99</v>
+        <v>1013</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>68.43000000000001</v>
+        <v>68.28</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>61.3</v>
+        <v>56.81</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>52.85</v>
+        <v>52.54</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>KANSAINER</t>
+          <t>ACUTAAS</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1410,22 +1650,22 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>222.07</v>
+        <v>2951.2</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>68.42</v>
+        <v>68.27</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>55.64</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>44.71</v>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>HCG</t>
+          <t>KIRLPNU</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1434,22 +1674,22 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>637.2</v>
+        <v>1607.3</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>68.28</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>58.85</v>
+        <v>77.81</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>60.02</v>
+        <v>64.81999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>RBA</t>
+          <t>INDIGOPNTS</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1458,22 +1698,22 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>67.73999999999999</v>
+        <v>1003.4</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>67.91</v>
+        <v>67.89</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>54.83</v>
+        <v>53.81</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>40.73</v>
+        <v>45.05</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>INNOVACAP</t>
+          <t>DHANUKA</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1482,22 +1722,22 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>858.3</v>
+        <v>1172.3</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>67.64</v>
+        <v>67.59</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>64.67</v>
+        <v>54.83</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>58.34</v>
+        <v>47.37</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>TEAMLEASE</t>
+          <t>VIYASH</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1506,22 +1746,22 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1364.6</v>
+        <v>246.06</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>67.33</v>
+        <v>67.19</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>47.91</v>
+        <v>76.33</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>35.68</v>
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>TDPOWERSYS</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1530,22 +1770,22 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1323.1</v>
+        <v>1295</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>66.87</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>66.01000000000001</v>
+        <v>79.43000000000001</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>68.40000000000001</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>REFEX</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1554,22 +1794,22 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>207.45</v>
+        <v>279.05</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>66.68000000000001</v>
+        <v>65.84</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>63.39</v>
+        <v>55.15</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>53.77</v>
+        <v>48.66</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>CYIENTDLM</t>
+          <t>RAIN</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1578,22 +1818,22 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>416.25</v>
+        <v>156.32</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>66.25</v>
+        <v>65.62</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>58.32</v>
+        <v>60.91</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>44.33</v>
+        <v>52.71</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>SUNFLAG</t>
+          <t>YATHARTH</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1602,22 +1842,22 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>373.45</v>
+        <v>862.15</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>66</v>
+        <v>65.48</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>68.7</v>
+        <v>64.23</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>66.01000000000001</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>SFL</t>
+          <t>HCG</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1626,22 +1866,22 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>604.95</v>
+        <v>654.3</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>65.79000000000001</v>
+        <v>65.47</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>56.27</v>
+        <v>61.97</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>42.16</v>
+        <v>61.25</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>V2RETAIL</t>
+          <t>AJAXENGG</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1650,22 +1890,22 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>228.24</v>
+        <v>569.95</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>65.38</v>
+        <v>65.22</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>60.72</v>
+        <v>55.94</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>66.95999999999999</v>
+        <v>48.59</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>ANURAS</t>
+          <t>RELIGARE</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1674,22 +1914,22 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1376</v>
+        <v>240.32</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>65.15000000000001</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>66.64</v>
+        <v>56.04</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>70.93000000000001</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>CEMPRO</t>
+          <t>GABRIEL</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1698,22 +1938,22 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>899.55</v>
+        <v>1120</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>65.06</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>68.12</v>
+        <v>59.48</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v/>
+        <v>65.01000000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>KIRLPNU</t>
+          <t>MAXESTATES</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1722,22 +1962,22 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1541.4</v>
+        <v>428.95</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>64.95999999999999</v>
+        <v>64.75</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>75.44</v>
+        <v>55.32</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>63.33</v>
+        <v>50.45</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>THYROCARE</t>
+          <t>V2RETAIL</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1746,22 +1986,22 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>462.15</v>
+        <v>233.33</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>64.95999999999999</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>60.08</v>
+        <v>62.46</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>61.81</v>
+        <v>67.76000000000001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>JSFB</t>
+          <t>CYIENTDLM</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1770,22 +2010,22 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>490.85</v>
+        <v>418.3</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>64.90000000000001</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>67.97</v>
+        <v>58.66</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>54.79</v>
+        <v>44.52</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>EMBDL</t>
+          <t>ORCHPHARMA</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1794,22 +2034,22 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>70.23999999999999</v>
+        <v>706.5</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>64.90000000000001</v>
+        <v>64.34</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>54.7</v>
+        <v>55.48</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>41.43</v>
+        <v>46.82</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>MARKSANS</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1818,22 +2058,22 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>514.35</v>
+        <v>211.86</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>64.77</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>61.13</v>
+        <v>65.12</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>50.45</v>
+        <v>54.47</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>ADVENZYMES</t>
+          <t>SUNFLAG</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1842,22 +2082,22 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>363.75</v>
+        <v>377.25</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>64.48</v>
+        <v>63.6</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>66.75</v>
+        <v>69.13</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>55.84</v>
+        <v>66.3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GABRIEL</t>
+          <t>ASTRAMICRO</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -1866,22 +2106,22 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>1091</v>
+        <v>1174.9</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>63.57</v>
+        <v>63.59</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>57.76</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>64.18000000000001</v>
+        <v>65.20999999999999</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>DCAL</t>
+          <t>RBA</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1890,22 +2130,22 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>194.25</v>
+        <v>67.7</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>63.33</v>
+        <v>63.42</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>48.75</v>
+        <v>54.73</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>47.86</v>
+        <v>40.7</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENT</t>
+          <t>INGERRAND</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -1914,22 +2154,22 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>70.5</v>
+        <v>4477.1</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>63.21</v>
+        <v>63.22</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>61.3</v>
+        <v>65.28</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>57.5</v>
+        <v>62.15</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>PGIL</t>
+          <t>GRWRHITECH</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -1938,22 +2178,22 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>1671.6</v>
+        <v>5353.4</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>62.86</v>
+        <v>63.2</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>56.82</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>63.4</v>
+        <v>63.09</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>ISGEC</t>
+          <t>ADVENZYMES</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -1962,22 +2202,22 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>1085.7</v>
+        <v>375.15</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>62.6</v>
+        <v>62.97</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>67.15000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>53.96</v>
+        <v>57.18</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>STYRENIX</t>
+          <t>TEAMLEASE</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -1986,22 +2226,22 @@
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>2344.8</v>
+        <v>1382.2</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>62.45</v>
+        <v>62.66</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>59.91</v>
+        <v>49.39</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>55.33</v>
+        <v>36.18</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>IIFLCAPS</t>
+          <t>SHAILY</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -2010,22 +2250,22 @@
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>342.95</v>
+        <v>2695.2</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>62.3</v>
+        <v>62.01</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>56.91</v>
+        <v>62.7</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>55.16</v>
+        <v>68.97</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>ACUTAAS</t>
+          <t>KANSAINER</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -2034,22 +2274,22 @@
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>2731</v>
+        <v>217.94</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>61.54</v>
+        <v>61.82</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>70.77</v>
+        <v>53.45</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v/>
+        <v>43.65</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GAEL</t>
+          <t>PRINCEPIPE</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -2058,22 +2298,22 @@
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>162.79</v>
+        <v>273.45</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>61.44</v>
+        <v>61.63</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>67.17</v>
+        <v>54.36</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>64.42</v>
+        <v>39.86</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>HEMIPROP</t>
+          <t>ICIL</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -2082,22 +2322,22 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>148.97</v>
+        <v>302.9</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>61.31</v>
+        <v>61.5</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>56.94</v>
+        <v>56.87</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>51.8</v>
+        <v>53.28</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GMRP&amp;UI</t>
+          <t>THYROCARE</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -2106,22 +2346,22 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>113.9</v>
+        <v>465.85</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>61.23</v>
+        <v>61.36</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>53.95</v>
+        <v>60.64</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>55.58</v>
+        <v>62.08</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>TIPSMUSIC</t>
+          <t>IIFLCAPS</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -2130,22 +2370,22 @@
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>646.65</v>
+        <v>342.55</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>60.98</v>
+        <v>60.76</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>64.20999999999999</v>
+        <v>56.81</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>59.06</v>
+        <v>55.11</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>VSTIND</t>
+          <t>POWERMECH</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -2154,22 +2394,22 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>260.2</v>
+        <v>2544.7</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>60.82</v>
+        <v>60.34</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>57.42</v>
+        <v>58.03</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>47.53</v>
+        <v>52.51</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>SPARC</t>
+          <t>POLYPLEX</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -2178,22 +2418,22 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>163.65</v>
+        <v>961.45</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>60.78</v>
+        <v>60.34</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>61.64</v>
+        <v>57.98</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>48.9</v>
+        <v>46.89</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>PRUDENT</t>
+          <t>TVSSCS</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -2202,22 +2442,22 @@
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>2832.3</v>
+        <v>121.57</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>60.58</v>
+        <v>60.17</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>61.8</v>
+        <v>54.53</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>59.77</v>
+        <v>43.93</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>BIRLACORPN</t>
+          <t>EMIL</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -2226,22 +2466,22 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>1018.65</v>
+        <v>120.65</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>60.56</v>
+        <v>60.05</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>51.09</v>
+        <v>58.47</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>44.74</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>EMIL</t>
+          <t>MIDHANI</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -2250,22 +2490,22 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>119.89</v>
+        <v>413.2</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>60.44</v>
+        <v>59.68</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>57.98</v>
+        <v>62.43</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>46.78</v>
+        <v>55.57</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>INGERRAND</t>
+          <t>GAEL</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -2274,22 +2514,22 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>4398.7</v>
+        <v>163.44</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>60.06</v>
+        <v>59.61</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>63.83</v>
+        <v>67.45999999999999</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>61.21</v>
+        <v>64.62</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>AARTIDRUGS</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -2298,22 +2538,22 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>211.13</v>
+        <v>389.95</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>59.63</v>
+        <v>59.3</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>68.06999999999999</v>
+        <v>51.19</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>65.68000000000001</v>
+        <v>45.85</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>VARROC</t>
+          <t>ISGEC</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -2322,22 +2562,22 @@
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>557.85</v>
+        <v>1078.4</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>59.39</v>
+        <v>59.23</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>51.96</v>
+        <v>65.94</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>52.67</v>
+        <v>53.67</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>MIDHANI</t>
+          <t>PRIVISCL</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -2346,22 +2586,22 @@
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>408.05</v>
+        <v>3318.3</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>59.35</v>
+        <v>59</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>61.56</v>
+        <v>59.71</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>55.17</v>
+        <v>68.90000000000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>VIYASH</t>
+          <t>ANURAS</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -2370,22 +2610,22 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>224.54</v>
+        <v>1366.1</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>59.07</v>
+        <v>58.96</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>67.87</v>
+        <v>64.75</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v/>
+        <v>70.58</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>SANOFICONR</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -2394,22 +2634,22 @@
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>4868.4</v>
+        <v>264.5</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>58.69</v>
+        <v>58.93</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>58.62</v>
+        <v>68.45</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>51.84</v>
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>RATEGAIN</t>
+          <t>INNOVACAP</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -2418,22 +2658,22 @@
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>625.35</v>
+        <v>848.3</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>58.56</v>
+        <v>58.89</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>57.21</v>
+        <v>63.02</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>52.97</v>
+        <v>57.75</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>INDIASHLTR</t>
+          <t>SENCO</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -2442,22 +2682,22 @@
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>826.55</v>
+        <v>347.95</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>58.35</v>
+        <v>58.43</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>56.51</v>
+        <v>55.25</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>56.22</v>
+        <v>49.85</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>VARROC</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -2466,22 +2706,22 @@
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>458.95</v>
+        <v>561.95</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>58.26</v>
+        <v>58.31</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>53.35</v>
+        <v>52.84</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>54.09</v>
+        <v>52.99</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>PRICOLLTD</t>
+          <t>FDC</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -2490,22 +2730,22 @@
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>614.7</v>
+        <v>373.25</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>58.01</v>
+        <v>58.29</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>56.68</v>
+        <v>48.61</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>60.87</v>
+        <v>45.38</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>TEXRAIL</t>
+          <t>HIKAL</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -2514,22 +2754,22 @@
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>116.23</v>
+        <v>205.34</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>57.83</v>
+        <v>58.04</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>51.69</v>
+        <v>49.46</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>45.39</v>
+        <v>39.92</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>DHANUKA</t>
+          <t>CMSINFO</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -2538,22 +2778,22 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>1083.5</v>
+        <v>306.4</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>57.81</v>
+        <v>57.92</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>45.44</v>
+        <v>44.43</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>44.39</v>
+        <v>39.93</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>ICIL</t>
+          <t>PURVA</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -2562,22 +2802,22 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>290.2</v>
+        <v>225.6</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>57.64</v>
+        <v>57.79</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>54.33</v>
+        <v>51.11</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>51.71</v>
+        <v>46.67</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>CEIGALL</t>
+          <t>CEMPRO</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -2586,22 +2826,22 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>345.4</v>
+        <v>862.8</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>57.44</v>
+        <v>57.77</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>66.31999999999999</v>
+        <v>63.71</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>62.77</v>
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GANESHHOU</t>
+          <t>DATAMATICS</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -2610,22 +2850,22 @@
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>685.5</v>
+        <v>784.85</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>57.35</v>
+        <v>57.73</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>47.7</v>
+        <v>52.77</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v/>
+        <v>54.71</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>JKPAPER</t>
+          <t>SKYGOLD</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -2634,22 +2874,22 @@
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>381.65</v>
+        <v>469.95</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>57.35</v>
+        <v>57.69</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>58.46</v>
+        <v>61.83</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>52.6</v>
+        <v>67.91</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>YATHARTH</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -2658,22 +2898,22 @@
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>815.6</v>
+        <v>283.5</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>57.24</v>
+        <v>57.41</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>60.72</v>
+        <v>55.46</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>62.73</v>
+        <v>55.88</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>NEOGEN</t>
+          <t>PARAS</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -2682,22 +2922,22 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>1664.8</v>
+        <v>812</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>57.09</v>
+        <v>57.22</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>60.87</v>
+        <v>58.05</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>53.82</v>
+        <v>53.21</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>PNCINFRA</t>
+          <t>KNRCON</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -2706,22 +2946,22 @@
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>217.64</v>
+        <v>132.12</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>57.07</v>
+        <v>57.17</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>47.11</v>
+        <v>44.7</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>40.53</v>
+        <v>35.29</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>LXCHEM</t>
+          <t>PGIL</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -2730,22 +2970,22 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>152.49</v>
+        <v>1620.3</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>56.66</v>
+        <v>57.07</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>51.3</v>
+        <v>54.56</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>39.89</v>
+        <v>62.49</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>ABDL</t>
+          <t>DCAL</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -2754,22 +2994,22 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>555.35</v>
+        <v>195.37</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>56.22</v>
+        <v>56.76</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>54.55</v>
+        <v>49.21</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>58.85</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>SKIPPER</t>
+          <t>VSTIND</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -2778,22 +3018,22 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>460.2</v>
+        <v>258.3</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>56.22</v>
+        <v>56.7</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>58.07</v>
+        <v>56.3</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>55.24</v>
+        <v>47.13</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>HIKAL</t>
+          <t>KSL</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -2802,22 +3042,22 @@
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>201.46</v>
+        <v>828.6</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>56.08</v>
+        <v>56.69</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>48.12</v>
+        <v>58.53</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>39.26</v>
+        <v>53.53</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>CMSINFO</t>
+          <t>GREAVESCOT</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -2826,22 +3066,22 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>302.95</v>
+        <v>169.45</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>55.94</v>
+        <v>56.43</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>43.02</v>
+        <v>51.09</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>39.33</v>
+        <v>48.23</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>MAXESTATES</t>
+          <t>NEOGEN</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -2850,22 +3090,22 @@
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>404.9</v>
+        <v>1687.1</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>55.91</v>
+        <v>56.36</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>49.83</v>
+        <v>61.63</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>48.3</v>
+        <v>54.26</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>SANDUMA</t>
+          <t>EPIGRAL</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -2874,22 +3114,22 @@
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>224.24</v>
+        <v>1251.1</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>55.74</v>
+        <v>56.23</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>55.72</v>
+        <v>53.26</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>61.02</v>
+        <v>45.91</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>SUPRIYA</t>
+          <t>TSFINV</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -2898,22 +3138,22 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>688.55</v>
+        <v>412.2</v>
       </c>
       <c r="D81" s="4" t="n">
-        <v>55.58</v>
+        <v>56.09</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>53.22</v>
+        <v>44.05</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>55.41</v>
+        <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>AZAD</t>
+          <t>BIRLACORPN</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -2922,22 +3162,22 @@
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>2098.2</v>
+        <v>1006.1</v>
       </c>
       <c r="D82" s="4" t="n">
-        <v>54.96</v>
+        <v>56.01</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>63.73</v>
+        <v>49.95</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>62.96</v>
+        <v>44.12</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>VMART</t>
+          <t>BELRISE</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -2946,22 +3186,22 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>641.2</v>
+        <v>216.36</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>54.28</v>
+        <v>55.98</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>50.24</v>
+        <v>65.19</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>46.38</v>
+        <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>ASTRAMICRO</t>
+          <t>GANESHHOU</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -2970,22 +3210,22 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>1106.6</v>
+        <v>690.75</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>54.28</v>
+        <v>55.97</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>59.53</v>
+        <v>48.57</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>62.42</v>
+        <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>KNRCON</t>
+          <t>WEBELSOLAR</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -2994,22 +3234,22 @@
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>129.56</v>
+        <v>107.89</v>
       </c>
       <c r="D85" s="4" t="n">
-        <v>54.24</v>
+        <v>55.92</v>
       </c>
       <c r="E85" s="4" t="n">
-        <v>43.11</v>
+        <v>58.43</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>34.65</v>
+        <v>54.12</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>GREAVESCOT</t>
+          <t>SOUTHBANK</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -3018,22 +3258,22 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>165.76</v>
+        <v>40.72</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>54.2</v>
+        <v>55.92</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>49.34</v>
+        <v>56.56</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>47.51</v>
+        <v>65.29000000000001</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>POWERMECH</t>
+          <t>MAHLIFE</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -3042,22 +3282,22 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>2441</v>
+        <v>341</v>
       </c>
       <c r="D87" s="4" t="n">
-        <v>54.11</v>
+        <v>55.91</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>54.75</v>
+        <v>46.95</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>51.06</v>
+        <v>43.07</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>KSL</t>
+          <t>CEIGALL</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -3066,22 +3306,22 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>814.05</v>
+        <v>343.55</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>53.95</v>
+        <v>55.77</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>57.13</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>52.93</v>
+        <v>62.38</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>EUREKAFORB</t>
+          <t>SANDUMA</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -3090,22 +3330,22 @@
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>511.8</v>
+        <v>225.66</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>53.93</v>
+        <v>55.76</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>48.5</v>
+        <v>56.11</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>45.95</v>
+        <v>61.24</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>EQUITASBNK</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -3114,22 +3354,22 @@
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>67.95999999999999</v>
+        <v>506.6</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>53.87</v>
+        <v>55.56</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>56.28</v>
+        <v>58.93</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>51.12</v>
+        <v>49.72</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>HCC</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -3138,22 +3378,22 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>21.41</v>
+        <v>455.3</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>53.81</v>
+        <v>55.49</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>53.24</v>
+        <v>52.21</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>45.61</v>
+        <v>53.66</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>WELENT</t>
+          <t>SKIPPER</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -3162,22 +3402,22 @@
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>510.75</v>
+        <v>460.05</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>53.72</v>
+        <v>54.83</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>54.71</v>
+        <v>58.03</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>54.76</v>
+        <v>55.22</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>ZYDUSWELL</t>
+          <t>VMART</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -3186,22 +3426,22 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>502.15</v>
+        <v>641.25</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>53.71</v>
+        <v>54.3</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>61.53</v>
+        <v>50.25</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>61.95</v>
+        <v>46.38</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>AJAXENGG</t>
+          <t>PARADEEP</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -3210,22 +3450,22 @@
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>526.45</v>
+        <v>127.19</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>53.68</v>
+        <v>54.18</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>49.22</v>
+        <v>46.62</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>43.33</v>
+        <v>50.25</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>SENCO</t>
+          <t>ARVINDFASN</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -3234,22 +3474,22 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>334.7</v>
+        <v>451</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>53.25</v>
+        <v>54.17</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>52.51</v>
+        <v>48.74</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>48.55</v>
+        <v>49.34</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>EASEMYTRIP</t>
+          <t>FIEMIND</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -3258,22 +3498,22 @@
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>7.91</v>
+        <v>2222.4</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>53.14</v>
+        <v>54.14</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>51.5</v>
+        <v>54.39</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>37.94</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>LMW</t>
+          <t>EASEMYTRIP</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -3282,22 +3522,22 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>14561</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>53.1</v>
+        <v>54.09</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>50.4</v>
+        <v>52.55</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>49.76</v>
+        <v>38.38</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>NESCO</t>
+          <t>IXIGO</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -3306,22 +3546,22 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>1230.4</v>
+        <v>171.17</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>53.06</v>
+        <v>54.01</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>53.81</v>
+        <v>40.67</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>58.9</v>
+        <v>43.89</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>SHARDAMOTR</t>
+          <t>BANCOINDIA</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -3330,22 +3570,22 @@
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>873.4</v>
+        <v>614.7</v>
       </c>
       <c r="D99" s="4" t="n">
-        <v>53</v>
+        <v>53.9</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>48.29</v>
+        <v>50.28</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>43.62</v>
+        <v>57.06</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>EPIGRAL</t>
+          <t>WABAG</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -3354,22 +3594,22 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>1216.4</v>
+        <v>1431.4</v>
       </c>
       <c r="D100" s="4" t="n">
-        <v>52.82</v>
+        <v>53.85</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>51.24</v>
+        <v>56.6</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>44.98</v>
+        <v>55.48</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>RATNAMANI</t>
+          <t>NESCO</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -3378,22 +3618,22 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>2693.4</v>
+        <v>1241.4</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>52.8</v>
+        <v>53.84</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>59.39</v>
+        <v>54.58</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>51.69</v>
+        <v>59.35</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>RALLIS</t>
+          <t>PNCINFRA</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -3402,22 +3642,22 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>263.7</v>
+        <v>215.32</v>
       </c>
       <c r="D102" s="4" t="n">
-        <v>52.77</v>
+        <v>53.6</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>49.54</v>
+        <v>46.18</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>48.73</v>
+        <v>40.14</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>CARTRADE</t>
+          <t>SAFARI</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -3426,22 +3666,22 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>1824.8</v>
+        <v>1527</v>
       </c>
       <c r="D103" s="4" t="n">
-        <v>52.72</v>
+        <v>53.58</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>43.57</v>
+        <v>39.06</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>51.4</v>
+        <v>40.92</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>HGINFRA</t>
+          <t>INOXGREEN</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -3450,22 +3690,22 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>604.2</v>
+        <v>180.35</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>52.47</v>
+        <v>53.54</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>43.54</v>
+        <v>51.67</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>37.87</v>
+        <v>53.22</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>JINDWORLD</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -3474,22 +3714,22 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>26.53</v>
+        <v>2774.2</v>
       </c>
       <c r="D105" s="4" t="n">
-        <v>52.39</v>
+        <v>53.26</v>
       </c>
       <c r="E105" s="4" t="n">
-        <v>46.39</v>
+        <v>51.78</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>36.44</v>
+        <v>49.11</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>CIGNITITEC</t>
+          <t>MANINFRA</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -3498,22 +3738,22 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>1260.3</v>
+        <v>118.34</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>52.32</v>
+        <v>53.19</v>
       </c>
       <c r="E106" s="4" t="n">
-        <v>44.74</v>
+        <v>51.31</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>46.95</v>
+        <v>44</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>GRINFRA</t>
+          <t>LLOYDSENT</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -3522,22 +3762,22 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>934.9</v>
+        <v>67.84</v>
       </c>
       <c r="D107" s="4" t="n">
-        <v>52.09</v>
+        <v>53.19</v>
       </c>
       <c r="E107" s="4" t="n">
-        <v>46.03</v>
+        <v>57.91</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>40.37</v>
+        <v>56.15</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>SKYGOLD</t>
+          <t>JKPAPER</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -3546,22 +3786,22 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>446.2</v>
+        <v>379.45</v>
       </c>
       <c r="D108" s="4" t="n">
-        <v>52.08</v>
+        <v>53.09</v>
       </c>
       <c r="E108" s="4" t="n">
-        <v>59.43</v>
+        <v>57.58</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>65.89</v>
+        <v>52.36</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>MANINFRA</t>
+          <t>HEMIPROP</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -3570,22 +3810,22 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>117.58</v>
+        <v>143.76</v>
       </c>
       <c r="D109" s="4" t="n">
-        <v>51.98</v>
+        <v>53.01</v>
       </c>
       <c r="E109" s="4" t="n">
-        <v>50.54</v>
+        <v>53.84</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>43.69</v>
+        <v>50.45</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>IMFA</t>
+          <t>GRINFRA</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -3594,22 +3834,22 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>1476.5</v>
+        <v>939.9</v>
       </c>
       <c r="D110" s="4" t="n">
-        <v>51.78</v>
+        <v>52.83</v>
       </c>
       <c r="E110" s="4" t="n">
-        <v>59.48</v>
+        <v>46.62</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>68.58</v>
+        <v>40.58</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>WEBELSOLAR</t>
+          <t>NFL</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -3618,22 +3858,22 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>103.44</v>
+        <v>76.37</v>
       </c>
       <c r="D111" s="4" t="n">
-        <v>51.55</v>
+        <v>52.82</v>
       </c>
       <c r="E111" s="4" t="n">
-        <v>56.39</v>
+        <v>45.21</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>52.96</v>
+        <v>45.04</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>OPTIEMUS</t>
+          <t>LXCHEM</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -3642,22 +3882,22 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>415.5</v>
+        <v>151.81</v>
       </c>
       <c r="D112" s="4" t="n">
-        <v>51.51</v>
+        <v>52.81</v>
       </c>
       <c r="E112" s="4" t="n">
-        <v>46.68</v>
+        <v>50.96</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>46.95</v>
+        <v>39.72</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>BAJAJELEC</t>
+          <t>OPTIEMUS</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -3666,22 +3906,22 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>393.1</v>
+        <v>418.9</v>
       </c>
       <c r="D113" s="4" t="n">
-        <v>51.5</v>
+        <v>52.8</v>
       </c>
       <c r="E113" s="4" t="n">
-        <v>41.5</v>
+        <v>47.22</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>31.07</v>
+        <v>47.16</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>INOXGREEN</t>
+          <t>ETHOSLTD</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -3690,22 +3930,22 @@
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>177.64</v>
+        <v>2407.8</v>
       </c>
       <c r="D114" s="4" t="n">
-        <v>51.46</v>
+        <v>52.6</v>
       </c>
       <c r="E114" s="4" t="n">
-        <v>50.68</v>
+        <v>47.09</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>52.79</v>
+        <v>48.75</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>PURVA</t>
+          <t>TANLA</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -3714,22 +3954,22 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>213.11</v>
+        <v>518.6</v>
       </c>
       <c r="D115" s="4" t="n">
-        <v>51.22</v>
+        <v>52.49</v>
       </c>
       <c r="E115" s="4" t="n">
-        <v>46.86</v>
+        <v>52.53</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>44.79</v>
+        <v>44.24</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>FDC</t>
+          <t>CIGNITITEC</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -3738,22 +3978,22 @@
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>366.15</v>
+        <v>1260.3</v>
       </c>
       <c r="D116" s="4" t="n">
-        <v>51.21</v>
+        <v>52.32</v>
       </c>
       <c r="E116" s="4" t="n">
-        <v>46.11</v>
+        <v>44.74</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>44.26</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>QUESS</t>
+          <t>WELENT</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -3762,22 +4002,22 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>202.97</v>
+        <v>505.15</v>
       </c>
       <c r="D117" s="4" t="n">
-        <v>50.72</v>
+        <v>52.32</v>
       </c>
       <c r="E117" s="4" t="n">
-        <v>47.72</v>
+        <v>53.3</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>32.91</v>
+        <v>54.25</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>GSFC</t>
+          <t>AWFIS</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -3786,22 +4026,22 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>170</v>
+        <v>343.55</v>
       </c>
       <c r="D118" s="4" t="n">
-        <v>50.65</v>
+        <v>52.28</v>
       </c>
       <c r="E118" s="4" t="n">
-        <v>48.29</v>
+        <v>43.53</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>46.92</v>
+        <v>34.58</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>BANCOINDIA</t>
+          <t>DYNAMATECH</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -3810,22 +4050,22 @@
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>608.35</v>
+        <v>11170</v>
       </c>
       <c r="D119" s="4" t="n">
-        <v>50.53</v>
+        <v>52.25</v>
       </c>
       <c r="E119" s="4" t="n">
-        <v>49.47</v>
+        <v>57.83</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>56.67</v>
+        <v>68.11</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>BOSCH-HCIL</t>
+          <t>SURYAROSNI</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -3834,22 +4074,22 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>1385.7</v>
+        <v>245.75</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>50.28</v>
+        <v>52.21</v>
       </c>
       <c r="E120" s="4" t="n">
-        <v>50.94</v>
+        <v>50.3</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v/>
+        <v>48.35</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>JKLAKSHMI</t>
+          <t>GOKEX</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -3858,22 +4098,22 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>653.7</v>
+        <v>697.3</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>50.22</v>
+        <v>52.05</v>
       </c>
       <c r="E121" s="4" t="n">
-        <v>42.18</v>
+        <v>48.67</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>43.41</v>
+        <v>47.83</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>SANOFICONR</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -3882,22 +4122,22 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>183.55</v>
+        <v>4735.1</v>
       </c>
       <c r="D122" s="4" t="n">
-        <v>50.19</v>
+        <v>51.92</v>
       </c>
       <c r="E122" s="4" t="n">
-        <v>56.11</v>
+        <v>54.48</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>60.02</v>
+        <v>49.46</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>GANECOS</t>
+          <t>JINDWORLD</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -3906,22 +4146,22 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>1016.9</v>
+        <v>26.43</v>
       </c>
       <c r="D123" s="4" t="n">
-        <v>50.15</v>
+        <v>51.81</v>
       </c>
       <c r="E123" s="4" t="n">
-        <v>53.12</v>
+        <v>46.16</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>45.64</v>
+        <v>36.36</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>GMMPFAUDLR</t>
+          <t>AZAD</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -3930,22 +4170,22 @@
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>896.5</v>
+        <v>2039.6</v>
       </c>
       <c r="D124" s="4" t="n">
-        <v>50.12</v>
+        <v>51.51</v>
       </c>
       <c r="E124" s="4" t="n">
-        <v>39.36</v>
+        <v>60.91</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>40.8</v>
+        <v>61.32</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>INDIAGLYCO</t>
+          <t>EMBDL</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -3954,22 +4194,22 @@
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>1019.3</v>
+        <v>61.71</v>
       </c>
       <c r="D125" s="4" t="n">
-        <v>50.05</v>
+        <v>51.34</v>
       </c>
       <c r="E125" s="4" t="n">
-        <v>55.48</v>
+        <v>48.39</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>61</v>
+        <v>38</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>DATAMATICS</t>
+          <t>MEDPLUS</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -3978,22 +4218,22 @@
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>741.8</v>
+        <v>898.75</v>
       </c>
       <c r="D126" s="4" t="n">
-        <v>50.04</v>
+        <v>51.32</v>
       </c>
       <c r="E126" s="4" t="n">
-        <v>48.75</v>
+        <v>56.91</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>52.81</v>
+        <v>58.22</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>POLYPLEX</t>
+          <t>IONEXCHANG</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -4002,22 +4242,22 @@
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>899.15</v>
+        <v>395.05</v>
       </c>
       <c r="D127" s="4" t="n">
-        <v>49.7</v>
+        <v>51.27</v>
       </c>
       <c r="E127" s="4" t="n">
-        <v>51.2</v>
+        <v>52.94</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>44.34</v>
+        <v>45.37</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>JAIBALAJI</t>
+          <t>RTNINDIA</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -4026,22 +4266,22 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>76.58</v>
+        <v>34.61</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>49.63</v>
+        <v>51.17</v>
       </c>
       <c r="E128" s="4" t="n">
-        <v>51.51</v>
+        <v>46.47</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>42.98</v>
+        <v>41.55</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>PRINCEPIPE</t>
+          <t>VAIBHAVGBL</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -4050,22 +4290,22 @@
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>251.8</v>
+        <v>220.65</v>
       </c>
       <c r="D129" s="4" t="n">
-        <v>49.56</v>
+        <v>50.97</v>
       </c>
       <c r="E129" s="4" t="n">
-        <v>46.09</v>
+        <v>49.71</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>37.44</v>
+        <v>44.42</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>FINEORG</t>
+          <t>JSFB</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -4074,22 +4314,22 @@
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>4631.3</v>
+        <v>450.45</v>
       </c>
       <c r="D130" s="4" t="n">
-        <v>49.49</v>
+        <v>50.7</v>
       </c>
       <c r="E130" s="4" t="n">
-        <v>53.6</v>
+        <v>56.78</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>51.38</v>
+        <v>50.44</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>SURYAROSNI</t>
+          <t>QUESS</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -4098,22 +4338,22 @@
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>242.85</v>
+        <v>202.74</v>
       </c>
       <c r="D131" s="4" t="n">
-        <v>49.39</v>
+        <v>50.54</v>
       </c>
       <c r="E131" s="4" t="n">
-        <v>49.38</v>
+        <v>47.63</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>48</v>
+        <v>32.87</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>HGINFRA</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -4122,22 +4362,22 @@
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>1172.6</v>
+        <v>599.15</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>49.35</v>
+        <v>50.31</v>
       </c>
       <c r="E132" s="4" t="n">
-        <v>62.82</v>
+        <v>43.03</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>62.55</v>
+        <v>37.62</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>TVSSCS</t>
+          <t>MASTEK</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -4146,22 +4386,22 @@
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>113.32</v>
+        <v>1635.2</v>
       </c>
       <c r="D133" s="4" t="n">
-        <v>49.29</v>
+        <v>50.3</v>
       </c>
       <c r="E133" s="4" t="n">
-        <v>50</v>
+        <v>41.01</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>41</v>
+        <v>39.77</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>GARFIBRES</t>
+          <t>ABDL</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -4170,22 +4410,22 @@
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>628.45</v>
+        <v>536.3</v>
       </c>
       <c r="D134" s="4" t="n">
-        <v>49.25</v>
+        <v>50.15</v>
       </c>
       <c r="E134" s="4" t="n">
-        <v>44.18</v>
+        <v>52.13</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>40.56</v>
+        <v>57.53</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>BELRISE</t>
+          <t>CARTRADE</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -4194,22 +4434,22 @@
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>209.46</v>
+        <v>1796.6</v>
       </c>
       <c r="D135" s="4" t="n">
-        <v>49.1</v>
+        <v>50.02</v>
       </c>
       <c r="E135" s="4" t="n">
-        <v>62.65</v>
+        <v>42.88</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v/>
+        <v>50.89</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>GOKEX</t>
+          <t>STYRENIX</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -4218,22 +4458,22 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>687.7</v>
+        <v>2223.8</v>
       </c>
       <c r="D136" s="4" t="n">
-        <v>49</v>
+        <v>49.97</v>
       </c>
       <c r="E136" s="4" t="n">
-        <v>47.79</v>
+        <v>53.63</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>47.48</v>
+        <v>52.82</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>RELIGARE</t>
+          <t>HCC</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -4242,22 +4482,22 @@
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>221.93</v>
+        <v>20.87</v>
       </c>
       <c r="D137" s="4" t="n">
-        <v>48.6</v>
+        <v>49.94</v>
       </c>
       <c r="E137" s="4" t="n">
-        <v>44.54</v>
+        <v>51.61</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>48.65</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>VINATIORGA</t>
+          <t>STARCEMENT</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -4266,22 +4506,22 @@
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>1322.8</v>
+        <v>220.99</v>
       </c>
       <c r="D138" s="4" t="n">
-        <v>48.34</v>
+        <v>49.79</v>
       </c>
       <c r="E138" s="4" t="n">
-        <v>37.89</v>
+        <v>49.32</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>35.97</v>
+        <v>52.69</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>BORORENEW</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -4290,22 +4530,22 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>711.75</v>
+        <v>508.65</v>
       </c>
       <c r="D139" s="4" t="n">
-        <v>48.19</v>
+        <v>49.66</v>
       </c>
       <c r="E139" s="4" t="n">
-        <v>48.27</v>
+        <v>50.73</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>52.06</v>
+        <v>49.94</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>LUXIND</t>
+          <t>SHAREINDIA</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -4314,22 +4554,22 @@
         </is>
       </c>
       <c r="C140" s="4" t="n">
-        <v>1367.1</v>
+        <v>141.57</v>
       </c>
       <c r="D140" s="4" t="n">
-        <v>47.93</v>
+        <v>49.57</v>
       </c>
       <c r="E140" s="4" t="n">
-        <v>56.13</v>
+        <v>47.27</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>49.97</v>
+        <v>40.88</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>IONEXCHANG</t>
+          <t>TEXRAIL</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -4338,22 +4578,22 @@
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>390.15</v>
+        <v>108.21</v>
       </c>
       <c r="D141" s="4" t="n">
-        <v>47.8</v>
+        <v>49.57</v>
       </c>
       <c r="E141" s="4" t="n">
-        <v>51.67</v>
+        <v>46.2</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>44.93</v>
+        <v>43.43</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>MOIL</t>
+          <t>AURIONPRO</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -4362,22 +4602,22 @@
         </is>
       </c>
       <c r="C142" s="4" t="n">
-        <v>306.95</v>
+        <v>819</v>
       </c>
       <c r="D142" s="4" t="n">
-        <v>47.76</v>
+        <v>49.53</v>
       </c>
       <c r="E142" s="4" t="n">
-        <v>47.38</v>
+        <v>41.13</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>48.52</v>
+        <v>41.04</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>ANUP</t>
+          <t>AARTIPHARM</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -4386,22 +4626,22 @@
         </is>
       </c>
       <c r="C143" s="4" t="n">
-        <v>1966.5</v>
+        <v>713.1</v>
       </c>
       <c r="D143" s="4" t="n">
-        <v>47.49</v>
+        <v>49.43</v>
       </c>
       <c r="E143" s="4" t="n">
-        <v>48.69</v>
+        <v>48.44</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>47.88</v>
+        <v>52.15</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>SUDARSCHEM</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -4410,22 +4650,22 @@
         </is>
       </c>
       <c r="C144" s="4" t="n">
-        <v>868.6</v>
+        <v>3817.3</v>
       </c>
       <c r="D144" s="4" t="n">
-        <v>47.47</v>
+        <v>49.35</v>
       </c>
       <c r="E144" s="4" t="n">
-        <v>43.3</v>
+        <v>55.09</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>46.89</v>
+        <v>70</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>RTNINDIA</t>
+          <t>ANUP</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -4434,22 +4674,22 @@
         </is>
       </c>
       <c r="C145" s="4" t="n">
-        <v>33.9</v>
+        <v>1977.6</v>
       </c>
       <c r="D145" s="4" t="n">
-        <v>47.46</v>
+        <v>49.26</v>
       </c>
       <c r="E145" s="4" t="n">
-        <v>45.04</v>
+        <v>49.1</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>41.21</v>
+        <v>48.06</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>ENTERO</t>
+          <t>VIPIND</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -4458,22 +4698,22 @@
         </is>
       </c>
       <c r="C146" s="4" t="n">
-        <v>1192.3</v>
+        <v>303.2</v>
       </c>
       <c r="D146" s="4" t="n">
-        <v>47.42</v>
+        <v>48.87</v>
       </c>
       <c r="E146" s="4" t="n">
-        <v>52.73</v>
+        <v>35.9</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>52.17</v>
+        <v>35.79</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>UNIMECH</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -4482,22 +4722,22 @@
         </is>
       </c>
       <c r="C147" s="4" t="n">
-        <v>941.2</v>
+        <v>181.34</v>
       </c>
       <c r="D147" s="4" t="n">
-        <v>47.31</v>
+        <v>48.84</v>
       </c>
       <c r="E147" s="4" t="n">
-        <v>50.7</v>
+        <v>54.4</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>43.93</v>
+        <v>59.34</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>SANSERA</t>
+          <t>FINEORG</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -4506,22 +4746,22 @@
         </is>
       </c>
       <c r="C148" s="4" t="n">
-        <v>2385</v>
+        <v>4604.1</v>
       </c>
       <c r="D148" s="4" t="n">
-        <v>47.3</v>
+        <v>48.7</v>
       </c>
       <c r="E148" s="4" t="n">
-        <v>62.86</v>
+        <v>52.85</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>68.81</v>
+        <v>51.1</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>SWSOLAR</t>
+          <t>DODLA</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -4530,22 +4770,22 @@
         </is>
       </c>
       <c r="C149" s="4" t="n">
-        <v>199.78</v>
+        <v>1062.8</v>
       </c>
       <c r="D149" s="4" t="n">
-        <v>47.2</v>
+        <v>48.69</v>
       </c>
       <c r="E149" s="4" t="n">
-        <v>47.66</v>
+        <v>42.28</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>38.85</v>
+        <v>48.17</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>TANLA</t>
+          <t>RELAXO</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -4554,22 +4794,22 @@
         </is>
       </c>
       <c r="C150" s="4" t="n">
-        <v>497.5</v>
+        <v>294.4</v>
       </c>
       <c r="D150" s="4" t="n">
-        <v>47.15</v>
+        <v>48.39</v>
       </c>
       <c r="E150" s="4" t="n">
-        <v>49.55</v>
+        <v>37.52</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>42.97</v>
+        <v>27.15</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>BORORENEW</t>
+          <t>KRBL</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -4578,22 +4818,22 @@
         </is>
       </c>
       <c r="C151" s="4" t="n">
-        <v>500.2</v>
+        <v>343.8</v>
       </c>
       <c r="D151" s="4" t="n">
-        <v>47.13</v>
+        <v>48.32</v>
       </c>
       <c r="E151" s="4" t="n">
-        <v>49.58</v>
+        <v>48.18</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>49.33</v>
+        <v>50.83</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>AARTIDRUGS</t>
+          <t>GMRP&amp;UI</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -4602,22 +4842,22 @@
         </is>
       </c>
       <c r="C152" s="4" t="n">
-        <v>367.75</v>
+        <v>108.16</v>
       </c>
       <c r="D152" s="4" t="n">
-        <v>47.07</v>
+        <v>48.31</v>
       </c>
       <c r="E152" s="4" t="n">
-        <v>44.6</v>
+        <v>49.57</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>43.44</v>
+        <v>53.76</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>ALIVUS</t>
+          <t>EQUITASBNK</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -4626,22 +4866,22 @@
         </is>
       </c>
       <c r="C153" s="4" t="n">
-        <v>1044.6</v>
+        <v>66.48</v>
       </c>
       <c r="D153" s="4" t="n">
-        <v>47.06</v>
+        <v>48.16</v>
       </c>
       <c r="E153" s="4" t="n">
-        <v>58.89</v>
+        <v>54.12</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>63.13</v>
+        <v>50.25</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>SOUTHBANK</t>
+          <t>IMFA</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -4650,22 +4890,22 @@
         </is>
       </c>
       <c r="C154" s="4" t="n">
-        <v>38.83</v>
+        <v>1433.2</v>
       </c>
       <c r="D154" s="4" t="n">
-        <v>47.04</v>
+        <v>48.12</v>
       </c>
       <c r="E154" s="4" t="n">
-        <v>52.06</v>
+        <v>56.71</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>62.78</v>
+        <v>66.67</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>WESTLIFE</t>
+          <t>BOSCH-HCIL</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -4674,22 +4914,22 @@
         </is>
       </c>
       <c r="C155" s="4" t="n">
-        <v>473.2</v>
+        <v>1361.6</v>
       </c>
       <c r="D155" s="4" t="n">
-        <v>47.03</v>
+        <v>48.06</v>
       </c>
       <c r="E155" s="4" t="n">
-        <v>41.32</v>
+        <v>48.89</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>31.28</v>
+        <v/>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>SHRIPISTON</t>
+          <t>ROUTE</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -4698,16 +4938,16 @@
         </is>
       </c>
       <c r="C156" s="4" t="n">
-        <v>3385.6</v>
+        <v>511.35</v>
       </c>
       <c r="D156" s="4" t="n">
-        <v>47.03</v>
+        <v>47.92</v>
       </c>
       <c r="E156" s="4" t="n">
-        <v>56.67</v>
+        <v>39.34</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>69.11</v>
+        <v>29.07</v>
       </c>
     </row>
     <row r="157">
@@ -4722,22 +4962,22 @@
         </is>
       </c>
       <c r="C157" s="4" t="n">
-        <v>579.5</v>
+        <v>580.35</v>
       </c>
       <c r="D157" s="4" t="n">
-        <v>46.99</v>
+        <v>47.89</v>
       </c>
       <c r="E157" s="4" t="n">
-        <v>43.45</v>
+        <v>43.58</v>
       </c>
       <c r="F157" s="4" t="n">
-        <v>43.89</v>
+        <v>43.93</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>OSWALPUMPS</t>
+          <t>RATNAMANI</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -4746,22 +4986,22 @@
         </is>
       </c>
       <c r="C158" s="4" t="n">
-        <v>385.05</v>
+        <v>2564.1</v>
       </c>
       <c r="D158" s="4" t="n">
-        <v>46.93</v>
+        <v>47.6</v>
       </c>
       <c r="E158" s="4" t="n">
-        <v>41.82</v>
+        <v>54.21</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v/>
+        <v>49.09</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>VIPIND</t>
+          <t>GARFIBRES</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -4770,22 +5010,22 @@
         </is>
       </c>
       <c r="C159" s="4" t="n">
-        <v>302.55</v>
+        <v>625.3</v>
       </c>
       <c r="D159" s="4" t="n">
-        <v>46.78</v>
+        <v>47.53</v>
       </c>
       <c r="E159" s="4" t="n">
-        <v>35.63</v>
+        <v>43.67</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>35.69</v>
+        <v>40.17</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>LUMAXTECH</t>
+          <t>VINATIORGA</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -4794,22 +5034,22 @@
         </is>
       </c>
       <c r="C160" s="4" t="n">
-        <v>1636.1</v>
+        <v>1318.5</v>
       </c>
       <c r="D160" s="4" t="n">
-        <v>46.75</v>
+        <v>47.48</v>
       </c>
       <c r="E160" s="4" t="n">
-        <v>53.96</v>
+        <v>37.58</v>
       </c>
       <c r="F160" s="4" t="n">
-        <v>68.56</v>
+        <v>35.82</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>ELECTCAST</t>
+          <t>GSFC</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -4818,22 +5058,22 @@
         </is>
       </c>
       <c r="C161" s="4" t="n">
-        <v>81.95999999999999</v>
+        <v>169.08</v>
       </c>
       <c r="D161" s="4" t="n">
-        <v>46.74</v>
+        <v>47.44</v>
       </c>
       <c r="E161" s="4" t="n">
-        <v>50.96</v>
+        <v>47.67</v>
       </c>
       <c r="F161" s="4" t="n">
-        <v>44.06</v>
+        <v>46.69</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>SYMPHONY</t>
+          <t>UNIMECH</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -4842,22 +5082,22 @@
         </is>
       </c>
       <c r="C162" s="4" t="n">
-        <v>784.1</v>
+        <v>936</v>
       </c>
       <c r="D162" s="4" t="n">
-        <v>46.62</v>
+        <v>47.4</v>
       </c>
       <c r="E162" s="4" t="n">
-        <v>43.73</v>
+        <v>50.26</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>41.32</v>
+        <v>43.72</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>FIEMIND</t>
+          <t>MOIL</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -4866,22 +5106,22 @@
         </is>
       </c>
       <c r="C163" s="4" t="n">
-        <v>2168.2</v>
+        <v>303.45</v>
       </c>
       <c r="D163" s="4" t="n">
-        <v>46.62</v>
+        <v>47.16</v>
       </c>
       <c r="E163" s="4" t="n">
-        <v>51.55</v>
+        <v>46.51</v>
       </c>
       <c r="F163" s="4" t="n">
-        <v>64.75</v>
+        <v>48.06</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>IFBIND</t>
+          <t>WESTLIFE</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -4890,22 +5130,22 @@
         </is>
       </c>
       <c r="C164" s="4" t="n">
-        <v>1113.1</v>
+        <v>471.35</v>
       </c>
       <c r="D164" s="4" t="n">
-        <v>46.42</v>
+        <v>47.15</v>
       </c>
       <c r="E164" s="4" t="n">
-        <v>41.07</v>
+        <v>40.99</v>
       </c>
       <c r="F164" s="4" t="n">
-        <v>45.39</v>
+        <v>31.16</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>KSCL</t>
+          <t>TARC</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -4914,22 +5154,22 @@
         </is>
       </c>
       <c r="C165" s="4" t="n">
-        <v>918.35</v>
+        <v>130.61</v>
       </c>
       <c r="D165" s="4" t="n">
-        <v>46.32</v>
+        <v>47.14</v>
       </c>
       <c r="E165" s="4" t="n">
-        <v>49.34</v>
+        <v>42.98</v>
       </c>
       <c r="F165" s="4" t="n">
-        <v>49.29</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>SHAREINDIA</t>
+          <t>EMUDHRA</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -4938,22 +5178,22 @@
         </is>
       </c>
       <c r="C166" s="4" t="n">
-        <v>138.49</v>
+        <v>471</v>
       </c>
       <c r="D166" s="4" t="n">
-        <v>46.21</v>
+        <v>47.03</v>
       </c>
       <c r="E166" s="4" t="n">
-        <v>45.46</v>
+        <v>41.8</v>
       </c>
       <c r="F166" s="4" t="n">
-        <v>40.22</v>
+        <v>39.87</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>IXIGO</t>
+          <t>ZYDUSWELL</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -4962,22 +5202,22 @@
         </is>
       </c>
       <c r="C167" s="4" t="n">
-        <v>165.62</v>
+        <v>490.4</v>
       </c>
       <c r="D167" s="4" t="n">
-        <v>46.16</v>
+        <v>47.01</v>
       </c>
       <c r="E167" s="4" t="n">
-        <v>38.09</v>
+        <v>58.38</v>
       </c>
       <c r="F167" s="4" t="n">
-        <v>42.34</v>
+        <v>60.25</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>MANORAMA</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -4986,22 +5226,22 @@
         </is>
       </c>
       <c r="C168" s="4" t="n">
-        <v>94.73999999999999</v>
+        <v>1386.4</v>
       </c>
       <c r="D168" s="4" t="n">
-        <v>46.12</v>
+        <v>46.98</v>
       </c>
       <c r="E168" s="4" t="n">
-        <v>36.78</v>
+        <v>51.3</v>
       </c>
       <c r="F168" s="4" t="n">
-        <v>37.25</v>
+        <v>59.42</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>CIEINDIA</t>
+          <t>MSTCLTD</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -5010,22 +5250,22 @@
         </is>
       </c>
       <c r="C169" s="4" t="n">
-        <v>460.75</v>
+        <v>426.25</v>
       </c>
       <c r="D169" s="4" t="n">
-        <v>46.11</v>
+        <v>46.97</v>
       </c>
       <c r="E169" s="4" t="n">
-        <v>54.82</v>
+        <v>45.14</v>
       </c>
       <c r="F169" s="4" t="n">
-        <v>54.78</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>TSFINV</t>
+          <t>SWSOLAR</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -5034,22 +5274,22 @@
         </is>
       </c>
       <c r="C170" s="4" t="n">
-        <v>391.7</v>
+        <v>198.04</v>
       </c>
       <c r="D170" s="4" t="n">
-        <v>46</v>
+        <v>46.95</v>
       </c>
       <c r="E170" s="4" t="n">
-        <v>38.38</v>
+        <v>47.07</v>
       </c>
       <c r="F170" s="4" t="n">
-        <v/>
+        <v>38.71</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>MAHLIFE</t>
+          <t>SAMHI</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -5058,22 +5298,22 @@
         </is>
       </c>
       <c r="C171" s="4" t="n">
-        <v>326.45</v>
+        <v>150.08</v>
       </c>
       <c r="D171" s="4" t="n">
-        <v>45.94</v>
+        <v>46.57</v>
       </c>
       <c r="E171" s="4" t="n">
-        <v>41.89</v>
+        <v>40.8</v>
       </c>
       <c r="F171" s="4" t="n">
-        <v>41.51</v>
+        <v>43.23</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>WAAREERTL</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -5082,22 +5322,22 @@
         </is>
       </c>
       <c r="C172" s="4" t="n">
-        <v>246.1</v>
+        <v>957.1</v>
       </c>
       <c r="D172" s="4" t="n">
-        <v>45.81</v>
+        <v>46.28</v>
       </c>
       <c r="E172" s="4" t="n">
-        <v>62.82</v>
+        <v>49.96</v>
       </c>
       <c r="F172" s="4" t="n">
-        <v>61.29</v>
+        <v/>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>SUBROS</t>
+          <t>AHLUCONT</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -5106,22 +5346,22 @@
         </is>
       </c>
       <c r="C173" s="4" t="n">
-        <v>748.1</v>
+        <v>806.35</v>
       </c>
       <c r="D173" s="4" t="n">
-        <v>45.68</v>
+        <v>46.27</v>
       </c>
       <c r="E173" s="4" t="n">
-        <v>45.87</v>
+        <v>45.95</v>
       </c>
       <c r="F173" s="4" t="n">
-        <v>51.2</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>DYNAMATECH</t>
+          <t>SHARDAMOTR</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -5130,22 +5370,22 @@
         </is>
       </c>
       <c r="C174" s="4" t="n">
-        <v>10736</v>
+        <v>853.1</v>
       </c>
       <c r="D174" s="4" t="n">
-        <v>45.61</v>
+        <v>46.26</v>
       </c>
       <c r="E174" s="4" t="n">
-        <v>55.74</v>
+        <v>46.35</v>
       </c>
       <c r="F174" s="4" t="n">
-        <v>65.27</v>
+        <v>43</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>VAIBHAVGBL</t>
+          <t>KSCL</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -5154,22 +5394,22 @@
         </is>
       </c>
       <c r="C175" s="4" t="n">
-        <v>213.49</v>
+        <v>918.35</v>
       </c>
       <c r="D175" s="4" t="n">
-        <v>45.6</v>
+        <v>46.25</v>
       </c>
       <c r="E175" s="4" t="n">
-        <v>47.2</v>
+        <v>49.34</v>
       </c>
       <c r="F175" s="4" t="n">
-        <v>43.36</v>
+        <v>49.29</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>PRSMJOHNSN</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -5178,22 +5418,22 @@
         </is>
       </c>
       <c r="C176" s="4" t="n">
-        <v>127.34</v>
+        <v>1109.6</v>
       </c>
       <c r="D176" s="4" t="n">
-        <v>45.54</v>
+        <v>46.21</v>
       </c>
       <c r="E176" s="4" t="n">
-        <v>45.26</v>
+        <v>58.4</v>
       </c>
       <c r="F176" s="4" t="n">
-        <v>44.31</v>
+        <v>59.72</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>RAYMONDLSL</t>
+          <t>AVANTIFEED</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -5202,22 +5442,22 @@
         </is>
       </c>
       <c r="C177" s="4" t="n">
-        <v>779.6</v>
+        <v>1306.8</v>
       </c>
       <c r="D177" s="4" t="n">
-        <v>45.47</v>
+        <v>46.02</v>
       </c>
       <c r="E177" s="4" t="n">
-        <v>37.25</v>
+        <v>59.1</v>
       </c>
       <c r="F177" s="4" t="n">
-        <v>22.63</v>
+        <v>70.73</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>EMUDHRA</t>
+          <t>KPIGREEN</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -5226,22 +5466,22 @@
         </is>
       </c>
       <c r="C178" s="4" t="n">
-        <v>470.55</v>
+        <v>426.8</v>
       </c>
       <c r="D178" s="4" t="n">
-        <v>45.42</v>
+        <v>45.85</v>
       </c>
       <c r="E178" s="4" t="n">
-        <v>41.71</v>
+        <v>49.78</v>
       </c>
       <c r="F178" s="4" t="n">
-        <v>39.84</v>
+        <v>50.44</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>ASHOKA</t>
+          <t>LUMAXTECH</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -5250,22 +5490,22 @@
         </is>
       </c>
       <c r="C179" s="4" t="n">
-        <v>128.09</v>
+        <v>1624.9</v>
       </c>
       <c r="D179" s="4" t="n">
-        <v>45.41</v>
+        <v>45.81</v>
       </c>
       <c r="E179" s="4" t="n">
-        <v>40.21</v>
+        <v>53.47</v>
       </c>
       <c r="F179" s="4" t="n">
-        <v>42.78</v>
+        <v>68.36</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>ARVINDFASN</t>
+          <t>INDIAGLYCO</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -5274,22 +5514,22 @@
         </is>
       </c>
       <c r="C180" s="4" t="n">
-        <v>433.4</v>
+        <v>988.2</v>
       </c>
       <c r="D180" s="4" t="n">
-        <v>45.37</v>
+        <v>45.65</v>
       </c>
       <c r="E180" s="4" t="n">
-        <v>45.39</v>
+        <v>52.89</v>
       </c>
       <c r="F180" s="4" t="n">
-        <v>47.3</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>AVANTIFEED</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -5298,22 +5538,22 @@
         </is>
       </c>
       <c r="C181" s="4" t="n">
-        <v>1323.2</v>
+        <v>193.77</v>
       </c>
       <c r="D181" s="4" t="n">
-        <v>45.34</v>
+        <v>45.43</v>
       </c>
       <c r="E181" s="4" t="n">
-        <v>60.18</v>
+        <v>57.76</v>
       </c>
       <c r="F181" s="4" t="n">
-        <v>71.66</v>
+        <v>59.89</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>GATEWAY</t>
+          <t>LMW</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -5322,22 +5562,22 @@
         </is>
       </c>
       <c r="C182" s="4" t="n">
-        <v>56.58</v>
+        <v>14180</v>
       </c>
       <c r="D182" s="4" t="n">
-        <v>45.32</v>
+        <v>45.41</v>
       </c>
       <c r="E182" s="4" t="n">
-        <v>47.8</v>
+        <v>47.35</v>
       </c>
       <c r="F182" s="4" t="n">
-        <v>41.28</v>
+        <v>48.46</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>PARAS</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -5346,22 +5586,22 @@
         </is>
       </c>
       <c r="C183" s="4" t="n">
-        <v>753.4</v>
+        <v>435.35</v>
       </c>
       <c r="D183" s="4" t="n">
-        <v>45.13</v>
+        <v>45.35</v>
       </c>
       <c r="E183" s="4" t="n">
-        <v>53.67</v>
+        <v>47.71</v>
       </c>
       <c r="F183" s="4" t="n">
-        <v>50.6</v>
+        <v>56.56</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>ROUTE</t>
+          <t>CSBBANK</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -5370,22 +5610,22 @@
         </is>
       </c>
       <c r="C184" s="4" t="n">
-        <v>503.55</v>
+        <v>361.25</v>
       </c>
       <c r="D184" s="4" t="n">
-        <v>45.08</v>
+        <v>45.27</v>
       </c>
       <c r="E184" s="4" t="n">
-        <v>37.87</v>
+        <v>43.48</v>
       </c>
       <c r="F184" s="4" t="n">
-        <v>28.86</v>
+        <v>49.92</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>WABAG</t>
+          <t>TEGA</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -5394,22 +5634,22 @@
         </is>
       </c>
       <c r="C185" s="4" t="n">
-        <v>1386.1</v>
+        <v>1603</v>
       </c>
       <c r="D185" s="4" t="n">
-        <v>45.01</v>
+        <v>45.18</v>
       </c>
       <c r="E185" s="4" t="n">
-        <v>53.53</v>
+        <v>38.52</v>
       </c>
       <c r="F185" s="4" t="n">
-        <v>54.13</v>
+        <v>50.54</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>TARC</t>
+          <t>ALIVUS</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -5418,22 +5658,22 @@
         </is>
       </c>
       <c r="C186" s="4" t="n">
-        <v>130.35</v>
+        <v>1039</v>
       </c>
       <c r="D186" s="4" t="n">
-        <v>44.9</v>
+        <v>45.08</v>
       </c>
       <c r="E186" s="4" t="n">
-        <v>42.79</v>
+        <v>57.98</v>
       </c>
       <c r="F186" s="4" t="n">
-        <v>46.35</v>
+        <v>62.62</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>TIMETECHNO</t>
+          <t>PRICOLLTD</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -5442,22 +5682,22 @@
         </is>
       </c>
       <c r="C187" s="4" t="n">
-        <v>178.12</v>
+        <v>556.65</v>
       </c>
       <c r="D187" s="4" t="n">
-        <v>44.79</v>
+        <v>44.8</v>
       </c>
       <c r="E187" s="4" t="n">
-        <v>45.75</v>
+        <v>47.55</v>
       </c>
       <c r="F187" s="4" t="n">
-        <v>50.86</v>
+        <v>56.47</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>RTNPOWER</t>
+          <t>PRUDENT</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -5466,22 +5706,22 @@
         </is>
       </c>
       <c r="C188" s="4" t="n">
-        <v>9.279999999999999</v>
+        <v>2647.8</v>
       </c>
       <c r="D188" s="4" t="n">
-        <v>44.42</v>
+        <v>44.63</v>
       </c>
       <c r="E188" s="4" t="n">
-        <v>48.33</v>
+        <v>53.13</v>
       </c>
       <c r="F188" s="4" t="n">
-        <v>47.08</v>
+        <v>56.31</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>SAFARI</t>
+          <t>GPPL</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -5490,22 +5730,22 @@
         </is>
       </c>
       <c r="C189" s="4" t="n">
-        <v>1458.1</v>
+        <v>152.26</v>
       </c>
       <c r="D189" s="4" t="n">
-        <v>44.41</v>
+        <v>44.36</v>
       </c>
       <c r="E189" s="4" t="n">
-        <v>34.98</v>
+        <v>43.62</v>
       </c>
       <c r="F189" s="4" t="n">
-        <v>39.03</v>
+        <v>49.74</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>EDELWEISS</t>
+          <t>LUXIND</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -5514,22 +5754,22 @@
         </is>
       </c>
       <c r="C190" s="4" t="n">
-        <v>113.39</v>
+        <v>1313.5</v>
       </c>
       <c r="D190" s="4" t="n">
-        <v>44.37</v>
+        <v>44.31</v>
       </c>
       <c r="E190" s="4" t="n">
-        <v>51.14</v>
+        <v>53.99</v>
       </c>
       <c r="F190" s="4" t="n">
-        <v>56.9</v>
+        <v>48.63</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>EIEL</t>
+          <t>ORIENTCEM</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -5538,22 +5778,22 @@
         </is>
       </c>
       <c r="C191" s="4" t="n">
-        <v>193.3</v>
+        <v>136.4</v>
       </c>
       <c r="D191" s="4" t="n">
-        <v>44.3</v>
+        <v>44.21</v>
       </c>
       <c r="E191" s="4" t="n">
-        <v>50.26</v>
+        <v>32.52</v>
       </c>
       <c r="F191" s="4" t="n">
-        <v>40.48</v>
+        <v>35.61</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>KRBL</t>
+          <t>BALUFORGE</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -5562,22 +5802,22 @@
         </is>
       </c>
       <c r="C192" s="4" t="n">
-        <v>338.85</v>
+        <v>475.75</v>
       </c>
       <c r="D192" s="4" t="n">
-        <v>44.2</v>
+        <v>44</v>
       </c>
       <c r="E192" s="4" t="n">
-        <v>46.93</v>
+        <v>45.91</v>
       </c>
       <c r="F192" s="4" t="n">
-        <v>50.3</v>
+        <v>47.42</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>NFL</t>
+          <t>EPL</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -5586,22 +5826,22 @@
         </is>
       </c>
       <c r="C193" s="4" t="n">
-        <v>74.39</v>
+        <v>216</v>
       </c>
       <c r="D193" s="4" t="n">
-        <v>44.08</v>
+        <v>43.72</v>
       </c>
       <c r="E193" s="4" t="n">
-        <v>41.71</v>
+        <v>50.57</v>
       </c>
       <c r="F193" s="4" t="n">
-        <v>44.3</v>
+        <v>51.92</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>GULFOILLUB</t>
+          <t>JKIL</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -5610,22 +5850,22 @@
         </is>
       </c>
       <c r="C194" s="4" t="n">
-        <v>942.25</v>
+        <v>487.2</v>
       </c>
       <c r="D194" s="4" t="n">
-        <v>43.97</v>
+        <v>43.72</v>
       </c>
       <c r="E194" s="4" t="n">
-        <v>38.46</v>
+        <v>39.19</v>
       </c>
       <c r="F194" s="4" t="n">
-        <v>46.38</v>
+        <v>41.37</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>PARKHOTELS</t>
+          <t>CCAVENUE</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -5634,22 +5874,22 @@
         </is>
       </c>
       <c r="C195" s="4" t="n">
-        <v>119.09</v>
+        <v>13.84</v>
       </c>
       <c r="D195" s="4" t="n">
-        <v>43.85</v>
+        <v>43.35</v>
       </c>
       <c r="E195" s="4" t="n">
-        <v>44.64</v>
+        <v>37.65</v>
       </c>
       <c r="F195" s="4" t="n">
-        <v>38.12</v>
+        <v/>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>VOLTAMP</t>
+          <t>KITEX</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -5658,22 +5898,22 @@
         </is>
       </c>
       <c r="C196" s="4" t="n">
-        <v>9501</v>
+        <v>157.86</v>
       </c>
       <c r="D196" s="4" t="n">
-        <v>43.82</v>
+        <v>43.15</v>
       </c>
       <c r="E196" s="4" t="n">
-        <v>54.85</v>
+        <v>42.38</v>
       </c>
       <c r="F196" s="4" t="n">
-        <v>54.3</v>
+        <v>48.55</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>MSTCLTD</t>
+          <t>ELECTCAST</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -5682,22 +5922,22 @@
         </is>
       </c>
       <c r="C197" s="4" t="n">
-        <v>422.25</v>
+        <v>78.13</v>
       </c>
       <c r="D197" s="4" t="n">
-        <v>43.55</v>
+        <v>43.03</v>
       </c>
       <c r="E197" s="4" t="n">
-        <v>44.33</v>
+        <v>47.7</v>
       </c>
       <c r="F197" s="4" t="n">
-        <v>44.85</v>
+        <v>42.92</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>JKIL</t>
+          <t>JAIBALAJI</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -5706,22 +5946,22 @@
         </is>
       </c>
       <c r="C198" s="4" t="n">
-        <v>493.8</v>
+        <v>72.03</v>
       </c>
       <c r="D198" s="4" t="n">
-        <v>43.44</v>
+        <v>42.8</v>
       </c>
       <c r="E198" s="4" t="n">
-        <v>40.33</v>
+        <v>48.18</v>
       </c>
       <c r="F198" s="4" t="n">
-        <v>41.84</v>
+        <v>41.96</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>SUNTECK</t>
+          <t>RALLIS</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -5730,22 +5970,22 @@
         </is>
       </c>
       <c r="C199" s="4" t="n">
-        <v>318</v>
+        <v>252.95</v>
       </c>
       <c r="D199" s="4" t="n">
-        <v>43.35</v>
+        <v>42.77</v>
       </c>
       <c r="E199" s="4" t="n">
-        <v>39.38</v>
+        <v>45.84</v>
       </c>
       <c r="F199" s="4" t="n">
-        <v>41.05</v>
+        <v>47.28</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>PARADEEP</t>
+          <t>INDIASHLTR</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -5754,22 +5994,22 @@
         </is>
       </c>
       <c r="C200" s="4" t="n">
-        <v>120.46</v>
+        <v>784.75</v>
       </c>
       <c r="D200" s="4" t="n">
-        <v>43.28</v>
+        <v>42.66</v>
       </c>
       <c r="E200" s="4" t="n">
-        <v>42.1</v>
+        <v>48.13</v>
       </c>
       <c r="F200" s="4" t="n">
-        <v>48.64</v>
+        <v>51.64</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>CSBBANK</t>
+          <t>TIMETECHNO</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -5778,22 +6018,22 @@
         </is>
       </c>
       <c r="C201" s="4" t="n">
-        <v>358.65</v>
+        <v>174.36</v>
       </c>
       <c r="D201" s="4" t="n">
-        <v>43.18</v>
+        <v>42.64</v>
       </c>
       <c r="E201" s="4" t="n">
-        <v>42.81</v>
+        <v>44.21</v>
       </c>
       <c r="F201" s="4" t="n">
-        <v>49.59</v>
+        <v>50.04</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>JISLJALEQS</t>
+          <t>RTNPOWER</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -5802,22 +6042,22 @@
         </is>
       </c>
       <c r="C202" s="4" t="n">
-        <v>31.12</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="D202" s="4" t="n">
-        <v>43.1</v>
+        <v>42.09</v>
       </c>
       <c r="E202" s="4" t="n">
-        <v>37.39</v>
+        <v>46.9</v>
       </c>
       <c r="F202" s="4" t="n">
-        <v>36.12</v>
+        <v>46.65</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>BALUFORGE</t>
+          <t>JUSTDIAL</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -5826,22 +6066,22 @@
         </is>
       </c>
       <c r="C203" s="4" t="n">
-        <v>478.15</v>
+        <v>520.15</v>
       </c>
       <c r="D203" s="4" t="n">
-        <v>43</v>
+        <v>42.05</v>
       </c>
       <c r="E203" s="4" t="n">
-        <v>46.17</v>
+        <v>33.49</v>
       </c>
       <c r="F203" s="4" t="n">
-        <v>47.53</v>
+        <v>34.44</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>VESUVIUS</t>
+          <t>JAMNAAUTO</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -5850,22 +6090,22 @@
         </is>
       </c>
       <c r="C204" s="4" t="n">
-        <v>477.85</v>
+        <v>114.82</v>
       </c>
       <c r="D204" s="4" t="n">
-        <v>42.96</v>
+        <v>42.05</v>
       </c>
       <c r="E204" s="4" t="n">
-        <v>47.54</v>
+        <v>46.44</v>
       </c>
       <c r="F204" s="4" t="n">
-        <v>52.5</v>
+        <v>52.49</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>KPIGREEN</t>
+          <t>IMAGICAA</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -5874,22 +6114,22 @@
         </is>
       </c>
       <c r="C205" s="4" t="n">
-        <v>420.6</v>
+        <v>42.92</v>
       </c>
       <c r="D205" s="4" t="n">
-        <v>42.95</v>
+        <v>42.01</v>
       </c>
       <c r="E205" s="4" t="n">
-        <v>48.7</v>
+        <v>42.25</v>
       </c>
       <c r="F205" s="4" t="n">
-        <v>50</v>
+        <v>40.54</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>RELAXO</t>
+          <t>SUBROS</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -5898,22 +6138,22 @@
         </is>
       </c>
       <c r="C206" s="4" t="n">
-        <v>288.4</v>
+        <v>725.95</v>
       </c>
       <c r="D206" s="4" t="n">
-        <v>42.91</v>
+        <v>42.01</v>
       </c>
       <c r="E206" s="4" t="n">
-        <v>35.5</v>
+        <v>43.85</v>
       </c>
       <c r="F206" s="4" t="n">
-        <v>26.83</v>
+        <v>50.17</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>ETHOSLTD</t>
+          <t>CIEINDIA</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -5922,22 +6162,22 @@
         </is>
       </c>
       <c r="C207" s="4" t="n">
-        <v>2318.2</v>
+        <v>451.15</v>
       </c>
       <c r="D207" s="4" t="n">
-        <v>42.89</v>
+        <v>41.99</v>
       </c>
       <c r="E207" s="4" t="n">
-        <v>43.97</v>
+        <v>52.09</v>
       </c>
       <c r="F207" s="4" t="n">
-        <v>47.26</v>
+        <v>53.31</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>ORIENTCEM</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -5946,22 +6186,22 @@
         </is>
       </c>
       <c r="C208" s="4" t="n">
-        <v>136.45</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="D208" s="4" t="n">
-        <v>42.73</v>
+        <v>41.94</v>
       </c>
       <c r="E208" s="4" t="n">
-        <v>32.55</v>
+        <v>35.44</v>
       </c>
       <c r="F208" s="4" t="n">
-        <v>35.61</v>
+        <v>36.48</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>GALLANTT</t>
+          <t>GREENPANEL</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -5970,22 +6210,22 @@
         </is>
       </c>
       <c r="C209" s="4" t="n">
-        <v>744.9</v>
+        <v>194.62</v>
       </c>
       <c r="D209" s="4" t="n">
-        <v>42.58</v>
+        <v>41.88</v>
       </c>
       <c r="E209" s="4" t="n">
-        <v>58.59</v>
+        <v>40.65</v>
       </c>
       <c r="F209" s="4" t="n">
-        <v>62.86</v>
+        <v>39.26</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>DBL</t>
+          <t>PATELENG</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -5994,22 +6234,22 @@
         </is>
       </c>
       <c r="C210" s="4" t="n">
-        <v>441.5</v>
+        <v>26.05</v>
       </c>
       <c r="D210" s="4" t="n">
-        <v>42.11</v>
+        <v>41.85</v>
       </c>
       <c r="E210" s="4" t="n">
-        <v>48.18</v>
+        <v>41</v>
       </c>
       <c r="F210" s="4" t="n">
-        <v>49.93</v>
+        <v>36.71</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>WAAREERTL</t>
+          <t>EDELWEISS</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -6018,22 +6258,22 @@
         </is>
       </c>
       <c r="C211" s="4" t="n">
-        <v>942.4</v>
+        <v>110.11</v>
       </c>
       <c r="D211" s="4" t="n">
-        <v>42.06</v>
+        <v>41.81</v>
       </c>
       <c r="E211" s="4" t="n">
-        <v>48.79</v>
+        <v>48.78</v>
       </c>
       <c r="F211" s="4" t="n">
-        <v/>
+        <v>55.43</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>UJJIVANSFB</t>
+          <t>PARKHOTELS</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -6042,22 +6282,22 @@
         </is>
       </c>
       <c r="C212" s="4" t="n">
-        <v>55.83</v>
+        <v>117.5</v>
       </c>
       <c r="D212" s="4" t="n">
-        <v>41.93</v>
+        <v>41.64</v>
       </c>
       <c r="E212" s="4" t="n">
-        <v>49.98</v>
+        <v>43.54</v>
       </c>
       <c r="F212" s="4" t="n">
-        <v>57.51</v>
+        <v>37.67</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>GATEWAY</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -6066,22 +6306,22 @@
         </is>
       </c>
       <c r="C213" s="4" t="n">
-        <v>1111.5</v>
+        <v>55.31</v>
       </c>
       <c r="D213" s="4" t="n">
-        <v>41.81</v>
+        <v>41.62</v>
       </c>
       <c r="E213" s="4" t="n">
-        <v>57.13</v>
+        <v>45.44</v>
       </c>
       <c r="F213" s="4" t="n">
-        <v>64.26000000000001</v>
+        <v>40.31</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>EPL</t>
+          <t>ASHOKA</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -6090,22 +6330,22 @@
         </is>
       </c>
       <c r="C214" s="4" t="n">
-        <v>215.29</v>
+        <v>123.44</v>
       </c>
       <c r="D214" s="4" t="n">
-        <v>41.71</v>
+        <v>41.19</v>
       </c>
       <c r="E214" s="4" t="n">
-        <v>50.28</v>
+        <v>38.16</v>
       </c>
       <c r="F214" s="4" t="n">
-        <v>51.75</v>
+        <v>42.12</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>PRIVISCL</t>
+          <t>NETWORK18</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -6114,22 +6354,22 @@
         </is>
       </c>
       <c r="C215" s="4" t="n">
-        <v>3091.8</v>
+        <v>31.82</v>
       </c>
       <c r="D215" s="4" t="n">
-        <v>41.64</v>
+        <v>41.13</v>
       </c>
       <c r="E215" s="4" t="n">
-        <v>54.08</v>
+        <v>35.71</v>
       </c>
       <c r="F215" s="4" t="n">
-        <v>63.79</v>
+        <v>35.99</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>GHCL</t>
+          <t>VOLTAMP</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -6138,22 +6378,22 @@
         </is>
       </c>
       <c r="C216" s="4" t="n">
-        <v>472.65</v>
+        <v>9134</v>
       </c>
       <c r="D216" s="4" t="n">
-        <v>41.28</v>
+        <v>41</v>
       </c>
       <c r="E216" s="4" t="n">
-        <v>40.8</v>
+        <v>51.97</v>
       </c>
       <c r="F216" s="4" t="n">
-        <v>43.92</v>
+        <v>52.97</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>GPPL</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -6162,22 +6402,22 @@
         </is>
       </c>
       <c r="C217" s="4" t="n">
-        <v>151.05</v>
+        <v>186.96</v>
       </c>
       <c r="D217" s="4" t="n">
-        <v>41.24</v>
+        <v>40.86</v>
       </c>
       <c r="E217" s="4" t="n">
-        <v>42.63</v>
+        <v>48.28</v>
       </c>
       <c r="F217" s="4" t="n">
-        <v>49.38</v>
+        <v>39.49</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>ALLCARGO</t>
+          <t>JISLJALEQS</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -6186,22 +6426,22 @@
         </is>
       </c>
       <c r="C218" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>29.73</v>
       </c>
       <c r="D218" s="4" t="n">
-        <v>41.19</v>
+        <v>40.69</v>
       </c>
       <c r="E218" s="4" t="n">
-        <v>33.82</v>
+        <v>35.3</v>
       </c>
       <c r="F218" s="4" t="n">
-        <v>27.65</v>
+        <v>35.34</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>PATELENG</t>
+          <t>GANECOS</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -6210,22 +6450,22 @@
         </is>
       </c>
       <c r="C219" s="4" t="n">
-        <v>26.26</v>
+        <v>955.6</v>
       </c>
       <c r="D219" s="4" t="n">
-        <v>41.19</v>
+        <v>40.57</v>
       </c>
       <c r="E219" s="4" t="n">
-        <v>41.49</v>
+        <v>49.13</v>
       </c>
       <c r="F219" s="4" t="n">
-        <v>36.88</v>
+        <v>44.19</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>BBL</t>
+          <t>SHAKTIPUMP</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -6234,22 +6474,22 @@
         </is>
       </c>
       <c r="C220" s="4" t="n">
-        <v>2563.8</v>
+        <v>505</v>
       </c>
       <c r="D220" s="4" t="n">
-        <v>41.1</v>
+        <v>40.57</v>
       </c>
       <c r="E220" s="4" t="n">
-        <v>46.69</v>
+        <v>36.99</v>
       </c>
       <c r="F220" s="4" t="n">
-        <v>46.73</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>HERITGFOOD</t>
+          <t>ZAGGLE</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -6258,22 +6498,22 @@
         </is>
       </c>
       <c r="C221" s="4" t="n">
-        <v>330.45</v>
+        <v>215.55</v>
       </c>
       <c r="D221" s="4" t="n">
-        <v>40.63</v>
+        <v>40.33</v>
       </c>
       <c r="E221" s="4" t="n">
-        <v>37.7</v>
+        <v>36.64</v>
       </c>
       <c r="F221" s="4" t="n">
-        <v>43.61</v>
+        <v>40.34</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>NETWORK18</t>
+          <t>VESUVIUS</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -6282,22 +6522,22 @@
         </is>
       </c>
       <c r="C222" s="4" t="n">
-        <v>32.22</v>
+        <v>466.9</v>
       </c>
       <c r="D222" s="4" t="n">
-        <v>40.59</v>
+        <v>40.14</v>
       </c>
       <c r="E222" s="4" t="n">
-        <v>36.43</v>
+        <v>45.22</v>
       </c>
       <c r="F222" s="4" t="n">
-        <v>36.18</v>
+        <v>51.33</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>SHAKTIPUMP</t>
+          <t>HERITGFOOD</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -6306,22 +6546,22 @@
         </is>
       </c>
       <c r="C223" s="4" t="n">
-        <v>508.6</v>
+        <v>326.6</v>
       </c>
       <c r="D223" s="4" t="n">
-        <v>40.56</v>
+        <v>39.8</v>
       </c>
       <c r="E223" s="4" t="n">
-        <v>37.34</v>
+        <v>36.91</v>
       </c>
       <c r="F223" s="4" t="n">
-        <v>44.26</v>
+        <v>43.28</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>AWFIS</t>
+          <t>SHRIPISTON</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -6330,22 +6570,22 @@
         </is>
       </c>
       <c r="C224" s="4" t="n">
-        <v>317.9</v>
+        <v>3253.6</v>
       </c>
       <c r="D224" s="4" t="n">
-        <v>40.51</v>
+        <v>39.49</v>
       </c>
       <c r="E224" s="4" t="n">
-        <v>38.87</v>
+        <v>53.33</v>
       </c>
       <c r="F224" s="4" t="n">
-        <v>33.09</v>
+        <v>65.95</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>IFBIND</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -6354,22 +6594,22 @@
         </is>
       </c>
       <c r="C225" s="4" t="n">
-        <v>431.45</v>
+        <v>1049.1</v>
       </c>
       <c r="D225" s="4" t="n">
-        <v>40.34</v>
+        <v>38.98</v>
       </c>
       <c r="E225" s="4" t="n">
-        <v>46.63</v>
+        <v>37.65</v>
       </c>
       <c r="F225" s="4" t="n">
-        <v>56.16</v>
+        <v>44.24</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>JUSTDIAL</t>
+          <t>ALLCARGO</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -6378,22 +6618,22 @@
         </is>
       </c>
       <c r="C226" s="4" t="n">
-        <v>521.35</v>
+        <v>8.6</v>
       </c>
       <c r="D226" s="4" t="n">
-        <v>40.22</v>
+        <v>38.82</v>
       </c>
       <c r="E226" s="4" t="n">
-        <v>33.63</v>
+        <v>33.27</v>
       </c>
       <c r="F226" s="4" t="n">
-        <v>34.49</v>
+        <v>27.55</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>DODLA</t>
+          <t>GALLANTT</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -6402,22 +6642,22 @@
         </is>
       </c>
       <c r="C227" s="4" t="n">
-        <v>1025.6</v>
+        <v>690</v>
       </c>
       <c r="D227" s="4" t="n">
-        <v>40.1</v>
+        <v>38.78</v>
       </c>
       <c r="E227" s="4" t="n">
-        <v>37.35</v>
+        <v>53.43</v>
       </c>
       <c r="F227" s="4" t="n">
-        <v>46.72</v>
+        <v>59.89</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>STARCEMENT</t>
+          <t>OSWALPUMPS</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -6426,22 +6666,22 @@
         </is>
       </c>
       <c r="C228" s="4" t="n">
-        <v>215.12</v>
+        <v>358.3</v>
       </c>
       <c r="D228" s="4" t="n">
-        <v>39.93</v>
+        <v>38.58</v>
       </c>
       <c r="E228" s="4" t="n">
-        <v>45.94</v>
+        <v>38.61</v>
       </c>
       <c r="F228" s="4" t="n">
-        <v>51.15</v>
+        <v/>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>JAMNAAUTO</t>
+          <t>DBL</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -6450,22 +6690,22 @@
         </is>
       </c>
       <c r="C229" s="4" t="n">
-        <v>116.19</v>
+        <v>429.9</v>
       </c>
       <c r="D229" s="4" t="n">
-        <v>39.53</v>
+        <v>38.37</v>
       </c>
       <c r="E229" s="4" t="n">
-        <v>47.23</v>
+        <v>46.12</v>
       </c>
       <c r="F229" s="4" t="n">
-        <v>52.98</v>
+        <v>48.68</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>SHARDACROP</t>
+          <t>PCJEWELLER</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -6474,22 +6714,22 @@
         </is>
       </c>
       <c r="C230" s="4" t="n">
-        <v>969</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="D230" s="4" t="n">
-        <v>39.53</v>
+        <v>38.17</v>
       </c>
       <c r="E230" s="4" t="n">
-        <v>48.87</v>
+        <v>38.17</v>
       </c>
       <c r="F230" s="4" t="n">
-        <v>56.29</v>
+        <v>45.36</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>KITEX</t>
+          <t>EUREKAFORB</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -6498,22 +6738,22 @@
         </is>
       </c>
       <c r="C231" s="4" t="n">
-        <v>156.75</v>
+        <v>464.45</v>
       </c>
       <c r="D231" s="4" t="n">
-        <v>39.41</v>
+        <v>38.02</v>
       </c>
       <c r="E231" s="4" t="n">
-        <v>41.86</v>
+        <v>40.11</v>
       </c>
       <c r="F231" s="4" t="n">
-        <v>48.38</v>
+        <v>41.49</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>TEGA</t>
+          <t>JKLAKSHMI</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -6522,22 +6762,22 @@
         </is>
       </c>
       <c r="C232" s="4" t="n">
-        <v>1585.3</v>
+        <v>611.5</v>
       </c>
       <c r="D232" s="4" t="n">
-        <v>39.34</v>
+        <v>37.63</v>
       </c>
       <c r="E232" s="4" t="n">
-        <v>36.73</v>
+        <v>37.11</v>
       </c>
       <c r="F232" s="4" t="n">
-        <v>49.94</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>GREENPANEL</t>
+          <t>GULFOILLUB</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -6546,22 +6786,22 @@
         </is>
       </c>
       <c r="C233" s="4" t="n">
-        <v>202.67</v>
+        <v>901.5</v>
       </c>
       <c r="D233" s="4" t="n">
-        <v>39.31</v>
+        <v>37.23</v>
       </c>
       <c r="E233" s="4" t="n">
-        <v>42.95</v>
+        <v>34.92</v>
       </c>
       <c r="F233" s="4" t="n">
-        <v>40.1</v>
+        <v>44.55</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>IMAGICAA</t>
+          <t>TRANSRAILL</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -6570,22 +6810,22 @@
         </is>
       </c>
       <c r="C234" s="4" t="n">
-        <v>43.22</v>
+        <v>507.25</v>
       </c>
       <c r="D234" s="4" t="n">
-        <v>39.24</v>
+        <v>36.49</v>
       </c>
       <c r="E234" s="4" t="n">
-        <v>42.7</v>
+        <v>42.25</v>
       </c>
       <c r="F234" s="4" t="n">
-        <v>40.73</v>
+        <v>45.01</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>SAMHI</t>
+          <t>SHARDACROP</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -6594,22 +6834,22 @@
         </is>
       </c>
       <c r="C235" s="4" t="n">
-        <v>146.59</v>
+        <v>893.1</v>
       </c>
       <c r="D235" s="4" t="n">
-        <v>38.74</v>
+        <v>36.02</v>
       </c>
       <c r="E235" s="4" t="n">
-        <v>38.29</v>
+        <v>44.75</v>
       </c>
       <c r="F235" s="4" t="n">
-        <v>42.51</v>
+        <v>53.72</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>AHLUCONT</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -6618,22 +6858,22 @@
         </is>
       </c>
       <c r="C236" s="4" t="n">
-        <v>794.3</v>
+        <v>534.9</v>
       </c>
       <c r="D236" s="4" t="n">
-        <v>38.67</v>
+        <v>35.17</v>
       </c>
       <c r="E236" s="4" t="n">
-        <v>44.61</v>
+        <v>40.62</v>
       </c>
       <c r="F236" s="4" t="n">
-        <v>46.52</v>
+        <v>43.58</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>MASTEK</t>
+          <t>BECTORFOOD</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -6642,22 +6882,22 @@
         </is>
       </c>
       <c r="C237" s="4" t="n">
-        <v>1549.9</v>
+        <v>177.78</v>
       </c>
       <c r="D237" s="4" t="n">
-        <v>38.37</v>
+        <v>34.75</v>
       </c>
       <c r="E237" s="4" t="n">
-        <v>35.27</v>
+        <v>31.81</v>
       </c>
       <c r="F237" s="4" t="n">
-        <v>38.48</v>
+        <v>38.16</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>CCAVENUE</t>
+          <t>RENUKA</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -6666,22 +6906,22 @@
         </is>
       </c>
       <c r="C238" s="4" t="n">
-        <v>13.68</v>
+        <v>23.85</v>
       </c>
       <c r="D238" s="4" t="n">
-        <v>38.2</v>
+        <v>34.06</v>
       </c>
       <c r="E238" s="4" t="n">
-        <v>36.05</v>
+        <v>40.2</v>
       </c>
       <c r="F238" s="4" t="n">
-        <v/>
+        <v>37.84</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>BLACKBUCK</t>
+          <t>SUNTECK</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
@@ -6690,22 +6930,22 @@
         </is>
       </c>
       <c r="C239" s="4" t="n">
-        <v>530.7</v>
+        <v>288.2</v>
       </c>
       <c r="D239" s="4" t="n">
-        <v>37.89</v>
+        <v>33.85</v>
       </c>
       <c r="E239" s="4" t="n">
-        <v>43.06</v>
+        <v>34.74</v>
       </c>
       <c r="F239" s="4" t="n">
-        <v>49.53</v>
+        <v>38.83</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>MANORAMA</t>
+          <t>RAYMONDLSL</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -6714,22 +6954,22 @@
         </is>
       </c>
       <c r="C240" s="4" t="n">
-        <v>1305.6</v>
+        <v>712.55</v>
       </c>
       <c r="D240" s="4" t="n">
-        <v>37.78</v>
+        <v>33.77</v>
       </c>
       <c r="E240" s="4" t="n">
-        <v>47.2</v>
+        <v>32.92</v>
       </c>
       <c r="F240" s="4" t="n">
-        <v>56.39</v>
+        <v>21.34</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>GHCL</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
@@ -6738,22 +6978,22 @@
         </is>
       </c>
       <c r="C241" s="4" t="n">
-        <v>3594.2</v>
+        <v>445.2</v>
       </c>
       <c r="D241" s="4" t="n">
-        <v>37.77</v>
+        <v>33.75</v>
       </c>
       <c r="E241" s="4" t="n">
-        <v>51.95</v>
+        <v>36.23</v>
       </c>
       <c r="F241" s="4" t="n">
-        <v>65.93000000000001</v>
+        <v>42.07</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>ZAGGLE</t>
+          <t>SYMPHONY</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -6762,22 +7002,22 @@
         </is>
       </c>
       <c r="C242" s="4" t="n">
-        <v>210.62</v>
+        <v>710.95</v>
       </c>
       <c r="D242" s="4" t="n">
-        <v>37.45</v>
+        <v>33.49</v>
       </c>
       <c r="E242" s="4" t="n">
-        <v>35.21</v>
+        <v>37.47</v>
       </c>
       <c r="F242" s="4" t="n">
-        <v>39.98</v>
+        <v>38.86</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>BECTORFOOD</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -6786,22 +7026,22 @@
         </is>
       </c>
       <c r="C243" s="4" t="n">
-        <v>181.83</v>
+        <v>1051.3</v>
       </c>
       <c r="D243" s="4" t="n">
-        <v>36.85</v>
+        <v>33.42</v>
       </c>
       <c r="E243" s="4" t="n">
-        <v>33.15</v>
+        <v>51.86</v>
       </c>
       <c r="F243" s="4" t="n">
-        <v>38.74</v>
+        <v>59.61</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>CELLO</t>
+          <t>UJJIVANSFB</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -6810,22 +7050,22 @@
         </is>
       </c>
       <c r="C244" s="4" t="n">
-        <v>397</v>
+        <v>52.49</v>
       </c>
       <c r="D244" s="4" t="n">
-        <v>36.49</v>
+        <v>33.21</v>
       </c>
       <c r="E244" s="4" t="n">
-        <v>32.14</v>
+        <v>45.37</v>
       </c>
       <c r="F244" s="4" t="n">
-        <v>30.71</v>
+        <v>54.48</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>PNGJL</t>
+          <t>CELLO</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
@@ -6834,22 +7074,22 @@
         </is>
       </c>
       <c r="C245" s="4" t="n">
-        <v>573.9</v>
+        <v>382.25</v>
       </c>
       <c r="D245" s="4" t="n">
-        <v>35.02</v>
+        <v>31.89</v>
       </c>
       <c r="E245" s="4" t="n">
-        <v>45.82</v>
+        <v>30</v>
       </c>
       <c r="F245" s="4" t="n">
-        <v>44.7</v>
+        <v>29.94</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>TRANSRAILL</t>
+          <t>PRSMJOHNSN</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -6858,22 +7098,22 @@
         </is>
       </c>
       <c r="C246" s="4" t="n">
-        <v>513.35</v>
+        <v>118.8</v>
       </c>
       <c r="D246" s="4" t="n">
-        <v>34.46</v>
+        <v>31.45</v>
       </c>
       <c r="E246" s="4" t="n">
-        <v>42.95</v>
+        <v>37.7</v>
       </c>
       <c r="F246" s="4" t="n">
-        <v>45.4</v>
+        <v>41.73</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>AURIONPRO</t>
+          <t>BLACKBUCK</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
@@ -6882,22 +7122,22 @@
         </is>
       </c>
       <c r="C247" s="4" t="n">
-        <v>750.9</v>
+        <v>500.2</v>
       </c>
       <c r="D247" s="4" t="n">
-        <v>33.56</v>
+        <v>31.22</v>
       </c>
       <c r="E247" s="4" t="n">
-        <v>35.15</v>
+        <v>40.14</v>
       </c>
       <c r="F247" s="4" t="n">
-        <v>39.29</v>
+        <v>45.78</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>PCJEWELLER</t>
+          <t>PNGJL</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -6906,22 +7146,22 @@
         </is>
       </c>
       <c r="C248" s="4" t="n">
-        <v>8.359999999999999</v>
+        <v>525.7</v>
       </c>
       <c r="D248" s="4" t="n">
-        <v>33.03</v>
+        <v>29.77</v>
       </c>
       <c r="E248" s="4" t="n">
-        <v>38.07</v>
+        <v>40.87</v>
       </c>
       <c r="F248" s="4" t="n">
-        <v>45.34</v>
+        <v>40.21</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>GMMPFAUDLR</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
@@ -6930,22 +7170,22 @@
         </is>
       </c>
       <c r="C249" s="4" t="n">
-        <v>537.4</v>
+        <v>807.1</v>
       </c>
       <c r="D249" s="4" t="n">
-        <v>31.47</v>
+        <v>29.35</v>
       </c>
       <c r="E249" s="4" t="n">
-        <v>40.98</v>
+        <v>31.23</v>
       </c>
       <c r="F249" s="4" t="n">
-        <v>43.77</v>
+        <v>38.47</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>RENUKA</t>
+          <t>BAJAJELEC</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
@@ -6954,16 +7194,16 @@
         </is>
       </c>
       <c r="C250" s="4" t="n">
-        <v>24.2</v>
+        <v>336.05</v>
       </c>
       <c r="D250" s="4" t="n">
-        <v>29.63</v>
+        <v>28.68</v>
       </c>
       <c r="E250" s="4" t="n">
-        <v>41.16</v>
+        <v>31.2</v>
       </c>
       <c r="F250" s="4" t="n">
-        <v>38.18</v>
+        <v>28.53</v>
       </c>
     </row>
     <row r="251">
@@ -6978,16 +7218,16 @@
         </is>
       </c>
       <c r="C251" s="4" t="n">
-        <v>3217.9</v>
+        <v>3163.2</v>
       </c>
       <c r="D251" s="4" t="n">
-        <v>28.34</v>
+        <v>27.77</v>
       </c>
       <c r="E251" s="4" t="n">
-        <v>27.02</v>
+        <v>25.93</v>
       </c>
       <c r="F251" s="4" t="n">
-        <v>29.66</v>
+        <v>29.31</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Micro250_stocks.xlsx
+++ b/reports/Micro250_stocks.xlsx
@@ -567,7 +567,7 @@
         <v>183.44</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>6428792</v>
+        <v>6428806</v>
       </c>
       <c r="K2" s="4" t="n">
         <v>21536</v>
@@ -606,7 +606,7 @@
         <v>1933.92</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>340211</v>
+        <v>340214</v>
       </c>
       <c r="K3" s="4" t="n">
         <v>17788</v>
@@ -684,7 +684,7 @@
         <v>3540.42</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>1522731</v>
+        <v>1522738</v>
       </c>
       <c r="K5" s="4" t="n">
         <v>24840</v>
@@ -723,7 +723,7 @@
         <v>934.16</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>373720</v>
+        <v>373721</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>10629</v>
@@ -762,7 +762,7 @@
         <v>697.35</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>483591</v>
+        <v>483597</v>
       </c>
       <c r="K7" s="4" t="n">
         <v>8307</v>
@@ -879,7 +879,7 @@
         <v>995.7</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>379596</v>
+        <v>379610</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>11155</v>
@@ -918,7 +918,7 @@
         <v>3859.81</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>151828</v>
+        <v>151829</v>
       </c>
       <c r="K11" s="4" t="n">
         <v>12437</v>
@@ -957,7 +957,7 @@
         <v>2159.04</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>531436</v>
+        <v>531437</v>
       </c>
       <c r="K12" s="4" t="n">
         <v>12397</v>
@@ -996,7 +996,7 @@
         <v>133.61</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1170635</v>
+        <v>1170638</v>
       </c>
       <c r="K13" s="4" t="n">
         <v>7497</v>
@@ -1035,7 +1035,7 @@
         <v>1213.33</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>338416</v>
+        <v>338425</v>
       </c>
       <c r="K14" s="4" t="n">
         <v>15553</v>
@@ -1074,7 +1074,7 @@
         <v>213</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>3249038</v>
+        <v>3249117</v>
       </c>
       <c r="K15" s="4" t="n">
         <v>10003</v>
@@ -1113,7 +1113,7 @@
         <v>287.34</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>734013</v>
+        <v>734024</v>
       </c>
       <c r="K16" s="4" t="n">
         <v>5985</v>
@@ -1152,7 +1152,7 @@
         <v>1709.9</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>584364</v>
+        <v>584401</v>
       </c>
       <c r="K17" s="4" t="n">
         <v>13172</v>

--- a/reports/Micro250_stocks.xlsx
+++ b/reports/Micro250_stocks.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -546,37 +546,37 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>441.15</v>
+        <v>536.15</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>81.41</v>
+        <v>89.34</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>93.23</v>
+        <v>95.06</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>86.44</v>
+        <v>88.95</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>34.82</v>
+        <v>46.37</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>202.48</v>
+        <v>221.78</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>183.44</v>
+        <v>198.93</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>6428806</v>
+        <v>4720429</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>21536</v>
+        <v>26173</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>SANSERA</t>
+          <t>ASTRAMICRO</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -585,37 +585,37 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>2853.8</v>
+        <v>1401.7</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>75.38</v>
+        <v>81.22</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>73.15000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>76.56</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>37.62</v>
+        <v>33.4</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>2041.39</v>
+        <v>1032.83</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>1933.92</v>
+        <v>1014.04</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>340214</v>
+        <v>959225</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>17788</v>
+        <v>13308</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ARVIND</t>
+          <t>GRWRHITECH</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -624,37 +624,37 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>480.35</v>
+        <v>6117.9</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>73.67</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>76.41</v>
+        <v>76.63</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>69.97</v>
+        <v>66.2</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>21.12</v>
+        <v>24.82</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>365.95</v>
+        <v>4076.39</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>359.38</v>
+        <v>3955.22</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>1126904</v>
+        <v>156507</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>12591</v>
+        <v>14213</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>MTARTECH</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -663,37 +663,37 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>8075.5</v>
+        <v>1520.5</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>73.51000000000001</v>
+        <v>72.81</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>92.06999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>88.06999999999999</v>
+        <v>72.33</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>32.3</v>
+        <v>24.57</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>3923.62</v>
+        <v>1053.96</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>3540.42</v>
+        <v>1017.89</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>1522738</v>
+        <v>708369</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>24840</v>
+        <v>10155</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>STAR</t>
+          <t>SHAILY</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -702,37 +702,37 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1153.2</v>
+        <v>2989.5</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>68.55</v>
+        <v>72.06</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>71.41</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>62.64</v>
+        <v>71.93000000000001</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>29.14</v>
+        <v>43.82</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>951.6900000000001</v>
+        <v>2257.38</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>934.16</v>
+        <v>2187.66</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>373721</v>
+        <v>471763</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>10629</v>
+        <v>13750</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>YATHARTH</t>
+          <t>MTARTECH</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -741,37 +741,37 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>862.15</v>
+        <v>7879.5</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>65.48</v>
+        <v>69.56</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>64.23</v>
+        <v>88.26000000000001</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>64.7</v>
+        <v>87.75</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>21.82</v>
+        <v>47.37</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>714.45</v>
+        <v>4179.5</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>697.35</v>
+        <v>3750.87</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>483597</v>
+        <v>1540753</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>8307</v>
+        <v>24237</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>V2RETAIL</t>
+          <t>SANSERA</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -780,37 +780,37 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>233.33</v>
+        <v>2861</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>64.56999999999999</v>
+        <v>68.2</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>62.46</v>
+        <v>73.27</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>67.76000000000001</v>
+        <v>76.62</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>20.37</v>
+        <v>28.03</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>205.07</v>
+        <v>2097.1</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>201.52</v>
+        <v>1981.15</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1414573</v>
+        <v>325488</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>8508</v>
+        <v>17833</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>SUNFLAG</t>
+          <t>MIDHANI</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -819,37 +819,37 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>377.25</v>
+        <v>420.65</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>63.6</v>
+        <v>62.05</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>69.13</v>
+        <v>63.7</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>66.3</v>
+        <v>56.13</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>33.76</v>
+        <v>32.18</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>275.12</v>
+        <v>363.94</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>270.66</v>
+        <v>363.14</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1425999</v>
+        <v>1326897</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>6799</v>
+        <v>7880</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ASTRAMICRO</t>
+          <t>SUNFLAG</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -858,37 +858,37 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1174.9</v>
+        <v>373.75</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>63.59</v>
+        <v>58.01</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>64.26000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>65.20999999999999</v>
+        <v>66.03</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>50.64</v>
+        <v>28.61</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1010.23</v>
+        <v>282.38</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>995.7</v>
+        <v>276.27</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>379610</v>
+        <v>1430405</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>11155</v>
+        <v>6736</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>GRWRHITECH</t>
+          <t>ZYDUSWELL</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -897,37 +897,37 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>5353.4</v>
+        <v>507.05</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>63.2</v>
+        <v>56.45</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>70.98999999999999</v>
+        <v>61.4</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>63.09</v>
+        <v>62.68</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>26.89</v>
+        <v>27.73</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>3957.29</v>
+        <v>454.23</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3859.81</v>
+        <v>446.36</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>151829</v>
+        <v>584585</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>12437</v>
+        <v>16132</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SHAILY</t>
+          <t>CEIGALL</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -936,37 +936,37 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2695.2</v>
+        <v>347.15</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>62.01</v>
+        <v>56.22</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>62.7</v>
+        <v>66.37</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>68.97</v>
+        <v>63.14</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>36.77</v>
+        <v>20.13</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2223.36</v>
+        <v>293.56</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>2159.04</v>
+        <v>289.67</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>531437</v>
+        <v>781161</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>12397</v>
+        <v>6048</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>GAEL</t>
+          <t>ADVENZYMES</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -975,37 +975,37 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>163.44</v>
+        <v>364</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>59.61</v>
+        <v>54.73</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>67.45999999999999</v>
+        <v>64.5</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>64.62</v>
+        <v>55.87</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>23.66</v>
+        <v>21.44</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>137.34</v>
+        <v>317.85</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>133.61</v>
+        <v>317.48</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1170638</v>
+        <v>573927</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>7497</v>
+        <v>4076</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>ANURAS</t>
+          <t>STAR</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1014,148 +1014,31 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1366.1</v>
+        <v>1111.8</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>58.96</v>
+        <v>50.57</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>64.75</v>
+        <v>65.16</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>70.58</v>
+        <v>61.3</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>25.6</v>
+        <v>36.54</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1250.4</v>
+        <v>962.2</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1213.33</v>
+        <v>942.48</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>338425</v>
+        <v>378206</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>15553</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>KTKBANK</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>264.5</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>58.93</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>68.45</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>66.59999999999999</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>25.51</v>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>218.8</v>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>213</v>
-      </c>
-      <c r="J15" s="4" t="n">
-        <v>3249117</v>
-      </c>
-      <c r="K15" s="4" t="n">
-        <v>10003</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>CEIGALL</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>343.55</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>55.77</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>65.56999999999999</v>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>62.38</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>28.17</v>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>290.58</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>287.34</v>
-      </c>
-      <c r="J16" s="4" t="n">
-        <v>734024</v>
-      </c>
-      <c r="K16" s="4" t="n">
-        <v>5985</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>AZAD</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>2039.6</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>51.51</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>60.91</v>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v>61.32</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>26.67</v>
-      </c>
-      <c r="H17" s="4" t="n">
-        <v>1743.05</v>
-      </c>
-      <c r="I17" s="4" t="n">
-        <v>1709.9</v>
-      </c>
-      <c r="J17" s="4" t="n">
-        <v>584401</v>
-      </c>
-      <c r="K17" s="4" t="n">
-        <v>13172</v>
+        <v>10248</v>
       </c>
     </row>
   </sheetData>
@@ -1173,9 +1056,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1242,22 +1122,22 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>441.15</v>
+        <v>536.15</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>81.41</v>
+        <v>89.34</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>93.23</v>
+        <v>95.06</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>86.44</v>
+        <v>88.95</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>SPARC</t>
+          <t>SUPRIYA</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -1266,22 +1146,22 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>209.77</v>
+        <v>968.7</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>77.76000000000001</v>
+        <v>87.2</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>73.56</v>
+        <v>79.01000000000001</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>57.05</v>
+        <v>67.98</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>SANSERA</t>
+          <t>REFEX</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -1290,22 +1170,22 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>2853.8</v>
+        <v>328.3</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>75.38</v>
+        <v>81.23</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>73.15000000000001</v>
+        <v>66.18000000000001</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>76.56</v>
+        <v>53.25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>ASTRAMICRO</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -1314,22 +1194,22 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1473</v>
+        <v>1401.7</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>74.83</v>
+        <v>81.22</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>70.77</v>
+        <v>74.8</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>71.48</v>
+        <v>71.20999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>BALAMINES</t>
+          <t>ORCHPHARMA</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -1338,22 +1218,22 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1822.5</v>
+        <v>792.5</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>74.77</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>79.26000000000001</v>
+        <v>63.34</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>54.61</v>
+        <v>49.65</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>SHILPAMED</t>
+          <t>RELAXO</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1362,22 +1242,22 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>490.25</v>
+        <v>345.3</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>74.42</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>74.01000000000001</v>
+        <v>51.41</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>65.94</v>
+        <v>33.62</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ARVIND</t>
+          <t>RAIN</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1386,22 +1266,22 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>480.35</v>
+        <v>188.07</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>73.67</v>
+        <v>76.44</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>76.41</v>
+        <v>70.45</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>69.97</v>
+        <v>58.28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MTARTECH</t>
+          <t>SKIPPER</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -1410,22 +1290,22 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>8075.5</v>
+        <v>549.35</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>73.51000000000001</v>
+        <v>75.72</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>92.06999999999999</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>88.06999999999999</v>
+        <v>62.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>SUPRIYA</t>
+          <t>CEMPRO</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1434,16 +1314,16 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>774.1</v>
+        <v>1071.15</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>73.36</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>65.51000000000001</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>60.24</v>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -1458,22 +1338,22 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>714.45</v>
+        <v>746.45</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>70.98999999999999</v>
+        <v>74.67</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>66.84999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>57.58</v>
+        <v>59.02</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENGG</t>
+          <t>GRWRHITECH</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1482,22 +1362,22 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>69.37</v>
+        <v>6117.9</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>70.42</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>67.03</v>
+        <v>76.63</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>56.21</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>DIACABS</t>
+          <t>MARKSANS</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1506,22 +1386,22 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>193.5</v>
+        <v>246.19</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>69.73</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>73.84</v>
+        <v>75.02</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>66.04000000000001</v>
+        <v>59.28</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>TIPSMUSIC</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1530,22 +1410,22 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>681.05</v>
+        <v>1520.5</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>69.67</v>
+        <v>72.81</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>68.23</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>61.35</v>
+        <v>72.33</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>SFL</t>
+          <t>ACUTAAS</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1554,22 +1434,22 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>638.5</v>
+        <v>3132.5</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>69.53</v>
+        <v>72.36</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>60.82</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>44.26</v>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>ENTERO</t>
+          <t>SHAILY</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1578,22 +1458,22 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1354.4</v>
+        <v>2989.5</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>69.33</v>
+        <v>72.06</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>63.53</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>59.51</v>
+        <v>71.93000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>STAR</t>
+          <t>AJAXENGG</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1602,22 +1482,22 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1153.2</v>
+        <v>590</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>68.55</v>
+        <v>70.41</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>71.41</v>
+        <v>58.65</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>62.64</v>
+        <v>50.69</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>SUDARSCHEM</t>
+          <t>THYROCARE</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1626,22 +1506,22 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1013</v>
+        <v>506.3</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>68.28</v>
+        <v>70.25</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>56.81</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>52.54</v>
+        <v>64.75</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>ACUTAAS</t>
+          <t>MTARTECH</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1650,22 +1530,22 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>2951.2</v>
+        <v>7879.5</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>68.27</v>
+        <v>69.56</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>74.59999999999999</v>
+        <v>88.26000000000001</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v/>
+        <v>87.75</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>KIRLPNU</t>
+          <t>VIYASH</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1674,22 +1554,22 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1607.3</v>
+        <v>261.94</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>67.95999999999999</v>
+        <v>69</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>77.81</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>64.81999999999999</v>
+        <v>64.92</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>INDIGOPNTS</t>
+          <t>SKYGOLD</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1698,22 +1578,22 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1003.4</v>
+        <v>521</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>67.89</v>
+        <v>68.97</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>53.81</v>
+        <v>66.42</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>45.05</v>
+        <v>70.76000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>DHANUKA</t>
+          <t>SHILPAMED</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1722,22 +1602,22 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1172.3</v>
+        <v>498.95</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>67.59</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>54.83</v>
+        <v>74.97</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>47.37</v>
+        <v>66.54000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>VIYASH</t>
+          <t>SANSERA</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1746,22 +1626,22 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>246.06</v>
+        <v>2861</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>67.19</v>
+        <v>68.2</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>76.33</v>
+        <v>73.27</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v/>
+        <v>76.62</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>NEOGEN</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1770,22 +1650,22 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1295</v>
+        <v>1858.1</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>66.18000000000001</v>
+        <v>68.13</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>79.43000000000001</v>
+        <v>66.92</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>84.40000000000001</v>
+        <v>57.36</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>REFEX</t>
+          <t>JINDWORLD</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1794,22 +1674,22 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>279.05</v>
+        <v>30.25</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>65.84</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>55.15</v>
+        <v>55.27</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>48.66</v>
+        <v>39.46</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>RAIN</t>
+          <t>IFBIND</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1818,22 +1698,22 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>156.32</v>
+        <v>1252.5</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>65.62</v>
+        <v>66.34</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>60.91</v>
+        <v>51.49</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>52.71</v>
+        <v>48.26</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>YATHARTH</t>
+          <t>BANCOINDIA</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1842,22 +1722,22 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>862.15</v>
+        <v>656.25</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>65.48</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>64.23</v>
+        <v>55.31</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>64.7</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>HCG</t>
+          <t>SPARC</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1866,22 +1746,22 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>654.3</v>
+        <v>212.11</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>65.47</v>
+        <v>65.95999999999999</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>61.97</v>
+        <v>74</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>61.25</v>
+        <v>57.39</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>AJAXENGG</t>
+          <t>MAXESTATES</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1890,22 +1770,22 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>569.95</v>
+        <v>444</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>65.22</v>
+        <v>65.88</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>55.94</v>
+        <v>58.39</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>48.59</v>
+        <v>51.71</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>RELIGARE</t>
+          <t>TEGA</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1914,22 +1794,22 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>240.32</v>
+        <v>1766</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>65.20999999999999</v>
+        <v>65.7</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>56.04</v>
+        <v>52.03</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>52.5</v>
+        <v>55.86</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GABRIEL</t>
+          <t>ICIL</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1938,22 +1818,22 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1120</v>
+        <v>312.1</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>65.15000000000001</v>
+        <v>65.7</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>59.48</v>
+        <v>58.67</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>65.01000000000001</v>
+        <v>54.35</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>MAXESTATES</t>
+          <t>LLOYDSENGG</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1962,22 +1842,22 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>428.95</v>
+        <v>73.61</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>64.75</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>55.32</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>50.45</v>
+        <v>58.18</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>V2RETAIL</t>
+          <t>RBA</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1986,22 +1866,22 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>233.33</v>
+        <v>68.66</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>64.56999999999999</v>
+        <v>65.58</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>62.46</v>
+        <v>56.83</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>67.76000000000001</v>
+        <v>41.51</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>CYIENTDLM</t>
+          <t>LMW</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -2010,22 +1890,22 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>418.3</v>
+        <v>15709</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>64.45999999999999</v>
+        <v>64.91</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>58.66</v>
+        <v>58.29</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>44.52</v>
+        <v>53.52</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>ORCHPHARMA</t>
+          <t>GREAVESCOT</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -2034,22 +1914,22 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>706.5</v>
+        <v>181.65</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>64.34</v>
+        <v>64.81</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>55.48</v>
+        <v>56.44</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>46.82</v>
+        <v>50.49</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -2058,22 +1938,22 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>211.86</v>
+        <v>4204.9</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>64.29000000000001</v>
+        <v>64.77</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>65.12</v>
+        <v>59.98</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>54.47</v>
+        <v>74.61</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>SUNFLAG</t>
+          <t>WABAG</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -2082,22 +1962,22 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>377.25</v>
+        <v>1527.8</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>63.6</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>69.13</v>
+        <v>62.29</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>66.3</v>
+        <v>58.42</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>ASTRAMICRO</t>
+          <t>PCJEWELLER</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -2106,22 +1986,22 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>1174.9</v>
+        <v>9.6</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>63.59</v>
+        <v>64.39</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>64.26000000000001</v>
+        <v>48.87</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>65.20999999999999</v>
+        <v>48.52</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>RBA</t>
+          <t>TDPOWERSYS</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -2130,22 +2010,22 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>67.7</v>
+        <v>1318.6</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>63.42</v>
+        <v>63.86</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>54.73</v>
+        <v>80.15000000000001</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>40.7</v>
+        <v>84.75</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>INGERRAND</t>
+          <t>BALAMINES</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -2154,22 +2034,22 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>4477.1</v>
+        <v>1775.6</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>63.22</v>
+        <v>63.81</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>65.28</v>
+        <v>75.41</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>62.15</v>
+        <v>53.77</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GRWRHITECH</t>
+          <t>ARVIND</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -2178,22 +2058,22 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>5353.4</v>
+        <v>473.35</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>63.2</v>
+        <v>63.59</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>70.98999999999999</v>
+        <v>73.87</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>63.09</v>
+        <v>69.45999999999999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>ADVENZYMES</t>
+          <t>JSFB</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -2202,22 +2082,22 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>375.15</v>
+        <v>495.25</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>62.97</v>
+        <v>63</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>68.90000000000001</v>
+        <v>63.88</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>57.18</v>
+        <v>55.22</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>TEAMLEASE</t>
+          <t>INDIGOPNTS</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -2226,22 +2106,22 @@
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>1382.2</v>
+        <v>990.9</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>62.66</v>
+        <v>62.9</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>49.39</v>
+        <v>52.53</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>36.18</v>
+        <v>44.62</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>SHAILY</t>
+          <t>FDC</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -2250,22 +2130,22 @@
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>2695.2</v>
+        <v>405</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>62.01</v>
+        <v>62.47</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>62.7</v>
+        <v>58.01</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>68.97</v>
+        <v>49.89</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>KANSAINER</t>
+          <t>VMART</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -2274,22 +2154,22 @@
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>217.94</v>
+        <v>666.75</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>61.82</v>
+        <v>62.12</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>53.45</v>
+        <v>53.79</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>43.65</v>
+        <v>47.79</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>PRINCEPIPE</t>
+          <t>DIACABS</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -2298,22 +2178,22 @@
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>273.45</v>
+        <v>194.31</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>61.63</v>
+        <v>62.08</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>54.36</v>
+        <v>74.06</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>39.86</v>
+        <v>66.15000000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>ICIL</t>
+          <t>MIDHANI</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -2322,22 +2202,22 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>302.9</v>
+        <v>420.65</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>61.5</v>
+        <v>62.05</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>56.87</v>
+        <v>63.7</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>53.28</v>
+        <v>56.13</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>THYROCARE</t>
+          <t>KANSAINER</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -2346,22 +2226,22 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>465.85</v>
+        <v>218.06</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>61.36</v>
+        <v>61.37</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>60.64</v>
+        <v>53.51</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>62.08</v>
+        <v>43.68</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>IIFLCAPS</t>
+          <t>TEAMLEASE</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -2370,22 +2250,22 @@
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>342.55</v>
+        <v>1381.6</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>60.76</v>
+        <v>60.96</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>56.81</v>
+        <v>49.34</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>55.11</v>
+        <v>36.16</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>POWERMECH</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -2394,22 +2274,22 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>2544.7</v>
+        <v>269.35</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>60.34</v>
+        <v>60.72</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>58.03</v>
+        <v>69.75</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>52.51</v>
+        <v>68.03</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>POLYPLEX</t>
+          <t>RTNPOWER</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -2418,22 +2298,22 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>961.45</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>60.34</v>
+        <v>60.53</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>57.98</v>
+        <v>53.73</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>46.89</v>
+        <v>48.72</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>TVSSCS</t>
+          <t>GARFIBRES</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -2442,22 +2322,22 @@
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>121.57</v>
+        <v>659.45</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>60.17</v>
+        <v>60.42</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>54.53</v>
+        <v>50.41</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>43.93</v>
+        <v>44.12</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>EMIL</t>
+          <t>SAMHI</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -2466,22 +2346,22 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>120.65</v>
+        <v>165.55</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>60.05</v>
+        <v>60.31</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>58.47</v>
+        <v>50.43</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>46.95</v>
+        <v>47.06</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>MIDHANI</t>
+          <t>PGIL</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -2490,22 +2370,22 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>413.2</v>
+        <v>1653.5</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>59.68</v>
+        <v>60.23</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>62.43</v>
+        <v>55.97</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>55.57</v>
+        <v>63.2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>GAEL</t>
+          <t>JAMNAAUTO</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -2514,22 +2394,22 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>163.44</v>
+        <v>127.67</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>59.61</v>
+        <v>60.01</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>67.45999999999999</v>
+        <v>54.16</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>64.62</v>
+        <v>56.88</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>AARTIDRUGS</t>
+          <t>HCC</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -2538,22 +2418,22 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>389.95</v>
+        <v>22.81</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>59.3</v>
+        <v>59.97</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>51.19</v>
+        <v>56.73</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>45.85</v>
+        <v>46.94</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>ISGEC</t>
+          <t>GANESHHOU</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -2562,22 +2442,22 @@
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>1078.4</v>
+        <v>705.85</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>59.23</v>
+        <v>59.51</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>65.94</v>
+        <v>50.09</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>53.67</v>
+        <v>46.18</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>PRIVISCL</t>
+          <t>LLOYDSENT</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -2586,22 +2466,22 @@
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>3318.3</v>
+        <v>72.06</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>59</v>
+        <v>59.5</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>59.71</v>
+        <v>61.54</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>68.90000000000001</v>
+        <v>58.21</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>ANURAS</t>
+          <t>RELIGARE</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -2610,22 +2490,22 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>1366.1</v>
+        <v>237.55</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>58.96</v>
+        <v>59.45</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>64.75</v>
+        <v>54.21</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>70.58</v>
+        <v>51.96</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>SOUTHBANK</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -2634,22 +2514,22 @@
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>264.5</v>
+        <v>41.42</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>58.93</v>
+        <v>58.99</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>68.45</v>
+        <v>58.12</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>66.59999999999999</v>
+        <v>65.98</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>INNOVACAP</t>
+          <t>CYIENTDLM</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -2658,22 +2538,22 @@
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>848.3</v>
+        <v>420.6</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>58.89</v>
+        <v>58.99</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>63.02</v>
+        <v>59.07</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>57.75</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>SENCO</t>
+          <t>LUMAXTECH</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -2682,22 +2562,22 @@
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>347.95</v>
+        <v>1724.8</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>58.43</v>
+        <v>58.93</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>55.25</v>
+        <v>57.19</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>49.85</v>
+        <v>70.11</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>VARROC</t>
+          <t>IIFLCAPS</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -2706,22 +2586,22 @@
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>561.95</v>
+        <v>341.4</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>58.31</v>
+        <v>58.37</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>52.84</v>
+        <v>56.5</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>52.99</v>
+        <v>54.81</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>FDC</t>
+          <t>INNOVACAP</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -2730,22 +2610,22 @@
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>373.25</v>
+        <v>850.4</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>58.29</v>
+        <v>58.35</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>48.61</v>
+        <v>63.23</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>45.38</v>
+        <v>57.88</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>HIKAL</t>
+          <t>V2RETAIL</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -2754,22 +2634,22 @@
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>205.34</v>
+        <v>230.03</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>58.04</v>
+        <v>58.25</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>49.46</v>
+        <v>60.59</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>39.92</v>
+        <v>67.23999999999999</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>CMSINFO</t>
+          <t>ABDL</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -2778,22 +2658,22 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>306.4</v>
+        <v>558.3</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>57.92</v>
+        <v>58.03</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>44.43</v>
+        <v>54.63</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>39.93</v>
+        <v>59.05</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>PURVA</t>
+          <t>SUNFLAG</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -2802,22 +2682,22 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>225.6</v>
+        <v>373.75</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>57.79</v>
+        <v>58.01</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>51.11</v>
+        <v>68.2</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>46.67</v>
+        <v>66.03</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>CEMPRO</t>
+          <t>GULFOILLUB</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -2826,22 +2706,22 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>862.8</v>
+        <v>973.05</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>57.77</v>
+        <v>57.89</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>63.71</v>
+        <v>44.57</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v/>
+        <v>47.86</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>DATAMATICS</t>
+          <t>TIPSMUSIC</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -2850,22 +2730,22 @@
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>784.85</v>
+        <v>662.45</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>57.73</v>
+        <v>57.61</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>52.77</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>54.71</v>
+        <v>60.19</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>SKYGOLD</t>
+          <t>SFL</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -2874,22 +2754,22 @@
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>469.95</v>
+        <v>605</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>57.69</v>
+        <v>57.4</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>61.83</v>
+        <v>54.7</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>67.91</v>
+        <v>42.16</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>KIRLPNU</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -2898,22 +2778,22 @@
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>283.5</v>
+        <v>1574.3</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>57.41</v>
+        <v>57.12</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>55.46</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>55.88</v>
+        <v>64.09</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>PARAS</t>
+          <t>WELENT</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -2922,22 +2802,22 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>812</v>
+        <v>517.15</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>57.22</v>
+        <v>56.55</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>58.05</v>
+        <v>55.93</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>53.21</v>
+        <v>55.35</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>KNRCON</t>
+          <t>EQUITASBNK</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -2946,22 +2826,22 @@
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>132.12</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>57.17</v>
+        <v>56.54</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>44.7</v>
+        <v>58.45</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>35.29</v>
+        <v>52.37</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>PGIL</t>
+          <t>ZYDUSWELL</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -2970,22 +2850,22 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>1620.3</v>
+        <v>507.05</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>57.07</v>
+        <v>56.45</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>54.56</v>
+        <v>61.4</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>62.49</v>
+        <v>62.68</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>DCAL</t>
+          <t>CEIGALL</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -2994,22 +2874,22 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>195.37</v>
+        <v>347.15</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>56.76</v>
+        <v>56.22</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>49.21</v>
+        <v>66.37</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>48.01</v>
+        <v>63.14</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>VSTIND</t>
+          <t>HCG</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -3018,22 +2898,22 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>258.3</v>
+        <v>637.25</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>56.7</v>
+        <v>56.02</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>56.3</v>
+        <v>57.31</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>47.13</v>
+        <v>60.02</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>KSL</t>
+          <t>SENCO</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -3042,22 +2922,22 @@
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>828.6</v>
+        <v>346.2</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>56.69</v>
+        <v>55.96</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>58.53</v>
+        <v>54.8</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>53.53</v>
+        <v>49.69</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>GREAVESCOT</t>
+          <t>ARVINDFASN</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -3066,22 +2946,22 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>169.45</v>
+        <v>461.35</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>56.43</v>
+        <v>55.82</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>51.09</v>
+        <v>50.66</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>48.23</v>
+        <v>50.54</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>NEOGEN</t>
+          <t>GABRIEL</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -3090,22 +2970,22 @@
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>1687.1</v>
+        <v>1100.1</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>56.36</v>
+        <v>55.79</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>61.63</v>
+        <v>57.74</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>54.26</v>
+        <v>64.44</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>EPIGRAL</t>
+          <t>POWERMECH</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -3114,22 +2994,22 @@
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>1251.1</v>
+        <v>2500.7</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>56.23</v>
+        <v>55.77</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>53.26</v>
+        <v>56.17</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>45.91</v>
+        <v>51.92</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>TSFINV</t>
+          <t>QUESS</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -3138,22 +3018,22 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>412.2</v>
+        <v>209.09</v>
       </c>
       <c r="D81" s="4" t="n">
-        <v>56.09</v>
+        <v>55.31</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>44.05</v>
+        <v>50.5</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v/>
+        <v>33.84</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>BIRLACORPN</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -3162,22 +3042,22 @@
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>1006.1</v>
+        <v>455.35</v>
       </c>
       <c r="D82" s="4" t="n">
-        <v>56.01</v>
+        <v>55.29</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>49.95</v>
+        <v>53</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>44.12</v>
+        <v>58.7</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>BELRISE</t>
+          <t>DHANUKA</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -3186,22 +3066,22 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>216.36</v>
+        <v>1134.8</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>55.98</v>
+        <v>55.29</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>65.19</v>
+        <v>50.85</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v/>
+        <v>46.15</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>GANESHHOU</t>
+          <t>WEBELSOLAR</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -3210,22 +3090,22 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>690.75</v>
+        <v>109.26</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>55.97</v>
+        <v>55.1</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>48.57</v>
+        <v>59.07</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v/>
+        <v>54.48</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>WEBELSOLAR</t>
+          <t>STYRENIX</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -3234,22 +3114,22 @@
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>107.89</v>
+        <v>2286</v>
       </c>
       <c r="D85" s="4" t="n">
-        <v>55.92</v>
+        <v>55.09</v>
       </c>
       <c r="E85" s="4" t="n">
-        <v>58.43</v>
+        <v>56.17</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>54.12</v>
+        <v>54.19</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>SOUTHBANK</t>
+          <t>MSTCLTD</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -3258,22 +3138,22 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>40.72</v>
+        <v>440.5</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>55.92</v>
+        <v>55</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>56.56</v>
+        <v>48.06</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>65.29000000000001</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>MAHLIFE</t>
+          <t>VARROC</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -3282,22 +3162,22 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>341</v>
+        <v>565.4</v>
       </c>
       <c r="D87" s="4" t="n">
-        <v>55.91</v>
+        <v>54.87</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>46.95</v>
+        <v>53.61</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>43.07</v>
+        <v>53.26</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>CEIGALL</t>
+          <t>DCAL</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -3306,22 +3186,22 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>343.55</v>
+        <v>194.7</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>55.77</v>
+        <v>54.79</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>65.56999999999999</v>
+        <v>48.92</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>62.38</v>
+        <v>47.92</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>SANDUMA</t>
+          <t>BELRISE</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -3330,22 +3210,22 @@
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>225.66</v>
+        <v>216.46</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>55.76</v>
+        <v>54.74</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>56.11</v>
+        <v>65.23</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>61.24</v>
+        <v/>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>ADVENZYMES</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -3354,16 +3234,16 @@
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>506.6</v>
+        <v>364</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>55.56</v>
+        <v>54.73</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>58.93</v>
+        <v>64.5</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>49.72</v>
+        <v>55.87</v>
       </c>
     </row>
     <row r="91">
@@ -3378,22 +3258,22 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>455.3</v>
+        <v>455.95</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>55.49</v>
+        <v>54.62</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>52.21</v>
+        <v>52.41</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>53.66</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>SKIPPER</t>
+          <t>PARAS</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -3402,22 +3282,22 @@
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>460.05</v>
+        <v>819.35</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>54.83</v>
+        <v>54.6</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>58.03</v>
+        <v>58.58</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>55.22</v>
+        <v>53.51</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>VMART</t>
+          <t>TANLA</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -3426,22 +3306,22 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>641.25</v>
+        <v>525.4</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>54.3</v>
+        <v>54.1</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>50.25</v>
+        <v>53.48</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>46.38</v>
+        <v>44.68</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>PARADEEP</t>
+          <t>TSFINV</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -3450,22 +3330,22 @@
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>127.19</v>
+        <v>408.9</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>54.18</v>
+        <v>53.87</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>46.62</v>
+        <v>47.94</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>50.25</v>
+        <v>53.65</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>ARVINDFASN</t>
+          <t>KSL</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -3474,22 +3354,22 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>451</v>
+        <v>826.25</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>54.17</v>
+        <v>53.4</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>48.74</v>
+        <v>58.2</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>49.34</v>
+        <v>53.43</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>FIEMIND</t>
+          <t>POLYPLEX</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -3498,22 +3378,22 @@
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>2222.4</v>
+        <v>926.1</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>54.14</v>
+        <v>53.38</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>54.39</v>
+        <v>53.44</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>66.2</v>
+        <v>45.37</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>EASEMYTRIP</t>
+          <t>BOSCH-HCIL</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -3522,22 +3402,22 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>8.029999999999999</v>
+        <v>1396.2</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>54.09</v>
+        <v>53.37</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>52.55</v>
+        <v>51.89</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>38.38</v>
+        <v/>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>IXIGO</t>
+          <t>BIRLACORPN</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -3546,22 +3426,22 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>171.17</v>
+        <v>997.3</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>54.01</v>
+        <v>53.32</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>40.67</v>
+        <v>49.12</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>43.89</v>
+        <v>43.68</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>BANCOINDIA</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -3570,22 +3450,22 @@
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>614.7</v>
+        <v>504.3</v>
       </c>
       <c r="D99" s="4" t="n">
-        <v>53.9</v>
+        <v>53.24</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>50.28</v>
+        <v>58.26</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>57.06</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>WABAG</t>
+          <t>ORIENTCEM</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -3594,22 +3474,22 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>1431.4</v>
+        <v>141.55</v>
       </c>
       <c r="D100" s="4" t="n">
-        <v>53.85</v>
+        <v>53.03</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>56.6</v>
+        <v>37.46</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>55.48</v>
+        <v>36.27</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>NESCO</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -3618,22 +3498,22 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>1241.4</v>
+        <v>2784.4</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>53.84</v>
+        <v>52.91</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>54.58</v>
+        <v>52.02</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>59.35</v>
+        <v>49.23</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>PNCINFRA</t>
+          <t>GPPL</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -3642,22 +3522,22 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>215.32</v>
+        <v>157.35</v>
       </c>
       <c r="D102" s="4" t="n">
-        <v>53.6</v>
+        <v>52.91</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>46.18</v>
+        <v>47.7</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>40.14</v>
+        <v>51.28</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>SAFARI</t>
+          <t>CMSINFO</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -3666,22 +3546,22 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>1527</v>
+        <v>304.5</v>
       </c>
       <c r="D103" s="4" t="n">
-        <v>53.58</v>
+        <v>52.87</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>39.06</v>
+        <v>43.79</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>40.92</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>INOXGREEN</t>
+          <t>FIEMIND</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -3690,22 +3570,22 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>180.35</v>
+        <v>2243</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>53.54</v>
+        <v>52.82</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>51.67</v>
+        <v>55.46</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>53.22</v>
+        <v>66.63</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>BBL</t>
+          <t>PATELENG</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -3714,22 +3594,22 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>2774.2</v>
+        <v>27.43</v>
       </c>
       <c r="D105" s="4" t="n">
-        <v>53.26</v>
+        <v>52.77</v>
       </c>
       <c r="E105" s="4" t="n">
-        <v>51.78</v>
+        <v>45.56</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>49.11</v>
+        <v>37.88</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>MANINFRA</t>
+          <t>PRIVISCL</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -3738,22 +3618,22 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>118.34</v>
+        <v>3255.2</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>53.19</v>
+        <v>52.52</v>
       </c>
       <c r="E106" s="4" t="n">
-        <v>51.31</v>
+        <v>57.59</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>44</v>
+        <v>67.39</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENT</t>
+          <t>DATAMATICS</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -3762,22 +3642,22 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>67.84</v>
+        <v>766.2</v>
       </c>
       <c r="D107" s="4" t="n">
-        <v>53.19</v>
+        <v>52.47</v>
       </c>
       <c r="E107" s="4" t="n">
-        <v>57.91</v>
+        <v>50.91</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>56.15</v>
+        <v>53.91</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>JKPAPER</t>
+          <t>INGERRAND</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -3786,22 +3666,22 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>379.45</v>
+        <v>4352</v>
       </c>
       <c r="D108" s="4" t="n">
-        <v>53.09</v>
+        <v>52.41</v>
       </c>
       <c r="E108" s="4" t="n">
-        <v>57.58</v>
+        <v>61.08</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>52.36</v>
+        <v>60.43</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>HEMIPROP</t>
+          <t>SUDARSCHEM</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -3810,22 +3690,22 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>143.76</v>
+        <v>938</v>
       </c>
       <c r="D109" s="4" t="n">
-        <v>53.01</v>
+        <v>52.37</v>
       </c>
       <c r="E109" s="4" t="n">
-        <v>53.84</v>
+        <v>50.13</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>50.45</v>
+        <v>49.65</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>GRINFRA</t>
+          <t>JKIL</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -3834,22 +3714,22 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>939.9</v>
+        <v>502.75</v>
       </c>
       <c r="D110" s="4" t="n">
-        <v>52.83</v>
+        <v>52.34</v>
       </c>
       <c r="E110" s="4" t="n">
-        <v>46.62</v>
+        <v>43.26</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>40.58</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>NFL</t>
+          <t>CIGNITITEC</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -3858,22 +3738,22 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>76.37</v>
+        <v>1260.3</v>
       </c>
       <c r="D111" s="4" t="n">
-        <v>52.82</v>
+        <v>52.32</v>
       </c>
       <c r="E111" s="4" t="n">
-        <v>45.21</v>
+        <v>44.74</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>45.04</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>LXCHEM</t>
+          <t>PRINCEPIPE</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -3882,22 +3762,22 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>151.81</v>
+        <v>262.15</v>
       </c>
       <c r="D112" s="4" t="n">
-        <v>52.81</v>
+        <v>52.28</v>
       </c>
       <c r="E112" s="4" t="n">
-        <v>50.96</v>
+        <v>50.04</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>39.72</v>
+        <v>38.41</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>OPTIEMUS</t>
+          <t>RTNINDIA</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -3906,22 +3786,22 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>418.9</v>
+        <v>34.95</v>
       </c>
       <c r="D113" s="4" t="n">
-        <v>52.8</v>
+        <v>52.19</v>
       </c>
       <c r="E113" s="4" t="n">
-        <v>47.22</v>
+        <v>47.18</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>47.16</v>
+        <v>41.72</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>ETHOSLTD</t>
+          <t>TVSSCS</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -3930,22 +3810,22 @@
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>2407.8</v>
+        <v>117.19</v>
       </c>
       <c r="D114" s="4" t="n">
-        <v>52.6</v>
+        <v>52.01</v>
       </c>
       <c r="E114" s="4" t="n">
-        <v>47.09</v>
+        <v>51.84</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>48.75</v>
+        <v>42.34</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>TANLA</t>
+          <t>VSTIND</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -3954,22 +3834,22 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>518.6</v>
+        <v>255.7</v>
       </c>
       <c r="D115" s="4" t="n">
-        <v>52.49</v>
+        <v>52.01</v>
       </c>
       <c r="E115" s="4" t="n">
-        <v>52.53</v>
+        <v>54.72</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>44.24</v>
+        <v>46.64</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>CIGNITITEC</t>
+          <t>ALLCARGO</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -3978,22 +3858,22 @@
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>1260.3</v>
+        <v>9.1</v>
       </c>
       <c r="D116" s="4" t="n">
-        <v>52.32</v>
+        <v>51.99</v>
       </c>
       <c r="E116" s="4" t="n">
-        <v>44.74</v>
+        <v>36.07</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>46.95</v>
+        <v>27.79</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>WELENT</t>
+          <t>SANDUMA</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -4002,22 +3882,22 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>505.15</v>
+        <v>226.31</v>
       </c>
       <c r="D117" s="4" t="n">
-        <v>52.32</v>
+        <v>51.98</v>
       </c>
       <c r="E117" s="4" t="n">
-        <v>53.3</v>
+        <v>56.3</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>54.25</v>
+        <v>61.34</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>AWFIS</t>
+          <t>IMAGICAA</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -4026,22 +3906,22 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>343.55</v>
+        <v>44.85</v>
       </c>
       <c r="D118" s="4" t="n">
-        <v>52.28</v>
+        <v>51.74</v>
       </c>
       <c r="E118" s="4" t="n">
-        <v>43.53</v>
+        <v>46.18</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>34.58</v>
+        <v>41.75</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>DYNAMATECH</t>
+          <t>SHRIPISTON</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -4050,22 +3930,22 @@
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>11170</v>
+        <v>3391</v>
       </c>
       <c r="D119" s="4" t="n">
-        <v>52.25</v>
+        <v>51.58</v>
       </c>
       <c r="E119" s="4" t="n">
-        <v>57.83</v>
+        <v>56.22</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>68.11</v>
+        <v>69.25</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>SURYAROSNI</t>
+          <t>DYNAMATECH</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -4074,22 +3954,22 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>245.75</v>
+        <v>11122</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>52.21</v>
+        <v>51.52</v>
       </c>
       <c r="E120" s="4" t="n">
-        <v>50.3</v>
+        <v>57.51</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>48.35</v>
+        <v>67.78</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>GOKEX</t>
+          <t>PRUDENT</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -4098,22 +3978,22 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>697.3</v>
+        <v>2720.2</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>52.05</v>
+        <v>51.43</v>
       </c>
       <c r="E121" s="4" t="n">
-        <v>48.67</v>
+        <v>55.75</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>47.83</v>
+        <v>57.63</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>SANOFICONR</t>
+          <t>PURVA</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -4122,22 +4002,22 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>4735.1</v>
+        <v>219.02</v>
       </c>
       <c r="D122" s="4" t="n">
-        <v>51.92</v>
+        <v>51.42</v>
       </c>
       <c r="E122" s="4" t="n">
-        <v>54.48</v>
+        <v>48.89</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>49.46</v>
+        <v>45.68</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>JINDWORLD</t>
+          <t>VAIBHAVGBL</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -4146,22 +4026,22 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>26.43</v>
+        <v>222.69</v>
       </c>
       <c r="D123" s="4" t="n">
-        <v>51.81</v>
+        <v>51.21</v>
       </c>
       <c r="E123" s="4" t="n">
-        <v>46.16</v>
+        <v>50.43</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>36.36</v>
+        <v>44.75</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>AZAD</t>
+          <t>PARADEEP</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -4170,22 +4050,22 @@
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>2039.6</v>
+        <v>125.96</v>
       </c>
       <c r="D124" s="4" t="n">
-        <v>51.51</v>
+        <v>51.2</v>
       </c>
       <c r="E124" s="4" t="n">
-        <v>60.91</v>
+        <v>45.92</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>61.32</v>
+        <v>49.95</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>EMBDL</t>
+          <t>MEDPLUS</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -4194,22 +4074,22 @@
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>61.71</v>
+        <v>895.2</v>
       </c>
       <c r="D125" s="4" t="n">
-        <v>51.34</v>
+        <v>51.12</v>
       </c>
       <c r="E125" s="4" t="n">
-        <v>48.39</v>
+        <v>56.31</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>38</v>
+        <v>57.95</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>MEDPLUS</t>
+          <t>DODLA</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -4218,22 +4098,22 @@
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>898.75</v>
+        <v>1081.1</v>
       </c>
       <c r="D126" s="4" t="n">
-        <v>51.32</v>
+        <v>50.85</v>
       </c>
       <c r="E126" s="4" t="n">
-        <v>56.91</v>
+        <v>44.59</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>58.22</v>
+        <v>48.91</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>IONEXCHANG</t>
+          <t>GMRP&amp;UI</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -4242,22 +4122,22 @@
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>395.05</v>
+        <v>109.52</v>
       </c>
       <c r="D127" s="4" t="n">
-        <v>51.27</v>
+        <v>50.85</v>
       </c>
       <c r="E127" s="4" t="n">
-        <v>52.94</v>
+        <v>50.59</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>45.37</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>RTNINDIA</t>
+          <t>AGI</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -4266,22 +4146,22 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>34.61</v>
+        <v>589.95</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>51.17</v>
+        <v>50.71</v>
       </c>
       <c r="E128" s="4" t="n">
-        <v>46.47</v>
+        <v>45.08</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>41.55</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>VAIBHAVGBL</t>
+          <t>MANORAMA</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -4290,22 +4170,22 @@
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>220.65</v>
+        <v>1426.4</v>
       </c>
       <c r="D129" s="4" t="n">
-        <v>50.97</v>
+        <v>50.64</v>
       </c>
       <c r="E129" s="4" t="n">
-        <v>49.71</v>
+        <v>53.24</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>44.42</v>
+        <v>61.05</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>JSFB</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -4314,22 +4194,22 @@
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>450.45</v>
+        <v>277.75</v>
       </c>
       <c r="D130" s="4" t="n">
-        <v>50.7</v>
+        <v>50.64</v>
       </c>
       <c r="E130" s="4" t="n">
-        <v>56.78</v>
+        <v>53.51</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>50.44</v>
+        <v>54.95</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>QUESS</t>
+          <t>AARTIDRUGS</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -4338,22 +4218,22 @@
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>202.74</v>
+        <v>380.4</v>
       </c>
       <c r="D131" s="4" t="n">
-        <v>50.54</v>
+        <v>50.62</v>
       </c>
       <c r="E131" s="4" t="n">
-        <v>47.63</v>
+        <v>48.52</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>32.87</v>
+        <v>44.74</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>HGINFRA</t>
+          <t>STAR</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -4362,22 +4242,22 @@
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>599.15</v>
+        <v>1111.8</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>50.31</v>
+        <v>50.57</v>
       </c>
       <c r="E132" s="4" t="n">
-        <v>43.03</v>
+        <v>65.16</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>37.62</v>
+        <v>61.3</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>MASTEK</t>
+          <t>IXIGO</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -4386,22 +4266,22 @@
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>1635.2</v>
+        <v>168.36</v>
       </c>
       <c r="D133" s="4" t="n">
-        <v>50.3</v>
+        <v>50.28</v>
       </c>
       <c r="E133" s="4" t="n">
-        <v>41.01</v>
+        <v>39.77</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>39.77</v>
+        <v>43.01</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>ABDL</t>
+          <t>FINEORG</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -4410,22 +4290,22 @@
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>536.3</v>
+        <v>4625.4</v>
       </c>
       <c r="D134" s="4" t="n">
-        <v>50.15</v>
+        <v>50.21</v>
       </c>
       <c r="E134" s="4" t="n">
-        <v>52.13</v>
+        <v>53.4</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>57.53</v>
+        <v>51.32</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>CARTRADE</t>
+          <t>SAFARI</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -4434,22 +4314,22 @@
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>1796.6</v>
+        <v>1503.7</v>
       </c>
       <c r="D135" s="4" t="n">
-        <v>50.02</v>
+        <v>49.97</v>
       </c>
       <c r="E135" s="4" t="n">
-        <v>42.88</v>
+        <v>38.19</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>50.89</v>
+        <v>40.3</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>STYRENIX</t>
+          <t>EMBDL</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -4458,22 +4338,22 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>2223.8</v>
+        <v>60.38</v>
       </c>
       <c r="D136" s="4" t="n">
-        <v>49.97</v>
+        <v>49.82</v>
       </c>
       <c r="E136" s="4" t="n">
-        <v>53.63</v>
+        <v>47.49</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>52.82</v>
+        <v>41.64</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>HCC</t>
+          <t>GOKEX</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -4482,22 +4362,22 @@
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>20.87</v>
+        <v>691.8</v>
       </c>
       <c r="D137" s="4" t="n">
-        <v>49.94</v>
+        <v>49.71</v>
       </c>
       <c r="E137" s="4" t="n">
-        <v>51.61</v>
+        <v>48.17</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>45.15</v>
+        <v>47.63</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>STARCEMENT</t>
+          <t>KRBL</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -4506,22 +4386,22 @@
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>220.99</v>
+        <v>350.2</v>
       </c>
       <c r="D138" s="4" t="n">
-        <v>49.79</v>
+        <v>49.68</v>
       </c>
       <c r="E138" s="4" t="n">
-        <v>49.32</v>
+        <v>49.82</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>52.69</v>
+        <v>51.53</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>BORORENEW</t>
+          <t>ETHOSLTD</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -4530,22 +4410,22 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>508.65</v>
+        <v>2381.5</v>
       </c>
       <c r="D139" s="4" t="n">
-        <v>49.66</v>
+        <v>49.56</v>
       </c>
       <c r="E139" s="4" t="n">
-        <v>50.73</v>
+        <v>46.28</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>49.94</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>SHAREINDIA</t>
+          <t>LUXIND</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -4554,22 +4434,22 @@
         </is>
       </c>
       <c r="C140" s="4" t="n">
-        <v>141.57</v>
+        <v>1380.3</v>
       </c>
       <c r="D140" s="4" t="n">
-        <v>49.57</v>
+        <v>49.44</v>
       </c>
       <c r="E140" s="4" t="n">
-        <v>47.27</v>
+        <v>56.23</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>40.88</v>
+        <v>50.31</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>TEXRAIL</t>
+          <t>SHAKTIPUMP</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -4578,22 +4458,22 @@
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>108.21</v>
+        <v>524.75</v>
       </c>
       <c r="D141" s="4" t="n">
-        <v>49.57</v>
+        <v>49.42</v>
       </c>
       <c r="E141" s="4" t="n">
-        <v>46.2</v>
+        <v>40.28</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>43.43</v>
+        <v>44.97</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>AURIONPRO</t>
+          <t>WAAREERTL</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -4602,22 +4482,22 @@
         </is>
       </c>
       <c r="C142" s="4" t="n">
-        <v>819</v>
+        <v>974</v>
       </c>
       <c r="D142" s="4" t="n">
-        <v>49.53</v>
+        <v>49.32</v>
       </c>
       <c r="E142" s="4" t="n">
-        <v>41.13</v>
+        <v>51.34</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>41.04</v>
+        <v/>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>NFL</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -4626,22 +4506,22 @@
         </is>
       </c>
       <c r="C143" s="4" t="n">
-        <v>713.1</v>
+        <v>76</v>
       </c>
       <c r="D143" s="4" t="n">
-        <v>49.43</v>
+        <v>49.05</v>
       </c>
       <c r="E143" s="4" t="n">
-        <v>48.44</v>
+        <v>44.67</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>52.15</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>EMIL</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -4650,22 +4530,22 @@
         </is>
       </c>
       <c r="C144" s="4" t="n">
-        <v>3817.3</v>
+        <v>114</v>
       </c>
       <c r="D144" s="4" t="n">
-        <v>49.35</v>
+        <v>49.04</v>
       </c>
       <c r="E144" s="4" t="n">
-        <v>55.09</v>
+        <v>52.66</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>70</v>
+        <v>45.51</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>ANUP</t>
+          <t>ALIVUS</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -4674,22 +4554,22 @@
         </is>
       </c>
       <c r="C145" s="4" t="n">
-        <v>1977.6</v>
+        <v>1055.5</v>
       </c>
       <c r="D145" s="4" t="n">
-        <v>49.26</v>
+        <v>48.93</v>
       </c>
       <c r="E145" s="4" t="n">
-        <v>49.1</v>
+        <v>59.9</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>48.06</v>
+        <v>59.35</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>VIPIND</t>
+          <t>MASTEK</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -4698,22 +4578,22 @@
         </is>
       </c>
       <c r="C146" s="4" t="n">
-        <v>303.2</v>
+        <v>1627</v>
       </c>
       <c r="D146" s="4" t="n">
-        <v>48.87</v>
+        <v>48.91</v>
       </c>
       <c r="E146" s="4" t="n">
-        <v>35.9</v>
+        <v>40.63</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>35.79</v>
+        <v>39.64</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>IMFA</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -4722,22 +4602,22 @@
         </is>
       </c>
       <c r="C147" s="4" t="n">
-        <v>181.34</v>
+        <v>1446.2</v>
       </c>
       <c r="D147" s="4" t="n">
-        <v>48.84</v>
+        <v>48.91</v>
       </c>
       <c r="E147" s="4" t="n">
-        <v>54.4</v>
+        <v>57.35</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>59.34</v>
+        <v>67.23999999999999</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>FINEORG</t>
+          <t>AZAD</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -4746,22 +4626,22 @@
         </is>
       </c>
       <c r="C148" s="4" t="n">
-        <v>4604.1</v>
+        <v>2016.7</v>
       </c>
       <c r="D148" s="4" t="n">
-        <v>48.7</v>
+        <v>48.87</v>
       </c>
       <c r="E148" s="4" t="n">
-        <v>52.85</v>
+        <v>59.8</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>51.1</v>
+        <v>60.7</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>DODLA</t>
+          <t>MAHLIFE</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -4770,22 +4650,22 @@
         </is>
       </c>
       <c r="C149" s="4" t="n">
-        <v>1062.8</v>
+        <v>332.7</v>
       </c>
       <c r="D149" s="4" t="n">
-        <v>48.69</v>
+        <v>48.82</v>
       </c>
       <c r="E149" s="4" t="n">
-        <v>42.28</v>
+        <v>44.56</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>48.17</v>
+        <v>42.16</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>RELAXO</t>
+          <t>KITEX</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -4794,22 +4674,22 @@
         </is>
       </c>
       <c r="C150" s="4" t="n">
-        <v>294.4</v>
+        <v>161.48</v>
       </c>
       <c r="D150" s="4" t="n">
-        <v>48.39</v>
+        <v>48.64</v>
       </c>
       <c r="E150" s="4" t="n">
-        <v>37.52</v>
+        <v>44.11</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>27.15</v>
+        <v>49.12</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>KRBL</t>
+          <t>VOLTAMP</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -4818,22 +4698,22 @@
         </is>
       </c>
       <c r="C151" s="4" t="n">
-        <v>343.8</v>
+        <v>9497</v>
       </c>
       <c r="D151" s="4" t="n">
-        <v>48.32</v>
+        <v>47.97</v>
       </c>
       <c r="E151" s="4" t="n">
-        <v>48.18</v>
+        <v>54.51</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>50.83</v>
+        <v>54.28</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>GMRP&amp;UI</t>
+          <t>MANINFRA</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -4842,22 +4722,22 @@
         </is>
       </c>
       <c r="C152" s="4" t="n">
-        <v>108.16</v>
+        <v>115.24</v>
       </c>
       <c r="D152" s="4" t="n">
-        <v>48.31</v>
+        <v>47.91</v>
       </c>
       <c r="E152" s="4" t="n">
-        <v>49.57</v>
+        <v>49.58</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>53.76</v>
+        <v>43.36</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>EQUITASBNK</t>
+          <t>HEMIPROP</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -4866,22 +4746,22 @@
         </is>
       </c>
       <c r="C153" s="4" t="n">
-        <v>66.48</v>
+        <v>139.77</v>
       </c>
       <c r="D153" s="4" t="n">
-        <v>48.16</v>
+        <v>47.67</v>
       </c>
       <c r="E153" s="4" t="n">
-        <v>54.12</v>
+        <v>51.53</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>50.25</v>
+        <v>49.36</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>IMFA</t>
+          <t>UNIMECH</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -4890,22 +4770,22 @@
         </is>
       </c>
       <c r="C154" s="4" t="n">
-        <v>1433.2</v>
+        <v>939</v>
       </c>
       <c r="D154" s="4" t="n">
-        <v>48.12</v>
+        <v>47.57</v>
       </c>
       <c r="E154" s="4" t="n">
-        <v>56.71</v>
+        <v>50.53</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>66.67</v>
+        <v>43.84</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>BOSCH-HCIL</t>
+          <t>LXCHEM</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -4914,22 +4794,22 @@
         </is>
       </c>
       <c r="C155" s="4" t="n">
-        <v>1361.6</v>
+        <v>148.08</v>
       </c>
       <c r="D155" s="4" t="n">
-        <v>48.06</v>
+        <v>47.54</v>
       </c>
       <c r="E155" s="4" t="n">
-        <v>48.89</v>
+        <v>49.06</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v/>
+        <v>38.74</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>ROUTE</t>
+          <t>SURYAROSNI</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -4938,22 +4818,22 @@
         </is>
       </c>
       <c r="C156" s="4" t="n">
-        <v>511.35</v>
+        <v>235.45</v>
       </c>
       <c r="D156" s="4" t="n">
-        <v>47.92</v>
+        <v>47.37</v>
       </c>
       <c r="E156" s="4" t="n">
-        <v>39.34</v>
+        <v>47.02</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>29.07</v>
+        <v>47.12</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>AGI</t>
+          <t>YATHARTH</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -4962,22 +4842,22 @@
         </is>
       </c>
       <c r="C157" s="4" t="n">
-        <v>580.35</v>
+        <v>796.5</v>
       </c>
       <c r="D157" s="4" t="n">
-        <v>47.89</v>
+        <v>47.26</v>
       </c>
       <c r="E157" s="4" t="n">
-        <v>43.58</v>
+        <v>56.56</v>
       </c>
       <c r="F157" s="4" t="n">
-        <v>43.93</v>
+        <v>61.44</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>RATNAMANI</t>
+          <t>STARCEMENT</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -4986,22 +4866,22 @@
         </is>
       </c>
       <c r="C158" s="4" t="n">
-        <v>2564.1</v>
+        <v>217.95</v>
       </c>
       <c r="D158" s="4" t="n">
-        <v>47.6</v>
+        <v>47.21</v>
       </c>
       <c r="E158" s="4" t="n">
-        <v>54.21</v>
+        <v>47.66</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v>49.09</v>
+        <v>51.88</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>GARFIBRES</t>
+          <t>EDELWEISS</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -5010,22 +4890,22 @@
         </is>
       </c>
       <c r="C159" s="4" t="n">
-        <v>625.3</v>
+        <v>112.82</v>
       </c>
       <c r="D159" s="4" t="n">
-        <v>47.53</v>
+        <v>47.17</v>
       </c>
       <c r="E159" s="4" t="n">
-        <v>43.67</v>
+        <v>50.8</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>40.17</v>
+        <v>56.64</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>VINATIORGA</t>
+          <t>RATNAMANI</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -5034,22 +4914,22 @@
         </is>
       </c>
       <c r="C160" s="4" t="n">
-        <v>1318.5</v>
+        <v>2552.7</v>
       </c>
       <c r="D160" s="4" t="n">
-        <v>47.48</v>
+        <v>47.1</v>
       </c>
       <c r="E160" s="4" t="n">
-        <v>37.58</v>
+        <v>53.76</v>
       </c>
       <c r="F160" s="4" t="n">
-        <v>35.82</v>
+        <v>48.87</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>GSFC</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -5058,22 +4938,22 @@
         </is>
       </c>
       <c r="C161" s="4" t="n">
-        <v>169.08</v>
+        <v>1107.3</v>
       </c>
       <c r="D161" s="4" t="n">
-        <v>47.44</v>
+        <v>46.89</v>
       </c>
       <c r="E161" s="4" t="n">
-        <v>47.67</v>
+        <v>58.24</v>
       </c>
       <c r="F161" s="4" t="n">
-        <v>46.69</v>
+        <v>59.62</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>UNIMECH</t>
+          <t>BORORENEW</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -5082,22 +4962,22 @@
         </is>
       </c>
       <c r="C162" s="4" t="n">
-        <v>936</v>
+        <v>501.75</v>
       </c>
       <c r="D162" s="4" t="n">
-        <v>47.4</v>
+        <v>46.82</v>
       </c>
       <c r="E162" s="4" t="n">
-        <v>50.26</v>
+        <v>49.74</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>43.72</v>
+        <v>49.44</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>MOIL</t>
+          <t>PRICOLLTD</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -5106,22 +4986,22 @@
         </is>
       </c>
       <c r="C163" s="4" t="n">
-        <v>303.45</v>
+        <v>562.1</v>
       </c>
       <c r="D163" s="4" t="n">
-        <v>47.16</v>
+        <v>46.79</v>
       </c>
       <c r="E163" s="4" t="n">
-        <v>46.51</v>
+        <v>48.39</v>
       </c>
       <c r="F163" s="4" t="n">
-        <v>48.06</v>
+        <v>56.99</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>WESTLIFE</t>
+          <t>VIPIND</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -5130,22 +5010,22 @@
         </is>
       </c>
       <c r="C164" s="4" t="n">
-        <v>471.35</v>
+        <v>299.4</v>
       </c>
       <c r="D164" s="4" t="n">
-        <v>47.15</v>
+        <v>46.72</v>
       </c>
       <c r="E164" s="4" t="n">
-        <v>40.99</v>
+        <v>34.97</v>
       </c>
       <c r="F164" s="4" t="n">
-        <v>31.16</v>
+        <v>35.17</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>TARC</t>
+          <t>JKPAPER</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -5154,22 +5034,22 @@
         </is>
       </c>
       <c r="C165" s="4" t="n">
-        <v>130.61</v>
+        <v>369.15</v>
       </c>
       <c r="D165" s="4" t="n">
-        <v>47.14</v>
+        <v>46.58</v>
       </c>
       <c r="E165" s="4" t="n">
-        <v>42.98</v>
+        <v>53.49</v>
       </c>
       <c r="F165" s="4" t="n">
-        <v>46.4</v>
+        <v>51.16</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>EMUDHRA</t>
+          <t>SANOFICONR</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -5178,22 +5058,22 @@
         </is>
       </c>
       <c r="C166" s="4" t="n">
-        <v>471</v>
+        <v>4588.5</v>
       </c>
       <c r="D166" s="4" t="n">
-        <v>47.03</v>
+        <v>46.35</v>
       </c>
       <c r="E166" s="4" t="n">
-        <v>41.8</v>
+        <v>50.28</v>
       </c>
       <c r="F166" s="4" t="n">
-        <v>39.87</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>ZYDUSWELL</t>
+          <t>KNRCON</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -5202,22 +5082,22 @@
         </is>
       </c>
       <c r="C167" s="4" t="n">
-        <v>490.4</v>
+        <v>126.66</v>
       </c>
       <c r="D167" s="4" t="n">
-        <v>47.01</v>
+        <v>46.26</v>
       </c>
       <c r="E167" s="4" t="n">
-        <v>58.38</v>
+        <v>42</v>
       </c>
       <c r="F167" s="4" t="n">
-        <v>60.25</v>
+        <v>33.92</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>MANORAMA</t>
+          <t>GATEWAY</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -5226,22 +5106,22 @@
         </is>
       </c>
       <c r="C168" s="4" t="n">
-        <v>1386.4</v>
+        <v>56</v>
       </c>
       <c r="D168" s="4" t="n">
-        <v>46.98</v>
+        <v>46.17</v>
       </c>
       <c r="E168" s="4" t="n">
-        <v>51.3</v>
+        <v>46.97</v>
       </c>
       <c r="F168" s="4" t="n">
-        <v>59.42</v>
+        <v>40.83</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>MSTCLTD</t>
+          <t>EMUDHRA</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -5250,22 +5130,22 @@
         </is>
       </c>
       <c r="C169" s="4" t="n">
-        <v>426.25</v>
+        <v>469.05</v>
       </c>
       <c r="D169" s="4" t="n">
-        <v>46.97</v>
+        <v>46.14</v>
       </c>
       <c r="E169" s="4" t="n">
-        <v>45.14</v>
+        <v>41.5</v>
       </c>
       <c r="F169" s="4" t="n">
-        <v>45.1</v>
+        <v>39.76</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>SWSOLAR</t>
+          <t>ROUTE</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -5274,22 +5154,22 @@
         </is>
       </c>
       <c r="C170" s="4" t="n">
-        <v>198.04</v>
+        <v>507.55</v>
       </c>
       <c r="D170" s="4" t="n">
-        <v>46.95</v>
+        <v>46.08</v>
       </c>
       <c r="E170" s="4" t="n">
-        <v>47.07</v>
+        <v>38.86</v>
       </c>
       <c r="F170" s="4" t="n">
-        <v>38.71</v>
+        <v>28.96</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>SAMHI</t>
+          <t>JUSTDIAL</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -5298,22 +5178,22 @@
         </is>
       </c>
       <c r="C171" s="4" t="n">
-        <v>150.08</v>
+        <v>524.6</v>
       </c>
       <c r="D171" s="4" t="n">
-        <v>46.57</v>
+        <v>45.93</v>
       </c>
       <c r="E171" s="4" t="n">
-        <v>40.8</v>
+        <v>34.55</v>
       </c>
       <c r="F171" s="4" t="n">
-        <v>43.23</v>
+        <v>34.63</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>WAAREERTL</t>
+          <t>OPTIEMUS</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -5322,22 +5202,22 @@
         </is>
       </c>
       <c r="C172" s="4" t="n">
-        <v>957.1</v>
+        <v>405.3</v>
       </c>
       <c r="D172" s="4" t="n">
-        <v>46.28</v>
+        <v>45.66</v>
       </c>
       <c r="E172" s="4" t="n">
-        <v>49.96</v>
+        <v>45.25</v>
       </c>
       <c r="F172" s="4" t="n">
-        <v/>
+        <v>46.4</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>AHLUCONT</t>
+          <t>TARC</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -5346,22 +5226,22 @@
         </is>
       </c>
       <c r="C173" s="4" t="n">
-        <v>806.35</v>
+        <v>129.76</v>
       </c>
       <c r="D173" s="4" t="n">
-        <v>46.27</v>
+        <v>45.51</v>
       </c>
       <c r="E173" s="4" t="n">
-        <v>45.95</v>
+        <v>42.5</v>
       </c>
       <c r="F173" s="4" t="n">
-        <v>46.95</v>
+        <v>46.23</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>SHARDAMOTR</t>
+          <t>ENTERO</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -5370,22 +5250,22 @@
         </is>
       </c>
       <c r="C174" s="4" t="n">
-        <v>853.1</v>
+        <v>1195.8</v>
       </c>
       <c r="D174" s="4" t="n">
-        <v>46.26</v>
+        <v>45.31</v>
       </c>
       <c r="E174" s="4" t="n">
-        <v>46.35</v>
+        <v>51.21</v>
       </c>
       <c r="F174" s="4" t="n">
-        <v>43</v>
+        <v>52.36</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>KSCL</t>
+          <t>CARTRADE</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -5394,22 +5274,22 @@
         </is>
       </c>
       <c r="C175" s="4" t="n">
-        <v>918.35</v>
+        <v>1735.2</v>
       </c>
       <c r="D175" s="4" t="n">
-        <v>46.25</v>
+        <v>45.24</v>
       </c>
       <c r="E175" s="4" t="n">
-        <v>49.34</v>
+        <v>41.33</v>
       </c>
       <c r="F175" s="4" t="n">
-        <v>49.29</v>
+        <v>49.75</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>HIKAL</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -5418,22 +5298,22 @@
         </is>
       </c>
       <c r="C176" s="4" t="n">
-        <v>1109.6</v>
+        <v>195.28</v>
       </c>
       <c r="D176" s="4" t="n">
-        <v>46.21</v>
+        <v>45.13</v>
       </c>
       <c r="E176" s="4" t="n">
-        <v>58.4</v>
+        <v>46.13</v>
       </c>
       <c r="F176" s="4" t="n">
-        <v>59.72</v>
+        <v>38.16</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>AVANTIFEED</t>
+          <t>CCAVENUE</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -5442,22 +5322,22 @@
         </is>
       </c>
       <c r="C177" s="4" t="n">
-        <v>1306.8</v>
+        <v>13.89</v>
       </c>
       <c r="D177" s="4" t="n">
-        <v>46.02</v>
+        <v>45.01</v>
       </c>
       <c r="E177" s="4" t="n">
-        <v>59.1</v>
+        <v>40.9</v>
       </c>
       <c r="F177" s="4" t="n">
-        <v>70.73</v>
+        <v>38.58</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>KPIGREEN</t>
+          <t>AWFIS</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -5466,22 +5346,22 @@
         </is>
       </c>
       <c r="C178" s="4" t="n">
-        <v>426.8</v>
+        <v>327.9</v>
       </c>
       <c r="D178" s="4" t="n">
-        <v>45.85</v>
+        <v>44.99</v>
       </c>
       <c r="E178" s="4" t="n">
-        <v>49.78</v>
+        <v>41.45</v>
       </c>
       <c r="F178" s="4" t="n">
-        <v>50.44</v>
+        <v>33.65</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>LUMAXTECH</t>
+          <t>BALUFORGE</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -5490,22 +5370,22 @@
         </is>
       </c>
       <c r="C179" s="4" t="n">
-        <v>1624.9</v>
+        <v>475.9</v>
       </c>
       <c r="D179" s="4" t="n">
-        <v>45.81</v>
+        <v>44.97</v>
       </c>
       <c r="E179" s="4" t="n">
-        <v>53.47</v>
+        <v>45.93</v>
       </c>
       <c r="F179" s="4" t="n">
-        <v>68.36</v>
+        <v>47.43</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>INDIAGLYCO</t>
+          <t>AURIONPRO</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -5514,22 +5394,22 @@
         </is>
       </c>
       <c r="C180" s="4" t="n">
-        <v>988.2</v>
+        <v>794.8</v>
       </c>
       <c r="D180" s="4" t="n">
-        <v>45.65</v>
+        <v>44.89</v>
       </c>
       <c r="E180" s="4" t="n">
-        <v>52.89</v>
+        <v>39.73</v>
       </c>
       <c r="F180" s="4" t="n">
-        <v>59.47</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>TEXRAIL</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -5538,22 +5418,22 @@
         </is>
       </c>
       <c r="C181" s="4" t="n">
-        <v>193.77</v>
+        <v>104.37</v>
       </c>
       <c r="D181" s="4" t="n">
-        <v>45.43</v>
+        <v>44.58</v>
       </c>
       <c r="E181" s="4" t="n">
-        <v>57.76</v>
+        <v>43.8</v>
       </c>
       <c r="F181" s="4" t="n">
-        <v>59.89</v>
+        <v>42.52</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>LMW</t>
+          <t>SHAREINDIA</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -5562,22 +5442,22 @@
         </is>
       </c>
       <c r="C182" s="4" t="n">
-        <v>14180</v>
+        <v>138.09</v>
       </c>
       <c r="D182" s="4" t="n">
-        <v>45.41</v>
+        <v>44.49</v>
       </c>
       <c r="E182" s="4" t="n">
-        <v>47.35</v>
+        <v>45.43</v>
       </c>
       <c r="F182" s="4" t="n">
-        <v>48.46</v>
+        <v>40.13</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>VINATIORGA</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -5586,22 +5466,22 @@
         </is>
       </c>
       <c r="C183" s="4" t="n">
-        <v>435.35</v>
+        <v>1301.1</v>
       </c>
       <c r="D183" s="4" t="n">
-        <v>45.35</v>
+        <v>44.37</v>
       </c>
       <c r="E183" s="4" t="n">
-        <v>47.71</v>
+        <v>36.27</v>
       </c>
       <c r="F183" s="4" t="n">
-        <v>56.56</v>
+        <v>35.31</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>CSBBANK</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -5610,22 +5490,22 @@
         </is>
       </c>
       <c r="C184" s="4" t="n">
-        <v>361.25</v>
+        <v>1098</v>
       </c>
       <c r="D184" s="4" t="n">
-        <v>45.27</v>
+        <v>44.32</v>
       </c>
       <c r="E184" s="4" t="n">
-        <v>43.48</v>
+        <v>55.31</v>
       </c>
       <c r="F184" s="4" t="n">
-        <v>49.92</v>
+        <v>63.15</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>TEGA</t>
+          <t>SHARDAMOTR</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -5634,22 +5514,22 @@
         </is>
       </c>
       <c r="C185" s="4" t="n">
-        <v>1603</v>
+        <v>843.3</v>
       </c>
       <c r="D185" s="4" t="n">
-        <v>45.18</v>
+        <v>44.22</v>
       </c>
       <c r="E185" s="4" t="n">
-        <v>38.52</v>
+        <v>45.4</v>
       </c>
       <c r="F185" s="4" t="n">
-        <v>50.54</v>
+        <v>42.74</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>ALIVUS</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -5658,22 +5538,22 @@
         </is>
       </c>
       <c r="C186" s="4" t="n">
-        <v>1039</v>
+        <v>190.02</v>
       </c>
       <c r="D186" s="4" t="n">
-        <v>45.08</v>
+        <v>43.8</v>
       </c>
       <c r="E186" s="4" t="n">
-        <v>57.98</v>
+        <v>49.31</v>
       </c>
       <c r="F186" s="4" t="n">
-        <v>62.62</v>
+        <v>39.96</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>PRICOLLTD</t>
+          <t>KPIGREEN</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -5682,22 +5562,22 @@
         </is>
       </c>
       <c r="C187" s="4" t="n">
-        <v>556.65</v>
+        <v>420.95</v>
       </c>
       <c r="D187" s="4" t="n">
-        <v>44.8</v>
+        <v>43.77</v>
       </c>
       <c r="E187" s="4" t="n">
-        <v>47.55</v>
+        <v>48.74</v>
       </c>
       <c r="F187" s="4" t="n">
-        <v>56.47</v>
+        <v>50.03</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>PRUDENT</t>
+          <t>JAIBALAJI</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -5706,22 +5586,22 @@
         </is>
       </c>
       <c r="C188" s="4" t="n">
-        <v>2647.8</v>
+        <v>72.37</v>
       </c>
       <c r="D188" s="4" t="n">
-        <v>44.63</v>
+        <v>43.71</v>
       </c>
       <c r="E188" s="4" t="n">
-        <v>53.13</v>
+        <v>48.45</v>
       </c>
       <c r="F188" s="4" t="n">
-        <v>56.31</v>
+        <v>42.04</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>GPPL</t>
+          <t>TIMETECHNO</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -5730,22 +5610,22 @@
         </is>
       </c>
       <c r="C189" s="4" t="n">
-        <v>152.26</v>
+        <v>174.71</v>
       </c>
       <c r="D189" s="4" t="n">
-        <v>44.36</v>
+        <v>43.65</v>
       </c>
       <c r="E189" s="4" t="n">
-        <v>43.62</v>
+        <v>44.4</v>
       </c>
       <c r="F189" s="4" t="n">
-        <v>49.74</v>
+        <v>50.11</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>LUXIND</t>
+          <t>INOXGREEN</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -5754,22 +5634,22 @@
         </is>
       </c>
       <c r="C190" s="4" t="n">
-        <v>1313.5</v>
+        <v>172.41</v>
       </c>
       <c r="D190" s="4" t="n">
-        <v>44.31</v>
+        <v>43.4</v>
       </c>
       <c r="E190" s="4" t="n">
-        <v>53.99</v>
+        <v>48.6</v>
       </c>
       <c r="F190" s="4" t="n">
-        <v>48.63</v>
+        <v>51.99</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>ORIENTCEM</t>
+          <t>INDIAGLYCO</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -5778,22 +5658,22 @@
         </is>
       </c>
       <c r="C191" s="4" t="n">
-        <v>136.4</v>
+        <v>975</v>
       </c>
       <c r="D191" s="4" t="n">
-        <v>44.21</v>
+        <v>43.11</v>
       </c>
       <c r="E191" s="4" t="n">
-        <v>32.52</v>
+        <v>51.78</v>
       </c>
       <c r="F191" s="4" t="n">
-        <v>35.61</v>
+        <v>58.84</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>BALUFORGE</t>
+          <t>HGINFRA</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -5802,22 +5682,22 @@
         </is>
       </c>
       <c r="C192" s="4" t="n">
-        <v>475.75</v>
+        <v>583.65</v>
       </c>
       <c r="D192" s="4" t="n">
-        <v>44</v>
+        <v>43.06</v>
       </c>
       <c r="E192" s="4" t="n">
-        <v>45.91</v>
+        <v>41.44</v>
       </c>
       <c r="F192" s="4" t="n">
-        <v>47.42</v>
+        <v>37.07</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>EPL</t>
+          <t>MOIL</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -5826,22 +5706,22 @@
         </is>
       </c>
       <c r="C193" s="4" t="n">
-        <v>216</v>
+        <v>297.45</v>
       </c>
       <c r="D193" s="4" t="n">
-        <v>43.72</v>
+        <v>42.89</v>
       </c>
       <c r="E193" s="4" t="n">
-        <v>50.57</v>
+        <v>44.97</v>
       </c>
       <c r="F193" s="4" t="n">
-        <v>51.92</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>JKIL</t>
+          <t>GAEL</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -5850,22 +5730,22 @@
         </is>
       </c>
       <c r="C194" s="4" t="n">
-        <v>487.2</v>
+        <v>154.89</v>
       </c>
       <c r="D194" s="4" t="n">
-        <v>43.72</v>
+        <v>42.81</v>
       </c>
       <c r="E194" s="4" t="n">
-        <v>39.19</v>
+        <v>59.81</v>
       </c>
       <c r="F194" s="4" t="n">
-        <v>41.37</v>
+        <v>61.73</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>CCAVENUE</t>
+          <t>UJJIVANSFB</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -5874,22 +5754,22 @@
         </is>
       </c>
       <c r="C195" s="4" t="n">
-        <v>13.84</v>
+        <v>54.39</v>
       </c>
       <c r="D195" s="4" t="n">
-        <v>43.35</v>
+        <v>42.77</v>
       </c>
       <c r="E195" s="4" t="n">
-        <v>37.65</v>
+        <v>48.29</v>
       </c>
       <c r="F195" s="4" t="n">
-        <v/>
+        <v>56.17</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>KITEX</t>
+          <t>SUBROS</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -5898,22 +5778,22 @@
         </is>
       </c>
       <c r="C196" s="4" t="n">
-        <v>157.86</v>
+        <v>720.6</v>
       </c>
       <c r="D196" s="4" t="n">
-        <v>43.15</v>
+        <v>42.28</v>
       </c>
       <c r="E196" s="4" t="n">
-        <v>42.38</v>
+        <v>43.36</v>
       </c>
       <c r="F196" s="4" t="n">
-        <v>48.55</v>
+        <v>49.93</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>ELECTCAST</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -5922,22 +5802,22 @@
         </is>
       </c>
       <c r="C197" s="4" t="n">
-        <v>78.13</v>
+        <v>175.33</v>
       </c>
       <c r="D197" s="4" t="n">
-        <v>43.03</v>
+        <v>42.12</v>
       </c>
       <c r="E197" s="4" t="n">
-        <v>47.7</v>
+        <v>49.93</v>
       </c>
       <c r="F197" s="4" t="n">
-        <v>42.92</v>
+        <v>57.55</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>JAIBALAJI</t>
+          <t>JISLJALEQS</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -5946,22 +5826,22 @@
         </is>
       </c>
       <c r="C198" s="4" t="n">
-        <v>72.03</v>
+        <v>29.85</v>
       </c>
       <c r="D198" s="4" t="n">
-        <v>42.8</v>
+        <v>42.06</v>
       </c>
       <c r="E198" s="4" t="n">
-        <v>48.18</v>
+        <v>35.63</v>
       </c>
       <c r="F198" s="4" t="n">
-        <v>41.96</v>
+        <v>35.41</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>RALLIS</t>
+          <t>AHLUCONT</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -5970,22 +5850,22 @@
         </is>
       </c>
       <c r="C199" s="4" t="n">
-        <v>252.95</v>
+        <v>792</v>
       </c>
       <c r="D199" s="4" t="n">
-        <v>42.77</v>
+        <v>42.02</v>
       </c>
       <c r="E199" s="4" t="n">
-        <v>45.84</v>
+        <v>44.57</v>
       </c>
       <c r="F199" s="4" t="n">
-        <v>47.28</v>
+        <v>46.44</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>INDIASHLTR</t>
+          <t>EPIGRAL</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -5994,22 +5874,22 @@
         </is>
       </c>
       <c r="C200" s="4" t="n">
-        <v>784.75</v>
+        <v>1160.9</v>
       </c>
       <c r="D200" s="4" t="n">
-        <v>42.66</v>
+        <v>41.88</v>
       </c>
       <c r="E200" s="4" t="n">
-        <v>48.13</v>
+        <v>47.73</v>
       </c>
       <c r="F200" s="4" t="n">
-        <v>51.64</v>
+        <v>44</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>TIMETECHNO</t>
+          <t>PNCINFRA</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -6018,22 +5898,22 @@
         </is>
       </c>
       <c r="C201" s="4" t="n">
-        <v>174.36</v>
+        <v>204.8</v>
       </c>
       <c r="D201" s="4" t="n">
-        <v>42.64</v>
+        <v>41.81</v>
       </c>
       <c r="E201" s="4" t="n">
-        <v>44.21</v>
+        <v>42.15</v>
       </c>
       <c r="F201" s="4" t="n">
-        <v>50.04</v>
+        <v>38.9</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>RTNPOWER</t>
+          <t>NESCO</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -6042,22 +5922,22 @@
         </is>
       </c>
       <c r="C202" s="4" t="n">
-        <v>9.119999999999999</v>
+        <v>1173.6</v>
       </c>
       <c r="D202" s="4" t="n">
-        <v>42.09</v>
+        <v>41.8</v>
       </c>
       <c r="E202" s="4" t="n">
-        <v>46.9</v>
+        <v>49.12</v>
       </c>
       <c r="F202" s="4" t="n">
-        <v>46.65</v>
+        <v>55.78</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>JUSTDIAL</t>
+          <t>EPL</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -6066,22 +5946,22 @@
         </is>
       </c>
       <c r="C203" s="4" t="n">
-        <v>520.15</v>
+        <v>213.65</v>
       </c>
       <c r="D203" s="4" t="n">
-        <v>42.05</v>
+        <v>41.78</v>
       </c>
       <c r="E203" s="4" t="n">
-        <v>33.49</v>
+        <v>49.53</v>
       </c>
       <c r="F203" s="4" t="n">
-        <v>34.44</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>JAMNAAUTO</t>
+          <t>CSBBANK</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -6090,22 +5970,22 @@
         </is>
       </c>
       <c r="C204" s="4" t="n">
-        <v>114.82</v>
+        <v>352.85</v>
       </c>
       <c r="D204" s="4" t="n">
-        <v>42.05</v>
+        <v>41.75</v>
       </c>
       <c r="E204" s="4" t="n">
-        <v>46.44</v>
+        <v>41.78</v>
       </c>
       <c r="F204" s="4" t="n">
-        <v>52.49</v>
+        <v>48.87</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>IMAGICAA</t>
+          <t>VESUVIUS</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -6114,22 +5994,22 @@
         </is>
       </c>
       <c r="C205" s="4" t="n">
-        <v>42.92</v>
+        <v>468.25</v>
       </c>
       <c r="D205" s="4" t="n">
-        <v>42.01</v>
+        <v>41.74</v>
       </c>
       <c r="E205" s="4" t="n">
-        <v>42.25</v>
+        <v>45.57</v>
       </c>
       <c r="F205" s="4" t="n">
-        <v>40.54</v>
+        <v>51.47</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>SUBROS</t>
+          <t>ELECTCAST</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -6138,22 +6018,22 @@
         </is>
       </c>
       <c r="C206" s="4" t="n">
-        <v>725.95</v>
+        <v>77.13</v>
       </c>
       <c r="D206" s="4" t="n">
-        <v>42.01</v>
+        <v>41.6</v>
       </c>
       <c r="E206" s="4" t="n">
-        <v>43.85</v>
+        <v>46.86</v>
       </c>
       <c r="F206" s="4" t="n">
-        <v>50.17</v>
+        <v>42.64</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>CIEINDIA</t>
+          <t>OSWALPUMPS</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -6162,22 +6042,22 @@
         </is>
       </c>
       <c r="C207" s="4" t="n">
-        <v>451.15</v>
+        <v>362.05</v>
       </c>
       <c r="D207" s="4" t="n">
-        <v>41.99</v>
+        <v>41.49</v>
       </c>
       <c r="E207" s="4" t="n">
-        <v>52.09</v>
+        <v>39.32</v>
       </c>
       <c r="F207" s="4" t="n">
-        <v>53.31</v>
+        <v/>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>PARKHOTELS</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -6186,22 +6066,22 @@
         </is>
       </c>
       <c r="C208" s="4" t="n">
-        <v>91.73999999999999</v>
+        <v>116.32</v>
       </c>
       <c r="D208" s="4" t="n">
-        <v>41.94</v>
+        <v>41.22</v>
       </c>
       <c r="E208" s="4" t="n">
-        <v>35.44</v>
+        <v>42.71</v>
       </c>
       <c r="F208" s="4" t="n">
-        <v>36.48</v>
+        <v>37.35</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>GREENPANEL</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -6210,22 +6090,22 @@
         </is>
       </c>
       <c r="C209" s="4" t="n">
-        <v>194.62</v>
+        <v>90.91</v>
       </c>
       <c r="D209" s="4" t="n">
-        <v>41.88</v>
+        <v>40.91</v>
       </c>
       <c r="E209" s="4" t="n">
-        <v>40.65</v>
+        <v>35.06</v>
       </c>
       <c r="F209" s="4" t="n">
-        <v>39.26</v>
+        <v>36.32</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>PATELENG</t>
+          <t>PRSMJOHNSN</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -6234,22 +6114,22 @@
         </is>
       </c>
       <c r="C210" s="4" t="n">
-        <v>26.05</v>
+        <v>120.42</v>
       </c>
       <c r="D210" s="4" t="n">
-        <v>41.85</v>
+        <v>40.77</v>
       </c>
       <c r="E210" s="4" t="n">
-        <v>41</v>
+        <v>39.75</v>
       </c>
       <c r="F210" s="4" t="n">
-        <v>36.71</v>
+        <v>42.2</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>EDELWEISS</t>
+          <t>CIEINDIA</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -6258,22 +6138,22 @@
         </is>
       </c>
       <c r="C211" s="4" t="n">
-        <v>110.11</v>
+        <v>446.45</v>
       </c>
       <c r="D211" s="4" t="n">
-        <v>41.81</v>
+        <v>40.71</v>
       </c>
       <c r="E211" s="4" t="n">
-        <v>48.78</v>
+        <v>50.76</v>
       </c>
       <c r="F211" s="4" t="n">
-        <v>55.43</v>
+        <v>52.62</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>PARKHOTELS</t>
+          <t>GRINFRA</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -6282,22 +6162,22 @@
         </is>
       </c>
       <c r="C212" s="4" t="n">
-        <v>117.5</v>
+        <v>899.7</v>
       </c>
       <c r="D212" s="4" t="n">
-        <v>41.64</v>
+        <v>40.65</v>
       </c>
       <c r="E212" s="4" t="n">
-        <v>43.54</v>
+        <v>42.57</v>
       </c>
       <c r="F212" s="4" t="n">
-        <v>37.67</v>
+        <v>39.23</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>GATEWAY</t>
+          <t>GHCL</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -6306,16 +6186,16 @@
         </is>
       </c>
       <c r="C213" s="4" t="n">
-        <v>55.31</v>
+        <v>454.15</v>
       </c>
       <c r="D213" s="4" t="n">
-        <v>41.62</v>
+        <v>40.6</v>
       </c>
       <c r="E213" s="4" t="n">
-        <v>45.44</v>
+        <v>38.64</v>
       </c>
       <c r="F213" s="4" t="n">
-        <v>40.31</v>
+        <v>42.66</v>
       </c>
     </row>
     <row r="214">
@@ -6330,22 +6210,22 @@
         </is>
       </c>
       <c r="C214" s="4" t="n">
-        <v>123.44</v>
+        <v>122.39</v>
       </c>
       <c r="D214" s="4" t="n">
-        <v>41.19</v>
+        <v>40.05</v>
       </c>
       <c r="E214" s="4" t="n">
-        <v>38.16</v>
+        <v>37.7</v>
       </c>
       <c r="F214" s="4" t="n">
-        <v>42.12</v>
+        <v>41.98</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>NETWORK18</t>
+          <t>SHARDACROP</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -6354,22 +6234,22 @@
         </is>
       </c>
       <c r="C215" s="4" t="n">
-        <v>31.82</v>
+        <v>905</v>
       </c>
       <c r="D215" s="4" t="n">
-        <v>41.13</v>
+        <v>39.26</v>
       </c>
       <c r="E215" s="4" t="n">
-        <v>35.71</v>
+        <v>45.53</v>
       </c>
       <c r="F215" s="4" t="n">
-        <v>35.99</v>
+        <v>54.1</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>VOLTAMP</t>
+          <t>BLACKBUCK</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -6378,22 +6258,22 @@
         </is>
       </c>
       <c r="C216" s="4" t="n">
-        <v>9134</v>
+        <v>510.55</v>
       </c>
       <c r="D216" s="4" t="n">
-        <v>41</v>
+        <v>38.77</v>
       </c>
       <c r="E216" s="4" t="n">
-        <v>51.97</v>
+        <v>41.59</v>
       </c>
       <c r="F216" s="4" t="n">
-        <v>52.97</v>
+        <v>46.99</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>EIEL</t>
+          <t>GSFC</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -6402,22 +6282,22 @@
         </is>
       </c>
       <c r="C217" s="4" t="n">
-        <v>186.96</v>
+        <v>163.11</v>
       </c>
       <c r="D217" s="4" t="n">
-        <v>40.86</v>
+        <v>38.3</v>
       </c>
       <c r="E217" s="4" t="n">
-        <v>48.28</v>
+        <v>43.69</v>
       </c>
       <c r="F217" s="4" t="n">
-        <v>39.49</v>
+        <v>45.26</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>JISLJALEQS</t>
+          <t>ZAGGLE</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -6426,22 +6306,22 @@
         </is>
       </c>
       <c r="C218" s="4" t="n">
-        <v>29.73</v>
+        <v>209.96</v>
       </c>
       <c r="D218" s="4" t="n">
-        <v>40.69</v>
+        <v>38.19</v>
       </c>
       <c r="E218" s="4" t="n">
-        <v>35.3</v>
+        <v>35.68</v>
       </c>
       <c r="F218" s="4" t="n">
-        <v>35.34</v>
+        <v>39.93</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>GANECOS</t>
+          <t>HERITGFOOD</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -6450,22 +6330,22 @@
         </is>
       </c>
       <c r="C219" s="4" t="n">
-        <v>955.6</v>
+        <v>320.8</v>
       </c>
       <c r="D219" s="4" t="n">
-        <v>40.57</v>
+        <v>38.01</v>
       </c>
       <c r="E219" s="4" t="n">
-        <v>49.13</v>
+        <v>35.71</v>
       </c>
       <c r="F219" s="4" t="n">
-        <v>44.19</v>
+        <v>42.78</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>SHAKTIPUMP</t>
+          <t>EASEMYTRIP</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -6474,22 +6354,22 @@
         </is>
       </c>
       <c r="C220" s="4" t="n">
-        <v>505</v>
+        <v>7.16</v>
       </c>
       <c r="D220" s="4" t="n">
-        <v>40.57</v>
+        <v>38</v>
       </c>
       <c r="E220" s="4" t="n">
-        <v>36.99</v>
+        <v>44.95</v>
       </c>
       <c r="F220" s="4" t="n">
-        <v>44.1</v>
+        <v>36.25</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>ZAGGLE</t>
+          <t>GANECOS</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -6498,22 +6378,22 @@
         </is>
       </c>
       <c r="C221" s="4" t="n">
-        <v>215.55</v>
+        <v>923.2</v>
       </c>
       <c r="D221" s="4" t="n">
-        <v>40.33</v>
+        <v>37.9</v>
       </c>
       <c r="E221" s="4" t="n">
-        <v>36.64</v>
+        <v>47.11</v>
       </c>
       <c r="F221" s="4" t="n">
-        <v>40.34</v>
+        <v>43.45</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>VESUVIUS</t>
+          <t>NETWORK18</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -6522,22 +6402,22 @@
         </is>
       </c>
       <c r="C222" s="4" t="n">
-        <v>466.9</v>
+        <v>31.23</v>
       </c>
       <c r="D222" s="4" t="n">
-        <v>40.14</v>
+        <v>37.82</v>
       </c>
       <c r="E222" s="4" t="n">
-        <v>45.22</v>
+        <v>34.63</v>
       </c>
       <c r="F222" s="4" t="n">
-        <v>51.33</v>
+        <v>35.72</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>HERITGFOOD</t>
+          <t>DBL</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -6546,22 +6426,22 @@
         </is>
       </c>
       <c r="C223" s="4" t="n">
-        <v>326.6</v>
+        <v>425.1</v>
       </c>
       <c r="D223" s="4" t="n">
-        <v>39.8</v>
+        <v>37.34</v>
       </c>
       <c r="E223" s="4" t="n">
-        <v>36.91</v>
+        <v>45.26</v>
       </c>
       <c r="F223" s="4" t="n">
-        <v>43.28</v>
+        <v>48.18</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>SHRIPISTON</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -6570,22 +6450,22 @@
         </is>
       </c>
       <c r="C224" s="4" t="n">
-        <v>3253.6</v>
+        <v>183.15</v>
       </c>
       <c r="D224" s="4" t="n">
-        <v>39.49</v>
+        <v>37.15</v>
       </c>
       <c r="E224" s="4" t="n">
-        <v>53.33</v>
+        <v>52.51</v>
       </c>
       <c r="F224" s="4" t="n">
-        <v>65.95</v>
+        <v>56.52</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>IFBIND</t>
+          <t>SWSOLAR</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -6594,22 +6474,22 @@
         </is>
       </c>
       <c r="C225" s="4" t="n">
-        <v>1049.1</v>
+        <v>187.58</v>
       </c>
       <c r="D225" s="4" t="n">
-        <v>38.98</v>
+        <v>37.11</v>
       </c>
       <c r="E225" s="4" t="n">
-        <v>37.65</v>
+        <v>43.61</v>
       </c>
       <c r="F225" s="4" t="n">
-        <v>44.24</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>ALLCARGO</t>
+          <t>GREENPANEL</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -6618,22 +6498,22 @@
         </is>
       </c>
       <c r="C226" s="4" t="n">
-        <v>8.6</v>
+        <v>185.57</v>
       </c>
       <c r="D226" s="4" t="n">
-        <v>38.82</v>
+        <v>37.1</v>
       </c>
       <c r="E226" s="4" t="n">
-        <v>33.27</v>
+        <v>38.18</v>
       </c>
       <c r="F226" s="4" t="n">
-        <v>27.55</v>
+        <v>38.35</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>GALLANTT</t>
+          <t>PNGJL</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -6642,22 +6522,22 @@
         </is>
       </c>
       <c r="C227" s="4" t="n">
-        <v>690</v>
+        <v>546.1</v>
       </c>
       <c r="D227" s="4" t="n">
-        <v>38.78</v>
+        <v>36.87</v>
       </c>
       <c r="E227" s="4" t="n">
-        <v>53.43</v>
+        <v>43.64</v>
       </c>
       <c r="F227" s="4" t="n">
-        <v>59.89</v>
+        <v>41.99</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>OSWALPUMPS</t>
+          <t>WESTLIFE</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -6666,22 +6546,22 @@
         </is>
       </c>
       <c r="C228" s="4" t="n">
-        <v>358.3</v>
+        <v>449.9</v>
       </c>
       <c r="D228" s="4" t="n">
-        <v>38.58</v>
+        <v>36.78</v>
       </c>
       <c r="E228" s="4" t="n">
-        <v>38.61</v>
+        <v>37.27</v>
       </c>
       <c r="F228" s="4" t="n">
-        <v/>
+        <v>29.8</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>DBL</t>
+          <t>INDIASHLTR</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -6690,22 +6570,22 @@
         </is>
       </c>
       <c r="C229" s="4" t="n">
-        <v>429.9</v>
+        <v>763.85</v>
       </c>
       <c r="D229" s="4" t="n">
-        <v>38.37</v>
+        <v>36.68</v>
       </c>
       <c r="E229" s="4" t="n">
-        <v>46.12</v>
+        <v>44.58</v>
       </c>
       <c r="F229" s="4" t="n">
-        <v>48.68</v>
+        <v>49.43</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>PCJEWELLER</t>
+          <t>ANUP</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -6714,22 +6594,22 @@
         </is>
       </c>
       <c r="C230" s="4" t="n">
-        <v>8.369999999999999</v>
+        <v>1840.4</v>
       </c>
       <c r="D230" s="4" t="n">
-        <v>38.17</v>
+        <v>36.32</v>
       </c>
       <c r="E230" s="4" t="n">
-        <v>38.17</v>
+        <v>44.35</v>
       </c>
       <c r="F230" s="4" t="n">
-        <v>45.36</v>
+        <v>45.91</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>EUREKAFORB</t>
+          <t>GALLANTT</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -6738,22 +6618,22 @@
         </is>
       </c>
       <c r="C231" s="4" t="n">
-        <v>464.45</v>
+        <v>669.45</v>
       </c>
       <c r="D231" s="4" t="n">
-        <v>38.02</v>
+        <v>36.22</v>
       </c>
       <c r="E231" s="4" t="n">
-        <v>40.11</v>
+        <v>51.6</v>
       </c>
       <c r="F231" s="4" t="n">
-        <v>41.49</v>
+        <v>58.85</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>JKLAKSHMI</t>
+          <t>IONEXCHANG</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -6762,22 +6642,22 @@
         </is>
       </c>
       <c r="C232" s="4" t="n">
-        <v>611.5</v>
+        <v>362.05</v>
       </c>
       <c r="D232" s="4" t="n">
-        <v>37.63</v>
+        <v>36.08</v>
       </c>
       <c r="E232" s="4" t="n">
-        <v>37.11</v>
+        <v>44.48</v>
       </c>
       <c r="F232" s="4" t="n">
-        <v>41.1</v>
+        <v>42.58</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>GULFOILLUB</t>
+          <t>SUNTECK</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -6786,22 +6666,22 @@
         </is>
       </c>
       <c r="C233" s="4" t="n">
-        <v>901.5</v>
+        <v>285.7</v>
       </c>
       <c r="D233" s="4" t="n">
-        <v>37.23</v>
+        <v>35.58</v>
       </c>
       <c r="E233" s="4" t="n">
-        <v>34.92</v>
+        <v>34.37</v>
       </c>
       <c r="F233" s="4" t="n">
-        <v>44.55</v>
+        <v>38.65</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>TRANSRAILL</t>
+          <t>AVANTIFEED</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -6810,22 +6690,22 @@
         </is>
       </c>
       <c r="C234" s="4" t="n">
-        <v>507.25</v>
+        <v>1203.6</v>
       </c>
       <c r="D234" s="4" t="n">
-        <v>36.49</v>
+        <v>35.14</v>
       </c>
       <c r="E234" s="4" t="n">
-        <v>42.25</v>
+        <v>52.67</v>
       </c>
       <c r="F234" s="4" t="n">
-        <v>45.01</v>
+        <v>65.36</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>SHARDACROP</t>
+          <t>ANURAS</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -6834,22 +6714,22 @@
         </is>
       </c>
       <c r="C235" s="4" t="n">
-        <v>893.1</v>
+        <v>1293.9</v>
       </c>
       <c r="D235" s="4" t="n">
-        <v>36.02</v>
+        <v>35.08</v>
       </c>
       <c r="E235" s="4" t="n">
-        <v>44.75</v>
+        <v>52.96</v>
       </c>
       <c r="F235" s="4" t="n">
-        <v>53.72</v>
+        <v>65.56999999999999</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>KSCL</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -6858,22 +6738,22 @@
         </is>
       </c>
       <c r="C236" s="4" t="n">
-        <v>534.9</v>
+        <v>866.6</v>
       </c>
       <c r="D236" s="4" t="n">
-        <v>35.17</v>
+        <v>34.46</v>
       </c>
       <c r="E236" s="4" t="n">
-        <v>40.62</v>
+        <v>44.2</v>
       </c>
       <c r="F236" s="4" t="n">
-        <v>43.58</v>
+        <v>47.05</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>BECTORFOOD</t>
+          <t>RAYMONDLSL</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -6882,22 +6762,22 @@
         </is>
       </c>
       <c r="C237" s="4" t="n">
-        <v>177.78</v>
+        <v>706.4</v>
       </c>
       <c r="D237" s="4" t="n">
-        <v>34.75</v>
+        <v>34.44</v>
       </c>
       <c r="E237" s="4" t="n">
-        <v>31.81</v>
+        <v>32.55</v>
       </c>
       <c r="F237" s="4" t="n">
-        <v>38.16</v>
+        <v>21.23</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>RENUKA</t>
+          <t>AARTIPHARM</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -6906,22 +6786,22 @@
         </is>
       </c>
       <c r="C238" s="4" t="n">
-        <v>23.85</v>
+        <v>633.25</v>
       </c>
       <c r="D238" s="4" t="n">
-        <v>34.06</v>
+        <v>34.26</v>
       </c>
       <c r="E238" s="4" t="n">
-        <v>40.2</v>
+        <v>39.88</v>
       </c>
       <c r="F238" s="4" t="n">
-        <v>37.84</v>
+        <v>47.54</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>SUNTECK</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
@@ -6930,22 +6810,22 @@
         </is>
       </c>
       <c r="C239" s="4" t="n">
-        <v>288.2</v>
+        <v>525.25</v>
       </c>
       <c r="D239" s="4" t="n">
-        <v>33.85</v>
+        <v>34.01</v>
       </c>
       <c r="E239" s="4" t="n">
-        <v>34.74</v>
+        <v>39.17</v>
       </c>
       <c r="F239" s="4" t="n">
-        <v>38.83</v>
+        <v>42.86</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>RAYMONDLSL</t>
+          <t>RALLIS</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -6954,22 +6834,22 @@
         </is>
       </c>
       <c r="C240" s="4" t="n">
-        <v>712.55</v>
+        <v>243.1</v>
       </c>
       <c r="D240" s="4" t="n">
-        <v>33.77</v>
+        <v>33.57</v>
       </c>
       <c r="E240" s="4" t="n">
-        <v>32.92</v>
+        <v>42.7</v>
       </c>
       <c r="F240" s="4" t="n">
-        <v>21.34</v>
+        <v>46.03</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>GHCL</t>
+          <t>CELLO</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
@@ -6978,16 +6858,16 @@
         </is>
       </c>
       <c r="C241" s="4" t="n">
-        <v>445.2</v>
+        <v>368.25</v>
       </c>
       <c r="D241" s="4" t="n">
-        <v>33.75</v>
+        <v>32.94</v>
       </c>
       <c r="E241" s="4" t="n">
-        <v>36.23</v>
+        <v>28.1</v>
       </c>
       <c r="F241" s="4" t="n">
-        <v>42.07</v>
+        <v>29.24</v>
       </c>
     </row>
     <row r="242">
@@ -7002,22 +6882,22 @@
         </is>
       </c>
       <c r="C242" s="4" t="n">
-        <v>710.95</v>
+        <v>696.15</v>
       </c>
       <c r="D242" s="4" t="n">
-        <v>33.49</v>
+        <v>32.27</v>
       </c>
       <c r="E242" s="4" t="n">
-        <v>37.47</v>
+        <v>36.33</v>
       </c>
       <c r="F242" s="4" t="n">
-        <v>38.86</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>JKLAKSHMI</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -7026,22 +6906,22 @@
         </is>
       </c>
       <c r="C243" s="4" t="n">
-        <v>1051.3</v>
+        <v>590.35</v>
       </c>
       <c r="D243" s="4" t="n">
-        <v>33.42</v>
+        <v>32.09</v>
       </c>
       <c r="E243" s="4" t="n">
-        <v>51.86</v>
+        <v>34.85</v>
       </c>
       <c r="F243" s="4" t="n">
-        <v>59.61</v>
+        <v>40.09</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>UJJIVANSFB</t>
+          <t>BECTORFOOD</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -7050,22 +6930,22 @@
         </is>
       </c>
       <c r="C244" s="4" t="n">
-        <v>52.49</v>
+        <v>171.71</v>
       </c>
       <c r="D244" s="4" t="n">
-        <v>33.21</v>
+        <v>31.48</v>
       </c>
       <c r="E244" s="4" t="n">
-        <v>45.37</v>
+        <v>29.86</v>
       </c>
       <c r="F244" s="4" t="n">
-        <v>54.48</v>
+        <v>37.31</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>CELLO</t>
+          <t>TRANSRAILL</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
@@ -7074,22 +6954,22 @@
         </is>
       </c>
       <c r="C245" s="4" t="n">
-        <v>382.25</v>
+        <v>479.5</v>
       </c>
       <c r="D245" s="4" t="n">
-        <v>31.89</v>
+        <v>31.26</v>
       </c>
       <c r="E245" s="4" t="n">
-        <v>30</v>
+        <v>39.09</v>
       </c>
       <c r="F245" s="4" t="n">
-        <v>29.94</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>PRSMJOHNSN</t>
+          <t>EUREKAFORB</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -7098,22 +6978,22 @@
         </is>
       </c>
       <c r="C246" s="4" t="n">
-        <v>118.8</v>
+        <v>440.25</v>
       </c>
       <c r="D246" s="4" t="n">
-        <v>31.45</v>
+        <v>30.87</v>
       </c>
       <c r="E246" s="4" t="n">
-        <v>37.7</v>
+        <v>36.62</v>
       </c>
       <c r="F246" s="4" t="n">
-        <v>41.73</v>
+        <v>39.62</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>BLACKBUCK</t>
+          <t>RENUKA</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
@@ -7122,22 +7002,22 @@
         </is>
       </c>
       <c r="C247" s="4" t="n">
-        <v>500.2</v>
+        <v>22.85</v>
       </c>
       <c r="D247" s="4" t="n">
-        <v>31.22</v>
+        <v>29.68</v>
       </c>
       <c r="E247" s="4" t="n">
-        <v>40.14</v>
+        <v>37.5</v>
       </c>
       <c r="F247" s="4" t="n">
-        <v>45.78</v>
+        <v>36.89</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>PNGJL</t>
+          <t>SANOFI</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -7146,22 +7026,22 @@
         </is>
       </c>
       <c r="C248" s="4" t="n">
-        <v>525.7</v>
+        <v>3097.1</v>
       </c>
       <c r="D248" s="4" t="n">
-        <v>29.77</v>
+        <v>27.8</v>
       </c>
       <c r="E248" s="4" t="n">
-        <v>40.87</v>
+        <v>24.64</v>
       </c>
       <c r="F248" s="4" t="n">
-        <v>40.21</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>GMMPFAUDLR</t>
+          <t>ISGEC</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
@@ -7170,22 +7050,22 @@
         </is>
       </c>
       <c r="C249" s="4" t="n">
-        <v>807.1</v>
+        <v>929.8</v>
       </c>
       <c r="D249" s="4" t="n">
-        <v>29.35</v>
+        <v>27.26</v>
       </c>
       <c r="E249" s="4" t="n">
-        <v>31.23</v>
+        <v>47.2</v>
       </c>
       <c r="F249" s="4" t="n">
-        <v>38.47</v>
+        <v>48.36</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>BAJAJELEC</t>
+          <t>GMMPFAUDLR</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
@@ -7194,22 +7074,22 @@
         </is>
       </c>
       <c r="C250" s="4" t="n">
-        <v>336.05</v>
+        <v>766.7</v>
       </c>
       <c r="D250" s="4" t="n">
-        <v>28.68</v>
+        <v>23.03</v>
       </c>
       <c r="E250" s="4" t="n">
-        <v>31.2</v>
+        <v>28.38</v>
       </c>
       <c r="F250" s="4" t="n">
-        <v>28.53</v>
+        <v>37.51</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>SANOFI</t>
+          <t>BAJAJELEC</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
@@ -7218,16 +7098,16 @@
         </is>
       </c>
       <c r="C251" s="4" t="n">
-        <v>3163.2</v>
+        <v>314.45</v>
       </c>
       <c r="D251" s="4" t="n">
-        <v>27.77</v>
+        <v>22.87</v>
       </c>
       <c r="E251" s="4" t="n">
-        <v>25.93</v>
+        <v>28.33</v>
       </c>
       <c r="F251" s="4" t="n">
-        <v>29.31</v>
+        <v>27.67</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Micro250_stocks.xlsx
+++ b/reports/Micro250_stocks.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -546,37 +546,37 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>536.15</v>
+        <v>619.25</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>89.34</v>
+        <v>82.20999999999999</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>95.06</v>
+        <v>96.06</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>88.95</v>
+        <v>90.59</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>46.37</v>
+        <v>43.64</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>221.78</v>
+        <v>246.78</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>198.93</v>
+        <v>218.92</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>4720429</v>
+        <v>4636097</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>26173</v>
+        <v>30230</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ASTRAMICRO</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -585,37 +585,37 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>1401.7</v>
+        <v>5351.9</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>81.22</v>
+        <v>78.47</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>74.8</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>71.20999999999999</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>33.4</v>
+        <v>28.8</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>1032.83</v>
+        <v>3534.7</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>1014.04</v>
+        <v>3337.59</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>959225</v>
+        <v>204219</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>13308</v>
+        <v>16635</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>GRWRHITECH</t>
+          <t>ASTRAMICRO</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -624,37 +624,37 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>6117.9</v>
+        <v>1419.5</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>73.81999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>76.63</v>
+        <v>75.42</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>66.2</v>
+        <v>71.63</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>24.82</v>
+        <v>27.96</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>4076.39</v>
+        <v>1053.32</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>3955.22</v>
+        <v>1029.74</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>156507</v>
+        <v>1086166</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>14213</v>
+        <v>13477</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>PARAS</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -663,37 +663,37 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1520.5</v>
+        <v>960.15</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>72.81</v>
+        <v>72.01000000000001</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>72.09999999999999</v>
+        <v>67.14</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>72.33</v>
+        <v>58.99</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>24.57</v>
+        <v>27.89</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>1053.96</v>
+        <v>732.88</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>1017.89</v>
+        <v>728.99</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>708369</v>
+        <v>2378812</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>10155</v>
+        <v>7738</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>SHAILY</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -702,37 +702,37 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>2989.5</v>
+        <v>1607.9</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>72.06</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>68.18000000000001</v>
+        <v>74.41</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>71.93000000000001</v>
+        <v>73.88</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>43.82</v>
+        <v>31.98</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>2257.38</v>
+        <v>1091.18</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>2187.66</v>
+        <v>1048.07</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>471763</v>
+        <v>741802</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>13750</v>
+        <v>10739</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>MTARTECH</t>
+          <t>SHAILY</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -741,37 +741,37 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>7879.5</v>
+        <v>3062.9</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>69.56</v>
+        <v>69.03</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>88.26000000000001</v>
+        <v>69.39</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>87.75</v>
+        <v>72.63</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>47.37</v>
+        <v>31.84</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>4179.5</v>
+        <v>2310.2</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3750.87</v>
+        <v>2230.96</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1540753</v>
+        <v>332096</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>24237</v>
+        <v>14088</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>SANSERA</t>
+          <t>SOUTHBANK</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -780,37 +780,37 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>2861</v>
+        <v>44</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>68.2</v>
+        <v>66.73</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>73.27</v>
+        <v>63.37</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>76.62</v>
+        <v>68.47</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>28.03</v>
+        <v>20.38</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2097.1</v>
+        <v>38.44</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1981.15</v>
+        <v>37.33</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>325488</v>
+        <v>15912561</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>17833</v>
+        <v>11518</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MIDHANI</t>
+          <t>EQUITASBNK</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -819,37 +819,37 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>420.65</v>
+        <v>73.95</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>62.05</v>
+        <v>64.88</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>63.7</v>
+        <v>62.29</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>56.13</v>
+        <v>54.46</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>32.18</v>
+        <v>25.98</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>363.94</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>363.14</v>
+        <v>64.27</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1326897</v>
+        <v>4912708</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>7880</v>
+        <v>8442</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>SUNFLAG</t>
+          <t>GRWRHITECH</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -858,37 +858,37 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>373.75</v>
+        <v>5893</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>58.01</v>
+        <v>63.5</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>68.2</v>
+        <v>72.19</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>66.03</v>
+        <v>64.48</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>28.61</v>
+        <v>24.61</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>282.38</v>
+        <v>4189.83</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>276.27</v>
+        <v>4046.71</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1430405</v>
+        <v>155227</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>6736</v>
+        <v>13691</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ZYDUSWELL</t>
+          <t>MIDHANI</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -897,37 +897,37 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>507.05</v>
+        <v>435.55</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>56.45</v>
+        <v>63.3</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>61.4</v>
+        <v>66.16</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>62.68</v>
+        <v>57.31</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>27.73</v>
+        <v>22.43</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>454.23</v>
+        <v>367.67</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>446.36</v>
+        <v>365.61</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>584585</v>
+        <v>1513301</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>16132</v>
+        <v>8160</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>CEIGALL</t>
+          <t>TIPSMUSIC</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -936,37 +936,37 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>347.15</v>
+        <v>690.95</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>56.22</v>
+        <v>63.24</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>66.37</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>63.14</v>
+        <v>62.07</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>20.13</v>
+        <v>24.52</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>293.56</v>
+        <v>585.33</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>289.67</v>
+        <v>582.74</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>781161</v>
+        <v>308431</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>6048</v>
+        <v>8833</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>ADVENZYMES</t>
+          <t>SPARC</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -975,37 +975,37 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>364</v>
+        <v>212.82</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>54.73</v>
+        <v>62.91</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>64.5</v>
+        <v>74.14</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>55.87</v>
+        <v>57.51</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>21.44</v>
+        <v>38.65</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>317.85</v>
+        <v>151.57</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>317.48</v>
+        <v>150.63</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>573927</v>
+        <v>9945647</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>4076</v>
+        <v>6906</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>STAR</t>
+          <t>AZAD</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1014,31 +1014,304 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1111.8</v>
+        <v>2207.7</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>50.57</v>
+        <v>61.87</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>65.16</v>
+        <v>65.47</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>61.3</v>
+        <v>63.97</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>36.54</v>
+        <v>29.14</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>962.2</v>
+        <v>1785.76</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>942.48</v>
+        <v>1745.76</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>378206</v>
+        <v>450312</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>10248</v>
+        <v>14258</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>MTARTECH</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>7535.5</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>58.27</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>81.86</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>83.44</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>4387.8</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>3928.21</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>1714303</v>
+      </c>
+      <c r="K15" s="4" t="n">
+        <v>23179</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>KRN</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>1216.8</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>58.07</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>63.41</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>62.77</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>75.52</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>964.52</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>928.45</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>501509</v>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>7965</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>KIRLPNU</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>1570.8</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>54.91</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>73.54000000000001</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>63.94</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>36.51</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>1286.82</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>1265.5</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>249636</v>
+      </c>
+      <c r="K17" s="4" t="n">
+        <v>10204</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>ZYDUSWELL</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>504.6</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>54.83</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>62.28</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>21.76</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>457.22</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>449.12</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>431974</v>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>16054</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>SUNFLAG</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>372.1</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>53.43</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>67.73999999999999</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>65.76000000000001</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>31.45</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>288.82</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>281.38</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>1525311</v>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>6706</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>ADVENZYMES</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>367.05</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>65.15000000000001</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>56.26</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>22.51</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>322.45</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>320.94</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>574335</v>
+      </c>
+      <c r="K20" s="4" t="n">
+        <v>4110</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>GAEL</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>155.86</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>47.07</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>60.36</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>62.08</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>49.71</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>139.81</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>135.77</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>1011467</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>7149</v>
       </c>
     </row>
   </sheetData>
@@ -1056,6 +1329,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1067,7 +1347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F251"/>
+  <dimension ref="A1:F250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1122,22 +1402,22 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>536.15</v>
+        <v>619.25</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>89.34</v>
+        <v>82.20999999999999</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>95.06</v>
+        <v>96.06</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>88.95</v>
+        <v>90.59</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>SUPRIYA</t>
+          <t>ORCHPHARMA</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -1146,22 +1426,22 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>968.7</v>
+        <v>844.25</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>87.2</v>
+        <v>79.18000000000001</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>79.01000000000001</v>
+        <v>67.11</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>67.98</v>
+        <v>51.33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>REFEX</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -1170,22 +1450,22 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>328.3</v>
+        <v>5351.9</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>81.23</v>
+        <v>78.47</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>66.18000000000001</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>53.25</v>
+        <v>80.93000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>ASTRAMICRO</t>
+          <t>SHILPAMED</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -1194,22 +1474,22 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1401.7</v>
+        <v>538.05</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>81.22</v>
+        <v>77.28</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>74.8</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>71.20999999999999</v>
+        <v>69.18000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>ORCHPHARMA</t>
+          <t>RAIN</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -1218,22 +1498,22 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>792.5</v>
+        <v>197.09</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>77.81999999999999</v>
+        <v>75.18000000000001</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>63.34</v>
+        <v>72.5</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>49.65</v>
+        <v>59.74</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>RELAXO</t>
+          <t>GANESHHOU</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1242,22 +1522,22 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>345.3</v>
+        <v>780.75</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>76.90000000000001</v>
+        <v>74.94</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>51.41</v>
+        <v>59.7</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>33.62</v>
+        <v>50.19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>RAIN</t>
+          <t>ACUTAAS</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1266,22 +1546,22 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>188.07</v>
+        <v>3328.3</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>76.44</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>70.45</v>
+        <v>79.45</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>58.28</v>
+        <v>89.43000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>SKIPPER</t>
+          <t>AJAXENGG</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -1290,22 +1570,22 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>549.35</v>
+        <v>601.75</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>75.72</v>
+        <v>73.41</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>70.18000000000001</v>
+        <v>60.2</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>62.2</v>
+        <v>51.94</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>CEMPRO</t>
+          <t>ASTRAMICRO</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1314,22 +1594,22 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1071.15</v>
+        <v>1419.5</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>75.68000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>73.98999999999999</v>
+        <v>75.42</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v/>
+        <v>71.63</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>RATEGAIN</t>
+          <t>WABAG</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -1338,22 +1618,22 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>746.45</v>
+        <v>1600.4</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>74.67</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>69.5</v>
+        <v>65.92</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>59.02</v>
+        <v>60.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>GRWRHITECH</t>
+          <t>PARAS</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1362,22 +1642,22 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>6117.9</v>
+        <v>960.15</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>73.81999999999999</v>
+        <v>72.01000000000001</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>76.63</v>
+        <v>67.14</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>66.2</v>
+        <v>58.99</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>QUESS</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1386,22 +1666,22 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>246.19</v>
+        <v>235.71</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>73.31999999999999</v>
+        <v>71.94</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>75.02</v>
+        <v>60.3</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>59.28</v>
+        <v>37.91</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>CEMPRO</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1410,22 +1690,22 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1520.5</v>
+        <v>1112.8</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>72.81</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>72.09999999999999</v>
+        <v>74.84</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>72.33</v>
+        <v>69.43000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>ACUTAAS</t>
+          <t>GREAVESCOT</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1434,22 +1714,22 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>3132.5</v>
+        <v>192.2</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>72.36</v>
+        <v>71.70999999999999</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>77.23999999999999</v>
+        <v>60.47</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v/>
+        <v>52.42</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>SHAILY</t>
+          <t>MSTCLTD</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1458,22 +1738,22 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2989.5</v>
+        <v>512.35</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>72.06</v>
+        <v>71.05</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>68.18000000000001</v>
+        <v>59.7</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>71.93000000000001</v>
+        <v>51.33</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>AJAXENGG</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1482,22 +1762,22 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>590</v>
+        <v>1607.9</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>70.41</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>58.65</v>
+        <v>74.41</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>50.69</v>
+        <v>73.88</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>THYROCARE</t>
+          <t>RATEGAIN</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1506,22 +1786,22 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>506.3</v>
+        <v>758.7</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>70.25</v>
+        <v>69.68000000000001</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>66.23999999999999</v>
+        <v>70.48</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>64.75</v>
+        <v>59.59</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>MTARTECH</t>
+          <t>SKIPPER</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1530,22 +1810,22 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>7879.5</v>
+        <v>556.6</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>69.56</v>
+        <v>69.54000000000001</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>88.26000000000001</v>
+        <v>70.92</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>87.75</v>
+        <v>62.69</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>VIYASH</t>
+          <t>TEGA</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1554,22 +1834,22 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>261.94</v>
+        <v>1847.7</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>69</v>
+        <v>69.41</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>72.34999999999999</v>
+        <v>57.11</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>64.92</v>
+        <v>58.27</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>SKYGOLD</t>
+          <t>BALAMINES</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1578,22 +1858,22 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>521</v>
+        <v>2043.3</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>68.97</v>
+        <v>69.34</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>66.42</v>
+        <v>81.06999999999999</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>70.76000000000001</v>
+        <v>58.49</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>SHILPAMED</t>
+          <t>THYROCARE</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1602,22 +1882,22 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>498.95</v>
+        <v>518</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>68.81999999999999</v>
+        <v>69.33</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>74.97</v>
+        <v>67.67</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>66.54000000000001</v>
+        <v>65.51000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>SANSERA</t>
+          <t>SHAILY</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1626,22 +1906,22 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2861</v>
+        <v>3062.9</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>68.2</v>
+        <v>69.03</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>73.27</v>
+        <v>69.39</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>76.62</v>
+        <v>72.63</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>NEOGEN</t>
+          <t>RTNINDIA</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1650,22 +1930,22 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1858.1</v>
+        <v>39.13</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>68.13</v>
+        <v>68.98</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>66.92</v>
+        <v>55.04</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>57.36</v>
+        <v>44.65</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>JINDWORLD</t>
+          <t>SANSERA</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1674,22 +1954,22 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>30.25</v>
+        <v>2945.1</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>66.45999999999999</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>55.27</v>
+        <v>74.72</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>39.46</v>
+        <v>77.43000000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>IFBIND</t>
+          <t>NEOGEN</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1698,22 +1978,22 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1252.5</v>
+        <v>1903.6</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>66.34</v>
+        <v>67.29000000000001</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>51.49</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>48.26</v>
+        <v>58.18</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>BANCOINDIA</t>
+          <t>SUPRIYA</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1722,22 +2002,22 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>656.25</v>
+        <v>947.95</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>66.09999999999999</v>
+        <v>66.84</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>55.31</v>
+        <v>75.61</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>59</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>SPARC</t>
+          <t>SOUTHBANK</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1746,22 +2026,22 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>212.11</v>
+        <v>44</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>65.95999999999999</v>
+        <v>66.73</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>74</v>
+        <v>63.37</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>57.39</v>
+        <v>68.47</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>MAXESTATES</t>
+          <t>SFL</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1770,22 +2050,22 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>444</v>
+        <v>642.75</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>65.88</v>
+        <v>66.03</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>58.39</v>
+        <v>59.63</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>51.71</v>
+        <v>44.69</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>TEGA</t>
+          <t>TVSSCS</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1794,22 +2074,22 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1766</v>
+        <v>129.67</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>65.7</v>
+        <v>65.19</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>52.03</v>
+        <v>58.16</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>55.86</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>ICIL</t>
+          <t>UNIMECH</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1818,22 +2098,22 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>312.1</v>
+        <v>1078.25</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>65.7</v>
+        <v>65.11</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>58.67</v>
+        <v>60.95</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>54.35</v>
+        <v>50.89</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENGG</t>
+          <t>HCC</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1842,22 +2122,22 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>73.61</v>
+        <v>24.02</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>65.65000000000001</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>70.18000000000001</v>
+        <v>59.6</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>58.18</v>
+        <v>48.22</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>RBA</t>
+          <t>WELENT</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1866,22 +2146,22 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>68.66</v>
+        <v>541.4</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>65.58</v>
+        <v>64.98</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>56.83</v>
+        <v>60.74</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>41.51</v>
+        <v>57.24</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>LMW</t>
+          <t>CYIENTDLM</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1890,22 +2170,22 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>15709</v>
+        <v>453.4</v>
       </c>
       <c r="D34" s="4" t="n">
         <v>64.91</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>58.29</v>
+        <v>64.42</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>53.52</v>
+        <v>47.76</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GREAVESCOT</t>
+          <t>EQUITASBNK</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1914,22 +2194,22 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>181.65</v>
+        <v>73.95</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>64.81</v>
+        <v>64.88</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>56.44</v>
+        <v>62.29</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>50.49</v>
+        <v>54.46</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>REFEX</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1938,22 +2218,22 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>4204.9</v>
+        <v>312.5</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>64.77</v>
+        <v>64.44</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>59.98</v>
+        <v>61</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>74.61</v>
+        <v>51.65</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>WABAG</t>
+          <t>OSWALPUMPS</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1962,22 +2242,22 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>1527.8</v>
+        <v>412.7</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>64.65000000000001</v>
+        <v>64.36</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>62.29</v>
+        <v>47.97</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>58.42</v>
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>PCJEWELLER</t>
+          <t>ABDL</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -1986,22 +2266,22 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>9.6</v>
+        <v>580.7</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>64.39</v>
+        <v>64.3</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>48.87</v>
+        <v>57.1</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>48.52</v>
+        <v>60.61</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>BANCOINDIA</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -2010,22 +2290,22 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>1318.6</v>
+        <v>655.45</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>63.86</v>
+        <v>63.89</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>80.15000000000001</v>
+        <v>55.19</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>84.75</v>
+        <v>58.95</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>BALAMINES</t>
+          <t>ARVIND</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -2034,22 +2314,22 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>1775.6</v>
+        <v>493.7</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>63.81</v>
+        <v>63.61</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>75.41</v>
+        <v>76.33</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>53.77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>ARVIND</t>
+          <t>GRWRHITECH</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -2058,22 +2338,22 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>473.35</v>
+        <v>5893</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>63.59</v>
+        <v>63.5</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>73.87</v>
+        <v>72.19</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>69.45999999999999</v>
+        <v>64.48</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>JSFB</t>
+          <t>OPTIEMUS</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -2082,22 +2362,22 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>495.25</v>
+        <v>453.5</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>63</v>
+        <v>63.48</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>63.88</v>
+        <v>52.75</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>55.22</v>
+        <v>49.42</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>INDIGOPNTS</t>
+          <t>ICIL</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -2106,22 +2386,22 @@
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>990.9</v>
+        <v>328.6</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>62.9</v>
+        <v>63.42</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>52.53</v>
+        <v>61.75</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>44.62</v>
+        <v>56.28</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>FDC</t>
+          <t>MIDHANI</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -2130,22 +2410,22 @@
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>405</v>
+        <v>435.55</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>62.47</v>
+        <v>63.3</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>58.01</v>
+        <v>66.16</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>49.89</v>
+        <v>57.31</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>VMART</t>
+          <t>TIPSMUSIC</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -2154,22 +2434,22 @@
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>666.75</v>
+        <v>690.95</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>62.12</v>
+        <v>63.24</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>53.79</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>47.79</v>
+        <v>62.07</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>DIACABS</t>
+          <t>CARTRADE</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -2178,22 +2458,22 @@
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>194.31</v>
+        <v>1958.4</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>62.08</v>
+        <v>63.02</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>74.06</v>
+        <v>48.6</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>66.15000000000001</v>
+        <v>53.94</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>MIDHANI</t>
+          <t>DIACABS</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -2202,22 +2482,22 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>420.65</v>
+        <v>203.6</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>62.05</v>
+        <v>62.92</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>63.7</v>
+        <v>76.52</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>56.13</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>KANSAINER</t>
+          <t>SPARC</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -2226,22 +2506,22 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>218.06</v>
+        <v>212.82</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>61.37</v>
+        <v>62.91</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>53.51</v>
+        <v>74.14</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>43.68</v>
+        <v>57.51</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>TEAMLEASE</t>
+          <t>V2RETAIL</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -2250,22 +2530,22 @@
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>1381.6</v>
+        <v>247.99</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>60.96</v>
+        <v>62.89</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>49.34</v>
+        <v>66.48</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>36.16</v>
+        <v>70.05</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>POWERMECH</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -2274,22 +2554,22 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>269.35</v>
+        <v>2601.8</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>60.72</v>
+        <v>62.32</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>69.75</v>
+        <v>59.4</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>68.03</v>
+        <v>53.37</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>RTNPOWER</t>
+          <t>VIYASH</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -2298,22 +2578,22 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>9.859999999999999</v>
+        <v>255.25</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>60.53</v>
+        <v>62.3</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>53.73</v>
+        <v>68.3</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>48.72</v>
+        <v>63.35</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GARFIBRES</t>
+          <t>AZAD</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -2322,22 +2602,22 @@
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>659.45</v>
+        <v>2207.7</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>60.42</v>
+        <v>61.87</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>50.41</v>
+        <v>65.47</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>44.12</v>
+        <v>63.97</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>SAMHI</t>
+          <t>RELAXO</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -2346,22 +2626,22 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>165.55</v>
+        <v>330.05</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>60.31</v>
+        <v>61.59</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>50.43</v>
+        <v>47.97</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>47.06</v>
+        <v>32.64</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>PGIL</t>
+          <t>MAXESTATES</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -2370,22 +2650,22 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>1653.5</v>
+        <v>444.5</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>60.23</v>
+        <v>61.49</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>55.97</v>
+        <v>58.49</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>63.2</v>
+        <v>51.75</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>JAMNAAUTO</t>
+          <t>SAFARI</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -2394,22 +2674,22 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>127.67</v>
+        <v>1633.1</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>60.01</v>
+        <v>61.46</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>54.16</v>
+        <v>45.48</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>56.88</v>
+        <v>43.87</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>HCC</t>
+          <t>INNOVACAP</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -2418,22 +2698,22 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>22.81</v>
+        <v>867.5</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>59.97</v>
+        <v>61.36</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>56.73</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>46.94</v>
+        <v>58.93</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>GANESHHOU</t>
+          <t>IFBIND</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -2442,22 +2722,22 @@
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>705.85</v>
+        <v>1255.7</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>59.51</v>
+        <v>61.19</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>50.09</v>
+        <v>51.67</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>46.18</v>
+        <v>48.33</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENT</t>
+          <t>LLOYDSENGG</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -2466,22 +2746,22 @@
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>72.06</v>
+        <v>72.69</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>59.5</v>
+        <v>61.11</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>61.54</v>
+        <v>68.69</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>58.21</v>
+        <v>58.55</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>RELIGARE</t>
+          <t>TEAMLEASE</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -2490,22 +2770,22 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>237.55</v>
+        <v>1385.3</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>59.45</v>
+        <v>61.09</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>54.21</v>
+        <v>49.69</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>51.96</v>
+        <v>36.28</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>SOUTHBANK</t>
+          <t>LMW</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -2514,22 +2794,22 @@
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>41.42</v>
+        <v>15679</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>58.99</v>
+        <v>61.04</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>58.12</v>
+        <v>58.03</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>65.98</v>
+        <v>53.41</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>CYIENTDLM</t>
+          <t>RBA</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -2538,22 +2818,22 @@
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>420.6</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>58.99</v>
+        <v>60.96</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>59.07</v>
+        <v>56.94</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>44.73</v>
+        <v>41.56</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>LUMAXTECH</t>
+          <t>SKYGOLD</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -2562,22 +2842,22 @@
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>1724.8</v>
+        <v>528.45</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>58.93</v>
+        <v>60.76</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>57.19</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>70.11</v>
+        <v>71.16</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>IIFLCAPS</t>
+          <t>CEIGALL</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -2586,22 +2866,22 @@
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>341.4</v>
+        <v>358.5</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>58.37</v>
+        <v>60.43</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>56.5</v>
+        <v>68.83</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>54.81</v>
+        <v>65.5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>INNOVACAP</t>
+          <t>VIPIND</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -2610,22 +2890,22 @@
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>850.4</v>
+        <v>329.85</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>58.35</v>
+        <v>60.38</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>63.23</v>
+        <v>46.79</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>57.88</v>
+        <v>40.15</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>V2RETAIL</t>
+          <t>GARFIBRES</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -2634,22 +2914,22 @@
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>230.03</v>
+        <v>665.5</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>58.25</v>
+        <v>59.86</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>60.59</v>
+        <v>51.52</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>67.23999999999999</v>
+        <v>44.81</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>ABDL</t>
+          <t>SURYAROSNI</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -2658,22 +2938,22 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>558.3</v>
+        <v>258.17</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>58.03</v>
+        <v>59.65</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>54.63</v>
+        <v>54.13</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>59.05</v>
+        <v>50.14</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>SUNFLAG</t>
+          <t>MARKSANS</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -2682,22 +2962,22 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>373.75</v>
+        <v>233.19</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>58.01</v>
+        <v>59.55</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>68.2</v>
+        <v>67.23999999999999</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>66.03</v>
+        <v>56.83</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>GULFOILLUB</t>
+          <t>TDPOWERSYS</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -2706,22 +2986,22 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>973.05</v>
+        <v>1312.8</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>57.89</v>
+        <v>59.48</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>44.57</v>
+        <v>79.41</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>47.86</v>
+        <v>84.26000000000001</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>TIPSMUSIC</t>
+          <t>PGIL</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -2730,22 +3010,22 @@
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>662.45</v>
+        <v>1665.6</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>57.61</v>
+        <v>59.48</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>64.04000000000001</v>
+        <v>56.51</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>60.19</v>
+        <v>63.49</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>SFL</t>
+          <t>IIFLCAPS</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -2754,22 +3034,22 @@
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>605</v>
+        <v>342.75</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>57.4</v>
+        <v>59.39</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>54.7</v>
+        <v>56.79</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>42.16</v>
+        <v>58.66</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>KIRLPNU</t>
+          <t>NETWORK18</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -2778,22 +3058,22 @@
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>1574.3</v>
+        <v>33.41</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>57.12</v>
+        <v>58.36</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>73.95999999999999</v>
+        <v>41.68</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>64.09</v>
+        <v>37.57</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>WELENT</t>
+          <t>MTARTECH</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -2802,22 +3082,22 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>517.15</v>
+        <v>7535.5</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>56.55</v>
+        <v>58.27</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>55.93</v>
+        <v>81.86</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>55.35</v>
+        <v>83.44</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>EQUITASBNK</t>
+          <t>VARROC</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -2826,22 +3106,22 @@
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>70.20999999999999</v>
+        <v>586.3</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>56.54</v>
+        <v>58.26</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>58.45</v>
+        <v>58.08</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>52.37</v>
+        <v>54.95</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>ZYDUSWELL</t>
+          <t>FINEORG</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -2850,22 +3130,22 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>507.05</v>
+        <v>4754.4</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>56.45</v>
+        <v>58.1</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>61.4</v>
+        <v>56.7</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>62.68</v>
+        <v>52.66</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>CEIGALL</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -2874,22 +3154,22 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>347.15</v>
+        <v>1216.8</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>56.22</v>
+        <v>58.07</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>66.37</v>
+        <v>63.41</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>63.14</v>
+        <v>62.77</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>HCG</t>
+          <t>FIEMIND</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -2898,16 +3178,16 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>637.25</v>
+        <v>2311.2</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>56.02</v>
+        <v>57.91</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>57.31</v>
+        <v>58.89</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>60.02</v>
+        <v>68.06999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -2922,22 +3202,22 @@
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>346.2</v>
+        <v>350.75</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>55.96</v>
+        <v>57.76</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>54.8</v>
+        <v>55.81</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>49.69</v>
+        <v>50.15</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>ARVINDFASN</t>
+          <t>LXCHEM</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -2946,22 +3226,22 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>461.35</v>
+        <v>158.66</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>55.82</v>
+        <v>57.35</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>50.66</v>
+        <v>54.27</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>50.54</v>
+        <v>41.63</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>GABRIEL</t>
+          <t>PRINCEPIPE</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -2970,22 +3250,22 @@
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>1100.1</v>
+        <v>271.15</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>55.79</v>
+        <v>57.19</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>57.74</v>
+        <v>53.23</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>64.44</v>
+        <v>39.66</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>POWERMECH</t>
+          <t>JINDWORLD</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -2994,22 +3274,22 @@
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>2500.7</v>
+        <v>29.39</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>55.77</v>
+        <v>57.1</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>56.17</v>
+        <v>53.09</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>51.92</v>
+        <v>39</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>QUESS</t>
+          <t>ARVINDFASN</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -3018,22 +3298,22 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>209.09</v>
+        <v>469.3</v>
       </c>
       <c r="D81" s="4" t="n">
-        <v>55.31</v>
+        <v>57.04</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>50.5</v>
+        <v>52.14</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>33.84</v>
+        <v>51.49</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>BBL</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -3042,22 +3322,22 @@
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>455.35</v>
+        <v>2841</v>
       </c>
       <c r="D82" s="4" t="n">
-        <v>55.29</v>
+        <v>56.94</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>53</v>
+        <v>53.4</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>58.7</v>
+        <v>49.97</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>DHANUKA</t>
+          <t>SHAKTIPUMP</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -3066,22 +3346,22 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>1134.8</v>
+        <v>540.5</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>55.29</v>
+        <v>56.9</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>50.85</v>
+        <v>42.84</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>46.15</v>
+        <v>45.87</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>WEBELSOLAR</t>
+          <t>SWSOLAR</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -3090,22 +3370,22 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>109.26</v>
+        <v>203.67</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>55.1</v>
+        <v>56.68</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>59.07</v>
+        <v>49.74</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>54.48</v>
+        <v>39.98</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>STYRENIX</t>
+          <t>DATAMATICS</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -3114,22 +3394,22 @@
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>2286</v>
+        <v>799.65</v>
       </c>
       <c r="D85" s="4" t="n">
-        <v>55.09</v>
+        <v>56.5</v>
       </c>
       <c r="E85" s="4" t="n">
-        <v>56.17</v>
+        <v>54.05</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>54.19</v>
+        <v>55.44</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>MSTCLTD</t>
+          <t>VOLTAMP</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -3138,22 +3418,22 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>440.5</v>
+        <v>9884.5</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>55</v>
+        <v>56.35</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>48.06</v>
+        <v>57.12</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>46.1</v>
+        <v>55.55</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>VARROC</t>
+          <t>WEBELSOLAR</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -3162,22 +3442,22 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>565.4</v>
+        <v>110.76</v>
       </c>
       <c r="D87" s="4" t="n">
-        <v>54.87</v>
+        <v>56.06</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>53.61</v>
+        <v>59.79</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>53.26</v>
+        <v>54.84</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>DCAL</t>
+          <t>MANORAMA</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -3186,22 +3466,22 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>194.7</v>
+        <v>1476.1</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>54.79</v>
+        <v>56.01</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>48.92</v>
+        <v>55.61</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>47.92</v>
+        <v>62.42</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>BELRISE</t>
+          <t>VMART</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -3210,22 +3490,22 @@
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>216.46</v>
+        <v>665.55</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>54.74</v>
+        <v>55.95</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>65.23</v>
+        <v>53.6</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v/>
+        <v>47.73</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>ADVENZYMES</t>
+          <t>RTNPOWER</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -3234,22 +3514,22 @@
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>364</v>
+        <v>9.74</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>54.73</v>
+        <v>55.89</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>64.5</v>
+        <v>52.55</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>55.87</v>
+        <v>48.35</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>VSTIND</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -3258,22 +3538,22 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>455.95</v>
+        <v>258.05</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>54.62</v>
+        <v>55.77</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>52.41</v>
+        <v>55.92</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>53.74</v>
+        <v>47.17</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>PARAS</t>
+          <t>KITEX</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -3282,22 +3562,22 @@
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>819.35</v>
+        <v>165.26</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>54.6</v>
+        <v>55.62</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>58.58</v>
+        <v>45.94</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>53.51</v>
+        <v>49.78</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>TANLA</t>
+          <t>KIRLPNU</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -3306,22 +3586,22 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>525.4</v>
+        <v>1570.8</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>54.1</v>
+        <v>54.91</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>53.48</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>44.68</v>
+        <v>63.94</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>TSFINV</t>
+          <t>ZYDUSWELL</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -3330,22 +3610,22 @@
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>408.9</v>
+        <v>504.6</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>53.87</v>
+        <v>54.83</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>47.94</v>
+        <v>60.7</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>53.65</v>
+        <v>62.28</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>KSL</t>
+          <t>PARADEEP</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -3354,22 +3634,22 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>826.25</v>
+        <v>127.58</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>53.4</v>
+        <v>54.72</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>58.2</v>
+        <v>47.05</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>53.43</v>
+        <v>50.37</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>POLYPLEX</t>
+          <t>SANOFICONR</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -3378,22 +3658,22 @@
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>926.1</v>
+        <v>4765.7</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>53.38</v>
+        <v>54.67</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>53.44</v>
+        <v>54.82</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>45.37</v>
+        <v>50.24</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>BOSCH-HCIL</t>
+          <t>JISLJALEQS</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -3402,22 +3682,22 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>1396.2</v>
+        <v>31.89</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>53.37</v>
+        <v>54.48</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>51.89</v>
+        <v>41.22</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v/>
+        <v>37.54</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>BIRLACORPN</t>
+          <t>BORORENEW</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -3426,22 +3706,22 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>997.3</v>
+        <v>524.3</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>53.32</v>
+        <v>54.33</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>49.12</v>
+        <v>52.98</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>43.68</v>
+        <v>51.16</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>CMSINFO</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -3450,22 +3730,22 @@
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>504.3</v>
+        <v>305.8</v>
       </c>
       <c r="D99" s="4" t="n">
-        <v>53.24</v>
+        <v>54.3</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>58.26</v>
+        <v>44.38</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>49.5</v>
+        <v>39.84</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>ORIENTCEM</t>
+          <t>JSFB</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -3474,22 +3754,22 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>141.55</v>
+        <v>477.55</v>
       </c>
       <c r="D100" s="4" t="n">
-        <v>53.03</v>
+        <v>54.19</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>37.46</v>
+        <v>59.71</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>36.27</v>
+        <v>53.05</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>BBL</t>
+          <t>HCG</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -3498,22 +3778,22 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>2784.4</v>
+        <v>635.95</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>52.91</v>
+        <v>54.02</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>52.02</v>
+        <v>56.96</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>49.23</v>
+        <v>59.87</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>GPPL</t>
+          <t>IMFA</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -3522,22 +3802,22 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>157.35</v>
+        <v>1499</v>
       </c>
       <c r="D102" s="4" t="n">
-        <v>52.91</v>
+        <v>53.9</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>47.7</v>
+        <v>59.95</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>51.28</v>
+        <v>68.40000000000001</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>CMSINFO</t>
+          <t>PCJEWELLER</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -3546,22 +3826,22 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>304.5</v>
+        <v>9.18</v>
       </c>
       <c r="D103" s="4" t="n">
-        <v>52.87</v>
+        <v>53.73</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>43.79</v>
+        <v>45.94</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>39.6</v>
+        <v>47.35</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>FIEMIND</t>
+          <t>VAIBHAVGBL</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -3570,22 +3850,22 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>2243</v>
+        <v>228.46</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>52.82</v>
+        <v>53.73</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>55.46</v>
+        <v>52.51</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>66.63</v>
+        <v>45.75</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>PATELENG</t>
+          <t>KRBL</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -3594,22 +3874,22 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>27.43</v>
+        <v>356.65</v>
       </c>
       <c r="D105" s="4" t="n">
-        <v>52.77</v>
+        <v>53.51</v>
       </c>
       <c r="E105" s="4" t="n">
-        <v>45.56</v>
+        <v>51.49</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>37.88</v>
+        <v>52.25</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>PRIVISCL</t>
+          <t>SUNFLAG</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -3618,22 +3898,22 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>3255.2</v>
+        <v>372.1</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>52.52</v>
+        <v>53.43</v>
       </c>
       <c r="E106" s="4" t="n">
-        <v>57.59</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>67.39</v>
+        <v>65.76000000000001</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>DATAMATICS</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -3642,22 +3922,22 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>766.2</v>
+        <v>1138.2</v>
       </c>
       <c r="D107" s="4" t="n">
-        <v>52.47</v>
+        <v>53.35</v>
       </c>
       <c r="E107" s="4" t="n">
-        <v>50.91</v>
+        <v>58.09</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>53.91</v>
+        <v>65.08</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>INGERRAND</t>
+          <t>ROUTE</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -3666,22 +3946,22 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>4352</v>
+        <v>525.45</v>
       </c>
       <c r="D108" s="4" t="n">
-        <v>52.41</v>
+        <v>53.27</v>
       </c>
       <c r="E108" s="4" t="n">
-        <v>61.08</v>
+        <v>42.44</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>60.43</v>
+        <v>30.24</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>SUDARSCHEM</t>
+          <t>MAHLIFE</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -3690,22 +3970,22 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>938</v>
+        <v>338.5</v>
       </c>
       <c r="D109" s="4" t="n">
-        <v>52.37</v>
+        <v>53.18</v>
       </c>
       <c r="E109" s="4" t="n">
-        <v>50.13</v>
+        <v>46.61</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>49.65</v>
+        <v>43.05</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>JKIL</t>
+          <t>SAMHI</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -3714,22 +3994,22 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>502.75</v>
+        <v>162.05</v>
       </c>
       <c r="D110" s="4" t="n">
-        <v>52.34</v>
+        <v>53.07</v>
       </c>
       <c r="E110" s="4" t="n">
-        <v>43.26</v>
+        <v>48.51</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>42.5</v>
+        <v>46.22</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>CIGNITITEC</t>
+          <t>RAYMONDLSL</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -3738,22 +4018,22 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>1260.3</v>
+        <v>767.65</v>
       </c>
       <c r="D111" s="4" t="n">
-        <v>52.32</v>
+        <v>53.03</v>
       </c>
       <c r="E111" s="4" t="n">
-        <v>44.74</v>
+        <v>39.86</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>46.95</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>PRINCEPIPE</t>
+          <t>DODLA</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -3762,22 +4042,22 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>262.15</v>
+        <v>1097.2</v>
       </c>
       <c r="D112" s="4" t="n">
-        <v>52.28</v>
+        <v>53</v>
       </c>
       <c r="E112" s="4" t="n">
-        <v>50.04</v>
+        <v>46.62</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>38.41</v>
+        <v>49.65</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>RTNINDIA</t>
+          <t>BELRISE</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -3786,22 +4066,22 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>34.95</v>
+        <v>215.98</v>
       </c>
       <c r="D113" s="4" t="n">
-        <v>52.19</v>
+        <v>52.87</v>
       </c>
       <c r="E113" s="4" t="n">
-        <v>47.18</v>
+        <v>64.87</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>41.72</v>
+        <v/>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>TVSSCS</t>
+          <t>AGI</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -3810,22 +4090,22 @@
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>117.19</v>
+        <v>598.95</v>
       </c>
       <c r="D114" s="4" t="n">
-        <v>52.01</v>
+        <v>52.7</v>
       </c>
       <c r="E114" s="4" t="n">
-        <v>51.84</v>
+        <v>46.52</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>42.34</v>
+        <v>44.79</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>VSTIND</t>
+          <t>EDELWEISS</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -3834,22 +4114,22 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>255.7</v>
+        <v>114.67</v>
       </c>
       <c r="D115" s="4" t="n">
-        <v>52.01</v>
+        <v>52.61</v>
       </c>
       <c r="E115" s="4" t="n">
-        <v>54.72</v>
+        <v>52.19</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>46.64</v>
+        <v>57.32</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>ALLCARGO</t>
+          <t>PATELENG</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -3858,22 +4138,22 @@
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>9.1</v>
+        <v>27.22</v>
       </c>
       <c r="D116" s="4" t="n">
-        <v>51.99</v>
+        <v>52.47</v>
       </c>
       <c r="E116" s="4" t="n">
-        <v>36.07</v>
+        <v>44.99</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>27.79</v>
+        <v>37.69</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>SANDUMA</t>
+          <t>GREENPANEL</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -3882,22 +4162,22 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>226.31</v>
+        <v>201.91</v>
       </c>
       <c r="D117" s="4" t="n">
-        <v>51.98</v>
+        <v>52.21</v>
       </c>
       <c r="E117" s="4" t="n">
-        <v>56.3</v>
+        <v>44.71</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>61.34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>IMAGICAA</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -3906,22 +4186,22 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>44.85</v>
+        <v>262</v>
       </c>
       <c r="D118" s="4" t="n">
-        <v>51.74</v>
+        <v>52.15</v>
       </c>
       <c r="E118" s="4" t="n">
-        <v>46.18</v>
+        <v>65.36</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>41.75</v>
+        <v>65.54000000000001</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>SHRIPISTON</t>
+          <t>KNRCON</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -3930,22 +4210,22 @@
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>3391</v>
+        <v>130.32</v>
       </c>
       <c r="D119" s="4" t="n">
-        <v>51.58</v>
+        <v>52.14</v>
       </c>
       <c r="E119" s="4" t="n">
-        <v>56.22</v>
+        <v>44.42</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>69.25</v>
+        <v>34.91</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>DYNAMATECH</t>
+          <t>SHRIPISTON</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -3954,22 +4234,22 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>11122</v>
+        <v>3406.1</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>51.52</v>
+        <v>51.95</v>
       </c>
       <c r="E120" s="4" t="n">
-        <v>57.51</v>
+        <v>56.54</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>67.78</v>
+        <v>69.43000000000001</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>PRUDENT</t>
+          <t>RATNAMANI</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -3978,22 +4258,22 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>2720.2</v>
+        <v>2614.9</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>51.43</v>
+        <v>51.88</v>
       </c>
       <c r="E121" s="4" t="n">
-        <v>55.75</v>
+        <v>55.89</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>57.63</v>
+        <v>50.19</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>PURVA</t>
+          <t>ADVENZYMES</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -4002,22 +4282,22 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>219.02</v>
+        <v>367.05</v>
       </c>
       <c r="D122" s="4" t="n">
-        <v>51.42</v>
+        <v>51.7</v>
       </c>
       <c r="E122" s="4" t="n">
-        <v>48.89</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>45.68</v>
+        <v>56.26</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>VAIBHAVGBL</t>
+          <t>MASTEK</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -4026,22 +4306,22 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>222.69</v>
+        <v>1660.1</v>
       </c>
       <c r="D123" s="4" t="n">
-        <v>51.21</v>
+        <v>51.7</v>
       </c>
       <c r="E123" s="4" t="n">
-        <v>50.43</v>
+        <v>42.89</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>44.75</v>
+        <v>40.47</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>PARADEEP</t>
+          <t>YATHARTH</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -4050,22 +4330,22 @@
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>125.96</v>
+        <v>808.9</v>
       </c>
       <c r="D124" s="4" t="n">
-        <v>51.2</v>
+        <v>50.81</v>
       </c>
       <c r="E124" s="4" t="n">
-        <v>45.92</v>
+        <v>57.59</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>49.95</v>
+        <v>61.99</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>MEDPLUS</t>
+          <t>INDIGOPNTS</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -4074,22 +4354,22 @@
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>895.2</v>
+        <v>954.2</v>
       </c>
       <c r="D125" s="4" t="n">
-        <v>51.12</v>
+        <v>50.53</v>
       </c>
       <c r="E125" s="4" t="n">
-        <v>56.31</v>
+        <v>48.84</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>57.95</v>
+        <v>43.57</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>DODLA</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -4098,22 +4378,22 @@
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>1081.1</v>
+        <v>499.75</v>
       </c>
       <c r="D126" s="4" t="n">
-        <v>50.85</v>
+        <v>50.51</v>
       </c>
       <c r="E126" s="4" t="n">
-        <v>44.59</v>
+        <v>56.88</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>48.91</v>
+        <v>49.04</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>GMRP&amp;UI</t>
+          <t>PRUDENT</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -4122,22 +4402,22 @@
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>109.52</v>
+        <v>2696.9</v>
       </c>
       <c r="D127" s="4" t="n">
-        <v>50.85</v>
+        <v>50.17</v>
       </c>
       <c r="E127" s="4" t="n">
-        <v>50.59</v>
+        <v>54.69</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>54.2</v>
+        <v>57.16</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>AGI</t>
+          <t>JAMNAAUTO</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -4146,22 +4426,22 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>589.95</v>
+        <v>121.65</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>50.71</v>
+        <v>50.16</v>
       </c>
       <c r="E128" s="4" t="n">
-        <v>45.08</v>
+        <v>50.49</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>44.3</v>
+        <v>54.47</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>MANORAMA</t>
+          <t>HEMIPROP</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -4170,22 +4450,22 @@
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>1426.4</v>
+        <v>141.07</v>
       </c>
       <c r="D129" s="4" t="n">
-        <v>50.64</v>
+        <v>50.07</v>
       </c>
       <c r="E129" s="4" t="n">
-        <v>53.24</v>
+        <v>52.25</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>61.05</v>
+        <v>49.75</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>DCAL</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -4194,22 +4474,22 @@
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>277.75</v>
+        <v>189.88</v>
       </c>
       <c r="D130" s="4" t="n">
-        <v>50.64</v>
+        <v>49.81</v>
       </c>
       <c r="E130" s="4" t="n">
-        <v>53.51</v>
+        <v>46.85</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>54.95</v>
+        <v>47.28</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>AARTIDRUGS</t>
+          <t>TANLA</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -4218,22 +4498,22 @@
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>380.4</v>
+        <v>517.15</v>
       </c>
       <c r="D131" s="4" t="n">
-        <v>50.62</v>
+        <v>49.8</v>
       </c>
       <c r="E131" s="4" t="n">
-        <v>48.52</v>
+        <v>52.11</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>44.74</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>STAR</t>
+          <t>GOKEX</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -4242,22 +4522,22 @@
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>1111.8</v>
+        <v>693.85</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>50.57</v>
+        <v>49.69</v>
       </c>
       <c r="E132" s="4" t="n">
-        <v>65.16</v>
+        <v>48.38</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>61.3</v>
+        <v>47.72</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>IXIGO</t>
+          <t>GPPL</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -4266,22 +4546,22 @@
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>168.36</v>
+        <v>155.74</v>
       </c>
       <c r="D133" s="4" t="n">
-        <v>50.28</v>
+        <v>49.55</v>
       </c>
       <c r="E133" s="4" t="n">
-        <v>39.77</v>
+        <v>46.55</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>43.01</v>
+        <v>50.74</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>FINEORG</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -4290,22 +4570,22 @@
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>4625.4</v>
+        <v>93.86</v>
       </c>
       <c r="D134" s="4" t="n">
-        <v>50.21</v>
+        <v>49.33</v>
       </c>
       <c r="E134" s="4" t="n">
-        <v>53.4</v>
+        <v>37.62</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>51.32</v>
+        <v>37.39</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>SAFARI</t>
+          <t>CCAVENUE</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -4314,22 +4594,22 @@
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>1503.7</v>
+        <v>14.01</v>
       </c>
       <c r="D135" s="4" t="n">
-        <v>49.97</v>
+        <v>49.19</v>
       </c>
       <c r="E135" s="4" t="n">
-        <v>38.19</v>
+        <v>41.73</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>40.3</v>
+        <v>38.92</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>EMBDL</t>
+          <t>PRIVISCL</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -4338,22 +4618,22 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>60.38</v>
+        <v>3230.7</v>
       </c>
       <c r="D136" s="4" t="n">
-        <v>49.82</v>
+        <v>49.06</v>
       </c>
       <c r="E136" s="4" t="n">
-        <v>47.49</v>
+        <v>56.75</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>41.64</v>
+        <v>66.79000000000001</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>GOKEX</t>
+          <t>FDC</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -4362,22 +4642,22 @@
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>691.8</v>
+        <v>381</v>
       </c>
       <c r="D137" s="4" t="n">
-        <v>49.71</v>
+        <v>49.01</v>
       </c>
       <c r="E137" s="4" t="n">
-        <v>48.17</v>
+        <v>50.49</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>47.63</v>
+        <v>46.75</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>KRBL</t>
+          <t>EPL</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -4386,16 +4666,16 @@
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>350.2</v>
+        <v>217.33</v>
       </c>
       <c r="D138" s="4" t="n">
-        <v>49.68</v>
+        <v>48.65</v>
       </c>
       <c r="E138" s="4" t="n">
-        <v>49.82</v>
+        <v>51.22</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>51.53</v>
+        <v>52.24</v>
       </c>
     </row>
     <row r="139">
@@ -4410,22 +4690,22 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>2381.5</v>
+        <v>2367.1</v>
       </c>
       <c r="D139" s="4" t="n">
-        <v>49.56</v>
+        <v>48.65</v>
       </c>
       <c r="E139" s="4" t="n">
-        <v>46.28</v>
+        <v>45.81</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>48.3</v>
+        <v>48.04</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>LUXIND</t>
+          <t>SANDUMA</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -4434,22 +4714,22 @@
         </is>
       </c>
       <c r="C140" s="4" t="n">
-        <v>1380.3</v>
+        <v>222.86</v>
       </c>
       <c r="D140" s="4" t="n">
-        <v>49.44</v>
+        <v>48.64</v>
       </c>
       <c r="E140" s="4" t="n">
-        <v>56.23</v>
+        <v>54.94</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>50.31</v>
+        <v>60.44</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>SHAKTIPUMP</t>
+          <t>PNGJL</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -4458,22 +4738,22 @@
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>524.75</v>
+        <v>572.35</v>
       </c>
       <c r="D141" s="4" t="n">
-        <v>49.42</v>
+        <v>48.51</v>
       </c>
       <c r="E141" s="4" t="n">
-        <v>40.28</v>
+        <v>47.08</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>44.97</v>
+        <v>45.36</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>WAAREERTL</t>
+          <t>LUMAXTECH</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -4482,22 +4762,22 @@
         </is>
       </c>
       <c r="C142" s="4" t="n">
-        <v>974</v>
+        <v>1664.4</v>
       </c>
       <c r="D142" s="4" t="n">
-        <v>49.32</v>
+        <v>48.48</v>
       </c>
       <c r="E142" s="4" t="n">
-        <v>51.34</v>
+        <v>54.36</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v/>
+        <v>67.67</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>NFL</t>
+          <t>PNCINFRA</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -4506,22 +4786,22 @@
         </is>
       </c>
       <c r="C143" s="4" t="n">
-        <v>76</v>
+        <v>209.91</v>
       </c>
       <c r="D143" s="4" t="n">
-        <v>49.05</v>
+        <v>48.25</v>
       </c>
       <c r="E143" s="4" t="n">
-        <v>44.67</v>
+        <v>44.68</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>44.9</v>
+        <v>39.81</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>EMIL</t>
+          <t>AARTIDRUGS</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -4530,22 +4810,22 @@
         </is>
       </c>
       <c r="C144" s="4" t="n">
-        <v>114</v>
+        <v>376.85</v>
       </c>
       <c r="D144" s="4" t="n">
-        <v>49.04</v>
+        <v>48.03</v>
       </c>
       <c r="E144" s="4" t="n">
-        <v>52.66</v>
+        <v>47.52</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>45.51</v>
+        <v>44.37</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>ALIVUS</t>
+          <t>KANSAINER</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -4554,22 +4834,22 @@
         </is>
       </c>
       <c r="C145" s="4" t="n">
-        <v>1055.5</v>
+        <v>210.89</v>
       </c>
       <c r="D145" s="4" t="n">
-        <v>48.93</v>
+        <v>48.01</v>
       </c>
       <c r="E145" s="4" t="n">
-        <v>59.9</v>
+        <v>49.58</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>59.35</v>
+        <v>42.16</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>MASTEK</t>
+          <t>BALUFORGE</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -4578,22 +4858,22 @@
         </is>
       </c>
       <c r="C146" s="4" t="n">
-        <v>1627</v>
+        <v>479.3</v>
       </c>
       <c r="D146" s="4" t="n">
-        <v>48.91</v>
+        <v>47.97</v>
       </c>
       <c r="E146" s="4" t="n">
-        <v>40.63</v>
+        <v>46.43</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>39.64</v>
+        <v>47.62</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>IMFA</t>
+          <t>TSFINV</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -4602,22 +4882,22 @@
         </is>
       </c>
       <c r="C147" s="4" t="n">
-        <v>1446.2</v>
+        <v>399.45</v>
       </c>
       <c r="D147" s="4" t="n">
-        <v>48.91</v>
+        <v>47.91</v>
       </c>
       <c r="E147" s="4" t="n">
-        <v>57.35</v>
+        <v>46.05</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>67.23999999999999</v>
+        <v>52.81</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>AZAD</t>
+          <t>GMRP&amp;UI</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -4626,22 +4906,22 @@
         </is>
       </c>
       <c r="C148" s="4" t="n">
-        <v>2016.7</v>
+        <v>108.31</v>
       </c>
       <c r="D148" s="4" t="n">
-        <v>48.87</v>
+        <v>47.89</v>
       </c>
       <c r="E148" s="4" t="n">
-        <v>59.8</v>
+        <v>49.63</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>60.7</v>
+        <v>53.71</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>MAHLIFE</t>
+          <t>INOXGREEN</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -4650,22 +4930,22 @@
         </is>
       </c>
       <c r="C149" s="4" t="n">
-        <v>332.7</v>
+        <v>173.5</v>
       </c>
       <c r="D149" s="4" t="n">
-        <v>48.82</v>
+        <v>47.83</v>
       </c>
       <c r="E149" s="4" t="n">
-        <v>44.56</v>
+        <v>49.04</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>42.16</v>
+        <v>52.15</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>KITEX</t>
+          <t>WAAREERTL</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -4674,22 +4954,22 @@
         </is>
       </c>
       <c r="C150" s="4" t="n">
-        <v>161.48</v>
+        <v>970.25</v>
       </c>
       <c r="D150" s="4" t="n">
-        <v>48.64</v>
+        <v>47.82</v>
       </c>
       <c r="E150" s="4" t="n">
-        <v>44.11</v>
+        <v>51</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>49.12</v>
+        <v/>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>VOLTAMP</t>
+          <t>BOSCH-HCIL</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -4698,22 +4978,22 @@
         </is>
       </c>
       <c r="C151" s="4" t="n">
-        <v>9497</v>
+        <v>1373.3</v>
       </c>
       <c r="D151" s="4" t="n">
-        <v>47.97</v>
+        <v>47.81</v>
       </c>
       <c r="E151" s="4" t="n">
-        <v>54.51</v>
+        <v>47.23</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>54.28</v>
+        <v>45.38</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>MANINFRA</t>
+          <t>GATEWAY</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -4722,22 +5002,22 @@
         </is>
       </c>
       <c r="C152" s="4" t="n">
-        <v>115.24</v>
+        <v>56.14</v>
       </c>
       <c r="D152" s="4" t="n">
-        <v>47.91</v>
+        <v>47.79</v>
       </c>
       <c r="E152" s="4" t="n">
-        <v>49.58</v>
+        <v>47.29</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>43.36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>HEMIPROP</t>
+          <t>DHANUKA</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -4746,22 +5026,22 @@
         </is>
       </c>
       <c r="C153" s="4" t="n">
-        <v>139.77</v>
+        <v>1095.9</v>
       </c>
       <c r="D153" s="4" t="n">
-        <v>47.67</v>
+        <v>47.75</v>
       </c>
       <c r="E153" s="4" t="n">
-        <v>51.53</v>
+        <v>47.04</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>49.36</v>
+        <v>44.98</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>UNIMECH</t>
+          <t>POLYPLEX</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -4770,22 +5050,22 @@
         </is>
       </c>
       <c r="C154" s="4" t="n">
-        <v>939</v>
+        <v>903.1</v>
       </c>
       <c r="D154" s="4" t="n">
-        <v>47.57</v>
+        <v>47.64</v>
       </c>
       <c r="E154" s="4" t="n">
-        <v>50.53</v>
+        <v>50.66</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>43.84</v>
+        <v>44.42</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>LXCHEM</t>
+          <t>EMBDL</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -4794,22 +5074,22 @@
         </is>
       </c>
       <c r="C155" s="4" t="n">
-        <v>148.08</v>
+        <v>58.59</v>
       </c>
       <c r="D155" s="4" t="n">
         <v>47.54</v>
       </c>
       <c r="E155" s="4" t="n">
-        <v>49.06</v>
+        <v>46.21</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>38.74</v>
+        <v>41.18</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>SURYAROSNI</t>
+          <t>RELIGARE</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -4818,22 +5098,22 @@
         </is>
       </c>
       <c r="C156" s="4" t="n">
-        <v>235.45</v>
+        <v>228.14</v>
       </c>
       <c r="D156" s="4" t="n">
-        <v>47.37</v>
+        <v>47.45</v>
       </c>
       <c r="E156" s="4" t="n">
-        <v>47.02</v>
+        <v>48.45</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>47.12</v>
+        <v>49.88</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>YATHARTH</t>
+          <t>MANINFRA</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -4842,22 +5122,22 @@
         </is>
       </c>
       <c r="C157" s="4" t="n">
-        <v>796.5</v>
+        <v>114.1</v>
       </c>
       <c r="D157" s="4" t="n">
-        <v>47.26</v>
+        <v>47.23</v>
       </c>
       <c r="E157" s="4" t="n">
-        <v>56.56</v>
+        <v>48.9</v>
       </c>
       <c r="F157" s="4" t="n">
-        <v>61.44</v>
+        <v>43.12</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>STARCEMENT</t>
+          <t>CSBBANK</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -4866,22 +5146,22 @@
         </is>
       </c>
       <c r="C158" s="4" t="n">
-        <v>217.95</v>
+        <v>362.05</v>
       </c>
       <c r="D158" s="4" t="n">
-        <v>47.21</v>
+        <v>47.12</v>
       </c>
       <c r="E158" s="4" t="n">
-        <v>47.66</v>
+        <v>44.35</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v>51.88</v>
+        <v>50.11</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>EDELWEISS</t>
+          <t>GAEL</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -4890,22 +5170,22 @@
         </is>
       </c>
       <c r="C159" s="4" t="n">
-        <v>112.82</v>
+        <v>155.86</v>
       </c>
       <c r="D159" s="4" t="n">
-        <v>47.17</v>
+        <v>47.07</v>
       </c>
       <c r="E159" s="4" t="n">
-        <v>50.8</v>
+        <v>60.36</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>56.64</v>
+        <v>62.08</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>RATNAMANI</t>
+          <t>KSL</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -4914,22 +5194,22 @@
         </is>
       </c>
       <c r="C160" s="4" t="n">
-        <v>2552.7</v>
+        <v>809.5</v>
       </c>
       <c r="D160" s="4" t="n">
-        <v>47.1</v>
+        <v>46.48</v>
       </c>
       <c r="E160" s="4" t="n">
-        <v>53.76</v>
+        <v>55.78</v>
       </c>
       <c r="F160" s="4" t="n">
-        <v>48.87</v>
+        <v>52.69</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>AHLUCONT</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -4938,22 +5218,22 @@
         </is>
       </c>
       <c r="C161" s="4" t="n">
-        <v>1107.3</v>
+        <v>792.95</v>
       </c>
       <c r="D161" s="4" t="n">
-        <v>46.89</v>
+        <v>46.43</v>
       </c>
       <c r="E161" s="4" t="n">
-        <v>58.24</v>
+        <v>44.69</v>
       </c>
       <c r="F161" s="4" t="n">
-        <v>59.62</v>
+        <v>46.49</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>BORORENEW</t>
+          <t>PRICOLLTD</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -4962,22 +5242,22 @@
         </is>
       </c>
       <c r="C162" s="4" t="n">
-        <v>501.75</v>
+        <v>561.35</v>
       </c>
       <c r="D162" s="4" t="n">
-        <v>46.82</v>
+        <v>46.41</v>
       </c>
       <c r="E162" s="4" t="n">
-        <v>49.74</v>
+        <v>48.28</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>49.44</v>
+        <v>56.91</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>PRICOLLTD</t>
+          <t>ANURAS</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -4986,22 +5266,22 @@
         </is>
       </c>
       <c r="C163" s="4" t="n">
-        <v>562.1</v>
+        <v>1328.2</v>
       </c>
       <c r="D163" s="4" t="n">
-        <v>46.79</v>
+        <v>46.24</v>
       </c>
       <c r="E163" s="4" t="n">
-        <v>48.39</v>
+        <v>56.97</v>
       </c>
       <c r="F163" s="4" t="n">
-        <v>56.99</v>
+        <v>67.03</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>VIPIND</t>
+          <t>CIEINDIA</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -5010,22 +5290,22 @@
         </is>
       </c>
       <c r="C164" s="4" t="n">
-        <v>299.4</v>
+        <v>452.05</v>
       </c>
       <c r="D164" s="4" t="n">
-        <v>46.72</v>
+        <v>46.22</v>
       </c>
       <c r="E164" s="4" t="n">
-        <v>34.97</v>
+        <v>52.32</v>
       </c>
       <c r="F164" s="4" t="n">
-        <v>35.17</v>
+        <v>53.39</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>JKPAPER</t>
+          <t>ANUP</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -5034,22 +5314,22 @@
         </is>
       </c>
       <c r="C165" s="4" t="n">
-        <v>369.15</v>
+        <v>1915.3</v>
       </c>
       <c r="D165" s="4" t="n">
-        <v>46.58</v>
+        <v>46.18</v>
       </c>
       <c r="E165" s="4" t="n">
-        <v>53.49</v>
+        <v>47.34</v>
       </c>
       <c r="F165" s="4" t="n">
-        <v>51.16</v>
+        <v>47.3</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>SANOFICONR</t>
+          <t>VESUVIUS</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -5058,22 +5338,22 @@
         </is>
       </c>
       <c r="C166" s="4" t="n">
-        <v>4588.5</v>
+        <v>473.65</v>
       </c>
       <c r="D166" s="4" t="n">
-        <v>46.35</v>
+        <v>46.12</v>
       </c>
       <c r="E166" s="4" t="n">
-        <v>50.28</v>
+        <v>47.04</v>
       </c>
       <c r="F166" s="4" t="n">
-        <v>46.95</v>
+        <v>52.04</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>KNRCON</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -5082,22 +5362,22 @@
         </is>
       </c>
       <c r="C167" s="4" t="n">
-        <v>126.66</v>
+        <v>271.5</v>
       </c>
       <c r="D167" s="4" t="n">
-        <v>46.26</v>
+        <v>45.98</v>
       </c>
       <c r="E167" s="4" t="n">
-        <v>42</v>
+        <v>51.41</v>
       </c>
       <c r="F167" s="4" t="n">
-        <v>33.92</v>
+        <v>53.63</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>GATEWAY</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -5106,22 +5386,22 @@
         </is>
       </c>
       <c r="C168" s="4" t="n">
-        <v>56</v>
+        <v>438.65</v>
       </c>
       <c r="D168" s="4" t="n">
-        <v>46.17</v>
+        <v>45.96</v>
       </c>
       <c r="E168" s="4" t="n">
-        <v>46.97</v>
+        <v>46.94</v>
       </c>
       <c r="F168" s="4" t="n">
-        <v>40.83</v>
+        <v>51.28</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>EMUDHRA</t>
+          <t>DYNAMATECH</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -5130,22 +5410,22 @@
         </is>
       </c>
       <c r="C169" s="4" t="n">
-        <v>469.05</v>
+        <v>10544</v>
       </c>
       <c r="D169" s="4" t="n">
-        <v>46.14</v>
+        <v>45.92</v>
       </c>
       <c r="E169" s="4" t="n">
-        <v>41.5</v>
+        <v>53.61</v>
       </c>
       <c r="F169" s="4" t="n">
-        <v>39.76</v>
+        <v>63.82</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>ROUTE</t>
+          <t>LLOYDSENT</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -5154,22 +5434,22 @@
         </is>
       </c>
       <c r="C170" s="4" t="n">
-        <v>507.55</v>
+        <v>66.86</v>
       </c>
       <c r="D170" s="4" t="n">
-        <v>46.08</v>
+        <v>45.65</v>
       </c>
       <c r="E170" s="4" t="n">
-        <v>38.86</v>
+        <v>55.22</v>
       </c>
       <c r="F170" s="4" t="n">
-        <v>28.96</v>
+        <v>54.94</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>JUSTDIAL</t>
+          <t>STYRENIX</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -5178,22 +5458,22 @@
         </is>
       </c>
       <c r="C171" s="4" t="n">
-        <v>524.6</v>
+        <v>2201.2</v>
       </c>
       <c r="D171" s="4" t="n">
-        <v>45.93</v>
+        <v>45.61</v>
       </c>
       <c r="E171" s="4" t="n">
-        <v>34.55</v>
+        <v>51.99</v>
       </c>
       <c r="F171" s="4" t="n">
-        <v>34.63</v>
+        <v>52.12</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>OPTIEMUS</t>
+          <t>TEXRAIL</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -5202,22 +5482,22 @@
         </is>
       </c>
       <c r="C172" s="4" t="n">
-        <v>405.3</v>
+        <v>104.37</v>
       </c>
       <c r="D172" s="4" t="n">
-        <v>45.66</v>
+        <v>45.51</v>
       </c>
       <c r="E172" s="4" t="n">
-        <v>45.25</v>
+        <v>43.8</v>
       </c>
       <c r="F172" s="4" t="n">
-        <v>46.4</v>
+        <v>42.52</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>TARC</t>
+          <t>LUXIND</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -5226,22 +5506,22 @@
         </is>
       </c>
       <c r="C173" s="4" t="n">
-        <v>129.76</v>
+        <v>1343.4</v>
       </c>
       <c r="D173" s="4" t="n">
-        <v>45.51</v>
+        <v>45.48</v>
       </c>
       <c r="E173" s="4" t="n">
-        <v>42.5</v>
+        <v>54.65</v>
       </c>
       <c r="F173" s="4" t="n">
-        <v>46.23</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>ENTERO</t>
+          <t>VINATIORGA</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -5250,22 +5530,22 @@
         </is>
       </c>
       <c r="C174" s="4" t="n">
-        <v>1195.8</v>
+        <v>1304.1</v>
       </c>
       <c r="D174" s="4" t="n">
-        <v>45.31</v>
+        <v>45.42</v>
       </c>
       <c r="E174" s="4" t="n">
-        <v>51.21</v>
+        <v>36.68</v>
       </c>
       <c r="F174" s="4" t="n">
-        <v>52.36</v>
+        <v>35.48</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>CARTRADE</t>
+          <t>JUSTDIAL</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -5274,22 +5554,22 @@
         </is>
       </c>
       <c r="C175" s="4" t="n">
-        <v>1735.2</v>
+        <v>523.6</v>
       </c>
       <c r="D175" s="4" t="n">
-        <v>45.24</v>
+        <v>45.29</v>
       </c>
       <c r="E175" s="4" t="n">
-        <v>41.33</v>
+        <v>34.42</v>
       </c>
       <c r="F175" s="4" t="n">
-        <v>49.75</v>
+        <v>34.58</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>HIKAL</t>
+          <t>EMIL</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -5298,22 +5578,22 @@
         </is>
       </c>
       <c r="C176" s="4" t="n">
-        <v>195.28</v>
+        <v>111.44</v>
       </c>
       <c r="D176" s="4" t="n">
-        <v>45.13</v>
+        <v>45.19</v>
       </c>
       <c r="E176" s="4" t="n">
-        <v>46.13</v>
+        <v>50.58</v>
       </c>
       <c r="F176" s="4" t="n">
-        <v>38.16</v>
+        <v>44.93</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>CCAVENUE</t>
+          <t>SUDARSCHEM</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -5322,22 +5602,22 @@
         </is>
       </c>
       <c r="C177" s="4" t="n">
-        <v>13.89</v>
+        <v>886.65</v>
       </c>
       <c r="D177" s="4" t="n">
-        <v>45.01</v>
+        <v>45.17</v>
       </c>
       <c r="E177" s="4" t="n">
-        <v>40.9</v>
+        <v>46.13</v>
       </c>
       <c r="F177" s="4" t="n">
-        <v>38.58</v>
+        <v>47.52</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>AWFIS</t>
+          <t>EPIGRAL</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -5346,22 +5626,22 @@
         </is>
       </c>
       <c r="C178" s="4" t="n">
-        <v>327.9</v>
+        <v>1163.9</v>
       </c>
       <c r="D178" s="4" t="n">
-        <v>44.99</v>
+        <v>45.05</v>
       </c>
       <c r="E178" s="4" t="n">
-        <v>41.45</v>
+        <v>48.24</v>
       </c>
       <c r="F178" s="4" t="n">
-        <v>33.65</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>BALUFORGE</t>
+          <t>EMUDHRA</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -5370,22 +5650,22 @@
         </is>
       </c>
       <c r="C179" s="4" t="n">
-        <v>475.9</v>
+        <v>465.95</v>
       </c>
       <c r="D179" s="4" t="n">
-        <v>44.97</v>
+        <v>44.49</v>
       </c>
       <c r="E179" s="4" t="n">
-        <v>45.93</v>
+        <v>40.99</v>
       </c>
       <c r="F179" s="4" t="n">
-        <v>47.43</v>
+        <v>39.58</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>AURIONPRO</t>
+          <t>INDIAGLYCO</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -5394,22 +5674,22 @@
         </is>
       </c>
       <c r="C180" s="4" t="n">
-        <v>794.8</v>
+        <v>978.4</v>
       </c>
       <c r="D180" s="4" t="n">
-        <v>44.89</v>
+        <v>44.48</v>
       </c>
       <c r="E180" s="4" t="n">
-        <v>39.73</v>
+        <v>52.06</v>
       </c>
       <c r="F180" s="4" t="n">
-        <v>40.4</v>
+        <v>58.96</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>TEXRAIL</t>
+          <t>BIRLACORPN</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -5418,22 +5698,22 @@
         </is>
       </c>
       <c r="C181" s="4" t="n">
-        <v>104.37</v>
+        <v>964.05</v>
       </c>
       <c r="D181" s="4" t="n">
-        <v>44.58</v>
+        <v>44.42</v>
       </c>
       <c r="E181" s="4" t="n">
-        <v>43.8</v>
+        <v>46.01</v>
       </c>
       <c r="F181" s="4" t="n">
-        <v>42.52</v>
+        <v>42.31</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>SHAREINDIA</t>
+          <t>IMAGICAA</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -5442,22 +5722,22 @@
         </is>
       </c>
       <c r="C182" s="4" t="n">
-        <v>138.09</v>
+        <v>43.55</v>
       </c>
       <c r="D182" s="4" t="n">
-        <v>44.49</v>
+        <v>44.28</v>
       </c>
       <c r="E182" s="4" t="n">
-        <v>45.43</v>
+        <v>44.01</v>
       </c>
       <c r="F182" s="4" t="n">
-        <v>40.13</v>
+        <v>40.87</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>VINATIORGA</t>
+          <t>PURVA</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -5466,22 +5746,22 @@
         </is>
       </c>
       <c r="C183" s="4" t="n">
-        <v>1301.1</v>
+        <v>210.44</v>
       </c>
       <c r="D183" s="4" t="n">
-        <v>44.37</v>
+        <v>44.13</v>
       </c>
       <c r="E183" s="4" t="n">
-        <v>36.27</v>
+        <v>46.08</v>
       </c>
       <c r="F183" s="4" t="n">
-        <v>35.31</v>
+        <v>44.52</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>MOIL</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -5490,22 +5770,22 @@
         </is>
       </c>
       <c r="C184" s="4" t="n">
-        <v>1098</v>
+        <v>297.8</v>
       </c>
       <c r="D184" s="4" t="n">
-        <v>44.32</v>
+        <v>43.99</v>
       </c>
       <c r="E184" s="4" t="n">
-        <v>55.31</v>
+        <v>45.09</v>
       </c>
       <c r="F184" s="4" t="n">
-        <v>63.15</v>
+        <v>47.35</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>SHARDAMOTR</t>
+          <t>TARC</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -5514,22 +5794,22 @@
         </is>
       </c>
       <c r="C185" s="4" t="n">
-        <v>843.3</v>
+        <v>128.91</v>
       </c>
       <c r="D185" s="4" t="n">
-        <v>44.22</v>
+        <v>43.83</v>
       </c>
       <c r="E185" s="4" t="n">
-        <v>45.4</v>
+        <v>41.99</v>
       </c>
       <c r="F185" s="4" t="n">
-        <v>42.74</v>
+        <v>46.04</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>EIEL</t>
+          <t>DBL</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -5538,22 +5818,22 @@
         </is>
       </c>
       <c r="C186" s="4" t="n">
-        <v>190.02</v>
+        <v>428.45</v>
       </c>
       <c r="D186" s="4" t="n">
-        <v>43.8</v>
+        <v>43.73</v>
       </c>
       <c r="E186" s="4" t="n">
-        <v>49.31</v>
+        <v>46.02</v>
       </c>
       <c r="F186" s="4" t="n">
-        <v>39.96</v>
+        <v>48.57</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>KPIGREEN</t>
+          <t>ALLCARGO</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -5562,22 +5842,22 @@
         </is>
       </c>
       <c r="C187" s="4" t="n">
-        <v>420.95</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D187" s="4" t="n">
-        <v>43.77</v>
+        <v>43.68</v>
       </c>
       <c r="E187" s="4" t="n">
-        <v>48.74</v>
+        <v>35.12</v>
       </c>
       <c r="F187" s="4" t="n">
-        <v>50.03</v>
+        <v>27.63</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>JAIBALAJI</t>
+          <t>JKPAPER</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -5586,22 +5866,22 @@
         </is>
       </c>
       <c r="C188" s="4" t="n">
-        <v>72.37</v>
+        <v>359.8</v>
       </c>
       <c r="D188" s="4" t="n">
-        <v>43.71</v>
+        <v>43.52</v>
       </c>
       <c r="E188" s="4" t="n">
-        <v>48.45</v>
+        <v>50.02</v>
       </c>
       <c r="F188" s="4" t="n">
-        <v>42.04</v>
+        <v>49.94</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>TIMETECHNO</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -5610,22 +5890,22 @@
         </is>
       </c>
       <c r="C189" s="4" t="n">
-        <v>174.71</v>
+        <v>175.42</v>
       </c>
       <c r="D189" s="4" t="n">
-        <v>43.65</v>
+        <v>43.34</v>
       </c>
       <c r="E189" s="4" t="n">
-        <v>44.4</v>
+        <v>50</v>
       </c>
       <c r="F189" s="4" t="n">
-        <v>50.11</v>
+        <v>57.57</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>INOXGREEN</t>
+          <t>AURIONPRO</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -5634,22 +5914,22 @@
         </is>
       </c>
       <c r="C190" s="4" t="n">
-        <v>172.41</v>
+        <v>778</v>
       </c>
       <c r="D190" s="4" t="n">
-        <v>43.4</v>
+        <v>43.22</v>
       </c>
       <c r="E190" s="4" t="n">
-        <v>48.6</v>
+        <v>38.74</v>
       </c>
       <c r="F190" s="4" t="n">
-        <v>51.99</v>
+        <v>39.93</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>INDIAGLYCO</t>
+          <t>MEDPLUS</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -5658,22 +5938,22 @@
         </is>
       </c>
       <c r="C191" s="4" t="n">
-        <v>975</v>
+        <v>858.7</v>
       </c>
       <c r="D191" s="4" t="n">
         <v>43.11</v>
       </c>
       <c r="E191" s="4" t="n">
-        <v>51.78</v>
+        <v>50.44</v>
       </c>
       <c r="F191" s="4" t="n">
-        <v>58.84</v>
+        <v>54.14</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>HGINFRA</t>
+          <t>SUBROS</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -5682,22 +5962,22 @@
         </is>
       </c>
       <c r="C192" s="4" t="n">
-        <v>583.65</v>
+        <v>718.85</v>
       </c>
       <c r="D192" s="4" t="n">
-        <v>43.06</v>
+        <v>43.09</v>
       </c>
       <c r="E192" s="4" t="n">
-        <v>41.44</v>
+        <v>43.18</v>
       </c>
       <c r="F192" s="4" t="n">
-        <v>37.07</v>
+        <v>49.85</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>MOIL</t>
+          <t>ALIVUS</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -5706,22 +5986,22 @@
         </is>
       </c>
       <c r="C193" s="4" t="n">
-        <v>297.45</v>
+        <v>1032.5</v>
       </c>
       <c r="D193" s="4" t="n">
-        <v>42.89</v>
+        <v>42.72</v>
       </c>
       <c r="E193" s="4" t="n">
-        <v>44.97</v>
+        <v>56.01</v>
       </c>
       <c r="F193" s="4" t="n">
-        <v>47.3</v>
+        <v>57.49</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>GAEL</t>
+          <t>SANOFI</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -5730,22 +6010,22 @@
         </is>
       </c>
       <c r="C194" s="4" t="n">
-        <v>154.89</v>
+        <v>3186.4</v>
       </c>
       <c r="D194" s="4" t="n">
-        <v>42.81</v>
+        <v>42.72</v>
       </c>
       <c r="E194" s="4" t="n">
-        <v>59.81</v>
+        <v>29.73</v>
       </c>
       <c r="F194" s="4" t="n">
-        <v>61.73</v>
+        <v>30.31</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>UJJIVANSFB</t>
+          <t>CELLO</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -5754,22 +6034,22 @@
         </is>
       </c>
       <c r="C195" s="4" t="n">
-        <v>54.39</v>
+        <v>382.1</v>
       </c>
       <c r="D195" s="4" t="n">
-        <v>42.77</v>
+        <v>42.56</v>
       </c>
       <c r="E195" s="4" t="n">
-        <v>48.29</v>
+        <v>32.65</v>
       </c>
       <c r="F195" s="4" t="n">
-        <v>56.17</v>
+        <v>30.96</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>SUBROS</t>
+          <t>HIKAL</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -5778,22 +6058,22 @@
         </is>
       </c>
       <c r="C196" s="4" t="n">
-        <v>720.6</v>
+        <v>189.62</v>
       </c>
       <c r="D196" s="4" t="n">
-        <v>42.28</v>
+        <v>42.53</v>
       </c>
       <c r="E196" s="4" t="n">
-        <v>43.36</v>
+        <v>44.33</v>
       </c>
       <c r="F196" s="4" t="n">
-        <v>49.93</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>TIMETECHNO</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -5802,22 +6082,22 @@
         </is>
       </c>
       <c r="C197" s="4" t="n">
-        <v>175.33</v>
+        <v>172.44</v>
       </c>
       <c r="D197" s="4" t="n">
-        <v>42.12</v>
+        <v>42.07</v>
       </c>
       <c r="E197" s="4" t="n">
-        <v>49.93</v>
+        <v>43.38</v>
       </c>
       <c r="F197" s="4" t="n">
-        <v>57.55</v>
+        <v>49.59</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>JISLJALEQS</t>
+          <t>WESTLIFE</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -5826,22 +6106,22 @@
         </is>
       </c>
       <c r="C198" s="4" t="n">
-        <v>29.85</v>
+        <v>444.2</v>
       </c>
       <c r="D198" s="4" t="n">
-        <v>42.06</v>
+        <v>41.85</v>
       </c>
       <c r="E198" s="4" t="n">
-        <v>35.63</v>
+        <v>36.33</v>
       </c>
       <c r="F198" s="4" t="n">
-        <v>35.41</v>
+        <v>29.44</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>AHLUCONT</t>
+          <t>UJJIVANSFB</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -5850,22 +6130,22 @@
         </is>
       </c>
       <c r="C199" s="4" t="n">
-        <v>792</v>
+        <v>53.56</v>
       </c>
       <c r="D199" s="4" t="n">
-        <v>42.02</v>
+        <v>41.76</v>
       </c>
       <c r="E199" s="4" t="n">
-        <v>44.57</v>
+        <v>47.11</v>
       </c>
       <c r="F199" s="4" t="n">
-        <v>46.44</v>
+        <v>55.36</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>EPIGRAL</t>
+          <t>GANECOS</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -5874,22 +6154,22 @@
         </is>
       </c>
       <c r="C200" s="4" t="n">
-        <v>1160.9</v>
+        <v>929.55</v>
       </c>
       <c r="D200" s="4" t="n">
-        <v>41.88</v>
+        <v>41.73</v>
       </c>
       <c r="E200" s="4" t="n">
-        <v>47.73</v>
+        <v>47.57</v>
       </c>
       <c r="F200" s="4" t="n">
-        <v>44</v>
+        <v>43.65</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>PNCINFRA</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -5898,22 +6178,22 @@
         </is>
       </c>
       <c r="C201" s="4" t="n">
-        <v>204.8</v>
+        <v>184.69</v>
       </c>
       <c r="D201" s="4" t="n">
-        <v>41.81</v>
+        <v>41.72</v>
       </c>
       <c r="E201" s="4" t="n">
-        <v>42.15</v>
+        <v>47.53</v>
       </c>
       <c r="F201" s="4" t="n">
-        <v>38.9</v>
+        <v>39.09</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>NESCO</t>
+          <t>GULFOILLUB</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -5922,22 +6202,22 @@
         </is>
       </c>
       <c r="C202" s="4" t="n">
-        <v>1173.6</v>
+        <v>905.9</v>
       </c>
       <c r="D202" s="4" t="n">
-        <v>41.8</v>
+        <v>41.65</v>
       </c>
       <c r="E202" s="4" t="n">
-        <v>49.12</v>
+        <v>38.76</v>
       </c>
       <c r="F202" s="4" t="n">
-        <v>55.78</v>
+        <v>44.52</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>EPL</t>
+          <t>GRINFRA</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -5946,22 +6226,22 @@
         </is>
       </c>
       <c r="C203" s="4" t="n">
-        <v>213.65</v>
+        <v>888.3</v>
       </c>
       <c r="D203" s="4" t="n">
-        <v>41.78</v>
+        <v>41.59</v>
       </c>
       <c r="E203" s="4" t="n">
-        <v>49.53</v>
+        <v>41.47</v>
       </c>
       <c r="F203" s="4" t="n">
-        <v>51.35</v>
+        <v>38.85</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>CSBBANK</t>
+          <t>NFL</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -5970,22 +6250,22 @@
         </is>
       </c>
       <c r="C204" s="4" t="n">
-        <v>352.85</v>
+        <v>73.84</v>
       </c>
       <c r="D204" s="4" t="n">
-        <v>41.75</v>
+        <v>41.56</v>
       </c>
       <c r="E204" s="4" t="n">
-        <v>41.78</v>
+        <v>41.56</v>
       </c>
       <c r="F204" s="4" t="n">
-        <v>48.87</v>
+        <v>44.03</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>VESUVIUS</t>
+          <t>INGERRAND</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -5994,22 +6274,22 @@
         </is>
       </c>
       <c r="C205" s="4" t="n">
-        <v>468.25</v>
+        <v>3960.6</v>
       </c>
       <c r="D205" s="4" t="n">
-        <v>41.74</v>
+        <v>41.22</v>
       </c>
       <c r="E205" s="4" t="n">
-        <v>45.57</v>
+        <v>50.21</v>
       </c>
       <c r="F205" s="4" t="n">
-        <v>51.47</v>
+        <v>54.21</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>ELECTCAST</t>
+          <t>PRSMJOHNSN</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -6018,22 +6298,22 @@
         </is>
       </c>
       <c r="C206" s="4" t="n">
-        <v>77.13</v>
+        <v>119.31</v>
       </c>
       <c r="D206" s="4" t="n">
-        <v>41.6</v>
+        <v>41.21</v>
       </c>
       <c r="E206" s="4" t="n">
-        <v>46.86</v>
+        <v>38.81</v>
       </c>
       <c r="F206" s="4" t="n">
-        <v>42.64</v>
+        <v>41.85</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>OSWALPUMPS</t>
+          <t>ASHOKA</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -6042,22 +6322,22 @@
         </is>
       </c>
       <c r="C207" s="4" t="n">
-        <v>362.05</v>
+        <v>122.36</v>
       </c>
       <c r="D207" s="4" t="n">
-        <v>41.49</v>
+        <v>41.16</v>
       </c>
       <c r="E207" s="4" t="n">
-        <v>39.32</v>
+        <v>37.68</v>
       </c>
       <c r="F207" s="4" t="n">
-        <v/>
+        <v>41.97</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>PARKHOTELS</t>
+          <t>SHAREINDIA</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -6066,22 +6346,22 @@
         </is>
       </c>
       <c r="C208" s="4" t="n">
-        <v>116.32</v>
+        <v>135.29</v>
       </c>
       <c r="D208" s="4" t="n">
-        <v>41.22</v>
+        <v>41.04</v>
       </c>
       <c r="E208" s="4" t="n">
-        <v>42.71</v>
+        <v>43.95</v>
       </c>
       <c r="F208" s="4" t="n">
-        <v>37.35</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>AWFIS</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -6090,22 +6370,22 @@
         </is>
       </c>
       <c r="C209" s="4" t="n">
-        <v>90.91</v>
+        <v>312.75</v>
       </c>
       <c r="D209" s="4" t="n">
-        <v>40.91</v>
+        <v>40.72</v>
       </c>
       <c r="E209" s="4" t="n">
-        <v>35.06</v>
+        <v>39.49</v>
       </c>
       <c r="F209" s="4" t="n">
-        <v>36.32</v>
+        <v>32.74</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>PRSMJOHNSN</t>
+          <t>IXIGO</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -6114,22 +6394,22 @@
         </is>
       </c>
       <c r="C210" s="4" t="n">
-        <v>120.42</v>
+        <v>155.55</v>
       </c>
       <c r="D210" s="4" t="n">
-        <v>40.77</v>
+        <v>40.66</v>
       </c>
       <c r="E210" s="4" t="n">
-        <v>39.75</v>
+        <v>35.86</v>
       </c>
       <c r="F210" s="4" t="n">
-        <v>42.2</v>
+        <v>39.93</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>CIEINDIA</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -6138,22 +6418,22 @@
         </is>
       </c>
       <c r="C211" s="4" t="n">
-        <v>446.45</v>
+        <v>184.39</v>
       </c>
       <c r="D211" s="4" t="n">
-        <v>40.71</v>
+        <v>40.58</v>
       </c>
       <c r="E211" s="4" t="n">
-        <v>50.76</v>
+        <v>53.05</v>
       </c>
       <c r="F211" s="4" t="n">
-        <v>52.62</v>
+        <v>56.83</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>GRINFRA</t>
+          <t>JAIBALAJI</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -6162,22 +6442,22 @@
         </is>
       </c>
       <c r="C212" s="4" t="n">
-        <v>899.7</v>
+        <v>69.56</v>
       </c>
       <c r="D212" s="4" t="n">
-        <v>40.65</v>
+        <v>40.06</v>
       </c>
       <c r="E212" s="4" t="n">
-        <v>42.57</v>
+        <v>46.31</v>
       </c>
       <c r="F212" s="4" t="n">
-        <v>39.23</v>
+        <v>41.39</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>GHCL</t>
+          <t>HERITGFOOD</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -6186,22 +6466,22 @@
         </is>
       </c>
       <c r="C213" s="4" t="n">
-        <v>454.15</v>
+        <v>320.15</v>
       </c>
       <c r="D213" s="4" t="n">
-        <v>40.6</v>
+        <v>40.04</v>
       </c>
       <c r="E213" s="4" t="n">
-        <v>38.64</v>
+        <v>35.56</v>
       </c>
       <c r="F213" s="4" t="n">
-        <v>42.66</v>
+        <v>42.72</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>ASHOKA</t>
+          <t>JKIL</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -6210,22 +6490,22 @@
         </is>
       </c>
       <c r="C214" s="4" t="n">
-        <v>122.39</v>
+        <v>483.4</v>
       </c>
       <c r="D214" s="4" t="n">
-        <v>40.05</v>
+        <v>39.89</v>
       </c>
       <c r="E214" s="4" t="n">
-        <v>37.7</v>
+        <v>39.7</v>
       </c>
       <c r="F214" s="4" t="n">
-        <v>41.98</v>
+        <v>41</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>SHARDACROP</t>
+          <t>GSFC</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -6234,22 +6514,22 @@
         </is>
       </c>
       <c r="C215" s="4" t="n">
-        <v>905</v>
+        <v>162.54</v>
       </c>
       <c r="D215" s="4" t="n">
-        <v>39.26</v>
+        <v>39.68</v>
       </c>
       <c r="E215" s="4" t="n">
-        <v>45.53</v>
+        <v>43.31</v>
       </c>
       <c r="F215" s="4" t="n">
-        <v>54.1</v>
+        <v>45.12</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>BLACKBUCK</t>
+          <t>PARKHOTELS</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -6258,22 +6538,22 @@
         </is>
       </c>
       <c r="C216" s="4" t="n">
-        <v>510.55</v>
+        <v>114.2</v>
       </c>
       <c r="D216" s="4" t="n">
-        <v>38.77</v>
+        <v>39.56</v>
       </c>
       <c r="E216" s="4" t="n">
-        <v>41.59</v>
+        <v>41.18</v>
       </c>
       <c r="F216" s="4" t="n">
-        <v>46.99</v>
+        <v>36.74</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>GSFC</t>
+          <t>TRANSRAILL</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -6282,22 +6562,22 @@
         </is>
       </c>
       <c r="C217" s="4" t="n">
-        <v>163.11</v>
+        <v>493.25</v>
       </c>
       <c r="D217" s="4" t="n">
-        <v>38.3</v>
+        <v>39.42</v>
       </c>
       <c r="E217" s="4" t="n">
-        <v>43.69</v>
+        <v>41.43</v>
       </c>
       <c r="F217" s="4" t="n">
-        <v>45.26</v>
+        <v>44.43</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>ZAGGLE</t>
+          <t>ORIENTCEM</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -6306,22 +6586,22 @@
         </is>
       </c>
       <c r="C218" s="4" t="n">
-        <v>209.96</v>
+        <v>133.39</v>
       </c>
       <c r="D218" s="4" t="n">
-        <v>38.19</v>
+        <v>39.23</v>
       </c>
       <c r="E218" s="4" t="n">
-        <v>35.68</v>
+        <v>33.3</v>
       </c>
       <c r="F218" s="4" t="n">
-        <v>39.93</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>HERITGFOOD</t>
+          <t>JKLAKSHMI</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -6330,22 +6610,22 @@
         </is>
       </c>
       <c r="C219" s="4" t="n">
-        <v>320.8</v>
+        <v>598.75</v>
       </c>
       <c r="D219" s="4" t="n">
-        <v>38.01</v>
+        <v>39.06</v>
       </c>
       <c r="E219" s="4" t="n">
-        <v>35.71</v>
+        <v>36.51</v>
       </c>
       <c r="F219" s="4" t="n">
-        <v>42.78</v>
+        <v>40.71</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>EASEMYTRIP</t>
+          <t>BLACKBUCK</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -6354,22 +6634,22 @@
         </is>
       </c>
       <c r="C220" s="4" t="n">
-        <v>7.16</v>
+        <v>506.7</v>
       </c>
       <c r="D220" s="4" t="n">
-        <v>38</v>
+        <v>38.79</v>
       </c>
       <c r="E220" s="4" t="n">
-        <v>44.95</v>
+        <v>41.19</v>
       </c>
       <c r="F220" s="4" t="n">
-        <v>36.25</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>GANECOS</t>
+          <t>STAR</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -6378,22 +6658,22 @@
         </is>
       </c>
       <c r="C221" s="4" t="n">
-        <v>923.2</v>
+        <v>1044.6</v>
       </c>
       <c r="D221" s="4" t="n">
-        <v>37.9</v>
+        <v>38.72</v>
       </c>
       <c r="E221" s="4" t="n">
-        <v>47.11</v>
+        <v>56.51</v>
       </c>
       <c r="F221" s="4" t="n">
-        <v>43.45</v>
+        <v>57.68</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>NETWORK18</t>
+          <t>SHARDACROP</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -6402,22 +6682,22 @@
         </is>
       </c>
       <c r="C222" s="4" t="n">
-        <v>31.23</v>
+        <v>892.7</v>
       </c>
       <c r="D222" s="4" t="n">
-        <v>37.82</v>
+        <v>38.45</v>
       </c>
       <c r="E222" s="4" t="n">
-        <v>34.63</v>
+        <v>44.83</v>
       </c>
       <c r="F222" s="4" t="n">
-        <v>35.72</v>
+        <v>53.67</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>DBL</t>
+          <t>INDIASHLTR</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -6426,22 +6706,22 @@
         </is>
       </c>
       <c r="C223" s="4" t="n">
-        <v>425.1</v>
+        <v>756.7</v>
       </c>
       <c r="D223" s="4" t="n">
-        <v>37.34</v>
+        <v>38.28</v>
       </c>
       <c r="E223" s="4" t="n">
-        <v>45.26</v>
+        <v>43.39</v>
       </c>
       <c r="F223" s="4" t="n">
-        <v>48.18</v>
+        <v>48.66</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -6450,22 +6730,22 @@
         </is>
       </c>
       <c r="C224" s="4" t="n">
-        <v>183.15</v>
+        <v>416.1</v>
       </c>
       <c r="D224" s="4" t="n">
-        <v>37.15</v>
+        <v>38.17</v>
       </c>
       <c r="E224" s="4" t="n">
-        <v>52.51</v>
+        <v>43.67</v>
       </c>
       <c r="F224" s="4" t="n">
-        <v>56.52</v>
+        <v>54.36</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>SWSOLAR</t>
+          <t>KPIGREEN</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -6474,22 +6754,22 @@
         </is>
       </c>
       <c r="C225" s="4" t="n">
-        <v>187.58</v>
+        <v>405.85</v>
       </c>
       <c r="D225" s="4" t="n">
-        <v>37.11</v>
+        <v>37.88</v>
       </c>
       <c r="E225" s="4" t="n">
-        <v>43.61</v>
+        <v>46.07</v>
       </c>
       <c r="F225" s="4" t="n">
-        <v>37.9</v>
+        <v>48.91</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>GREENPANEL</t>
+          <t>ENTERO</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -6498,22 +6778,22 @@
         </is>
       </c>
       <c r="C226" s="4" t="n">
-        <v>185.57</v>
+        <v>1113.8</v>
       </c>
       <c r="D226" s="4" t="n">
-        <v>37.1</v>
+        <v>37.83</v>
       </c>
       <c r="E226" s="4" t="n">
-        <v>38.18</v>
+        <v>46.21</v>
       </c>
       <c r="F226" s="4" t="n">
-        <v>38.35</v>
+        <v>47.92</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>PNGJL</t>
+          <t>STARCEMENT</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -6522,22 +6802,22 @@
         </is>
       </c>
       <c r="C227" s="4" t="n">
-        <v>546.1</v>
+        <v>209.06</v>
       </c>
       <c r="D227" s="4" t="n">
-        <v>36.87</v>
+        <v>37.51</v>
       </c>
       <c r="E227" s="4" t="n">
-        <v>43.64</v>
+        <v>43.08</v>
       </c>
       <c r="F227" s="4" t="n">
-        <v>41.99</v>
+        <v>49.48</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>WESTLIFE</t>
+          <t>AARTIPHARM</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -6546,22 +6826,22 @@
         </is>
       </c>
       <c r="C228" s="4" t="n">
-        <v>449.9</v>
+        <v>628.3</v>
       </c>
       <c r="D228" s="4" t="n">
-        <v>36.78</v>
+        <v>37.12</v>
       </c>
       <c r="E228" s="4" t="n">
-        <v>37.27</v>
+        <v>39.41</v>
       </c>
       <c r="F228" s="4" t="n">
-        <v>29.8</v>
+        <v>47.26</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>INDIASHLTR</t>
+          <t>SUNTECK</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -6570,22 +6850,22 @@
         </is>
       </c>
       <c r="C229" s="4" t="n">
-        <v>763.85</v>
+        <v>282.3</v>
       </c>
       <c r="D229" s="4" t="n">
-        <v>36.68</v>
+        <v>36.71</v>
       </c>
       <c r="E229" s="4" t="n">
-        <v>44.58</v>
+        <v>33.85</v>
       </c>
       <c r="F229" s="4" t="n">
-        <v>49.43</v>
+        <v>38.4</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>ANUP</t>
+          <t>GABRIEL</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -6594,22 +6874,22 @@
         </is>
       </c>
       <c r="C230" s="4" t="n">
-        <v>1840.4</v>
+        <v>1000.6</v>
       </c>
       <c r="D230" s="4" t="n">
-        <v>36.32</v>
+        <v>36.66</v>
       </c>
       <c r="E230" s="4" t="n">
-        <v>44.35</v>
+        <v>49.9</v>
       </c>
       <c r="F230" s="4" t="n">
-        <v>45.91</v>
+        <v>59.29</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>GALLANTT</t>
+          <t>ELECTCAST</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -6618,22 +6898,22 @@
         </is>
       </c>
       <c r="C231" s="4" t="n">
-        <v>669.45</v>
+        <v>74</v>
       </c>
       <c r="D231" s="4" t="n">
-        <v>36.22</v>
+        <v>36.48</v>
       </c>
       <c r="E231" s="4" t="n">
-        <v>51.6</v>
+        <v>44.24</v>
       </c>
       <c r="F231" s="4" t="n">
-        <v>58.85</v>
+        <v>41.69</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>IONEXCHANG</t>
+          <t>GMMPFAUDLR</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -6642,22 +6922,22 @@
         </is>
       </c>
       <c r="C232" s="4" t="n">
-        <v>362.05</v>
+        <v>788</v>
       </c>
       <c r="D232" s="4" t="n">
-        <v>36.08</v>
+        <v>36.35</v>
       </c>
       <c r="E232" s="4" t="n">
-        <v>44.48</v>
+        <v>31.91</v>
       </c>
       <c r="F232" s="4" t="n">
-        <v>42.58</v>
+        <v>38.39</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>SUNTECK</t>
+          <t>SHARDAMOTR</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -6666,22 +6946,22 @@
         </is>
       </c>
       <c r="C233" s="4" t="n">
-        <v>285.7</v>
+        <v>813.35</v>
       </c>
       <c r="D233" s="4" t="n">
-        <v>35.58</v>
+        <v>36.08</v>
       </c>
       <c r="E233" s="4" t="n">
-        <v>34.37</v>
+        <v>42.53</v>
       </c>
       <c r="F233" s="4" t="n">
-        <v>38.65</v>
+        <v>41.92</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>AVANTIFEED</t>
+          <t>GHCL</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -6690,22 +6970,22 @@
         </is>
       </c>
       <c r="C234" s="4" t="n">
-        <v>1203.6</v>
+        <v>440.75</v>
       </c>
       <c r="D234" s="4" t="n">
-        <v>35.14</v>
+        <v>35.98</v>
       </c>
       <c r="E234" s="4" t="n">
-        <v>52.67</v>
+        <v>36.42</v>
       </c>
       <c r="F234" s="4" t="n">
-        <v>65.36</v>
+        <v>41.72</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>ANURAS</t>
+          <t>GALLANTT</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -6714,22 +6994,22 @@
         </is>
       </c>
       <c r="C235" s="4" t="n">
-        <v>1293.9</v>
+        <v>648.9</v>
       </c>
       <c r="D235" s="4" t="n">
-        <v>35.08</v>
+        <v>35.64</v>
       </c>
       <c r="E235" s="4" t="n">
-        <v>52.96</v>
+        <v>49.76</v>
       </c>
       <c r="F235" s="4" t="n">
-        <v>65.56999999999999</v>
+        <v>57.77</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>KSCL</t>
+          <t>NESCO</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -6738,22 +7018,22 @@
         </is>
       </c>
       <c r="C236" s="4" t="n">
-        <v>866.6</v>
+        <v>1112.6</v>
       </c>
       <c r="D236" s="4" t="n">
-        <v>34.46</v>
+        <v>35.49</v>
       </c>
       <c r="E236" s="4" t="n">
-        <v>44.2</v>
+        <v>44.78</v>
       </c>
       <c r="F236" s="4" t="n">
-        <v>47.05</v>
+        <v>52.51</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>RAYMONDLSL</t>
+          <t>ZAGGLE</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -6762,22 +7042,22 @@
         </is>
       </c>
       <c r="C237" s="4" t="n">
-        <v>706.4</v>
+        <v>200.81</v>
       </c>
       <c r="D237" s="4" t="n">
-        <v>34.44</v>
+        <v>35.4</v>
       </c>
       <c r="E237" s="4" t="n">
-        <v>32.55</v>
+        <v>34.1</v>
       </c>
       <c r="F237" s="4" t="n">
-        <v>21.23</v>
+        <v>39.22</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>BECTORFOOD</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -6786,22 +7066,22 @@
         </is>
       </c>
       <c r="C238" s="4" t="n">
-        <v>633.25</v>
+        <v>172.2</v>
       </c>
       <c r="D238" s="4" t="n">
-        <v>34.26</v>
+        <v>34.88</v>
       </c>
       <c r="E238" s="4" t="n">
-        <v>39.88</v>
+        <v>30.24</v>
       </c>
       <c r="F238" s="4" t="n">
-        <v>47.54</v>
+        <v>37.44</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>IONEXCHANG</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
@@ -6810,22 +7090,22 @@
         </is>
       </c>
       <c r="C239" s="4" t="n">
-        <v>525.25</v>
+        <v>350.65</v>
       </c>
       <c r="D239" s="4" t="n">
-        <v>34.01</v>
+        <v>34.6</v>
       </c>
       <c r="E239" s="4" t="n">
-        <v>39.17</v>
+        <v>41.98</v>
       </c>
       <c r="F239" s="4" t="n">
-        <v>42.86</v>
+        <v>41.63</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>RALLIS</t>
+          <t>RENUKA</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -6834,22 +7114,22 @@
         </is>
       </c>
       <c r="C240" s="4" t="n">
-        <v>243.1</v>
+        <v>22.44</v>
       </c>
       <c r="D240" s="4" t="n">
-        <v>33.57</v>
+        <v>34.44</v>
       </c>
       <c r="E240" s="4" t="n">
-        <v>42.7</v>
+        <v>36.42</v>
       </c>
       <c r="F240" s="4" t="n">
-        <v>46.03</v>
+        <v>36.49</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>CELLO</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
@@ -6858,22 +7138,22 @@
         </is>
       </c>
       <c r="C241" s="4" t="n">
-        <v>368.25</v>
+        <v>518.3</v>
       </c>
       <c r="D241" s="4" t="n">
-        <v>32.94</v>
+        <v>34.27</v>
       </c>
       <c r="E241" s="4" t="n">
-        <v>28.1</v>
+        <v>38.48</v>
       </c>
       <c r="F241" s="4" t="n">
-        <v>29.24</v>
+        <v>42.51</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>SYMPHONY</t>
+          <t>KSCL</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -6882,22 +7162,22 @@
         </is>
       </c>
       <c r="C242" s="4" t="n">
-        <v>696.15</v>
+        <v>858.4</v>
       </c>
       <c r="D242" s="4" t="n">
-        <v>32.27</v>
+        <v>34.01</v>
       </c>
       <c r="E242" s="4" t="n">
-        <v>36.33</v>
+        <v>43.43</v>
       </c>
       <c r="F242" s="4" t="n">
-        <v>38.4</v>
+        <v>46.69</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>JKLAKSHMI</t>
+          <t>EUREKAFORB</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -6906,22 +7186,22 @@
         </is>
       </c>
       <c r="C243" s="4" t="n">
-        <v>590.35</v>
+        <v>440.8</v>
       </c>
       <c r="D243" s="4" t="n">
-        <v>32.09</v>
+        <v>33.77</v>
       </c>
       <c r="E243" s="4" t="n">
-        <v>34.85</v>
+        <v>36.76</v>
       </c>
       <c r="F243" s="4" t="n">
-        <v>40.09</v>
+        <v>39.68</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>BECTORFOOD</t>
+          <t>EASEMYTRIP</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -6930,22 +7210,22 @@
         </is>
       </c>
       <c r="C244" s="4" t="n">
-        <v>171.71</v>
+        <v>6.74</v>
       </c>
       <c r="D244" s="4" t="n">
-        <v>31.48</v>
+        <v>33.07</v>
       </c>
       <c r="E244" s="4" t="n">
-        <v>29.86</v>
+        <v>41.8</v>
       </c>
       <c r="F244" s="4" t="n">
-        <v>37.31</v>
+        <v>35.35</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>TRANSRAILL</t>
+          <t>ISGEC</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
@@ -6954,22 +7234,22 @@
         </is>
       </c>
       <c r="C245" s="4" t="n">
-        <v>479.5</v>
+        <v>928.15</v>
       </c>
       <c r="D245" s="4" t="n">
-        <v>31.26</v>
+        <v>32.86</v>
       </c>
       <c r="E245" s="4" t="n">
-        <v>39.09</v>
+        <v>47.04</v>
       </c>
       <c r="F245" s="4" t="n">
-        <v>43.3</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>EUREKAFORB</t>
+          <t>HGINFRA</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -6978,22 +7258,22 @@
         </is>
       </c>
       <c r="C246" s="4" t="n">
-        <v>440.25</v>
+        <v>548.65</v>
       </c>
       <c r="D246" s="4" t="n">
-        <v>30.87</v>
+        <v>32.15</v>
       </c>
       <c r="E246" s="4" t="n">
-        <v>36.62</v>
+        <v>38.01</v>
       </c>
       <c r="F246" s="4" t="n">
-        <v>39.62</v>
+        <v>35.98</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>RENUKA</t>
+          <t>SYMPHONY</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
@@ -7002,22 +7282,22 @@
         </is>
       </c>
       <c r="C247" s="4" t="n">
-        <v>22.85</v>
+        <v>687.4</v>
       </c>
       <c r="D247" s="4" t="n">
-        <v>29.68</v>
+        <v>31.2</v>
       </c>
       <c r="E247" s="4" t="n">
-        <v>37.5</v>
+        <v>35.65</v>
       </c>
       <c r="F247" s="4" t="n">
-        <v>36.89</v>
+        <v>38.11</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>SANOFI</t>
+          <t>AVANTIFEED</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -7026,22 +7306,22 @@
         </is>
       </c>
       <c r="C248" s="4" t="n">
-        <v>3097.1</v>
+        <v>1110.6</v>
       </c>
       <c r="D248" s="4" t="n">
-        <v>27.8</v>
+        <v>28.92</v>
       </c>
       <c r="E248" s="4" t="n">
-        <v>24.64</v>
+        <v>47.64</v>
       </c>
       <c r="F248" s="4" t="n">
-        <v>28.9</v>
+        <v>60.88</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>ISGEC</t>
+          <t>BAJAJELEC</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
@@ -7050,22 +7330,22 @@
         </is>
       </c>
       <c r="C249" s="4" t="n">
-        <v>929.8</v>
+        <v>311.5</v>
       </c>
       <c r="D249" s="4" t="n">
-        <v>27.26</v>
+        <v>27.82</v>
       </c>
       <c r="E249" s="4" t="n">
-        <v>47.2</v>
+        <v>27.96</v>
       </c>
       <c r="F249" s="4" t="n">
-        <v>48.36</v>
+        <v>27.55</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>GMMPFAUDLR</t>
+          <t>RALLIS</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
@@ -7074,40 +7354,16 @@
         </is>
       </c>
       <c r="C250" s="4" t="n">
-        <v>766.7</v>
+        <v>227.24</v>
       </c>
       <c r="D250" s="4" t="n">
-        <v>23.03</v>
+        <v>25.89</v>
       </c>
       <c r="E250" s="4" t="n">
-        <v>28.38</v>
+        <v>38.92</v>
       </c>
       <c r="F250" s="4" t="n">
-        <v>37.51</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="2" t="inlineStr">
-        <is>
-          <t>BAJAJELEC</t>
-        </is>
-      </c>
-      <c r="B251" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C251" s="4" t="n">
-        <v>314.45</v>
-      </c>
-      <c r="D251" s="4" t="n">
-        <v>22.87</v>
-      </c>
-      <c r="E251" s="4" t="n">
-        <v>28.33</v>
-      </c>
-      <c r="F251" s="4" t="n">
-        <v>27.67</v>
+        <v>44.37</v>
       </c>
     </row>
   </sheetData>
@@ -7361,7 +7617,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B248" r:id="rId247"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B249" r:id="rId248"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B250" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B251" r:id="rId250"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/Micro250_stocks.xlsx
+++ b/reports/Micro250_stocks.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -537,7 +537,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>CUPID</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -546,37 +546,37 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>619.25</v>
+        <v>159.97</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>82.20999999999999</v>
+        <v>85.08</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>96.06</v>
+        <v>81.56</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>90.59</v>
+        <v>86.81</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>43.64</v>
+        <v>41.44</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>246.78</v>
+        <v>94.73</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>218.92</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>4636097</v>
+        <v>17259028</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>30230</v>
+        <v>21511</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>PARAS</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -585,37 +585,37 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>5351.9</v>
+        <v>1097.15</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>78.47</v>
+        <v>75.06999999999999</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>70.29000000000001</v>
+        <v>72.98</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>80.93000000000001</v>
+        <v>63.21</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>28.8</v>
+        <v>20.93</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>3534.7</v>
+        <v>751.91</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>3337.59</v>
+        <v>743.9400000000001</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>204219</v>
+        <v>3213385</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>16635</v>
+        <v>8842</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ASTRAMICRO</t>
+          <t>SOUTHBANK</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -624,37 +624,37 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>1419.5</v>
+        <v>46.66</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>73.3</v>
+        <v>72.22</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>75.42</v>
+        <v>67.84</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>71.63</v>
+        <v>70.69</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>27.96</v>
+        <v>22.22</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>1053.32</v>
+        <v>38.88</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>1029.74</v>
+        <v>37.72</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>1086166</v>
+        <v>18136178</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>13477</v>
+        <v>12214</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>PARAS</t>
+          <t>INOXINDIA</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -663,31 +663,31 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>960.15</v>
+        <v>1808.2</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>72.01000000000001</v>
+        <v>71.28</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>67.14</v>
+        <v>81.58</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>58.99</v>
+        <v>80.23999999999999</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>27.89</v>
+        <v>24.41</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>732.88</v>
+        <v>1321.1</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>728.99</v>
+        <v>1286.45</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>2378812</v>
+        <v>456227</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>7738</v>
+        <v>16412</v>
       </c>
     </row>
     <row r="6">
@@ -702,37 +702,37 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1607.9</v>
+        <v>1687</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>70.40000000000001</v>
+        <v>68.41</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>74.41</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>73.88</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>31.98</v>
+        <v>37.93</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1091.18</v>
+        <v>1124.49</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>1048.07</v>
+        <v>1075.64</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>741802</v>
+        <v>784424</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>10739</v>
+        <v>11267</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>SHAILY</t>
+          <t>ASTRAMICRO</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -741,37 +741,37 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>3062.9</v>
+        <v>1443.8</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>69.03</v>
+        <v>68.3</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>69.39</v>
+        <v>76.27</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>72.63</v>
+        <v>72.18000000000001</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>31.84</v>
+        <v>29.42</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>2310.2</v>
+        <v>1077.58</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>2230.96</v>
+        <v>1050.02</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>332096</v>
+        <v>1214939</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>14088</v>
+        <v>13708</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>SOUTHBANK</t>
+          <t>TMB</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -780,37 +780,37 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>44</v>
+        <v>767.05</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>66.73</v>
+        <v>68</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>63.37</v>
+        <v>69.03</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>68.47</v>
+        <v>71.8</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>20.38</v>
+        <v>22.1</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>38.44</v>
+        <v>614.38</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>37.33</v>
+        <v>588.5</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>15912561</v>
+        <v>343615</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>11518</v>
+        <v>12146</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>EQUITASBNK</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -819,37 +819,37 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>73.95</v>
+        <v>583.65</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>64.88</v>
+        <v>65.95999999999999</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>62.29</v>
+        <v>87.84</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>54.46</v>
+        <v>89.95999999999999</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>25.98</v>
+        <v>40.8</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>64.51000000000001</v>
+        <v>268.74</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>64.27</v>
+        <v>236.94</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>4912708</v>
+        <v>3912750</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>8442</v>
+        <v>28492</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>GRWRHITECH</t>
+          <t>BALAMINES</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -858,37 +858,37 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>5893</v>
+        <v>2133</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>63.5</v>
+        <v>65.02</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>72.19</v>
+        <v>82.52</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>64.48</v>
+        <v>59.86</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>24.61</v>
+        <v>22.49</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>4189.83</v>
+        <v>1410.42</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>4046.71</v>
+        <v>1404.65</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>155227</v>
+        <v>667820</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>13691</v>
+        <v>6911</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>MIDHANI</t>
+          <t>SPARC</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -897,37 +897,37 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>435.55</v>
+        <v>223.76</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>63.3</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>66.16</v>
+        <v>76.27</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>57.31</v>
+        <v>59.15</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>22.43</v>
+        <v>37.82</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>367.67</v>
+        <v>155.32</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>365.61</v>
+        <v>153.57</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1513301</v>
+        <v>10027945</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>8160</v>
+        <v>7261</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>TIPSMUSIC</t>
+          <t>GRWRHITECH</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -936,37 +936,37 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>690.95</v>
+        <v>6131.5</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>63.24</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>67.34999999999999</v>
+        <v>73.92</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>62.07</v>
+        <v>66.25</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>24.52</v>
+        <v>22.76</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>585.33</v>
+        <v>4315.55</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>582.74</v>
+        <v>4151.16</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>308431</v>
+        <v>155856</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>8833</v>
+        <v>14245</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>SPARC</t>
+          <t>BBOX</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -975,37 +975,37 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>212.82</v>
+        <v>1018.6</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>62.91</v>
+        <v>63.88</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>74.14</v>
+        <v>78.56</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>57.51</v>
+        <v>75.28</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>38.65</v>
+        <v>29.82</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>151.57</v>
+        <v>658.24</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>150.63</v>
+        <v>624.39</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>9945647</v>
+        <v>1506723</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>6906</v>
+        <v>18090</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>AZAD</t>
+          <t>PRIVISCL</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1014,37 +1014,37 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2207.7</v>
+        <v>3444.3</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>61.87</v>
+        <v>63.84</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>65.47</v>
+        <v>61.97</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>63.97</v>
+        <v>69.54000000000001</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>29.14</v>
+        <v>49.3</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1785.76</v>
+        <v>2988.2</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1745.76</v>
+        <v>2888.32</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>450312</v>
+        <v>108364</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>14258</v>
+        <v>13454</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>MTARTECH</t>
+          <t>THYROCARE</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1053,37 +1053,37 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>7535.5</v>
+        <v>528.9</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>58.27</v>
+        <v>63.32</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>81.86</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>83.44</v>
+        <v>66.19</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>60.5</v>
+        <v>24.19</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>4387.8</v>
+        <v>433.41</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>3928.21</v>
+        <v>422.1</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1714303</v>
+        <v>824494</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>23179</v>
+        <v>8418</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>EQUITASBNK</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1092,37 +1092,37 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1216.8</v>
+        <v>75.54000000000001</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>58.07</v>
+        <v>63.04</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>63.41</v>
+        <v>63.82</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>62.77</v>
+        <v>55.3</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>75.52</v>
+        <v>27.02</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>964.52</v>
+        <v>65.13</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>928.45</v>
+        <v>64.78</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>501509</v>
+        <v>5960044</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>7965</v>
+        <v>8640</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KIRLPNU</t>
+          <t>ARVIND</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1131,37 +1131,37 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1570.8</v>
+        <v>494.5</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>54.91</v>
+        <v>62.05</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>73.54000000000001</v>
+        <v>76.43000000000001</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>63.94</v>
+        <v>71.06</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>36.51</v>
+        <v>21.12</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1286.82</v>
+        <v>388.51</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>1265.5</v>
+        <v>377.68</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>249636</v>
+        <v>1310620</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>10204</v>
+        <v>12962</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>ZYDUSWELL</t>
+          <t>SANSERA</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1170,37 +1170,37 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>504.6</v>
+        <v>2914.2</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>54.83</v>
+        <v>61.12</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>60.7</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>62.28</v>
+        <v>77.14</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>21.76</v>
+        <v>25.37</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>457.22</v>
+        <v>2198.45</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>449.12</v>
+        <v>2070.5</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>431974</v>
+        <v>318575</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>16054</v>
+        <v>18165</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>SUNFLAG</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1209,37 +1209,37 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>372.1</v>
+        <v>275.7</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>53.43</v>
+        <v>60.97</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>67.73999999999999</v>
+        <v>69.23999999999999</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>65.76000000000001</v>
+        <v>69.04000000000001</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>31.45</v>
+        <v>24.54</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>288.82</v>
+        <v>227.48</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>281.38</v>
+        <v>220.48</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1525311</v>
+        <v>2898589</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>6706</v>
+        <v>10426</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>ADVENZYMES</t>
+          <t>WABAG</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1248,70 +1248,499 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>367.05</v>
+        <v>1577.8</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>51.7</v>
+        <v>60.26</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>65.15000000000001</v>
+        <v>63.86</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>56.26</v>
+        <v>59.66</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>22.51</v>
+        <v>37.71</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>322.45</v>
+        <v>1385.57</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>320.94</v>
+        <v>1383.87</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>574335</v>
+        <v>318217</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>4110</v>
+        <v>9832</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>KRN</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>1261.2</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>59.01</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>65.29000000000001</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>63.91</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>67.33</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>981.33</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>942.91</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>382890</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>8256</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>YATHARTH</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>839.75</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>58.74</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>60.12</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>63.29</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>38.65</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>732.99</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>713.9400000000001</v>
+      </c>
+      <c r="J22" s="4" t="n">
+        <v>445462</v>
+      </c>
+      <c r="K22" s="4" t="n">
+        <v>8091</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>SHAILY</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>2972</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>58.54</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>66.05</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>71.48999999999999</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>22.09</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>2356.48</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>2270.06</v>
+      </c>
+      <c r="J23" s="4" t="n">
+        <v>286665</v>
+      </c>
+      <c r="K23" s="4" t="n">
+        <v>13670</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>KIRLPNU</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>1606</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>56.18</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>75.06</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>64.84999999999999</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>53.96</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>1307.87</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>1283.65</v>
+      </c>
+      <c r="J24" s="4" t="n">
+        <v>149813</v>
+      </c>
+      <c r="K24" s="4" t="n">
+        <v>10432</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>AZAD</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>2150.1</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>54.69</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>63.04</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>39.31</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>1810.38</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>1767.43</v>
+      </c>
+      <c r="J25" s="4" t="n">
+        <v>427263</v>
+      </c>
+      <c r="K25" s="4" t="n">
+        <v>13886</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>GOKULAGRO</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>233.07</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>54.18</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>66.23999999999999</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>68.84</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>28.64</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>198.38</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>191.16</v>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>618053</v>
+      </c>
+      <c r="K26" s="4" t="n">
+        <v>6878</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>SKYGOLD</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>508.95</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>63.71</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>69.19</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>30.27</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>397.82</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>382.38</v>
+      </c>
+      <c r="J27" s="4" t="n">
+        <v>1778179</v>
+      </c>
+      <c r="K27" s="4" t="n">
+        <v>7882</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>AXISCADES</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>1947.6</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>53.74</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>61.44</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>52.14</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>1626.26</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>1546.73</v>
+      </c>
+      <c r="J28" s="4" t="n">
+        <v>179470</v>
+      </c>
+      <c r="K28" s="4" t="n">
+        <v>8283</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>ADVENZYMES</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>368.95</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>52.08</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>65.58</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>34.51</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>325.47</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>323.36</v>
+      </c>
+      <c r="J29" s="4" t="n">
+        <v>492991</v>
+      </c>
+      <c r="K29" s="4" t="n">
+        <v>4131</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>MTARTECH</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>7159.5</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>51.67</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>75.42</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>79.19</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>63.1</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>4557.33</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>4079.55</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>1973289</v>
+      </c>
+      <c r="K30" s="4" t="n">
+        <v>22022</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
           <t>GAEL</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>155.86</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>47.07</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>60.36</v>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>62.08</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>49.71</v>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>139.81</v>
-      </c>
-      <c r="I21" s="4" t="n">
-        <v>135.77</v>
-      </c>
-      <c r="J21" s="4" t="n">
-        <v>1011467</v>
-      </c>
-      <c r="K21" s="4" t="n">
-        <v>7149</v>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>157.83</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>50.59</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>61.51</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>62.77</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>41.28</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>140.98</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>136.93</v>
+      </c>
+      <c r="J31" s="4" t="n">
+        <v>1026983</v>
+      </c>
+      <c r="K31" s="4" t="n">
+        <v>7239</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>TDPOWERSYS</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>1192.8</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>65.87</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>75.23</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>31.09</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>938.95</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>871.87</v>
+      </c>
+      <c r="J32" s="4" t="n">
+        <v>1608996</v>
+      </c>
+      <c r="K32" s="4" t="n">
+        <v>18635</v>
       </c>
     </row>
   </sheetData>
@@ -1336,6 +1765,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1347,7 +1787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F250"/>
+  <dimension ref="A1:F251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1393,7 +1833,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>CUPID</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -1402,22 +1842,22 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>619.25</v>
+        <v>159.97</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>82.20999999999999</v>
+        <v>85.08</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>96.06</v>
+        <v>81.56</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>90.59</v>
+        <v>86.81</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ORCHPHARMA</t>
+          <t>AKUMS</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -1426,16 +1866,16 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>844.25</v>
+        <v>622.9</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>79.18000000000001</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>67.11</v>
+        <v>71.47</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>51.33</v>
+        <v>53.94</v>
       </c>
     </row>
     <row r="4">
@@ -1450,22 +1890,22 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>5351.9</v>
+        <v>5478.7</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>78.47</v>
+        <v>77.55</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>70.29000000000001</v>
+        <v>71.18000000000001</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>80.93000000000001</v>
+        <v>81.44</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>SHILPAMED</t>
+          <t>QUESS</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -1474,22 +1914,22 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>538.05</v>
+        <v>244.02</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>77.28</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>78.79000000000001</v>
+        <v>62.78</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>69.18000000000001</v>
+        <v>39.07</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>RAIN</t>
+          <t>NEOGEN</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -1498,22 +1938,22 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>197.09</v>
+        <v>2033.7</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>75.18000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>72.5</v>
+        <v>71.52</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>59.74</v>
+        <v>60.34</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>GANESHHOU</t>
+          <t>PARAS</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1522,22 +1962,22 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>780.75</v>
+        <v>1097.15</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>74.94</v>
+        <v>75.06999999999999</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>59.7</v>
+        <v>72.98</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>50.19</v>
+        <v>63.21</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ACUTAAS</t>
+          <t>MSTCLTD</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1546,22 +1986,22 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>3328.3</v>
+        <v>568.55</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>74.56999999999999</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>79.45</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>89.43000000000001</v>
+        <v>54.77</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>AJAXENGG</t>
+          <t>SFL</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -1570,22 +2010,22 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>601.75</v>
+        <v>703.55</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>73.41</v>
+        <v>72.25</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>60.2</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>51.94</v>
+        <v>48.33</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ASTRAMICRO</t>
+          <t>SOUTHBANK</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1594,22 +2034,22 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1419.5</v>
+        <v>46.66</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>73.3</v>
+        <v>72.22</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>75.42</v>
+        <v>67.84</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>71.63</v>
+        <v>70.69</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>WABAG</t>
+          <t>INOXINDIA</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -1618,22 +2058,22 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1600.4</v>
+        <v>1808.2</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>72.45999999999999</v>
+        <v>71.28</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>65.92</v>
+        <v>81.58</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>60.2</v>
+        <v>80.23999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>PARAS</t>
+          <t>RUBICON</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1642,22 +2082,22 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>960.15</v>
+        <v>1295.5</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>72.01000000000001</v>
+        <v>70.73</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>67.14</v>
+        <v>89.95999999999999</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>58.99</v>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>QUESS</t>
+          <t>WEWORK</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1666,22 +2106,22 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>235.71</v>
+        <v>639.35</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>71.94</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>60.3</v>
+        <v>64.03</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>37.91</v>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>CEMPRO</t>
+          <t>VMART</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1690,22 +2130,22 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1112.8</v>
+        <v>719.75</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>71.70999999999999</v>
+        <v>69.54000000000001</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>74.84</v>
+        <v>60.51</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>69.43000000000001</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>GREAVESCOT</t>
+          <t>POWERMECH</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1714,22 +2154,22 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>192.2</v>
+        <v>2789.5</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>71.70999999999999</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>60.47</v>
+        <v>64.61</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>52.42</v>
+        <v>55.84</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>MSTCLTD</t>
+          <t>CERA</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1738,22 +2178,22 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>512.35</v>
+        <v>6144</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>71.05</v>
+        <v>69.31</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>59.7</v>
+        <v>64.73</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>51.33</v>
+        <v>50.98</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>RATEGAIN</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1762,22 +2202,22 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1607.9</v>
+        <v>783.05</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>70.40000000000001</v>
+        <v>69.27</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>74.41</v>
+        <v>72.37</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>73.88</v>
+        <v>60.67</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>RATEGAIN</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1786,22 +2226,22 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>758.7</v>
+        <v>1687</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>69.68000000000001</v>
+        <v>68.41</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>70.48</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>59.59</v>
+        <v>75.15000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>SKIPPER</t>
+          <t>ASTRAMICRO</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1810,22 +2250,22 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>556.6</v>
+        <v>1443.8</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>69.54000000000001</v>
+        <v>68.3</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>70.92</v>
+        <v>76.27</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>62.69</v>
+        <v>72.18000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>TEGA</t>
+          <t>TMB</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1834,22 +2274,22 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1847.7</v>
+        <v>767.05</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>69.41</v>
+        <v>68</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>57.11</v>
+        <v>69.03</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>58.27</v>
+        <v>71.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>BALAMINES</t>
+          <t>SHILPAMED</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1858,22 +2298,22 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2043.3</v>
+        <v>546.75</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>69.34</v>
+        <v>66.83</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>81.06999999999999</v>
+        <v>79.54000000000001</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>58.49</v>
+        <v>69.70999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>THYROCARE</t>
+          <t>MARKSANS</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1882,22 +2322,22 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>518</v>
+        <v>252.37</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>69.33</v>
+        <v>66.73</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>67.67</v>
+        <v>71.87</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>65.51000000000001</v>
+        <v>60.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>SHAILY</t>
+          <t>RAIN</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1906,22 +2346,22 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>3062.9</v>
+        <v>196.87</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>69.03</v>
+        <v>66.37</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>69.39</v>
+        <v>72.37</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>72.63</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>RTNINDIA</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1930,22 +2370,22 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>39.13</v>
+        <v>583.65</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>68.98</v>
+        <v>65.95999999999999</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>55.04</v>
+        <v>87.84</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>44.65</v>
+        <v>89.95999999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>SANSERA</t>
+          <t>SUPRIYA</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1954,22 +2394,22 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2945.1</v>
+        <v>977.15</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>67.70999999999999</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>74.72</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>77.43000000000001</v>
+        <v>68.27</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>NEOGEN</t>
+          <t>INOXGREEN</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1978,22 +2418,22 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1903.6</v>
+        <v>189.9</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>67.29000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>68.18000000000001</v>
+        <v>55.35</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>58.18</v>
+        <v>54.48</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>SUPRIYA</t>
+          <t>BALAMINES</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -2002,22 +2442,22 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>947.95</v>
+        <v>2133</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>66.84</v>
+        <v>65.02</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>75.61</v>
+        <v>82.52</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>66.5</v>
+        <v>59.86</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>SOUTHBANK</t>
+          <t>ICIL</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -2026,22 +2466,22 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>44</v>
+        <v>344.45</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>66.73</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>63.37</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>68.47</v>
+        <v>57.99</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>SFL</t>
+          <t>SPARC</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -2050,22 +2490,22 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>642.75</v>
+        <v>223.76</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>66.03</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>59.63</v>
+        <v>76.27</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>44.69</v>
+        <v>59.15</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>TVSSCS</t>
+          <t>PRUDENT</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -2074,22 +2514,22 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>129.67</v>
+        <v>2909.1</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>65.19</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>58.16</v>
+        <v>61.82</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>46.95</v>
+        <v>60.25</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>UNIMECH</t>
+          <t>WELENT</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -2098,22 +2538,22 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1078.25</v>
+        <v>552.25</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>65.11</v>
+        <v>64.59</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>60.95</v>
+        <v>62.7</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>50.89</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>HCC</t>
+          <t>GRWRHITECH</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -2122,22 +2562,22 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>24.02</v>
+        <v>6131.5</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>65.06999999999999</v>
+        <v>64.51000000000001</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>59.6</v>
+        <v>73.92</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>48.22</v>
+        <v>66.25</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>WELENT</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -2146,22 +2586,22 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>541.4</v>
+        <v>109.78</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>64.98</v>
+        <v>64.42</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>60.74</v>
+        <v>49.23</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>57.24</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>CYIENTDLM</t>
+          <t>MANORAMA</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -2170,22 +2610,22 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>453.4</v>
+        <v>1564.4</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>64.91</v>
+        <v>64.31</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>64.42</v>
+        <v>59.52</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>47.76</v>
+        <v>64.64</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>EQUITASBNK</t>
+          <t>BANCOINDIA</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -2194,22 +2634,22 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>73.95</v>
+        <v>689.55</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>64.88</v>
+        <v>64.03</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>62.29</v>
+        <v>59.12</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>54.46</v>
+        <v>60.49</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>REFEX</t>
+          <t>BBOX</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -2218,22 +2658,22 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>312.5</v>
+        <v>1018.6</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>64.44</v>
+        <v>63.88</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>61</v>
+        <v>78.56</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>51.65</v>
+        <v>75.28</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>OSWALPUMPS</t>
+          <t>PRIVISCL</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -2242,22 +2682,22 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>412.7</v>
+        <v>3444.3</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>64.36</v>
+        <v>63.84</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>47.97</v>
+        <v>61.97</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v/>
+        <v>69.54000000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>ABDL</t>
+          <t>SKFINDUS</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -2266,22 +2706,22 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>580.7</v>
+        <v>2386.9</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>64.3</v>
+        <v>63.52</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>57.1</v>
+        <v>52.59</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>60.61</v>
+        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>BANCOINDIA</t>
+          <t>THYROCARE</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -2290,22 +2730,22 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>655.45</v>
+        <v>528.9</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>63.89</v>
+        <v>63.32</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>55.19</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>58.95</v>
+        <v>66.19</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>ARVIND</t>
+          <t>EQUITASBNK</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -2314,22 +2754,22 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>493.7</v>
+        <v>75.54000000000001</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>63.61</v>
+        <v>63.04</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>76.33</v>
+        <v>63.82</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>71</v>
+        <v>55.3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GRWRHITECH</t>
+          <t>QPOWER</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -2338,22 +2778,22 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>5893</v>
+        <v>1221.1</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>63.5</v>
+        <v>62.83</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>72.19</v>
+        <v>61.57</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>64.48</v>
+        <v>65.95</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>OPTIEMUS</t>
+          <t>IXIGO</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -2362,22 +2802,22 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>453.5</v>
+        <v>178.22</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>63.48</v>
+        <v>62.57</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>52.75</v>
+        <v>45.99</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>49.42</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>ICIL</t>
+          <t>ARVIND</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -2386,22 +2826,22 @@
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>328.6</v>
+        <v>494.5</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>63.42</v>
+        <v>62.05</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>61.75</v>
+        <v>76.43000000000001</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>56.28</v>
+        <v>71.06</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>MIDHANI</t>
+          <t>TVSSCS</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -2410,22 +2850,22 @@
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>435.55</v>
+        <v>132.26</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>63.3</v>
+        <v>61.78</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>66.16</v>
+        <v>59.35</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>57.31</v>
+        <v>47.82</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>TIPSMUSIC</t>
+          <t>RELAXO</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -2434,22 +2874,22 @@
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>690.95</v>
+        <v>342.65</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>63.24</v>
+        <v>61.63</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>67.34999999999999</v>
+        <v>50.89</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>62.07</v>
+        <v>33.44</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>CARTRADE</t>
+          <t>IFBIND</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -2458,22 +2898,22 @@
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>1958.4</v>
+        <v>1287.8</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>63.02</v>
+        <v>61.32</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>48.6</v>
+        <v>53.55</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>53.94</v>
+        <v>49.02</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>DIACABS</t>
+          <t>STYL</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -2482,22 +2922,22 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>203.6</v>
+        <v>279.8</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>62.92</v>
+        <v>61.29</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>76.52</v>
+        <v>52.87</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>67.5</v>
+        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>SPARC</t>
+          <t>RELIGARE</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -2506,22 +2946,22 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>212.82</v>
+        <v>239.82</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>62.91</v>
+        <v>61.29</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>74.14</v>
+        <v>54.87</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>57.51</v>
+        <v>52.44</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>V2RETAIL</t>
+          <t>SANSERA</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -2530,22 +2970,22 @@
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>247.99</v>
+        <v>2914.2</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>62.89</v>
+        <v>61.12</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>66.48</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>70.05</v>
+        <v>77.14</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>POWERMECH</t>
+          <t>SAATVIKGL</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -2554,22 +2994,22 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>2601.8</v>
+        <v>476.4</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>62.32</v>
+        <v>61.04</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>59.4</v>
+        <v>59.57</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>53.37</v>
+        <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>VIYASH</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -2578,22 +3018,22 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>255.25</v>
+        <v>275.7</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>62.3</v>
+        <v>60.97</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>68.3</v>
+        <v>69.23999999999999</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>63.35</v>
+        <v>69.04000000000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>AZAD</t>
+          <t>SUDEEPPHRM</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -2602,22 +3042,22 @@
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>2207.7</v>
+        <v>749.5</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>61.87</v>
+        <v>60.79</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>65.47</v>
+        <v>61.5</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>63.97</v>
+        <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>RELAXO</t>
+          <t>SURYAROSNI</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -2626,22 +3066,22 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>330.05</v>
+        <v>263.01</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>61.59</v>
+        <v>60.76</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>47.97</v>
+        <v>55.51</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>32.64</v>
+        <v>50.74</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>MAXESTATES</t>
+          <t>SKIPPER</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -2650,22 +3090,22 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>444.5</v>
+        <v>544.65</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>61.49</v>
+        <v>60.26</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>58.49</v>
+        <v>67.94</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>51.75</v>
+        <v>61.68</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>SAFARI</t>
+          <t>WABAG</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -2674,22 +3114,22 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>1633.1</v>
+        <v>1577.8</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>61.46</v>
+        <v>60.26</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>45.48</v>
+        <v>63.86</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>43.87</v>
+        <v>59.66</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>INNOVACAP</t>
+          <t>RBA</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -2698,22 +3138,22 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>867.5</v>
+        <v>68.84999999999999</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>61.36</v>
+        <v>60.25</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>64.98999999999999</v>
+        <v>57.28</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>58.93</v>
+        <v>41.69</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>IFBIND</t>
+          <t>ALKYLAMINE</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -2722,22 +3162,22 @@
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>1255.7</v>
+        <v>1831.8</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>61.19</v>
+        <v>60.15</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>51.67</v>
+        <v>65.19</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>48.33</v>
+        <v>49.67</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENGG</t>
+          <t>APOLLO</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -2746,22 +3186,22 @@
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>72.69</v>
+        <v>409.4</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>61.11</v>
+        <v>59.99</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>68.69</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>58.55</v>
+        <v>72.04000000000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>TEAMLEASE</t>
+          <t>SHRIPISTON</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -2770,22 +3210,22 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>1385.3</v>
+        <v>3524.4</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>61.09</v>
+        <v>59.47</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>49.69</v>
+        <v>59.05</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>36.28</v>
+        <v>70.78</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>LMW</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -2794,22 +3234,22 @@
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>15679</v>
+        <v>1261.2</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>61.04</v>
+        <v>59.01</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>58.03</v>
+        <v>65.29000000000001</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>53.41</v>
+        <v>63.91</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>RBA</t>
+          <t>REFEX</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -2818,22 +3258,22 @@
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>68.70999999999999</v>
+        <v>311</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>60.96</v>
+        <v>58.98</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>56.94</v>
+        <v>60.51</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>41.56</v>
+        <v>51.51</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>SKYGOLD</t>
+          <t>DIACABS</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -2842,22 +3282,22 @@
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>528.45</v>
+        <v>201.91</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>60.76</v>
+        <v>58.96</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>67.04000000000001</v>
+        <v>75.12</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>71.16</v>
+        <v>67.27</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>CEIGALL</t>
+          <t>BORORENEW</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -2866,22 +3306,22 @@
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>358.5</v>
+        <v>544.6</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>60.43</v>
+        <v>58.92</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>68.83</v>
+        <v>55.76</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>65.5</v>
+        <v>52.61</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>VIPIND</t>
+          <t>YATHARTH</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -2890,22 +3330,22 @@
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>329.85</v>
+        <v>839.75</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>60.38</v>
+        <v>58.74</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>46.79</v>
+        <v>60.12</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>40.15</v>
+        <v>63.29</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>GARFIBRES</t>
+          <t>KIRLOSBROS</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -2914,22 +3354,22 @@
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>665.5</v>
+        <v>1729.4</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>59.86</v>
+        <v>58.59</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>51.52</v>
+        <v>54.23</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>44.81</v>
+        <v>53.04</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>SURYAROSNI</t>
+          <t>SHAILY</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -2938,22 +3378,22 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>258.17</v>
+        <v>2972</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>59.65</v>
+        <v>58.54</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>54.13</v>
+        <v>66.05</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>50.14</v>
+        <v>71.48999999999999</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>INDIGOPNTS</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -2962,22 +3402,22 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>233.19</v>
+        <v>995.2</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>59.55</v>
+        <v>58.53</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>67.23999999999999</v>
+        <v>52.82</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>56.83</v>
+        <v>44.78</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>KRBL</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -2986,22 +3426,22 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>1312.8</v>
+        <v>366.8</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>59.48</v>
+        <v>58.28</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>79.41</v>
+        <v>54.08</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>84.26000000000001</v>
+        <v>53.34</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>PGIL</t>
+          <t>SWSOLAR</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -3010,22 +3450,22 @@
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>1665.6</v>
+        <v>208.23</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>59.48</v>
+        <v>58.19</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>56.51</v>
+        <v>51.35</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>63.49</v>
+        <v>40.55</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>IIFLCAPS</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -3034,22 +3474,22 @@
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>342.75</v>
+        <v>285.85</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>59.39</v>
+        <v>58.1</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>56.79</v>
+        <v>55.72</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>58.66</v>
+        <v>56.34</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>NETWORK18</t>
+          <t>KANSAINER</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -3058,22 +3498,22 @@
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>33.41</v>
+        <v>216.5</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>58.36</v>
+        <v>57.99</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>41.68</v>
+        <v>52.52</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>37.57</v>
+        <v>43.34</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>MTARTECH</t>
+          <t>GREAVESCOT</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -3082,22 +3522,22 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>7535.5</v>
+        <v>185.04</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>58.27</v>
+        <v>57.85</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>81.86</v>
+        <v>56.64</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>83.44</v>
+        <v>51.12</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>VARROC</t>
+          <t>RAYMONDLSL</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -3106,22 +3546,22 @@
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>586.3</v>
+        <v>794.75</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>58.26</v>
+        <v>57.42</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>58.08</v>
+        <v>42.82</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>54.95</v>
+        <v>27.1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>FINEORG</t>
+          <t>MIDHANI</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -3130,22 +3570,22 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>4754.4</v>
+        <v>435.1</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>58.1</v>
+        <v>57.25</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>56.7</v>
+        <v>66.02</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>52.66</v>
+        <v>57.27</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>EPL</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -3154,22 +3594,22 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>1216.8</v>
+        <v>224.8</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>58.07</v>
+        <v>57.05</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>63.41</v>
+        <v>54.55</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>62.77</v>
+        <v>53.95</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>FIEMIND</t>
+          <t>BLACKBUCK</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -3178,22 +3618,22 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>2311.2</v>
+        <v>546.4</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>57.91</v>
+        <v>56.46</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>58.89</v>
+        <v>46.85</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>68.06999999999999</v>
+        <v>51.74</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>SENCO</t>
+          <t>IIFLCAPS</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -3202,22 +3642,22 @@
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>350.75</v>
+        <v>342</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>57.76</v>
+        <v>56.31</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>55.81</v>
+        <v>56.56</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>50.15</v>
+        <v>58.59</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>LXCHEM</t>
+          <t>HCC</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -3226,22 +3666,22 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>158.66</v>
+        <v>23.37</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>57.35</v>
+        <v>56.25</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>54.27</v>
+        <v>57.4</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>41.63</v>
+        <v>47.54</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>PRINCEPIPE</t>
+          <t>FIEMIND</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -3250,22 +3690,22 @@
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>271.15</v>
+        <v>2308.7</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>57.19</v>
+        <v>56.22</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>53.23</v>
+        <v>58.71</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>39.66</v>
+        <v>68.02</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>JINDWORLD</t>
+          <t>KIRLPNU</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -3274,22 +3714,22 @@
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>29.39</v>
+        <v>1606</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>57.1</v>
+        <v>56.18</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>53.09</v>
+        <v>75.06</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>39</v>
+        <v>64.84999999999999</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>ARVINDFASN</t>
+          <t>BLUESTONE</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -3298,22 +3738,22 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>469.3</v>
+        <v>520.5</v>
       </c>
       <c r="D81" s="4" t="n">
-        <v>57.04</v>
+        <v>56.18</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>52.14</v>
+        <v>51.92</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>51.49</v>
+        <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>BBL</t>
+          <t>VIYASH</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -3322,22 +3762,22 @@
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>2841</v>
+        <v>249.95</v>
       </c>
       <c r="D82" s="4" t="n">
-        <v>56.94</v>
+        <v>56.16</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>53.4</v>
+        <v>65.18000000000001</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>49.97</v>
+        <v>62.16</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>SHAKTIPUMP</t>
+          <t>JUSTDIAL</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -3346,22 +3786,22 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>540.5</v>
+        <v>538.2</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>56.9</v>
+        <v>55.96</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>42.84</v>
+        <v>38.17</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>45.87</v>
+        <v>35.75</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>SWSOLAR</t>
+          <t>INDIASHLTR</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -3370,22 +3810,22 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>203.67</v>
+        <v>793.4</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>56.68</v>
+        <v>55.62</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>49.74</v>
+        <v>50.63</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>39.98</v>
+        <v>52.52</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>DATAMATICS</t>
+          <t>STARCEMENT</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -3394,22 +3834,22 @@
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>799.65</v>
+        <v>218.57</v>
       </c>
       <c r="D85" s="4" t="n">
-        <v>56.5</v>
+        <v>55.56</v>
       </c>
       <c r="E85" s="4" t="n">
-        <v>54.05</v>
+        <v>48.75</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>55.44</v>
+        <v>52.04</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>VOLTAMP</t>
+          <t>OSWALPUMPS</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -3418,22 +3858,22 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>9884.5</v>
+        <v>398.2</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>56.35</v>
+        <v>55.28</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>57.12</v>
+        <v>45.95</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>55.55</v>
+        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>WEBELSOLAR</t>
+          <t>ELLEN</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -3442,22 +3882,22 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>110.76</v>
+        <v>275.85</v>
       </c>
       <c r="D87" s="4" t="n">
-        <v>56.06</v>
+        <v>55.11</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>59.79</v>
+        <v>46.03</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>54.84</v>
+        <v/>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>MANORAMA</t>
+          <t>VAIBHAVGBL</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -3466,22 +3906,22 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>1476.1</v>
+        <v>230.46</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>56.01</v>
+        <v>55.05</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>55.61</v>
+        <v>53.24</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>62.42</v>
+        <v>46.09</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>VMART</t>
+          <t>SAMHI</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -3490,22 +3930,22 @@
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>665.55</v>
+        <v>163.49</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>55.95</v>
+        <v>55.04</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>53.6</v>
+        <v>49.36</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>47.73</v>
+        <v>46.57</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>RTNPOWER</t>
+          <t>TRIVENI</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -3514,22 +3954,22 @@
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>9.74</v>
+        <v>385.95</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>55.89</v>
+        <v>54.89</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>52.55</v>
+        <v>52.25</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>48.35</v>
+        <v>52.62</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>VSTIND</t>
+          <t>JSFB</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -3538,22 +3978,22 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>258.05</v>
+        <v>479.75</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>55.77</v>
+        <v>54.8</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>55.92</v>
+        <v>60.06</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>47.17</v>
+        <v>53.31</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>KITEX</t>
+          <t>SHAKTIPUMP</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -3562,22 +4002,22 @@
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>165.26</v>
+        <v>537.15</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>55.62</v>
+        <v>54.79</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>45.94</v>
+        <v>42.43</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>49.78</v>
+        <v>45.68</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>KIRLPNU</t>
+          <t>PARKHOSPS</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -3586,22 +4026,22 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>1570.8</v>
+        <v>274.6</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>54.91</v>
+        <v>54.69</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>73.54000000000001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>63.94</v>
+        <v/>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>ZYDUSWELL</t>
+          <t>AZAD</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -3610,22 +4050,22 @@
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>504.6</v>
+        <v>2150.1</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>54.83</v>
+        <v>54.69</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>60.7</v>
+        <v>62.6</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>62.28</v>
+        <v>63.04</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>PARADEEP</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -3634,22 +4074,22 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>127.58</v>
+        <v>1142.9</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>54.72</v>
+        <v>54.58</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>47.05</v>
+        <v>58.41</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>50.37</v>
+        <v>65.29000000000001</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>SANOFICONR</t>
+          <t>SMLMAH</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -3658,22 +4098,22 @@
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>4765.7</v>
+        <v>3883.8</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>54.67</v>
+        <v>54.54</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>54.82</v>
+        <v>51.14</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>50.24</v>
+        <v>60.26</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>JISLJALEQS</t>
+          <t>LLOYDSENGG</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -3682,22 +4122,22 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>31.89</v>
+        <v>70.94</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>54.48</v>
+        <v>54.52</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>41.22</v>
+        <v>65.84</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>37.54</v>
+        <v>57.52</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>BORORENEW</t>
+          <t>ASHAPURMIN</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -3706,22 +4146,22 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>524.3</v>
+        <v>692.05</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>54.33</v>
+        <v>54.2</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>52.98</v>
+        <v>56.63</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>51.16</v>
+        <v>58.61</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>CMSINFO</t>
+          <t>GOKULAGRO</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -3730,22 +4170,22 @@
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>305.8</v>
+        <v>233.07</v>
       </c>
       <c r="D99" s="4" t="n">
-        <v>54.3</v>
+        <v>54.18</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>44.38</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>39.84</v>
+        <v>68.84</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>JSFB</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -3754,22 +4194,22 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>477.55</v>
+        <v>179.86</v>
       </c>
       <c r="D100" s="4" t="n">
-        <v>54.19</v>
+        <v>54.15</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>59.71</v>
+        <v>54.3</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>53.05</v>
+        <v>58.89</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>HCG</t>
+          <t>SKYGOLD</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -3778,22 +4218,22 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>635.95</v>
+        <v>508.95</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>54.02</v>
+        <v>54.1</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>56.96</v>
+        <v>63.71</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>59.87</v>
+        <v>69.19</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>IMFA</t>
+          <t>UTLSOLAR</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -3802,22 +4242,22 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>1499</v>
+        <v>310.15</v>
       </c>
       <c r="D102" s="4" t="n">
-        <v>53.9</v>
+        <v>53.88</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>59.95</v>
+        <v>67.45999999999999</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>68.40000000000001</v>
+        <v/>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>PCJEWELLER</t>
+          <t>AXISCADES</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -3826,22 +4266,22 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>9.18</v>
+        <v>1947.6</v>
       </c>
       <c r="D103" s="4" t="n">
-        <v>53.73</v>
+        <v>53.74</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>45.94</v>
+        <v>61.44</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>47.35</v>
+        <v>69.59999999999999</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>VAIBHAVGBL</t>
+          <t>CRAMC</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -3850,22 +4290,22 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>228.46</v>
+        <v>250.15</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>53.73</v>
+        <v>53.35</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>52.51</v>
+        <v>45.15</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>45.75</v>
+        <v/>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>KRBL</t>
+          <t>RTNINDIA</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -3874,22 +4314,22 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>356.65</v>
+        <v>36.4</v>
       </c>
       <c r="D105" s="4" t="n">
-        <v>53.51</v>
+        <v>53.35</v>
       </c>
       <c r="E105" s="4" t="n">
-        <v>51.49</v>
+        <v>49.82</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>52.25</v>
+        <v>42.77</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>SUNFLAG</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -3898,22 +4338,22 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>372.1</v>
+        <v>1728.3</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>53.43</v>
+        <v>53.07</v>
       </c>
       <c r="E106" s="4" t="n">
-        <v>67.73999999999999</v>
+        <v>62.34</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>65.76000000000001</v>
+        <v/>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -3922,22 +4362,22 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>1138.2</v>
+        <v>503.85</v>
       </c>
       <c r="D107" s="4" t="n">
-        <v>53.35</v>
+        <v>52.94</v>
       </c>
       <c r="E107" s="4" t="n">
-        <v>58.09</v>
+        <v>57.84</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>65.08</v>
+        <v>49.45</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>ROUTE</t>
+          <t>METROPOLIS</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -3946,22 +4386,22 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>525.45</v>
+        <v>530.7</v>
       </c>
       <c r="D108" s="4" t="n">
-        <v>53.27</v>
+        <v>52.87</v>
       </c>
       <c r="E108" s="4" t="n">
-        <v>42.44</v>
+        <v>58.69</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>30.24</v>
+        <v>57.35</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>MAHLIFE</t>
+          <t>KSB</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -3970,22 +4410,22 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>338.5</v>
+        <v>834.8</v>
       </c>
       <c r="D109" s="4" t="n">
-        <v>53.18</v>
+        <v>52.69</v>
       </c>
       <c r="E109" s="4" t="n">
-        <v>46.61</v>
+        <v>52.44</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>43.05</v>
+        <v>54.96</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>SAMHI</t>
+          <t>BECTORFOOD</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -3994,22 +4434,22 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>162.05</v>
+        <v>181.65</v>
       </c>
       <c r="D110" s="4" t="n">
-        <v>53.07</v>
+        <v>52.38</v>
       </c>
       <c r="E110" s="4" t="n">
-        <v>48.51</v>
+        <v>37.14</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>46.22</v>
+        <v>39.67</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>RAYMONDLSL</t>
+          <t>VIKRAMSOLR</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -4018,22 +4458,22 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>767.65</v>
+        <v>209.86</v>
       </c>
       <c r="D111" s="4" t="n">
-        <v>53.03</v>
+        <v>52.31</v>
       </c>
       <c r="E111" s="4" t="n">
-        <v>39.86</v>
+        <v>44.82</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>25.4</v>
+        <v/>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>DODLA</t>
+          <t>JLHL</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -4042,22 +4482,22 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>1097.2</v>
+        <v>1315.7</v>
       </c>
       <c r="D112" s="4" t="n">
-        <v>53</v>
+        <v>52.21</v>
       </c>
       <c r="E112" s="4" t="n">
-        <v>46.62</v>
+        <v>50.01</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>49.65</v>
+        <v>48.18</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>BELRISE</t>
+          <t>ATLANTAELE</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -4066,13 +4506,13 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>215.98</v>
+        <v>1843.7</v>
       </c>
       <c r="D113" s="4" t="n">
-        <v>52.87</v>
+        <v>52.15</v>
       </c>
       <c r="E113" s="4" t="n">
-        <v>64.87</v>
+        <v>68.13</v>
       </c>
       <c r="F113" s="4" t="n">
         <v/>
@@ -4081,7 +4521,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>AGI</t>
+          <t>PGIL</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -4090,22 +4530,22 @@
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>598.95</v>
+        <v>1630.9</v>
       </c>
       <c r="D114" s="4" t="n">
-        <v>52.7</v>
+        <v>52.12</v>
       </c>
       <c r="E114" s="4" t="n">
-        <v>46.52</v>
+        <v>54.43</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>44.79</v>
+        <v>62.48</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>EDELWEISS</t>
+          <t>VOLTAMP</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -4114,22 +4554,22 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>114.67</v>
+        <v>9719.5</v>
       </c>
       <c r="D115" s="4" t="n">
-        <v>52.61</v>
+        <v>52.11</v>
       </c>
       <c r="E115" s="4" t="n">
-        <v>52.19</v>
+        <v>55.66</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>57.32</v>
+        <v>55.02</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>PATELENG</t>
+          <t>AVL</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -4138,22 +4578,22 @@
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>27.22</v>
+        <v>536.9</v>
       </c>
       <c r="D116" s="4" t="n">
-        <v>52.47</v>
+        <v>52.1</v>
       </c>
       <c r="E116" s="4" t="n">
-        <v>44.99</v>
+        <v>55.89</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>37.69</v>
+        <v>57.69</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>GREENPANEL</t>
+          <t>ADVENZYMES</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -4162,22 +4602,22 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>201.91</v>
+        <v>368.95</v>
       </c>
       <c r="D117" s="4" t="n">
-        <v>52.21</v>
+        <v>52.08</v>
       </c>
       <c r="E117" s="4" t="n">
-        <v>44.71</v>
+        <v>65.58</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>41</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>VIPIND</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -4186,22 +4626,22 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>262</v>
+        <v>314.95</v>
       </c>
       <c r="D118" s="4" t="n">
-        <v>52.15</v>
+        <v>51.93</v>
       </c>
       <c r="E118" s="4" t="n">
-        <v>65.36</v>
+        <v>42.7</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>65.54000000000001</v>
+        <v>37.81</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>KNRCON</t>
+          <t>LXCHEM</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -4210,22 +4650,22 @@
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>130.32</v>
+        <v>153.88</v>
       </c>
       <c r="D119" s="4" t="n">
-        <v>52.14</v>
+        <v>51.84</v>
       </c>
       <c r="E119" s="4" t="n">
-        <v>44.42</v>
+        <v>51.7</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>34.91</v>
+        <v>40.36</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>SHRIPISTON</t>
+          <t>SMARTWORKS</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -4234,22 +4674,22 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>3406.1</v>
+        <v>446.35</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>51.95</v>
+        <v>51.7</v>
       </c>
       <c r="E120" s="4" t="n">
-        <v>56.54</v>
+        <v>50.42</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>69.43000000000001</v>
+        <v/>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>RATNAMANI</t>
+          <t>DATAMATICS</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -4258,22 +4698,22 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>2614.9</v>
+        <v>778.4</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>51.88</v>
+        <v>51.7</v>
       </c>
       <c r="E121" s="4" t="n">
-        <v>55.89</v>
+        <v>51.78</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>50.19</v>
+        <v>54.48</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>ADVENZYMES</t>
+          <t>MTARTECH</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -4282,22 +4722,22 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>367.05</v>
+        <v>7159.5</v>
       </c>
       <c r="D122" s="4" t="n">
-        <v>51.7</v>
+        <v>51.67</v>
       </c>
       <c r="E122" s="4" t="n">
-        <v>65.15000000000001</v>
+        <v>75.42</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>56.26</v>
+        <v>79.19</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>MASTEK</t>
+          <t>ETHOSLTD</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -4306,22 +4746,22 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>1660.1</v>
+        <v>2391.8</v>
       </c>
       <c r="D123" s="4" t="n">
-        <v>51.7</v>
+        <v>51.64</v>
       </c>
       <c r="E123" s="4" t="n">
-        <v>42.89</v>
+        <v>46.8</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>40.47</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>YATHARTH</t>
+          <t>JAMNAAUTO</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -4330,22 +4770,22 @@
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>808.9</v>
+        <v>121.8</v>
       </c>
       <c r="D124" s="4" t="n">
-        <v>50.81</v>
+        <v>51.61</v>
       </c>
       <c r="E124" s="4" t="n">
-        <v>57.59</v>
+        <v>50.58</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>61.99</v>
+        <v>54.53</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>INDIGOPNTS</t>
+          <t>CSBBANK</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -4354,22 +4794,22 @@
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>954.2</v>
+        <v>366.35</v>
       </c>
       <c r="D125" s="4" t="n">
-        <v>50.53</v>
+        <v>51.43</v>
       </c>
       <c r="E125" s="4" t="n">
-        <v>48.84</v>
+        <v>45.56</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>43.57</v>
+        <v>50.67</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>OPTIEMUS</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -4378,22 +4818,22 @@
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>499.75</v>
+        <v>423.3</v>
       </c>
       <c r="D126" s="4" t="n">
-        <v>50.51</v>
+        <v>51.39</v>
       </c>
       <c r="E126" s="4" t="n">
-        <v>56.88</v>
+        <v>48.29</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>49.04</v>
+        <v>47.57</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>PRUDENT</t>
+          <t>VARROC</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -4402,22 +4842,22 @@
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>2696.9</v>
+        <v>570.35</v>
       </c>
       <c r="D127" s="4" t="n">
-        <v>50.17</v>
+        <v>51.32</v>
       </c>
       <c r="E127" s="4" t="n">
-        <v>54.69</v>
+        <v>53.82</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>57.16</v>
+        <v>53.67</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>JAMNAAUTO</t>
+          <t>ROUTE</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -4426,22 +4866,22 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>121.65</v>
+        <v>521.9</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>50.16</v>
+        <v>51.28</v>
       </c>
       <c r="E128" s="4" t="n">
-        <v>50.49</v>
+        <v>41.92</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>54.47</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>HEMIPROP</t>
+          <t>HCG</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -4450,22 +4890,22 @@
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>141.07</v>
+        <v>630.5</v>
       </c>
       <c r="D129" s="4" t="n">
-        <v>50.07</v>
+        <v>51.2</v>
       </c>
       <c r="E129" s="4" t="n">
-        <v>52.25</v>
+        <v>55.43</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>49.75</v>
+        <v>59.22</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>DCAL</t>
+          <t>RCF</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -4474,22 +4914,22 @@
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>189.88</v>
+        <v>127.35</v>
       </c>
       <c r="D130" s="4" t="n">
-        <v>49.81</v>
+        <v>51</v>
       </c>
       <c r="E130" s="4" t="n">
-        <v>46.85</v>
+        <v>47.59</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>47.28</v>
+        <v>46.79</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>TANLA</t>
+          <t>REDTAPE</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -4498,22 +4938,22 @@
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>517.15</v>
+        <v>133.87</v>
       </c>
       <c r="D131" s="4" t="n">
-        <v>49.8</v>
+        <v>50.96</v>
       </c>
       <c r="E131" s="4" t="n">
-        <v>52.11</v>
+        <v>52.74</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>44.22</v>
+        <v>35.38</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>GOKEX</t>
+          <t>GAEL</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -4522,22 +4962,22 @@
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>693.85</v>
+        <v>157.83</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>49.69</v>
+        <v>50.59</v>
       </c>
       <c r="E132" s="4" t="n">
-        <v>48.38</v>
+        <v>61.51</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>47.72</v>
+        <v>62.77</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>GPPL</t>
+          <t>MEDPLUS</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -4546,22 +4986,22 @@
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>155.74</v>
+        <v>881.95</v>
       </c>
       <c r="D133" s="4" t="n">
-        <v>49.55</v>
+        <v>50.44</v>
       </c>
       <c r="E133" s="4" t="n">
-        <v>46.55</v>
+        <v>53.75</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>50.74</v>
+        <v>56.51</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>SENCO</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -4570,22 +5010,22 @@
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>93.86</v>
+        <v>338.35</v>
       </c>
       <c r="D134" s="4" t="n">
-        <v>49.33</v>
+        <v>50.26</v>
       </c>
       <c r="E134" s="4" t="n">
-        <v>37.62</v>
+        <v>52.38</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>37.39</v>
+        <v>48.89</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>CCAVENUE</t>
+          <t>RATNAMANI</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -4594,22 +5034,22 @@
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>14.01</v>
+        <v>2580.5</v>
       </c>
       <c r="D135" s="4" t="n">
-        <v>49.19</v>
+        <v>50.21</v>
       </c>
       <c r="E135" s="4" t="n">
-        <v>41.73</v>
+        <v>54.4</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>38.92</v>
+        <v>49.47</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>PRIVISCL</t>
+          <t>UJJIVANSFB</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -4618,22 +5058,22 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>3230.7</v>
+        <v>54.76</v>
       </c>
       <c r="D136" s="4" t="n">
-        <v>49.06</v>
+        <v>50.19</v>
       </c>
       <c r="E136" s="4" t="n">
-        <v>56.75</v>
+        <v>49.05</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>66.79000000000001</v>
+        <v>56.45</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>FDC</t>
+          <t>ALIVUS</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -4642,22 +5082,22 @@
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>381</v>
+        <v>1045.7</v>
       </c>
       <c r="D137" s="4" t="n">
-        <v>49.01</v>
+        <v>50.12</v>
       </c>
       <c r="E137" s="4" t="n">
-        <v>50.49</v>
+        <v>57.7</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>46.75</v>
+        <v>58.54</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>EPL</t>
+          <t>HEMIPROP</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -4666,22 +5106,22 @@
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>217.33</v>
+        <v>140.37</v>
       </c>
       <c r="D138" s="4" t="n">
-        <v>48.65</v>
+        <v>50.07</v>
       </c>
       <c r="E138" s="4" t="n">
-        <v>51.22</v>
+        <v>51.8</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>52.24</v>
+        <v>49.54</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>ETHOSLTD</t>
+          <t>EMBDL</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -4690,22 +5130,22 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>2367.1</v>
+        <v>59.06</v>
       </c>
       <c r="D139" s="4" t="n">
-        <v>48.65</v>
+        <v>49.69</v>
       </c>
       <c r="E139" s="4" t="n">
-        <v>45.81</v>
+        <v>46.62</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>48.04</v>
+        <v>41.3</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>SANDUMA</t>
+          <t>TEXRAIL</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -4714,22 +5154,22 @@
         </is>
       </c>
       <c r="C140" s="4" t="n">
-        <v>222.86</v>
+        <v>105.86</v>
       </c>
       <c r="D140" s="4" t="n">
-        <v>48.64</v>
+        <v>49.67</v>
       </c>
       <c r="E140" s="4" t="n">
-        <v>54.94</v>
+        <v>45.09</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>60.44</v>
+        <v>42.93</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>PNGJL</t>
+          <t>APLLTD</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -4738,22 +5178,22 @@
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>572.35</v>
+        <v>743.35</v>
       </c>
       <c r="D141" s="4" t="n">
-        <v>48.51</v>
+        <v>49.65</v>
       </c>
       <c r="E141" s="4" t="n">
-        <v>47.08</v>
+        <v>44.31</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>45.36</v>
+        <v>43.75</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>LUMAXTECH</t>
+          <t>TANLA</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -4762,22 +5202,22 @@
         </is>
       </c>
       <c r="C142" s="4" t="n">
-        <v>1664.4</v>
+        <v>513.7</v>
       </c>
       <c r="D142" s="4" t="n">
-        <v>48.48</v>
+        <v>49.51</v>
       </c>
       <c r="E142" s="4" t="n">
-        <v>54.36</v>
+        <v>51.52</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>67.67</v>
+        <v>44.03</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>PNCINFRA</t>
+          <t>SAFARI</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -4786,22 +5226,22 @@
         </is>
       </c>
       <c r="C143" s="4" t="n">
-        <v>209.91</v>
+        <v>1535.1</v>
       </c>
       <c r="D143" s="4" t="n">
-        <v>48.25</v>
+        <v>49.49</v>
       </c>
       <c r="E143" s="4" t="n">
-        <v>44.68</v>
+        <v>41.49</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>39.81</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>AARTIDRUGS</t>
+          <t>AHLUCONT</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -4810,22 +5250,22 @@
         </is>
       </c>
       <c r="C144" s="4" t="n">
-        <v>376.85</v>
+        <v>798.1</v>
       </c>
       <c r="D144" s="4" t="n">
-        <v>48.03</v>
+        <v>49.15</v>
       </c>
       <c r="E144" s="4" t="n">
-        <v>47.52</v>
+        <v>45.37</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>44.37</v>
+        <v>46.71</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>KANSAINER</t>
+          <t>PCJEWELLER</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -4834,22 +5274,22 @@
         </is>
       </c>
       <c r="C145" s="4" t="n">
-        <v>210.89</v>
+        <v>8.92</v>
       </c>
       <c r="D145" s="4" t="n">
-        <v>48.01</v>
+        <v>49.13</v>
       </c>
       <c r="E145" s="4" t="n">
-        <v>49.58</v>
+        <v>44.18</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>42.16</v>
+        <v>46.66</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>BALUFORGE</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -4858,22 +5298,22 @@
         </is>
       </c>
       <c r="C146" s="4" t="n">
-        <v>479.3</v>
+        <v>543</v>
       </c>
       <c r="D146" s="4" t="n">
-        <v>47.97</v>
+        <v>49.12</v>
       </c>
       <c r="E146" s="4" t="n">
-        <v>46.43</v>
+        <v>44.43</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>47.62</v>
+        <v>44.92</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>TSFINV</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -4882,22 +5322,22 @@
         </is>
       </c>
       <c r="C147" s="4" t="n">
-        <v>399.45</v>
+        <v>434.9</v>
       </c>
       <c r="D147" s="4" t="n">
-        <v>47.91</v>
+        <v>49.04</v>
       </c>
       <c r="E147" s="4" t="n">
-        <v>46.05</v>
+        <v>48.36</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>52.81</v>
+        <v>56.36</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>GMRP&amp;UI</t>
+          <t>NFL</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -4906,22 +5346,22 @@
         </is>
       </c>
       <c r="C148" s="4" t="n">
-        <v>108.31</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="D148" s="4" t="n">
-        <v>47.89</v>
+        <v>49.02</v>
       </c>
       <c r="E148" s="4" t="n">
-        <v>49.63</v>
+        <v>43.9</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>53.71</v>
+        <v>44.51</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>INOXGREEN</t>
+          <t>NETWORK18</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -4930,22 +5370,22 @@
         </is>
       </c>
       <c r="C149" s="4" t="n">
-        <v>173.5</v>
+        <v>31.51</v>
       </c>
       <c r="D149" s="4" t="n">
-        <v>47.83</v>
+        <v>48.99</v>
       </c>
       <c r="E149" s="4" t="n">
-        <v>49.04</v>
+        <v>37.85</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>52.15</v>
+        <v>35.97</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>WAAREERTL</t>
+          <t>INDIAGLYCO</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -4954,22 +5394,22 @@
         </is>
       </c>
       <c r="C150" s="4" t="n">
-        <v>970.25</v>
+        <v>986.65</v>
       </c>
       <c r="D150" s="4" t="n">
-        <v>47.82</v>
+        <v>48.96</v>
       </c>
       <c r="E150" s="4" t="n">
-        <v>51</v>
+        <v>52.77</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v/>
+        <v>59.25</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>BOSCH-HCIL</t>
+          <t>SHAREINDIA</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -4978,22 +5418,22 @@
         </is>
       </c>
       <c r="C151" s="4" t="n">
-        <v>1373.3</v>
+        <v>136.38</v>
       </c>
       <c r="D151" s="4" t="n">
-        <v>47.81</v>
+        <v>48.88</v>
       </c>
       <c r="E151" s="4" t="n">
-        <v>47.23</v>
+        <v>44.71</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>45.38</v>
+        <v>39.87</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>GATEWAY</t>
+          <t>FINPIPE</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -5002,22 +5442,22 @@
         </is>
       </c>
       <c r="C152" s="4" t="n">
-        <v>56.14</v>
+        <v>173.02</v>
       </c>
       <c r="D152" s="4" t="n">
-        <v>47.79</v>
+        <v>48.88</v>
       </c>
       <c r="E152" s="4" t="n">
-        <v>47.29</v>
+        <v>47.55</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>41</v>
+        <v>44.48</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>DHANUKA</t>
+          <t>MAHSCOOTER</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -5026,22 +5466,22 @@
         </is>
       </c>
       <c r="C153" s="4" t="n">
-        <v>1095.9</v>
+        <v>12335</v>
       </c>
       <c r="D153" s="4" t="n">
-        <v>47.75</v>
+        <v>48.84</v>
       </c>
       <c r="E153" s="4" t="n">
-        <v>47.04</v>
+        <v>45</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>44.98</v>
+        <v>53.09</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>POLYPLEX</t>
+          <t>ASHOKA</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -5050,22 +5490,22 @@
         </is>
       </c>
       <c r="C154" s="4" t="n">
-        <v>903.1</v>
+        <v>123.06</v>
       </c>
       <c r="D154" s="4" t="n">
-        <v>47.64</v>
+        <v>48.55</v>
       </c>
       <c r="E154" s="4" t="n">
-        <v>50.66</v>
+        <v>38.27</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>44.42</v>
+        <v>42.11</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>EMBDL</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -5074,22 +5514,22 @@
         </is>
       </c>
       <c r="C155" s="4" t="n">
-        <v>58.59</v>
+        <v>189.2</v>
       </c>
       <c r="D155" s="4" t="n">
-        <v>47.54</v>
+        <v>48.45</v>
       </c>
       <c r="E155" s="4" t="n">
-        <v>46.21</v>
+        <v>55.16</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>41.18</v>
+        <v>57.97</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>RELIGARE</t>
+          <t>FEDFINA</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -5098,22 +5538,22 @@
         </is>
       </c>
       <c r="C156" s="4" t="n">
-        <v>228.14</v>
+        <v>152.79</v>
       </c>
       <c r="D156" s="4" t="n">
-        <v>47.45</v>
+        <v>48.42</v>
       </c>
       <c r="E156" s="4" t="n">
-        <v>48.45</v>
+        <v>56.49</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>49.88</v>
+        <v>58.15</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>MANINFRA</t>
+          <t>LLOYDSENT</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -5122,22 +5562,22 @@
         </is>
       </c>
       <c r="C157" s="4" t="n">
-        <v>114.1</v>
+        <v>66.93000000000001</v>
       </c>
       <c r="D157" s="4" t="n">
-        <v>47.23</v>
+        <v>48.37</v>
       </c>
       <c r="E157" s="4" t="n">
-        <v>48.9</v>
+        <v>55.29</v>
       </c>
       <c r="F157" s="4" t="n">
-        <v>43.12</v>
+        <v>54.98</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>CSBBANK</t>
+          <t>PICCADIL</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -5146,22 +5586,22 @@
         </is>
       </c>
       <c r="C158" s="4" t="n">
-        <v>362.05</v>
+        <v>580.95</v>
       </c>
       <c r="D158" s="4" t="n">
-        <v>47.12</v>
+        <v>48.19</v>
       </c>
       <c r="E158" s="4" t="n">
-        <v>44.35</v>
+        <v>48.94</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v>50.11</v>
+        <v/>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>GAEL</t>
+          <t>GPPL</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -5170,22 +5610,22 @@
         </is>
       </c>
       <c r="C159" s="4" t="n">
-        <v>155.86</v>
+        <v>153.88</v>
       </c>
       <c r="D159" s="4" t="n">
-        <v>47.07</v>
+        <v>48.13</v>
       </c>
       <c r="E159" s="4" t="n">
-        <v>60.36</v>
+        <v>45.2</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>62.08</v>
+        <v>50.14</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>KSL</t>
+          <t>ANUP</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -5194,22 +5634,22 @@
         </is>
       </c>
       <c r="C160" s="4" t="n">
-        <v>809.5</v>
+        <v>1901.1</v>
       </c>
       <c r="D160" s="4" t="n">
-        <v>46.48</v>
+        <v>48.09</v>
       </c>
       <c r="E160" s="4" t="n">
-        <v>55.78</v>
+        <v>46.83</v>
       </c>
       <c r="F160" s="4" t="n">
-        <v>52.69</v>
+        <v>47.04</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>AHLUCONT</t>
+          <t>MAHSEAMLES</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -5218,22 +5658,22 @@
         </is>
       </c>
       <c r="C161" s="4" t="n">
-        <v>792.95</v>
+        <v>617.1</v>
       </c>
       <c r="D161" s="4" t="n">
-        <v>46.43</v>
+        <v>47.87</v>
       </c>
       <c r="E161" s="4" t="n">
-        <v>44.69</v>
+        <v>55.19</v>
       </c>
       <c r="F161" s="4" t="n">
-        <v>46.49</v>
+        <v>50.97</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>PRICOLLTD</t>
+          <t>SUBROS</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -5242,22 +5682,22 @@
         </is>
       </c>
       <c r="C162" s="4" t="n">
-        <v>561.35</v>
+        <v>721.55</v>
       </c>
       <c r="D162" s="4" t="n">
-        <v>46.41</v>
+        <v>47.59</v>
       </c>
       <c r="E162" s="4" t="n">
-        <v>48.28</v>
+        <v>43.56</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>56.91</v>
+        <v>49.98</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>ANURAS</t>
+          <t>STAR</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -5266,22 +5706,22 @@
         </is>
       </c>
       <c r="C163" s="4" t="n">
-        <v>1328.2</v>
+        <v>1055.5</v>
       </c>
       <c r="D163" s="4" t="n">
-        <v>46.24</v>
+        <v>47.55</v>
       </c>
       <c r="E163" s="4" t="n">
-        <v>56.97</v>
+        <v>57.49</v>
       </c>
       <c r="F163" s="4" t="n">
-        <v>67.03</v>
+        <v>58.24</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>CIEINDIA</t>
+          <t>ORIENTCEM</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -5290,22 +5730,22 @@
         </is>
       </c>
       <c r="C164" s="4" t="n">
-        <v>452.05</v>
+        <v>134.77</v>
       </c>
       <c r="D164" s="4" t="n">
-        <v>46.22</v>
+        <v>47.51</v>
       </c>
       <c r="E164" s="4" t="n">
-        <v>52.32</v>
+        <v>35.11</v>
       </c>
       <c r="F164" s="4" t="n">
-        <v>53.39</v>
+        <v>35.41</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>ANUP</t>
+          <t>TDPOWERSYS</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -5314,22 +5754,22 @@
         </is>
       </c>
       <c r="C165" s="4" t="n">
-        <v>1915.3</v>
+        <v>1192.8</v>
       </c>
       <c r="D165" s="4" t="n">
-        <v>46.18</v>
+        <v>47.4</v>
       </c>
       <c r="E165" s="4" t="n">
-        <v>47.34</v>
+        <v>65.87</v>
       </c>
       <c r="F165" s="4" t="n">
-        <v>47.3</v>
+        <v>75.23</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>VESUVIUS</t>
+          <t>TIPSMUSIC</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -5338,22 +5778,22 @@
         </is>
       </c>
       <c r="C166" s="4" t="n">
-        <v>473.65</v>
+        <v>640.25</v>
       </c>
       <c r="D166" s="4" t="n">
-        <v>46.12</v>
+        <v>47.34</v>
       </c>
       <c r="E166" s="4" t="n">
-        <v>47.04</v>
+        <v>57.26</v>
       </c>
       <c r="F166" s="4" t="n">
-        <v>52.04</v>
+        <v>57.97</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>DBL</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -5362,22 +5802,22 @@
         </is>
       </c>
       <c r="C167" s="4" t="n">
-        <v>271.5</v>
+        <v>430.5</v>
       </c>
       <c r="D167" s="4" t="n">
-        <v>45.98</v>
+        <v>47.28</v>
       </c>
       <c r="E167" s="4" t="n">
-        <v>51.41</v>
+        <v>46.51</v>
       </c>
       <c r="F167" s="4" t="n">
-        <v>53.63</v>
+        <v>48.82</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>JSLL</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -5386,22 +5826,22 @@
         </is>
       </c>
       <c r="C168" s="4" t="n">
-        <v>438.65</v>
+        <v>612.2</v>
       </c>
       <c r="D168" s="4" t="n">
-        <v>45.96</v>
+        <v>47.2</v>
       </c>
       <c r="E168" s="4" t="n">
-        <v>46.94</v>
+        <v>43.65</v>
       </c>
       <c r="F168" s="4" t="n">
-        <v>51.28</v>
+        <v>42.96</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>DYNAMATECH</t>
+          <t>WEBELSOLAR</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -5410,22 +5850,22 @@
         </is>
       </c>
       <c r="C169" s="4" t="n">
-        <v>10544</v>
+        <v>103.63</v>
       </c>
       <c r="D169" s="4" t="n">
-        <v>45.92</v>
+        <v>47.13</v>
       </c>
       <c r="E169" s="4" t="n">
-        <v>53.61</v>
+        <v>54.82</v>
       </c>
       <c r="F169" s="4" t="n">
-        <v>63.82</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENT</t>
+          <t>DBREALTY</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -5434,22 +5874,22 @@
         </is>
       </c>
       <c r="C170" s="4" t="n">
-        <v>66.86</v>
+        <v>111.88</v>
       </c>
       <c r="D170" s="4" t="n">
-        <v>45.65</v>
+        <v>47</v>
       </c>
       <c r="E170" s="4" t="n">
-        <v>55.22</v>
+        <v>46.93</v>
       </c>
       <c r="F170" s="4" t="n">
-        <v>54.94</v>
+        <v>44.26</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>STYRENIX</t>
+          <t>ARVINDFASN</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -5458,22 +5898,22 @@
         </is>
       </c>
       <c r="C171" s="4" t="n">
-        <v>2201.2</v>
+        <v>450.2</v>
       </c>
       <c r="D171" s="4" t="n">
-        <v>45.61</v>
+        <v>46.99</v>
       </c>
       <c r="E171" s="4" t="n">
-        <v>51.99</v>
+        <v>48.38</v>
       </c>
       <c r="F171" s="4" t="n">
-        <v>52.12</v>
+        <v>49.19</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>TEXRAIL</t>
+          <t>AEQUS</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -5482,22 +5922,22 @@
         </is>
       </c>
       <c r="C172" s="4" t="n">
-        <v>104.37</v>
+        <v>182.53</v>
       </c>
       <c r="D172" s="4" t="n">
-        <v>45.51</v>
+        <v>46.97</v>
       </c>
       <c r="E172" s="4" t="n">
-        <v>43.8</v>
+        <v>59.36</v>
       </c>
       <c r="F172" s="4" t="n">
-        <v>42.52</v>
+        <v/>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>LUXIND</t>
+          <t>SUDARSCHEM</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -5506,22 +5946,22 @@
         </is>
       </c>
       <c r="C173" s="4" t="n">
-        <v>1343.4</v>
+        <v>882.15</v>
       </c>
       <c r="D173" s="4" t="n">
-        <v>45.48</v>
+        <v>46.93</v>
       </c>
       <c r="E173" s="4" t="n">
-        <v>54.65</v>
+        <v>45.79</v>
       </c>
       <c r="F173" s="4" t="n">
-        <v>49.3</v>
+        <v>47.34</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>VINATIORGA</t>
+          <t>V2RETAIL</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -5530,22 +5970,22 @@
         </is>
       </c>
       <c r="C174" s="4" t="n">
-        <v>1304.1</v>
+        <v>223.48</v>
       </c>
       <c r="D174" s="4" t="n">
-        <v>45.42</v>
+        <v>46.91</v>
       </c>
       <c r="E174" s="4" t="n">
-        <v>36.68</v>
+        <v>54.51</v>
       </c>
       <c r="F174" s="4" t="n">
-        <v>35.48</v>
+        <v>65.02</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>JUSTDIAL</t>
+          <t>LUMAXTECH</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -5554,22 +5994,22 @@
         </is>
       </c>
       <c r="C175" s="4" t="n">
-        <v>523.6</v>
+        <v>1634</v>
       </c>
       <c r="D175" s="4" t="n">
-        <v>45.29</v>
+        <v>46.89</v>
       </c>
       <c r="E175" s="4" t="n">
-        <v>34.42</v>
+        <v>52.94</v>
       </c>
       <c r="F175" s="4" t="n">
-        <v>34.58</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>EMIL</t>
+          <t>SHARDACROP</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -5578,22 +6018,22 @@
         </is>
       </c>
       <c r="C176" s="4" t="n">
-        <v>111.44</v>
+        <v>923.35</v>
       </c>
       <c r="D176" s="4" t="n">
-        <v>45.19</v>
+        <v>46.81</v>
       </c>
       <c r="E176" s="4" t="n">
-        <v>50.58</v>
+        <v>47.01</v>
       </c>
       <c r="F176" s="4" t="n">
-        <v>44.93</v>
+        <v>54.65</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>SUDARSCHEM</t>
+          <t>MANYAVAR</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -5602,22 +6042,22 @@
         </is>
       </c>
       <c r="C177" s="4" t="n">
-        <v>886.65</v>
+        <v>407.4</v>
       </c>
       <c r="D177" s="4" t="n">
-        <v>45.17</v>
+        <v>46.78</v>
       </c>
       <c r="E177" s="4" t="n">
-        <v>46.13</v>
+        <v>36.82</v>
       </c>
       <c r="F177" s="4" t="n">
-        <v>47.52</v>
+        <v>28.31</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>EPIGRAL</t>
+          <t>EDELWEISS</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -5626,22 +6066,22 @@
         </is>
       </c>
       <c r="C178" s="4" t="n">
-        <v>1163.9</v>
+        <v>109.93</v>
       </c>
       <c r="D178" s="4" t="n">
-        <v>45.05</v>
+        <v>46.77</v>
       </c>
       <c r="E178" s="4" t="n">
-        <v>48.24</v>
+        <v>48.42</v>
       </c>
       <c r="F178" s="4" t="n">
-        <v>44.22</v>
+        <v>55.26</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>EMUDHRA</t>
+          <t>SANOFICONR</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -5650,22 +6090,22 @@
         </is>
       </c>
       <c r="C179" s="4" t="n">
-        <v>465.95</v>
+        <v>4616.9</v>
       </c>
       <c r="D179" s="4" t="n">
-        <v>44.49</v>
+        <v>46.77</v>
       </c>
       <c r="E179" s="4" t="n">
-        <v>40.99</v>
+        <v>50.63</v>
       </c>
       <c r="F179" s="4" t="n">
-        <v>39.58</v>
+        <v>47.51</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>INDIAGLYCO</t>
+          <t>TSFINV</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -5674,22 +6114,22 @@
         </is>
       </c>
       <c r="C180" s="4" t="n">
-        <v>978.4</v>
+        <v>394.2</v>
       </c>
       <c r="D180" s="4" t="n">
-        <v>44.48</v>
+        <v>46.71</v>
       </c>
       <c r="E180" s="4" t="n">
-        <v>52.06</v>
+        <v>44.98</v>
       </c>
       <c r="F180" s="4" t="n">
-        <v>58.96</v>
+        <v>52.36</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>BIRLACORPN</t>
+          <t>KNRCON</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -5698,22 +6138,22 @@
         </is>
       </c>
       <c r="C181" s="4" t="n">
-        <v>964.05</v>
+        <v>125.17</v>
       </c>
       <c r="D181" s="4" t="n">
-        <v>44.42</v>
+        <v>46.61</v>
       </c>
       <c r="E181" s="4" t="n">
-        <v>46.01</v>
+        <v>41.78</v>
       </c>
       <c r="F181" s="4" t="n">
-        <v>42.31</v>
+        <v>33.72</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>IMAGICAA</t>
+          <t>AURIONPRO</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -5722,22 +6162,22 @@
         </is>
       </c>
       <c r="C182" s="4" t="n">
-        <v>43.55</v>
+        <v>777.25</v>
       </c>
       <c r="D182" s="4" t="n">
-        <v>44.28</v>
+        <v>46.59</v>
       </c>
       <c r="E182" s="4" t="n">
-        <v>44.01</v>
+        <v>38.7</v>
       </c>
       <c r="F182" s="4" t="n">
-        <v>40.87</v>
+        <v>39.91</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>PURVA</t>
+          <t>WAAREERTL</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -5746,22 +6186,22 @@
         </is>
       </c>
       <c r="C183" s="4" t="n">
-        <v>210.44</v>
+        <v>954.15</v>
       </c>
       <c r="D183" s="4" t="n">
-        <v>44.13</v>
+        <v>46.54</v>
       </c>
       <c r="E183" s="4" t="n">
-        <v>46.08</v>
+        <v>49.51</v>
       </c>
       <c r="F183" s="4" t="n">
-        <v>44.52</v>
+        <v/>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>MOIL</t>
+          <t>WESTLIFE</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -5770,22 +6210,22 @@
         </is>
       </c>
       <c r="C184" s="4" t="n">
-        <v>297.8</v>
+        <v>445.85</v>
       </c>
       <c r="D184" s="4" t="n">
-        <v>43.99</v>
+        <v>46.42</v>
       </c>
       <c r="E184" s="4" t="n">
-        <v>45.09</v>
+        <v>36.83</v>
       </c>
       <c r="F184" s="4" t="n">
-        <v>47.35</v>
+        <v>29.54</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>TARC</t>
+          <t>AARTIDRUGS</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -5794,22 +6234,22 @@
         </is>
       </c>
       <c r="C185" s="4" t="n">
-        <v>128.91</v>
+        <v>371.7</v>
       </c>
       <c r="D185" s="4" t="n">
-        <v>43.83</v>
+        <v>46.34</v>
       </c>
       <c r="E185" s="4" t="n">
-        <v>41.99</v>
+        <v>46.05</v>
       </c>
       <c r="F185" s="4" t="n">
-        <v>46.04</v>
+        <v>43.85</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>DBL</t>
+          <t>PURVA</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -5818,22 +6258,22 @@
         </is>
       </c>
       <c r="C186" s="4" t="n">
-        <v>428.45</v>
+        <v>209.18</v>
       </c>
       <c r="D186" s="4" t="n">
-        <v>43.73</v>
+        <v>46.34</v>
       </c>
       <c r="E186" s="4" t="n">
-        <v>46.02</v>
+        <v>45.67</v>
       </c>
       <c r="F186" s="4" t="n">
-        <v>48.57</v>
+        <v>44.35</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>ALLCARGO</t>
+          <t>SANDUMA</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -5842,22 +6282,22 @@
         </is>
       </c>
       <c r="C187" s="4" t="n">
-        <v>8.800000000000001</v>
+        <v>215.85</v>
       </c>
       <c r="D187" s="4" t="n">
-        <v>43.68</v>
+        <v>46.29</v>
       </c>
       <c r="E187" s="4" t="n">
-        <v>35.12</v>
+        <v>52.18</v>
       </c>
       <c r="F187" s="4" t="n">
-        <v>27.63</v>
+        <v>58.7</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>JKPAPER</t>
+          <t>GSFC</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -5866,22 +6306,22 @@
         </is>
       </c>
       <c r="C188" s="4" t="n">
-        <v>359.8</v>
+        <v>164.34</v>
       </c>
       <c r="D188" s="4" t="n">
-        <v>43.52</v>
+        <v>46.24</v>
       </c>
       <c r="E188" s="4" t="n">
-        <v>50.02</v>
+        <v>44.91</v>
       </c>
       <c r="F188" s="4" t="n">
-        <v>49.94</v>
+        <v>45.63</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -5890,22 +6330,22 @@
         </is>
       </c>
       <c r="C189" s="4" t="n">
-        <v>175.42</v>
+        <v>185.54</v>
       </c>
       <c r="D189" s="4" t="n">
-        <v>43.34</v>
+        <v>45.83</v>
       </c>
       <c r="E189" s="4" t="n">
-        <v>50</v>
+        <v>47.85</v>
       </c>
       <c r="F189" s="4" t="n">
-        <v>57.57</v>
+        <v>39.22</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>AURIONPRO</t>
+          <t>CMSINFO</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -5914,22 +6354,22 @@
         </is>
       </c>
       <c r="C190" s="4" t="n">
-        <v>778</v>
+        <v>296.75</v>
       </c>
       <c r="D190" s="4" t="n">
-        <v>43.22</v>
+        <v>45.83</v>
       </c>
       <c r="E190" s="4" t="n">
-        <v>38.74</v>
+        <v>41.12</v>
       </c>
       <c r="F190" s="4" t="n">
-        <v>39.93</v>
+        <v>38.68</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>MEDPLUS</t>
+          <t>ZAGGLE</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -5938,22 +6378,22 @@
         </is>
       </c>
       <c r="C191" s="4" t="n">
-        <v>858.7</v>
+        <v>208.8</v>
       </c>
       <c r="D191" s="4" t="n">
-        <v>43.11</v>
+        <v>45.64</v>
       </c>
       <c r="E191" s="4" t="n">
-        <v>50.44</v>
+        <v>36.73</v>
       </c>
       <c r="F191" s="4" t="n">
-        <v>54.14</v>
+        <v>39.84</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>SUBROS</t>
+          <t>GMRP&amp;UI</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -5962,22 +6402,22 @@
         </is>
       </c>
       <c r="C192" s="4" t="n">
-        <v>718.85</v>
+        <v>105.57</v>
       </c>
       <c r="D192" s="4" t="n">
-        <v>43.09</v>
+        <v>45.57</v>
       </c>
       <c r="E192" s="4" t="n">
-        <v>43.18</v>
+        <v>47.43</v>
       </c>
       <c r="F192" s="4" t="n">
-        <v>49.85</v>
+        <v>52.62</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>ALIVUS</t>
+          <t>GOKEX</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -5986,22 +6426,22 @@
         </is>
       </c>
       <c r="C193" s="4" t="n">
-        <v>1032.5</v>
+        <v>674.5</v>
       </c>
       <c r="D193" s="4" t="n">
-        <v>42.72</v>
+        <v>45.44</v>
       </c>
       <c r="E193" s="4" t="n">
-        <v>56.01</v>
+        <v>46.43</v>
       </c>
       <c r="F193" s="4" t="n">
-        <v>57.49</v>
+        <v>46.96</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>SANOFI</t>
+          <t>KSCL</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -6010,22 +6450,22 @@
         </is>
       </c>
       <c r="C194" s="4" t="n">
-        <v>3186.4</v>
+        <v>878.85</v>
       </c>
       <c r="D194" s="4" t="n">
-        <v>42.72</v>
+        <v>45.38</v>
       </c>
       <c r="E194" s="4" t="n">
-        <v>29.73</v>
+        <v>45.96</v>
       </c>
       <c r="F194" s="4" t="n">
-        <v>30.31</v>
+        <v>47.65</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>CELLO</t>
+          <t>RTNPOWER</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -6034,22 +6474,22 @@
         </is>
       </c>
       <c r="C195" s="4" t="n">
-        <v>382.1</v>
+        <v>9.24</v>
       </c>
       <c r="D195" s="4" t="n">
-        <v>42.56</v>
+        <v>45.28</v>
       </c>
       <c r="E195" s="4" t="n">
-        <v>32.65</v>
+        <v>47.83</v>
       </c>
       <c r="F195" s="4" t="n">
-        <v>30.96</v>
+        <v>46.84</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>HIKAL</t>
+          <t>CAMPUS</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -6058,22 +6498,22 @@
         </is>
       </c>
       <c r="C196" s="4" t="n">
-        <v>189.62</v>
+        <v>238.4</v>
       </c>
       <c r="D196" s="4" t="n">
-        <v>42.53</v>
+        <v>44.99</v>
       </c>
       <c r="E196" s="4" t="n">
-        <v>44.33</v>
+        <v>44.23</v>
       </c>
       <c r="F196" s="4" t="n">
-        <v>37.5</v>
+        <v>43.66</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>TIMETECHNO</t>
+          <t>IMFA</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -6082,22 +6522,22 @@
         </is>
       </c>
       <c r="C197" s="4" t="n">
-        <v>172.44</v>
+        <v>1398.9</v>
       </c>
       <c r="D197" s="4" t="n">
-        <v>42.07</v>
+        <v>44.94</v>
       </c>
       <c r="E197" s="4" t="n">
-        <v>43.38</v>
+        <v>53.31</v>
       </c>
       <c r="F197" s="4" t="n">
-        <v>49.59</v>
+        <v>65.08</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>WESTLIFE</t>
+          <t>SUNTECK</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -6106,22 +6546,22 @@
         </is>
       </c>
       <c r="C198" s="4" t="n">
-        <v>444.2</v>
+        <v>287.35</v>
       </c>
       <c r="D198" s="4" t="n">
-        <v>41.85</v>
+        <v>44.91</v>
       </c>
       <c r="E198" s="4" t="n">
-        <v>36.33</v>
+        <v>35.42</v>
       </c>
       <c r="F198" s="4" t="n">
-        <v>29.44</v>
+        <v>38.85</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>UJJIVANSFB</t>
+          <t>LOTUSDEV</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -6130,22 +6570,22 @@
         </is>
       </c>
       <c r="C199" s="4" t="n">
-        <v>53.56</v>
+        <v>134.04</v>
       </c>
       <c r="D199" s="4" t="n">
-        <v>41.76</v>
+        <v>44.65</v>
       </c>
       <c r="E199" s="4" t="n">
-        <v>47.11</v>
+        <v>40.98</v>
       </c>
       <c r="F199" s="4" t="n">
-        <v>55.36</v>
+        <v/>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>GANECOS</t>
+          <t>CAPILLARY</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -6154,22 +6594,22 @@
         </is>
       </c>
       <c r="C200" s="4" t="n">
-        <v>929.55</v>
+        <v>508.05</v>
       </c>
       <c r="D200" s="4" t="n">
-        <v>41.73</v>
+        <v>44.5</v>
       </c>
       <c r="E200" s="4" t="n">
-        <v>47.57</v>
+        <v>38.92</v>
       </c>
       <c r="F200" s="4" t="n">
-        <v>43.65</v>
+        <v/>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>EIEL</t>
+          <t>AARTIPHARM</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -6178,22 +6618,22 @@
         </is>
       </c>
       <c r="C201" s="4" t="n">
-        <v>184.69</v>
+        <v>641.15</v>
       </c>
       <c r="D201" s="4" t="n">
-        <v>41.72</v>
+        <v>44.18</v>
       </c>
       <c r="E201" s="4" t="n">
-        <v>47.53</v>
+        <v>41.32</v>
       </c>
       <c r="F201" s="4" t="n">
-        <v>39.09</v>
+        <v>48.03</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>GULFOILLUB</t>
+          <t>BIRLACORPN</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -6202,22 +6642,22 @@
         </is>
       </c>
       <c r="C202" s="4" t="n">
-        <v>905.9</v>
+        <v>951.1</v>
       </c>
       <c r="D202" s="4" t="n">
-        <v>41.65</v>
+        <v>43.99</v>
       </c>
       <c r="E202" s="4" t="n">
-        <v>38.76</v>
+        <v>44.82</v>
       </c>
       <c r="F202" s="4" t="n">
-        <v>44.52</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>GRINFRA</t>
+          <t>TIMETECHNO</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -6226,22 +6666,22 @@
         </is>
       </c>
       <c r="C203" s="4" t="n">
-        <v>888.3</v>
+        <v>169.48</v>
       </c>
       <c r="D203" s="4" t="n">
-        <v>41.59</v>
+        <v>43.9</v>
       </c>
       <c r="E203" s="4" t="n">
-        <v>41.47</v>
+        <v>42.02</v>
       </c>
       <c r="F203" s="4" t="n">
-        <v>38.85</v>
+        <v>48.93</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>NFL</t>
+          <t>PFOCUS</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -6250,22 +6690,22 @@
         </is>
       </c>
       <c r="C204" s="4" t="n">
-        <v>73.84</v>
+        <v>239.27</v>
       </c>
       <c r="D204" s="4" t="n">
-        <v>41.56</v>
+        <v>43.84</v>
       </c>
       <c r="E204" s="4" t="n">
-        <v>41.56</v>
+        <v>45.72</v>
       </c>
       <c r="F204" s="4" t="n">
-        <v>44.03</v>
+        <v>59.51</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>INGERRAND</t>
+          <t>HGINFRA</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -6274,22 +6714,22 @@
         </is>
       </c>
       <c r="C205" s="4" t="n">
-        <v>3960.6</v>
+        <v>562.9</v>
       </c>
       <c r="D205" s="4" t="n">
-        <v>41.22</v>
+        <v>43.78</v>
       </c>
       <c r="E205" s="4" t="n">
-        <v>50.21</v>
+        <v>40.18</v>
       </c>
       <c r="F205" s="4" t="n">
-        <v>54.21</v>
+        <v>36.42</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>PRSMJOHNSN</t>
+          <t>PRICOLLTD</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -6298,22 +6738,22 @@
         </is>
       </c>
       <c r="C206" s="4" t="n">
-        <v>119.31</v>
+        <v>550.5</v>
       </c>
       <c r="D206" s="4" t="n">
-        <v>41.21</v>
+        <v>43.73</v>
       </c>
       <c r="E206" s="4" t="n">
-        <v>38.81</v>
+        <v>46.56</v>
       </c>
       <c r="F206" s="4" t="n">
-        <v>41.85</v>
+        <v>55.81</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>ASHOKA</t>
+          <t>TARC</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -6322,22 +6762,22 @@
         </is>
       </c>
       <c r="C207" s="4" t="n">
-        <v>122.36</v>
+        <v>125.33</v>
       </c>
       <c r="D207" s="4" t="n">
-        <v>41.16</v>
+        <v>43.62</v>
       </c>
       <c r="E207" s="4" t="n">
-        <v>37.68</v>
+        <v>39.84</v>
       </c>
       <c r="F207" s="4" t="n">
-        <v>41.97</v>
+        <v>45.28</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>SHAREINDIA</t>
+          <t>MOIL</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -6346,22 +6786,22 @@
         </is>
       </c>
       <c r="C208" s="4" t="n">
-        <v>135.29</v>
+        <v>291.9</v>
       </c>
       <c r="D208" s="4" t="n">
-        <v>41.04</v>
+        <v>43.59</v>
       </c>
       <c r="E208" s="4" t="n">
-        <v>43.95</v>
+        <v>43.46</v>
       </c>
       <c r="F208" s="4" t="n">
-        <v>39.7</v>
+        <v>46.56</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>AWFIS</t>
+          <t>GODREJAGRO</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -6370,22 +6810,22 @@
         </is>
       </c>
       <c r="C209" s="4" t="n">
-        <v>312.75</v>
+        <v>564.95</v>
       </c>
       <c r="D209" s="4" t="n">
-        <v>40.72</v>
+        <v>43.53</v>
       </c>
       <c r="E209" s="4" t="n">
-        <v>39.49</v>
+        <v>43.56</v>
       </c>
       <c r="F209" s="4" t="n">
-        <v>32.74</v>
+        <v>44.87</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>IXIGO</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -6394,22 +6834,22 @@
         </is>
       </c>
       <c r="C210" s="4" t="n">
-        <v>155.55</v>
+        <v>429.35</v>
       </c>
       <c r="D210" s="4" t="n">
-        <v>40.66</v>
+        <v>43.46</v>
       </c>
       <c r="E210" s="4" t="n">
-        <v>35.86</v>
+        <v>44.27</v>
       </c>
       <c r="F210" s="4" t="n">
-        <v>39.93</v>
+        <v>50.05</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>JKPAPER</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -6418,22 +6858,22 @@
         </is>
       </c>
       <c r="C211" s="4" t="n">
-        <v>184.39</v>
+        <v>353.35</v>
       </c>
       <c r="D211" s="4" t="n">
-        <v>40.58</v>
+        <v>43.39</v>
       </c>
       <c r="E211" s="4" t="n">
-        <v>53.05</v>
+        <v>47.72</v>
       </c>
       <c r="F211" s="4" t="n">
-        <v>56.83</v>
+        <v>49.13</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>JAIBALAJI</t>
+          <t>ENTERO</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -6442,22 +6882,22 @@
         </is>
       </c>
       <c r="C212" s="4" t="n">
-        <v>69.56</v>
+        <v>1136.7</v>
       </c>
       <c r="D212" s="4" t="n">
-        <v>40.06</v>
+        <v>43.33</v>
       </c>
       <c r="E212" s="4" t="n">
-        <v>46.31</v>
+        <v>47.75</v>
       </c>
       <c r="F212" s="4" t="n">
-        <v>41.39</v>
+        <v>49.08</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>HERITGFOOD</t>
+          <t>DYNAMATECH</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -6466,22 +6906,22 @@
         </is>
       </c>
       <c r="C213" s="4" t="n">
-        <v>320.15</v>
+        <v>10171</v>
       </c>
       <c r="D213" s="4" t="n">
-        <v>40.04</v>
+        <v>43.3</v>
       </c>
       <c r="E213" s="4" t="n">
-        <v>35.56</v>
+        <v>51.2</v>
       </c>
       <c r="F213" s="4" t="n">
-        <v>42.72</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>JKIL</t>
+          <t>HERITGFOOD</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -6490,22 +6930,22 @@
         </is>
       </c>
       <c r="C214" s="4" t="n">
-        <v>483.4</v>
+        <v>320</v>
       </c>
       <c r="D214" s="4" t="n">
-        <v>39.89</v>
+        <v>43.28</v>
       </c>
       <c r="E214" s="4" t="n">
-        <v>39.7</v>
+        <v>35.53</v>
       </c>
       <c r="F214" s="4" t="n">
-        <v>41</v>
+        <v>42.7</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>GSFC</t>
+          <t>BALUFORGE</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -6514,22 +6954,22 @@
         </is>
       </c>
       <c r="C215" s="4" t="n">
-        <v>162.54</v>
+        <v>448.8</v>
       </c>
       <c r="D215" s="4" t="n">
-        <v>39.68</v>
+        <v>42.9</v>
       </c>
       <c r="E215" s="4" t="n">
-        <v>43.31</v>
+        <v>42.6</v>
       </c>
       <c r="F215" s="4" t="n">
-        <v>45.12</v>
+        <v>46.06</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>PARKHOTELS</t>
+          <t>KPIGREEN</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -6538,22 +6978,22 @@
         </is>
       </c>
       <c r="C216" s="4" t="n">
-        <v>114.2</v>
+        <v>401.4</v>
       </c>
       <c r="D216" s="4" t="n">
-        <v>39.56</v>
+        <v>42.86</v>
       </c>
       <c r="E216" s="4" t="n">
-        <v>41.18</v>
+        <v>45.29</v>
       </c>
       <c r="F216" s="4" t="n">
-        <v>36.74</v>
+        <v>48.58</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>TRANSRAILL</t>
+          <t>PNGJL</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -6562,22 +7002,22 @@
         </is>
       </c>
       <c r="C217" s="4" t="n">
-        <v>493.25</v>
+        <v>547.55</v>
       </c>
       <c r="D217" s="4" t="n">
-        <v>39.42</v>
+        <v>42.76</v>
       </c>
       <c r="E217" s="4" t="n">
-        <v>41.43</v>
+        <v>44.33</v>
       </c>
       <c r="F217" s="4" t="n">
-        <v>44.43</v>
+        <v>42.19</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>ORIENTCEM</t>
+          <t>CRIZAC</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -6586,22 +7026,22 @@
         </is>
       </c>
       <c r="C218" s="4" t="n">
-        <v>133.39</v>
+        <v>205.96</v>
       </c>
       <c r="D218" s="4" t="n">
-        <v>39.23</v>
+        <v>42.29</v>
       </c>
       <c r="E218" s="4" t="n">
-        <v>33.3</v>
+        <v>40.73</v>
       </c>
       <c r="F218" s="4" t="n">
-        <v>35.15</v>
+        <v/>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>JKLAKSHMI</t>
+          <t>CELLO</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -6610,22 +7050,22 @@
         </is>
       </c>
       <c r="C219" s="4" t="n">
-        <v>598.75</v>
+        <v>377.3</v>
       </c>
       <c r="D219" s="4" t="n">
-        <v>39.06</v>
+        <v>42</v>
       </c>
       <c r="E219" s="4" t="n">
-        <v>36.51</v>
+        <v>31.9</v>
       </c>
       <c r="F219" s="4" t="n">
-        <v>40.71</v>
+        <v>30.37</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>BLACKBUCK</t>
+          <t>MASTEK</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -6634,22 +7074,22 @@
         </is>
       </c>
       <c r="C220" s="4" t="n">
-        <v>506.7</v>
+        <v>1577.4</v>
       </c>
       <c r="D220" s="4" t="n">
-        <v>38.79</v>
+        <v>41.89</v>
       </c>
       <c r="E220" s="4" t="n">
-        <v>41.19</v>
+        <v>38.91</v>
       </c>
       <c r="F220" s="4" t="n">
-        <v>46.5</v>
+        <v>38.83</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>STAR</t>
+          <t>AWFIS</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -6658,22 +7098,22 @@
         </is>
       </c>
       <c r="C221" s="4" t="n">
-        <v>1044.6</v>
+        <v>303.05</v>
       </c>
       <c r="D221" s="4" t="n">
-        <v>38.72</v>
+        <v>41.39</v>
       </c>
       <c r="E221" s="4" t="n">
-        <v>56.51</v>
+        <v>38.24</v>
       </c>
       <c r="F221" s="4" t="n">
-        <v>57.68</v>
+        <v>32.18</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>SHARDACROP</t>
+          <t>PNCINFRA</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -6682,22 +7122,22 @@
         </is>
       </c>
       <c r="C222" s="4" t="n">
-        <v>892.7</v>
+        <v>201.62</v>
       </c>
       <c r="D222" s="4" t="n">
-        <v>38.45</v>
+        <v>41.02</v>
       </c>
       <c r="E222" s="4" t="n">
-        <v>44.83</v>
+        <v>41.51</v>
       </c>
       <c r="F222" s="4" t="n">
-        <v>53.67</v>
+        <v>38.54</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>INDIASHLTR</t>
+          <t>VGUARD</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -6706,22 +7146,22 @@
         </is>
       </c>
       <c r="C223" s="4" t="n">
-        <v>756.7</v>
+        <v>299.15</v>
       </c>
       <c r="D223" s="4" t="n">
-        <v>38.28</v>
+        <v>40.95</v>
       </c>
       <c r="E223" s="4" t="n">
-        <v>43.39</v>
+        <v>35.89</v>
       </c>
       <c r="F223" s="4" t="n">
-        <v>48.66</v>
+        <v>41.18</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>STYRENIX</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -6730,22 +7170,22 @@
         </is>
       </c>
       <c r="C224" s="4" t="n">
-        <v>416.1</v>
+        <v>2133</v>
       </c>
       <c r="D224" s="4" t="n">
-        <v>38.17</v>
+        <v>40.83</v>
       </c>
       <c r="E224" s="4" t="n">
-        <v>43.67</v>
+        <v>48.84</v>
       </c>
       <c r="F224" s="4" t="n">
-        <v>54.36</v>
+        <v>50.56</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>KPIGREEN</t>
+          <t>EMIL</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -6754,22 +7194,22 @@
         </is>
       </c>
       <c r="C225" s="4" t="n">
-        <v>405.85</v>
+        <v>105.5</v>
       </c>
       <c r="D225" s="4" t="n">
-        <v>37.88</v>
+        <v>40.06</v>
       </c>
       <c r="E225" s="4" t="n">
-        <v>46.07</v>
+        <v>46.03</v>
       </c>
       <c r="F225" s="4" t="n">
-        <v>48.91</v>
+        <v>43.65</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>ENTERO</t>
+          <t>SKFINDIA</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -6778,22 +7218,22 @@
         </is>
       </c>
       <c r="C226" s="4" t="n">
-        <v>1113.8</v>
+        <v>1589.3</v>
       </c>
       <c r="D226" s="4" t="n">
-        <v>37.83</v>
+        <v>39.97</v>
       </c>
       <c r="E226" s="4" t="n">
-        <v>46.21</v>
+        <v>30.97</v>
       </c>
       <c r="F226" s="4" t="n">
-        <v>47.92</v>
+        <v>31.76</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>STARCEMENT</t>
+          <t>CCAVENUE</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -6802,22 +7242,22 @@
         </is>
       </c>
       <c r="C227" s="4" t="n">
-        <v>209.06</v>
+        <v>13.5</v>
       </c>
       <c r="D227" s="4" t="n">
-        <v>37.51</v>
+        <v>39.97</v>
       </c>
       <c r="E227" s="4" t="n">
-        <v>43.08</v>
+        <v>39.2</v>
       </c>
       <c r="F227" s="4" t="n">
-        <v>49.48</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>ALOKINDS</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -6826,22 +7266,22 @@
         </is>
       </c>
       <c r="C228" s="4" t="n">
-        <v>628.3</v>
+        <v>12.16</v>
       </c>
       <c r="D228" s="4" t="n">
-        <v>37.12</v>
+        <v>39.78</v>
       </c>
       <c r="E228" s="4" t="n">
-        <v>39.41</v>
+        <v>36.17</v>
       </c>
       <c r="F228" s="4" t="n">
-        <v>47.26</v>
+        <v>37.49</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>SUNTECK</t>
+          <t>IONEXCHANG</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -6850,22 +7290,22 @@
         </is>
       </c>
       <c r="C229" s="4" t="n">
-        <v>282.3</v>
+        <v>345.6</v>
       </c>
       <c r="D229" s="4" t="n">
-        <v>36.71</v>
+        <v>39.76</v>
       </c>
       <c r="E229" s="4" t="n">
-        <v>33.85</v>
+        <v>40.89</v>
       </c>
       <c r="F229" s="4" t="n">
-        <v>38.4</v>
+        <v>41.22</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>GABRIEL</t>
+          <t>PRSMJOHNSN</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -6874,22 +7314,22 @@
         </is>
       </c>
       <c r="C230" s="4" t="n">
-        <v>1000.6</v>
+        <v>117.89</v>
       </c>
       <c r="D230" s="4" t="n">
-        <v>36.66</v>
+        <v>39.54</v>
       </c>
       <c r="E230" s="4" t="n">
-        <v>49.9</v>
+        <v>37.58</v>
       </c>
       <c r="F230" s="4" t="n">
-        <v>59.29</v>
+        <v>41.42</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>ELECTCAST</t>
+          <t>JAYNECOIND</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -6898,22 +7338,22 @@
         </is>
       </c>
       <c r="C231" s="4" t="n">
-        <v>74</v>
+        <v>90.86</v>
       </c>
       <c r="D231" s="4" t="n">
-        <v>36.48</v>
+        <v>38.99</v>
       </c>
       <c r="E231" s="4" t="n">
-        <v>44.24</v>
+        <v>53.32</v>
       </c>
       <c r="F231" s="4" t="n">
-        <v>41.69</v>
+        <v>61.55</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>GMMPFAUDLR</t>
+          <t>RENUKA</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -6922,22 +7362,22 @@
         </is>
       </c>
       <c r="C232" s="4" t="n">
-        <v>788</v>
+        <v>22.29</v>
       </c>
       <c r="D232" s="4" t="n">
+        <v>38.34</v>
+      </c>
+      <c r="E232" s="4" t="n">
+        <v>36.01</v>
+      </c>
+      <c r="F232" s="4" t="n">
         <v>36.35</v>
-      </c>
-      <c r="E232" s="4" t="n">
-        <v>31.91</v>
-      </c>
-      <c r="F232" s="4" t="n">
-        <v>38.39</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>SHARDAMOTR</t>
+          <t>ELECTCAST</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -6946,16 +7386,16 @@
         </is>
       </c>
       <c r="C233" s="4" t="n">
-        <v>813.35</v>
+        <v>71.87</v>
       </c>
       <c r="D233" s="4" t="n">
-        <v>36.08</v>
+        <v>38.33</v>
       </c>
       <c r="E233" s="4" t="n">
-        <v>42.53</v>
+        <v>42.49</v>
       </c>
       <c r="F233" s="4" t="n">
-        <v>41.92</v>
+        <v>41.08</v>
       </c>
     </row>
     <row r="234">
@@ -6970,22 +7410,22 @@
         </is>
       </c>
       <c r="C234" s="4" t="n">
-        <v>440.75</v>
+        <v>430.45</v>
       </c>
       <c r="D234" s="4" t="n">
-        <v>35.98</v>
+        <v>38.3</v>
       </c>
       <c r="E234" s="4" t="n">
-        <v>36.42</v>
+        <v>34.77</v>
       </c>
       <c r="F234" s="4" t="n">
-        <v>41.72</v>
+        <v>41.03</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>GALLANTT</t>
+          <t>TRANSRAILL</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -6994,22 +7434,22 @@
         </is>
       </c>
       <c r="C235" s="4" t="n">
-        <v>648.9</v>
+        <v>478.1</v>
       </c>
       <c r="D235" s="4" t="n">
-        <v>35.64</v>
+        <v>38.18</v>
       </c>
       <c r="E235" s="4" t="n">
-        <v>49.76</v>
+        <v>39.63</v>
       </c>
       <c r="F235" s="4" t="n">
-        <v>57.77</v>
+        <v>43.21</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>NESCO</t>
+          <t>HAPPSTMNDS</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -7018,22 +7458,22 @@
         </is>
       </c>
       <c r="C236" s="4" t="n">
-        <v>1112.6</v>
+        <v>349.95</v>
       </c>
       <c r="D236" s="4" t="n">
-        <v>35.49</v>
+        <v>37.42</v>
       </c>
       <c r="E236" s="4" t="n">
-        <v>44.78</v>
+        <v>35.67</v>
       </c>
       <c r="F236" s="4" t="n">
-        <v>52.51</v>
+        <v>24.51</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>ZAGGLE</t>
+          <t>JKLAKSHMI</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -7042,22 +7482,22 @@
         </is>
       </c>
       <c r="C237" s="4" t="n">
-        <v>200.81</v>
+        <v>588.85</v>
       </c>
       <c r="D237" s="4" t="n">
-        <v>35.4</v>
+        <v>37.37</v>
       </c>
       <c r="E237" s="4" t="n">
-        <v>34.1</v>
+        <v>35.37</v>
       </c>
       <c r="F237" s="4" t="n">
-        <v>39.22</v>
+        <v>40.01</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>BECTORFOOD</t>
+          <t>EUREKAFORB</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -7066,22 +7506,22 @@
         </is>
       </c>
       <c r="C238" s="4" t="n">
-        <v>172.2</v>
+        <v>438.25</v>
       </c>
       <c r="D238" s="4" t="n">
-        <v>34.88</v>
+        <v>37</v>
       </c>
       <c r="E238" s="4" t="n">
-        <v>30.24</v>
+        <v>36.37</v>
       </c>
       <c r="F238" s="4" t="n">
-        <v>37.44</v>
+        <v>39.46</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>IONEXCHANG</t>
+          <t>JAIBALAJI</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
@@ -7090,22 +7530,22 @@
         </is>
       </c>
       <c r="C239" s="4" t="n">
-        <v>350.65</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="D239" s="4" t="n">
-        <v>34.6</v>
+        <v>36.76</v>
       </c>
       <c r="E239" s="4" t="n">
-        <v>41.98</v>
+        <v>43.58</v>
       </c>
       <c r="F239" s="4" t="n">
-        <v>41.63</v>
+        <v>40.56</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>RENUKA</t>
+          <t>ORKLAINDIA</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -7114,22 +7554,22 @@
         </is>
       </c>
       <c r="C240" s="4" t="n">
-        <v>22.44</v>
+        <v>604.45</v>
       </c>
       <c r="D240" s="4" t="n">
-        <v>34.44</v>
+        <v>36.59</v>
       </c>
       <c r="E240" s="4" t="n">
-        <v>36.42</v>
+        <v>44.92</v>
       </c>
       <c r="F240" s="4" t="n">
-        <v>36.49</v>
+        <v/>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>GMMPFAUDLR</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
@@ -7138,22 +7578,22 @@
         </is>
       </c>
       <c r="C241" s="4" t="n">
-        <v>518.3</v>
+        <v>760.1</v>
       </c>
       <c r="D241" s="4" t="n">
-        <v>34.27</v>
+        <v>36.55</v>
       </c>
       <c r="E241" s="4" t="n">
-        <v>38.48</v>
+        <v>29.83</v>
       </c>
       <c r="F241" s="4" t="n">
-        <v>42.51</v>
+        <v>37.34</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>KSCL</t>
+          <t>RALLIS</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -7162,22 +7602,22 @@
         </is>
       </c>
       <c r="C242" s="4" t="n">
-        <v>858.4</v>
+        <v>228.77</v>
       </c>
       <c r="D242" s="4" t="n">
-        <v>34.01</v>
+        <v>36.49</v>
       </c>
       <c r="E242" s="4" t="n">
-        <v>43.43</v>
+        <v>40.09</v>
       </c>
       <c r="F242" s="4" t="n">
-        <v>46.69</v>
+        <v>44.56</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>EUREKAFORB</t>
+          <t>WAKEFIT</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -7186,22 +7626,22 @@
         </is>
       </c>
       <c r="C243" s="4" t="n">
-        <v>440.8</v>
+        <v>114.76</v>
       </c>
       <c r="D243" s="4" t="n">
-        <v>33.77</v>
+        <v>36.02</v>
       </c>
       <c r="E243" s="4" t="n">
-        <v>36.76</v>
+        <v>27.48</v>
       </c>
       <c r="F243" s="4" t="n">
-        <v>39.68</v>
+        <v/>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>EASEMYTRIP</t>
+          <t>AGARWALEYE</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -7210,22 +7650,22 @@
         </is>
       </c>
       <c r="C244" s="4" t="n">
-        <v>6.74</v>
+        <v>439.75</v>
       </c>
       <c r="D244" s="4" t="n">
-        <v>33.07</v>
+        <v>35.5</v>
       </c>
       <c r="E244" s="4" t="n">
-        <v>41.8</v>
+        <v>45.34</v>
       </c>
       <c r="F244" s="4" t="n">
-        <v>35.35</v>
+        <v>48.54</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>ISGEC</t>
+          <t>PRAJIND</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
@@ -7234,22 +7674,22 @@
         </is>
       </c>
       <c r="C245" s="4" t="n">
-        <v>928.15</v>
+        <v>332.1</v>
       </c>
       <c r="D245" s="4" t="n">
-        <v>32.86</v>
+        <v>34.76</v>
       </c>
       <c r="E245" s="4" t="n">
-        <v>47.04</v>
+        <v>44.88</v>
       </c>
       <c r="F245" s="4" t="n">
-        <v>48.3</v>
+        <v>42</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>HGINFRA</t>
+          <t>NESCO</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -7258,22 +7698,22 @@
         </is>
       </c>
       <c r="C246" s="4" t="n">
-        <v>548.65</v>
+        <v>1089.8</v>
       </c>
       <c r="D246" s="4" t="n">
-        <v>32.15</v>
+        <v>34.02</v>
       </c>
       <c r="E246" s="4" t="n">
-        <v>38.01</v>
+        <v>43.24</v>
       </c>
       <c r="F246" s="4" t="n">
-        <v>35.98</v>
+        <v>51.38</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>SYMPHONY</t>
+          <t>BAJAJELEC</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
@@ -7282,22 +7722,22 @@
         </is>
       </c>
       <c r="C247" s="4" t="n">
-        <v>687.4</v>
+        <v>310.95</v>
       </c>
       <c r="D247" s="4" t="n">
-        <v>31.2</v>
+        <v>33.96</v>
       </c>
       <c r="E247" s="4" t="n">
-        <v>35.65</v>
+        <v>27.88</v>
       </c>
       <c r="F247" s="4" t="n">
-        <v>38.11</v>
+        <v>27.53</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>AVANTIFEED</t>
+          <t>JYOTHYLAB</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -7306,22 +7746,22 @@
         </is>
       </c>
       <c r="C248" s="4" t="n">
-        <v>1110.6</v>
+        <v>200.96</v>
       </c>
       <c r="D248" s="4" t="n">
-        <v>28.92</v>
+        <v>33.86</v>
       </c>
       <c r="E248" s="4" t="n">
-        <v>47.64</v>
+        <v>32.85</v>
       </c>
       <c r="F248" s="4" t="n">
-        <v>60.88</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>BAJAJELEC</t>
+          <t>KITEX</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
@@ -7330,22 +7770,22 @@
         </is>
       </c>
       <c r="C249" s="4" t="n">
-        <v>311.5</v>
+        <v>145.02</v>
       </c>
       <c r="D249" s="4" t="n">
-        <v>27.82</v>
+        <v>32.39</v>
       </c>
       <c r="E249" s="4" t="n">
-        <v>27.96</v>
+        <v>38.65</v>
       </c>
       <c r="F249" s="4" t="n">
-        <v>27.55</v>
+        <v>46.46</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>RALLIS</t>
+          <t>AVANTIFEED</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
@@ -7354,16 +7794,40 @@
         </is>
       </c>
       <c r="C250" s="4" t="n">
-        <v>227.24</v>
+        <v>1060.1</v>
       </c>
       <c r="D250" s="4" t="n">
-        <v>25.89</v>
+        <v>32.19</v>
       </c>
       <c r="E250" s="4" t="n">
-        <v>38.92</v>
+        <v>45.13</v>
       </c>
       <c r="F250" s="4" t="n">
-        <v>44.37</v>
+        <v>58.7</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>CENTURYPLY</t>
+        </is>
+      </c>
+      <c r="B251" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C251" s="4" t="n">
+        <v>724.6</v>
+      </c>
+      <c r="D251" s="4" t="n">
+        <v>32.07</v>
+      </c>
+      <c r="E251" s="4" t="n">
+        <v>44.07</v>
+      </c>
+      <c r="F251" s="4" t="n">
+        <v>48.94</v>
       </c>
     </row>
   </sheetData>
@@ -7617,6 +8081,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B248" r:id="rId247"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B249" r:id="rId248"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B251" r:id="rId250"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/Micro250_stocks.xlsx
+++ b/reports/Micro250_stocks.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L32"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -546,37 +546,37 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>159.97</v>
+        <v>176.92</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>85.08</v>
+        <v>90.16</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>81.56</v>
+        <v>84.37</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>86.81</v>
+        <v>88.17</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>41.44</v>
+        <v>48.43</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>94.73</v>
+        <v>99.48999999999999</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>85.59999999999999</v>
+        <v>89.64</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>17259028</v>
+        <v>18329801</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>21511</v>
+        <v>23790</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>PARAS</t>
+          <t>WABAG</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -585,37 +585,37 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>1097.15</v>
+        <v>1983.6</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>75.06999999999999</v>
+        <v>83.31</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>72.98</v>
+        <v>77.47</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>63.21</v>
+        <v>67.52</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>20.93</v>
+        <v>30.03</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>751.91</v>
+        <v>1411.88</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>743.9400000000001</v>
+        <v>1403.94</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>3213385</v>
+        <v>554008</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>8842</v>
+        <v>12361</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>SOUTHBANK</t>
+          <t>ASTRAMICRO</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -624,37 +624,37 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>46.66</v>
+        <v>1684.1</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>72.22</v>
+        <v>81.44</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>67.84</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>70.69</v>
+        <v>76.63</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>22.22</v>
+        <v>24.97</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>38.88</v>
+        <v>1109.79</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>37.72</v>
+        <v>1076.25</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>18136178</v>
+        <v>1453405</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>12214</v>
+        <v>15990</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>INOXINDIA</t>
+          <t>KIRLPNU</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -663,37 +663,37 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1808.2</v>
+        <v>1950</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>71.28</v>
+        <v>78.76000000000001</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>81.58</v>
+        <v>84.45999999999999</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>80.23999999999999</v>
+        <v>71.39</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>24.41</v>
+        <v>38.35</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>1321.1</v>
+        <v>1338.25</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>1286.45</v>
+        <v>1307.62</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>456227</v>
+        <v>184422</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>16412</v>
+        <v>12667</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>SOUTHBANK</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -702,37 +702,37 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1687</v>
+        <v>48.46</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>68.41</v>
+        <v>76.86</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>76.31999999999999</v>
+        <v>70.45999999999999</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>75.15000000000001</v>
+        <v>72.02</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>37.93</v>
+        <v>23.34</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1124.49</v>
+        <v>39.47</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>1075.64</v>
+        <v>38.22</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>784424</v>
+        <v>17591440</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>11267</v>
+        <v>12685</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>ASTRAMICRO</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -741,37 +741,37 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1443.8</v>
+        <v>654.35</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>68.3</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>76.27</v>
+        <v>89.72</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>72.18000000000001</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>29.42</v>
+        <v>41.57</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1077.58</v>
+        <v>292.08</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>1050.02</v>
+        <v>256.16</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1214939</v>
+        <v>3621671</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>13708</v>
+        <v>31943</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>TMB</t>
+          <t>ICIL</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -780,37 +780,37 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>767.05</v>
+        <v>394.6</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>68</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>69.03</v>
+        <v>71.45</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>71.8</v>
+        <v>62.62</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>22.1</v>
+        <v>29.12</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>614.38</v>
+        <v>289.72</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>588.5</v>
+        <v>288.55</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>343615</v>
+        <v>934526</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>12146</v>
+        <v>7815</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>LLOYDSENGG</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -819,37 +819,37 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>583.65</v>
+        <v>86.84</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>65.95999999999999</v>
+        <v>69.88</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>87.84</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>89.95999999999999</v>
+        <v>63.99</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>40.8</v>
+        <v>32.44</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>268.74</v>
+        <v>60.03</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>236.94</v>
+        <v>59.75</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>3912750</v>
+        <v>22324808</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>28492</v>
+        <v>12377</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>BALAMINES</t>
+          <t>ARVIND</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -858,37 +858,37 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2133</v>
+        <v>516.6</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>65.02</v>
+        <v>69.7</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>82.52</v>
+        <v>78.92</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>59.86</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>22.49</v>
+        <v>27.63</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1410.42</v>
+        <v>395.96</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1404.65</v>
+        <v>383.81</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>667820</v>
+        <v>974663</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>6911</v>
+        <v>13541</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SPARC</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -897,37 +897,37 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>223.76</v>
+        <v>5454.6</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>64.65000000000001</v>
+        <v>69.37</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>76.27</v>
+        <v>70.75</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>59.15</v>
+        <v>81.34999999999999</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>37.82</v>
+        <v>22.52</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>155.32</v>
+        <v>3777.29</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>153.57</v>
+        <v>3541.77</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>10027945</v>
+        <v>242325</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>7261</v>
+        <v>16954</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>GRWRHITECH</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -936,37 +936,37 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>6131.5</v>
+        <v>1744.6</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>64.51000000000001</v>
+        <v>68.92</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>73.92</v>
+        <v>77.64</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>66.25</v>
+        <v>75.98999999999999</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>22.76</v>
+        <v>40.3</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>4315.55</v>
+        <v>1164.69</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>4151.16</v>
+        <v>1108.42</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>155856</v>
+        <v>554855</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>14245</v>
+        <v>11652</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>BBOX</t>
+          <t>TMB</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -975,37 +975,37 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1018.6</v>
+        <v>780.6</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>63.88</v>
+        <v>67.86</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>78.56</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>75.28</v>
+        <v>72.43000000000001</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>29.82</v>
+        <v>22.77</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>658.24</v>
+        <v>624.8</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>624.39</v>
+        <v>597.65</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1506723</v>
+        <v>321251</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>18090</v>
+        <v>12361</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>PRIVISCL</t>
+          <t>SPARC</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1014,37 +1014,37 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>3444.3</v>
+        <v>238.09</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>63.84</v>
+        <v>67.41</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>61.97</v>
+        <v>78.75</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>69.54000000000001</v>
+        <v>61.12</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>49.3</v>
+        <v>36.74</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2988.2</v>
+        <v>160.63</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2888.32</v>
+        <v>157.74</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>108364</v>
+        <v>9195258</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>13454</v>
+        <v>7727</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>THYROCARE</t>
+          <t>PGIL</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1053,37 +1053,37 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>528.9</v>
+        <v>1793.5</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>63.32</v>
+        <v>67.01000000000001</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>68.98999999999999</v>
+        <v>61.56</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>66.19</v>
+        <v>66.14</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>24.19</v>
+        <v>44.14</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>433.41</v>
+        <v>1545.02</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>422.1</v>
+        <v>1513.1</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>824494</v>
+        <v>125340</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>8418</v>
+        <v>8283</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>EQUITASBNK</t>
+          <t>THYROCARE</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1092,37 +1092,37 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>75.54000000000001</v>
+        <v>540.55</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>63.04</v>
+        <v>66.53</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>63.82</v>
+        <v>70.39</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>55.3</v>
+        <v>66.88</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>27.02</v>
+        <v>21.46</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>65.13</v>
+        <v>439.99</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>64.78</v>
+        <v>427.58</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>5960044</v>
+        <v>417056</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>8640</v>
+        <v>8603</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>ARVIND</t>
+          <t>LLOYDSENT</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1131,37 +1131,37 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>494.5</v>
+        <v>77.22</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>62.05</v>
+        <v>66.12</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>76.43000000000001</v>
+        <v>63.81</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>71.06</v>
+        <v>60.54</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>21.12</v>
+        <v>47.83</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>388.51</v>
+        <v>63.32</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>377.68</v>
+        <v>62.82</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>1310620</v>
+        <v>3815399</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>12962</v>
+        <v>11788</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>SANSERA</t>
+          <t>AKUMS</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1170,37 +1170,37 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>2914.2</v>
+        <v>604.7</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>61.12</v>
+        <v>65.39</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>73.15000000000001</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>77.14</v>
+        <v>52.33</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>25.37</v>
+        <v>39.76</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>2198.45</v>
+        <v>510.27</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>2070.5</v>
+        <v>510.16</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>318575</v>
+        <v>381583</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>18165</v>
+        <v>9258</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>PRIVISCL</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1209,37 +1209,37 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>275.7</v>
+        <v>3493.9</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>60.97</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>69.23999999999999</v>
+        <v>63.08</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>69.04000000000001</v>
+        <v>70.05</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>24.54</v>
+        <v>38.81</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>227.48</v>
+        <v>3019.46</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>220.48</v>
+        <v>2916.94</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>2898589</v>
+        <v>106112</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>10426</v>
+        <v>13648</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>WABAG</t>
+          <t>EQUITASBNK</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1248,37 +1248,37 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1577.8</v>
+        <v>77.25</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>60.26</v>
+        <v>63</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>63.86</v>
+        <v>65.44</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>59.66</v>
+        <v>56.16</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>37.71</v>
+        <v>36.41</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1385.57</v>
+        <v>65.98</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1383.87</v>
+        <v>65.48</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>318217</v>
+        <v>4254743</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>9832</v>
+        <v>8835</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>APOLLO</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1287,37 +1287,37 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1261.2</v>
+        <v>433.15</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>59.01</v>
+        <v>62.95</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>65.29000000000001</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>63.91</v>
+        <v>73.37</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>67.33</v>
+        <v>41.56</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>981.33</v>
+        <v>292.2</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>942.91</v>
+        <v>276.1</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>382890</v>
+        <v>30426358</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>8256</v>
+        <v>15623</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>YATHARTH</t>
+          <t>MTARTECH</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1326,37 +1326,37 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>839.75</v>
+        <v>8374.5</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>58.74</v>
+        <v>62.63</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>60.12</v>
+        <v>80.7</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>63.29</v>
+        <v>88.59</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>38.65</v>
+        <v>60</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>732.99</v>
+        <v>4780.46</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>713.9400000000001</v>
+        <v>4272.01</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>445462</v>
+        <v>2387010</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>8091</v>
+        <v>25760</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>SHAILY</t>
+          <t>BBOX</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1365,37 +1365,37 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2972</v>
+        <v>1023</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>58.54</v>
+        <v>61.92</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>66.05</v>
+        <v>78.72</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>71.48999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>22.09</v>
+        <v>21.5</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2356.48</v>
+        <v>681.72</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>2270.06</v>
+        <v>643.77</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>286665</v>
+        <v>1396173</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>13670</v>
+        <v>18168</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>KIRLPNU</t>
+          <t>SHILPAMED</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1404,37 +1404,37 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1606</v>
+        <v>551.35</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>56.18</v>
+        <v>60.84</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>75.06</v>
+        <v>79.94</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>64.84999999999999</v>
+        <v>69.98</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>53.96</v>
+        <v>22.78</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1307.87</v>
+        <v>412.45</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1283.65</v>
+        <v>401.94</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>149813</v>
+        <v>1381188</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>10432</v>
+        <v>10783</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>AZAD</t>
+          <t>SANSERA</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1443,37 +1443,37 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2150.1</v>
+        <v>2945.8</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>54.69</v>
+        <v>60.71</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>62.6</v>
+        <v>73.76000000000001</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>63.04</v>
+        <v>77.44</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>39.31</v>
+        <v>34.85</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1810.38</v>
+        <v>2243.67</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1767.43</v>
+        <v>2111.33</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>427263</v>
+        <v>323667</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>13886</v>
+        <v>18362</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GOKULAGRO</t>
+          <t>SKIPPER</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1482,37 +1482,37 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>233.07</v>
+        <v>543.3</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>54.18</v>
+        <v>58.06</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>66.23999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>68.84</v>
+        <v>61.53</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>28.64</v>
+        <v>46.61</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>198.38</v>
+        <v>455</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>191.16</v>
+        <v>453.94</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>618053</v>
+        <v>1058360</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>6878</v>
+        <v>6134</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>SKYGOLD</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1521,37 +1521,37 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>508.95</v>
+        <v>274.7</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>54.1</v>
+        <v>57.48</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>63.71</v>
+        <v>68.64</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>69.19</v>
+        <v>68.89</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>30.27</v>
+        <v>27.24</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>397.82</v>
+        <v>230.64</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>382.38</v>
+        <v>223.25</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1778179</v>
+        <v>2842668</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>7882</v>
+        <v>10389</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>AXISCADES</t>
+          <t>NEOGEN</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1560,37 +1560,37 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1947.6</v>
+        <v>1932</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>53.74</v>
+        <v>57.15</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>61.44</v>
+        <v>65.72</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>69.59999999999999</v>
+        <v>58.67</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>52.14</v>
+        <v>26.73</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1626.26</v>
+        <v>1546.98</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>1546.73</v>
+        <v>1527.81</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>179470</v>
+        <v>121466</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>8283</v>
+        <v>5290</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>ADVENZYMES</t>
+          <t>YATHARTH</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1599,37 +1599,37 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>368.95</v>
+        <v>839.75</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>52.08</v>
+        <v>57.02</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>65.58</v>
+        <v>60.12</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>56.5</v>
+        <v>63.29</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>34.51</v>
+        <v>43.26</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>325.47</v>
+        <v>739.41</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>323.36</v>
+        <v>719.62</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>492991</v>
+        <v>409113</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>4131</v>
+        <v>8091</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>MTARTECH</t>
+          <t>STAR</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1638,37 +1638,37 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>7159.5</v>
+        <v>1110.9</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>51.67</v>
+        <v>56.16</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>75.42</v>
+        <v>62.19</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>79.19</v>
+        <v>61.25</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>63.1</v>
+        <v>52.27</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>4557.33</v>
+        <v>982.11</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>4079.55</v>
+        <v>961.3200000000001</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1973289</v>
+        <v>337113</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>22022</v>
+        <v>10239</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>GAEL</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1677,31 +1677,31 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>157.83</v>
+        <v>1235.2</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>50.59</v>
+        <v>55.82</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>61.51</v>
+        <v>63.24</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>62.77</v>
+        <v>63.25</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>41.28</v>
+        <v>68.02</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>140.98</v>
+        <v>997.4</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>136.93</v>
+        <v>956.9400000000001</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>1026983</v>
+        <v>276698</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>7239</v>
+        <v>8085</v>
       </c>
     </row>
     <row r="32">
@@ -1716,31 +1716,226 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1192.8</v>
+        <v>1272.7</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>47.4</v>
+        <v>55.55</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>65.87</v>
+        <v>69.59</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>75.23</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>31.09</v>
+        <v>34.18</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>938.95</v>
+        <v>957.64</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>871.87</v>
+        <v>889.41</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>1608996</v>
+        <v>1548652</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>18635</v>
+        <v>19883</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>ADVENZYMES</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>373.7</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>54.95</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>66.68000000000001</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>26.16</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>328.44</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>325.8</v>
+      </c>
+      <c r="J33" s="4" t="n">
+        <v>456452</v>
+      </c>
+      <c r="K33" s="4" t="n">
+        <v>4185</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>GAEL</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>159.98</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>54.36</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>62.78</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>63.49</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>24.43</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>142.06</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>137.89</v>
+      </c>
+      <c r="J34" s="4" t="n">
+        <v>877752</v>
+      </c>
+      <c r="K34" s="4" t="n">
+        <v>7338</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>AXISCADES</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>1943.2</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>53.23</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>61.21</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>69.53</v>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>36.94</v>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>1644.53</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>1565.11</v>
+      </c>
+      <c r="J35" s="4" t="n">
+        <v>182722</v>
+      </c>
+      <c r="K35" s="4" t="n">
+        <v>8265</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>SKYGOLD</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>509.4</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>52.17</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>63.75</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>69.25</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>28.79</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>405.94</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>389.33</v>
+      </c>
+      <c r="J36" s="4" t="n">
+        <v>1609797</v>
+      </c>
+      <c r="K36" s="4" t="n">
+        <v>7889</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>SHAILY</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>2803.8</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>47.87</v>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>60.25</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>67.55</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>2388.83</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>2299.27</v>
+      </c>
+      <c r="J37" s="4" t="n">
+        <v>395958</v>
+      </c>
+      <c r="K37" s="4" t="n">
+        <v>12896</v>
       </c>
     </row>
   </sheetData>
@@ -1776,6 +1971,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1842,22 +2042,22 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>159.97</v>
+        <v>176.92</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>85.08</v>
+        <v>90.16</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>81.56</v>
+        <v>84.37</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>86.81</v>
+        <v>88.17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>AKUMS</t>
+          <t>PARAS</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -1866,22 +2066,22 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>622.9</v>
+        <v>1408.65</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>77.65000000000001</v>
+        <v>85.16</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>71.47</v>
+        <v>81.18000000000001</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>53.94</v>
+        <v>70.19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>WABAG</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -1890,22 +2090,22 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>5478.7</v>
+        <v>1983.6</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>77.55</v>
+        <v>83.31</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>71.18000000000001</v>
+        <v>77.47</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>81.44</v>
+        <v>67.52</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>QUESS</t>
+          <t>VMART</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -1914,22 +2114,22 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>244.02</v>
+        <v>797.8</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>75.90000000000001</v>
+        <v>81.59</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>62.78</v>
+        <v>67.92</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>39.07</v>
+        <v>54.43</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>NEOGEN</t>
+          <t>ASTRAMICRO</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -1938,22 +2138,22 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>2033.7</v>
+        <v>1684.1</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>75.09999999999999</v>
+        <v>81.44</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>71.52</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>60.34</v>
+        <v>76.63</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>PARAS</t>
+          <t>MSTCLTD</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1962,22 +2162,22 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>1097.15</v>
+        <v>692.75</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>75.06999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>72.98</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>63.21</v>
+        <v>60.88</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>MSTCLTD</t>
+          <t>RBA</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1986,22 +2186,22 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>568.55</v>
+        <v>73.67</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>74.76000000000001</v>
+        <v>80.02</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>66.09999999999999</v>
+        <v>66.84</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>54.77</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>SFL</t>
+          <t>KIRLPNU</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2010,22 +2210,22 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>703.55</v>
+        <v>1950</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>72.25</v>
+        <v>78.76000000000001</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>66.04000000000001</v>
+        <v>84.45999999999999</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>48.33</v>
+        <v>71.39</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>SOUTHBANK</t>
+          <t>QUESS</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2034,22 +2234,22 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>46.66</v>
+        <v>249.87</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>72.22</v>
+        <v>77.87</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>67.84</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>70.69</v>
+        <v>39.86</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>INOXINDIA</t>
+          <t>SOUTHBANK</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2058,22 +2258,22 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1808.2</v>
+        <v>48.46</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>71.28</v>
+        <v>76.86</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>81.58</v>
+        <v>70.45999999999999</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>80.23999999999999</v>
+        <v>72.02</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>RUBICON</t>
+          <t>AVL</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2082,22 +2282,22 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1295.5</v>
+        <v>629.9</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>70.73</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>89.95999999999999</v>
+        <v>68.59</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v/>
+        <v>68.01000000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>WEWORK</t>
+          <t>GRWRHITECH</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -2106,22 +2306,22 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>639.35</v>
+        <v>6785.5</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>70.48999999999999</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>64.03</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v/>
+        <v>68.68000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>VMART</t>
+          <t>SKFINDUS</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -2130,22 +2330,22 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>719.75</v>
+        <v>2626.8</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>69.54000000000001</v>
+        <v>74.68000000000001</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>60.51</v>
+        <v>62.15</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>50.7</v>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>POWERMECH</t>
+          <t>KIRLOSBROS</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -2154,22 +2354,22 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>2789.5</v>
+        <v>1933.6</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>69.31999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>64.61</v>
+        <v>63.09</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>55.84</v>
+        <v>57.04</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>CERA</t>
+          <t>RATEGAIN</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -2178,22 +2378,22 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>6144</v>
+        <v>867.7</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>69.31</v>
+        <v>74.06</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>64.73</v>
+        <v>77.72</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>50.98</v>
+        <v>64.02</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>RATEGAIN</t>
+          <t>GOKEX</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -2202,22 +2402,22 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>783.05</v>
+        <v>818.7</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>69.27</v>
+        <v>73.87</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>72.37</v>
+        <v>59.53</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>60.67</v>
+        <v>52.62</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>CERA</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -2226,22 +2426,22 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1687</v>
+        <v>6448</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>68.41</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>76.31999999999999</v>
+        <v>68.64</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>75.15000000000001</v>
+        <v>53.24</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>ASTRAMICRO</t>
+          <t>SWSOLAR</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2250,22 +2450,22 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1443.8</v>
+        <v>235.47</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>68.3</v>
+        <v>72.83</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>76.27</v>
+        <v>59.67</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>72.18000000000001</v>
+        <v>43.71</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>TMB</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -2274,22 +2474,22 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>767.05</v>
+        <v>654.35</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>68</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>69.03</v>
+        <v>89.72</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>71.8</v>
+        <v>91.15000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>SHILPAMED</t>
+          <t>ANUP</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -2298,22 +2498,22 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>546.75</v>
+        <v>2246</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>66.83</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>79.54000000000001</v>
+        <v>58.59</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>69.70999999999999</v>
+        <v>52.66</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>RELIGARE</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -2322,22 +2522,22 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>252.37</v>
+        <v>253.4</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>66.73</v>
+        <v>72.04000000000001</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>71.87</v>
+        <v>60.95</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>60.1</v>
+        <v>55.12</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>RAIN</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -2346,22 +2546,22 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>196.87</v>
+        <v>567.65</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>66.37</v>
+        <v>72</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>72.37</v>
+        <v>69.37</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>59.7</v>
+        <v>55.31</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>ICIL</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -2370,22 +2570,22 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>583.65</v>
+        <v>394.6</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>65.95999999999999</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>87.84</v>
+        <v>71.45</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>89.95999999999999</v>
+        <v>62.62</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>SUPRIYA</t>
+          <t>BORORENEW</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -2394,22 +2594,22 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>977.15</v>
+        <v>598.25</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>65.70999999999999</v>
+        <v>70.44</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>77.09999999999999</v>
+        <v>62.12</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>68.27</v>
+        <v>56.07</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>INOXGREEN</t>
+          <t>LLOYDSENGG</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -2418,22 +2618,22 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>189.9</v>
+        <v>86.84</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>65.59999999999999</v>
+        <v>69.88</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>55.35</v>
+        <v>75.70999999999999</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>54.48</v>
+        <v>63.99</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>BALAMINES</t>
+          <t>ARVIND</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -2442,22 +2642,22 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2133</v>
+        <v>516.6</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>65.02</v>
+        <v>69.7</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>82.52</v>
+        <v>78.92</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>59.86</v>
+        <v>72.56999999999999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>ICIL</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -2466,22 +2666,22 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>344.45</v>
+        <v>5454.6</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>64.98999999999999</v>
+        <v>69.37</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>64.48999999999999</v>
+        <v>70.75</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>57.99</v>
+        <v>81.34999999999999</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>SPARC</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -2490,22 +2690,22 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>223.76</v>
+        <v>1868.6</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>64.65000000000001</v>
+        <v>69.33</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>76.27</v>
+        <v>70.34</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>59.15</v>
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>PRUDENT</t>
+          <t>INOXGREEN</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -2514,22 +2714,22 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2909.1</v>
+        <v>199.47</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>64.59999999999999</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>61.82</v>
+        <v>58.57</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>60.25</v>
+        <v>55.73</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>WELENT</t>
+          <t>SUDEEPPHRM</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -2538,22 +2738,22 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>552.25</v>
+        <v>842.95</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>64.59</v>
+        <v>69.29000000000001</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>62.7</v>
+        <v>70.39</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>58.03</v>
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>GRWRHITECH</t>
+          <t>RUBICON</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -2562,22 +2762,22 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>6131.5</v>
+        <v>1361.8</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>64.51000000000001</v>
+        <v>69.28</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>73.92</v>
+        <v>91.08</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>66.25</v>
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -2586,22 +2786,22 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>109.78</v>
+        <v>1744.6</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>64.42</v>
+        <v>68.92</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>49.23</v>
+        <v>77.64</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>42.6</v>
+        <v>75.98999999999999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>MANORAMA</t>
+          <t>INOXINDIA</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -2610,22 +2810,22 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>1564.4</v>
+        <v>1917.8</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>64.31</v>
+        <v>68.84</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>59.52</v>
+        <v>83.98</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>64.64</v>
+        <v>82.08</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>BANCOINDIA</t>
+          <t>CCAVENUE</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -2634,22 +2834,22 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>689.55</v>
+        <v>15.07</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>64.03</v>
+        <v>68.79000000000001</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>59.12</v>
+        <v>49.37</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>60.49</v>
+        <v>41.74</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>BBOX</t>
+          <t>HCC</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -2658,22 +2858,22 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>1018.6</v>
+        <v>27.02</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>63.88</v>
+        <v>68.75</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>78.56</v>
+        <v>65.19</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>75.28</v>
+        <v>51.12</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>PRIVISCL</t>
+          <t>KSB</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -2682,22 +2882,22 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>3444.3</v>
+        <v>902.55</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>63.84</v>
+        <v>68.73</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>61.97</v>
+        <v>59.84</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>69.54000000000001</v>
+        <v>58.42</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>SKFINDUS</t>
+          <t>QPOWER</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -2706,22 +2906,22 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>2386.9</v>
+        <v>1320.6</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>63.52</v>
+        <v>68.69</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>52.59</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v/>
+        <v>67.8</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>THYROCARE</t>
+          <t>SFL</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -2730,22 +2930,22 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>528.9</v>
+        <v>700.65</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>63.32</v>
+        <v>67.89</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>68.98999999999999</v>
+        <v>65.51000000000001</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>66.19</v>
+        <v>48.16</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>EQUITASBNK</t>
+          <t>TMB</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -2754,22 +2954,22 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>75.54000000000001</v>
+        <v>780.6</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>63.04</v>
+        <v>67.86</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>63.82</v>
+        <v>70.20999999999999</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>55.3</v>
+        <v>72.43000000000001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>QPOWER</t>
+          <t>GREAVESCOT</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -2778,22 +2978,22 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>1221.1</v>
+        <v>198.54</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>62.83</v>
+        <v>67.7</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>61.57</v>
+        <v>61.58</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>65.95</v>
+        <v>53.51</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>IXIGO</t>
+          <t>STYL</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -2802,22 +3002,22 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>178.22</v>
+        <v>293.15</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>62.57</v>
+        <v>67.56</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>45.99</v>
+        <v>57.43</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>46.2</v>
+        <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>ARVIND</t>
+          <t>TVSSCS</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -2826,22 +3026,22 @@
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>494.5</v>
+        <v>140.31</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>62.05</v>
+        <v>67.55</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>76.43000000000001</v>
+        <v>62.89</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>71.06</v>
+        <v>50.34</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>TVSSCS</t>
+          <t>REFEX</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -2850,22 +3050,22 @@
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>132.26</v>
+        <v>336.9</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>61.78</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>59.35</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>47.82</v>
+        <v>54.02</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>RELAXO</t>
+          <t>PNCINFRA</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -2874,22 +3074,22 @@
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>342.65</v>
+        <v>226.01</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>61.63</v>
+        <v>67.48</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>50.89</v>
+        <v>52.24</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>33.44</v>
+        <v>42.52</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>IFBIND</t>
+          <t>SPARC</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -2898,22 +3098,22 @@
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>1287.8</v>
+        <v>238.09</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>61.32</v>
+        <v>67.41</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>53.55</v>
+        <v>78.75</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>49.02</v>
+        <v>61.12</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>STYL</t>
+          <t>MARKSANS</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -2922,22 +3122,22 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>279.8</v>
+        <v>259.67</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>61.29</v>
+        <v>67.25</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>52.87</v>
+        <v>73.42</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v/>
+        <v>61.02</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>RELIGARE</t>
+          <t>AEQUS</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -2946,22 +3146,22 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>239.82</v>
+        <v>222.13</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>61.29</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>54.87</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>52.44</v>
+        <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>SANSERA</t>
+          <t>PGIL</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -2970,22 +3170,22 @@
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>2914.2</v>
+        <v>1793.5</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>61.12</v>
+        <v>67.01000000000001</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>73.15000000000001</v>
+        <v>61.56</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>77.14</v>
+        <v>66.14</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>SAATVIKGL</t>
+          <t>POWERMECH</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -2994,22 +3194,22 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>476.4</v>
+        <v>2839.9</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>61.04</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>59.57</v>
+        <v>65.87</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v/>
+        <v>56.46</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>THYROCARE</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -3018,22 +3218,22 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>275.7</v>
+        <v>540.55</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>60.97</v>
+        <v>66.53</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>69.23999999999999</v>
+        <v>70.39</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>69.04000000000001</v>
+        <v>66.88</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>SUDEEPPHRM</t>
+          <t>LLOYDSENT</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -3042,22 +3242,22 @@
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>749.5</v>
+        <v>77.22</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>60.79</v>
+        <v>66.12</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>61.5</v>
+        <v>63.81</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v/>
+        <v>60.54</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>SURYAROSNI</t>
+          <t>WELENT</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -3066,22 +3266,22 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>263.01</v>
+        <v>567.85</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>60.76</v>
+        <v>66.05</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>55.51</v>
+        <v>65.37</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>50.74</v>
+        <v>59.12</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>SKIPPER</t>
+          <t>EDELWEISS</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -3090,22 +3290,22 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>544.65</v>
+        <v>124.71</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>60.26</v>
+        <v>66.02</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>67.94</v>
+        <v>58.49</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>61.68</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>WABAG</t>
+          <t>SAMHI</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -3114,22 +3314,22 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>1577.8</v>
+        <v>175.81</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>60.26</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>63.86</v>
+        <v>56.08</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>59.66</v>
+        <v>49.74</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>RBA</t>
+          <t>BLACKBUCK</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -3138,22 +3338,22 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>68.84999999999999</v>
+        <v>574.05</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>60.25</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>57.28</v>
+        <v>50.43</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>41.69</v>
+        <v>54.85</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>ALKYLAMINE</t>
+          <t>IXIGO</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -3162,22 +3362,22 @@
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>1831.8</v>
+        <v>189.98</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>60.15</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>65.19</v>
+        <v>50.37</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>49.67</v>
+        <v>49.56</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>APOLLO</t>
+          <t>RCF</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -3186,22 +3386,22 @@
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>409.4</v>
+        <v>136.65</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>59.99</v>
+        <v>65.44</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>71.79000000000001</v>
+        <v>55.27</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>72.04000000000001</v>
+        <v>49.84</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>SHRIPISTON</t>
+          <t>PRUDENT</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -3210,22 +3410,22 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>3524.4</v>
+        <v>3029.2</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>59.47</v>
+        <v>65.44</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>59.05</v>
+        <v>65.16</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>70.78</v>
+        <v>61.76</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>AKUMS</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -3234,22 +3434,22 @@
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>1261.2</v>
+        <v>604.7</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>59.01</v>
+        <v>65.39</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>65.29000000000001</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>63.91</v>
+        <v>52.33</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>REFEX</t>
+          <t>KNRCON</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -3258,22 +3458,22 @@
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>311</v>
+        <v>140.86</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>58.98</v>
+        <v>65.39</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>60.51</v>
+        <v>51.29</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>51.51</v>
+        <v>37.6</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>DIACABS</t>
+          <t>PRIVISCL</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -3282,22 +3482,22 @@
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>201.91</v>
+        <v>3493.9</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>58.96</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>75.12</v>
+        <v>63.08</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>67.27</v>
+        <v>70.05</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>BORORENEW</t>
+          <t>RATNAMANI</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -3306,22 +3506,22 @@
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>544.6</v>
+        <v>2770.9</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>58.92</v>
+        <v>64.88</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>55.76</v>
+        <v>60.66</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>52.61</v>
+        <v>53.23</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>YATHARTH</t>
+          <t>SHRIPISTON</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -3330,22 +3530,22 @@
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>839.75</v>
+        <v>3739.7</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>58.74</v>
+        <v>64.59</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>60.12</v>
+        <v>63.22</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>63.29</v>
+        <v>72.95</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>KIRLOSBROS</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -3354,22 +3554,22 @@
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>1729.4</v>
+        <v>470</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>58.59</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>54.23</v>
+        <v>56.05</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>53.04</v>
+        <v>55.47</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>SHAILY</t>
+          <t>KRBL</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -3378,22 +3578,22 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>2972</v>
+        <v>384.95</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>58.54</v>
+        <v>63.82</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>66.05</v>
+        <v>58.36</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>71.48999999999999</v>
+        <v>55.17</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>INDIGOPNTS</t>
+          <t>JAMNAAUTO</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -3402,22 +3602,22 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>995.2</v>
+        <v>132.37</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>58.53</v>
+        <v>63.36</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>52.82</v>
+        <v>56.57</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>44.78</v>
+        <v>58.32</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>KRBL</t>
+          <t>SUNTECK</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -3426,22 +3626,22 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>366.8</v>
+        <v>326.1</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>58.28</v>
+        <v>63.23</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>54.08</v>
+        <v>46.01</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>53.34</v>
+        <v>43.13</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>SWSOLAR</t>
+          <t>TRIVENI</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -3450,22 +3650,22 @@
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>208.23</v>
+        <v>403.55</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>58.19</v>
+        <v>63.22</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>51.35</v>
+        <v>56.92</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>40.55</v>
+        <v>54.8</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>EQUITASBNK</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -3474,22 +3674,22 @@
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>285.85</v>
+        <v>77.25</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>58.1</v>
+        <v>63</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>55.72</v>
+        <v>65.44</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>56.34</v>
+        <v>56.16</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>KANSAINER</t>
+          <t>APOLLO</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -3498,22 +3698,22 @@
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>216.5</v>
+        <v>433.15</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>57.99</v>
+        <v>62.95</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>52.52</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>43.34</v>
+        <v>73.37</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>GREAVESCOT</t>
+          <t>BECTORFOOD</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -3522,22 +3722,22 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>185.04</v>
+        <v>190.32</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>57.85</v>
+        <v>62.94</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>56.64</v>
+        <v>42.74</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>51.12</v>
+        <v>41.58</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>RAYMONDLSL</t>
+          <t>EMIL</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -3546,22 +3746,22 @@
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>794.75</v>
+        <v>120.86</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>57.42</v>
+        <v>62.88</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>42.82</v>
+        <v>56.84</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>27.1</v>
+        <v>47.31</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>MIDHANI</t>
+          <t>MTARTECH</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -3570,22 +3770,22 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>435.1</v>
+        <v>8374.5</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>57.25</v>
+        <v>62.63</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>66.02</v>
+        <v>80.7</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>57.27</v>
+        <v>88.59</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>EPL</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -3594,22 +3794,22 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>224.8</v>
+        <v>297.35</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>57.05</v>
+        <v>62.61</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>54.55</v>
+        <v>58.87</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>53.95</v>
+        <v>58.18</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>BLACKBUCK</t>
+          <t>INDIGOPNTS</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -3618,22 +3818,22 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>546.4</v>
+        <v>1025.15</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>56.46</v>
+        <v>62.51</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>46.85</v>
+        <v>55.55</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>51.74</v>
+        <v>45.85</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>IIFLCAPS</t>
+          <t>VARROC</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -3642,22 +3842,22 @@
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>342</v>
+        <v>615.2</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>56.31</v>
+        <v>62.45</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>56.56</v>
+        <v>62.22</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>58.59</v>
+        <v>57.09</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>HCC</t>
+          <t>ASHOKA</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -3666,22 +3866,22 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>23.37</v>
+        <v>135.16</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>56.25</v>
+        <v>62.35</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>57.4</v>
+        <v>47.44</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>47.54</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>FIEMIND</t>
+          <t>RELAXO</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -3690,22 +3890,22 @@
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>2308.7</v>
+        <v>355.85</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>56.22</v>
+        <v>62.23</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>58.71</v>
+        <v>53.82</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>68.02</v>
+        <v>34.97</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>KIRLPNU</t>
+          <t>BBOX</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -3714,22 +3914,22 @@
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>1606</v>
+        <v>1023</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>56.18</v>
+        <v>61.92</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>75.06</v>
+        <v>78.72</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>64.84999999999999</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>BLUESTONE</t>
+          <t>ARVINDFASN</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -3738,22 +3938,22 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>520.5</v>
+        <v>484.05</v>
       </c>
       <c r="D81" s="4" t="n">
-        <v>56.18</v>
+        <v>61.87</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>51.92</v>
+        <v>54.62</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v/>
+        <v>53.15</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>VIYASH</t>
+          <t>AURIONPRO</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -3762,22 +3962,22 @@
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>249.95</v>
+        <v>876.4</v>
       </c>
       <c r="D82" s="4" t="n">
-        <v>56.16</v>
+        <v>61.84</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>65.18000000000001</v>
+        <v>47.6</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>62.16</v>
+        <v>43.59</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>JUSTDIAL</t>
+          <t>SMLMAH</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -3786,22 +3986,22 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>538.2</v>
+        <v>4092.2</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>55.96</v>
+        <v>61.74</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>38.17</v>
+        <v>54.55</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>35.75</v>
+        <v>61.68</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>INDIASHLTR</t>
+          <t>BALAMINES</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -3810,22 +4010,22 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>793.4</v>
+        <v>2138.2</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>55.62</v>
+        <v>61.45</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>50.63</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>52.52</v>
+        <v>59.94</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>STARCEMENT</t>
+          <t>OSWALPUMPS</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -3834,22 +4034,22 @@
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>218.57</v>
+        <v>422.9</v>
       </c>
       <c r="D85" s="4" t="n">
-        <v>55.56</v>
+        <v>61.28</v>
       </c>
       <c r="E85" s="4" t="n">
-        <v>48.75</v>
+        <v>49.83</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>52.04</v>
+        <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>OSWALPUMPS</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -3858,22 +4058,22 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>398.2</v>
+        <v>205.87</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>55.28</v>
+        <v>61.27</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>45.95</v>
+        <v>55.02</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v/>
+        <v>43.72</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>ELLEN</t>
+          <t>WEWORK</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -3882,13 +4082,13 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>275.85</v>
+        <v>630.55</v>
       </c>
       <c r="D87" s="4" t="n">
-        <v>55.11</v>
+        <v>61.22</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>46.03</v>
+        <v>62.1</v>
       </c>
       <c r="F87" s="4" t="n">
         <v/>
@@ -3897,7 +4097,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>VAIBHAVGBL</t>
+          <t>SURYAROSNI</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -3906,22 +4106,22 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>230.46</v>
+        <v>266.34</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>55.05</v>
+        <v>61.19</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>53.24</v>
+        <v>56.47</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>46.09</v>
+        <v>51.14</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>SAMHI</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -3930,22 +4130,22 @@
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>163.49</v>
+        <v>111.6</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>55.04</v>
+        <v>61.19</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>49.36</v>
+        <v>50.37</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>46.57</v>
+        <v>43.14</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>TRIVENI</t>
+          <t>SAFARI</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -3954,22 +4154,22 @@
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>385.95</v>
+        <v>1675.5</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>54.89</v>
+        <v>61.01</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>52.25</v>
+        <v>48.47</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>52.62</v>
+        <v>44.94</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>JSFB</t>
+          <t>STYRENIX</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -3978,22 +4178,22 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>479.75</v>
+        <v>2312.9</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>54.8</v>
+        <v>60.98</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>60.06</v>
+        <v>56.35</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>53.31</v>
+        <v>54.76</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>SHAKTIPUMP</t>
+          <t>METROPOLIS</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -4002,22 +4202,22 @@
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>537.15</v>
+        <v>552.75</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>54.79</v>
+        <v>60.95</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>42.43</v>
+        <v>62.38</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>45.68</v>
+        <v>60.57</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>PARKHOSPS</t>
+          <t>SHILPAMED</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -4026,22 +4226,22 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>274.6</v>
+        <v>551.35</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>54.69</v>
+        <v>60.84</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>77.09999999999999</v>
+        <v>79.94</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v/>
+        <v>69.98</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>AZAD</t>
+          <t>VAIBHAVGBL</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -4050,22 +4250,22 @@
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>2150.1</v>
+        <v>244.33</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>54.69</v>
+        <v>60.82</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>62.6</v>
+        <v>58.06</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>63.04</v>
+        <v>48.31</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>MANORAMA</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -4074,22 +4274,22 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>1142.9</v>
+        <v>1558.2</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>54.58</v>
+        <v>60.75</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>58.41</v>
+        <v>59.13</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>65.29000000000001</v>
+        <v>64.48999999999999</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>SMLMAH</t>
+          <t>SANSERA</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -4098,22 +4298,22 @@
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>3883.8</v>
+        <v>2945.8</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>54.54</v>
+        <v>60.71</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>51.14</v>
+        <v>73.76000000000001</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>60.26</v>
+        <v>77.44</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENGG</t>
+          <t>VOLTAMP</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -4122,22 +4322,22 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>70.94</v>
+        <v>10237.5</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>54.52</v>
+        <v>59.94</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>65.84</v>
+        <v>59.19</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>57.52</v>
+        <v>56.64</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>ASHAPURMIN</t>
+          <t>SAATVIKGL</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -4146,22 +4346,22 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>692.05</v>
+        <v>477.2</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>54.2</v>
+        <v>59.9</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>56.63</v>
+        <v>59.71</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>58.61</v>
+        <v/>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>GOKULAGRO</t>
+          <t>ALOKINDS</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -4170,22 +4370,22 @@
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>233.07</v>
+        <v>13.29</v>
       </c>
       <c r="D99" s="4" t="n">
-        <v>54.18</v>
+        <v>59.68</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>66.23999999999999</v>
+        <v>44.82</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>68.84</v>
+        <v>40.08</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>DIACABS</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -4194,22 +4394,22 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>179.86</v>
+        <v>209.24</v>
       </c>
       <c r="D100" s="4" t="n">
-        <v>54.15</v>
+        <v>59.62</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>54.3</v>
+        <v>77.06999999999999</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>58.89</v>
+        <v>68.27</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>SKYGOLD</t>
+          <t>SANOFICONR</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -4218,22 +4418,22 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>508.95</v>
+        <v>4812.5</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>54.1</v>
+        <v>59.59</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>63.71</v>
+        <v>57.03</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>69.19</v>
+        <v>52.26</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>UTLSOLAR</t>
+          <t>ALKYLAMINE</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -4242,22 +4442,22 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>310.15</v>
+        <v>1845.4</v>
       </c>
       <c r="D102" s="4" t="n">
-        <v>53.88</v>
+        <v>59.55</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>67.45999999999999</v>
+        <v>65.84</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v/>
+        <v>49.97</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>AXISCADES</t>
+          <t>IFBIND</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -4266,22 +4466,22 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>1947.6</v>
+        <v>1284.5</v>
       </c>
       <c r="D103" s="4" t="n">
-        <v>53.74</v>
+        <v>59.52</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>61.44</v>
+        <v>53.32</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>69.59999999999999</v>
+        <v>48.95</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>CRAMC</t>
+          <t>RAYMONDLSL</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -4290,22 +4490,22 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>250.15</v>
+        <v>810.65</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>53.35</v>
+        <v>59.28</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>45.15</v>
+        <v>44.54</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v/>
+        <v>28.07</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>RTNINDIA</t>
+          <t>EPL</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -4314,22 +4514,22 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>36.4</v>
+        <v>229.57</v>
       </c>
       <c r="D105" s="4" t="n">
-        <v>53.35</v>
+        <v>59.25</v>
       </c>
       <c r="E105" s="4" t="n">
-        <v>49.82</v>
+        <v>56.58</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>42.77</v>
+        <v>54.98</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>JLHL</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -4338,22 +4538,22 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>1728.3</v>
+        <v>1342.1</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>53.07</v>
+        <v>59.1</v>
       </c>
       <c r="E106" s="4" t="n">
-        <v>62.34</v>
+        <v>53.28</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v/>
+        <v>49.63</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>ROUTE</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -4362,22 +4562,22 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>503.85</v>
+        <v>545.5</v>
       </c>
       <c r="D107" s="4" t="n">
-        <v>52.94</v>
+        <v>59.01</v>
       </c>
       <c r="E107" s="4" t="n">
-        <v>57.84</v>
+        <v>46.64</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>49.45</v>
+        <v>31.62</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>METROPOLIS</t>
+          <t>VIYASH</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -4386,22 +4586,22 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>530.7</v>
+        <v>254.95</v>
       </c>
       <c r="D108" s="4" t="n">
-        <v>52.87</v>
+        <v>58.98</v>
       </c>
       <c r="E108" s="4" t="n">
-        <v>58.69</v>
+        <v>66.72</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>57.35</v>
+        <v>63.28</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>KSB</t>
+          <t>AHLUCONT</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -4410,22 +4610,22 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>834.8</v>
+        <v>838.8</v>
       </c>
       <c r="D109" s="4" t="n">
-        <v>52.69</v>
+        <v>58.7</v>
       </c>
       <c r="E109" s="4" t="n">
-        <v>52.44</v>
+        <v>50.55</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>54.96</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>BECTORFOOD</t>
+          <t>AGARWALEYE</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -4434,22 +4634,22 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>181.65</v>
+        <v>466.65</v>
       </c>
       <c r="D110" s="4" t="n">
-        <v>52.38</v>
+        <v>58.62</v>
       </c>
       <c r="E110" s="4" t="n">
-        <v>37.14</v>
+        <v>52.8</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>39.67</v>
+        <v>52.15</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>VIKRAMSOLR</t>
+          <t>SHAKTIPUMP</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -4458,22 +4658,22 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>209.86</v>
+        <v>551.05</v>
       </c>
       <c r="D111" s="4" t="n">
-        <v>52.31</v>
+        <v>58.54</v>
       </c>
       <c r="E111" s="4" t="n">
         <v>44.82</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v/>
+        <v>46.46</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>JLHL</t>
+          <t>AARTIPHARM</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -4482,22 +4682,22 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>1315.7</v>
+        <v>691.8</v>
       </c>
       <c r="D112" s="4" t="n">
-        <v>52.21</v>
+        <v>58.51</v>
       </c>
       <c r="E112" s="4" t="n">
-        <v>50.01</v>
+        <v>48.26</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>48.18</v>
+        <v>50.96</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>ATLANTAELE</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -4506,22 +4706,22 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>1843.7</v>
+        <v>184.59</v>
       </c>
       <c r="D113" s="4" t="n">
-        <v>52.15</v>
+        <v>58.42</v>
       </c>
       <c r="E113" s="4" t="n">
-        <v>68.13</v>
+        <v>57.52</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v/>
+        <v>59.89</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>PGIL</t>
+          <t>SUPRIYA</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -4530,22 +4730,22 @@
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>1630.9</v>
+        <v>932.2</v>
       </c>
       <c r="D114" s="4" t="n">
-        <v>52.12</v>
+        <v>58.25</v>
       </c>
       <c r="E114" s="4" t="n">
-        <v>54.43</v>
+        <v>70</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>62.48</v>
+        <v>65.41</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>VOLTAMP</t>
+          <t>APLLTD</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -4554,22 +4754,22 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>9719.5</v>
+        <v>763</v>
       </c>
       <c r="D115" s="4" t="n">
-        <v>52.11</v>
+        <v>58.09</v>
       </c>
       <c r="E115" s="4" t="n">
-        <v>55.66</v>
+        <v>48.15</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>55.02</v>
+        <v>45.05</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>AVL</t>
+          <t>NETWORK18</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -4578,22 +4778,22 @@
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>536.9</v>
+        <v>33.98</v>
       </c>
       <c r="D116" s="4" t="n">
-        <v>52.1</v>
+        <v>58.08</v>
       </c>
       <c r="E116" s="4" t="n">
-        <v>55.89</v>
+        <v>44.94</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>57.69</v>
+        <v>38.04</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>ADVENZYMES</t>
+          <t>SKIPPER</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -4602,22 +4802,22 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>368.95</v>
+        <v>543.3</v>
       </c>
       <c r="D117" s="4" t="n">
-        <v>52.08</v>
+        <v>58.06</v>
       </c>
       <c r="E117" s="4" t="n">
-        <v>65.58</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>56.5</v>
+        <v>61.53</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>VIPIND</t>
+          <t>BIRLACORPN</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -4626,22 +4826,22 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>314.95</v>
+        <v>1018.3</v>
       </c>
       <c r="D118" s="4" t="n">
-        <v>51.93</v>
+        <v>57.61</v>
       </c>
       <c r="E118" s="4" t="n">
-        <v>42.7</v>
+        <v>51.78</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>37.81</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>LXCHEM</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -4650,22 +4850,22 @@
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>153.88</v>
+        <v>274.7</v>
       </c>
       <c r="D119" s="4" t="n">
-        <v>51.84</v>
+        <v>57.48</v>
       </c>
       <c r="E119" s="4" t="n">
-        <v>51.7</v>
+        <v>68.64</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>40.36</v>
+        <v>68.89</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>SMARTWORKS</t>
+          <t>NFL</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -4674,22 +4874,22 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>446.35</v>
+        <v>77.86</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>51.7</v>
+        <v>57.47</v>
       </c>
       <c r="E120" s="4" t="n">
-        <v>50.42</v>
+        <v>49.06</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v/>
+        <v>45.83</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>DATAMATICS</t>
+          <t>ELLEN</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -4698,22 +4898,22 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>778.4</v>
+        <v>281.55</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>51.7</v>
+        <v>57.33</v>
       </c>
       <c r="E121" s="4" t="n">
-        <v>51.78</v>
+        <v>47.75</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>54.48</v>
+        <v/>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>MTARTECH</t>
+          <t>ELECTCAST</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -4722,22 +4922,22 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>7159.5</v>
+        <v>81.34</v>
       </c>
       <c r="D122" s="4" t="n">
-        <v>51.67</v>
+        <v>57.32</v>
       </c>
       <c r="E122" s="4" t="n">
-        <v>75.42</v>
+        <v>51.63</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>79.19</v>
+        <v>44.32</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>ETHOSLTD</t>
+          <t>NEOGEN</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -4746,22 +4946,22 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>2391.8</v>
+        <v>1932</v>
       </c>
       <c r="D123" s="4" t="n">
-        <v>51.64</v>
+        <v>57.15</v>
       </c>
       <c r="E123" s="4" t="n">
-        <v>46.8</v>
+        <v>65.72</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>48.5</v>
+        <v>58.67</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>JAMNAAUTO</t>
+          <t>YATHARTH</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -4770,22 +4970,22 @@
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>121.8</v>
+        <v>839.75</v>
       </c>
       <c r="D124" s="4" t="n">
-        <v>51.61</v>
+        <v>57.02</v>
       </c>
       <c r="E124" s="4" t="n">
-        <v>50.58</v>
+        <v>60.12</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>54.53</v>
+        <v>63.29</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>CSBBANK</t>
+          <t>KITEX</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -4794,22 +4994,22 @@
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>366.35</v>
+        <v>163.41</v>
       </c>
       <c r="D125" s="4" t="n">
-        <v>51.43</v>
+        <v>56.91</v>
       </c>
       <c r="E125" s="4" t="n">
-        <v>45.56</v>
+        <v>46.9</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>50.67</v>
+        <v>49.46</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>OPTIEMUS</t>
+          <t>ALIVUS</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -4818,22 +5018,22 @@
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>423.3</v>
+        <v>1070.3</v>
       </c>
       <c r="D126" s="4" t="n">
-        <v>51.39</v>
+        <v>56.8</v>
       </c>
       <c r="E126" s="4" t="n">
-        <v>48.29</v>
+        <v>60.75</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>47.57</v>
+        <v>60.19</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>VARROC</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -4842,22 +5042,22 @@
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>570.35</v>
+        <v>1162.3</v>
       </c>
       <c r="D127" s="4" t="n">
-        <v>51.32</v>
+        <v>56.74</v>
       </c>
       <c r="E127" s="4" t="n">
-        <v>53.82</v>
+        <v>59.8</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>53.67</v>
+        <v>66.14</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>ROUTE</t>
+          <t>IIFLCAPS</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -4866,22 +5066,22 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>521.9</v>
+        <v>344.4</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>51.28</v>
+        <v>56.61</v>
       </c>
       <c r="E128" s="4" t="n">
-        <v>41.92</v>
+        <v>57.16</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>29.99</v>
+        <v>58.81</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>HCG</t>
+          <t>ASHAPURMIN</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -4890,22 +5090,22 @@
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>630.5</v>
+        <v>708.15</v>
       </c>
       <c r="D129" s="4" t="n">
-        <v>51.2</v>
+        <v>56.57</v>
       </c>
       <c r="E129" s="4" t="n">
-        <v>55.43</v>
+        <v>58.13</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>59.22</v>
+        <v>59.46</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>RCF</t>
+          <t>UJJIVANSFB</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -4914,22 +5114,22 @@
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>127.35</v>
+        <v>57.27</v>
       </c>
       <c r="D130" s="4" t="n">
-        <v>51</v>
+        <v>56.47</v>
       </c>
       <c r="E130" s="4" t="n">
-        <v>47.59</v>
+        <v>52.95</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>46.79</v>
+        <v>58.27</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>REDTAPE</t>
+          <t>STAR</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -4938,22 +5138,22 @@
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>133.87</v>
+        <v>1110.9</v>
       </c>
       <c r="D131" s="4" t="n">
-        <v>50.96</v>
+        <v>56.16</v>
       </c>
       <c r="E131" s="4" t="n">
-        <v>52.74</v>
+        <v>62.19</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>35.38</v>
+        <v>61.25</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>GAEL</t>
+          <t>LOTUSDEV</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -4962,22 +5162,22 @@
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>157.83</v>
+        <v>142.48</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>50.59</v>
+        <v>56.06</v>
       </c>
       <c r="E132" s="4" t="n">
-        <v>61.51</v>
+        <v>48.52</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>62.77</v>
+        <v/>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>MEDPLUS</t>
+          <t>OPTIEMUS</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -4986,22 +5186,22 @@
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>881.95</v>
+        <v>440.85</v>
       </c>
       <c r="D133" s="4" t="n">
-        <v>50.44</v>
+        <v>56.05</v>
       </c>
       <c r="E133" s="4" t="n">
-        <v>53.75</v>
+        <v>50.89</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>56.51</v>
+        <v>48.66</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>SENCO</t>
+          <t>RAIN</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -5010,22 +5210,22 @@
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>338.35</v>
+        <v>191</v>
       </c>
       <c r="D134" s="4" t="n">
-        <v>50.26</v>
+        <v>56.04</v>
       </c>
       <c r="E134" s="4" t="n">
-        <v>52.38</v>
+        <v>68.77</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>48.89</v>
+        <v>58.77</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>RATNAMANI</t>
+          <t>PARKHOSPS</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -5034,22 +5234,22 @@
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>2580.5</v>
+        <v>277.6</v>
       </c>
       <c r="D135" s="4" t="n">
-        <v>50.21</v>
+        <v>55.9</v>
       </c>
       <c r="E135" s="4" t="n">
-        <v>54.4</v>
+        <v>77.7</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>49.47</v>
+        <v/>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>UJJIVANSFB</t>
+          <t>MIDHANI</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -5058,22 +5258,22 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>54.76</v>
+        <v>437</v>
       </c>
       <c r="D136" s="4" t="n">
-        <v>50.19</v>
+        <v>55.84</v>
       </c>
       <c r="E136" s="4" t="n">
-        <v>49.05</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>56.45</v>
+        <v>57.42</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>ALIVUS</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -5082,22 +5282,22 @@
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>1045.7</v>
+        <v>1235.2</v>
       </c>
       <c r="D137" s="4" t="n">
-        <v>50.12</v>
+        <v>55.82</v>
       </c>
       <c r="E137" s="4" t="n">
-        <v>57.7</v>
+        <v>63.24</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>58.54</v>
+        <v>63.25</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>HEMIPROP</t>
+          <t>ATLANTAELE</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -5106,22 +5306,22 @@
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>140.37</v>
+        <v>1915.7</v>
       </c>
       <c r="D138" s="4" t="n">
-        <v>50.07</v>
+        <v>55.59</v>
       </c>
       <c r="E138" s="4" t="n">
-        <v>51.8</v>
+        <v>69.81</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>49.54</v>
+        <v/>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>EMBDL</t>
+          <t>TDPOWERSYS</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -5130,22 +5330,22 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>59.06</v>
+        <v>1272.7</v>
       </c>
       <c r="D139" s="4" t="n">
-        <v>49.69</v>
+        <v>55.55</v>
       </c>
       <c r="E139" s="4" t="n">
-        <v>46.62</v>
+        <v>69.59</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>41.3</v>
+        <v>81.01000000000001</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>TEXRAIL</t>
+          <t>CRAMC</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -5154,22 +5354,22 @@
         </is>
       </c>
       <c r="C140" s="4" t="n">
-        <v>105.86</v>
+        <v>254.6</v>
       </c>
       <c r="D140" s="4" t="n">
-        <v>49.67</v>
+        <v>55.54</v>
       </c>
       <c r="E140" s="4" t="n">
-        <v>45.09</v>
+        <v>47.38</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>42.93</v>
+        <v/>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>APLLTD</t>
+          <t>BLUESTONE</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -5178,22 +5378,22 @@
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>743.35</v>
+        <v>522.8</v>
       </c>
       <c r="D141" s="4" t="n">
-        <v>49.65</v>
+        <v>55.54</v>
       </c>
       <c r="E141" s="4" t="n">
-        <v>44.31</v>
+        <v>52.21</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>43.75</v>
+        <v/>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>TANLA</t>
+          <t>SMARTWORKS</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -5202,22 +5402,22 @@
         </is>
       </c>
       <c r="C142" s="4" t="n">
-        <v>513.7</v>
+        <v>462.8</v>
       </c>
       <c r="D142" s="4" t="n">
-        <v>49.51</v>
+        <v>55.45</v>
       </c>
       <c r="E142" s="4" t="n">
-        <v>51.52</v>
+        <v>53.98</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>44.03</v>
+        <v/>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>SAFARI</t>
+          <t>WAAREERTL</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -5226,22 +5426,22 @@
         </is>
       </c>
       <c r="C143" s="4" t="n">
-        <v>1535.1</v>
+        <v>988.05</v>
       </c>
       <c r="D143" s="4" t="n">
-        <v>49.49</v>
+        <v>55.44</v>
       </c>
       <c r="E143" s="4" t="n">
-        <v>41.49</v>
+        <v>52.66</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>41.2</v>
+        <v/>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>AHLUCONT</t>
+          <t>INDIASHLTR</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -5250,22 +5450,22 @@
         </is>
       </c>
       <c r="C144" s="4" t="n">
-        <v>798.1</v>
+        <v>784.35</v>
       </c>
       <c r="D144" s="4" t="n">
-        <v>49.15</v>
+        <v>55.43</v>
       </c>
       <c r="E144" s="4" t="n">
-        <v>45.37</v>
+        <v>50.87</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>46.71</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>PCJEWELLER</t>
+          <t>PURVA</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -5274,22 +5474,22 @@
         </is>
       </c>
       <c r="C145" s="4" t="n">
-        <v>8.92</v>
+        <v>220.36</v>
       </c>
       <c r="D145" s="4" t="n">
-        <v>49.13</v>
+        <v>55.42</v>
       </c>
       <c r="E145" s="4" t="n">
-        <v>44.18</v>
+        <v>49.97</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>46.66</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>DATAMATICS</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -5298,22 +5498,22 @@
         </is>
       </c>
       <c r="C146" s="4" t="n">
-        <v>543</v>
+        <v>801.5</v>
       </c>
       <c r="D146" s="4" t="n">
-        <v>49.12</v>
+        <v>55.34</v>
       </c>
       <c r="E146" s="4" t="n">
-        <v>44.43</v>
+        <v>54.04</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>44.92</v>
+        <v>55.52</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>DYNAMATECH</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -5322,22 +5522,22 @@
         </is>
       </c>
       <c r="C147" s="4" t="n">
-        <v>434.9</v>
+        <v>10923</v>
       </c>
       <c r="D147" s="4" t="n">
-        <v>49.04</v>
+        <v>55.03</v>
       </c>
       <c r="E147" s="4" t="n">
-        <v>48.36</v>
+        <v>55.54</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>56.36</v>
+        <v>66.36</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>NFL</t>
+          <t>EUREKAFORB</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -5346,22 +5546,22 @@
         </is>
       </c>
       <c r="C148" s="4" t="n">
-        <v>75.04000000000001</v>
+        <v>468.75</v>
       </c>
       <c r="D148" s="4" t="n">
-        <v>49.02</v>
+        <v>55.03</v>
       </c>
       <c r="E148" s="4" t="n">
-        <v>43.9</v>
+        <v>43.95</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>44.51</v>
+        <v>42.89</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>NETWORK18</t>
+          <t>ADVENZYMES</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -5370,22 +5570,22 @@
         </is>
       </c>
       <c r="C149" s="4" t="n">
-        <v>31.51</v>
+        <v>373.7</v>
       </c>
       <c r="D149" s="4" t="n">
-        <v>48.99</v>
+        <v>54.95</v>
       </c>
       <c r="E149" s="4" t="n">
-        <v>37.85</v>
+        <v>66.68000000000001</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>35.97</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>INDIAGLYCO</t>
+          <t>V2RETAIL</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -5394,22 +5594,22 @@
         </is>
       </c>
       <c r="C150" s="4" t="n">
-        <v>986.65</v>
+        <v>236.85</v>
       </c>
       <c r="D150" s="4" t="n">
-        <v>48.96</v>
+        <v>54.89</v>
       </c>
       <c r="E150" s="4" t="n">
-        <v>52.77</v>
+        <v>58.86</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>59.25</v>
+        <v>68.37</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>SHAREINDIA</t>
+          <t>SUBROS</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -5418,22 +5618,22 @@
         </is>
       </c>
       <c r="C151" s="4" t="n">
-        <v>136.38</v>
+        <v>747.45</v>
       </c>
       <c r="D151" s="4" t="n">
-        <v>48.88</v>
+        <v>54.87</v>
       </c>
       <c r="E151" s="4" t="n">
-        <v>44.71</v>
+        <v>47.14</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>39.87</v>
+        <v>51.21</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>FINPIPE</t>
+          <t>BANCOINDIA</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -5442,22 +5642,22 @@
         </is>
       </c>
       <c r="C152" s="4" t="n">
-        <v>173.02</v>
+        <v>663.05</v>
       </c>
       <c r="D152" s="4" t="n">
-        <v>48.88</v>
+        <v>54.84</v>
       </c>
       <c r="E152" s="4" t="n">
-        <v>47.55</v>
+        <v>55.08</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>44.48</v>
+        <v>59.32</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>MAHSCOOTER</t>
+          <t>TEXRAIL</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -5466,22 +5666,22 @@
         </is>
       </c>
       <c r="C153" s="4" t="n">
-        <v>12335</v>
+        <v>109.29</v>
       </c>
       <c r="D153" s="4" t="n">
-        <v>48.84</v>
+        <v>54.82</v>
       </c>
       <c r="E153" s="4" t="n">
-        <v>45</v>
+        <v>48.03</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>53.09</v>
+        <v>43.86</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>ASHOKA</t>
+          <t>WESTLIFE</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -5490,22 +5690,22 @@
         </is>
       </c>
       <c r="C154" s="4" t="n">
-        <v>123.06</v>
+        <v>467.1</v>
       </c>
       <c r="D154" s="4" t="n">
-        <v>48.55</v>
+        <v>54.81</v>
       </c>
       <c r="E154" s="4" t="n">
-        <v>38.27</v>
+        <v>43.01</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>42.11</v>
+        <v>32.34</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>GAEL</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -5514,22 +5714,22 @@
         </is>
       </c>
       <c r="C155" s="4" t="n">
-        <v>189.2</v>
+        <v>159.98</v>
       </c>
       <c r="D155" s="4" t="n">
-        <v>48.45</v>
+        <v>54.36</v>
       </c>
       <c r="E155" s="4" t="n">
-        <v>55.16</v>
+        <v>62.78</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>57.97</v>
+        <v>63.49</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>FEDFINA</t>
+          <t>DBREALTY</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -5538,22 +5738,22 @@
         </is>
       </c>
       <c r="C156" s="4" t="n">
-        <v>152.79</v>
+        <v>118.12</v>
       </c>
       <c r="D156" s="4" t="n">
-        <v>48.42</v>
+        <v>54.34</v>
       </c>
       <c r="E156" s="4" t="n">
-        <v>56.49</v>
+        <v>50.04</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>58.15</v>
+        <v>45.31</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENT</t>
+          <t>TIMETECHNO</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -5562,22 +5762,22 @@
         </is>
       </c>
       <c r="C157" s="4" t="n">
-        <v>66.93000000000001</v>
+        <v>178.42</v>
       </c>
       <c r="D157" s="4" t="n">
-        <v>48.37</v>
+        <v>54.1</v>
       </c>
       <c r="E157" s="4" t="n">
-        <v>55.29</v>
+        <v>47.37</v>
       </c>
       <c r="F157" s="4" t="n">
-        <v>54.98</v>
+        <v>50.95</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>PICCADIL</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -5586,22 +5786,22 @@
         </is>
       </c>
       <c r="C158" s="4" t="n">
-        <v>580.95</v>
+        <v>443.1</v>
       </c>
       <c r="D158" s="4" t="n">
-        <v>48.19</v>
+        <v>53.97</v>
       </c>
       <c r="E158" s="4" t="n">
-        <v>48.94</v>
+        <v>50.3</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v/>
+        <v>57.27</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>GPPL</t>
+          <t>JUSTDIAL</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -5610,22 +5810,22 @@
         </is>
       </c>
       <c r="C159" s="4" t="n">
-        <v>153.88</v>
+        <v>539.9</v>
       </c>
       <c r="D159" s="4" t="n">
-        <v>48.13</v>
+        <v>53.95</v>
       </c>
       <c r="E159" s="4" t="n">
-        <v>45.2</v>
+        <v>38.61</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>50.14</v>
+        <v>35.89</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>ANUP</t>
+          <t>MAHSEAMLES</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -5634,22 +5834,22 @@
         </is>
       </c>
       <c r="C160" s="4" t="n">
-        <v>1901.1</v>
+        <v>630.65</v>
       </c>
       <c r="D160" s="4" t="n">
-        <v>48.09</v>
+        <v>53.85</v>
       </c>
       <c r="E160" s="4" t="n">
-        <v>46.83</v>
+        <v>58.93</v>
       </c>
       <c r="F160" s="4" t="n">
-        <v>47.04</v>
+        <v>52.16</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>MAHSEAMLES</t>
+          <t>MAHSCOOTER</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -5658,22 +5858,22 @@
         </is>
       </c>
       <c r="C161" s="4" t="n">
-        <v>617.1</v>
+        <v>12597</v>
       </c>
       <c r="D161" s="4" t="n">
-        <v>47.87</v>
+        <v>53.71</v>
       </c>
       <c r="E161" s="4" t="n">
-        <v>55.19</v>
+        <v>47.17</v>
       </c>
       <c r="F161" s="4" t="n">
-        <v>50.97</v>
+        <v>54.33</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>SUBROS</t>
+          <t>DBL</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -5682,22 +5882,22 @@
         </is>
       </c>
       <c r="C162" s="4" t="n">
-        <v>721.55</v>
+        <v>439.5</v>
       </c>
       <c r="D162" s="4" t="n">
-        <v>47.59</v>
+        <v>53.32</v>
       </c>
       <c r="E162" s="4" t="n">
-        <v>43.56</v>
+        <v>48.7</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>49.98</v>
+        <v>49.85</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>STAR</t>
+          <t>AXISCADES</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -5706,22 +5906,22 @@
         </is>
       </c>
       <c r="C163" s="4" t="n">
-        <v>1055.5</v>
+        <v>1943.2</v>
       </c>
       <c r="D163" s="4" t="n">
-        <v>47.55</v>
+        <v>53.23</v>
       </c>
       <c r="E163" s="4" t="n">
-        <v>57.49</v>
+        <v>61.21</v>
       </c>
       <c r="F163" s="4" t="n">
-        <v>58.24</v>
+        <v>69.53</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>ORIENTCEM</t>
+          <t>UTLSOLAR</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -5730,22 +5930,22 @@
         </is>
       </c>
       <c r="C164" s="4" t="n">
-        <v>134.77</v>
+        <v>311</v>
       </c>
       <c r="D164" s="4" t="n">
-        <v>47.51</v>
+        <v>53.19</v>
       </c>
       <c r="E164" s="4" t="n">
-        <v>35.11</v>
+        <v>67.61</v>
       </c>
       <c r="F164" s="4" t="n">
-        <v>35.41</v>
+        <v/>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>EMBDL</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -5754,22 +5954,22 @@
         </is>
       </c>
       <c r="C165" s="4" t="n">
-        <v>1192.8</v>
+        <v>62.14</v>
       </c>
       <c r="D165" s="4" t="n">
-        <v>47.4</v>
+        <v>53.08</v>
       </c>
       <c r="E165" s="4" t="n">
-        <v>65.87</v>
+        <v>49.31</v>
       </c>
       <c r="F165" s="4" t="n">
-        <v>75.23</v>
+        <v>42.28</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>TIPSMUSIC</t>
+          <t>VGUARD</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -5778,22 +5978,22 @@
         </is>
       </c>
       <c r="C166" s="4" t="n">
-        <v>640.25</v>
+        <v>311.25</v>
       </c>
       <c r="D166" s="4" t="n">
-        <v>47.34</v>
+        <v>52.76</v>
       </c>
       <c r="E166" s="4" t="n">
-        <v>57.26</v>
+        <v>43.5</v>
       </c>
       <c r="F166" s="4" t="n">
-        <v>57.97</v>
+        <v>43.54</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>DBL</t>
+          <t>SUDARSCHEM</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -5802,22 +6002,22 @@
         </is>
       </c>
       <c r="C167" s="4" t="n">
-        <v>430.5</v>
+        <v>913.6</v>
       </c>
       <c r="D167" s="4" t="n">
-        <v>47.28</v>
+        <v>52.66</v>
       </c>
       <c r="E167" s="4" t="n">
-        <v>46.51</v>
+        <v>48.67</v>
       </c>
       <c r="F167" s="4" t="n">
-        <v>48.82</v>
+        <v>48.61</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>JSLL</t>
+          <t>TRANSRAILL</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -5826,22 +6026,22 @@
         </is>
       </c>
       <c r="C168" s="4" t="n">
-        <v>612.2</v>
+        <v>507.7</v>
       </c>
       <c r="D168" s="4" t="n">
-        <v>47.2</v>
+        <v>52.53</v>
       </c>
       <c r="E168" s="4" t="n">
-        <v>43.65</v>
+        <v>44.68</v>
       </c>
       <c r="F168" s="4" t="n">
-        <v>42.96</v>
+        <v>45.56</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>WEBELSOLAR</t>
+          <t>FINPIPE</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -5850,22 +6050,22 @@
         </is>
       </c>
       <c r="C169" s="4" t="n">
-        <v>103.63</v>
+        <v>175.58</v>
       </c>
       <c r="D169" s="4" t="n">
-        <v>47.13</v>
+        <v>52.24</v>
       </c>
       <c r="E169" s="4" t="n">
-        <v>54.82</v>
+        <v>49.12</v>
       </c>
       <c r="F169" s="4" t="n">
-        <v>52.9</v>
+        <v>45</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>DBREALTY</t>
+          <t>HGINFRA</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -5874,22 +6074,22 @@
         </is>
       </c>
       <c r="C170" s="4" t="n">
-        <v>111.88</v>
+        <v>582.85</v>
       </c>
       <c r="D170" s="4" t="n">
-        <v>47</v>
+        <v>52.22</v>
       </c>
       <c r="E170" s="4" t="n">
-        <v>46.93</v>
+        <v>43.18</v>
       </c>
       <c r="F170" s="4" t="n">
-        <v>44.26</v>
+        <v>37.04</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>ARVINDFASN</t>
+          <t>HERITGFOOD</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -5898,22 +6098,22 @@
         </is>
       </c>
       <c r="C171" s="4" t="n">
-        <v>450.2</v>
+        <v>330</v>
       </c>
       <c r="D171" s="4" t="n">
-        <v>46.99</v>
+        <v>52.2</v>
       </c>
       <c r="E171" s="4" t="n">
-        <v>48.38</v>
+        <v>39.75</v>
       </c>
       <c r="F171" s="4" t="n">
-        <v>49.19</v>
+        <v>43.88</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>AEQUS</t>
+          <t>SKYGOLD</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -5922,22 +6122,22 @@
         </is>
       </c>
       <c r="C172" s="4" t="n">
-        <v>182.53</v>
+        <v>509.4</v>
       </c>
       <c r="D172" s="4" t="n">
-        <v>46.97</v>
+        <v>52.17</v>
       </c>
       <c r="E172" s="4" t="n">
-        <v>59.36</v>
+        <v>63.75</v>
       </c>
       <c r="F172" s="4" t="n">
-        <v/>
+        <v>69.25</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>SUDARSCHEM</t>
+          <t>SHAREINDIA</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -5946,22 +6146,22 @@
         </is>
       </c>
       <c r="C173" s="4" t="n">
-        <v>882.15</v>
+        <v>138.9</v>
       </c>
       <c r="D173" s="4" t="n">
-        <v>46.93</v>
+        <v>52.13</v>
       </c>
       <c r="E173" s="4" t="n">
-        <v>45.79</v>
+        <v>46.5</v>
       </c>
       <c r="F173" s="4" t="n">
-        <v>47.34</v>
+        <v>40.32</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>V2RETAIL</t>
+          <t>VIPIND</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -5970,22 +6170,22 @@
         </is>
       </c>
       <c r="C174" s="4" t="n">
-        <v>223.48</v>
+        <v>317.5</v>
       </c>
       <c r="D174" s="4" t="n">
-        <v>46.91</v>
+        <v>52.12</v>
       </c>
       <c r="E174" s="4" t="n">
-        <v>54.51</v>
+        <v>43.61</v>
       </c>
       <c r="F174" s="4" t="n">
-        <v>65.02</v>
+        <v>38.22</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>LUMAXTECH</t>
+          <t>WAKEFIT</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -5994,22 +6194,22 @@
         </is>
       </c>
       <c r="C175" s="4" t="n">
-        <v>1634</v>
+        <v>127.43</v>
       </c>
       <c r="D175" s="4" t="n">
-        <v>46.89</v>
+        <v>51.94</v>
       </c>
       <c r="E175" s="4" t="n">
-        <v>52.94</v>
+        <v>36.5</v>
       </c>
       <c r="F175" s="4" t="n">
-        <v>66.5</v>
+        <v/>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>SHARDACROP</t>
+          <t>TIPSMUSIC</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -6018,22 +6218,22 @@
         </is>
       </c>
       <c r="C176" s="4" t="n">
-        <v>923.35</v>
+        <v>653</v>
       </c>
       <c r="D176" s="4" t="n">
-        <v>46.81</v>
+        <v>51.85</v>
       </c>
       <c r="E176" s="4" t="n">
-        <v>47.01</v>
+        <v>58.92</v>
       </c>
       <c r="F176" s="4" t="n">
-        <v>54.65</v>
+        <v>59.22</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>MANYAVAR</t>
+          <t>GMMPFAUDLR</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -6042,22 +6242,22 @@
         </is>
       </c>
       <c r="C177" s="4" t="n">
-        <v>407.4</v>
+        <v>809.65</v>
       </c>
       <c r="D177" s="4" t="n">
-        <v>46.78</v>
+        <v>51.7</v>
       </c>
       <c r="E177" s="4" t="n">
-        <v>36.82</v>
+        <v>37.6</v>
       </c>
       <c r="F177" s="4" t="n">
-        <v>28.31</v>
+        <v>39.25</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>EDELWEISS</t>
+          <t>IONEXCHANG</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -6066,22 +6266,22 @@
         </is>
       </c>
       <c r="C178" s="4" t="n">
-        <v>109.93</v>
+        <v>370.4</v>
       </c>
       <c r="D178" s="4" t="n">
-        <v>46.77</v>
+        <v>51.49</v>
       </c>
       <c r="E178" s="4" t="n">
-        <v>48.42</v>
+        <v>48.05</v>
       </c>
       <c r="F178" s="4" t="n">
-        <v>55.26</v>
+        <v>43.52</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>SANOFICONR</t>
+          <t>FIEMIND</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -6090,22 +6290,22 @@
         </is>
       </c>
       <c r="C179" s="4" t="n">
-        <v>4616.9</v>
+        <v>2286.7</v>
       </c>
       <c r="D179" s="4" t="n">
-        <v>46.77</v>
+        <v>51.36</v>
       </c>
       <c r="E179" s="4" t="n">
-        <v>50.63</v>
+        <v>57.07</v>
       </c>
       <c r="F179" s="4" t="n">
-        <v>47.51</v>
+        <v>67.56999999999999</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>TSFINV</t>
+          <t>TANLA</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -6114,22 +6314,22 @@
         </is>
       </c>
       <c r="C180" s="4" t="n">
-        <v>394.2</v>
+        <v>521.35</v>
       </c>
       <c r="D180" s="4" t="n">
-        <v>46.71</v>
+        <v>51.31</v>
       </c>
       <c r="E180" s="4" t="n">
-        <v>44.98</v>
+        <v>52.8</v>
       </c>
       <c r="F180" s="4" t="n">
-        <v>52.36</v>
+        <v>44.46</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>KNRCON</t>
+          <t>REDTAPE</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -6138,22 +6338,22 @@
         </is>
       </c>
       <c r="C181" s="4" t="n">
-        <v>125.17</v>
+        <v>134.13</v>
       </c>
       <c r="D181" s="4" t="n">
-        <v>46.61</v>
+        <v>51.1</v>
       </c>
       <c r="E181" s="4" t="n">
-        <v>41.78</v>
+        <v>52.93</v>
       </c>
       <c r="F181" s="4" t="n">
-        <v>33.72</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>AURIONPRO</t>
+          <t>CELLO</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -6162,22 +6362,22 @@
         </is>
       </c>
       <c r="C182" s="4" t="n">
-        <v>777.25</v>
+        <v>390.2</v>
       </c>
       <c r="D182" s="4" t="n">
-        <v>46.59</v>
+        <v>51.07</v>
       </c>
       <c r="E182" s="4" t="n">
-        <v>38.7</v>
+        <v>36.17</v>
       </c>
       <c r="F182" s="4" t="n">
-        <v>39.91</v>
+        <v>31.93</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>WAAREERTL</t>
+          <t>CRIZAC</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -6186,13 +6386,13 @@
         </is>
       </c>
       <c r="C183" s="4" t="n">
-        <v>954.15</v>
+        <v>214.59</v>
       </c>
       <c r="D183" s="4" t="n">
-        <v>46.54</v>
+        <v>50.36</v>
       </c>
       <c r="E183" s="4" t="n">
-        <v>49.51</v>
+        <v>44.49</v>
       </c>
       <c r="F183" s="4" t="n">
         <v/>
@@ -6201,7 +6401,7 @@
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>WESTLIFE</t>
+          <t>CENTURYPLY</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -6210,22 +6410,22 @@
         </is>
       </c>
       <c r="C184" s="4" t="n">
-        <v>445.85</v>
+        <v>758.5</v>
       </c>
       <c r="D184" s="4" t="n">
-        <v>46.42</v>
+        <v>50.26</v>
       </c>
       <c r="E184" s="4" t="n">
-        <v>36.83</v>
+        <v>50.36</v>
       </c>
       <c r="F184" s="4" t="n">
-        <v>29.54</v>
+        <v>51.55</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>AARTIDRUGS</t>
+          <t>CSBBANK</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -6234,22 +6434,22 @@
         </is>
       </c>
       <c r="C185" s="4" t="n">
-        <v>371.7</v>
+        <v>365.5</v>
       </c>
       <c r="D185" s="4" t="n">
-        <v>46.34</v>
+        <v>50.15</v>
       </c>
       <c r="E185" s="4" t="n">
-        <v>46.05</v>
+        <v>45.35</v>
       </c>
       <c r="F185" s="4" t="n">
-        <v>43.85</v>
+        <v>50.56</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>PURVA</t>
+          <t>SENCO</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -6258,22 +6458,22 @@
         </is>
       </c>
       <c r="C186" s="4" t="n">
-        <v>209.18</v>
+        <v>340.4</v>
       </c>
       <c r="D186" s="4" t="n">
-        <v>46.34</v>
+        <v>50.1</v>
       </c>
       <c r="E186" s="4" t="n">
-        <v>45.67</v>
+        <v>52.89</v>
       </c>
       <c r="F186" s="4" t="n">
-        <v>44.35</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>SANDUMA</t>
+          <t>SKFINDIA</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -6282,22 +6482,22 @@
         </is>
       </c>
       <c r="C187" s="4" t="n">
-        <v>215.85</v>
+        <v>1638.3</v>
       </c>
       <c r="D187" s="4" t="n">
-        <v>46.29</v>
+        <v>50.09</v>
       </c>
       <c r="E187" s="4" t="n">
-        <v>52.18</v>
+        <v>34.74</v>
       </c>
       <c r="F187" s="4" t="n">
-        <v>58.7</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>GSFC</t>
+          <t>LXCHEM</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -6306,22 +6506,22 @@
         </is>
       </c>
       <c r="C188" s="4" t="n">
-        <v>164.34</v>
+        <v>152.37</v>
       </c>
       <c r="D188" s="4" t="n">
-        <v>46.24</v>
+        <v>50</v>
       </c>
       <c r="E188" s="4" t="n">
-        <v>44.91</v>
+        <v>50.88</v>
       </c>
       <c r="F188" s="4" t="n">
-        <v>45.63</v>
+        <v>39.95</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>EIEL</t>
+          <t>GODREJAGRO</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -6330,22 +6530,22 @@
         </is>
       </c>
       <c r="C189" s="4" t="n">
-        <v>185.54</v>
+        <v>574.95</v>
       </c>
       <c r="D189" s="4" t="n">
-        <v>45.83</v>
+        <v>49.85</v>
       </c>
       <c r="E189" s="4" t="n">
-        <v>47.85</v>
+        <v>45.89</v>
       </c>
       <c r="F189" s="4" t="n">
-        <v>39.22</v>
+        <v>45.59</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>CMSINFO</t>
+          <t>AZAD</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -6354,22 +6554,22 @@
         </is>
       </c>
       <c r="C190" s="4" t="n">
-        <v>296.75</v>
+        <v>2095.2</v>
       </c>
       <c r="D190" s="4" t="n">
-        <v>45.83</v>
+        <v>49.82</v>
       </c>
       <c r="E190" s="4" t="n">
-        <v>41.12</v>
+        <v>59.91</v>
       </c>
       <c r="F190" s="4" t="n">
-        <v>38.68</v>
+        <v>62.11</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>ZAGGLE</t>
+          <t>MANYAVAR</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -6378,22 +6578,22 @@
         </is>
       </c>
       <c r="C191" s="4" t="n">
-        <v>208.8</v>
+        <v>412.5</v>
       </c>
       <c r="D191" s="4" t="n">
-        <v>45.64</v>
+        <v>49.65</v>
       </c>
       <c r="E191" s="4" t="n">
-        <v>36.73</v>
+        <v>38.23</v>
       </c>
       <c r="F191" s="4" t="n">
-        <v>39.84</v>
+        <v>28.71</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>GMRP&amp;UI</t>
+          <t>CMSINFO</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -6402,22 +6602,22 @@
         </is>
       </c>
       <c r="C192" s="4" t="n">
-        <v>105.57</v>
+        <v>298.7</v>
       </c>
       <c r="D192" s="4" t="n">
-        <v>45.57</v>
+        <v>49.58</v>
       </c>
       <c r="E192" s="4" t="n">
-        <v>47.43</v>
+        <v>42.11</v>
       </c>
       <c r="F192" s="4" t="n">
-        <v>52.62</v>
+        <v>38.91</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>GOKEX</t>
+          <t>ZAGGLE</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -6426,22 +6626,22 @@
         </is>
       </c>
       <c r="C193" s="4" t="n">
-        <v>674.5</v>
+        <v>213.17</v>
       </c>
       <c r="D193" s="4" t="n">
-        <v>45.44</v>
+        <v>49.43</v>
       </c>
       <c r="E193" s="4" t="n">
-        <v>46.43</v>
+        <v>38.18</v>
       </c>
       <c r="F193" s="4" t="n">
-        <v>46.96</v>
+        <v>40.31</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>KSCL</t>
+          <t>ETHOSLTD</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -6450,22 +6650,22 @@
         </is>
       </c>
       <c r="C194" s="4" t="n">
-        <v>878.85</v>
+        <v>2380.9</v>
       </c>
       <c r="D194" s="4" t="n">
-        <v>45.38</v>
+        <v>49.24</v>
       </c>
       <c r="E194" s="4" t="n">
-        <v>45.96</v>
+        <v>46.4</v>
       </c>
       <c r="F194" s="4" t="n">
-        <v>47.65</v>
+        <v>48.29</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>RTNPOWER</t>
+          <t>LUMAXTECH</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -6474,22 +6674,22 @@
         </is>
       </c>
       <c r="C195" s="4" t="n">
-        <v>9.24</v>
+        <v>1646.4</v>
       </c>
       <c r="D195" s="4" t="n">
-        <v>45.28</v>
+        <v>48.71</v>
       </c>
       <c r="E195" s="4" t="n">
-        <v>47.83</v>
+        <v>53.47</v>
       </c>
       <c r="F195" s="4" t="n">
-        <v>46.84</v>
+        <v>66.97</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>CAMPUS</t>
+          <t>HEMIPROP</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -6498,22 +6698,22 @@
         </is>
       </c>
       <c r="C196" s="4" t="n">
-        <v>238.4</v>
+        <v>139.55</v>
       </c>
       <c r="D196" s="4" t="n">
-        <v>44.99</v>
+        <v>48.69</v>
       </c>
       <c r="E196" s="4" t="n">
-        <v>44.23</v>
+        <v>51.25</v>
       </c>
       <c r="F196" s="4" t="n">
-        <v>43.66</v>
+        <v>49.3</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>IMFA</t>
+          <t>ORIENTCEM</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -6522,22 +6722,22 @@
         </is>
       </c>
       <c r="C197" s="4" t="n">
-        <v>1398.9</v>
+        <v>135.51</v>
       </c>
       <c r="D197" s="4" t="n">
-        <v>44.94</v>
+        <v>48.65</v>
       </c>
       <c r="E197" s="4" t="n">
-        <v>53.31</v>
+        <v>35.88</v>
       </c>
       <c r="F197" s="4" t="n">
-        <v>65.08</v>
+        <v>35.51</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>SUNTECK</t>
+          <t>FEDFINA</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -6546,22 +6746,22 @@
         </is>
       </c>
       <c r="C198" s="4" t="n">
-        <v>287.35</v>
+        <v>154.57</v>
       </c>
       <c r="D198" s="4" t="n">
-        <v>44.91</v>
+        <v>48.6</v>
       </c>
       <c r="E198" s="4" t="n">
-        <v>35.42</v>
+        <v>57.79</v>
       </c>
       <c r="F198" s="4" t="n">
-        <v>38.85</v>
+        <v>58.93</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>LOTUSDEV</t>
+          <t>RTNPOWER</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -6570,22 +6770,22 @@
         </is>
       </c>
       <c r="C199" s="4" t="n">
-        <v>134.04</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="D199" s="4" t="n">
-        <v>44.65</v>
+        <v>48.57</v>
       </c>
       <c r="E199" s="4" t="n">
-        <v>40.98</v>
+        <v>49.11</v>
       </c>
       <c r="F199" s="4" t="n">
-        <v/>
+        <v>47.22</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>CAPILLARY</t>
+          <t>WEBELSOLAR</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -6594,22 +6794,22 @@
         </is>
       </c>
       <c r="C200" s="4" t="n">
-        <v>508.05</v>
+        <v>104.71</v>
       </c>
       <c r="D200" s="4" t="n">
-        <v>44.5</v>
+        <v>48.55</v>
       </c>
       <c r="E200" s="4" t="n">
-        <v>38.92</v>
+        <v>55.43</v>
       </c>
       <c r="F200" s="4" t="n">
-        <v/>
+        <v>53.2</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>GSFC</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -6618,22 +6818,22 @@
         </is>
       </c>
       <c r="C201" s="4" t="n">
-        <v>641.15</v>
+        <v>165.44</v>
       </c>
       <c r="D201" s="4" t="n">
-        <v>44.18</v>
+        <v>48.5</v>
       </c>
       <c r="E201" s="4" t="n">
-        <v>41.32</v>
+        <v>45.91</v>
       </c>
       <c r="F201" s="4" t="n">
-        <v>48.03</v>
+        <v>45.96</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>BIRLACORPN</t>
+          <t>PCJEWELLER</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -6642,22 +6842,22 @@
         </is>
       </c>
       <c r="C202" s="4" t="n">
-        <v>951.1</v>
+        <v>8.91</v>
       </c>
       <c r="D202" s="4" t="n">
-        <v>43.99</v>
+        <v>48.47</v>
       </c>
       <c r="E202" s="4" t="n">
-        <v>44.82</v>
+        <v>44.11</v>
       </c>
       <c r="F202" s="4" t="n">
-        <v>41.8</v>
+        <v>46.63</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>TIMETECHNO</t>
+          <t>JKLAKSHMI</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -6666,22 +6866,22 @@
         </is>
       </c>
       <c r="C203" s="4" t="n">
-        <v>169.48</v>
+        <v>605.5</v>
       </c>
       <c r="D203" s="4" t="n">
-        <v>43.9</v>
+        <v>48.31</v>
       </c>
       <c r="E203" s="4" t="n">
-        <v>42.02</v>
+        <v>38.83</v>
       </c>
       <c r="F203" s="4" t="n">
-        <v>48.93</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>PFOCUS</t>
+          <t>IMFA</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -6690,22 +6890,22 @@
         </is>
       </c>
       <c r="C204" s="4" t="n">
-        <v>239.27</v>
+        <v>1429.1</v>
       </c>
       <c r="D204" s="4" t="n">
-        <v>43.84</v>
+        <v>48.17</v>
       </c>
       <c r="E204" s="4" t="n">
-        <v>45.72</v>
+        <v>54.93</v>
       </c>
       <c r="F204" s="4" t="n">
-        <v>59.51</v>
+        <v>66.44</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>HGINFRA</t>
+          <t>RTNINDIA</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -6714,22 +6914,22 @@
         </is>
       </c>
       <c r="C205" s="4" t="n">
-        <v>562.9</v>
+        <v>35.07</v>
       </c>
       <c r="D205" s="4" t="n">
-        <v>43.78</v>
+        <v>47.99</v>
       </c>
       <c r="E205" s="4" t="n">
-        <v>40.18</v>
+        <v>47.46</v>
       </c>
       <c r="F205" s="4" t="n">
-        <v>36.42</v>
+        <v>41.81</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>PRICOLLTD</t>
+          <t>SHAILY</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -6738,22 +6938,22 @@
         </is>
       </c>
       <c r="C206" s="4" t="n">
-        <v>550.5</v>
+        <v>2803.8</v>
       </c>
       <c r="D206" s="4" t="n">
-        <v>43.73</v>
+        <v>47.87</v>
       </c>
       <c r="E206" s="4" t="n">
-        <v>46.56</v>
+        <v>60.25</v>
       </c>
       <c r="F206" s="4" t="n">
-        <v>55.81</v>
+        <v>67.55</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>TARC</t>
+          <t>PICCADIL</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -6762,22 +6962,22 @@
         </is>
       </c>
       <c r="C207" s="4" t="n">
-        <v>125.33</v>
+        <v>579</v>
       </c>
       <c r="D207" s="4" t="n">
-        <v>43.62</v>
+        <v>47.78</v>
       </c>
       <c r="E207" s="4" t="n">
-        <v>39.84</v>
+        <v>48.51</v>
       </c>
       <c r="F207" s="4" t="n">
-        <v>45.28</v>
+        <v/>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>MOIL</t>
+          <t>STARCEMENT</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -6786,22 +6986,22 @@
         </is>
       </c>
       <c r="C208" s="4" t="n">
-        <v>291.9</v>
+        <v>213.25</v>
       </c>
       <c r="D208" s="4" t="n">
-        <v>43.59</v>
+        <v>47.6</v>
       </c>
       <c r="E208" s="4" t="n">
-        <v>43.46</v>
+        <v>45.99</v>
       </c>
       <c r="F208" s="4" t="n">
-        <v>46.56</v>
+        <v>50.58</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>GODREJAGRO</t>
+          <t>PRICOLLTD</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -6810,22 +7010,22 @@
         </is>
       </c>
       <c r="C209" s="4" t="n">
-        <v>564.95</v>
+        <v>559.15</v>
       </c>
       <c r="D209" s="4" t="n">
-        <v>43.53</v>
+        <v>47.49</v>
       </c>
       <c r="E209" s="4" t="n">
-        <v>43.56</v>
+        <v>48.14</v>
       </c>
       <c r="F209" s="4" t="n">
-        <v>44.87</v>
+        <v>56.69</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>TSFINV</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -6834,22 +7034,22 @@
         </is>
       </c>
       <c r="C210" s="4" t="n">
-        <v>429.35</v>
+        <v>395.4</v>
       </c>
       <c r="D210" s="4" t="n">
-        <v>43.46</v>
+        <v>47.38</v>
       </c>
       <c r="E210" s="4" t="n">
-        <v>44.27</v>
+        <v>45.29</v>
       </c>
       <c r="F210" s="4" t="n">
-        <v>50.05</v>
+        <v>52.47</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>JKPAPER</t>
+          <t>ORKLAINDIA</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -6858,22 +7058,22 @@
         </is>
       </c>
       <c r="C211" s="4" t="n">
-        <v>353.35</v>
+        <v>619.1</v>
       </c>
       <c r="D211" s="4" t="n">
-        <v>43.39</v>
+        <v>47.21</v>
       </c>
       <c r="E211" s="4" t="n">
-        <v>47.72</v>
+        <v>49.03</v>
       </c>
       <c r="F211" s="4" t="n">
-        <v>49.13</v>
+        <v/>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>ENTERO</t>
+          <t>KANSAINER</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -6882,22 +7082,22 @@
         </is>
       </c>
       <c r="C212" s="4" t="n">
-        <v>1136.7</v>
+        <v>211.13</v>
       </c>
       <c r="D212" s="4" t="n">
-        <v>43.33</v>
+        <v>47.18</v>
       </c>
       <c r="E212" s="4" t="n">
-        <v>47.75</v>
+        <v>49.54</v>
       </c>
       <c r="F212" s="4" t="n">
-        <v>49.08</v>
+        <v>42.21</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>DYNAMATECH</t>
+          <t>KPIGREEN</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -6906,22 +7106,22 @@
         </is>
       </c>
       <c r="C213" s="4" t="n">
-        <v>10171</v>
+        <v>409.15</v>
       </c>
       <c r="D213" s="4" t="n">
-        <v>43.3</v>
+        <v>47.17</v>
       </c>
       <c r="E213" s="4" t="n">
-        <v>51.2</v>
+        <v>46.98</v>
       </c>
       <c r="F213" s="4" t="n">
-        <v>61.5</v>
+        <v>49.15</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>HERITGFOOD</t>
+          <t>NESCO</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -6930,22 +7130,22 @@
         </is>
       </c>
       <c r="C214" s="4" t="n">
-        <v>320</v>
+        <v>1138</v>
       </c>
       <c r="D214" s="4" t="n">
-        <v>43.28</v>
+        <v>47.13</v>
       </c>
       <c r="E214" s="4" t="n">
-        <v>35.53</v>
+        <v>47.36</v>
       </c>
       <c r="F214" s="4" t="n">
-        <v>42.7</v>
+        <v>53.82</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>BALUFORGE</t>
+          <t>GHCL</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -6954,22 +7154,22 @@
         </is>
       </c>
       <c r="C215" s="4" t="n">
-        <v>448.8</v>
+        <v>435.4</v>
       </c>
       <c r="D215" s="4" t="n">
-        <v>42.9</v>
+        <v>46.93</v>
       </c>
       <c r="E215" s="4" t="n">
-        <v>42.6</v>
+        <v>39.56</v>
       </c>
       <c r="F215" s="4" t="n">
-        <v>46.06</v>
+        <v>42.16</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>KPIGREEN</t>
+          <t>RENUKA</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -6978,22 +7178,22 @@
         </is>
       </c>
       <c r="C216" s="4" t="n">
-        <v>401.4</v>
+        <v>23.09</v>
       </c>
       <c r="D216" s="4" t="n">
-        <v>42.86</v>
+        <v>46.48</v>
       </c>
       <c r="E216" s="4" t="n">
-        <v>45.29</v>
+        <v>39.88</v>
       </c>
       <c r="F216" s="4" t="n">
-        <v>48.58</v>
+        <v>37.3</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>PNGJL</t>
+          <t>CAMPUS</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -7002,22 +7202,22 @@
         </is>
       </c>
       <c r="C217" s="4" t="n">
-        <v>547.55</v>
+        <v>237.45</v>
       </c>
       <c r="D217" s="4" t="n">
-        <v>42.76</v>
+        <v>46.29</v>
       </c>
       <c r="E217" s="4" t="n">
-        <v>44.33</v>
+        <v>43.79</v>
       </c>
       <c r="F217" s="4" t="n">
-        <v>42.19</v>
+        <v>43.51</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>CRIZAC</t>
+          <t>MASTEK</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -7026,22 +7226,22 @@
         </is>
       </c>
       <c r="C218" s="4" t="n">
-        <v>205.96</v>
+        <v>1605.5</v>
       </c>
       <c r="D218" s="4" t="n">
-        <v>42.29</v>
+        <v>46.28</v>
       </c>
       <c r="E218" s="4" t="n">
-        <v>40.73</v>
+        <v>40.92</v>
       </c>
       <c r="F218" s="4" t="n">
-        <v/>
+        <v>39.29</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>CELLO</t>
+          <t>GPPL</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -7050,22 +7250,22 @@
         </is>
       </c>
       <c r="C219" s="4" t="n">
-        <v>377.3</v>
+        <v>153.08</v>
       </c>
       <c r="D219" s="4" t="n">
-        <v>42</v>
+        <v>46.25</v>
       </c>
       <c r="E219" s="4" t="n">
-        <v>31.9</v>
+        <v>44.6</v>
       </c>
       <c r="F219" s="4" t="n">
-        <v>30.37</v>
+        <v>49.89</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>MASTEK</t>
+          <t>AARTIDRUGS</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -7074,22 +7274,22 @@
         </is>
       </c>
       <c r="C220" s="4" t="n">
-        <v>1577.4</v>
+        <v>370.35</v>
       </c>
       <c r="D220" s="4" t="n">
-        <v>41.89</v>
+        <v>46.08</v>
       </c>
       <c r="E220" s="4" t="n">
-        <v>38.91</v>
+        <v>45.65</v>
       </c>
       <c r="F220" s="4" t="n">
-        <v>38.83</v>
+        <v>43.72</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>AWFIS</t>
+          <t>JSFB</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -7098,22 +7298,22 @@
         </is>
       </c>
       <c r="C221" s="4" t="n">
-        <v>303.05</v>
+        <v>460.1</v>
       </c>
       <c r="D221" s="4" t="n">
-        <v>41.39</v>
+        <v>45.97</v>
       </c>
       <c r="E221" s="4" t="n">
-        <v>38.24</v>
+        <v>55.43</v>
       </c>
       <c r="F221" s="4" t="n">
-        <v>32.18</v>
+        <v>51.07</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>PNCINFRA</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -7122,22 +7322,22 @@
         </is>
       </c>
       <c r="C222" s="4" t="n">
-        <v>201.62</v>
+        <v>186.65</v>
       </c>
       <c r="D222" s="4" t="n">
-        <v>41.02</v>
+        <v>45.84</v>
       </c>
       <c r="E222" s="4" t="n">
-        <v>41.51</v>
+        <v>53.78</v>
       </c>
       <c r="F222" s="4" t="n">
-        <v>38.54</v>
+        <v>57.37</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>VGUARD</t>
+          <t>MOIL</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -7146,22 +7346,22 @@
         </is>
       </c>
       <c r="C223" s="4" t="n">
-        <v>299.15</v>
+        <v>293.85</v>
       </c>
       <c r="D223" s="4" t="n">
-        <v>40.95</v>
+        <v>45.63</v>
       </c>
       <c r="E223" s="4" t="n">
-        <v>35.89</v>
+        <v>44.18</v>
       </c>
       <c r="F223" s="4" t="n">
-        <v>41.18</v>
+        <v>46.82</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>STYRENIX</t>
+          <t>BAJAJELEC</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -7170,22 +7370,22 @@
         </is>
       </c>
       <c r="C224" s="4" t="n">
-        <v>2133</v>
+        <v>325.65</v>
       </c>
       <c r="D224" s="4" t="n">
-        <v>40.83</v>
+        <v>45.52</v>
       </c>
       <c r="E224" s="4" t="n">
-        <v>48.84</v>
+        <v>33.03</v>
       </c>
       <c r="F224" s="4" t="n">
-        <v>50.56</v>
+        <v>28.87</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>EMIL</t>
+          <t>TARC</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -7194,22 +7394,22 @@
         </is>
       </c>
       <c r="C225" s="4" t="n">
-        <v>105.5</v>
+        <v>126.18</v>
       </c>
       <c r="D225" s="4" t="n">
-        <v>40.06</v>
+        <v>45.01</v>
       </c>
       <c r="E225" s="4" t="n">
-        <v>46.03</v>
+        <v>40.62</v>
       </c>
       <c r="F225" s="4" t="n">
-        <v>43.65</v>
+        <v>45.46</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>SKFINDIA</t>
+          <t>PNGJL</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -7218,22 +7418,22 @@
         </is>
       </c>
       <c r="C226" s="4" t="n">
-        <v>1589.3</v>
+        <v>552.8</v>
       </c>
       <c r="D226" s="4" t="n">
-        <v>39.97</v>
+        <v>44.84</v>
       </c>
       <c r="E226" s="4" t="n">
-        <v>30.97</v>
+        <v>45.06</v>
       </c>
       <c r="F226" s="4" t="n">
-        <v>31.76</v>
+        <v>42.89</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>CCAVENUE</t>
+          <t>PRSMJOHNSN</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -7242,22 +7442,22 @@
         </is>
       </c>
       <c r="C227" s="4" t="n">
-        <v>13.5</v>
+        <v>119.26</v>
       </c>
       <c r="D227" s="4" t="n">
-        <v>39.97</v>
+        <v>44.27</v>
       </c>
       <c r="E227" s="4" t="n">
-        <v>39.2</v>
+        <v>39.57</v>
       </c>
       <c r="F227" s="4" t="n">
-        <v>37.9</v>
+        <v>41.83</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>ALOKINDS</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -7266,22 +7466,22 @@
         </is>
       </c>
       <c r="C228" s="4" t="n">
-        <v>12.16</v>
+        <v>527.75</v>
       </c>
       <c r="D228" s="4" t="n">
-        <v>39.78</v>
+        <v>43.85</v>
       </c>
       <c r="E228" s="4" t="n">
-        <v>36.17</v>
+        <v>41.85</v>
       </c>
       <c r="F228" s="4" t="n">
-        <v>37.49</v>
+        <v>43.38</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>IONEXCHANG</t>
+          <t>JAIBALAJI</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -7290,22 +7490,22 @@
         </is>
       </c>
       <c r="C229" s="4" t="n">
-        <v>345.6</v>
+        <v>67.97</v>
       </c>
       <c r="D229" s="4" t="n">
-        <v>39.76</v>
+        <v>43.84</v>
       </c>
       <c r="E229" s="4" t="n">
-        <v>40.89</v>
+        <v>45.56</v>
       </c>
       <c r="F229" s="4" t="n">
-        <v>41.22</v>
+        <v>41.03</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>PRSMJOHNSN</t>
+          <t>BALUFORGE</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -7314,22 +7514,22 @@
         </is>
       </c>
       <c r="C230" s="4" t="n">
-        <v>117.89</v>
+        <v>448.75</v>
       </c>
       <c r="D230" s="4" t="n">
-        <v>39.54</v>
+        <v>43.41</v>
       </c>
       <c r="E230" s="4" t="n">
-        <v>37.58</v>
+        <v>42.6</v>
       </c>
       <c r="F230" s="4" t="n">
-        <v>41.42</v>
+        <v>46.06</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>JAYNECOIND</t>
+          <t>SHARDACROP</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -7338,22 +7538,22 @@
         </is>
       </c>
       <c r="C231" s="4" t="n">
-        <v>90.86</v>
+        <v>900.8</v>
       </c>
       <c r="D231" s="4" t="n">
-        <v>38.99</v>
+        <v>43.38</v>
       </c>
       <c r="E231" s="4" t="n">
-        <v>53.32</v>
+        <v>45.58</v>
       </c>
       <c r="F231" s="4" t="n">
-        <v>61.55</v>
+        <v>53.96</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>RENUKA</t>
+          <t>VIKRAMSOLR</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -7362,22 +7562,22 @@
         </is>
       </c>
       <c r="C232" s="4" t="n">
-        <v>22.29</v>
+        <v>200.42</v>
       </c>
       <c r="D232" s="4" t="n">
-        <v>38.34</v>
+        <v>43.1</v>
       </c>
       <c r="E232" s="4" t="n">
-        <v>36.01</v>
+        <v>41.65</v>
       </c>
       <c r="F232" s="4" t="n">
-        <v>36.35</v>
+        <v/>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>ELECTCAST</t>
+          <t>SANDUMA</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -7386,22 +7586,22 @@
         </is>
       </c>
       <c r="C233" s="4" t="n">
-        <v>71.87</v>
+        <v>211.72</v>
       </c>
       <c r="D233" s="4" t="n">
-        <v>38.33</v>
+        <v>43.09</v>
       </c>
       <c r="E233" s="4" t="n">
-        <v>42.49</v>
+        <v>50.57</v>
       </c>
       <c r="F233" s="4" t="n">
-        <v>41.08</v>
+        <v>57.71</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>GHCL</t>
+          <t>GOKULAGRO</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -7410,22 +7610,22 @@
         </is>
       </c>
       <c r="C234" s="4" t="n">
-        <v>430.45</v>
+        <v>221.77</v>
       </c>
       <c r="D234" s="4" t="n">
-        <v>38.3</v>
+        <v>43.04</v>
       </c>
       <c r="E234" s="4" t="n">
-        <v>34.77</v>
+        <v>59.29</v>
       </c>
       <c r="F234" s="4" t="n">
-        <v>41.03</v>
+        <v>65.98</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>TRANSRAILL</t>
+          <t>INDIAGLYCO</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -7434,22 +7634,22 @@
         </is>
       </c>
       <c r="C235" s="4" t="n">
-        <v>478.1</v>
+        <v>957.75</v>
       </c>
       <c r="D235" s="4" t="n">
-        <v>38.18</v>
+        <v>42.28</v>
       </c>
       <c r="E235" s="4" t="n">
-        <v>39.63</v>
+        <v>49.97</v>
       </c>
       <c r="F235" s="4" t="n">
-        <v>43.21</v>
+        <v>57.98</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>HAPPSTMNDS</t>
+          <t>AWFIS</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -7458,22 +7658,22 @@
         </is>
       </c>
       <c r="C236" s="4" t="n">
-        <v>349.95</v>
+        <v>304.1</v>
       </c>
       <c r="D236" s="4" t="n">
-        <v>37.42</v>
+        <v>42.18</v>
       </c>
       <c r="E236" s="4" t="n">
-        <v>35.67</v>
+        <v>38.47</v>
       </c>
       <c r="F236" s="4" t="n">
-        <v>24.51</v>
+        <v>32.24</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>JKLAKSHMI</t>
+          <t>PFOCUS</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -7482,22 +7682,22 @@
         </is>
       </c>
       <c r="C237" s="4" t="n">
-        <v>588.85</v>
+        <v>231.72</v>
       </c>
       <c r="D237" s="4" t="n">
-        <v>37.37</v>
+        <v>41.78</v>
       </c>
       <c r="E237" s="4" t="n">
-        <v>35.37</v>
+        <v>43.84</v>
       </c>
       <c r="F237" s="4" t="n">
-        <v>40.01</v>
+        <v>58.46</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>EUREKAFORB</t>
+          <t>JKPAPER</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -7506,22 +7706,22 @@
         </is>
       </c>
       <c r="C238" s="4" t="n">
-        <v>438.25</v>
+        <v>349.9</v>
       </c>
       <c r="D238" s="4" t="n">
-        <v>37</v>
+        <v>41.52</v>
       </c>
       <c r="E238" s="4" t="n">
-        <v>36.37</v>
+        <v>46.49</v>
       </c>
       <c r="F238" s="4" t="n">
-        <v>39.46</v>
+        <v>48.7</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>JAIBALAJI</t>
+          <t>HCG</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
@@ -7530,22 +7730,22 @@
         </is>
       </c>
       <c r="C239" s="4" t="n">
-        <v>65.84999999999999</v>
+        <v>610.95</v>
       </c>
       <c r="D239" s="4" t="n">
-        <v>36.76</v>
+        <v>41.46</v>
       </c>
       <c r="E239" s="4" t="n">
-        <v>43.58</v>
+        <v>50.2</v>
       </c>
       <c r="F239" s="4" t="n">
-        <v>40.56</v>
+        <v>57.01</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>ORKLAINDIA</t>
+          <t>PRAJIND</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -7554,22 +7754,22 @@
         </is>
       </c>
       <c r="C240" s="4" t="n">
-        <v>604.45</v>
+        <v>340.5</v>
       </c>
       <c r="D240" s="4" t="n">
-        <v>36.59</v>
+        <v>40.86</v>
       </c>
       <c r="E240" s="4" t="n">
-        <v>44.92</v>
+        <v>47.1</v>
       </c>
       <c r="F240" s="4" t="n">
-        <v/>
+        <v>42.55</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>GMMPFAUDLR</t>
+          <t>JSLL</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
@@ -7578,22 +7778,22 @@
         </is>
       </c>
       <c r="C241" s="4" t="n">
-        <v>760.1</v>
+        <v>557.2</v>
       </c>
       <c r="D241" s="4" t="n">
-        <v>36.55</v>
+        <v>40.52</v>
       </c>
       <c r="E241" s="4" t="n">
-        <v>29.83</v>
+        <v>39.49</v>
       </c>
       <c r="F241" s="4" t="n">
-        <v>37.34</v>
+        <v>41.83</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>RALLIS</t>
+          <t>MEDPLUS</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -7602,22 +7802,22 @@
         </is>
       </c>
       <c r="C242" s="4" t="n">
-        <v>228.77</v>
+        <v>844.45</v>
       </c>
       <c r="D242" s="4" t="n">
-        <v>36.49</v>
+        <v>40.17</v>
       </c>
       <c r="E242" s="4" t="n">
-        <v>40.09</v>
+        <v>48.17</v>
       </c>
       <c r="F242" s="4" t="n">
-        <v>44.56</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>WAKEFIT</t>
+          <t>JAYNECOIND</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -7626,22 +7826,22 @@
         </is>
       </c>
       <c r="C243" s="4" t="n">
-        <v>114.76</v>
+        <v>89.68000000000001</v>
       </c>
       <c r="D243" s="4" t="n">
-        <v>36.02</v>
+        <v>40.06</v>
       </c>
       <c r="E243" s="4" t="n">
-        <v>27.48</v>
+        <v>52.33</v>
       </c>
       <c r="F243" s="4" t="n">
-        <v/>
+        <v>60.98</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>AGARWALEYE</t>
+          <t>RALLIS</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -7650,22 +7850,22 @@
         </is>
       </c>
       <c r="C244" s="4" t="n">
-        <v>439.75</v>
+        <v>229.78</v>
       </c>
       <c r="D244" s="4" t="n">
-        <v>35.5</v>
+        <v>39.25</v>
       </c>
       <c r="E244" s="4" t="n">
-        <v>45.34</v>
+        <v>40.55</v>
       </c>
       <c r="F244" s="4" t="n">
-        <v>48.54</v>
+        <v>44.69</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>PRAJIND</t>
+          <t>JYOTHYLAB</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
@@ -7674,22 +7874,22 @@
         </is>
       </c>
       <c r="C245" s="4" t="n">
-        <v>332.1</v>
+        <v>202.28</v>
       </c>
       <c r="D245" s="4" t="n">
-        <v>34.76</v>
+        <v>37.89</v>
       </c>
       <c r="E245" s="4" t="n">
-        <v>44.88</v>
+        <v>33.57</v>
       </c>
       <c r="F245" s="4" t="n">
-        <v>42</v>
+        <v>36.52</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>NESCO</t>
+          <t>CAPILLARY</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -7698,22 +7898,22 @@
         </is>
       </c>
       <c r="C246" s="4" t="n">
-        <v>1089.8</v>
+        <v>495.25</v>
       </c>
       <c r="D246" s="4" t="n">
-        <v>34.02</v>
+        <v>37.89</v>
       </c>
       <c r="E246" s="4" t="n">
-        <v>43.24</v>
+        <v>36.65</v>
       </c>
       <c r="F246" s="4" t="n">
-        <v>51.38</v>
+        <v/>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>BAJAJELEC</t>
+          <t>GMRP&amp;UI</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
@@ -7722,22 +7922,22 @@
         </is>
       </c>
       <c r="C247" s="4" t="n">
-        <v>310.95</v>
+        <v>100.51</v>
       </c>
       <c r="D247" s="4" t="n">
-        <v>33.96</v>
+        <v>37.25</v>
       </c>
       <c r="E247" s="4" t="n">
-        <v>27.88</v>
+        <v>43.58</v>
       </c>
       <c r="F247" s="4" t="n">
-        <v>27.53</v>
+        <v>50.72</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>JYOTHYLAB</t>
+          <t>ENTERO</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -7746,22 +7946,22 @@
         </is>
       </c>
       <c r="C248" s="4" t="n">
-        <v>200.96</v>
+        <v>1089.4</v>
       </c>
       <c r="D248" s="4" t="n">
-        <v>33.86</v>
+        <v>36.82</v>
       </c>
       <c r="E248" s="4" t="n">
-        <v>32.85</v>
+        <v>44.9</v>
       </c>
       <c r="F248" s="4" t="n">
-        <v>36.4</v>
+        <v>46.74</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>KITEX</t>
+          <t>KSCL</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
@@ -7770,22 +7970,22 @@
         </is>
       </c>
       <c r="C249" s="4" t="n">
-        <v>145.02</v>
+        <v>849.5</v>
       </c>
       <c r="D249" s="4" t="n">
-        <v>32.39</v>
+        <v>36.66</v>
       </c>
       <c r="E249" s="4" t="n">
-        <v>38.65</v>
+        <v>42.99</v>
       </c>
       <c r="F249" s="4" t="n">
-        <v>46.46</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>AVANTIFEED</t>
+          <t>HAPPSTMNDS</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
@@ -7794,22 +7994,22 @@
         </is>
       </c>
       <c r="C250" s="4" t="n">
-        <v>1060.1</v>
+        <v>345.35</v>
       </c>
       <c r="D250" s="4" t="n">
-        <v>32.19</v>
+        <v>36.15</v>
       </c>
       <c r="E250" s="4" t="n">
-        <v>45.13</v>
+        <v>34.83</v>
       </c>
       <c r="F250" s="4" t="n">
-        <v>58.7</v>
+        <v>24.25</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>CENTURYPLY</t>
+          <t>AVANTIFEED</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
@@ -7818,16 +8018,16 @@
         </is>
       </c>
       <c r="C251" s="4" t="n">
-        <v>724.6</v>
+        <v>967.7</v>
       </c>
       <c r="D251" s="4" t="n">
-        <v>32.07</v>
+        <v>25.32</v>
       </c>
       <c r="E251" s="4" t="n">
-        <v>44.07</v>
+        <v>40.87</v>
       </c>
       <c r="F251" s="4" t="n">
-        <v>48.94</v>
+        <v>55.08</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Micro250_stocks.xlsx
+++ b/reports/Micro250_stocks.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -546,31 +546,31 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>176.92</v>
+        <v>182.61</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>90.16</v>
+        <v>86.95</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>84.37</v>
+        <v>85.23999999999999</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>88.17</v>
+        <v>88.59</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>48.43</v>
+        <v>58.18</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>99.48999999999999</v>
+        <v>103.72</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>89.64</v>
+        <v>93.22</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>18329801</v>
+        <v>19443983</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>23790</v>
+        <v>24607</v>
       </c>
     </row>
     <row r="3">
@@ -585,37 +585,37 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>1983.6</v>
+        <v>2110.8</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>83.31</v>
+        <v>86.44</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>77.47</v>
+        <v>79.91</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>67.52</v>
+        <v>69.31</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>30.03</v>
+        <v>20.18</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>1411.88</v>
+        <v>1447.34</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>1403.94</v>
+        <v>1432.08</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>554008</v>
+        <v>712039</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>12361</v>
+        <v>13129</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ASTRAMICRO</t>
+          <t>PGIL</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -624,37 +624,37 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>1684.1</v>
+        <v>2071</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>81.44</v>
+        <v>79.72</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>82.65000000000001</v>
+        <v>70.03</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>76.63</v>
+        <v>70.69</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>24.97</v>
+        <v>46.8</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>1109.79</v>
+        <v>1567.82</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>1076.25</v>
+        <v>1532.31</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>1453405</v>
+        <v>232006</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>15990</v>
+        <v>9542</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KIRLPNU</t>
+          <t>ICIL</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -663,37 +663,37 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1950</v>
+        <v>426.4</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>78.76000000000001</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>84.45999999999999</v>
+        <v>74.88</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>71.39</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>38.35</v>
+        <v>20.88</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>1338.25</v>
+        <v>296.05</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>1307.62</v>
+        <v>293.5</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>184422</v>
+        <v>1433676</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>12667</v>
+        <v>8457</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>SOUTHBANK</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -702,37 +702,37 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>48.46</v>
+        <v>1325.1</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>76.86</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>70.45999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>72.02</v>
+        <v>71.75</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>23.34</v>
+        <v>22.1</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>39.47</v>
+        <v>1049.91</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>38.22</v>
+        <v>1014.72</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>17591440</v>
+        <v>439408</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>12685</v>
+        <v>17518</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>ARVIND</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -741,37 +741,37 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>654.35</v>
+        <v>547.25</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>72.81999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>89.72</v>
+        <v>82.16</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>91.15000000000001</v>
+        <v>74.68000000000001</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>41.57</v>
+        <v>26.92</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>292.08</v>
+        <v>403.1</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>256.16</v>
+        <v>389.63</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>3621671</v>
+        <v>1044280</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>31943</v>
+        <v>14469</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ICIL</t>
+          <t>SANSERA</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -780,37 +780,37 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>394.6</v>
+        <v>3146.2</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>71.95999999999999</v>
+        <v>70.41</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>71.45</v>
+        <v>77.34</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>62.62</v>
+        <v>79.2</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>29.12</v>
+        <v>25.55</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>289.72</v>
+        <v>2288.28</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>288.55</v>
+        <v>2150.29</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>934526</v>
+        <v>398145</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>7815</v>
+        <v>19663</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENGG</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -819,37 +819,37 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>86.84</v>
+        <v>5594.2</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>69.88</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>75.70999999999999</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>63.99</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>32.44</v>
+        <v>20.65</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>60.03</v>
+        <v>3866.87</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>59.75</v>
+        <v>3620.46</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>22324808</v>
+        <v>222161</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>12377</v>
+        <v>17359</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ARVIND</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -858,37 +858,37 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>516.6</v>
+        <v>1750.3</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>69.7</v>
+        <v>67.52</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>78.92</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>72.56999999999999</v>
+        <v>76.12</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>27.63</v>
+        <v>39.63</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>395.96</v>
+        <v>1194.83</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>383.81</v>
+        <v>1133.62</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>974663</v>
+        <v>552345</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>13541</v>
+        <v>11719</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>AKUMS</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -897,37 +897,37 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>5454.6</v>
+        <v>609.35</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>69.37</v>
+        <v>63.69</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>70.75</v>
+        <v>67.26000000000001</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>81.34999999999999</v>
+        <v>52.6</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>22.52</v>
+        <v>37.35</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>3777.29</v>
+        <v>515.7</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>3541.77</v>
+        <v>514.26</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>242325</v>
+        <v>350432</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>16954</v>
+        <v>9302</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>KIRLPNU</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -936,37 +936,37 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1744.6</v>
+        <v>1899.2</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>68.92</v>
+        <v>63.49</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>77.64</v>
+        <v>80.38</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>75.98999999999999</v>
+        <v>70.70999999999999</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>40.3</v>
+        <v>31.3</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1164.69</v>
+        <v>1371.15</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1108.42</v>
+        <v>1334.18</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>554855</v>
+        <v>246045</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>11652</v>
+        <v>12388</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>TMB</t>
+          <t>LLOYDSENGG</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -975,37 +975,37 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>780.6</v>
+        <v>84.91</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>67.86</v>
+        <v>62.61</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>70.20999999999999</v>
+        <v>72.94</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>72.43000000000001</v>
+        <v>63.35</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>22.77</v>
+        <v>42.75</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>624.8</v>
+        <v>61.44</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>597.65</v>
+        <v>60.86</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>321251</v>
+        <v>21408146</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>12361</v>
+        <v>12101</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>SPARC</t>
+          <t>MANORAMA</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1014,37 +1014,37 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>238.09</v>
+        <v>1573.5</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>67.41</v>
+        <v>61.07</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>78.75</v>
+        <v>60.04</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>61.12</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>36.74</v>
+        <v>32.47</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>160.63</v>
+        <v>1402.59</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>157.74</v>
+        <v>1379.67</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>9195258</v>
+        <v>152434</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>7727</v>
+        <v>9421</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>PGIL</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1053,37 +1053,37 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1793.5</v>
+        <v>613.35</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>67.01000000000001</v>
+        <v>60.3</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>61.56</v>
+        <v>81.81</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>66.14</v>
+        <v>90.48999999999999</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>44.14</v>
+        <v>51.14</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1545.02</v>
+        <v>308.45</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1513.1</v>
+        <v>269.95</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>125340</v>
+        <v>2713201</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>8283</v>
+        <v>29942</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>THYROCARE</t>
+          <t>VARROC</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1092,37 +1092,37 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>540.55</v>
+        <v>611.65</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>66.53</v>
+        <v>58.08</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>70.39</v>
+        <v>61.1</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>66.88</v>
+        <v>56.79</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>21.46</v>
+        <v>23.42</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>439.99</v>
+        <v>563.9</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>427.58</v>
+        <v>563.87</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>417056</v>
+        <v>122267</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>8603</v>
+        <v>9336</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENT</t>
+          <t>SPARC</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1131,37 +1131,37 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>77.22</v>
+        <v>224.92</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>66.12</v>
+        <v>57.15</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>63.81</v>
+        <v>71.17</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>60.54</v>
+        <v>59.26</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>47.83</v>
+        <v>35.7</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>63.32</v>
+        <v>164.31</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>62.82</v>
+        <v>160.72</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>3815399</v>
+        <v>9230898</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>11788</v>
+        <v>7286</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>AKUMS</t>
+          <t>MTARTECH</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1170,37 +1170,37 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>604.7</v>
+        <v>7976.5</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>65.39</v>
+        <v>56.22</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>66.90000000000001</v>
+        <v>75.06</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>52.33</v>
+        <v>87.93000000000001</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>39.76</v>
+        <v>57.22</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>510.27</v>
+        <v>4949.73</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>510.16</v>
+        <v>4419.59</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>381583</v>
+        <v>2147408</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>9258</v>
+        <v>24546</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>PRIVISCL</t>
+          <t>METROPOLIS</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1209,31 +1209,31 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>3493.9</v>
+        <v>543.35</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>65.06999999999999</v>
+        <v>54.52</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>63.08</v>
+        <v>60.32</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>70.05</v>
+        <v>59.39</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>38.81</v>
+        <v>25.23</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>3019.46</v>
+        <v>496.72</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>2916.94</v>
+        <v>492.42</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>106112</v>
+        <v>223604</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>13648</v>
+        <v>11299</v>
       </c>
     </row>
     <row r="20">
@@ -1248,37 +1248,37 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>77.25</v>
+        <v>75.14</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>63</v>
+        <v>54.28</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>65.44</v>
+        <v>62.17</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>56.16</v>
+        <v>55.22</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>36.41</v>
+        <v>40.35</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>65.98</v>
+        <v>66.52</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>65.48</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>4254743</v>
+        <v>4300889</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>8835</v>
+        <v>8623</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>APOLLO</t>
+          <t>SKIPPER</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1287,37 +1287,37 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>433.15</v>
+        <v>533.15</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>62.95</v>
+        <v>52.7</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>74.04000000000001</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>73.37</v>
+        <v>60.38</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>41.56</v>
+        <v>56.85</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>292.2</v>
+        <v>459.48</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>276.1</v>
+        <v>457.29</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>30426358</v>
+        <v>1033451</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>15623</v>
+        <v>6012</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>MTARTECH</t>
+          <t>TDPOWERSYS</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1326,37 +1326,37 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>8374.5</v>
+        <v>1255.1</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>62.63</v>
+        <v>51.39</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>80.7</v>
+        <v>67.83</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>88.59</v>
+        <v>79.65000000000001</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>4780.46</v>
+        <v>975.36</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>4272.01</v>
+        <v>905.35</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2387010</v>
+        <v>1595373</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>25760</v>
+        <v>19607</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>BBOX</t>
+          <t>SHAILY</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1365,37 +1365,37 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1023</v>
+        <v>2849.7</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>61.92</v>
+        <v>51.27</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>78.72</v>
+        <v>61.26</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>75.59999999999999</v>
+        <v>68.59</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>21.5</v>
+        <v>34.64</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>681.72</v>
+        <v>2410.67</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>643.77</v>
+        <v>2319.58</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1396173</v>
+        <v>383532</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>18168</v>
+        <v>13109</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>SHILPAMED</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1404,37 +1404,37 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>551.35</v>
+        <v>1191</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>60.84</v>
+        <v>50.19</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>79.94</v>
+        <v>60.18</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>69.98</v>
+        <v>62.21</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>22.78</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>412.45</v>
+        <v>1007.78</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>401.94</v>
+        <v>966.37</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1381188</v>
+        <v>205341</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>10783</v>
+        <v>7829</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>SANSERA</t>
+          <t>GAEL</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1443,37 +1443,37 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2945.8</v>
+        <v>158.27</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>60.71</v>
+        <v>49.76</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>73.76000000000001</v>
+        <v>61.68</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>77.44</v>
+        <v>63.13</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>34.85</v>
+        <v>20.3</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2243.67</v>
+        <v>143.02</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>2111.33</v>
+        <v>138.75</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>323667</v>
+        <v>691508</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>18362</v>
+        <v>7288</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>SKIPPER</t>
+          <t>NEOGEN</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1482,37 +1482,37 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>543.3</v>
+        <v>1874.8</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>58.06</v>
+        <v>49.56</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>67.59999999999999</v>
+        <v>62.86</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>61.53</v>
+        <v>57.74</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>46.61</v>
+        <v>38.19</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>455</v>
+        <v>1566.27</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>453.94</v>
+        <v>1543.61</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1058360</v>
+        <v>120838</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>6134</v>
+        <v>5145</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>SKYGOLD</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1521,37 +1521,37 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>274.7</v>
+        <v>499.15</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>57.48</v>
+        <v>49.17</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>68.64</v>
+        <v>61.85</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>68.89</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>27.24</v>
+        <v>38.19</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>230.64</v>
+        <v>410.97</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>223.25</v>
+        <v>393.98</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>2842668</v>
+        <v>1448527</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>10389</v>
+        <v>7728</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>NEOGEN</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1560,37 +1560,37 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1932</v>
+        <v>265.6</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>57.15</v>
+        <v>48.6</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>65.72</v>
+        <v>62.97</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>58.67</v>
+        <v>66.59</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>26.73</v>
+        <v>37.17</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>1546.98</v>
+        <v>232.6</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>1527.81</v>
+        <v>225.01</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>121466</v>
+        <v>2809444</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>5290</v>
+        <v>10027</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>YATHARTH</t>
+          <t>BBOX</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1599,37 +1599,37 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>839.75</v>
+        <v>957.9</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>57.02</v>
+        <v>48.54</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>60.12</v>
+        <v>70.5</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>63.29</v>
+        <v>71.16</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>43.26</v>
+        <v>20.51</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>739.41</v>
+        <v>697.46</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>719.62</v>
+        <v>657.5</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>409113</v>
+        <v>927938</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>8091</v>
+        <v>17025</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>STAR</t>
+          <t>TMB</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1638,37 +1638,37 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1110.9</v>
+        <v>732.6</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>56.16</v>
+        <v>48.37</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>62.19</v>
+        <v>61.79</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>61.25</v>
+        <v>70.04000000000001</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>52.27</v>
+        <v>29.56</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>982.11</v>
+        <v>631.61</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>961.3200000000001</v>
+        <v>603.87</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>337113</v>
+        <v>297975</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>10239</v>
+        <v>11599</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>APOLLO</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1677,265 +1677,31 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1235.2</v>
+        <v>384.4</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>55.82</v>
+        <v>46.82</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>63.24</v>
+        <v>62.91</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>63.25</v>
+        <v>68.43000000000001</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>68.02</v>
+        <v>53.36</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>997.4</v>
+        <v>297.93</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>956.9400000000001</v>
+        <v>281.04</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>276698</v>
+        <v>30772072</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>8085</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>TDPOWERSYS</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>1272.7</v>
-      </c>
-      <c r="D32" s="4" t="n">
-        <v>55.55</v>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>69.59</v>
-      </c>
-      <c r="F32" s="4" t="n">
-        <v>81.01000000000001</v>
-      </c>
-      <c r="G32" s="4" t="n">
-        <v>34.18</v>
-      </c>
-      <c r="H32" s="4" t="n">
-        <v>957.64</v>
-      </c>
-      <c r="I32" s="4" t="n">
-        <v>889.41</v>
-      </c>
-      <c r="J32" s="4" t="n">
-        <v>1548652</v>
-      </c>
-      <c r="K32" s="4" t="n">
-        <v>19883</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>ADVENZYMES</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>373.7</v>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>54.95</v>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>66.68000000000001</v>
-      </c>
-      <c r="F33" s="4" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="G33" s="4" t="n">
-        <v>26.16</v>
-      </c>
-      <c r="H33" s="4" t="n">
-        <v>328.44</v>
-      </c>
-      <c r="I33" s="4" t="n">
-        <v>325.8</v>
-      </c>
-      <c r="J33" s="4" t="n">
-        <v>456452</v>
-      </c>
-      <c r="K33" s="4" t="n">
-        <v>4185</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>GAEL</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="n">
-        <v>159.98</v>
-      </c>
-      <c r="D34" s="4" t="n">
-        <v>54.36</v>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>62.78</v>
-      </c>
-      <c r="F34" s="4" t="n">
-        <v>63.49</v>
-      </c>
-      <c r="G34" s="4" t="n">
-        <v>24.43</v>
-      </c>
-      <c r="H34" s="4" t="n">
-        <v>142.06</v>
-      </c>
-      <c r="I34" s="4" t="n">
-        <v>137.89</v>
-      </c>
-      <c r="J34" s="4" t="n">
-        <v>877752</v>
-      </c>
-      <c r="K34" s="4" t="n">
-        <v>7338</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>AXISCADES</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="n">
-        <v>1943.2</v>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>53.23</v>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>61.21</v>
-      </c>
-      <c r="F35" s="4" t="n">
-        <v>69.53</v>
-      </c>
-      <c r="G35" s="4" t="n">
-        <v>36.94</v>
-      </c>
-      <c r="H35" s="4" t="n">
-        <v>1644.53</v>
-      </c>
-      <c r="I35" s="4" t="n">
-        <v>1565.11</v>
-      </c>
-      <c r="J35" s="4" t="n">
-        <v>182722</v>
-      </c>
-      <c r="K35" s="4" t="n">
-        <v>8265</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>SKYGOLD</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="n">
-        <v>509.4</v>
-      </c>
-      <c r="D36" s="4" t="n">
-        <v>52.17</v>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>63.75</v>
-      </c>
-      <c r="F36" s="4" t="n">
-        <v>69.25</v>
-      </c>
-      <c r="G36" s="4" t="n">
-        <v>28.79</v>
-      </c>
-      <c r="H36" s="4" t="n">
-        <v>405.94</v>
-      </c>
-      <c r="I36" s="4" t="n">
-        <v>389.33</v>
-      </c>
-      <c r="J36" s="4" t="n">
-        <v>1609797</v>
-      </c>
-      <c r="K36" s="4" t="n">
-        <v>7889</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>SHAILY</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="n">
-        <v>2803.8</v>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>47.87</v>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>60.25</v>
-      </c>
-      <c r="F37" s="4" t="n">
-        <v>67.55</v>
-      </c>
-      <c r="G37" s="4" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="H37" s="4" t="n">
-        <v>2388.83</v>
-      </c>
-      <c r="I37" s="4" t="n">
-        <v>2299.27</v>
-      </c>
-      <c r="J37" s="4" t="n">
-        <v>395958</v>
-      </c>
-      <c r="K37" s="4" t="n">
-        <v>12896</v>
+        <v>14277</v>
       </c>
     </row>
   </sheetData>
@@ -1970,12 +1736,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2042,22 +1802,22 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>176.92</v>
+        <v>182.61</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>90.16</v>
+        <v>86.95</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>84.37</v>
+        <v>85.23999999999999</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>88.17</v>
+        <v>88.59</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>PARAS</t>
+          <t>WABAG</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -2066,22 +1826,22 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>1408.65</v>
+        <v>2110.8</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>85.16</v>
+        <v>86.44</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>81.18000000000001</v>
+        <v>79.91</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>70.19</v>
+        <v>69.31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>WABAG</t>
+          <t>SKFINDUS</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -2090,22 +1850,22 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>1983.6</v>
+        <v>2906</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>83.31</v>
+        <v>83.45</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>77.47</v>
+        <v>70.61</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>67.52</v>
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>VMART</t>
+          <t>PGIL</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2114,16 +1874,16 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>797.8</v>
+        <v>2071</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>81.59</v>
+        <v>79.72</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>67.92</v>
+        <v>70.03</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>54.43</v>
+        <v>70.69</v>
       </c>
     </row>
     <row r="6">
@@ -2138,22 +1898,22 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1684.1</v>
+        <v>1721.7</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>81.44</v>
+        <v>78.89</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>82.65000000000001</v>
+        <v>83.37</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>76.63</v>
+        <v>77.17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>MSTCLTD</t>
+          <t>RBA</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2162,22 +1922,22 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>692.75</v>
+        <v>79.38</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>80.40000000000001</v>
+        <v>78.84999999999999</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>75.40000000000001</v>
+        <v>73.94</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>60.88</v>
+        <v>49.64</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>RBA</t>
+          <t>CCAVENUE</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2186,22 +1946,22 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>73.67</v>
+        <v>16.07</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>80.02</v>
+        <v>77.63</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>66.84</v>
+        <v>54.49</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>45.71</v>
+        <v>44.12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>KIRLPNU</t>
+          <t>RELAXO</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2210,22 +1970,22 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1950</v>
+        <v>413.55</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>78.76000000000001</v>
+        <v>77.61</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>84.45999999999999</v>
+        <v>64.27</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>71.39</v>
+        <v>41.72</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>QUESS</t>
+          <t>RELIGARE</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2234,22 +1994,22 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>249.87</v>
+        <v>274.43</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>77.87</v>
+        <v>77.42</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>64.45999999999999</v>
+        <v>68.55</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>39.86</v>
+        <v>58.96</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>SOUTHBANK</t>
+          <t>AVL</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2258,22 +2018,22 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>48.46</v>
+        <v>660.5</v>
       </c>
       <c r="D11" s="4" t="n">
         <v>76.86</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>70.45999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>72.02</v>
+        <v>70.39</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>AVL</t>
+          <t>GOKEX</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2282,22 +2042,22 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>629.9</v>
+        <v>854.75</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>75.70999999999999</v>
+        <v>76.64</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>68.59</v>
+        <v>62.11</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>68.01000000000001</v>
+        <v>53.91</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>GRWRHITECH</t>
+          <t>SHRIPISTON</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -2306,22 +2066,22 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>6785.5</v>
+        <v>4033</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>74.98999999999999</v>
+        <v>74.87</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>77.95999999999999</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>68.68000000000001</v>
+        <v>75.43000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>SKFINDUS</t>
+          <t>SWSOLAR</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -2330,22 +2090,22 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2626.8</v>
+        <v>246.68</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>74.68000000000001</v>
+        <v>74.76000000000001</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>62.15</v>
+        <v>62.32</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v/>
+        <v>44.82</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>KIRLOSBROS</t>
+          <t>ICIL</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -2354,22 +2114,22 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1933.6</v>
+        <v>426.4</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>74.40000000000001</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>63.09</v>
+        <v>74.88</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>57.04</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>RATEGAIN</t>
+          <t>STYL</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -2378,22 +2138,22 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>867.7</v>
+        <v>308.75</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>74.06</v>
+        <v>73.20999999999999</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>77.72</v>
+        <v>62.37</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>64.02</v>
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GOKEX</t>
+          <t>QUESS</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -2402,22 +2162,22 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>818.7</v>
+        <v>251.1</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>73.87</v>
+        <v>73.11</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>59.53</v>
+        <v>64.73</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>52.62</v>
+        <v>39.99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>CERA</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -2426,22 +2186,22 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>6448</v>
+        <v>1325.1</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>73.34999999999999</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>68.64</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>53.24</v>
+        <v>71.75</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>SWSOLAR</t>
+          <t>KIRLOSBROS</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2450,22 +2210,22 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>235.47</v>
+        <v>2018.5</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>72.83</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>59.67</v>
+        <v>66.08</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>43.71</v>
+        <v>58.53</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>RUBICON</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -2474,22 +2234,22 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>654.35</v>
+        <v>1416.6</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>72.81999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>89.72</v>
+        <v>91.87</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>91.15000000000001</v>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>ANUP</t>
+          <t>BORORENEW</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -2498,22 +2258,22 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2246</v>
+        <v>615.7</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>72.06999999999999</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>58.59</v>
+        <v>64.06999999999999</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>52.66</v>
+        <v>57.17</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>RELIGARE</t>
+          <t>ARVIND</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -2522,22 +2282,22 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>253.4</v>
+        <v>547.25</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>72.04000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>60.95</v>
+        <v>82.16</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>55.12</v>
+        <v>74.68000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>GREAVESCOT</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -2546,22 +2306,22 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>567.65</v>
+        <v>214.09</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>72</v>
+        <v>71.06</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>69.37</v>
+        <v>66.25</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>55.31</v>
+        <v>55.93</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>ICIL</t>
+          <t>SANSERA</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -2570,22 +2330,22 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>394.6</v>
+        <v>3146.2</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>71.95999999999999</v>
+        <v>70.41</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>71.45</v>
+        <v>77.34</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>62.62</v>
+        <v>79.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>BORORENEW</t>
+          <t>KSB</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -2594,22 +2354,22 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>598.25</v>
+        <v>934.35</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>70.44</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>62.12</v>
+        <v>62.74</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>56.07</v>
+        <v>59.86</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENGG</t>
+          <t>REFEX</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -2618,22 +2378,22 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>86.84</v>
+        <v>348.95</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>69.88</v>
+        <v>69.66</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>75.70999999999999</v>
+        <v>67.58</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>63.99</v>
+        <v>55.01</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>ARVIND</t>
+          <t>ANUP</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -2642,16 +2402,16 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>516.6</v>
+        <v>2297.9</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>69.7</v>
+        <v>69.48</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>78.92</v>
+        <v>60.58</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>72.56999999999999</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="28">
@@ -2666,22 +2426,22 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>5454.6</v>
+        <v>5594.2</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>69.37</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>70.75</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>81.34999999999999</v>
+        <v>81.84999999999999</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>SFL</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -2690,16 +2450,16 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1868.6</v>
+        <v>725.6</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>69.33</v>
+        <v>68</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>70.34</v>
+        <v>68.13</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v/>
+        <v>49.66</v>
       </c>
     </row>
     <row r="30">
@@ -2714,22 +2474,22 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>199.47</v>
+        <v>204.15</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>69.31999999999999</v>
+        <v>67.95</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>58.57</v>
+        <v>59.08</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>55.73</v>
+        <v>55.93</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>SUDEEPPHRM</t>
+          <t>JLHL</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -2738,22 +2498,22 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>842.95</v>
+        <v>1375.3</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>69.29000000000001</v>
+        <v>67.87</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>70.39</v>
+        <v>58.68</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v/>
+        <v>52.18</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>RUBICON</t>
+          <t>AGARWALEYE</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -2762,22 +2522,22 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1361.8</v>
+        <v>484.65</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>69.28</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>91.08</v>
+        <v>56.24</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v/>
+        <v>54.31</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>PNCINFRA</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -2786,22 +2546,22 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1744.6</v>
+        <v>232.3</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>68.92</v>
+        <v>67.64</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>77.64</v>
+        <v>54.09</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>75.98999999999999</v>
+        <v>43.3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>INOXINDIA</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -2810,22 +2570,22 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>1917.8</v>
+        <v>1750.3</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>68.84</v>
+        <v>67.52</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>83.98</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>82.08</v>
+        <v>76.12</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>CCAVENUE</t>
+          <t>GRWRHITECH</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -2834,22 +2594,22 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>15.07</v>
+        <v>6688.5</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>68.79000000000001</v>
+        <v>66.58</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>49.37</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>41.74</v>
+        <v>68.28</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>HCC</t>
+          <t>AEQUS</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -2858,22 +2618,22 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>27.02</v>
+        <v>228.95</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>68.75</v>
+        <v>66.14</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>65.19</v>
+        <v>72.59</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>51.12</v>
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>KSB</t>
+          <t>SMARTWORKS</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -2882,22 +2642,22 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>902.55</v>
+        <v>489.55</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>68.73</v>
+        <v>66.13</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>59.84</v>
+        <v>59.34</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>58.42</v>
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>QPOWER</t>
+          <t>SUBROS</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -2906,22 +2666,22 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>1320.6</v>
+        <v>835.45</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>68.69</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>65.09999999999999</v>
+        <v>57.06</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>67.8</v>
+        <v>54.95</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>SFL</t>
+          <t>MSTCLTD</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -2930,22 +2690,22 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>700.65</v>
+        <v>647.4</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>67.89</v>
+        <v>65.16</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>65.51000000000001</v>
+        <v>67.94</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>48.16</v>
+        <v>58.81</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>TMB</t>
+          <t>LOTUSDEV</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -2954,22 +2714,22 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>780.6</v>
+        <v>150.69</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>67.86</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>70.20999999999999</v>
+        <v>54.74</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>72.43000000000001</v>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GREAVESCOT</t>
+          <t>SAMHI</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -2978,22 +2738,22 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>198.54</v>
+        <v>179.85</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>67.7</v>
+        <v>64.95</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>61.58</v>
+        <v>58.57</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>53.51</v>
+        <v>51</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>STYL</t>
+          <t>SHAKTIPUMP</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -3002,22 +2762,22 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>293.15</v>
+        <v>580.9</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>67.56</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>57.43</v>
+        <v>49.73</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v/>
+        <v>48.09</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>TVSSCS</t>
+          <t>WELENT</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -3026,22 +2786,22 @@
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>140.31</v>
+        <v>572.45</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>67.55</v>
+        <v>64.53</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>62.89</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>50.34</v>
+        <v>59.58</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>REFEX</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -3050,22 +2810,22 @@
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>336.9</v>
+        <v>1893.3</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>67.48999999999999</v>
+        <v>64.31</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>65.59999999999999</v>
+        <v>71.94</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>54.02</v>
+        <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>PNCINFRA</t>
+          <t>VIYASH</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -3074,22 +2834,22 @@
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>226.01</v>
+        <v>269.3</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>67.48</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>52.24</v>
+        <v>70.33</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>42.52</v>
+        <v>65.65000000000001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>SPARC</t>
+          <t>OPTIEMUS</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -3098,22 +2858,22 @@
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>238.09</v>
+        <v>469.3</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>67.41</v>
+        <v>64</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>78.75</v>
+        <v>55.19</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>61.12</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>VMART</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -3122,22 +2882,22 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>259.67</v>
+        <v>762.1</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>67.25</v>
+        <v>63.87</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>73.42</v>
+        <v>61.4</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>61.02</v>
+        <v>52.54</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>AEQUS</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -3146,22 +2906,22 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>222.13</v>
+        <v>218.55</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>67.09999999999999</v>
+        <v>63.8</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>71.09999999999999</v>
+        <v>58.22</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v/>
+        <v>45.97</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>PGIL</t>
+          <t>AKUMS</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -3170,22 +2930,22 @@
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>1793.5</v>
+        <v>609.35</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>67.01000000000001</v>
+        <v>63.69</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>61.56</v>
+        <v>67.26000000000001</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>66.14</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>POWERMECH</t>
+          <t>KIRLPNU</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -3194,22 +2954,22 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>2839.9</v>
+        <v>1899.2</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>66.65000000000001</v>
+        <v>63.49</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>65.87</v>
+        <v>80.38</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>56.46</v>
+        <v>70.70999999999999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>THYROCARE</t>
+          <t>AURIONPRO</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -3218,22 +2978,22 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>540.55</v>
+        <v>895.1</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>66.53</v>
+        <v>63.46</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>70.39</v>
+        <v>48.94</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>66.88</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENT</t>
+          <t>ALIVUS</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -3242,22 +3002,22 @@
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>77.22</v>
+        <v>1108.3</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>66.12</v>
+        <v>63.46</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>63.81</v>
+        <v>64.42</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>60.54</v>
+        <v>61.91</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>WELENT</t>
+          <t>PARAS</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -3266,22 +3026,22 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>567.85</v>
+        <v>1233.75</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>66.05</v>
+        <v>63.43</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>65.37</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>59.12</v>
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>EDELWEISS</t>
+          <t>HCC</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -3290,22 +3050,22 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>124.71</v>
+        <v>26.76</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>66.02</v>
+        <v>62.88</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>58.49</v>
+        <v>64.39</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>60.68</v>
+        <v>50.91</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>SAMHI</t>
+          <t>RATEGAIN</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -3314,22 +3074,22 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>175.81</v>
+        <v>840.95</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>65.84999999999999</v>
+        <v>62.77</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>56.08</v>
+        <v>73.52</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>49.74</v>
+        <v>63.16</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>BLACKBUCK</t>
+          <t>LLOYDSENGG</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -3338,22 +3098,22 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>574.05</v>
+        <v>84.91</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>65.73999999999999</v>
+        <v>62.61</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>50.43</v>
+        <v>72.94</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>54.85</v>
+        <v>63.35</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>IXIGO</t>
+          <t>DBL</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -3362,22 +3122,22 @@
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>189.98</v>
+        <v>459.7</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>65.73999999999999</v>
+        <v>62.57</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>50.37</v>
+        <v>52.41</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>49.56</v>
+        <v>51.58</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>RCF</t>
+          <t>OSWALPUMPS</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -3386,22 +3146,22 @@
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>136.65</v>
+        <v>431.85</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>65.44</v>
+        <v>62.47</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>55.27</v>
+        <v>51.12</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>49.84</v>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>PRUDENT</t>
+          <t>CERA</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -3410,22 +3170,22 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>3029.2</v>
+        <v>6330.5</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>65.44</v>
+        <v>62.08</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>65.16</v>
+        <v>65.47</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>61.76</v>
+        <v>52.35</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>AKUMS</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -3434,22 +3194,22 @@
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>604.7</v>
+        <v>300.65</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>65.39</v>
+        <v>61.98</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>66.90000000000001</v>
+        <v>59.6</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>52.33</v>
+        <v>58.58</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>KNRCON</t>
+          <t>IXIGO</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -3458,22 +3218,22 @@
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>140.86</v>
+        <v>189.83</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>65.39</v>
+        <v>61.67</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>51.29</v>
+        <v>50.35</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>37.6</v>
+        <v>49.55</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>PRIVISCL</t>
+          <t>SHILPAMED</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -3482,22 +3242,22 @@
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>3493.9</v>
+        <v>571.6</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>65.06999999999999</v>
+        <v>61.64</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>63.08</v>
+        <v>81.65000000000001</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>70.05</v>
+        <v>71.13</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>RATNAMANI</t>
+          <t>PRIVISCL</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -3506,22 +3266,22 @@
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>2770.9</v>
+        <v>3550.5</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>64.88</v>
+        <v>61.64</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>60.66</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>53.23</v>
+        <v>70.59</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>SHRIPISTON</t>
+          <t>WAAREERTL</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -3530,22 +3290,22 @@
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>3739.7</v>
+        <v>1020.65</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>64.59</v>
+        <v>61.53</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>63.22</v>
+        <v>55.48</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>72.95</v>
+        <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>TRIVENI</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -3554,22 +3314,22 @@
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>470</v>
+        <v>409.8</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>64.40000000000001</v>
+        <v>61.26</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>56.05</v>
+        <v>58.28</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>55.47</v>
+        <v>55.44</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>KRBL</t>
+          <t>IONEXCHANG</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -3578,22 +3338,22 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>384.95</v>
+        <v>398.65</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>63.82</v>
+        <v>61.24</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>58.36</v>
+        <v>54.64</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>55.17</v>
+        <v>46.44</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>JAMNAAUTO</t>
+          <t>MANORAMA</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -3602,22 +3362,22 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>132.37</v>
+        <v>1573.5</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>63.36</v>
+        <v>61.07</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>56.57</v>
+        <v>60.04</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>58.32</v>
+        <v>64.95999999999999</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>SUNTECK</t>
+          <t>WESTLIFE</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -3626,22 +3386,22 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>326.1</v>
+        <v>486.3</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>63.23</v>
+        <v>60.66</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>46.01</v>
+        <v>47.66</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>43.13</v>
+        <v>34.79</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>TRIVENI</t>
+          <t>SMLMAH</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -3650,22 +3410,22 @@
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>403.55</v>
+        <v>4092.9</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>63.22</v>
+        <v>60.42</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>56.92</v>
+        <v>54.1</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>54.8</v>
+        <v>61.53</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>EQUITASBNK</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -3674,22 +3434,22 @@
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>77.25</v>
+        <v>613.35</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>63</v>
+        <v>60.3</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>65.44</v>
+        <v>81.81</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>56.16</v>
+        <v>90.48999999999999</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>APOLLO</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -3698,22 +3458,22 @@
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>433.15</v>
+        <v>464.8</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>62.95</v>
+        <v>60</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>74.04000000000001</v>
+        <v>54.61</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>73.37</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>BECTORFOOD</t>
+          <t>PRUDENT</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -3722,22 +3482,22 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>190.32</v>
+        <v>2988.7</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>62.94</v>
+        <v>59.68</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>42.74</v>
+        <v>62.98</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>41.58</v>
+        <v>61.22</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>EMIL</t>
+          <t>MARKSANS</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -3746,22 +3506,22 @@
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>120.86</v>
+        <v>256.07</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>62.88</v>
+        <v>59.55</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>56.84</v>
+        <v>72.44</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>47.31</v>
+        <v>60.81</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>MTARTECH</t>
+          <t>STYRENIX</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -3770,22 +3530,22 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>8374.5</v>
+        <v>2334.4</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>62.63</v>
+        <v>59.54</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>80.7</v>
+        <v>56.45</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>88.59</v>
+        <v>54.81</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>KRBL</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -3794,22 +3554,22 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>297.35</v>
+        <v>385.35</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>62.61</v>
+        <v>59.49</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>58.87</v>
+        <v>58.6</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>58.18</v>
+        <v>55.27</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>INDIGOPNTS</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -3818,22 +3578,22 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>1025.15</v>
+        <v>186.15</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>62.51</v>
+        <v>59.09</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>55.55</v>
+        <v>58.15</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>45.85</v>
+        <v>60.09</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>VARROC</t>
+          <t>BLUESTONE</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -3842,22 +3602,22 @@
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>615.2</v>
+        <v>533.15</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>62.45</v>
+        <v>58.92</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>62.22</v>
+        <v>53.93</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>57.09</v>
+        <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>ASHOKA</t>
+          <t>INOXINDIA</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -3866,22 +3626,22 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>135.16</v>
+        <v>1872.9</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>62.35</v>
+        <v>58.76</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>47.44</v>
+        <v>80</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>44.5</v>
+        <v>81.47</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>RELAXO</t>
+          <t>BLACKBUCK</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -3890,22 +3650,22 @@
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>355.85</v>
+        <v>562.8</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>62.23</v>
+        <v>58.75</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>53.82</v>
+        <v>49.26</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>34.97</v>
+        <v>53.88</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>BBOX</t>
+          <t>TIMETECHNO</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -3914,22 +3674,22 @@
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>1023</v>
+        <v>182.08</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>61.92</v>
+        <v>58.74</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>78.72</v>
+        <v>50.01</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>75.59999999999999</v>
+        <v>51.99</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>ARVINDFASN</t>
+          <t>JAMNAAUTO</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -3938,22 +3698,22 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>484.05</v>
+        <v>130.79</v>
       </c>
       <c r="D81" s="4" t="n">
-        <v>61.87</v>
+        <v>58.58</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>54.62</v>
+        <v>55.54</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>53.15</v>
+        <v>57.88</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>AURIONPRO</t>
+          <t>KSCL</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -3962,22 +3722,22 @@
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>876.4</v>
+        <v>925.6</v>
       </c>
       <c r="D82" s="4" t="n">
-        <v>61.84</v>
+        <v>58.42</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>47.6</v>
+        <v>51.36</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>43.59</v>
+        <v>49.68</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>SMLMAH</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -3986,22 +3746,22 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>4092.2</v>
+        <v>111.5</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>61.74</v>
+        <v>58.42</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>54.55</v>
+        <v>49.97</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>61.68</v>
+        <v>42.96</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>BALAMINES</t>
+          <t>PARKHOSPS</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -4010,22 +3770,22 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>2138.2</v>
+        <v>285.5</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>61.45</v>
+        <v>58.37</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>82.59999999999999</v>
+        <v>79.34999999999999</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>59.94</v>
+        <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>OSWALPUMPS</t>
+          <t>APLLTD</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -4034,22 +3794,22 @@
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>422.9</v>
+        <v>771.5</v>
       </c>
       <c r="D85" s="4" t="n">
-        <v>61.28</v>
+        <v>58.25</v>
       </c>
       <c r="E85" s="4" t="n">
-        <v>49.83</v>
+        <v>49.29</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v/>
+        <v>45.43</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>EIEL</t>
+          <t>PRICOLLTD</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -4058,22 +3818,22 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>205.87</v>
+        <v>586.7</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>61.27</v>
+        <v>58.24</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>55.02</v>
+        <v>52.34</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>43.72</v>
+        <v>58.57</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>WEWORK</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -4082,22 +3842,22 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>630.55</v>
+        <v>546.85</v>
       </c>
       <c r="D87" s="4" t="n">
-        <v>61.22</v>
+        <v>58.1</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>62.1</v>
+        <v>63.33</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v/>
+        <v>53.57</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>SURYAROSNI</t>
+          <t>VOLTAMP</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -4106,22 +3866,22 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>266.34</v>
+        <v>10304</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>61.19</v>
+        <v>58.09</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>56.47</v>
+        <v>59.93</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>51.14</v>
+        <v>56.97</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>VARROC</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -4130,22 +3890,22 @@
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>111.6</v>
+        <v>611.65</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>61.19</v>
+        <v>58.08</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>50.37</v>
+        <v>61.1</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>43.14</v>
+        <v>56.79</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>SAFARI</t>
+          <t>AHLUCONT</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -4154,22 +3914,22 @@
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>1675.5</v>
+        <v>848.1</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>61.01</v>
+        <v>57.84</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>48.47</v>
+        <v>52.01</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>44.94</v>
+        <v>48.88</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>STYRENIX</t>
+          <t>QPOWER</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -4178,22 +3938,22 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>2312.9</v>
+        <v>1255.4</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>60.98</v>
+        <v>57.76</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>56.35</v>
+        <v>61.11</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>54.76</v>
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>METROPOLIS</t>
+          <t>SUDEEPPHRM</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -4202,22 +3962,22 @@
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>552.75</v>
+        <v>809.2</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>60.95</v>
+        <v>57.65</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>62.38</v>
+        <v>64.95999999999999</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>60.57</v>
+        <v/>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>SHILPAMED</t>
+          <t>IFBIND</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -4226,22 +3986,22 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>551.35</v>
+        <v>1278.4</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>60.84</v>
+        <v>57.58</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>79.94</v>
+        <v>52.88</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>69.98</v>
+        <v>48.82</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>VAIBHAVGBL</t>
+          <t>EMIL</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -4250,22 +4010,22 @@
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>244.33</v>
+        <v>119.14</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>60.82</v>
+        <v>57.44</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>58.06</v>
+        <v>55.11</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>48.31</v>
+        <v>46.74</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>MANORAMA</t>
+          <t>HERITGFOOD</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -4274,22 +4034,22 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>1558.2</v>
+        <v>336.8</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>60.75</v>
+        <v>57.43</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>59.13</v>
+        <v>42.55</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>64.48999999999999</v>
+        <v>44.68</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>SANSERA</t>
+          <t>SPARC</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -4298,22 +4058,22 @@
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>2945.8</v>
+        <v>224.92</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>60.71</v>
+        <v>57.15</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>73.76000000000001</v>
+        <v>71.17</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>77.44</v>
+        <v>59.26</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>VOLTAMP</t>
+          <t>EDELWEISS</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -4322,22 +4082,22 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>10237.5</v>
+        <v>122.45</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>59.94</v>
+        <v>57.14</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>59.19</v>
+        <v>56.55</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>56.64</v>
+        <v>59.92</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>SAATVIKGL</t>
+          <t>POWERMECH</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -4346,22 +4106,22 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>477.2</v>
+        <v>2760.1</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>59.9</v>
+        <v>57.07</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>59.71</v>
+        <v>62.64</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v/>
+        <v>55.62</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>ALOKINDS</t>
+          <t>SUNTECK</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -4370,16 +4130,16 @@
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>13.29</v>
+        <v>319</v>
       </c>
       <c r="D99" s="4" t="n">
-        <v>59.68</v>
+        <v>57</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>44.82</v>
+        <v>44.42</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>40.08</v>
+        <v>42.31</v>
       </c>
     </row>
     <row r="100">
@@ -4394,22 +4154,22 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>209.24</v>
+        <v>206.28</v>
       </c>
       <c r="D100" s="4" t="n">
-        <v>59.62</v>
+        <v>56.83</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>77.06999999999999</v>
+        <v>74.72</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>68.27</v>
+        <v>67.90000000000001</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>SANOFICONR</t>
+          <t>SURYAROSNI</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -4418,22 +4178,22 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>4812.5</v>
+        <v>261.56</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>59.59</v>
+        <v>56.69</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>57.03</v>
+        <v>54.43</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>52.26</v>
+        <v>50.49</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>ALKYLAMINE</t>
+          <t>EPL</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -4442,22 +4202,22 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>1845.4</v>
+        <v>229.22</v>
       </c>
       <c r="D102" s="4" t="n">
-        <v>59.55</v>
+        <v>56.24</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>65.84</v>
+        <v>56.99</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>49.97</v>
+        <v>55.18</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>IFBIND</t>
+          <t>MTARTECH</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -4466,22 +4226,22 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>1284.5</v>
+        <v>7976.5</v>
       </c>
       <c r="D103" s="4" t="n">
-        <v>59.52</v>
+        <v>56.22</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>53.32</v>
+        <v>75.06</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>48.95</v>
+        <v>87.93000000000001</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>RAYMONDLSL</t>
+          <t>REDTAPE</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -4490,22 +4250,22 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>810.65</v>
+        <v>136.9</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>59.28</v>
+        <v>56.16</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>44.54</v>
+        <v>54.99</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>28.07</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>EPL</t>
+          <t>EMBDL</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -4514,22 +4274,22 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>229.57</v>
+        <v>63.71</v>
       </c>
       <c r="D105" s="4" t="n">
-        <v>59.25</v>
+        <v>55.91</v>
       </c>
       <c r="E105" s="4" t="n">
-        <v>56.58</v>
+        <v>50.6</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>54.98</v>
+        <v>42.81</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>JLHL</t>
+          <t>WEWORK</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -4538,22 +4298,22 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>1342.1</v>
+        <v>626.55</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>59.1</v>
+        <v>55.82</v>
       </c>
       <c r="E106" s="4" t="n">
-        <v>53.28</v>
+        <v>60.88</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>49.63</v>
+        <v/>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>ROUTE</t>
+          <t>SUPRIYA</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -4562,22 +4322,22 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>545.5</v>
+        <v>928.15</v>
       </c>
       <c r="D107" s="4" t="n">
-        <v>59.01</v>
+        <v>55.65</v>
       </c>
       <c r="E107" s="4" t="n">
-        <v>46.64</v>
+        <v>70.44</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>31.62</v>
+        <v>65.87</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>VIYASH</t>
+          <t>AARTIPHARM</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -4586,22 +4346,22 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>254.95</v>
+        <v>690.7</v>
       </c>
       <c r="D108" s="4" t="n">
-        <v>58.98</v>
+        <v>55.33</v>
       </c>
       <c r="E108" s="4" t="n">
-        <v>66.72</v>
+        <v>49.18</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>63.28</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>AHLUCONT</t>
+          <t>ENTERO</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -4610,22 +4370,22 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>838.8</v>
+        <v>1180.4</v>
       </c>
       <c r="D109" s="4" t="n">
-        <v>58.7</v>
+        <v>55.29</v>
       </c>
       <c r="E109" s="4" t="n">
-        <v>50.55</v>
+        <v>50.93</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>48.4</v>
+        <v>51.44</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>AGARWALEYE</t>
+          <t>ETHOSLTD</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -4634,22 +4394,22 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>466.65</v>
+        <v>2436.9</v>
       </c>
       <c r="D110" s="4" t="n">
-        <v>58.62</v>
+        <v>55.24</v>
       </c>
       <c r="E110" s="4" t="n">
-        <v>52.8</v>
+        <v>49.05</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>52.15</v>
+        <v>49.44</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>SHAKTIPUMP</t>
+          <t>TVSSCS</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -4658,22 +4418,22 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>551.05</v>
+        <v>131.49</v>
       </c>
       <c r="D111" s="4" t="n">
-        <v>58.54</v>
+        <v>55.09</v>
       </c>
       <c r="E111" s="4" t="n">
-        <v>44.82</v>
+        <v>56.38</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>46.46</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>INDIGOPNTS</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -4682,22 +4442,22 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>691.8</v>
+        <v>1006.25</v>
       </c>
       <c r="D112" s="4" t="n">
-        <v>58.51</v>
+        <v>55.08</v>
       </c>
       <c r="E112" s="4" t="n">
-        <v>48.26</v>
+        <v>54.27</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>50.96</v>
+        <v>45.45</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>SOUTHBANK</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -4706,22 +4466,22 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>184.59</v>
+        <v>45.41</v>
       </c>
       <c r="D113" s="4" t="n">
-        <v>58.42</v>
+        <v>55.04</v>
       </c>
       <c r="E113" s="4" t="n">
-        <v>57.52</v>
+        <v>61.43</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>59.89</v>
+        <v>69.72</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>SUPRIYA</t>
+          <t>RCF</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -4730,22 +4490,22 @@
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>932.2</v>
+        <v>132.62</v>
       </c>
       <c r="D114" s="4" t="n">
-        <v>58.25</v>
+        <v>55.03</v>
       </c>
       <c r="E114" s="4" t="n">
-        <v>70</v>
+        <v>51.68</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>65.41</v>
+        <v>48.52</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>APLLTD</t>
+          <t>SAATVIKGL</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -4754,22 +4514,22 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>763</v>
+        <v>475.35</v>
       </c>
       <c r="D115" s="4" t="n">
-        <v>58.09</v>
+        <v>54.98</v>
       </c>
       <c r="E115" s="4" t="n">
-        <v>48.15</v>
+        <v>60.22</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>45.05</v>
+        <v/>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>NETWORK18</t>
+          <t>METROPOLIS</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -4778,22 +4538,22 @@
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>33.98</v>
+        <v>543.35</v>
       </c>
       <c r="D116" s="4" t="n">
-        <v>58.08</v>
+        <v>54.52</v>
       </c>
       <c r="E116" s="4" t="n">
-        <v>44.94</v>
+        <v>60.32</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>38.04</v>
+        <v>59.39</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>SKIPPER</t>
+          <t>EQUITASBNK</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -4802,22 +4562,22 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>543.3</v>
+        <v>75.14</v>
       </c>
       <c r="D117" s="4" t="n">
-        <v>58.06</v>
+        <v>54.28</v>
       </c>
       <c r="E117" s="4" t="n">
-        <v>67.59999999999999</v>
+        <v>62.17</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>61.53</v>
+        <v>55.22</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>BIRLACORPN</t>
+          <t>ASHOKA</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -4826,22 +4586,22 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>1018.3</v>
+        <v>131.03</v>
       </c>
       <c r="D118" s="4" t="n">
-        <v>57.61</v>
+        <v>54.27</v>
       </c>
       <c r="E118" s="4" t="n">
-        <v>51.78</v>
+        <v>45.13</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>44.8</v>
+        <v>43.76</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>TEXRAIL</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -4850,22 +4610,22 @@
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>274.7</v>
+        <v>110</v>
       </c>
       <c r="D119" s="4" t="n">
-        <v>57.48</v>
+        <v>54.24</v>
       </c>
       <c r="E119" s="4" t="n">
-        <v>68.64</v>
+        <v>48.3</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>68.89</v>
+        <v>43.94</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>NFL</t>
+          <t>LLOYDSENT</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -4874,22 +4634,22 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>77.86</v>
+        <v>73.17</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>57.47</v>
+        <v>54.16</v>
       </c>
       <c r="E120" s="4" t="n">
-        <v>49.06</v>
+        <v>58.86</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>45.83</v>
+        <v>58.66</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>ELLEN</t>
+          <t>DATAMATICS</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -4898,22 +4658,22 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>281.55</v>
+        <v>799.8</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>57.33</v>
+        <v>54.01</v>
       </c>
       <c r="E121" s="4" t="n">
-        <v>47.75</v>
+        <v>53.61</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v/>
+        <v>55.36</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>ELECTCAST</t>
+          <t>ALKYLAMINE</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -4922,22 +4682,22 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>81.34</v>
+        <v>1788.7</v>
       </c>
       <c r="D122" s="4" t="n">
-        <v>57.32</v>
+        <v>53.97</v>
       </c>
       <c r="E122" s="4" t="n">
-        <v>51.63</v>
+        <v>62.13</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>44.32</v>
+        <v>49.07</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>NEOGEN</t>
+          <t>KNRCON</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -4946,22 +4706,22 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>1932</v>
+        <v>134.2</v>
       </c>
       <c r="D123" s="4" t="n">
-        <v>57.15</v>
+        <v>53.91</v>
       </c>
       <c r="E123" s="4" t="n">
-        <v>65.72</v>
+        <v>47.87</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>58.67</v>
+        <v>36</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>YATHARTH</t>
+          <t>BIRLACORPN</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -4970,22 +4730,22 @@
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>839.75</v>
+        <v>1003.9</v>
       </c>
       <c r="D124" s="4" t="n">
-        <v>57.02</v>
+        <v>53.81</v>
       </c>
       <c r="E124" s="4" t="n">
-        <v>60.12</v>
+        <v>50.21</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>63.29</v>
+        <v>43.97</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>KITEX</t>
+          <t>SKFINDIA</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -4994,22 +4754,22 @@
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>163.41</v>
+        <v>1658</v>
       </c>
       <c r="D125" s="4" t="n">
-        <v>56.91</v>
+        <v>53.76</v>
       </c>
       <c r="E125" s="4" t="n">
-        <v>46.9</v>
+        <v>36.18</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>49.46</v>
+        <v>32.37</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>ALIVUS</t>
+          <t>KITEX</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -5018,22 +4778,22 @@
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>1070.3</v>
+        <v>162.43</v>
       </c>
       <c r="D126" s="4" t="n">
-        <v>56.8</v>
+        <v>53.64</v>
       </c>
       <c r="E126" s="4" t="n">
-        <v>60.75</v>
+        <v>46.49</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>60.19</v>
+        <v>49.26</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>YATHARTH</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -5042,22 +4802,22 @@
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>1162.3</v>
+        <v>837.05</v>
       </c>
       <c r="D127" s="4" t="n">
-        <v>56.74</v>
+        <v>53.48</v>
       </c>
       <c r="E127" s="4" t="n">
-        <v>59.8</v>
+        <v>59.69</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>66.14</v>
+        <v>63.16</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>IIFLCAPS</t>
+          <t>RAYMONDLSL</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -5066,22 +4826,22 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>344.4</v>
+        <v>794.95</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>56.61</v>
+        <v>53.14</v>
       </c>
       <c r="E128" s="4" t="n">
-        <v>57.16</v>
+        <v>42.78</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>58.81</v>
+        <v>26.84</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>ASHAPURMIN</t>
+          <t>TRANSRAILL</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -5090,22 +4850,22 @@
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>708.15</v>
+        <v>511.95</v>
       </c>
       <c r="D129" s="4" t="n">
-        <v>56.57</v>
+        <v>53.08</v>
       </c>
       <c r="E129" s="4" t="n">
-        <v>58.13</v>
+        <v>45.32</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>59.46</v>
+        <v>45.85</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>UJJIVANSFB</t>
+          <t>ARVINDFASN</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -5114,22 +4874,22 @@
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>57.27</v>
+        <v>469.25</v>
       </c>
       <c r="D130" s="4" t="n">
-        <v>56.47</v>
+        <v>52.89</v>
       </c>
       <c r="E130" s="4" t="n">
-        <v>52.95</v>
+        <v>51.63</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>58.27</v>
+        <v>51.45</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>STAR</t>
+          <t>SKIPPER</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -5138,22 +4898,22 @@
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>1110.9</v>
+        <v>533.15</v>
       </c>
       <c r="D131" s="4" t="n">
-        <v>56.16</v>
+        <v>52.7</v>
       </c>
       <c r="E131" s="4" t="n">
-        <v>62.19</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>61.25</v>
+        <v>60.38</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>LOTUSDEV</t>
+          <t>BANCOINDIA</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -5162,22 +4922,22 @@
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>142.48</v>
+        <v>658.85</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>56.06</v>
+        <v>52.28</v>
       </c>
       <c r="E132" s="4" t="n">
-        <v>48.52</v>
+        <v>54.43</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v/>
+        <v>59.12</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>OPTIEMUS</t>
+          <t>LXCHEM</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -5186,22 +4946,22 @@
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>440.85</v>
+        <v>155.99</v>
       </c>
       <c r="D133" s="4" t="n">
-        <v>56.05</v>
+        <v>51.9</v>
       </c>
       <c r="E133" s="4" t="n">
-        <v>50.89</v>
+        <v>52.66</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>48.66</v>
+        <v>40.85</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>RAIN</t>
+          <t>THYROCARE</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -5210,22 +4970,22 @@
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>191</v>
+        <v>517.2</v>
       </c>
       <c r="D134" s="4" t="n">
-        <v>56.04</v>
+        <v>51.9</v>
       </c>
       <c r="E134" s="4" t="n">
-        <v>68.77</v>
+        <v>64.77</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>58.77</v>
+        <v>65.62</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>PARKHOSPS</t>
+          <t>UTLSOLAR</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -5234,13 +4994,13 @@
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>277.6</v>
+        <v>309.5</v>
       </c>
       <c r="D135" s="4" t="n">
-        <v>55.9</v>
+        <v>51.77</v>
       </c>
       <c r="E135" s="4" t="n">
-        <v>77.7</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="F135" s="4" t="n">
         <v/>
@@ -5249,7 +5009,7 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>MIDHANI</t>
+          <t>RATNAMANI</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -5258,22 +5018,22 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>437</v>
+        <v>2647.1</v>
       </c>
       <c r="D136" s="4" t="n">
-        <v>55.84</v>
+        <v>51.55</v>
       </c>
       <c r="E136" s="4" t="n">
-        <v>66.34999999999999</v>
+        <v>55.46</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>57.42</v>
+        <v>50.91</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>TDPOWERSYS</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -5282,22 +5042,22 @@
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>1235.2</v>
+        <v>1255.1</v>
       </c>
       <c r="D137" s="4" t="n">
-        <v>55.82</v>
+        <v>51.39</v>
       </c>
       <c r="E137" s="4" t="n">
-        <v>63.24</v>
+        <v>67.83</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>63.25</v>
+        <v>79.65000000000001</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>ATLANTAELE</t>
+          <t>UJJIVANSFB</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -5306,22 +5066,22 @@
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>1915.7</v>
+        <v>56.14</v>
       </c>
       <c r="D138" s="4" t="n">
-        <v>55.59</v>
+        <v>51.32</v>
       </c>
       <c r="E138" s="4" t="n">
-        <v>69.81</v>
+        <v>51.01</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v/>
+        <v>57.45</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>SHAILY</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -5330,22 +5090,22 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>1272.7</v>
+        <v>2849.7</v>
       </c>
       <c r="D139" s="4" t="n">
-        <v>55.55</v>
+        <v>51.27</v>
       </c>
       <c r="E139" s="4" t="n">
-        <v>69.59</v>
+        <v>61.26</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>81.01000000000001</v>
+        <v>68.59</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>CRAMC</t>
+          <t>BALAMINES</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -5354,22 +5114,22 @@
         </is>
       </c>
       <c r="C140" s="4" t="n">
-        <v>254.6</v>
+        <v>1989</v>
       </c>
       <c r="D140" s="4" t="n">
-        <v>55.54</v>
+        <v>51.17</v>
       </c>
       <c r="E140" s="4" t="n">
-        <v>47.38</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v/>
+        <v>57.63</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>BLUESTONE</t>
+          <t>RAIN</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -5378,22 +5138,22 @@
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>522.8</v>
+        <v>185.49</v>
       </c>
       <c r="D141" s="4" t="n">
-        <v>55.54</v>
+        <v>51.02</v>
       </c>
       <c r="E141" s="4" t="n">
-        <v>52.21</v>
+        <v>65.63</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v/>
+        <v>57.75</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>SMARTWORKS</t>
+          <t>FINPIPE</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -5402,22 +5162,22 @@
         </is>
       </c>
       <c r="C142" s="4" t="n">
-        <v>462.8</v>
+        <v>176.25</v>
       </c>
       <c r="D142" s="4" t="n">
-        <v>55.45</v>
+        <v>51.02</v>
       </c>
       <c r="E142" s="4" t="n">
-        <v>53.98</v>
+        <v>48.82</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v/>
+        <v>44.9</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>WAAREERTL</t>
+          <t>MAHSCOOTER</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -5426,22 +5186,22 @@
         </is>
       </c>
       <c r="C143" s="4" t="n">
-        <v>988.05</v>
+        <v>12506</v>
       </c>
       <c r="D143" s="4" t="n">
-        <v>55.44</v>
+        <v>50.97</v>
       </c>
       <c r="E143" s="4" t="n">
-        <v>52.66</v>
+        <v>46.44</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v/>
+        <v>53.86</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>INDIASHLTR</t>
+          <t>VAIBHAVGBL</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -5450,22 +5210,22 @@
         </is>
       </c>
       <c r="C144" s="4" t="n">
-        <v>784.35</v>
+        <v>232.9</v>
       </c>
       <c r="D144" s="4" t="n">
-        <v>55.43</v>
+        <v>50.96</v>
       </c>
       <c r="E144" s="4" t="n">
-        <v>50.87</v>
+        <v>53.93</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>52.65</v>
+        <v>46.8</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>PURVA</t>
+          <t>IIFLCAPS</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -5474,22 +5234,22 @@
         </is>
       </c>
       <c r="C145" s="4" t="n">
-        <v>220.36</v>
+        <v>340.95</v>
       </c>
       <c r="D145" s="4" t="n">
-        <v>55.42</v>
+        <v>50.84</v>
       </c>
       <c r="E145" s="4" t="n">
-        <v>49.97</v>
+        <v>56.06</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>45.9</v>
+        <v>58.51</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>DATAMATICS</t>
+          <t>SAFARI</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -5498,22 +5258,22 @@
         </is>
       </c>
       <c r="C146" s="4" t="n">
-        <v>801.5</v>
+        <v>1590.6</v>
       </c>
       <c r="D146" s="4" t="n">
-        <v>55.34</v>
+        <v>50.83</v>
       </c>
       <c r="E146" s="4" t="n">
-        <v>54.04</v>
+        <v>45.1</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>55.52</v>
+        <v>42.83</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>DYNAMATECH</t>
+          <t>TANLA</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -5522,22 +5282,22 @@
         </is>
       </c>
       <c r="C147" s="4" t="n">
-        <v>10923</v>
+        <v>520.05</v>
       </c>
       <c r="D147" s="4" t="n">
-        <v>55.03</v>
+        <v>50.62</v>
       </c>
       <c r="E147" s="4" t="n">
-        <v>55.54</v>
+        <v>52.44</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>66.36</v>
+        <v>44.35</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>EUREKAFORB</t>
+          <t>ORKLAINDIA</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -5546,22 +5306,22 @@
         </is>
       </c>
       <c r="C148" s="4" t="n">
-        <v>468.75</v>
+        <v>621.3</v>
       </c>
       <c r="D148" s="4" t="n">
-        <v>55.03</v>
+        <v>50.46</v>
       </c>
       <c r="E148" s="4" t="n">
-        <v>43.95</v>
+        <v>49.28</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>42.89</v>
+        <v/>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>ADVENZYMES</t>
+          <t>MAHSEAMLES</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -5570,22 +5330,22 @@
         </is>
       </c>
       <c r="C149" s="4" t="n">
-        <v>373.7</v>
+        <v>628.4</v>
       </c>
       <c r="D149" s="4" t="n">
-        <v>54.95</v>
+        <v>50.33</v>
       </c>
       <c r="E149" s="4" t="n">
-        <v>66.68000000000001</v>
+        <v>59.22</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>57.1</v>
+        <v>52.25</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>V2RETAIL</t>
+          <t>JUSTDIAL</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -5594,22 +5354,22 @@
         </is>
       </c>
       <c r="C150" s="4" t="n">
-        <v>236.85</v>
+        <v>537.7</v>
       </c>
       <c r="D150" s="4" t="n">
-        <v>54.89</v>
+        <v>50.27</v>
       </c>
       <c r="E150" s="4" t="n">
-        <v>58.86</v>
+        <v>38.19</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>68.37</v>
+        <v>35.69</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>SUBROS</t>
+          <t>NETWORK18</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -5618,22 +5378,22 @@
         </is>
       </c>
       <c r="C151" s="4" t="n">
-        <v>747.45</v>
+        <v>32.63</v>
       </c>
       <c r="D151" s="4" t="n">
-        <v>54.87</v>
+        <v>50.21</v>
       </c>
       <c r="E151" s="4" t="n">
-        <v>47.14</v>
+        <v>41.72</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>51.21</v>
+        <v>36.75</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>BANCOINDIA</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -5642,22 +5402,22 @@
         </is>
       </c>
       <c r="C152" s="4" t="n">
-        <v>663.05</v>
+        <v>1191</v>
       </c>
       <c r="D152" s="4" t="n">
-        <v>54.84</v>
+        <v>50.19</v>
       </c>
       <c r="E152" s="4" t="n">
-        <v>55.08</v>
+        <v>60.18</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>59.32</v>
+        <v>62.21</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>TEXRAIL</t>
+          <t>INDIASHLTR</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -5666,22 +5426,22 @@
         </is>
       </c>
       <c r="C153" s="4" t="n">
-        <v>109.29</v>
+        <v>768.75</v>
       </c>
       <c r="D153" s="4" t="n">
-        <v>54.82</v>
+        <v>50.11</v>
       </c>
       <c r="E153" s="4" t="n">
-        <v>48.03</v>
+        <v>48.18</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>43.86</v>
+        <v>51.18</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>WESTLIFE</t>
+          <t>ELECTCAST</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -5690,22 +5450,22 @@
         </is>
       </c>
       <c r="C154" s="4" t="n">
-        <v>467.1</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="D154" s="4" t="n">
-        <v>54.81</v>
+        <v>50.1</v>
       </c>
       <c r="E154" s="4" t="n">
-        <v>43.01</v>
+        <v>49.11</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>32.34</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>GAEL</t>
+          <t>MANYAVAR</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -5714,22 +5474,22 @@
         </is>
       </c>
       <c r="C155" s="4" t="n">
-        <v>159.98</v>
+        <v>412.6</v>
       </c>
       <c r="D155" s="4" t="n">
-        <v>54.36</v>
+        <v>49.91</v>
       </c>
       <c r="E155" s="4" t="n">
-        <v>62.78</v>
+        <v>38.44</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>63.49</v>
+        <v>28.78</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>DBREALTY</t>
+          <t>ALOKINDS</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -5738,22 +5498,22 @@
         </is>
       </c>
       <c r="C156" s="4" t="n">
-        <v>118.12</v>
+        <v>12.83</v>
       </c>
       <c r="D156" s="4" t="n">
-        <v>54.34</v>
+        <v>49.82</v>
       </c>
       <c r="E156" s="4" t="n">
-        <v>50.04</v>
+        <v>41.84</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>45.31</v>
+        <v>38.52</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>TIMETECHNO</t>
+          <t>CAPILLARY</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -5762,22 +5522,22 @@
         </is>
       </c>
       <c r="C157" s="4" t="n">
-        <v>178.42</v>
+        <v>507.55</v>
       </c>
       <c r="D157" s="4" t="n">
-        <v>54.1</v>
+        <v>49.8</v>
       </c>
       <c r="E157" s="4" t="n">
-        <v>47.37</v>
+        <v>40.24</v>
       </c>
       <c r="F157" s="4" t="n">
-        <v>50.95</v>
+        <v/>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>GAEL</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -5786,22 +5546,22 @@
         </is>
       </c>
       <c r="C158" s="4" t="n">
-        <v>443.1</v>
+        <v>158.27</v>
       </c>
       <c r="D158" s="4" t="n">
-        <v>53.97</v>
+        <v>49.76</v>
       </c>
       <c r="E158" s="4" t="n">
-        <v>50.3</v>
+        <v>61.68</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v>57.27</v>
+        <v>63.13</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>JUSTDIAL</t>
+          <t>NEOGEN</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -5810,22 +5570,22 @@
         </is>
       </c>
       <c r="C159" s="4" t="n">
-        <v>539.9</v>
+        <v>1874.8</v>
       </c>
       <c r="D159" s="4" t="n">
-        <v>53.95</v>
+        <v>49.56</v>
       </c>
       <c r="E159" s="4" t="n">
-        <v>38.61</v>
+        <v>62.86</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>35.89</v>
+        <v>57.74</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>MAHSEAMLES</t>
+          <t>HEMIPROP</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -5834,22 +5594,22 @@
         </is>
       </c>
       <c r="C160" s="4" t="n">
-        <v>630.65</v>
+        <v>139.55</v>
       </c>
       <c r="D160" s="4" t="n">
-        <v>53.85</v>
+        <v>49.54</v>
       </c>
       <c r="E160" s="4" t="n">
-        <v>58.93</v>
+        <v>50.95</v>
       </c>
       <c r="F160" s="4" t="n">
-        <v>52.16</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>MAHSCOOTER</t>
+          <t>BECTORFOOD</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -5858,22 +5618,22 @@
         </is>
       </c>
       <c r="C161" s="4" t="n">
-        <v>12597</v>
+        <v>182.67</v>
       </c>
       <c r="D161" s="4" t="n">
-        <v>53.71</v>
+        <v>49.49</v>
       </c>
       <c r="E161" s="4" t="n">
-        <v>47.17</v>
+        <v>39.13</v>
       </c>
       <c r="F161" s="4" t="n">
-        <v>54.33</v>
+        <v>39.75</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>DBL</t>
+          <t>GMMPFAUDLR</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -5882,22 +5642,22 @@
         </is>
       </c>
       <c r="C162" s="4" t="n">
-        <v>439.5</v>
+        <v>804.55</v>
       </c>
       <c r="D162" s="4" t="n">
-        <v>53.32</v>
+        <v>49.4</v>
       </c>
       <c r="E162" s="4" t="n">
-        <v>48.7</v>
+        <v>37.43</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>49.85</v>
+        <v>39.18</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>AXISCADES</t>
+          <t>SKYGOLD</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -5906,22 +5666,22 @@
         </is>
       </c>
       <c r="C163" s="4" t="n">
-        <v>1943.2</v>
+        <v>499.15</v>
       </c>
       <c r="D163" s="4" t="n">
-        <v>53.23</v>
+        <v>49.17</v>
       </c>
       <c r="E163" s="4" t="n">
-        <v>61.21</v>
+        <v>61.85</v>
       </c>
       <c r="F163" s="4" t="n">
-        <v>69.53</v>
+        <v>67.95999999999999</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>UTLSOLAR</t>
+          <t>ROUTE</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -5930,22 +5690,22 @@
         </is>
       </c>
       <c r="C164" s="4" t="n">
-        <v>311</v>
+        <v>525</v>
       </c>
       <c r="D164" s="4" t="n">
-        <v>53.19</v>
+        <v>49.15</v>
       </c>
       <c r="E164" s="4" t="n">
-        <v>67.61</v>
+        <v>43.38</v>
       </c>
       <c r="F164" s="4" t="n">
-        <v/>
+        <v>30.23</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>EMBDL</t>
+          <t>VIPIND</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -5954,22 +5714,22 @@
         </is>
       </c>
       <c r="C165" s="4" t="n">
-        <v>62.14</v>
+        <v>312.45</v>
       </c>
       <c r="D165" s="4" t="n">
-        <v>53.08</v>
+        <v>49.06</v>
       </c>
       <c r="E165" s="4" t="n">
-        <v>49.31</v>
+        <v>42.33</v>
       </c>
       <c r="F165" s="4" t="n">
-        <v>42.28</v>
+        <v>37.49</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>VGUARD</t>
+          <t>STAR</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -5978,22 +5738,22 @@
         </is>
       </c>
       <c r="C166" s="4" t="n">
-        <v>311.25</v>
+        <v>1082.2</v>
       </c>
       <c r="D166" s="4" t="n">
-        <v>52.76</v>
+        <v>48.97</v>
       </c>
       <c r="E166" s="4" t="n">
-        <v>43.5</v>
+        <v>57.75</v>
       </c>
       <c r="F166" s="4" t="n">
-        <v>43.54</v>
+        <v>59.27</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>SUDARSCHEM</t>
+          <t>JSLL</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -6002,22 +5762,22 @@
         </is>
       </c>
       <c r="C167" s="4" t="n">
-        <v>913.6</v>
+        <v>602.25</v>
       </c>
       <c r="D167" s="4" t="n">
-        <v>52.66</v>
+        <v>48.9</v>
       </c>
       <c r="E167" s="4" t="n">
-        <v>48.67</v>
+        <v>44.15</v>
       </c>
       <c r="F167" s="4" t="n">
-        <v>48.61</v>
+        <v>42.74</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>TRANSRAILL</t>
+          <t>KANSAINER</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -6026,22 +5786,22 @@
         </is>
       </c>
       <c r="C168" s="4" t="n">
-        <v>507.7</v>
+        <v>212.41</v>
       </c>
       <c r="D168" s="4" t="n">
-        <v>52.53</v>
+        <v>48.83</v>
       </c>
       <c r="E168" s="4" t="n">
-        <v>44.68</v>
+        <v>50.83</v>
       </c>
       <c r="F168" s="4" t="n">
-        <v>45.56</v>
+        <v>42.69</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>FINPIPE</t>
+          <t>CENTURYPLY</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -6050,22 +5810,22 @@
         </is>
       </c>
       <c r="C169" s="4" t="n">
-        <v>175.58</v>
+        <v>754.55</v>
       </c>
       <c r="D169" s="4" t="n">
-        <v>52.24</v>
+        <v>48.76</v>
       </c>
       <c r="E169" s="4" t="n">
-        <v>49.12</v>
+        <v>48.88</v>
       </c>
       <c r="F169" s="4" t="n">
-        <v>45</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>HGINFRA</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -6074,22 +5834,22 @@
         </is>
       </c>
       <c r="C170" s="4" t="n">
-        <v>582.85</v>
+        <v>265.6</v>
       </c>
       <c r="D170" s="4" t="n">
-        <v>52.22</v>
+        <v>48.6</v>
       </c>
       <c r="E170" s="4" t="n">
-        <v>43.18</v>
+        <v>62.97</v>
       </c>
       <c r="F170" s="4" t="n">
-        <v>37.04</v>
+        <v>66.59</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>HERITGFOOD</t>
+          <t>BBOX</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -6098,22 +5858,22 @@
         </is>
       </c>
       <c r="C171" s="4" t="n">
-        <v>330</v>
+        <v>957.9</v>
       </c>
       <c r="D171" s="4" t="n">
-        <v>52.2</v>
+        <v>48.54</v>
       </c>
       <c r="E171" s="4" t="n">
-        <v>39.75</v>
+        <v>70.5</v>
       </c>
       <c r="F171" s="4" t="n">
-        <v>43.88</v>
+        <v>71.16</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>SKYGOLD</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -6122,22 +5882,22 @@
         </is>
       </c>
       <c r="C172" s="4" t="n">
-        <v>509.4</v>
+        <v>433.8</v>
       </c>
       <c r="D172" s="4" t="n">
-        <v>52.17</v>
+        <v>48.47</v>
       </c>
       <c r="E172" s="4" t="n">
-        <v>63.75</v>
+        <v>48.64</v>
       </c>
       <c r="F172" s="4" t="n">
-        <v>69.25</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>SHAREINDIA</t>
+          <t>TMB</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -6146,22 +5906,22 @@
         </is>
       </c>
       <c r="C173" s="4" t="n">
-        <v>138.9</v>
+        <v>732.6</v>
       </c>
       <c r="D173" s="4" t="n">
-        <v>52.13</v>
+        <v>48.37</v>
       </c>
       <c r="E173" s="4" t="n">
-        <v>46.5</v>
+        <v>61.79</v>
       </c>
       <c r="F173" s="4" t="n">
-        <v>40.32</v>
+        <v>70.04000000000001</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>VIPIND</t>
+          <t>TSFINV</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -6170,22 +5930,22 @@
         </is>
       </c>
       <c r="C174" s="4" t="n">
-        <v>317.5</v>
+        <v>396.75</v>
       </c>
       <c r="D174" s="4" t="n">
-        <v>52.12</v>
+        <v>48.34</v>
       </c>
       <c r="E174" s="4" t="n">
-        <v>43.61</v>
+        <v>45.46</v>
       </c>
       <c r="F174" s="4" t="n">
-        <v>38.22</v>
+        <v>52.52</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>WAKEFIT</t>
+          <t>ELLEN</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -6194,13 +5954,13 @@
         </is>
       </c>
       <c r="C175" s="4" t="n">
-        <v>127.43</v>
+        <v>269.85</v>
       </c>
       <c r="D175" s="4" t="n">
-        <v>51.94</v>
+        <v>48.3</v>
       </c>
       <c r="E175" s="4" t="n">
-        <v>36.5</v>
+        <v>44.18</v>
       </c>
       <c r="F175" s="4" t="n">
         <v/>
@@ -6209,7 +5969,7 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>TIPSMUSIC</t>
+          <t>CAMPUS</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -6218,22 +5978,22 @@
         </is>
       </c>
       <c r="C176" s="4" t="n">
-        <v>653</v>
+        <v>237.85</v>
       </c>
       <c r="D176" s="4" t="n">
-        <v>51.85</v>
+        <v>48.17</v>
       </c>
       <c r="E176" s="4" t="n">
-        <v>58.92</v>
+        <v>43.57</v>
       </c>
       <c r="F176" s="4" t="n">
-        <v>59.22</v>
+        <v>43.44</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>GMMPFAUDLR</t>
+          <t>SUDARSCHEM</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -6242,22 +6002,22 @@
         </is>
       </c>
       <c r="C177" s="4" t="n">
-        <v>809.65</v>
+        <v>891.25</v>
       </c>
       <c r="D177" s="4" t="n">
-        <v>51.7</v>
+        <v>48.12</v>
       </c>
       <c r="E177" s="4" t="n">
-        <v>37.6</v>
+        <v>46.45</v>
       </c>
       <c r="F177" s="4" t="n">
-        <v>39.25</v>
+        <v>47.55</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>IONEXCHANG</t>
+          <t>AARTIDRUGS</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -6266,22 +6026,22 @@
         </is>
       </c>
       <c r="C178" s="4" t="n">
-        <v>370.4</v>
+        <v>372.7</v>
       </c>
       <c r="D178" s="4" t="n">
-        <v>51.49</v>
+        <v>48.1</v>
       </c>
       <c r="E178" s="4" t="n">
-        <v>48.05</v>
+        <v>46.81</v>
       </c>
       <c r="F178" s="4" t="n">
-        <v>43.52</v>
+        <v>44.03</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>FIEMIND</t>
+          <t>EUREKAFORB</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -6290,22 +6050,22 @@
         </is>
       </c>
       <c r="C179" s="4" t="n">
-        <v>2286.7</v>
+        <v>458.3</v>
       </c>
       <c r="D179" s="4" t="n">
-        <v>51.36</v>
+        <v>47.98</v>
       </c>
       <c r="E179" s="4" t="n">
-        <v>57.07</v>
+        <v>41.86</v>
       </c>
       <c r="F179" s="4" t="n">
-        <v>67.56999999999999</v>
+        <v>41.57</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>TANLA</t>
+          <t>PURVA</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -6314,22 +6074,22 @@
         </is>
       </c>
       <c r="C180" s="4" t="n">
-        <v>521.35</v>
+        <v>212.97</v>
       </c>
       <c r="D180" s="4" t="n">
-        <v>51.31</v>
+        <v>47.97</v>
       </c>
       <c r="E180" s="4" t="n">
-        <v>52.8</v>
+        <v>46.99</v>
       </c>
       <c r="F180" s="4" t="n">
-        <v>44.46</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>REDTAPE</t>
+          <t>CRAMC</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -6338,22 +6098,22 @@
         </is>
       </c>
       <c r="C181" s="4" t="n">
-        <v>134.13</v>
+        <v>247.61</v>
       </c>
       <c r="D181" s="4" t="n">
-        <v>51.1</v>
+        <v>47.87</v>
       </c>
       <c r="E181" s="4" t="n">
-        <v>52.93</v>
+        <v>44.48</v>
       </c>
       <c r="F181" s="4" t="n">
-        <v>35.4</v>
+        <v/>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>CELLO</t>
+          <t>SANOFICONR</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -6362,22 +6122,22 @@
         </is>
       </c>
       <c r="C182" s="4" t="n">
-        <v>390.2</v>
+        <v>4618.1</v>
       </c>
       <c r="D182" s="4" t="n">
-        <v>51.07</v>
+        <v>47.78</v>
       </c>
       <c r="E182" s="4" t="n">
-        <v>36.17</v>
+        <v>51.79</v>
       </c>
       <c r="F182" s="4" t="n">
-        <v>31.93</v>
+        <v>48.72</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>CRIZAC</t>
+          <t>GPPL</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -6386,22 +6146,22 @@
         </is>
       </c>
       <c r="C183" s="4" t="n">
-        <v>214.59</v>
+        <v>153.81</v>
       </c>
       <c r="D183" s="4" t="n">
-        <v>50.36</v>
+        <v>47.75</v>
       </c>
       <c r="E183" s="4" t="n">
-        <v>44.49</v>
+        <v>45.32</v>
       </c>
       <c r="F183" s="4" t="n">
-        <v/>
+        <v>50.12</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>CENTURYPLY</t>
+          <t>ATLANTAELE</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -6410,22 +6170,22 @@
         </is>
       </c>
       <c r="C184" s="4" t="n">
-        <v>758.5</v>
+        <v>1812</v>
       </c>
       <c r="D184" s="4" t="n">
-        <v>50.26</v>
+        <v>47.11</v>
       </c>
       <c r="E184" s="4" t="n">
-        <v>50.36</v>
+        <v>64.34999999999999</v>
       </c>
       <c r="F184" s="4" t="n">
-        <v>51.55</v>
+        <v/>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>CSBBANK</t>
+          <t>PRAJIND</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -6434,22 +6194,22 @@
         </is>
       </c>
       <c r="C185" s="4" t="n">
-        <v>365.5</v>
+        <v>348.65</v>
       </c>
       <c r="D185" s="4" t="n">
-        <v>50.15</v>
+        <v>47</v>
       </c>
       <c r="E185" s="4" t="n">
-        <v>45.35</v>
+        <v>49.15</v>
       </c>
       <c r="F185" s="4" t="n">
-        <v>50.56</v>
+        <v>43.09</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>SENCO</t>
+          <t>APOLLO</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -6458,22 +6218,22 @@
         </is>
       </c>
       <c r="C186" s="4" t="n">
-        <v>340.4</v>
+        <v>384.4</v>
       </c>
       <c r="D186" s="4" t="n">
-        <v>50.1</v>
+        <v>46.82</v>
       </c>
       <c r="E186" s="4" t="n">
-        <v>52.89</v>
+        <v>62.91</v>
       </c>
       <c r="F186" s="4" t="n">
-        <v>49.1</v>
+        <v>68.43000000000001</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>SKFINDIA</t>
+          <t>VGUARD</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -6482,22 +6242,22 @@
         </is>
       </c>
       <c r="C187" s="4" t="n">
-        <v>1638.3</v>
+        <v>306.2</v>
       </c>
       <c r="D187" s="4" t="n">
-        <v>50.09</v>
+        <v>46.8</v>
       </c>
       <c r="E187" s="4" t="n">
-        <v>34.74</v>
+        <v>41.01</v>
       </c>
       <c r="F187" s="4" t="n">
-        <v>32.1</v>
+        <v>42.26</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>LXCHEM</t>
+          <t>DBREALTY</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -6506,22 +6266,22 @@
         </is>
       </c>
       <c r="C188" s="4" t="n">
-        <v>152.37</v>
+        <v>112.96</v>
       </c>
       <c r="D188" s="4" t="n">
-        <v>50</v>
+        <v>46.57</v>
       </c>
       <c r="E188" s="4" t="n">
-        <v>50.88</v>
+        <v>47.69</v>
       </c>
       <c r="F188" s="4" t="n">
-        <v>39.95</v>
+        <v>44.48</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>GODREJAGRO</t>
+          <t>ORIENTCEM</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -6530,22 +6290,22 @@
         </is>
       </c>
       <c r="C189" s="4" t="n">
-        <v>574.95</v>
+        <v>133.92</v>
       </c>
       <c r="D189" s="4" t="n">
-        <v>49.85</v>
+        <v>46.44</v>
       </c>
       <c r="E189" s="4" t="n">
-        <v>45.89</v>
+        <v>35.34</v>
       </c>
       <c r="F189" s="4" t="n">
-        <v>45.59</v>
+        <v>35.38</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>AZAD</t>
+          <t>TIPSMUSIC</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -6554,22 +6314,22 @@
         </is>
       </c>
       <c r="C190" s="4" t="n">
-        <v>2095.2</v>
+        <v>637.85</v>
       </c>
       <c r="D190" s="4" t="n">
-        <v>49.82</v>
+        <v>46.33</v>
       </c>
       <c r="E190" s="4" t="n">
-        <v>59.91</v>
+        <v>56.49</v>
       </c>
       <c r="F190" s="4" t="n">
-        <v>62.11</v>
+        <v>57.94</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>MANYAVAR</t>
+          <t>NFL</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -6578,22 +6338,22 @@
         </is>
       </c>
       <c r="C191" s="4" t="n">
-        <v>412.5</v>
+        <v>75.18000000000001</v>
       </c>
       <c r="D191" s="4" t="n">
-        <v>49.65</v>
+        <v>46.3</v>
       </c>
       <c r="E191" s="4" t="n">
-        <v>38.23</v>
+        <v>45.29</v>
       </c>
       <c r="F191" s="4" t="n">
-        <v>28.71</v>
+        <v>44.69</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>CMSINFO</t>
+          <t>ASHAPURMIN</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -6602,22 +6362,22 @@
         </is>
       </c>
       <c r="C192" s="4" t="n">
-        <v>298.7</v>
+        <v>671.3</v>
       </c>
       <c r="D192" s="4" t="n">
-        <v>49.58</v>
+        <v>46</v>
       </c>
       <c r="E192" s="4" t="n">
-        <v>42.11</v>
+        <v>53.41</v>
       </c>
       <c r="F192" s="4" t="n">
-        <v>38.91</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>ZAGGLE</t>
+          <t>BALUFORGE</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -6626,22 +6386,22 @@
         </is>
       </c>
       <c r="C193" s="4" t="n">
-        <v>213.17</v>
+        <v>453.95</v>
       </c>
       <c r="D193" s="4" t="n">
-        <v>49.43</v>
+        <v>45.76</v>
       </c>
       <c r="E193" s="4" t="n">
-        <v>38.18</v>
+        <v>43.66</v>
       </c>
       <c r="F193" s="4" t="n">
-        <v>40.31</v>
+        <v>46.35</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>ETHOSLTD</t>
+          <t>MIDHANI</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -6650,22 +6410,22 @@
         </is>
       </c>
       <c r="C194" s="4" t="n">
-        <v>2380.9</v>
+        <v>413.05</v>
       </c>
       <c r="D194" s="4" t="n">
-        <v>49.24</v>
+        <v>45.63</v>
       </c>
       <c r="E194" s="4" t="n">
-        <v>46.4</v>
+        <v>58.18</v>
       </c>
       <c r="F194" s="4" t="n">
-        <v>48.29</v>
+        <v>55.25</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>LUMAXTECH</t>
+          <t>SHAREINDIA</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -6674,22 +6434,22 @@
         </is>
       </c>
       <c r="C195" s="4" t="n">
-        <v>1646.4</v>
+        <v>135.19</v>
       </c>
       <c r="D195" s="4" t="n">
-        <v>48.71</v>
+        <v>45.37</v>
       </c>
       <c r="E195" s="4" t="n">
-        <v>53.47</v>
+        <v>44.2</v>
       </c>
       <c r="F195" s="4" t="n">
-        <v>66.97</v>
+        <v>39.68</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>HEMIPROP</t>
+          <t>FIEMIND</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -6698,22 +6458,22 @@
         </is>
       </c>
       <c r="C196" s="4" t="n">
-        <v>139.55</v>
+        <v>2229.1</v>
       </c>
       <c r="D196" s="4" t="n">
-        <v>48.69</v>
+        <v>45.27</v>
       </c>
       <c r="E196" s="4" t="n">
-        <v>51.25</v>
+        <v>53.1</v>
       </c>
       <c r="F196" s="4" t="n">
-        <v>49.3</v>
+        <v>66.15000000000001</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>ORIENTCEM</t>
+          <t>JAIBALAJI</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -6722,22 +6482,22 @@
         </is>
       </c>
       <c r="C197" s="4" t="n">
-        <v>135.51</v>
+        <v>68.19</v>
       </c>
       <c r="D197" s="4" t="n">
-        <v>48.65</v>
+        <v>45.03</v>
       </c>
       <c r="E197" s="4" t="n">
-        <v>35.88</v>
+        <v>45.78</v>
       </c>
       <c r="F197" s="4" t="n">
-        <v>35.51</v>
+        <v>41.08</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>FEDFINA</t>
+          <t>AWFIS</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -6746,22 +6506,22 @@
         </is>
       </c>
       <c r="C198" s="4" t="n">
-        <v>154.57</v>
+        <v>304.85</v>
       </c>
       <c r="D198" s="4" t="n">
-        <v>48.6</v>
+        <v>44.64</v>
       </c>
       <c r="E198" s="4" t="n">
-        <v>57.79</v>
+        <v>38.45</v>
       </c>
       <c r="F198" s="4" t="n">
-        <v>58.93</v>
+        <v>32.23</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>RTNPOWER</t>
+          <t>AZAD</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -6770,22 +6530,22 @@
         </is>
       </c>
       <c r="C199" s="4" t="n">
-        <v>9.369999999999999</v>
+        <v>2020.1</v>
       </c>
       <c r="D199" s="4" t="n">
-        <v>48.57</v>
+        <v>44.23</v>
       </c>
       <c r="E199" s="4" t="n">
-        <v>49.11</v>
+        <v>56.63</v>
       </c>
       <c r="F199" s="4" t="n">
-        <v>47.22</v>
+        <v>60.89</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>WEBELSOLAR</t>
+          <t>HGINFRA</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -6794,22 +6554,22 @@
         </is>
       </c>
       <c r="C200" s="4" t="n">
-        <v>104.71</v>
+        <v>567.5</v>
       </c>
       <c r="D200" s="4" t="n">
-        <v>48.55</v>
+        <v>44.21</v>
       </c>
       <c r="E200" s="4" t="n">
-        <v>55.43</v>
+        <v>41.95</v>
       </c>
       <c r="F200" s="4" t="n">
-        <v>53.2</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>GSFC</t>
+          <t>STARCEMENT</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -6818,22 +6578,22 @@
         </is>
       </c>
       <c r="C201" s="4" t="n">
-        <v>165.44</v>
+        <v>210.65</v>
       </c>
       <c r="D201" s="4" t="n">
-        <v>48.5</v>
+        <v>44.19</v>
       </c>
       <c r="E201" s="4" t="n">
-        <v>45.91</v>
+        <v>44.44</v>
       </c>
       <c r="F201" s="4" t="n">
-        <v>45.96</v>
+        <v>49.78</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>PCJEWELLER</t>
+          <t>INDIAGLYCO</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -6842,22 +6602,22 @@
         </is>
       </c>
       <c r="C202" s="4" t="n">
-        <v>8.91</v>
+        <v>955.45</v>
       </c>
       <c r="D202" s="4" t="n">
-        <v>48.47</v>
+        <v>43.99</v>
       </c>
       <c r="E202" s="4" t="n">
-        <v>44.11</v>
+        <v>49.36</v>
       </c>
       <c r="F202" s="4" t="n">
-        <v>46.63</v>
+        <v>57.67</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>JKLAKSHMI</t>
+          <t>V2RETAIL</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -6866,22 +6626,22 @@
         </is>
       </c>
       <c r="C203" s="4" t="n">
-        <v>605.5</v>
+        <v>221.23</v>
       </c>
       <c r="D203" s="4" t="n">
-        <v>48.31</v>
+        <v>43.98</v>
       </c>
       <c r="E203" s="4" t="n">
-        <v>38.83</v>
+        <v>52.44</v>
       </c>
       <c r="F203" s="4" t="n">
-        <v>41.2</v>
+        <v>64.20999999999999</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>IMFA</t>
+          <t>GSFC</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -6890,22 +6650,22 @@
         </is>
       </c>
       <c r="C204" s="4" t="n">
-        <v>1429.1</v>
+        <v>163.13</v>
       </c>
       <c r="D204" s="4" t="n">
-        <v>48.17</v>
+        <v>43.94</v>
       </c>
       <c r="E204" s="4" t="n">
-        <v>54.93</v>
+        <v>44.61</v>
       </c>
       <c r="F204" s="4" t="n">
-        <v>66.44</v>
+        <v>45.47</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>RTNINDIA</t>
+          <t>BAJAJELEC</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -6914,22 +6674,22 @@
         </is>
       </c>
       <c r="C205" s="4" t="n">
-        <v>35.07</v>
+        <v>322.35</v>
       </c>
       <c r="D205" s="4" t="n">
-        <v>47.99</v>
+        <v>43.93</v>
       </c>
       <c r="E205" s="4" t="n">
-        <v>47.46</v>
+        <v>32.53</v>
       </c>
       <c r="F205" s="4" t="n">
-        <v>41.81</v>
+        <v>28.55</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>SHAILY</t>
+          <t>WEBELSOLAR</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -6938,22 +6698,22 @@
         </is>
       </c>
       <c r="C206" s="4" t="n">
-        <v>2803.8</v>
+        <v>101.48</v>
       </c>
       <c r="D206" s="4" t="n">
-        <v>47.87</v>
+        <v>43.6</v>
       </c>
       <c r="E206" s="4" t="n">
-        <v>60.25</v>
+        <v>53.05</v>
       </c>
       <c r="F206" s="4" t="n">
-        <v>67.55</v>
+        <v>52.29</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>PICCADIL</t>
+          <t>GHCL</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -6962,22 +6722,22 @@
         </is>
       </c>
       <c r="C207" s="4" t="n">
-        <v>579</v>
+        <v>429.1</v>
       </c>
       <c r="D207" s="4" t="n">
-        <v>47.78</v>
+        <v>43.52</v>
       </c>
       <c r="E207" s="4" t="n">
-        <v>48.51</v>
+        <v>37.71</v>
       </c>
       <c r="F207" s="4" t="n">
-        <v/>
+        <v>41.68</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>STARCEMENT</t>
+          <t>CELLO</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -6986,22 +6746,22 @@
         </is>
       </c>
       <c r="C208" s="4" t="n">
-        <v>213.25</v>
+        <v>378.45</v>
       </c>
       <c r="D208" s="4" t="n">
-        <v>47.6</v>
+        <v>43.37</v>
       </c>
       <c r="E208" s="4" t="n">
-        <v>45.99</v>
+        <v>34.16</v>
       </c>
       <c r="F208" s="4" t="n">
-        <v>50.58</v>
+        <v>30.58</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>PRICOLLTD</t>
+          <t>WAKEFIT</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -7010,22 +6770,22 @@
         </is>
       </c>
       <c r="C209" s="4" t="n">
-        <v>559.15</v>
+        <v>119.83</v>
       </c>
       <c r="D209" s="4" t="n">
-        <v>47.49</v>
+        <v>43.36</v>
       </c>
       <c r="E209" s="4" t="n">
-        <v>48.14</v>
+        <v>34.17</v>
       </c>
       <c r="F209" s="4" t="n">
-        <v>56.69</v>
+        <v/>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>TSFINV</t>
+          <t>DYNAMATECH</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -7034,22 +6794,22 @@
         </is>
       </c>
       <c r="C210" s="4" t="n">
-        <v>395.4</v>
+        <v>10232</v>
       </c>
       <c r="D210" s="4" t="n">
-        <v>47.38</v>
+        <v>43.32</v>
       </c>
       <c r="E210" s="4" t="n">
-        <v>45.29</v>
+        <v>50.81</v>
       </c>
       <c r="F210" s="4" t="n">
-        <v>52.47</v>
+        <v>61.63</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>ORKLAINDIA</t>
+          <t>ZAGGLE</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -7058,22 +6818,22 @@
         </is>
       </c>
       <c r="C211" s="4" t="n">
-        <v>619.1</v>
+        <v>205.6</v>
       </c>
       <c r="D211" s="4" t="n">
-        <v>47.21</v>
+        <v>43.08</v>
       </c>
       <c r="E211" s="4" t="n">
-        <v>49.03</v>
+        <v>36.59</v>
       </c>
       <c r="F211" s="4" t="n">
-        <v/>
+        <v>39.58</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>KANSAINER</t>
+          <t>MASTEK</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -7082,22 +6842,22 @@
         </is>
       </c>
       <c r="C212" s="4" t="n">
-        <v>211.13</v>
+        <v>1575.2</v>
       </c>
       <c r="D212" s="4" t="n">
-        <v>47.18</v>
+        <v>42.7</v>
       </c>
       <c r="E212" s="4" t="n">
-        <v>49.54</v>
+        <v>39.22</v>
       </c>
       <c r="F212" s="4" t="n">
-        <v>42.21</v>
+        <v>38.73</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>KPIGREEN</t>
+          <t>JKLAKSHMI</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -7106,22 +6866,22 @@
         </is>
       </c>
       <c r="C213" s="4" t="n">
-        <v>409.15</v>
+        <v>594.6</v>
       </c>
       <c r="D213" s="4" t="n">
-        <v>47.17</v>
+        <v>42.64</v>
       </c>
       <c r="E213" s="4" t="n">
-        <v>46.98</v>
+        <v>37.72</v>
       </c>
       <c r="F213" s="4" t="n">
-        <v>49.15</v>
+        <v>40.58</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>NESCO</t>
+          <t>RTNINDIA</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -7130,22 +6890,22 @@
         </is>
       </c>
       <c r="C214" s="4" t="n">
-        <v>1138</v>
+        <v>33.88</v>
       </c>
       <c r="D214" s="4" t="n">
-        <v>47.13</v>
+        <v>42.57</v>
       </c>
       <c r="E214" s="4" t="n">
-        <v>47.36</v>
+        <v>45.42</v>
       </c>
       <c r="F214" s="4" t="n">
-        <v>53.82</v>
+        <v>41.17</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>GHCL</t>
+          <t>RTNPOWER</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -7154,22 +6914,22 @@
         </is>
       </c>
       <c r="C215" s="4" t="n">
-        <v>435.4</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="D215" s="4" t="n">
-        <v>46.93</v>
+        <v>42.42</v>
       </c>
       <c r="E215" s="4" t="n">
-        <v>39.56</v>
+        <v>46.47</v>
       </c>
       <c r="F215" s="4" t="n">
-        <v>42.16</v>
+        <v>46.41</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>RENUKA</t>
+          <t>TARC</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -7178,22 +6938,22 @@
         </is>
       </c>
       <c r="C216" s="4" t="n">
-        <v>23.09</v>
+        <v>123.77</v>
       </c>
       <c r="D216" s="4" t="n">
-        <v>46.48</v>
+        <v>42.01</v>
       </c>
       <c r="E216" s="4" t="n">
-        <v>39.88</v>
+        <v>38.91</v>
       </c>
       <c r="F216" s="4" t="n">
-        <v>37.3</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>CAMPUS</t>
+          <t>PRSMJOHNSN</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -7202,22 +6962,22 @@
         </is>
       </c>
       <c r="C217" s="4" t="n">
-        <v>237.45</v>
+        <v>117.92</v>
       </c>
       <c r="D217" s="4" t="n">
-        <v>46.29</v>
+        <v>41.92</v>
       </c>
       <c r="E217" s="4" t="n">
-        <v>43.79</v>
+        <v>38.24</v>
       </c>
       <c r="F217" s="4" t="n">
-        <v>43.51</v>
+        <v>41.41</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>MASTEK</t>
+          <t>RENUKA</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -7226,22 +6986,22 @@
         </is>
       </c>
       <c r="C218" s="4" t="n">
-        <v>1605.5</v>
+        <v>22.4</v>
       </c>
       <c r="D218" s="4" t="n">
-        <v>46.28</v>
+        <v>41.74</v>
       </c>
       <c r="E218" s="4" t="n">
-        <v>40.92</v>
+        <v>37.7</v>
       </c>
       <c r="F218" s="4" t="n">
-        <v>39.29</v>
+        <v>36.43</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>GPPL</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -7250,22 +7010,22 @@
         </is>
       </c>
       <c r="C219" s="4" t="n">
-        <v>153.08</v>
+        <v>181.8</v>
       </c>
       <c r="D219" s="4" t="n">
-        <v>46.25</v>
+        <v>41.66</v>
       </c>
       <c r="E219" s="4" t="n">
-        <v>44.6</v>
+        <v>51.19</v>
       </c>
       <c r="F219" s="4" t="n">
-        <v>49.89</v>
+        <v>56.11</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>AARTIDRUGS</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -7274,22 +7034,22 @@
         </is>
       </c>
       <c r="C220" s="4" t="n">
-        <v>370.35</v>
+        <v>522.5</v>
       </c>
       <c r="D220" s="4" t="n">
-        <v>46.08</v>
+        <v>41.66</v>
       </c>
       <c r="E220" s="4" t="n">
-        <v>45.65</v>
+        <v>40.72</v>
       </c>
       <c r="F220" s="4" t="n">
-        <v>43.72</v>
+        <v>42.73</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>JSFB</t>
+          <t>KPIGREEN</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -7298,22 +7058,22 @@
         </is>
       </c>
       <c r="C221" s="4" t="n">
-        <v>460.1</v>
+        <v>398.7</v>
       </c>
       <c r="D221" s="4" t="n">
-        <v>45.97</v>
+        <v>41.64</v>
       </c>
       <c r="E221" s="4" t="n">
-        <v>55.43</v>
+        <v>44.91</v>
       </c>
       <c r="F221" s="4" t="n">
-        <v>51.07</v>
+        <v>48.37</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>FEDFINA</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -7322,22 +7082,22 @@
         </is>
       </c>
       <c r="C222" s="4" t="n">
-        <v>186.65</v>
+        <v>148.37</v>
       </c>
       <c r="D222" s="4" t="n">
-        <v>45.84</v>
+        <v>41.57</v>
       </c>
       <c r="E222" s="4" t="n">
-        <v>53.78</v>
+        <v>51.81</v>
       </c>
       <c r="F222" s="4" t="n">
-        <v>57.37</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>MOIL</t>
+          <t>GODREJAGRO</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -7346,22 +7106,22 @@
         </is>
       </c>
       <c r="C223" s="4" t="n">
-        <v>293.85</v>
+        <v>562.05</v>
       </c>
       <c r="D223" s="4" t="n">
-        <v>45.63</v>
+        <v>41.45</v>
       </c>
       <c r="E223" s="4" t="n">
-        <v>44.18</v>
+        <v>43.58</v>
       </c>
       <c r="F223" s="4" t="n">
-        <v>46.82</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>BAJAJELEC</t>
+          <t>LUMAXTECH</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -7370,22 +7130,22 @@
         </is>
       </c>
       <c r="C224" s="4" t="n">
-        <v>325.65</v>
+        <v>1548.9</v>
       </c>
       <c r="D224" s="4" t="n">
-        <v>45.52</v>
+        <v>41.21</v>
       </c>
       <c r="E224" s="4" t="n">
-        <v>33.03</v>
+        <v>48.75</v>
       </c>
       <c r="F224" s="4" t="n">
-        <v>28.87</v>
+        <v>63.41</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>TARC</t>
+          <t>PICCADIL</t>
         </is>
       </c>
       <c r="B225" s="3" t="inlineStr">
@@ -7394,22 +7154,22 @@
         </is>
       </c>
       <c r="C225" s="4" t="n">
-        <v>126.18</v>
+        <v>564.75</v>
       </c>
       <c r="D225" s="4" t="n">
-        <v>45.01</v>
+        <v>40.88</v>
       </c>
       <c r="E225" s="4" t="n">
-        <v>40.62</v>
+        <v>45.44</v>
       </c>
       <c r="F225" s="4" t="n">
-        <v>45.46</v>
+        <v/>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>PNGJL</t>
+          <t>JSFB</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -7418,22 +7178,22 @@
         </is>
       </c>
       <c r="C226" s="4" t="n">
-        <v>552.8</v>
+        <v>448.5</v>
       </c>
       <c r="D226" s="4" t="n">
-        <v>44.84</v>
+        <v>40.53</v>
       </c>
       <c r="E226" s="4" t="n">
-        <v>45.06</v>
+        <v>52.53</v>
       </c>
       <c r="F226" s="4" t="n">
-        <v>42.89</v>
+        <v>49.68</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>PRSMJOHNSN</t>
+          <t>CMSINFO</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -7442,22 +7202,22 @@
         </is>
       </c>
       <c r="C227" s="4" t="n">
-        <v>119.26</v>
+        <v>291.1</v>
       </c>
       <c r="D227" s="4" t="n">
-        <v>44.27</v>
+        <v>40.42</v>
       </c>
       <c r="E227" s="4" t="n">
-        <v>39.57</v>
+        <v>39.24</v>
       </c>
       <c r="F227" s="4" t="n">
-        <v>41.83</v>
+        <v>38</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>SENCO</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -7466,22 +7226,22 @@
         </is>
       </c>
       <c r="C228" s="4" t="n">
-        <v>527.75</v>
+        <v>323.55</v>
       </c>
       <c r="D228" s="4" t="n">
-        <v>43.85</v>
+        <v>40.07</v>
       </c>
       <c r="E228" s="4" t="n">
-        <v>41.85</v>
+        <v>48.63</v>
       </c>
       <c r="F228" s="4" t="n">
-        <v>43.38</v>
+        <v>47.61</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>JAIBALAJI</t>
+          <t>GOKULAGRO</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -7490,22 +7250,22 @@
         </is>
       </c>
       <c r="C229" s="4" t="n">
-        <v>67.97</v>
+        <v>217.58</v>
       </c>
       <c r="D229" s="4" t="n">
-        <v>43.84</v>
+        <v>39.93</v>
       </c>
       <c r="E229" s="4" t="n">
-        <v>45.56</v>
+        <v>57.5</v>
       </c>
       <c r="F229" s="4" t="n">
-        <v>41.03</v>
+        <v>65.06</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>BALUFORGE</t>
+          <t>PCJEWELLER</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -7514,22 +7274,22 @@
         </is>
       </c>
       <c r="C230" s="4" t="n">
-        <v>448.75</v>
+        <v>8.57</v>
       </c>
       <c r="D230" s="4" t="n">
-        <v>43.41</v>
+        <v>39.92</v>
       </c>
       <c r="E230" s="4" t="n">
-        <v>42.6</v>
+        <v>41.69</v>
       </c>
       <c r="F230" s="4" t="n">
-        <v>46.06</v>
+        <v>45.75</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>SHARDACROP</t>
+          <t>SANDUMA</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -7538,22 +7298,22 @@
         </is>
       </c>
       <c r="C231" s="4" t="n">
-        <v>900.8</v>
+        <v>207.03</v>
       </c>
       <c r="D231" s="4" t="n">
-        <v>43.38</v>
+        <v>39.57</v>
       </c>
       <c r="E231" s="4" t="n">
-        <v>45.58</v>
+        <v>48.79</v>
       </c>
       <c r="F231" s="4" t="n">
-        <v>53.96</v>
+        <v>56.67</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>VIKRAMSOLR</t>
+          <t>RALLIS</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -7562,22 +7322,22 @@
         </is>
       </c>
       <c r="C232" s="4" t="n">
-        <v>200.42</v>
+        <v>227.52</v>
       </c>
       <c r="D232" s="4" t="n">
-        <v>43.1</v>
+        <v>39.39</v>
       </c>
       <c r="E232" s="4" t="n">
-        <v>41.65</v>
+        <v>39.95</v>
       </c>
       <c r="F232" s="4" t="n">
-        <v/>
+        <v>44.46</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>SANDUMA</t>
+          <t>SHARDACROP</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -7586,22 +7346,22 @@
         </is>
       </c>
       <c r="C233" s="4" t="n">
-        <v>211.72</v>
+        <v>876.55</v>
       </c>
       <c r="D233" s="4" t="n">
-        <v>43.09</v>
+        <v>39.22</v>
       </c>
       <c r="E233" s="4" t="n">
-        <v>50.57</v>
+        <v>44.25</v>
       </c>
       <c r="F233" s="4" t="n">
-        <v>57.71</v>
+        <v>53.24</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>GOKULAGRO</t>
+          <t>HCG</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -7610,22 +7370,22 @@
         </is>
       </c>
       <c r="C234" s="4" t="n">
-        <v>221.77</v>
+        <v>600.4</v>
       </c>
       <c r="D234" s="4" t="n">
-        <v>43.04</v>
+        <v>39.17</v>
       </c>
       <c r="E234" s="4" t="n">
-        <v>59.29</v>
+        <v>47.94</v>
       </c>
       <c r="F234" s="4" t="n">
-        <v>65.98</v>
+        <v>56.04</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>INDIAGLYCO</t>
+          <t>MEDPLUS</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -7634,22 +7394,22 @@
         </is>
       </c>
       <c r="C235" s="4" t="n">
-        <v>957.75</v>
+        <v>835</v>
       </c>
       <c r="D235" s="4" t="n">
-        <v>42.28</v>
+        <v>38.99</v>
       </c>
       <c r="E235" s="4" t="n">
-        <v>49.97</v>
+        <v>47.4</v>
       </c>
       <c r="F235" s="4" t="n">
-        <v>57.98</v>
+        <v>52.28</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>AWFIS</t>
+          <t>CRIZAC</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -7658,22 +7418,22 @@
         </is>
       </c>
       <c r="C236" s="4" t="n">
-        <v>304.1</v>
+        <v>201.39</v>
       </c>
       <c r="D236" s="4" t="n">
-        <v>42.18</v>
+        <v>38.93</v>
       </c>
       <c r="E236" s="4" t="n">
-        <v>38.47</v>
+        <v>39.84</v>
       </c>
       <c r="F236" s="4" t="n">
-        <v>32.24</v>
+        <v/>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>PFOCUS</t>
+          <t>GMRP&amp;UI</t>
         </is>
       </c>
       <c r="B237" s="3" t="inlineStr">
@@ -7682,22 +7442,22 @@
         </is>
       </c>
       <c r="C237" s="4" t="n">
-        <v>231.72</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="D237" s="4" t="n">
-        <v>41.78</v>
+        <v>37.54</v>
       </c>
       <c r="E237" s="4" t="n">
-        <v>43.84</v>
+        <v>43.12</v>
       </c>
       <c r="F237" s="4" t="n">
-        <v>58.46</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>JKPAPER</t>
+          <t>ADVENZYMES</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -7706,22 +7466,22 @@
         </is>
       </c>
       <c r="C238" s="4" t="n">
-        <v>349.9</v>
+        <v>348.35</v>
       </c>
       <c r="D238" s="4" t="n">
-        <v>41.52</v>
+        <v>37.4</v>
       </c>
       <c r="E238" s="4" t="n">
-        <v>46.49</v>
+        <v>55.84</v>
       </c>
       <c r="F238" s="4" t="n">
-        <v>48.7</v>
+        <v>53.19</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>HCG</t>
+          <t>JYOTHYLAB</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
@@ -7730,22 +7490,22 @@
         </is>
       </c>
       <c r="C239" s="4" t="n">
-        <v>610.95</v>
+        <v>200.4</v>
       </c>
       <c r="D239" s="4" t="n">
-        <v>41.46</v>
+        <v>37.24</v>
       </c>
       <c r="E239" s="4" t="n">
-        <v>50.2</v>
+        <v>33.17</v>
       </c>
       <c r="F239" s="4" t="n">
-        <v>57.01</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>PRAJIND</t>
+          <t>JKPAPER</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -7754,22 +7514,22 @@
         </is>
       </c>
       <c r="C240" s="4" t="n">
-        <v>340.5</v>
+        <v>341.9</v>
       </c>
       <c r="D240" s="4" t="n">
-        <v>40.86</v>
+        <v>37.1</v>
       </c>
       <c r="E240" s="4" t="n">
-        <v>47.1</v>
+        <v>43.38</v>
       </c>
       <c r="F240" s="4" t="n">
-        <v>42.55</v>
+        <v>47.65</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>JSLL</t>
+          <t>PNGJL</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
@@ -7778,22 +7538,22 @@
         </is>
       </c>
       <c r="C241" s="4" t="n">
-        <v>557.2</v>
+        <v>532.65</v>
       </c>
       <c r="D241" s="4" t="n">
-        <v>40.52</v>
+        <v>36.96</v>
       </c>
       <c r="E241" s="4" t="n">
-        <v>39.49</v>
+        <v>42.66</v>
       </c>
       <c r="F241" s="4" t="n">
-        <v>41.83</v>
+        <v>40.65</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>MEDPLUS</t>
+          <t>NESCO</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -7802,22 +7562,22 @@
         </is>
       </c>
       <c r="C242" s="4" t="n">
-        <v>844.45</v>
+        <v>1087.8</v>
       </c>
       <c r="D242" s="4" t="n">
-        <v>40.17</v>
+        <v>36.67</v>
       </c>
       <c r="E242" s="4" t="n">
-        <v>48.17</v>
+        <v>43.94</v>
       </c>
       <c r="F242" s="4" t="n">
-        <v>52.78</v>
+        <v>51.39</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>JAYNECOIND</t>
+          <t>AXISCADES</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -7826,22 +7586,22 @@
         </is>
       </c>
       <c r="C243" s="4" t="n">
-        <v>89.68000000000001</v>
+        <v>1691</v>
       </c>
       <c r="D243" s="4" t="n">
-        <v>40.06</v>
+        <v>36.62</v>
       </c>
       <c r="E243" s="4" t="n">
-        <v>52.33</v>
+        <v>50</v>
       </c>
       <c r="F243" s="4" t="n">
-        <v>60.98</v>
+        <v>62.8</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>RALLIS</t>
+          <t>IMFA</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -7850,22 +7610,22 @@
         </is>
       </c>
       <c r="C244" s="4" t="n">
-        <v>229.78</v>
+        <v>1327</v>
       </c>
       <c r="D244" s="4" t="n">
-        <v>39.25</v>
+        <v>36.46</v>
       </c>
       <c r="E244" s="4" t="n">
-        <v>40.55</v>
+        <v>48.87</v>
       </c>
       <c r="F244" s="4" t="n">
-        <v>44.69</v>
+        <v>62.15</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>JYOTHYLAB</t>
+          <t>HAPPSTMNDS</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
@@ -7874,22 +7634,22 @@
         </is>
       </c>
       <c r="C245" s="4" t="n">
-        <v>202.28</v>
+        <v>342.45</v>
       </c>
       <c r="D245" s="4" t="n">
-        <v>37.89</v>
+        <v>35.99</v>
       </c>
       <c r="E245" s="4" t="n">
-        <v>33.57</v>
+        <v>34.2</v>
       </c>
       <c r="F245" s="4" t="n">
-        <v>36.52</v>
+        <v>24.07</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>CAPILLARY</t>
+          <t>JAYNECOIND</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -7898,22 +7658,22 @@
         </is>
       </c>
       <c r="C246" s="4" t="n">
-        <v>495.25</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="D246" s="4" t="n">
-        <v>37.89</v>
+        <v>34.93</v>
       </c>
       <c r="E246" s="4" t="n">
-        <v>36.65</v>
+        <v>49.14</v>
       </c>
       <c r="F246" s="4" t="n">
-        <v/>
+        <v>59.2</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>GMRP&amp;UI</t>
+          <t>PFOCUS</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
@@ -7922,22 +7682,22 @@
         </is>
       </c>
       <c r="C247" s="4" t="n">
-        <v>100.51</v>
+        <v>209.94</v>
       </c>
       <c r="D247" s="4" t="n">
-        <v>37.25</v>
+        <v>33.5</v>
       </c>
       <c r="E247" s="4" t="n">
-        <v>43.58</v>
+        <v>38.64</v>
       </c>
       <c r="F247" s="4" t="n">
-        <v>50.72</v>
+        <v>54.56</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>ENTERO</t>
+          <t>MOIL</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -7946,22 +7706,22 @@
         </is>
       </c>
       <c r="C248" s="4" t="n">
-        <v>1089.4</v>
+        <v>279.55</v>
       </c>
       <c r="D248" s="4" t="n">
-        <v>36.82</v>
+        <v>33.19</v>
       </c>
       <c r="E248" s="4" t="n">
-        <v>44.9</v>
+        <v>40.13</v>
       </c>
       <c r="F248" s="4" t="n">
-        <v>46.74</v>
+        <v>45</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>KSCL</t>
+          <t>VIKRAMSOLR</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
@@ -7970,22 +7730,22 @@
         </is>
       </c>
       <c r="C249" s="4" t="n">
-        <v>849.5</v>
+        <v>185.28</v>
       </c>
       <c r="D249" s="4" t="n">
-        <v>36.66</v>
+        <v>32.46</v>
       </c>
       <c r="E249" s="4" t="n">
-        <v>42.99</v>
+        <v>37.31</v>
       </c>
       <c r="F249" s="4" t="n">
-        <v>46.3</v>
+        <v/>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>HAPPSTMNDS</t>
+          <t>CSBBANK</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
@@ -7994,16 +7754,16 @@
         </is>
       </c>
       <c r="C250" s="4" t="n">
-        <v>345.35</v>
+        <v>324.6</v>
       </c>
       <c r="D250" s="4" t="n">
-        <v>36.15</v>
+        <v>29.47</v>
       </c>
       <c r="E250" s="4" t="n">
-        <v>34.83</v>
+        <v>36.51</v>
       </c>
       <c r="F250" s="4" t="n">
-        <v>24.25</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="251">
@@ -8018,16 +7778,16 @@
         </is>
       </c>
       <c r="C251" s="4" t="n">
-        <v>967.7</v>
+        <v>962.2</v>
       </c>
       <c r="D251" s="4" t="n">
-        <v>25.32</v>
+        <v>28.72</v>
       </c>
       <c r="E251" s="4" t="n">
-        <v>40.87</v>
+        <v>40.57</v>
       </c>
       <c r="F251" s="4" t="n">
-        <v>55.08</v>
+        <v>54.84</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Micro250_stocks.xlsx
+++ b/reports/Micro250_stocks.xlsx
@@ -43,7 +43,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +53,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +87,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -94,6 +99,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -461,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -546,37 +560,37 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>182.61</v>
+        <v>198.84</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>86.95</v>
+        <v>89.06</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>85.23999999999999</v>
+        <v>87.23999999999999</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>88.59</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>58.18</v>
+        <v>56.61</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>103.72</v>
+        <v>110.43</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>93.22</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>19443983</v>
+        <v>19898789</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>24607</v>
+        <v>26737</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>WABAG</t>
+          <t>ASTRAMICRO</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -585,37 +599,37 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>2110.8</v>
+        <v>1848.5</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>86.44</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>79.91</v>
+        <v>85.66</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>69.31</v>
+        <v>79.04000000000001</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>20.18</v>
+        <v>26.31</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>1447.34</v>
+        <v>1180.89</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>1432.08</v>
+        <v>1133.01</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>712039</v>
+        <v>1627652</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>13129</v>
+        <v>17551</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>PGIL</t>
+          <t>MSTCLTD</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -624,37 +638,37 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>2071</v>
+        <v>715.7</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>79.72</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>70.03</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>70.69</v>
+        <v>61.89</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>46.8</v>
+        <v>20.73</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>1567.82</v>
+        <v>503.5</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>1532.31</v>
+        <v>502.23</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>232006</v>
+        <v>2435624</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>9542</v>
+        <v>5039</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>ICIL</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -663,37 +677,37 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>426.4</v>
+        <v>1788.3</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>73.79000000000001</v>
+        <v>68.25</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>74.88</v>
+        <v>78.67</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>65.09999999999999</v>
+        <v>76.14</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>20.88</v>
+        <v>36.65</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>296.05</v>
+        <v>1240.32</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>293.5</v>
+        <v>1171.51</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>1433676</v>
+        <v>366801</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>8457</v>
+        <v>11948</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>ARVIND</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -702,37 +716,37 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1325.1</v>
+        <v>569.05</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>73.01000000000001</v>
+        <v>68.05</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>68.90000000000001</v>
+        <v>83.51000000000001</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>71.75</v>
+        <v>73.56</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>22.1</v>
+        <v>20.38</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1049.91</v>
+        <v>415.47</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>1014.72</v>
+        <v>399.9</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>439408</v>
+        <v>981539</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>17518</v>
+        <v>14916</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>ARVIND</t>
+          <t>SKIPPER</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -741,37 +755,37 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>547.25</v>
+        <v>574.95</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>71.59999999999999</v>
+        <v>67.06</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>82.16</v>
+        <v>70.16</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>74.68000000000001</v>
+        <v>63.3</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>26.92</v>
+        <v>60.23</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>403.1</v>
+        <v>466.39</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>389.63</v>
+        <v>462.73</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1044280</v>
+        <v>1049438</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>14469</v>
+        <v>6491</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>SANSERA</t>
+          <t>PGIL</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -780,37 +794,37 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>3146.2</v>
+        <v>2016.3</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>70.41</v>
+        <v>66.41</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>77.34</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>79.2</v>
+        <v>69.87</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>25.55</v>
+        <v>29.26</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>2288.28</v>
+        <v>1598.27</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>2150.29</v>
+        <v>1557.03</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>398145</v>
+        <v>174669</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>19663</v>
+        <v>9312</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>AKUMS</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -819,37 +833,37 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>5594.2</v>
+        <v>626.8</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>68.31999999999999</v>
+        <v>65.47</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>71.73999999999999</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>81.84999999999999</v>
+        <v>54.57</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>20.65</v>
+        <v>35.68</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3866.87</v>
+        <v>520.58</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>3620.46</v>
+        <v>517.4299999999999</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>222161</v>
+        <v>324618</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>17359</v>
+        <v>9596</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>SPARC</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -858,37 +872,37 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1750.3</v>
+        <v>239.37</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>67.52</v>
+        <v>65.08</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>77.84999999999999</v>
+        <v>74.23</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>76.12</v>
+        <v>61.34</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>39.63</v>
+        <v>29.26</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1194.83</v>
+        <v>169.71</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1133.62</v>
+        <v>164.97</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>552345</v>
+        <v>6409404</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>11719</v>
+        <v>7768</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AKUMS</t>
+          <t>AVL</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -897,37 +911,37 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>609.35</v>
+        <v>638.55</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>63.69</v>
+        <v>64.27</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>67.26000000000001</v>
+        <v>66.73</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>52.6</v>
+        <v>66.77</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>37.35</v>
+        <v>20.36</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>515.7</v>
+        <v>527.86</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>514.26</v>
+        <v>517.49</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>350432</v>
+        <v>336097</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>9302</v>
+        <v>8246</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>KIRLPNU</t>
+          <t>APOLLO</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -936,37 +950,37 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1899.2</v>
+        <v>450.05</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>63.49</v>
+        <v>63.88</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>80.38</v>
+        <v>69.56</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>70.70999999999999</v>
+        <v>74.33</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>31.3</v>
+        <v>41.15</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1371.15</v>
+        <v>307.41</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1334.18</v>
+        <v>289.18</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>246045</v>
+        <v>24916643</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>12388</v>
+        <v>16724</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENGG</t>
+          <t>SKYGOLD</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -975,37 +989,37 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>84.91</v>
+        <v>560</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>62.61</v>
+        <v>63.81</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>72.94</v>
+        <v>67.91</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>63.35</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>42.75</v>
+        <v>26.56</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>61.44</v>
+        <v>420.44</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>60.86</v>
+        <v>402.14</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>21408146</v>
+        <v>1457765</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>12101</v>
+        <v>8673</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>MANORAMA</t>
+          <t>KSB</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1014,37 +1028,37 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1573.5</v>
+        <v>936.1</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>61.07</v>
+        <v>63.59</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>60.04</v>
+        <v>62.9</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>64.95999999999999</v>
+        <v>59.39</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>32.47</v>
+        <v>28.92</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1402.59</v>
+        <v>828.61</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1379.67</v>
+        <v>819.85</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>152434</v>
+        <v>177937</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>9421</v>
+        <v>16292</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>TIPSMUSIC</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1053,37 +1067,37 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>613.35</v>
+        <v>684.65</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>60.3</v>
+        <v>63</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>81.81</v>
+        <v>62.13</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>90.48999999999999</v>
+        <v>60.73</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>51.14</v>
+        <v>28.15</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>308.45</v>
+        <v>599.9400000000001</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>269.95</v>
+        <v>594.84</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>2713201</v>
+        <v>231075</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>29942</v>
+        <v>8752</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>VARROC</t>
+          <t>TMB</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1092,37 +1106,37 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>611.65</v>
+        <v>778.65</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>58.08</v>
+        <v>62.96</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>61.1</v>
+        <v>65.94</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>56.79</v>
+        <v>72.62</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>23.42</v>
+        <v>28.08</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>563.9</v>
+        <v>640.2</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>563.87</v>
+        <v>612.01</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>122267</v>
+        <v>322435</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>9336</v>
+        <v>12330</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>SPARC</t>
+          <t>YATHARTH</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1131,37 +1145,37 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>224.92</v>
+        <v>865.55</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>57.15</v>
+        <v>62.41</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>71.17</v>
+        <v>62.34</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>59.26</v>
+        <v>64.33</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>35.7</v>
+        <v>26.93</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>164.31</v>
+        <v>753.59</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>160.72</v>
+        <v>732.3</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>9230898</v>
+        <v>382214</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>7286</v>
+        <v>8340</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>MTARTECH</t>
+          <t>BALAMINES</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1170,37 +1184,37 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>7976.5</v>
+        <v>2194.2</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>56.22</v>
+        <v>61.07</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>75.06</v>
+        <v>76.66</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>87.93000000000001</v>
+        <v>61.06</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>57.22</v>
+        <v>24.25</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>4949.73</v>
+        <v>1526.68</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>4419.59</v>
+        <v>1494.5</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>2147408</v>
+        <v>459830</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>24546</v>
+        <v>7109</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>METROPOLIS</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1209,37 +1223,37 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>543.35</v>
+        <v>189.27</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>54.52</v>
+        <v>58.84</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>60.32</v>
+        <v>60.52</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>59.39</v>
+        <v>60.9</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>25.23</v>
+        <v>25.68</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>496.72</v>
+        <v>175.32</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>492.42</v>
+        <v>170.95</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>223604</v>
+        <v>901270</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>11299</v>
+        <v>6096</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>EQUITASBNK</t>
+          <t>STAR</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1248,37 +1262,37 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>75.14</v>
+        <v>1126.8</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>54.28</v>
+        <v>58.67</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>62.17</v>
+        <v>62.24</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>55.22</v>
+        <v>61.52</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>40.35</v>
+        <v>29.67</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>66.52</v>
+        <v>997.4299999999999</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>65.90000000000001</v>
+        <v>974.97</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>4300889</v>
+        <v>203699</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>8623</v>
+        <v>10386</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>SKIPPER</t>
+          <t>METROPOLIS</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1287,37 +1301,37 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>533.15</v>
+        <v>556</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>52.7</v>
+        <v>58.63</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>64.76000000000001</v>
+        <v>62.13</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>60.38</v>
+        <v>60.3</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>56.85</v>
+        <v>39.58</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>459.48</v>
+        <v>499.63</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>457.29</v>
+        <v>494.94</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1033451</v>
+        <v>242645</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>6012</v>
+        <v>11528</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>LLOYDSENT</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1326,37 +1340,37 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1255.1</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>51.39</v>
+        <v>58.31</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>67.83</v>
+        <v>60.78</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>79.65000000000001</v>
+        <v>59.81</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>33</v>
+        <v>50.2</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>975.36</v>
+        <v>64.73</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>905.35</v>
+        <v>63.93</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1595373</v>
+        <v>3899130</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>19607</v>
+        <v>11503</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>SHAILY</t>
+          <t>LLOYDSENGG</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1365,37 +1379,37 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2849.7</v>
+        <v>83.94</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>51.27</v>
+        <v>58.3</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>61.26</v>
+        <v>71.54000000000001</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>68.59</v>
+        <v>62.3</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>34.64</v>
+        <v>47.26</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2410.67</v>
+        <v>63.25</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>2319.58</v>
+        <v>62.24</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>383532</v>
+        <v>21539632</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>13109</v>
+        <v>11964</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>AZAD</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1404,37 +1418,37 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1191</v>
+        <v>2149.1</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>50.19</v>
+        <v>57.24</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>60.18</v>
+        <v>60.67</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>62.21</v>
+        <v>63.14</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>66.09999999999999</v>
+        <v>39.89</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1007.78</v>
+        <v>1857.59</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>966.37</v>
+        <v>1810.49</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>205341</v>
+        <v>443110</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>7829</v>
+        <v>13879</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>GAEL</t>
+          <t>NEOGEN</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1443,37 +1457,37 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>158.27</v>
+        <v>1968.3</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>49.76</v>
+        <v>56.8</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>61.68</v>
+        <v>65.48</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>63.13</v>
+        <v>58.77</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>20.3</v>
+        <v>30.71</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>143.02</v>
+        <v>1596.14</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>138.75</v>
+        <v>1566.95</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>691508</v>
+        <v>131169</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>7288</v>
+        <v>5390</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>NEOGEN</t>
+          <t>EQUITASBNK</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1482,37 +1496,37 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1874.8</v>
+        <v>76.3</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>49.56</v>
+        <v>56.07</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>62.86</v>
+        <v>62.99</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>57.74</v>
+        <v>55.67</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>38.19</v>
+        <v>50.82</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1566.27</v>
+        <v>67.13</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>1543.61</v>
+        <v>66.34</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>120838</v>
+        <v>4236095</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>5145</v>
+        <v>8728</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>SKYGOLD</t>
+          <t>BBOX</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1521,37 +1535,37 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>499.15</v>
+        <v>994.95</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>49.17</v>
+        <v>55.62</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>61.85</v>
+        <v>72.22</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>67.95999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>38.19</v>
+        <v>31.93</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>410.97</v>
+        <v>718.04</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>393.98</v>
+        <v>675.7</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1448527</v>
+        <v>745017</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>7728</v>
+        <v>17670</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>SHAILY</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1560,37 +1574,37 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>265.6</v>
+        <v>2901.6</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>48.6</v>
+        <v>53.89</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>62.97</v>
+        <v>62.4</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>66.59</v>
+        <v>69.72</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>37.17</v>
+        <v>31.78</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>232.6</v>
+        <v>2447.84</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>225.01</v>
+        <v>2353.56</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>2809444</v>
+        <v>345157</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>10027</v>
+        <v>13346</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>BBOX</t>
+          <t>KIRLPNU</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1599,37 +1613,37 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>957.9</v>
+        <v>1825.9</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>48.54</v>
+        <v>53.77</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>70.5</v>
+        <v>73.92</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>71.16</v>
+        <v>66.81</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>20.51</v>
+        <v>22.37</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>697.46</v>
+        <v>1406.02</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>657.5</v>
+        <v>1361.22</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>927938</v>
+        <v>255021</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>17025</v>
+        <v>11862</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>TMB</t>
+          <t>RAIN</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1638,37 +1652,37 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>732.6</v>
+        <v>187.74</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>48.37</v>
+        <v>52.81</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>61.79</v>
+        <v>66.19</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>70.04000000000001</v>
+        <v>57.91</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>29.56</v>
+        <v>27.7</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>631.61</v>
+        <v>153.44</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>603.87</v>
+        <v>150.22</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>297975</v>
+        <v>6523813</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>11599</v>
+        <v>6315</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>APOLLO</t>
+          <t>MIDHANI</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1677,31 +1691,148 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>384.4</v>
+        <v>427.85</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>46.82</v>
+        <v>52.34</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>62.91</v>
+        <v>61.48</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>68.43000000000001</v>
+        <v>56.72</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>53.36</v>
+        <v>34.39</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>297.93</v>
+        <v>382.37</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>281.04</v>
+        <v>377.83</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>30772072</v>
+        <v>1348920</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>14277</v>
+        <v>8015</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>KRN</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>1214.8</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>51.89</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>61.04</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>61.94</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>59.39</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>1024.66</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>981.5700000000001</v>
+      </c>
+      <c r="J32" s="4" t="n">
+        <v>135627</v>
+      </c>
+      <c r="K32" s="4" t="n">
+        <v>7952</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>STLTECH</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>576.8</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>51.11</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>75.43000000000001</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>84.48</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>68.89</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>330.6</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>289</v>
+      </c>
+      <c r="J33" s="4" t="n">
+        <v>2556221</v>
+      </c>
+      <c r="K33" s="4" t="n">
+        <v>29642</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>KTKBANK</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>263.4</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>45.53</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>61.92</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>64.91</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>34.21</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>235.37</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>227.54</v>
+      </c>
+      <c r="J34" s="4" t="n">
+        <v>2025654</v>
+      </c>
+      <c r="K34" s="4" t="n">
+        <v>9961</v>
       </c>
     </row>
   </sheetData>
@@ -1736,6 +1867,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1802,22 +1936,22 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>182.61</v>
+        <v>198.84</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>86.95</v>
+        <v>89.06</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>85.23999999999999</v>
+        <v>87.23999999999999</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>88.59</v>
+        <v>89.59999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>WABAG</t>
+          <t>QUESS</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -1826,22 +1960,22 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>2110.8</v>
+        <v>290.85</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>86.44</v>
+        <v>85.7</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>79.91</v>
+        <v>73.14</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>69.31</v>
+        <v>44.99</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>SKFINDUS</t>
+          <t>ASTRAMICRO</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -1850,22 +1984,22 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>2906</v>
+        <v>1848.5</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>83.45</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>70.61</v>
+        <v>85.66</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v/>
+        <v>79.04000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>PGIL</t>
+          <t>JLHL</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -1874,22 +2008,22 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>2071</v>
+        <v>1456.3</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>79.72</v>
+        <v>82.01000000000001</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>70.03</v>
+        <v>64.61</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>70.69</v>
+        <v>55.31</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>ASTRAMICRO</t>
+          <t>WEWORK</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -1898,22 +2032,22 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1721.7</v>
+        <v>739.65</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>78.89</v>
+        <v>77.73999999999999</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>83.37</v>
+        <v>73.09</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>77.17</v>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>RBA</t>
+          <t>IXIGO</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1922,22 +2056,22 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>79.38</v>
+        <v>222.23</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>78.84999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>73.94</v>
+        <v>60.53</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>49.64</v>
+        <v>57.33</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>CCAVENUE</t>
+          <t>STYL</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1946,22 +2080,22 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>16.07</v>
+        <v>325.65</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>77.63</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>54.49</v>
+        <v>66.3</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>44.12</v>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>RELAXO</t>
+          <t>PICCADIL</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -1970,22 +2104,22 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>413.55</v>
+        <v>647.35</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>77.61</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>64.27</v>
+        <v>61</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>41.72</v>
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>RELIGARE</t>
+          <t>VIYASH</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1994,22 +2128,22 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>274.43</v>
+        <v>294.15</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>77.42</v>
+        <v>75.64</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>68.55</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>58.96</v>
+        <v>68.79000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AVL</t>
+          <t>EMIL</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2018,22 +2152,22 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>660.5</v>
+        <v>140.68</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>76.86</v>
+        <v>75.62</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>71.5</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>70.39</v>
+        <v>52.22</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>GOKEX</t>
+          <t>OPTIEMUS</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2042,22 +2176,22 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>854.75</v>
+        <v>521.55</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>76.64</v>
+        <v>75.51000000000001</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>62.11</v>
+        <v>61.07</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>53.91</v>
+        <v>53.38</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>SHRIPISTON</t>
+          <t>RATEGAIN</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -2066,22 +2200,22 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>4033</v>
+        <v>941.05</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>74.87</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>67.98999999999999</v>
+        <v>78.31</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>75.43000000000001</v>
+        <v>66.59</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>SWSOLAR</t>
+          <t>CCAVENUE</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -2090,22 +2224,22 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>246.68</v>
+        <v>17.08</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>74.76000000000001</v>
+        <v>74.48999999999999</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>62.32</v>
+        <v>59.15</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>44.82</v>
+        <v>46.52</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>ICIL</t>
+          <t>PCJEWELLER</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -2114,22 +2248,22 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>426.4</v>
+        <v>10.3</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>73.79000000000001</v>
+        <v>74.08</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>74.88</v>
+        <v>55.17</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>65.09999999999999</v>
+        <v>50.81</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>STYL</t>
+          <t>TRIVENI</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -2138,22 +2272,22 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>308.75</v>
+        <v>458.65</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>73.20999999999999</v>
+        <v>73.88</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>62.37</v>
+        <v>68.11</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v/>
+        <v>60.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>QUESS</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -2162,22 +2296,22 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>251.1</v>
+        <v>2037.9</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>73.11</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>64.73</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>39.99</v>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>SFL</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -2186,22 +2320,22 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1325.1</v>
+        <v>766.55</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>73.01000000000001</v>
+        <v>73.11</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>68.90000000000001</v>
+        <v>71.44</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>71.75</v>
+        <v>51.7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>KIRLOSBROS</t>
+          <t>SANSERA</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2210,22 +2344,22 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>2018.5</v>
+        <v>3251.5</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>73.01000000000001</v>
+        <v>72.97</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>66.08</v>
+        <v>78.86</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>58.53</v>
+        <v>79.98</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>RUBICON</t>
+          <t>TSFINV</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -2234,22 +2368,22 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1416.6</v>
+        <v>455.5</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>72.8</v>
+        <v>72.81</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>91.87</v>
+        <v>58.77</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v/>
+        <v>57.02</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>BORORENEW</t>
+          <t>SWSOLAR</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -2258,22 +2392,22 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>615.7</v>
+        <v>246.9</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>71.73999999999999</v>
+        <v>72.62</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>64.06999999999999</v>
+        <v>62.57</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>57.17</v>
+        <v>44.96</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>ARVIND</t>
+          <t>VARROC</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -2282,22 +2416,22 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>547.25</v>
+        <v>667.55</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>71.59999999999999</v>
+        <v>72.42</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>82.16</v>
+        <v>69.23999999999999</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>74.68000000000001</v>
+        <v>60.66</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>GREAVESCOT</t>
+          <t>SKFINDUS</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -2306,22 +2440,22 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>214.09</v>
+        <v>2825.8</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>71.06</v>
+        <v>72.20999999999999</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>66.25</v>
+        <v>66.17</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>55.93</v>
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>SANSERA</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -2330,22 +2464,22 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3146.2</v>
+        <v>235.46</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>70.41</v>
+        <v>71.72</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>77.34</v>
+        <v>63.28</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>79.2</v>
+        <v>49.78</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>KSB</t>
+          <t>INDIAGLYCO</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -2354,22 +2488,22 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>934.35</v>
+        <v>1075.75</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>70.06999999999999</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>62.74</v>
+        <v>59.95</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>59.86</v>
+        <v>62.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>REFEX</t>
+          <t>GREAVESCOT</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -2378,22 +2512,22 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>348.95</v>
+        <v>226.57</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>69.66</v>
+        <v>70.76000000000001</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>67.58</v>
+        <v>69.61</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>55.01</v>
+        <v>57.79</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>ANUP</t>
+          <t>WELENT</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -2402,22 +2536,22 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2297.9</v>
+        <v>603.25</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>69.48</v>
+        <v>70.45999999999999</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>60.58</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>53.7</v>
+        <v>61.59</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>THANGAMAYL</t>
+          <t>MSTCLTD</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -2426,22 +2560,22 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>5594.2</v>
+        <v>715.7</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>68.31999999999999</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>71.73999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>81.84999999999999</v>
+        <v>61.89</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>SFL</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -2450,22 +2584,22 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>725.6</v>
+        <v>1359.6</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>68</v>
+        <v>69.64</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>68.13</v>
+        <v>70.68000000000001</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>49.66</v>
+        <v>72.88</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>INOXGREEN</t>
+          <t>BORORENEW</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -2474,22 +2608,22 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>204.15</v>
+        <v>621.7</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>67.95</v>
+        <v>69.59</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>59.08</v>
+        <v>64.56</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>55.93</v>
+        <v>57.51</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>JLHL</t>
+          <t>BLUESTONE</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -2498,22 +2632,22 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1375.3</v>
+        <v>569.65</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>67.87</v>
+        <v>69.47</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>58.68</v>
+        <v>58.09</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>52.18</v>
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>AGARWALEYE</t>
+          <t>REFEX</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -2522,22 +2656,22 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>484.65</v>
+        <v>358.4</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>67.73999999999999</v>
+        <v>69.34</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>56.24</v>
+        <v>69.25</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>54.31</v>
+        <v>55.86</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>PNCINFRA</t>
+          <t>PRICOLLTD</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -2546,22 +2680,22 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>232.3</v>
+        <v>621.7</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>67.64</v>
+        <v>69.3</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>54.09</v>
+        <v>58.2</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>43.3</v>
+        <v>61.29</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>APLLTD</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -2570,22 +2704,22 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>1750.3</v>
+        <v>823.7</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>67.52</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>77.84999999999999</v>
+        <v>58.32</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>76.12</v>
+        <v>48.66</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>GRWRHITECH</t>
+          <t>VMART</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -2594,22 +2728,22 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>6688.5</v>
+        <v>797.9</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>66.58</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>75.76000000000001</v>
+        <v>65.34</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>68.28</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>AEQUS</t>
+          <t>SHRIPISTON</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -2618,22 +2752,22 @@
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>228.95</v>
+        <v>4197.5</v>
       </c>
       <c r="D36" s="4" t="n">
-        <v>66.14</v>
+        <v>68.62</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>72.59</v>
+        <v>70.33</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v/>
+        <v>76.64</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>SMARTWORKS</t>
+          <t>GOKEX</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -2642,22 +2776,22 @@
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>489.55</v>
+        <v>858.9</v>
       </c>
       <c r="D37" s="4" t="n">
-        <v>66.13</v>
+        <v>68.29000000000001</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>59.34</v>
+        <v>62.32</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v/>
+        <v>53.88</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>SUBROS</t>
+          <t>ALIVUS</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -2666,22 +2800,22 @@
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>835.45</v>
+        <v>1157.7</v>
       </c>
       <c r="D38" s="4" t="n">
-        <v>65.43000000000001</v>
+        <v>68.25</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>57.06</v>
+        <v>69.52</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>54.95</v>
+        <v>64.47</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>MSTCLTD</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -2690,22 +2824,22 @@
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>647.4</v>
+        <v>1788.3</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>65.16</v>
+        <v>68.25</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>67.94</v>
+        <v>78.67</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>58.81</v>
+        <v>76.14</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>LOTUSDEV</t>
+          <t>ARVIND</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -2714,22 +2848,22 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>150.69</v>
+        <v>569.05</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>64.98999999999999</v>
+        <v>68.05</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>54.74</v>
+        <v>83.51000000000001</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v/>
+        <v>73.56</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>SAMHI</t>
+          <t>ICIL</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -2738,22 +2872,22 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>179.85</v>
+        <v>426.5</v>
       </c>
       <c r="D41" s="4" t="n">
-        <v>64.95</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>58.57</v>
+        <v>74.83</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>51</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>SHAKTIPUMP</t>
+          <t>GRWRHITECH</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -2762,22 +2896,22 @@
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>580.9</v>
+        <v>6875</v>
       </c>
       <c r="D42" s="4" t="n">
-        <v>64.84999999999999</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>49.73</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>48.09</v>
+        <v>69.03</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>WELENT</t>
+          <t>PNCINFRA</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -2786,22 +2920,22 @@
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>572.45</v>
+        <v>236</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>64.53</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>66.51000000000001</v>
+        <v>55.91</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>59.58</v>
+        <v>44.16</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>IONEXCHANG</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -2810,22 +2944,22 @@
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>1893.3</v>
+        <v>418.35</v>
       </c>
       <c r="D44" s="4" t="n">
-        <v>64.31</v>
+        <v>67.09</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>71.94</v>
+        <v>58.77</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v/>
+        <v>48.47</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>VIYASH</t>
+          <t>SKIPPER</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -2834,22 +2968,22 @@
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>269.3</v>
+        <v>574.95</v>
       </c>
       <c r="D45" s="4" t="n">
-        <v>64.01000000000001</v>
+        <v>67.06</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>70.33</v>
+        <v>70.16</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>65.65000000000001</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>OPTIEMUS</t>
+          <t>SUDEEPPHRM</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -2858,22 +2992,22 @@
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>469.3</v>
+        <v>868.05</v>
       </c>
       <c r="D46" s="4" t="n">
-        <v>64</v>
+        <v>66.93000000000001</v>
       </c>
       <c r="E46" s="4" t="n">
-        <v>55.19</v>
+        <v>69.34</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>50.5</v>
+        <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>VMART</t>
+          <t>WABAG</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -2882,22 +3016,22 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>762.1</v>
+        <v>2080.9</v>
       </c>
       <c r="D47" s="4" t="n">
-        <v>63.87</v>
+        <v>66.81</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>61.4</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>52.54</v>
+        <v>69.04000000000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>EIEL</t>
+          <t>JAMNAAUTO</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -2906,22 +3040,22 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>218.55</v>
+        <v>138.75</v>
       </c>
       <c r="D48" s="4" t="n">
-        <v>63.8</v>
+        <v>66.76000000000001</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>58.22</v>
+        <v>59.67</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>45.97</v>
+        <v>60.23</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>AKUMS</t>
+          <t>PGIL</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -2930,22 +3064,22 @@
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>609.35</v>
+        <v>2016.3</v>
       </c>
       <c r="D49" s="4" t="n">
-        <v>63.69</v>
+        <v>66.41</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>67.26000000000001</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>52.6</v>
+        <v>69.87</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>KIRLPNU</t>
+          <t>ANUP</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -2954,22 +3088,22 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>1899.2</v>
+        <v>2313.4</v>
       </c>
       <c r="D50" s="4" t="n">
-        <v>63.49</v>
+        <v>66.17</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>80.38</v>
+        <v>60.47</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>70.70999999999999</v>
+        <v>53.57</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>AURIONPRO</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -2978,22 +3112,22 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>895.1</v>
+        <v>6159.5</v>
       </c>
       <c r="D51" s="4" t="n">
-        <v>63.46</v>
+        <v>65.78</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>48.94</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>44.2</v>
+        <v>80.78</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>ALIVUS</t>
+          <t>PRIVISCL</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -3002,22 +3136,22 @@
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>1108.3</v>
+        <v>3694.9</v>
       </c>
       <c r="D52" s="4" t="n">
-        <v>63.46</v>
+        <v>65.61</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>64.42</v>
+        <v>67.45999999999999</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>61.91</v>
+        <v>71.95</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>PARAS</t>
+          <t>AKUMS</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -3026,22 +3160,22 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>1233.75</v>
+        <v>626.8</v>
       </c>
       <c r="D53" s="4" t="n">
-        <v>63.43</v>
+        <v>65.47</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>68.48999999999999</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>66.59999999999999</v>
+        <v>54.57</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>HCC</t>
+          <t>INDIGOPNTS</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -3050,22 +3184,22 @@
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>26.76</v>
+        <v>1065.9</v>
       </c>
       <c r="D54" s="4" t="n">
-        <v>62.88</v>
+        <v>65.29000000000001</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>64.39</v>
+        <v>58.74</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>50.91</v>
+        <v>47.36</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>RATEGAIN</t>
+          <t>SHILPAMED</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -3074,22 +3208,22 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>840.95</v>
+        <v>608.95</v>
       </c>
       <c r="D55" s="4" t="n">
-        <v>62.77</v>
+        <v>65.22</v>
       </c>
       <c r="E55" s="4" t="n">
-        <v>73.52</v>
+        <v>84.31</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>63.16</v>
+        <v>73.06999999999999</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENGG</t>
+          <t>WESTLIFE</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -3098,22 +3232,22 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>84.91</v>
+        <v>507.8</v>
       </c>
       <c r="D56" s="4" t="n">
-        <v>62.61</v>
+        <v>65.16</v>
       </c>
       <c r="E56" s="4" t="n">
-        <v>72.94</v>
+        <v>52.9</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>63.35</v>
+        <v>37.85</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>DBL</t>
+          <t>SPARC</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -3122,22 +3256,22 @@
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>459.7</v>
+        <v>239.37</v>
       </c>
       <c r="D57" s="4" t="n">
-        <v>62.57</v>
+        <v>65.08</v>
       </c>
       <c r="E57" s="4" t="n">
-        <v>52.41</v>
+        <v>74.23</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>51.58</v>
+        <v>61.34</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>OSWALPUMPS</t>
+          <t>NAZARA</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -3146,22 +3280,22 @@
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>431.85</v>
+        <v>305.65</v>
       </c>
       <c r="D58" s="4" t="n">
-        <v>62.47</v>
+        <v>65.08</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>51.12</v>
+        <v>61.12</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v/>
+        <v>59.43</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>CERA</t>
+          <t>SUBROS</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -3170,22 +3304,22 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>6330.5</v>
+        <v>848.1</v>
       </c>
       <c r="D59" s="4" t="n">
-        <v>62.08</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>65.47</v>
+        <v>58.32</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>52.35</v>
+        <v>55.47</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>NAZARA</t>
+          <t>CERA</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -3194,22 +3328,22 @@
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>300.65</v>
+        <v>6460</v>
       </c>
       <c r="D60" s="4" t="n">
-        <v>61.98</v>
+        <v>64.59</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>59.6</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>58.58</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>IXIGO</t>
+          <t>AEQUS</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -3218,22 +3352,22 @@
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>189.83</v>
+        <v>236.54</v>
       </c>
       <c r="D61" s="4" t="n">
-        <v>61.67</v>
+        <v>64.37</v>
       </c>
       <c r="E61" s="4" t="n">
-        <v>50.35</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>49.55</v>
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>SHILPAMED</t>
+          <t>AVL</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -3242,22 +3376,22 @@
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>571.6</v>
+        <v>638.55</v>
       </c>
       <c r="D62" s="4" t="n">
-        <v>61.64</v>
+        <v>64.27</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>81.65000000000001</v>
+        <v>66.73</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>71.13</v>
+        <v>66.77</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>PRIVISCL</t>
+          <t>RELAXO</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -3266,22 +3400,22 @@
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>3550.5</v>
+        <v>397.15</v>
       </c>
       <c r="D63" s="4" t="n">
-        <v>61.64</v>
+        <v>64.25</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>64.29000000000001</v>
+        <v>59.92</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>70.59</v>
+        <v>40.04</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>WAAREERTL</t>
+          <t>UTLSOLAR</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -3290,13 +3424,13 @@
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>1020.65</v>
+        <v>342.75</v>
       </c>
       <c r="D64" s="4" t="n">
-        <v>61.53</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>55.48</v>
+        <v>72.89</v>
       </c>
       <c r="F64" s="4" t="n">
         <v/>
@@ -3305,7 +3439,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>TRIVENI</t>
+          <t>APOLLO</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -3314,22 +3448,22 @@
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>409.8</v>
+        <v>450.05</v>
       </c>
       <c r="D65" s="4" t="n">
-        <v>61.26</v>
+        <v>63.88</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>58.28</v>
+        <v>69.56</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>55.44</v>
+        <v>74.33</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>IONEXCHANG</t>
+          <t>SKYGOLD</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -3338,22 +3472,22 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>398.65</v>
+        <v>560</v>
       </c>
       <c r="D66" s="4" t="n">
-        <v>61.24</v>
+        <v>63.81</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>54.64</v>
+        <v>67.91</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>46.44</v>
+        <v>72.84999999999999</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>MANORAMA</t>
+          <t>EPL</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
@@ -3362,22 +3496,22 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>1573.5</v>
+        <v>237.17</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>61.07</v>
+        <v>63.76</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>60.04</v>
+        <v>59.84</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>64.95999999999999</v>
+        <v>56.68</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>WESTLIFE</t>
+          <t>KSB</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
@@ -3386,22 +3520,22 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>486.3</v>
+        <v>936.1</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>60.66</v>
+        <v>63.59</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>47.66</v>
+        <v>62.9</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>34.79</v>
+        <v>59.39</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>SMLMAH</t>
+          <t>HCG</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
@@ -3410,22 +3544,22 @@
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>4092.9</v>
+        <v>654.8</v>
       </c>
       <c r="D69" s="4" t="n">
-        <v>60.42</v>
+        <v>63.51</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>54.1</v>
+        <v>59.32</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>61.53</v>
+        <v>61.11</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>STLTECH</t>
+          <t>MAHSCOOTER</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -3434,22 +3568,22 @@
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>613.35</v>
+        <v>13014</v>
       </c>
       <c r="D70" s="4" t="n">
-        <v>60.3</v>
+        <v>63.5</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>81.81</v>
+        <v>51.27</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>90.48999999999999</v>
+        <v>56.16</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>ASKAUTOLTD</t>
+          <t>ORIENTCEM</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -3458,22 +3592,22 @@
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>464.8</v>
+        <v>142.29</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>60</v>
+        <v>63.13</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>54.61</v>
+        <v>43.14</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>54.9</v>
+        <v>37.49</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>PRUDENT</t>
+          <t>THYROCARE</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
@@ -3482,22 +3616,22 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>2988.7</v>
+        <v>555.6</v>
       </c>
       <c r="D72" s="4" t="n">
-        <v>59.68</v>
+        <v>63.04</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>62.98</v>
+        <v>70.62</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>61.22</v>
+        <v>67.86</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>MARKSANS</t>
+          <t>TIPSMUSIC</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -3506,22 +3640,22 @@
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>256.07</v>
+        <v>684.65</v>
       </c>
       <c r="D73" s="4" t="n">
-        <v>59.55</v>
+        <v>63</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>72.44</v>
+        <v>62.13</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>60.81</v>
+        <v>60.73</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>STYRENIX</t>
+          <t>TMB</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -3530,22 +3664,22 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>2334.4</v>
+        <v>778.65</v>
       </c>
       <c r="D74" s="4" t="n">
-        <v>59.54</v>
+        <v>62.96</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>56.45</v>
+        <v>65.94</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>54.81</v>
+        <v>72.62</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>KRBL</t>
+          <t>BANCOINDIA</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -3554,22 +3688,22 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>385.35</v>
+        <v>689.1</v>
       </c>
       <c r="D75" s="4" t="n">
-        <v>59.49</v>
+        <v>62.81</v>
       </c>
       <c r="E75" s="4" t="n">
-        <v>58.6</v>
+        <v>58.04</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>55.27</v>
+        <v>60.78</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>YATHARTH</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -3578,22 +3712,22 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>186.15</v>
+        <v>865.55</v>
       </c>
       <c r="D76" s="4" t="n">
-        <v>59.09</v>
+        <v>62.41</v>
       </c>
       <c r="E76" s="4" t="n">
-        <v>58.15</v>
+        <v>62.34</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>60.09</v>
+        <v>64.33</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>BLUESTONE</t>
+          <t>RELIGARE</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
@@ -3602,22 +3736,22 @@
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>533.15</v>
+        <v>262.85</v>
       </c>
       <c r="D77" s="4" t="n">
-        <v>58.92</v>
+        <v>62.23</v>
       </c>
       <c r="E77" s="4" t="n">
-        <v>53.93</v>
+        <v>61.43</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v/>
+        <v>56.31</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>INOXINDIA</t>
+          <t>PARAS</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
@@ -3626,22 +3760,22 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>1872.9</v>
+        <v>1294</v>
       </c>
       <c r="D78" s="4" t="n">
-        <v>58.76</v>
+        <v>62.15</v>
       </c>
       <c r="E78" s="4" t="n">
-        <v>80</v>
+        <v>70.3</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>81.47</v>
+        <v>67.97</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>BLACKBUCK</t>
+          <t>ROUTE</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
@@ -3650,22 +3784,22 @@
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>562.8</v>
+        <v>553.45</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>58.75</v>
+        <v>62.01</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>49.26</v>
+        <v>48.75</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>53.88</v>
+        <v>32.23</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>TIMETECHNO</t>
+          <t>SUNTECK</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
@@ -3674,22 +3808,22 @@
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>182.08</v>
+        <v>330.95</v>
       </c>
       <c r="D80" s="4" t="n">
-        <v>58.74</v>
+        <v>61.76</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>50.01</v>
+        <v>47.55</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>51.99</v>
+        <v>43.78</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>JAMNAAUTO</t>
+          <t>ETHOSLTD</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -3698,22 +3832,22 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>130.79</v>
+        <v>2494.8</v>
       </c>
       <c r="D81" s="4" t="n">
-        <v>58.58</v>
+        <v>61.46</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>55.54</v>
+        <v>51.31</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>57.88</v>
+        <v>50.46</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>KSCL</t>
+          <t>INOXGREEN</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
@@ -3722,22 +3856,22 @@
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>925.6</v>
+        <v>199.94</v>
       </c>
       <c r="D82" s="4" t="n">
-        <v>58.42</v>
+        <v>61.27</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>51.36</v>
+        <v>58.03</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>49.68</v>
+        <v>55.81</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>BALAMINES</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
@@ -3746,22 +3880,22 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>111.5</v>
+        <v>2194.2</v>
       </c>
       <c r="D83" s="4" t="n">
-        <v>58.42</v>
+        <v>61.07</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>49.97</v>
+        <v>76.66</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>42.96</v>
+        <v>61.06</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>PARKHOSPS</t>
+          <t>AARTIDRUGS</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
@@ -3770,22 +3904,22 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>285.5</v>
+        <v>386.6</v>
       </c>
       <c r="D84" s="4" t="n">
-        <v>58.37</v>
+        <v>60.91</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>79.34999999999999</v>
+        <v>51.47</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v/>
+        <v>45.64</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>APLLTD</t>
+          <t>MARKSANS</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
@@ -3794,22 +3928,22 @@
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>771.5</v>
+        <v>264.45</v>
       </c>
       <c r="D85" s="4" t="n">
-        <v>58.25</v>
+        <v>60.54</v>
       </c>
       <c r="E85" s="4" t="n">
-        <v>49.29</v>
+        <v>73.23</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>45.43</v>
+        <v>60.89</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>PRICOLLTD</t>
+          <t>SAMHI</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
@@ -3818,22 +3952,22 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>586.7</v>
+        <v>177.95</v>
       </c>
       <c r="D86" s="4" t="n">
-        <v>58.24</v>
+        <v>60.47</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>52.34</v>
+        <v>56.76</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>58.57</v>
+        <v>50.33</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>GNFC</t>
+          <t>REDTAPE</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
@@ -3842,22 +3976,22 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>546.85</v>
+        <v>139.18</v>
       </c>
       <c r="D87" s="4" t="n">
-        <v>58.1</v>
+        <v>60.12</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>63.33</v>
+        <v>56.79</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>53.57</v>
+        <v>35.97</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>VOLTAMP</t>
+          <t>ENTERO</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
@@ -3866,22 +4000,22 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>10304</v>
+        <v>1212.4</v>
       </c>
       <c r="D88" s="4" t="n">
-        <v>58.09</v>
+        <v>60.01</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>59.93</v>
+        <v>52.92</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>56.97</v>
+        <v>53.28</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>VARROC</t>
+          <t>PARKHOSPS</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
@@ -3890,22 +4024,22 @@
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>611.65</v>
+        <v>294.8</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>58.08</v>
+        <v>59.94</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>61.1</v>
+        <v>80.94</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>56.79</v>
+        <v/>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>AHLUCONT</t>
+          <t>TVSSCS</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
@@ -3914,22 +4048,22 @@
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>848.1</v>
+        <v>136.41</v>
       </c>
       <c r="D90" s="4" t="n">
-        <v>57.84</v>
+        <v>59.76</v>
       </c>
       <c r="E90" s="4" t="n">
-        <v>52.01</v>
+        <v>59.31</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>48.88</v>
+        <v>49.19</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>QPOWER</t>
+          <t>TEXRAIL</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
@@ -3938,22 +4072,22 @@
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>1255.4</v>
+        <v>113.2</v>
       </c>
       <c r="D91" s="4" t="n">
-        <v>57.76</v>
+        <v>59.68</v>
       </c>
       <c r="E91" s="4" t="n">
-        <v>61.11</v>
+        <v>51.42</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>66.59999999999999</v>
+        <v>44.99</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>SUDEEPPHRM</t>
+          <t>TANLA</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
@@ -3962,22 +4096,22 @@
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>809.2</v>
+        <v>539.05</v>
       </c>
       <c r="D92" s="4" t="n">
-        <v>57.65</v>
+        <v>59.58</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>64.95999999999999</v>
+        <v>55.86</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v/>
+        <v>45.6</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>IFBIND</t>
+          <t>PRUDENT</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
@@ -3986,22 +4120,22 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>1278.4</v>
+        <v>3003</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>57.58</v>
+        <v>59.35</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>52.88</v>
+        <v>63.58</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>48.82</v>
+        <v>61.44</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>EMIL</t>
+          <t>UJJIVANSFB</t>
         </is>
       </c>
       <c r="B94" s="3" t="inlineStr">
@@ -4010,22 +4144,22 @@
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>119.14</v>
+        <v>59.6</v>
       </c>
       <c r="D94" s="4" t="n">
-        <v>57.44</v>
+        <v>59.21</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>55.11</v>
+        <v>56.22</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>46.74</v>
+        <v>59.81</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>HERITGFOOD</t>
+          <t>DCBBANK</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
@@ -4034,22 +4168,22 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>336.8</v>
+        <v>189.27</v>
       </c>
       <c r="D95" s="4" t="n">
-        <v>57.43</v>
+        <v>58.84</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>42.55</v>
+        <v>60.52</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>44.68</v>
+        <v>60.9</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>SPARC</t>
+          <t>SUPRIYA</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
@@ -4058,22 +4192,22 @@
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>224.92</v>
+        <v>978.9</v>
       </c>
       <c r="D96" s="4" t="n">
-        <v>57.15</v>
+        <v>58.81</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>71.17</v>
+        <v>72.65000000000001</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>59.26</v>
+        <v>66.72</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>EDELWEISS</t>
+          <t>SHAKTIPUMP</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
@@ -4082,22 +4216,22 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>122.45</v>
+        <v>574.1</v>
       </c>
       <c r="D97" s="4" t="n">
-        <v>57.14</v>
+        <v>58.7</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>56.55</v>
+        <v>48.63</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>59.92</v>
+        <v>47.72</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>POWERMECH</t>
+          <t>STAR</t>
         </is>
       </c>
       <c r="B98" s="3" t="inlineStr">
@@ -4106,22 +4240,22 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>2760.1</v>
+        <v>1126.8</v>
       </c>
       <c r="D98" s="4" t="n">
-        <v>57.07</v>
+        <v>58.67</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>62.64</v>
+        <v>62.24</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>55.62</v>
+        <v>61.52</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>SUNTECK</t>
+          <t>SOUTHBANK</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
@@ -4130,22 +4264,22 @@
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>319</v>
+        <v>46.1</v>
       </c>
       <c r="D99" s="4" t="n">
-        <v>57</v>
+        <v>58.66</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>44.42</v>
+        <v>62.51</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>42.31</v>
+        <v>70.28</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>DIACABS</t>
+          <t>METROPOLIS</t>
         </is>
       </c>
       <c r="B100" s="3" t="inlineStr">
@@ -4154,22 +4288,22 @@
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>206.28</v>
+        <v>556</v>
       </c>
       <c r="D100" s="4" t="n">
-        <v>56.83</v>
+        <v>58.63</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>74.72</v>
+        <v>62.13</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>67.90000000000001</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>SURYAROSNI</t>
+          <t>CENTURYPLY</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
@@ -4178,22 +4312,22 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>261.56</v>
+        <v>775.1</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>56.69</v>
+        <v>58.62</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>54.43</v>
+        <v>53.3</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>50.49</v>
+        <v>52.84</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>EPL</t>
+          <t>GAEL</t>
         </is>
       </c>
       <c r="B102" s="3" t="inlineStr">
@@ -4202,22 +4336,22 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>229.22</v>
+        <v>164.52</v>
       </c>
       <c r="D102" s="4" t="n">
-        <v>56.24</v>
+        <v>58.47</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>56.99</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>55.18</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>MTARTECH</t>
+          <t>AARTIPHARM</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
@@ -4226,22 +4360,22 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>7976.5</v>
+        <v>706.35</v>
       </c>
       <c r="D103" s="4" t="n">
-        <v>56.22</v>
+        <v>58.43</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>75.06</v>
+        <v>50.23</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>87.93000000000001</v>
+        <v>51.84</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>REDTAPE</t>
+          <t>LOTUSDEV</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
@@ -4250,22 +4384,22 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>136.9</v>
+        <v>148.73</v>
       </c>
       <c r="D104" s="4" t="n">
-        <v>56.16</v>
+        <v>58.38</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>54.99</v>
+        <v>53</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>35.6</v>
+        <v/>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>EMBDL</t>
+          <t>EDELWEISS</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
@@ -4274,22 +4408,22 @@
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>63.71</v>
+        <v>124.33</v>
       </c>
       <c r="D105" s="4" t="n">
-        <v>55.91</v>
+        <v>58.36</v>
       </c>
       <c r="E105" s="4" t="n">
-        <v>50.6</v>
+        <v>57.85</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>42.81</v>
+        <v>60.55</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>WEWORK</t>
+          <t>LLOYDSENT</t>
         </is>
       </c>
       <c r="B106" s="3" t="inlineStr">
@@ -4298,22 +4432,22 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>626.55</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="D106" s="4" t="n">
-        <v>55.82</v>
+        <v>58.31</v>
       </c>
       <c r="E106" s="4" t="n">
-        <v>60.88</v>
+        <v>60.78</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v/>
+        <v>59.81</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>SUPRIYA</t>
+          <t>LLOYDSENGG</t>
         </is>
       </c>
       <c r="B107" s="3" t="inlineStr">
@@ -4322,22 +4456,22 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>928.15</v>
+        <v>83.94</v>
       </c>
       <c r="D107" s="4" t="n">
-        <v>55.65</v>
+        <v>58.3</v>
       </c>
       <c r="E107" s="4" t="n">
-        <v>70.44</v>
+        <v>71.54000000000001</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>65.87</v>
+        <v>62.3</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>PURVA</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
@@ -4346,22 +4480,22 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>690.7</v>
+        <v>221.57</v>
       </c>
       <c r="D108" s="4" t="n">
-        <v>55.33</v>
+        <v>58.21</v>
       </c>
       <c r="E108" s="4" t="n">
-        <v>49.18</v>
+        <v>50.61</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>51.35</v>
+        <v>46.25</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>ENTERO</t>
+          <t>CRAMC</t>
         </is>
       </c>
       <c r="B109" s="3" t="inlineStr">
@@ -4370,22 +4504,22 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>1180.4</v>
+        <v>255.78</v>
       </c>
       <c r="D109" s="4" t="n">
-        <v>55.29</v>
+        <v>58.11</v>
       </c>
       <c r="E109" s="4" t="n">
-        <v>50.93</v>
+        <v>48.49</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>51.44</v>
+        <v/>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>ETHOSLTD</t>
+          <t>WAAREERTL</t>
         </is>
       </c>
       <c r="B110" s="3" t="inlineStr">
@@ -4394,22 +4528,22 @@
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>2436.9</v>
+        <v>1020.3</v>
       </c>
       <c r="D110" s="4" t="n">
-        <v>55.24</v>
+        <v>57.95</v>
       </c>
       <c r="E110" s="4" t="n">
-        <v>49.05</v>
+        <v>55.49</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>49.44</v>
+        <v>50.62</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>TVSSCS</t>
+          <t>AGARWALEYE</t>
         </is>
       </c>
       <c r="B111" s="3" t="inlineStr">
@@ -4418,22 +4552,22 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>131.49</v>
+        <v>477.6</v>
       </c>
       <c r="D111" s="4" t="n">
-        <v>55.09</v>
+        <v>57.95</v>
       </c>
       <c r="E111" s="4" t="n">
-        <v>56.38</v>
+        <v>54.95</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>47.2</v>
+        <v>53.76</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>INDIGOPNTS</t>
+          <t>DATAMATICS</t>
         </is>
       </c>
       <c r="B112" s="3" t="inlineStr">
@@ -4442,22 +4576,22 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>1006.25</v>
+        <v>819.35</v>
       </c>
       <c r="D112" s="4" t="n">
-        <v>55.08</v>
+        <v>57.95</v>
       </c>
       <c r="E112" s="4" t="n">
-        <v>54.27</v>
+        <v>55.85</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>45.45</v>
+        <v>56.35</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>SOUTHBANK</t>
+          <t>LXCHEM</t>
         </is>
       </c>
       <c r="B113" s="3" t="inlineStr">
@@ -4466,22 +4600,22 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>45.41</v>
+        <v>161.48</v>
       </c>
       <c r="D113" s="4" t="n">
-        <v>55.04</v>
+        <v>57.93</v>
       </c>
       <c r="E113" s="4" t="n">
-        <v>61.43</v>
+        <v>55.66</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>69.72</v>
+        <v>42.49</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>RCF</t>
+          <t>PNGJL</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
@@ -4490,22 +4624,22 @@
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>132.62</v>
+        <v>569.35</v>
       </c>
       <c r="D114" s="4" t="n">
-        <v>55.03</v>
+        <v>57.82</v>
       </c>
       <c r="E114" s="4" t="n">
-        <v>51.68</v>
+        <v>48</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>48.52</v>
+        <v>45.5</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>SAATVIKGL</t>
+          <t>SURYAROSNI</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
@@ -4514,22 +4648,22 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>475.35</v>
+        <v>263.3</v>
       </c>
       <c r="D115" s="4" t="n">
-        <v>54.98</v>
+        <v>57.69</v>
       </c>
       <c r="E115" s="4" t="n">
-        <v>60.22</v>
+        <v>55.21</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v/>
+        <v>50.79</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>METROPOLIS</t>
+          <t>AURIONPRO</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
@@ -4538,22 +4672,22 @@
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>543.35</v>
+        <v>879.65</v>
       </c>
       <c r="D116" s="4" t="n">
-        <v>54.52</v>
+        <v>57.6</v>
       </c>
       <c r="E116" s="4" t="n">
-        <v>60.32</v>
+        <v>47.88</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>59.39</v>
+        <v>43.75</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>EQUITASBNK</t>
+          <t>RBA</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
@@ -4562,22 +4696,22 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>75.14</v>
+        <v>75.72</v>
       </c>
       <c r="D117" s="4" t="n">
-        <v>54.28</v>
+        <v>57.48</v>
       </c>
       <c r="E117" s="4" t="n">
-        <v>62.17</v>
+        <v>64.34</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>55.22</v>
+        <v>47.34</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>ASHOKA</t>
+          <t>AZAD</t>
         </is>
       </c>
       <c r="B118" s="3" t="inlineStr">
@@ -4586,22 +4720,22 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>131.03</v>
+        <v>2149.1</v>
       </c>
       <c r="D118" s="4" t="n">
-        <v>54.27</v>
+        <v>57.24</v>
       </c>
       <c r="E118" s="4" t="n">
-        <v>45.13</v>
+        <v>60.67</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>43.76</v>
+        <v>63.14</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>TEXRAIL</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="B119" s="3" t="inlineStr">
@@ -4610,22 +4744,22 @@
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>110</v>
+        <v>451.75</v>
       </c>
       <c r="D119" s="4" t="n">
-        <v>54.24</v>
+        <v>57.24</v>
       </c>
       <c r="E119" s="4" t="n">
-        <v>48.3</v>
+        <v>52.44</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>43.94</v>
+        <v>58.25</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENT</t>
+          <t>ALKYLAMINE</t>
         </is>
       </c>
       <c r="B120" s="3" t="inlineStr">
@@ -4634,22 +4768,22 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>73.17</v>
+        <v>1827</v>
       </c>
       <c r="D120" s="4" t="n">
-        <v>54.16</v>
+        <v>56.97</v>
       </c>
       <c r="E120" s="4" t="n">
-        <v>58.86</v>
+        <v>63.68</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>58.66</v>
+        <v>49.97</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>DATAMATICS</t>
+          <t>INDIASHLTR</t>
         </is>
       </c>
       <c r="B121" s="3" t="inlineStr">
@@ -4658,22 +4792,22 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>799.8</v>
+        <v>789.85</v>
       </c>
       <c r="D121" s="4" t="n">
-        <v>54.01</v>
+        <v>56.95</v>
       </c>
       <c r="E121" s="4" t="n">
-        <v>53.61</v>
+        <v>52</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>55.36</v>
+        <v>53.33</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>ALKYLAMINE</t>
+          <t>NEOGEN</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
@@ -4682,22 +4816,22 @@
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>1788.7</v>
+        <v>1968.3</v>
       </c>
       <c r="D122" s="4" t="n">
-        <v>53.97</v>
+        <v>56.8</v>
       </c>
       <c r="E122" s="4" t="n">
-        <v>62.13</v>
+        <v>65.48</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>49.07</v>
+        <v>58.77</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>KNRCON</t>
+          <t>HEMIPROP</t>
         </is>
       </c>
       <c r="B123" s="3" t="inlineStr">
@@ -4706,22 +4840,22 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>134.2</v>
+        <v>142.94</v>
       </c>
       <c r="D123" s="4" t="n">
-        <v>53.91</v>
+        <v>56.44</v>
       </c>
       <c r="E123" s="4" t="n">
-        <v>47.87</v>
+        <v>53.62</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>36</v>
+        <v>50.38</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>BIRLACORPN</t>
+          <t>EUREKAFORB</t>
         </is>
       </c>
       <c r="B124" s="3" t="inlineStr">
@@ -4730,22 +4864,22 @@
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>1003.9</v>
+        <v>476</v>
       </c>
       <c r="D124" s="4" t="n">
-        <v>53.81</v>
+        <v>56.39</v>
       </c>
       <c r="E124" s="4" t="n">
-        <v>50.21</v>
+        <v>46.23</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>43.97</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>SKFINDIA</t>
+          <t>IFBIND</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
@@ -4754,22 +4888,22 @@
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>1658</v>
+        <v>1282.8</v>
       </c>
       <c r="D125" s="4" t="n">
-        <v>53.76</v>
+        <v>56.39</v>
       </c>
       <c r="E125" s="4" t="n">
-        <v>36.18</v>
+        <v>53.18</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>32.37</v>
+        <v>48.91</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>KITEX</t>
+          <t>HERITGFOOD</t>
         </is>
       </c>
       <c r="B126" s="3" t="inlineStr">
@@ -4778,22 +4912,22 @@
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>162.43</v>
+        <v>336.1</v>
       </c>
       <c r="D126" s="4" t="n">
-        <v>53.64</v>
+        <v>56.14</v>
       </c>
       <c r="E126" s="4" t="n">
-        <v>46.49</v>
+        <v>42.28</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>49.26</v>
+        <v>44.64</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>YATHARTH</t>
+          <t>EQUITASBNK</t>
         </is>
       </c>
       <c r="B127" s="3" t="inlineStr">
@@ -4802,22 +4936,22 @@
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>837.05</v>
+        <v>76.3</v>
       </c>
       <c r="D127" s="4" t="n">
-        <v>53.48</v>
+        <v>56.07</v>
       </c>
       <c r="E127" s="4" t="n">
-        <v>59.69</v>
+        <v>62.99</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>63.16</v>
+        <v>55.67</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>RAYMONDLSL</t>
+          <t>JUSTDIAL</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
@@ -4826,22 +4960,22 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>794.95</v>
+        <v>549.85</v>
       </c>
       <c r="D128" s="4" t="n">
-        <v>53.14</v>
+        <v>56</v>
       </c>
       <c r="E128" s="4" t="n">
-        <v>42.78</v>
+        <v>41.63</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>26.84</v>
+        <v>36.83</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>TRANSRAILL</t>
+          <t>INOXINDIA</t>
         </is>
       </c>
       <c r="B129" s="3" t="inlineStr">
@@ -4850,22 +4984,22 @@
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>511.95</v>
+        <v>1871</v>
       </c>
       <c r="D129" s="4" t="n">
-        <v>53.08</v>
+        <v>55.98</v>
       </c>
       <c r="E129" s="4" t="n">
-        <v>45.32</v>
+        <v>79.22</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>45.85</v>
+        <v>76.72</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>ARVINDFASN</t>
+          <t>KSCL</t>
         </is>
       </c>
       <c r="B130" s="3" t="inlineStr">
@@ -4874,22 +5008,22 @@
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>469.25</v>
+        <v>919.2</v>
       </c>
       <c r="D130" s="4" t="n">
-        <v>52.89</v>
+        <v>55.84</v>
       </c>
       <c r="E130" s="4" t="n">
-        <v>51.63</v>
+        <v>51</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>51.45</v>
+        <v>49.64</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>SKIPPER</t>
+          <t>BBOX</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
@@ -4898,22 +5032,22 @@
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>533.15</v>
+        <v>994.95</v>
       </c>
       <c r="D131" s="4" t="n">
-        <v>52.7</v>
+        <v>55.62</v>
       </c>
       <c r="E131" s="4" t="n">
-        <v>64.76000000000001</v>
+        <v>72.22</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>60.38</v>
+        <v>71.75</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>BANCOINDIA</t>
+          <t>RCF</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
@@ -4922,22 +5056,22 @@
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>658.85</v>
+        <v>132.98</v>
       </c>
       <c r="D132" s="4" t="n">
-        <v>52.28</v>
+        <v>55.51</v>
       </c>
       <c r="E132" s="4" t="n">
-        <v>54.43</v>
+        <v>52.01</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>59.12</v>
+        <v>48.67</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>LXCHEM</t>
+          <t>ALOKINDS</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
@@ -4946,22 +5080,22 @@
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>155.99</v>
+        <v>13.15</v>
       </c>
       <c r="D133" s="4" t="n">
-        <v>51.9</v>
+        <v>55.48</v>
       </c>
       <c r="E133" s="4" t="n">
-        <v>52.66</v>
+        <v>44.63</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>40.85</v>
+        <v>39.82</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>THYROCARE</t>
+          <t>CAPILLARY</t>
         </is>
       </c>
       <c r="B134" s="3" t="inlineStr">
@@ -4970,22 +5104,22 @@
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>517.2</v>
+        <v>515.05</v>
       </c>
       <c r="D134" s="4" t="n">
-        <v>51.9</v>
+        <v>55.3</v>
       </c>
       <c r="E134" s="4" t="n">
-        <v>64.77</v>
+        <v>42.4</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>65.62</v>
+        <v/>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>UTLSOLAR</t>
+          <t>ASHOKA</t>
         </is>
       </c>
       <c r="B135" s="3" t="inlineStr">
@@ -4994,22 +5128,22 @@
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>309.5</v>
+        <v>132.05</v>
       </c>
       <c r="D135" s="4" t="n">
-        <v>51.77</v>
+        <v>55.22</v>
       </c>
       <c r="E135" s="4" t="n">
-        <v>66.81999999999999</v>
+        <v>45.73</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v/>
+        <v>43.93</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>RATNAMANI</t>
+          <t>WEBELSOLAR</t>
         </is>
       </c>
       <c r="B136" s="3" t="inlineStr">
@@ -5018,22 +5152,22 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>2647.1</v>
+        <v>106.81</v>
       </c>
       <c r="D136" s="4" t="n">
-        <v>51.55</v>
+        <v>55.2</v>
       </c>
       <c r="E136" s="4" t="n">
-        <v>55.46</v>
+        <v>56.34</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>50.91</v>
+        <v>53.67</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>TDPOWERSYS</t>
+          <t>TRANSRAILL</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
@@ -5042,22 +5176,22 @@
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>1255.1</v>
+        <v>518.75</v>
       </c>
       <c r="D137" s="4" t="n">
-        <v>51.39</v>
+        <v>55.15</v>
       </c>
       <c r="E137" s="4" t="n">
-        <v>67.83</v>
+        <v>46.57</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>79.65000000000001</v>
+        <v>46.43</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>UJJIVANSFB</t>
+          <t>TIMETECHNO</t>
         </is>
       </c>
       <c r="B138" s="3" t="inlineStr">
@@ -5066,22 +5200,22 @@
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>56.14</v>
+        <v>181.04</v>
       </c>
       <c r="D138" s="4" t="n">
-        <v>51.32</v>
+        <v>54.73</v>
       </c>
       <c r="E138" s="4" t="n">
-        <v>51.01</v>
+        <v>48.85</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>57.45</v>
+        <v>51.54</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>SHAILY</t>
+          <t>VAIBHAVGBL</t>
         </is>
       </c>
       <c r="B139" s="3" t="inlineStr">
@@ -5090,22 +5224,22 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>2849.7</v>
+        <v>236.12</v>
       </c>
       <c r="D139" s="4" t="n">
-        <v>51.27</v>
+        <v>54.31</v>
       </c>
       <c r="E139" s="4" t="n">
-        <v>61.26</v>
+        <v>54.93</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>68.59</v>
+        <v>47.29</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>BALAMINES</t>
+          <t>SMARTWORKS</t>
         </is>
       </c>
       <c r="B140" s="3" t="inlineStr">
@@ -5114,22 +5248,22 @@
         </is>
       </c>
       <c r="C140" s="4" t="n">
-        <v>1989</v>
+        <v>474.55</v>
       </c>
       <c r="D140" s="4" t="n">
-        <v>51.17</v>
+        <v>54.3</v>
       </c>
       <c r="E140" s="4" t="n">
-        <v>72.06999999999999</v>
+        <v>55.38</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>57.63</v>
+        <v/>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>RAIN</t>
+          <t>RUBICON</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
@@ -5138,22 +5272,22 @@
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>185.49</v>
+        <v>1307</v>
       </c>
       <c r="D141" s="4" t="n">
-        <v>51.02</v>
+        <v>54.12</v>
       </c>
       <c r="E141" s="4" t="n">
-        <v>65.63</v>
+        <v>76.89</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>57.75</v>
+        <v/>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>FINPIPE</t>
+          <t>SUDARSCHEM</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
@@ -5162,22 +5296,22 @@
         </is>
       </c>
       <c r="C142" s="4" t="n">
-        <v>176.25</v>
+        <v>910.35</v>
       </c>
       <c r="D142" s="4" t="n">
-        <v>51.02</v>
+        <v>54.06</v>
       </c>
       <c r="E142" s="4" t="n">
-        <v>48.82</v>
+        <v>48.62</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>44.9</v>
+        <v>48.63</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>MAHSCOOTER</t>
+          <t>SHAILY</t>
         </is>
       </c>
       <c r="B143" s="3" t="inlineStr">
@@ -5186,22 +5320,22 @@
         </is>
       </c>
       <c r="C143" s="4" t="n">
-        <v>12506</v>
+        <v>2901.6</v>
       </c>
       <c r="D143" s="4" t="n">
-        <v>50.97</v>
+        <v>53.89</v>
       </c>
       <c r="E143" s="4" t="n">
-        <v>46.44</v>
+        <v>62.4</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>53.86</v>
+        <v>69.72</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>VAIBHAVGBL</t>
+          <t>MANORAMA</t>
         </is>
       </c>
       <c r="B144" s="3" t="inlineStr">
@@ -5210,22 +5344,22 @@
         </is>
       </c>
       <c r="C144" s="4" t="n">
-        <v>232.9</v>
+        <v>1562.4</v>
       </c>
       <c r="D144" s="4" t="n">
-        <v>50.96</v>
+        <v>53.83</v>
       </c>
       <c r="E144" s="4" t="n">
-        <v>53.93</v>
+        <v>59.04</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>46.8</v>
+        <v>62.72</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>IIFLCAPS</t>
+          <t>SKFINDIA</t>
         </is>
       </c>
       <c r="B145" s="3" t="inlineStr">
@@ -5234,22 +5368,22 @@
         </is>
       </c>
       <c r="C145" s="4" t="n">
-        <v>340.95</v>
+        <v>1632.5</v>
       </c>
       <c r="D145" s="4" t="n">
-        <v>50.84</v>
+        <v>53.82</v>
       </c>
       <c r="E145" s="4" t="n">
-        <v>56.06</v>
+        <v>37.42</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>58.51</v>
+        <v>32.62</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>SAFARI</t>
+          <t>ACI</t>
         </is>
       </c>
       <c r="B146" s="3" t="inlineStr">
@@ -5258,22 +5392,22 @@
         </is>
       </c>
       <c r="C146" s="4" t="n">
-        <v>1590.6</v>
+        <v>539.65</v>
       </c>
       <c r="D146" s="4" t="n">
-        <v>50.83</v>
+        <v>53.8</v>
       </c>
       <c r="E146" s="4" t="n">
-        <v>45.1</v>
+        <v>44.94</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>42.83</v>
+        <v>44.71</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>TANLA</t>
+          <t>KIRLPNU</t>
         </is>
       </c>
       <c r="B147" s="3" t="inlineStr">
@@ -5282,22 +5416,22 @@
         </is>
       </c>
       <c r="C147" s="4" t="n">
-        <v>520.05</v>
+        <v>1825.9</v>
       </c>
       <c r="D147" s="4" t="n">
-        <v>50.62</v>
+        <v>53.77</v>
       </c>
       <c r="E147" s="4" t="n">
-        <v>52.44</v>
+        <v>73.92</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>44.35</v>
+        <v>66.81</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>ORKLAINDIA</t>
+          <t>EMBDL</t>
         </is>
       </c>
       <c r="B148" s="3" t="inlineStr">
@@ -5306,22 +5440,22 @@
         </is>
       </c>
       <c r="C148" s="4" t="n">
-        <v>621.3</v>
+        <v>63.02</v>
       </c>
       <c r="D148" s="4" t="n">
-        <v>50.46</v>
+        <v>53.7</v>
       </c>
       <c r="E148" s="4" t="n">
-        <v>49.28</v>
+        <v>50.03</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v/>
+        <v>42.62</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>MAHSEAMLES</t>
+          <t>SAFARI</t>
         </is>
       </c>
       <c r="B149" s="3" t="inlineStr">
@@ -5330,22 +5464,22 @@
         </is>
       </c>
       <c r="C149" s="4" t="n">
-        <v>628.4</v>
+        <v>1617.5</v>
       </c>
       <c r="D149" s="4" t="n">
-        <v>50.33</v>
+        <v>53.52</v>
       </c>
       <c r="E149" s="4" t="n">
-        <v>59.22</v>
+        <v>46.29</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>52.25</v>
+        <v>43.51</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>JUSTDIAL</t>
+          <t>KANSAINER</t>
         </is>
       </c>
       <c r="B150" s="3" t="inlineStr">
@@ -5354,22 +5488,22 @@
         </is>
       </c>
       <c r="C150" s="4" t="n">
-        <v>537.7</v>
+        <v>211.83</v>
       </c>
       <c r="D150" s="4" t="n">
-        <v>50.27</v>
+        <v>53.39</v>
       </c>
       <c r="E150" s="4" t="n">
-        <v>38.19</v>
+        <v>51.4</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>35.69</v>
+        <v>43.57</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>NETWORK18</t>
+          <t>STYRENIX</t>
         </is>
       </c>
       <c r="B151" s="3" t="inlineStr">
@@ -5378,22 +5512,22 @@
         </is>
       </c>
       <c r="C151" s="4" t="n">
-        <v>32.63</v>
+        <v>2295.7</v>
       </c>
       <c r="D151" s="4" t="n">
-        <v>50.21</v>
+        <v>53.05</v>
       </c>
       <c r="E151" s="4" t="n">
-        <v>41.72</v>
+        <v>55.21</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>36.75</v>
+        <v>54.19</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>RAIN</t>
         </is>
       </c>
       <c r="B152" s="3" t="inlineStr">
@@ -5402,22 +5536,22 @@
         </is>
       </c>
       <c r="C152" s="4" t="n">
-        <v>1191</v>
+        <v>187.74</v>
       </c>
       <c r="D152" s="4" t="n">
-        <v>50.19</v>
+        <v>52.81</v>
       </c>
       <c r="E152" s="4" t="n">
-        <v>60.18</v>
+        <v>66.19</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>62.21</v>
+        <v>57.91</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>INDIASHLTR</t>
+          <t>KRBL</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
@@ -5426,22 +5560,22 @@
         </is>
       </c>
       <c r="C153" s="4" t="n">
-        <v>768.75</v>
+        <v>375.5</v>
       </c>
       <c r="D153" s="4" t="n">
-        <v>50.11</v>
+        <v>52.79</v>
       </c>
       <c r="E153" s="4" t="n">
-        <v>48.18</v>
+        <v>55.22</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>51.18</v>
+        <v>54.24</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>ELECTCAST</t>
+          <t>ARVINDFASN</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
@@ -5450,22 +5584,22 @@
         </is>
       </c>
       <c r="C154" s="4" t="n">
-        <v>78.59999999999999</v>
+        <v>470.15</v>
       </c>
       <c r="D154" s="4" t="n">
-        <v>50.1</v>
+        <v>52.63</v>
       </c>
       <c r="E154" s="4" t="n">
-        <v>49.11</v>
+        <v>51.85</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>43.2</v>
+        <v>51.57</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>MANYAVAR</t>
+          <t>NETWORK18</t>
         </is>
       </c>
       <c r="B155" s="3" t="inlineStr">
@@ -5474,22 +5608,22 @@
         </is>
       </c>
       <c r="C155" s="4" t="n">
-        <v>412.6</v>
+        <v>32.96</v>
       </c>
       <c r="D155" s="4" t="n">
-        <v>49.91</v>
+        <v>52.6</v>
       </c>
       <c r="E155" s="4" t="n">
-        <v>38.44</v>
+        <v>43.06</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>28.78</v>
+        <v>37.29</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>ALOKINDS</t>
+          <t>SHAREINDIA</t>
         </is>
       </c>
       <c r="B156" s="3" t="inlineStr">
@@ -5498,22 +5632,22 @@
         </is>
       </c>
       <c r="C156" s="4" t="n">
-        <v>12.83</v>
+        <v>138.62</v>
       </c>
       <c r="D156" s="4" t="n">
-        <v>49.82</v>
+        <v>52.57</v>
       </c>
       <c r="E156" s="4" t="n">
-        <v>41.84</v>
+        <v>46.81</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>38.52</v>
+        <v>40.56</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>CAPILLARY</t>
+          <t>WAKEFIT</t>
         </is>
       </c>
       <c r="B157" s="3" t="inlineStr">
@@ -5522,13 +5656,13 @@
         </is>
       </c>
       <c r="C157" s="4" t="n">
-        <v>507.55</v>
+        <v>125.99</v>
       </c>
       <c r="D157" s="4" t="n">
-        <v>49.8</v>
+        <v>52.44</v>
       </c>
       <c r="E157" s="4" t="n">
-        <v>40.24</v>
+        <v>37.82</v>
       </c>
       <c r="F157" s="4" t="n">
         <v/>
@@ -5537,7 +5671,7 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>GAEL</t>
+          <t>MIDHANI</t>
         </is>
       </c>
       <c r="B158" s="3" t="inlineStr">
@@ -5546,22 +5680,22 @@
         </is>
       </c>
       <c r="C158" s="4" t="n">
-        <v>158.27</v>
+        <v>427.85</v>
       </c>
       <c r="D158" s="4" t="n">
-        <v>49.76</v>
+        <v>52.34</v>
       </c>
       <c r="E158" s="4" t="n">
-        <v>61.68</v>
+        <v>61.48</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v>63.13</v>
+        <v>56.72</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>NEOGEN</t>
+          <t>JAIBALAJI</t>
         </is>
       </c>
       <c r="B159" s="3" t="inlineStr">
@@ -5570,22 +5704,22 @@
         </is>
       </c>
       <c r="C159" s="4" t="n">
-        <v>1874.8</v>
+        <v>70.41</v>
       </c>
       <c r="D159" s="4" t="n">
-        <v>49.56</v>
+        <v>52.3</v>
       </c>
       <c r="E159" s="4" t="n">
-        <v>62.86</v>
+        <v>47.97</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>57.74</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>HEMIPROP</t>
+          <t>ASKAUTOLTD</t>
         </is>
       </c>
       <c r="B160" s="3" t="inlineStr">
@@ -5594,22 +5728,22 @@
         </is>
       </c>
       <c r="C160" s="4" t="n">
-        <v>139.55</v>
+        <v>454.65</v>
       </c>
       <c r="D160" s="4" t="n">
-        <v>49.54</v>
+        <v>51.89</v>
       </c>
       <c r="E160" s="4" t="n">
-        <v>50.95</v>
+        <v>51.4</v>
       </c>
       <c r="F160" s="4" t="n">
-        <v>49.17</v>
+        <v>53.48</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>BECTORFOOD</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B161" s="3" t="inlineStr">
@@ -5618,22 +5752,22 @@
         </is>
       </c>
       <c r="C161" s="4" t="n">
-        <v>182.67</v>
+        <v>1214.8</v>
       </c>
       <c r="D161" s="4" t="n">
-        <v>49.49</v>
+        <v>51.89</v>
       </c>
       <c r="E161" s="4" t="n">
-        <v>39.13</v>
+        <v>61.04</v>
       </c>
       <c r="F161" s="4" t="n">
-        <v>39.75</v>
+        <v>61.94</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>GMMPFAUDLR</t>
+          <t>MASTEK</t>
         </is>
       </c>
       <c r="B162" s="3" t="inlineStr">
@@ -5642,22 +5776,22 @@
         </is>
       </c>
       <c r="C162" s="4" t="n">
-        <v>804.55</v>
+        <v>1621.3</v>
       </c>
       <c r="D162" s="4" t="n">
-        <v>49.4</v>
+        <v>51.86</v>
       </c>
       <c r="E162" s="4" t="n">
-        <v>37.43</v>
+        <v>42.88</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>39.18</v>
+        <v>39.82</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>SKYGOLD</t>
+          <t>ZAGGLE</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
@@ -5666,22 +5800,22 @@
         </is>
       </c>
       <c r="C163" s="4" t="n">
-        <v>499.15</v>
+        <v>212.95</v>
       </c>
       <c r="D163" s="4" t="n">
-        <v>49.17</v>
+        <v>51.82</v>
       </c>
       <c r="E163" s="4" t="n">
-        <v>61.85</v>
+        <v>39.22</v>
       </c>
       <c r="F163" s="4" t="n">
-        <v>67.95999999999999</v>
+        <v>40.46</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>ROUTE</t>
+          <t>BLACKBUCK</t>
         </is>
       </c>
       <c r="B164" s="3" t="inlineStr">
@@ -5690,22 +5824,22 @@
         </is>
       </c>
       <c r="C164" s="4" t="n">
-        <v>525</v>
+        <v>549</v>
       </c>
       <c r="D164" s="4" t="n">
-        <v>49.15</v>
+        <v>51.74</v>
       </c>
       <c r="E164" s="4" t="n">
-        <v>43.38</v>
+        <v>47.2</v>
       </c>
       <c r="F164" s="4" t="n">
-        <v>30.23</v>
+        <v>52.21</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>VIPIND</t>
+          <t>SMLMAH</t>
         </is>
       </c>
       <c r="B165" s="3" t="inlineStr">
@@ -5714,22 +5848,22 @@
         </is>
       </c>
       <c r="C165" s="4" t="n">
-        <v>312.45</v>
+        <v>3957.6</v>
       </c>
       <c r="D165" s="4" t="n">
-        <v>49.06</v>
+        <v>51.62</v>
       </c>
       <c r="E165" s="4" t="n">
-        <v>42.33</v>
+        <v>52.29</v>
       </c>
       <c r="F165" s="4" t="n">
-        <v>37.49</v>
+        <v>60.4</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>STAR</t>
+          <t>JSFB</t>
         </is>
       </c>
       <c r="B166" s="3" t="inlineStr">
@@ -5738,22 +5872,22 @@
         </is>
       </c>
       <c r="C166" s="4" t="n">
-        <v>1082.2</v>
+        <v>469.3</v>
       </c>
       <c r="D166" s="4" t="n">
-        <v>48.97</v>
+        <v>51.61</v>
       </c>
       <c r="E166" s="4" t="n">
-        <v>57.75</v>
+        <v>56.74</v>
       </c>
       <c r="F166" s="4" t="n">
-        <v>59.27</v>
+        <v>52.09</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>JSLL</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B167" s="3" t="inlineStr">
@@ -5762,22 +5896,22 @@
         </is>
       </c>
       <c r="C167" s="4" t="n">
-        <v>602.25</v>
+        <v>576.8</v>
       </c>
       <c r="D167" s="4" t="n">
-        <v>48.9</v>
+        <v>51.11</v>
       </c>
       <c r="E167" s="4" t="n">
-        <v>44.15</v>
+        <v>75.43000000000001</v>
       </c>
       <c r="F167" s="4" t="n">
-        <v>42.74</v>
+        <v>84.48</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>KANSAINER</t>
+          <t>GPPL</t>
         </is>
       </c>
       <c r="B168" s="3" t="inlineStr">
@@ -5786,22 +5920,22 @@
         </is>
       </c>
       <c r="C168" s="4" t="n">
-        <v>212.41</v>
+        <v>154.69</v>
       </c>
       <c r="D168" s="4" t="n">
-        <v>48.83</v>
+        <v>50.97</v>
       </c>
       <c r="E168" s="4" t="n">
-        <v>50.83</v>
+        <v>46.08</v>
       </c>
       <c r="F168" s="4" t="n">
-        <v>42.69</v>
+        <v>50.3</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>CENTURYPLY</t>
+          <t>PFOCUS</t>
         </is>
       </c>
       <c r="B169" s="3" t="inlineStr">
@@ -5810,22 +5944,22 @@
         </is>
       </c>
       <c r="C169" s="4" t="n">
-        <v>754.55</v>
+        <v>235.99</v>
       </c>
       <c r="D169" s="4" t="n">
-        <v>48.76</v>
+        <v>50.88</v>
       </c>
       <c r="E169" s="4" t="n">
-        <v>48.88</v>
+        <v>46.65</v>
       </c>
       <c r="F169" s="4" t="n">
-        <v>50.87</v>
+        <v>58.58</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>KTKBANK</t>
+          <t>BAJAJELEC</t>
         </is>
       </c>
       <c r="B170" s="3" t="inlineStr">
@@ -5834,22 +5968,22 @@
         </is>
       </c>
       <c r="C170" s="4" t="n">
-        <v>265.6</v>
+        <v>328.95</v>
       </c>
       <c r="D170" s="4" t="n">
-        <v>48.6</v>
+        <v>50.82</v>
       </c>
       <c r="E170" s="4" t="n">
-        <v>62.97</v>
+        <v>34.86</v>
       </c>
       <c r="F170" s="4" t="n">
-        <v>66.59</v>
+        <v>29.28</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>BBOX</t>
+          <t>BALUFORGE</t>
         </is>
       </c>
       <c r="B171" s="3" t="inlineStr">
@@ -5858,22 +5992,22 @@
         </is>
       </c>
       <c r="C171" s="4" t="n">
-        <v>957.9</v>
+        <v>465.7</v>
       </c>
       <c r="D171" s="4" t="n">
-        <v>48.54</v>
+        <v>50.61</v>
       </c>
       <c r="E171" s="4" t="n">
-        <v>70.5</v>
+        <v>45.64</v>
       </c>
       <c r="F171" s="4" t="n">
-        <v>71.16</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>V2RETAIL</t>
         </is>
       </c>
       <c r="B172" s="3" t="inlineStr">
@@ -5882,22 +6016,22 @@
         </is>
       </c>
       <c r="C172" s="4" t="n">
-        <v>433.8</v>
+        <v>230.37</v>
       </c>
       <c r="D172" s="4" t="n">
-        <v>48.47</v>
+        <v>50.54</v>
       </c>
       <c r="E172" s="4" t="n">
-        <v>48.64</v>
+        <v>55.55</v>
       </c>
       <c r="F172" s="4" t="n">
-        <v>56.5</v>
+        <v>66.78</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>TMB</t>
+          <t>KITEX</t>
         </is>
       </c>
       <c r="B173" s="3" t="inlineStr">
@@ -5906,22 +6040,22 @@
         </is>
       </c>
       <c r="C173" s="4" t="n">
-        <v>732.6</v>
+        <v>159.88</v>
       </c>
       <c r="D173" s="4" t="n">
-        <v>48.37</v>
+        <v>50.49</v>
       </c>
       <c r="E173" s="4" t="n">
-        <v>61.79</v>
+        <v>45.56</v>
       </c>
       <c r="F173" s="4" t="n">
-        <v>70.04000000000001</v>
+        <v>48.84</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>TSFINV</t>
+          <t>PRAJIND</t>
         </is>
       </c>
       <c r="B174" s="3" t="inlineStr">
@@ -5930,22 +6064,22 @@
         </is>
       </c>
       <c r="C174" s="4" t="n">
-        <v>396.75</v>
+        <v>353.7</v>
       </c>
       <c r="D174" s="4" t="n">
-        <v>48.34</v>
+        <v>50.46</v>
       </c>
       <c r="E174" s="4" t="n">
-        <v>45.46</v>
+        <v>50.56</v>
       </c>
       <c r="F174" s="4" t="n">
-        <v>52.52</v>
+        <v>43.49</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>ELLEN</t>
+          <t>IIFLCAPS</t>
         </is>
       </c>
       <c r="B175" s="3" t="inlineStr">
@@ -5954,22 +6088,22 @@
         </is>
       </c>
       <c r="C175" s="4" t="n">
-        <v>269.85</v>
+        <v>340.15</v>
       </c>
       <c r="D175" s="4" t="n">
-        <v>48.3</v>
+        <v>50.42</v>
       </c>
       <c r="E175" s="4" t="n">
-        <v>44.18</v>
+        <v>55.65</v>
       </c>
       <c r="F175" s="4" t="n">
-        <v/>
+        <v>58.33</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>CAMPUS</t>
+          <t>NESCO</t>
         </is>
       </c>
       <c r="B176" s="3" t="inlineStr">
@@ -5978,22 +6112,22 @@
         </is>
       </c>
       <c r="C176" s="4" t="n">
-        <v>237.85</v>
+        <v>1125.1</v>
       </c>
       <c r="D176" s="4" t="n">
-        <v>48.17</v>
+        <v>50.18</v>
       </c>
       <c r="E176" s="4" t="n">
-        <v>43.57</v>
+        <v>46.98</v>
       </c>
       <c r="F176" s="4" t="n">
-        <v>43.44</v>
+        <v>53.02</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>SUDARSCHEM</t>
+          <t>SHARDACROP</t>
         </is>
       </c>
       <c r="B177" s="3" t="inlineStr">
@@ -6002,22 +6136,22 @@
         </is>
       </c>
       <c r="C177" s="4" t="n">
-        <v>891.25</v>
+        <v>910.65</v>
       </c>
       <c r="D177" s="4" t="n">
-        <v>48.12</v>
+        <v>50.14</v>
       </c>
       <c r="E177" s="4" t="n">
-        <v>46.45</v>
+        <v>46.76</v>
       </c>
       <c r="F177" s="4" t="n">
-        <v>47.55</v>
+        <v>54.17</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>AARTIDRUGS</t>
+          <t>FEDFINA</t>
         </is>
       </c>
       <c r="B178" s="3" t="inlineStr">
@@ -6026,22 +6160,22 @@
         </is>
       </c>
       <c r="C178" s="4" t="n">
-        <v>372.7</v>
+        <v>152.97</v>
       </c>
       <c r="D178" s="4" t="n">
-        <v>48.1</v>
+        <v>50.12</v>
       </c>
       <c r="E178" s="4" t="n">
-        <v>46.81</v>
+        <v>55.55</v>
       </c>
       <c r="F178" s="4" t="n">
-        <v>44.03</v>
+        <v>57.83</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>EUREKAFORB</t>
+          <t>DBREALTY</t>
         </is>
       </c>
       <c r="B179" s="3" t="inlineStr">
@@ -6050,22 +6184,22 @@
         </is>
       </c>
       <c r="C179" s="4" t="n">
-        <v>458.3</v>
+        <v>114.66</v>
       </c>
       <c r="D179" s="4" t="n">
-        <v>47.98</v>
+        <v>49.91</v>
       </c>
       <c r="E179" s="4" t="n">
-        <v>41.86</v>
+        <v>48.46</v>
       </c>
       <c r="F179" s="4" t="n">
-        <v>41.57</v>
+        <v>44.92</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>PURVA</t>
+          <t>JAYNECOIND</t>
         </is>
       </c>
       <c r="B180" s="3" t="inlineStr">
@@ -6074,22 +6208,22 @@
         </is>
       </c>
       <c r="C180" s="4" t="n">
-        <v>212.97</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="D180" s="4" t="n">
-        <v>47.97</v>
+        <v>49.7</v>
       </c>
       <c r="E180" s="4" t="n">
-        <v>46.99</v>
+        <v>53.26</v>
       </c>
       <c r="F180" s="4" t="n">
-        <v>44.73</v>
+        <v>60.74</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>CRAMC</t>
+          <t>OSWALPUMPS</t>
         </is>
       </c>
       <c r="B181" s="3" t="inlineStr">
@@ -6098,13 +6232,13 @@
         </is>
       </c>
       <c r="C181" s="4" t="n">
-        <v>247.61</v>
+        <v>409.45</v>
       </c>
       <c r="D181" s="4" t="n">
-        <v>47.87</v>
+        <v>49.67</v>
       </c>
       <c r="E181" s="4" t="n">
-        <v>44.48</v>
+        <v>47.7</v>
       </c>
       <c r="F181" s="4" t="n">
         <v/>
@@ -6113,7 +6247,7 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>SANOFICONR</t>
+          <t>GNFC</t>
         </is>
       </c>
       <c r="B182" s="3" t="inlineStr">
@@ -6122,22 +6256,22 @@
         </is>
       </c>
       <c r="C182" s="4" t="n">
-        <v>4618.1</v>
+        <v>529.2</v>
       </c>
       <c r="D182" s="4" t="n">
-        <v>47.78</v>
+        <v>49.65</v>
       </c>
       <c r="E182" s="4" t="n">
-        <v>51.79</v>
+        <v>58.64</v>
       </c>
       <c r="F182" s="4" t="n">
-        <v>48.72</v>
+        <v>51.69</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>GPPL</t>
+          <t>HCC</t>
         </is>
       </c>
       <c r="B183" s="3" t="inlineStr">
@@ -6146,22 +6280,22 @@
         </is>
       </c>
       <c r="C183" s="4" t="n">
-        <v>153.81</v>
+        <v>24.83</v>
       </c>
       <c r="D183" s="4" t="n">
-        <v>47.75</v>
+        <v>49.6</v>
       </c>
       <c r="E183" s="4" t="n">
-        <v>45.32</v>
+        <v>57.89</v>
       </c>
       <c r="F183" s="4" t="n">
-        <v>50.12</v>
+        <v>49.01</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>ATLANTAELE</t>
+          <t>AHLUCONT</t>
         </is>
       </c>
       <c r="B184" s="3" t="inlineStr">
@@ -6170,22 +6304,22 @@
         </is>
       </c>
       <c r="C184" s="4" t="n">
-        <v>1812</v>
+        <v>829.4</v>
       </c>
       <c r="D184" s="4" t="n">
-        <v>47.11</v>
+        <v>49.5</v>
       </c>
       <c r="E184" s="4" t="n">
-        <v>64.34999999999999</v>
+        <v>49.24</v>
       </c>
       <c r="F184" s="4" t="n">
-        <v/>
+        <v>48.02</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>PRAJIND</t>
+          <t>NFL</t>
         </is>
       </c>
       <c r="B185" s="3" t="inlineStr">
@@ -6194,22 +6328,22 @@
         </is>
       </c>
       <c r="C185" s="4" t="n">
-        <v>348.65</v>
+        <v>75.63</v>
       </c>
       <c r="D185" s="4" t="n">
-        <v>47</v>
+        <v>49.5</v>
       </c>
       <c r="E185" s="4" t="n">
-        <v>49.15</v>
+        <v>45.65</v>
       </c>
       <c r="F185" s="4" t="n">
-        <v>43.09</v>
+        <v>44.78</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>APOLLO</t>
+          <t>KIRLOSBROS</t>
         </is>
       </c>
       <c r="B186" s="3" t="inlineStr">
@@ -6218,22 +6352,22 @@
         </is>
       </c>
       <c r="C186" s="4" t="n">
-        <v>384.4</v>
+        <v>1852.5</v>
       </c>
       <c r="D186" s="4" t="n">
-        <v>46.82</v>
+        <v>49.46</v>
       </c>
       <c r="E186" s="4" t="n">
-        <v>62.91</v>
+        <v>56.54</v>
       </c>
       <c r="F186" s="4" t="n">
-        <v>68.43000000000001</v>
+        <v>54.4</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>VGUARD</t>
+          <t>CSBBANK</t>
         </is>
       </c>
       <c r="B187" s="3" t="inlineStr">
@@ -6242,22 +6376,22 @@
         </is>
       </c>
       <c r="C187" s="4" t="n">
-        <v>306.2</v>
+        <v>352.2</v>
       </c>
       <c r="D187" s="4" t="n">
-        <v>46.8</v>
+        <v>49.38</v>
       </c>
       <c r="E187" s="4" t="n">
-        <v>41.01</v>
+        <v>44.4</v>
       </c>
       <c r="F187" s="4" t="n">
-        <v>42.26</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>DBREALTY</t>
+          <t>FIEMIND</t>
         </is>
       </c>
       <c r="B188" s="3" t="inlineStr">
@@ -6266,22 +6400,22 @@
         </is>
       </c>
       <c r="C188" s="4" t="n">
-        <v>112.96</v>
+        <v>2261.7</v>
       </c>
       <c r="D188" s="4" t="n">
-        <v>46.57</v>
+        <v>49.33</v>
       </c>
       <c r="E188" s="4" t="n">
-        <v>47.69</v>
+        <v>54.9</v>
       </c>
       <c r="F188" s="4" t="n">
-        <v>44.48</v>
+        <v>67.02</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>ORIENTCEM</t>
+          <t>TARC</t>
         </is>
       </c>
       <c r="B189" s="3" t="inlineStr">
@@ -6290,22 +6424,22 @@
         </is>
       </c>
       <c r="C189" s="4" t="n">
-        <v>133.92</v>
+        <v>126.85</v>
       </c>
       <c r="D189" s="4" t="n">
-        <v>46.44</v>
+        <v>49.08</v>
       </c>
       <c r="E189" s="4" t="n">
-        <v>35.34</v>
+        <v>42.1</v>
       </c>
       <c r="F189" s="4" t="n">
-        <v>35.38</v>
+        <v>45.63</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>TIPSMUSIC</t>
+          <t>DBL</t>
         </is>
       </c>
       <c r="B190" s="3" t="inlineStr">
@@ -6314,22 +6448,22 @@
         </is>
       </c>
       <c r="C190" s="4" t="n">
-        <v>637.85</v>
+        <v>441.6</v>
       </c>
       <c r="D190" s="4" t="n">
-        <v>46.33</v>
+        <v>49.04</v>
       </c>
       <c r="E190" s="4" t="n">
-        <v>56.49</v>
+        <v>49.05</v>
       </c>
       <c r="F190" s="4" t="n">
-        <v>57.94</v>
+        <v>50.01</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>NFL</t>
+          <t>KNRCON</t>
         </is>
       </c>
       <c r="B191" s="3" t="inlineStr">
@@ -6338,22 +6472,22 @@
         </is>
       </c>
       <c r="C191" s="4" t="n">
-        <v>75.18000000000001</v>
+        <v>131.4</v>
       </c>
       <c r="D191" s="4" t="n">
-        <v>46.3</v>
+        <v>49.03</v>
       </c>
       <c r="E191" s="4" t="n">
-        <v>45.29</v>
+        <v>46.27</v>
       </c>
       <c r="F191" s="4" t="n">
-        <v>44.69</v>
+        <v>35.37</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>ASHAPURMIN</t>
+          <t>RENUKA</t>
         </is>
       </c>
       <c r="B192" s="3" t="inlineStr">
@@ -6362,22 +6496,22 @@
         </is>
       </c>
       <c r="C192" s="4" t="n">
-        <v>671.3</v>
+        <v>22.99</v>
       </c>
       <c r="D192" s="4" t="n">
-        <v>46</v>
+        <v>48.99</v>
       </c>
       <c r="E192" s="4" t="n">
-        <v>53.41</v>
+        <v>40.67</v>
       </c>
       <c r="F192" s="4" t="n">
-        <v>57.5</v>
+        <v>37.72</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>BALUFORGE</t>
+          <t>FINPIPE</t>
         </is>
       </c>
       <c r="B193" s="3" t="inlineStr">
@@ -6386,22 +6520,22 @@
         </is>
       </c>
       <c r="C193" s="4" t="n">
-        <v>453.95</v>
+        <v>174.77</v>
       </c>
       <c r="D193" s="4" t="n">
-        <v>45.76</v>
+        <v>48.91</v>
       </c>
       <c r="E193" s="4" t="n">
-        <v>43.66</v>
+        <v>48.57</v>
       </c>
       <c r="F193" s="4" t="n">
-        <v>46.35</v>
+        <v>44.78</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>MIDHANI</t>
+          <t>SANOFICONR</t>
         </is>
       </c>
       <c r="B194" s="3" t="inlineStr">
@@ -6410,22 +6544,22 @@
         </is>
       </c>
       <c r="C194" s="4" t="n">
-        <v>413.05</v>
+        <v>4624.7</v>
       </c>
       <c r="D194" s="4" t="n">
-        <v>45.63</v>
+        <v>48.63</v>
       </c>
       <c r="E194" s="4" t="n">
-        <v>58.18</v>
+        <v>51.91</v>
       </c>
       <c r="F194" s="4" t="n">
-        <v>55.25</v>
+        <v>49.01</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>SHAREINDIA</t>
+          <t>DIACABS</t>
         </is>
       </c>
       <c r="B195" s="3" t="inlineStr">
@@ -6434,22 +6568,22 @@
         </is>
       </c>
       <c r="C195" s="4" t="n">
-        <v>135.19</v>
+        <v>198.89</v>
       </c>
       <c r="D195" s="4" t="n">
-        <v>45.37</v>
+        <v>48.39</v>
       </c>
       <c r="E195" s="4" t="n">
-        <v>44.2</v>
+        <v>68.47</v>
       </c>
       <c r="F195" s="4" t="n">
-        <v>39.68</v>
+        <v>65.20999999999999</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>FIEMIND</t>
+          <t>ELECTCAST</t>
         </is>
       </c>
       <c r="B196" s="3" t="inlineStr">
@@ -6458,22 +6592,22 @@
         </is>
       </c>
       <c r="C196" s="4" t="n">
-        <v>2229.1</v>
+        <v>77.83</v>
       </c>
       <c r="D196" s="4" t="n">
-        <v>45.27</v>
+        <v>48.27</v>
       </c>
       <c r="E196" s="4" t="n">
-        <v>53.1</v>
+        <v>48.5</v>
       </c>
       <c r="F196" s="4" t="n">
-        <v>66.15000000000001</v>
+        <v>43.03</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>JAIBALAJI</t>
+          <t>HGINFRA</t>
         </is>
       </c>
       <c r="B197" s="3" t="inlineStr">
@@ -6482,22 +6616,22 @@
         </is>
       </c>
       <c r="C197" s="4" t="n">
-        <v>68.19</v>
+        <v>571.8</v>
       </c>
       <c r="D197" s="4" t="n">
-        <v>45.03</v>
+        <v>48.23</v>
       </c>
       <c r="E197" s="4" t="n">
-        <v>45.78</v>
+        <v>42.15</v>
       </c>
       <c r="F197" s="4" t="n">
-        <v>41.08</v>
+        <v>36.72</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>AWFIS</t>
+          <t>BIRLACORPN</t>
         </is>
       </c>
       <c r="B198" s="3" t="inlineStr">
@@ -6506,22 +6640,22 @@
         </is>
       </c>
       <c r="C198" s="4" t="n">
-        <v>304.85</v>
+        <v>981.55</v>
       </c>
       <c r="D198" s="4" t="n">
-        <v>44.64</v>
+        <v>48.21</v>
       </c>
       <c r="E198" s="4" t="n">
-        <v>38.45</v>
+        <v>48.04</v>
       </c>
       <c r="F198" s="4" t="n">
-        <v>32.23</v>
+        <v>42.99</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>AZAD</t>
+          <t>HAPPSTMNDS</t>
         </is>
       </c>
       <c r="B199" s="3" t="inlineStr">
@@ -6530,22 +6664,22 @@
         </is>
       </c>
       <c r="C199" s="4" t="n">
-        <v>2020.1</v>
+        <v>350.05</v>
       </c>
       <c r="D199" s="4" t="n">
-        <v>44.23</v>
+        <v>48.08</v>
       </c>
       <c r="E199" s="4" t="n">
-        <v>56.63</v>
+        <v>37.04</v>
       </c>
       <c r="F199" s="4" t="n">
-        <v>60.89</v>
+        <v>25.53</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>HGINFRA</t>
+          <t>KPIGREEN</t>
         </is>
       </c>
       <c r="B200" s="3" t="inlineStr">
@@ -6554,22 +6688,22 @@
         </is>
       </c>
       <c r="C200" s="4" t="n">
-        <v>567.5</v>
+        <v>404.3</v>
       </c>
       <c r="D200" s="4" t="n">
-        <v>44.21</v>
+        <v>47.71</v>
       </c>
       <c r="E200" s="4" t="n">
-        <v>41.95</v>
+        <v>46.29</v>
       </c>
       <c r="F200" s="4" t="n">
-        <v>36.7</v>
+        <v>48.85</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>STARCEMENT</t>
+          <t>VIPIND</t>
         </is>
       </c>
       <c r="B201" s="3" t="inlineStr">
@@ -6578,22 +6712,22 @@
         </is>
       </c>
       <c r="C201" s="4" t="n">
-        <v>210.65</v>
+        <v>308.35</v>
       </c>
       <c r="D201" s="4" t="n">
-        <v>44.19</v>
+        <v>47.35</v>
       </c>
       <c r="E201" s="4" t="n">
-        <v>44.44</v>
+        <v>41.01</v>
       </c>
       <c r="F201" s="4" t="n">
-        <v>49.78</v>
+        <v>36.77</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>INDIAGLYCO</t>
+          <t>RAYMONDLSL</t>
         </is>
       </c>
       <c r="B202" s="3" t="inlineStr">
@@ -6602,22 +6736,22 @@
         </is>
       </c>
       <c r="C202" s="4" t="n">
-        <v>955.45</v>
+        <v>774</v>
       </c>
       <c r="D202" s="4" t="n">
-        <v>43.99</v>
+        <v>47.22</v>
       </c>
       <c r="E202" s="4" t="n">
-        <v>49.36</v>
+        <v>41.4</v>
       </c>
       <c r="F202" s="4" t="n">
-        <v>57.67</v>
+        <v>26.31</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>V2RETAIL</t>
+          <t>IMFA</t>
         </is>
       </c>
       <c r="B203" s="3" t="inlineStr">
@@ -6626,22 +6760,22 @@
         </is>
       </c>
       <c r="C203" s="4" t="n">
-        <v>221.23</v>
+        <v>1374.5</v>
       </c>
       <c r="D203" s="4" t="n">
-        <v>43.98</v>
+        <v>47.2</v>
       </c>
       <c r="E203" s="4" t="n">
-        <v>52.44</v>
+        <v>51.49</v>
       </c>
       <c r="F203" s="4" t="n">
-        <v>64.20999999999999</v>
+        <v>62.38</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>GSFC</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B204" s="3" t="inlineStr">
@@ -6650,22 +6784,22 @@
         </is>
       </c>
       <c r="C204" s="4" t="n">
-        <v>163.13</v>
+        <v>104.17</v>
       </c>
       <c r="D204" s="4" t="n">
-        <v>43.94</v>
+        <v>47.09</v>
       </c>
       <c r="E204" s="4" t="n">
-        <v>44.61</v>
+        <v>45.54</v>
       </c>
       <c r="F204" s="4" t="n">
-        <v>45.47</v>
+        <v>41.19</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>BAJAJELEC</t>
+          <t>JKPAPER</t>
         </is>
       </c>
       <c r="B205" s="3" t="inlineStr">
@@ -6674,22 +6808,22 @@
         </is>
       </c>
       <c r="C205" s="4" t="n">
-        <v>322.35</v>
+        <v>348.95</v>
       </c>
       <c r="D205" s="4" t="n">
-        <v>43.93</v>
+        <v>46.42</v>
       </c>
       <c r="E205" s="4" t="n">
-        <v>32.53</v>
+        <v>46.72</v>
       </c>
       <c r="F205" s="4" t="n">
-        <v>28.55</v>
+        <v>48.53</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>WEBELSOLAR</t>
+          <t>GSFC</t>
         </is>
       </c>
       <c r="B206" s="3" t="inlineStr">
@@ -6698,22 +6832,22 @@
         </is>
       </c>
       <c r="C206" s="4" t="n">
-        <v>101.48</v>
+        <v>162.38</v>
       </c>
       <c r="D206" s="4" t="n">
-        <v>43.6</v>
+        <v>46.21</v>
       </c>
       <c r="E206" s="4" t="n">
-        <v>53.05</v>
+        <v>43.43</v>
       </c>
       <c r="F206" s="4" t="n">
-        <v>52.29</v>
+        <v>45.13</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>GHCL</t>
+          <t>CAMPUS</t>
         </is>
       </c>
       <c r="B207" s="3" t="inlineStr">
@@ -6722,22 +6856,22 @@
         </is>
       </c>
       <c r="C207" s="4" t="n">
-        <v>429.1</v>
+        <v>235.06</v>
       </c>
       <c r="D207" s="4" t="n">
-        <v>43.52</v>
+        <v>46.09</v>
       </c>
       <c r="E207" s="4" t="n">
-        <v>37.71</v>
+        <v>42.6</v>
       </c>
       <c r="F207" s="4" t="n">
-        <v>41.68</v>
+        <v>43.12</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>CELLO</t>
+          <t>DYNAMATECH</t>
         </is>
       </c>
       <c r="B208" s="3" t="inlineStr">
@@ -6746,22 +6880,22 @@
         </is>
       </c>
       <c r="C208" s="4" t="n">
-        <v>378.45</v>
+        <v>10288</v>
       </c>
       <c r="D208" s="4" t="n">
-        <v>43.37</v>
+        <v>45.83</v>
       </c>
       <c r="E208" s="4" t="n">
-        <v>34.16</v>
+        <v>51.39</v>
       </c>
       <c r="F208" s="4" t="n">
-        <v>30.58</v>
+        <v>62.14</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>WAKEFIT</t>
+          <t>SANDUMA</t>
         </is>
       </c>
       <c r="B209" s="3" t="inlineStr">
@@ -6770,22 +6904,22 @@
         </is>
       </c>
       <c r="C209" s="4" t="n">
-        <v>119.83</v>
+        <v>209.73</v>
       </c>
       <c r="D209" s="4" t="n">
-        <v>43.36</v>
+        <v>45.81</v>
       </c>
       <c r="E209" s="4" t="n">
-        <v>34.17</v>
+        <v>49.86</v>
       </c>
       <c r="F209" s="4" t="n">
-        <v/>
+        <v>56.95</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>DYNAMATECH</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="B210" s="3" t="inlineStr">
@@ -6794,22 +6928,22 @@
         </is>
       </c>
       <c r="C210" s="4" t="n">
-        <v>10232</v>
+        <v>263.4</v>
       </c>
       <c r="D210" s="4" t="n">
-        <v>43.32</v>
+        <v>45.53</v>
       </c>
       <c r="E210" s="4" t="n">
-        <v>50.81</v>
+        <v>61.92</v>
       </c>
       <c r="F210" s="4" t="n">
-        <v>61.63</v>
+        <v>64.91</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>ZAGGLE</t>
+          <t>POWERMECH</t>
         </is>
       </c>
       <c r="B211" s="3" t="inlineStr">
@@ -6818,22 +6952,22 @@
         </is>
       </c>
       <c r="C211" s="4" t="n">
-        <v>205.6</v>
+        <v>2631.3</v>
       </c>
       <c r="D211" s="4" t="n">
-        <v>43.08</v>
+        <v>45.52</v>
       </c>
       <c r="E211" s="4" t="n">
-        <v>36.59</v>
+        <v>56.44</v>
       </c>
       <c r="F211" s="4" t="n">
-        <v>39.58</v>
+        <v>53.35</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>MASTEK</t>
+          <t>VOLTAMP</t>
         </is>
       </c>
       <c r="B212" s="3" t="inlineStr">
@@ -6842,22 +6976,22 @@
         </is>
       </c>
       <c r="C212" s="4" t="n">
-        <v>1575.2</v>
+        <v>9702</v>
       </c>
       <c r="D212" s="4" t="n">
-        <v>42.7</v>
+        <v>45.45</v>
       </c>
       <c r="E212" s="4" t="n">
-        <v>39.22</v>
+        <v>53.91</v>
       </c>
       <c r="F212" s="4" t="n">
-        <v>38.73</v>
+        <v>54.31</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>JKLAKSHMI</t>
+          <t>RTNPOWER</t>
         </is>
       </c>
       <c r="B213" s="3" t="inlineStr">
@@ -6866,22 +7000,22 @@
         </is>
       </c>
       <c r="C213" s="4" t="n">
-        <v>594.6</v>
+        <v>9.16</v>
       </c>
       <c r="D213" s="4" t="n">
-        <v>42.64</v>
+        <v>45.4</v>
       </c>
       <c r="E213" s="4" t="n">
-        <v>37.72</v>
+        <v>47.18</v>
       </c>
       <c r="F213" s="4" t="n">
-        <v>40.58</v>
+        <v>46.69</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>RTNINDIA</t>
+          <t>VGUARD</t>
         </is>
       </c>
       <c r="B214" s="3" t="inlineStr">
@@ -6890,22 +7024,22 @@
         </is>
       </c>
       <c r="C214" s="4" t="n">
-        <v>33.88</v>
+        <v>302.9</v>
       </c>
       <c r="D214" s="4" t="n">
-        <v>42.57</v>
+        <v>45.38</v>
       </c>
       <c r="E214" s="4" t="n">
-        <v>45.42</v>
+        <v>39.88</v>
       </c>
       <c r="F214" s="4" t="n">
-        <v>41.17</v>
+        <v>42.06</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>RTNPOWER</t>
+          <t>ORKLAINDIA</t>
         </is>
       </c>
       <c r="B215" s="3" t="inlineStr">
@@ -6914,22 +7048,22 @@
         </is>
       </c>
       <c r="C215" s="4" t="n">
-        <v>9.119999999999999</v>
+        <v>607.8</v>
       </c>
       <c r="D215" s="4" t="n">
-        <v>42.42</v>
+        <v>45.35</v>
       </c>
       <c r="E215" s="4" t="n">
-        <v>46.47</v>
+        <v>46.01</v>
       </c>
       <c r="F215" s="4" t="n">
-        <v>46.41</v>
+        <v/>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>TARC</t>
+          <t>STARCEMENT</t>
         </is>
       </c>
       <c r="B216" s="3" t="inlineStr">
@@ -6938,22 +7072,22 @@
         </is>
       </c>
       <c r="C216" s="4" t="n">
-        <v>123.77</v>
+        <v>209.69</v>
       </c>
       <c r="D216" s="4" t="n">
-        <v>42.01</v>
+        <v>45.25</v>
       </c>
       <c r="E216" s="4" t="n">
-        <v>38.91</v>
+        <v>44.18</v>
       </c>
       <c r="F216" s="4" t="n">
-        <v>44.9</v>
+        <v>49.67</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>PRSMJOHNSN</t>
+          <t>MAHSEAMLES</t>
         </is>
       </c>
       <c r="B217" s="3" t="inlineStr">
@@ -6962,22 +7096,22 @@
         </is>
       </c>
       <c r="C217" s="4" t="n">
-        <v>117.92</v>
+        <v>610.05</v>
       </c>
       <c r="D217" s="4" t="n">
-        <v>41.92</v>
+        <v>44.9</v>
       </c>
       <c r="E217" s="4" t="n">
-        <v>38.24</v>
+        <v>51.41</v>
       </c>
       <c r="F217" s="4" t="n">
-        <v>41.41</v>
+        <v>50.36</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>RENUKA</t>
+          <t>AWFIS</t>
         </is>
       </c>
       <c r="B218" s="3" t="inlineStr">
@@ -6986,22 +7120,22 @@
         </is>
       </c>
       <c r="C218" s="4" t="n">
-        <v>22.4</v>
+        <v>301.4</v>
       </c>
       <c r="D218" s="4" t="n">
-        <v>41.74</v>
+        <v>44.66</v>
       </c>
       <c r="E218" s="4" t="n">
-        <v>37.7</v>
+        <v>38.11</v>
       </c>
       <c r="F218" s="4" t="n">
-        <v>36.43</v>
+        <v>32.08</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>PTC</t>
+          <t>JSLL</t>
         </is>
       </c>
       <c r="B219" s="3" t="inlineStr">
@@ -7010,22 +7144,22 @@
         </is>
       </c>
       <c r="C219" s="4" t="n">
-        <v>181.8</v>
+        <v>576.05</v>
       </c>
       <c r="D219" s="4" t="n">
-        <v>41.66</v>
+        <v>44.62</v>
       </c>
       <c r="E219" s="4" t="n">
-        <v>51.19</v>
+        <v>42.13</v>
       </c>
       <c r="F219" s="4" t="n">
-        <v>56.11</v>
+        <v>42.18</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>ACI</t>
+          <t>RALLIS</t>
         </is>
       </c>
       <c r="B220" s="3" t="inlineStr">
@@ -7034,22 +7168,22 @@
         </is>
       </c>
       <c r="C220" s="4" t="n">
-        <v>522.5</v>
+        <v>228.14</v>
       </c>
       <c r="D220" s="4" t="n">
-        <v>41.66</v>
+        <v>44.53</v>
       </c>
       <c r="E220" s="4" t="n">
-        <v>40.72</v>
+        <v>39.67</v>
       </c>
       <c r="F220" s="4" t="n">
-        <v>42.73</v>
+        <v>44.69</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>KPIGREEN</t>
+          <t>RTNINDIA</t>
         </is>
       </c>
       <c r="B221" s="3" t="inlineStr">
@@ -7058,22 +7192,22 @@
         </is>
       </c>
       <c r="C221" s="4" t="n">
-        <v>398.7</v>
+        <v>33.59</v>
       </c>
       <c r="D221" s="4" t="n">
-        <v>41.64</v>
+        <v>44.45</v>
       </c>
       <c r="E221" s="4" t="n">
-        <v>44.91</v>
+        <v>44.88</v>
       </c>
       <c r="F221" s="4" t="n">
-        <v>48.37</v>
+        <v>41.08</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>FEDFINA</t>
+          <t>GHCL</t>
         </is>
       </c>
       <c r="B222" s="3" t="inlineStr">
@@ -7082,22 +7216,22 @@
         </is>
       </c>
       <c r="C222" s="4" t="n">
-        <v>148.37</v>
+        <v>430.15</v>
       </c>
       <c r="D222" s="4" t="n">
-        <v>41.57</v>
+        <v>44.43</v>
       </c>
       <c r="E222" s="4" t="n">
-        <v>51.81</v>
+        <v>38.7</v>
       </c>
       <c r="F222" s="4" t="n">
-        <v>56.2</v>
+        <v>41.68</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>GODREJAGRO</t>
+          <t>SENCO</t>
         </is>
       </c>
       <c r="B223" s="3" t="inlineStr">
@@ -7106,22 +7240,22 @@
         </is>
       </c>
       <c r="C223" s="4" t="n">
-        <v>562.05</v>
+        <v>326.05</v>
       </c>
       <c r="D223" s="4" t="n">
-        <v>41.45</v>
+        <v>43.74</v>
       </c>
       <c r="E223" s="4" t="n">
-        <v>43.58</v>
+        <v>48.97</v>
       </c>
       <c r="F223" s="4" t="n">
-        <v>44.73</v>
+        <v>47.68</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>LUMAXTECH</t>
+          <t>ELLEN</t>
         </is>
       </c>
       <c r="B224" s="3" t="inlineStr">
@@ -7130,46 +7264,46 @@
         </is>
       </c>
       <c r="C224" s="4" t="n">
-        <v>1548.9</v>
+        <v>261.25</v>
       </c>
       <c r="D224" s="4" t="n">
-        <v>41.21</v>
+        <v>43.62</v>
       </c>
       <c r="E224" s="4" t="n">
-        <v>48.75</v>
+        <v>42.4</v>
       </c>
       <c r="F224" s="4" t="n">
-        <v>63.41</v>
+        <v/>
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="inlineStr">
-        <is>
-          <t>PICCADIL</t>
-        </is>
-      </c>
-      <c r="B225" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C225" s="4" t="n">
-        <v>564.75</v>
-      </c>
-      <c r="D225" s="4" t="n">
-        <v>40.88</v>
-      </c>
-      <c r="E225" s="4" t="n">
-        <v>45.44</v>
-      </c>
-      <c r="F225" s="4" t="n">
-        <v/>
+      <c r="A225" s="5" t="inlineStr">
+        <is>
+          <t>MTARTECH</t>
+        </is>
+      </c>
+      <c r="B225" s="6" t="inlineStr">
+        <is>
+          <t>Chart</t>
+        </is>
+      </c>
+      <c r="C225" s="7" t="n">
+        <v>7033.5</v>
+      </c>
+      <c r="D225" s="7" t="n">
+        <v>43.14</v>
+      </c>
+      <c r="E225" s="7" t="n">
+        <v>63.59</v>
+      </c>
+      <c r="F225" s="7" t="n">
+        <v>77.40000000000001</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>JSFB</t>
+          <t>GODREJAGRO</t>
         </is>
       </c>
       <c r="B226" s="3" t="inlineStr">
@@ -7178,22 +7312,22 @@
         </is>
       </c>
       <c r="C226" s="4" t="n">
-        <v>448.5</v>
+        <v>559.5</v>
       </c>
       <c r="D226" s="4" t="n">
-        <v>40.53</v>
+        <v>43.08</v>
       </c>
       <c r="E226" s="4" t="n">
-        <v>52.53</v>
+        <v>42.88</v>
       </c>
       <c r="F226" s="4" t="n">
-        <v>49.68</v>
+        <v>44.63</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>CMSINFO</t>
+          <t>MANYAVAR</t>
         </is>
       </c>
       <c r="B227" s="3" t="inlineStr">
@@ -7202,22 +7336,22 @@
         </is>
       </c>
       <c r="C227" s="4" t="n">
-        <v>291.1</v>
+        <v>401.1</v>
       </c>
       <c r="D227" s="4" t="n">
-        <v>40.42</v>
+        <v>42.77</v>
       </c>
       <c r="E227" s="4" t="n">
-        <v>39.24</v>
+        <v>36.14</v>
       </c>
       <c r="F227" s="4" t="n">
-        <v>38</v>
+        <v>28.02</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>SENCO</t>
+          <t>VIKRAMSOLR</t>
         </is>
       </c>
       <c r="B228" s="3" t="inlineStr">
@@ -7226,22 +7360,22 @@
         </is>
       </c>
       <c r="C228" s="4" t="n">
-        <v>323.55</v>
+        <v>188.87</v>
       </c>
       <c r="D228" s="4" t="n">
-        <v>40.07</v>
+        <v>42.64</v>
       </c>
       <c r="E228" s="4" t="n">
-        <v>48.63</v>
+        <v>38.82</v>
       </c>
       <c r="F228" s="4" t="n">
-        <v>47.61</v>
+        <v/>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>GOKULAGRO</t>
+          <t>RATNAMANI</t>
         </is>
       </c>
       <c r="B229" s="3" t="inlineStr">
@@ -7250,22 +7384,22 @@
         </is>
       </c>
       <c r="C229" s="4" t="n">
-        <v>217.58</v>
+        <v>2512.5</v>
       </c>
       <c r="D229" s="4" t="n">
-        <v>39.93</v>
+        <v>42.63</v>
       </c>
       <c r="E229" s="4" t="n">
-        <v>57.5</v>
+        <v>50.18</v>
       </c>
       <c r="F229" s="4" t="n">
-        <v>65.06</v>
+        <v>48.04</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>PCJEWELLER</t>
+          <t>BECTORFOOD</t>
         </is>
       </c>
       <c r="B230" s="3" t="inlineStr">
@@ -7274,22 +7408,22 @@
         </is>
       </c>
       <c r="C230" s="4" t="n">
-        <v>8.57</v>
+        <v>176.61</v>
       </c>
       <c r="D230" s="4" t="n">
-        <v>39.92</v>
+        <v>42.02</v>
       </c>
       <c r="E230" s="4" t="n">
-        <v>41.69</v>
+        <v>36.98</v>
       </c>
       <c r="F230" s="4" t="n">
-        <v>45.75</v>
+        <v>38.66</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>SANDUMA</t>
+          <t>ASHAPURMIN</t>
         </is>
       </c>
       <c r="B231" s="3" t="inlineStr">
@@ -7298,22 +7432,22 @@
         </is>
       </c>
       <c r="C231" s="4" t="n">
-        <v>207.03</v>
+        <v>645.6</v>
       </c>
       <c r="D231" s="4" t="n">
-        <v>39.57</v>
+        <v>41.48</v>
       </c>
       <c r="E231" s="4" t="n">
-        <v>48.79</v>
+        <v>50.58</v>
       </c>
       <c r="F231" s="4" t="n">
-        <v>56.67</v>
+        <v>56.26</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>RALLIS</t>
+          <t>GMMPFAUDLR</t>
         </is>
       </c>
       <c r="B232" s="3" t="inlineStr">
@@ -7322,22 +7456,22 @@
         </is>
       </c>
       <c r="C232" s="4" t="n">
-        <v>227.52</v>
+        <v>776.75</v>
       </c>
       <c r="D232" s="4" t="n">
-        <v>39.39</v>
+        <v>41.34</v>
       </c>
       <c r="E232" s="4" t="n">
-        <v>39.95</v>
+        <v>34.67</v>
       </c>
       <c r="F232" s="4" t="n">
-        <v>44.46</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>SHARDACROP</t>
+          <t>MOIL</t>
         </is>
       </c>
       <c r="B233" s="3" t="inlineStr">
@@ -7346,22 +7480,22 @@
         </is>
       </c>
       <c r="C233" s="4" t="n">
-        <v>876.55</v>
+        <v>282.2</v>
       </c>
       <c r="D233" s="4" t="n">
-        <v>39.22</v>
+        <v>41.03</v>
       </c>
       <c r="E233" s="4" t="n">
-        <v>44.25</v>
+        <v>41.2</v>
       </c>
       <c r="F233" s="4" t="n">
-        <v>53.24</v>
+        <v>45.36</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>HCG</t>
+          <t>LUMAXTECH</t>
         </is>
       </c>
       <c r="B234" s="3" t="inlineStr">
@@ -7370,22 +7504,22 @@
         </is>
       </c>
       <c r="C234" s="4" t="n">
-        <v>600.4</v>
+        <v>1524.5</v>
       </c>
       <c r="D234" s="4" t="n">
-        <v>39.17</v>
+        <v>40.61</v>
       </c>
       <c r="E234" s="4" t="n">
-        <v>47.94</v>
+        <v>47.67</v>
       </c>
       <c r="F234" s="4" t="n">
-        <v>56.04</v>
+        <v>62.56</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>MEDPLUS</t>
+          <t>QPOWER</t>
         </is>
       </c>
       <c r="B235" s="3" t="inlineStr">
@@ -7394,22 +7528,22 @@
         </is>
       </c>
       <c r="C235" s="4" t="n">
-        <v>835</v>
+        <v>1132.1</v>
       </c>
       <c r="D235" s="4" t="n">
-        <v>38.99</v>
+        <v>40.55</v>
       </c>
       <c r="E235" s="4" t="n">
-        <v>47.4</v>
+        <v>54.39</v>
       </c>
       <c r="F235" s="4" t="n">
-        <v>52.28</v>
+        <v>62.44</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>CRIZAC</t>
+          <t>SAATVIKGL</t>
         </is>
       </c>
       <c r="B236" s="3" t="inlineStr">
@@ -7418,13 +7552,13 @@
         </is>
       </c>
       <c r="C236" s="4" t="n">
-        <v>201.39</v>
+        <v>440.2</v>
       </c>
       <c r="D236" s="4" t="n">
-        <v>38.93</v>
+        <v>40.22</v>
       </c>
       <c r="E236" s="4" t="n">
-        <v>39.84</v>
+        <v>50.46</v>
       </c>
       <c r="F236" s="4" t="n">
         <v/>
@@ -7442,22 +7576,22 @@
         </is>
       </c>
       <c r="C237" s="4" t="n">
-        <v>99.59999999999999</v>
+        <v>99.95</v>
       </c>
       <c r="D237" s="4" t="n">
-        <v>37.54</v>
+        <v>39.85</v>
       </c>
       <c r="E237" s="4" t="n">
-        <v>43.12</v>
+        <v>43.27</v>
       </c>
       <c r="F237" s="4" t="n">
-        <v>50.5</v>
+        <v>50.53</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>ADVENZYMES</t>
+          <t>MEDPLUS</t>
         </is>
       </c>
       <c r="B238" s="3" t="inlineStr">
@@ -7466,22 +7600,22 @@
         </is>
       </c>
       <c r="C238" s="4" t="n">
-        <v>348.35</v>
+        <v>822</v>
       </c>
       <c r="D238" s="4" t="n">
-        <v>37.4</v>
+        <v>39.85</v>
       </c>
       <c r="E238" s="4" t="n">
-        <v>55.84</v>
+        <v>45.02</v>
       </c>
       <c r="F238" s="4" t="n">
-        <v>53.19</v>
+        <v>50.82</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>JYOTHYLAB</t>
+          <t>CRIZAC</t>
         </is>
       </c>
       <c r="B239" s="3" t="inlineStr">
@@ -7490,22 +7624,22 @@
         </is>
       </c>
       <c r="C239" s="4" t="n">
-        <v>200.4</v>
+        <v>198.95</v>
       </c>
       <c r="D239" s="4" t="n">
-        <v>37.24</v>
+        <v>39.77</v>
       </c>
       <c r="E239" s="4" t="n">
-        <v>33.17</v>
+        <v>39.42</v>
       </c>
       <c r="F239" s="4" t="n">
-        <v>36.4</v>
+        <v/>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>JKPAPER</t>
+          <t>JKLAKSHMI</t>
         </is>
       </c>
       <c r="B240" s="3" t="inlineStr">
@@ -7514,22 +7648,22 @@
         </is>
       </c>
       <c r="C240" s="4" t="n">
-        <v>341.9</v>
+        <v>579.45</v>
       </c>
       <c r="D240" s="4" t="n">
-        <v>37.1</v>
+        <v>39.21</v>
       </c>
       <c r="E240" s="4" t="n">
-        <v>43.38</v>
+        <v>35.49</v>
       </c>
       <c r="F240" s="4" t="n">
-        <v>47.65</v>
+        <v>39.82</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>PNGJL</t>
+          <t>GOKULAGRO</t>
         </is>
       </c>
       <c r="B241" s="3" t="inlineStr">
@@ -7538,22 +7672,22 @@
         </is>
       </c>
       <c r="C241" s="4" t="n">
-        <v>532.65</v>
+        <v>209.25</v>
       </c>
       <c r="D241" s="4" t="n">
-        <v>36.96</v>
+        <v>37.91</v>
       </c>
       <c r="E241" s="4" t="n">
-        <v>42.66</v>
+        <v>52.39</v>
       </c>
       <c r="F241" s="4" t="n">
-        <v>40.65</v>
+        <v>62.24</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>NESCO</t>
+          <t>PTC</t>
         </is>
       </c>
       <c r="B242" s="3" t="inlineStr">
@@ -7562,22 +7696,22 @@
         </is>
       </c>
       <c r="C242" s="4" t="n">
-        <v>1087.8</v>
+        <v>177.66</v>
       </c>
       <c r="D242" s="4" t="n">
-        <v>36.67</v>
+        <v>37.69</v>
       </c>
       <c r="E242" s="4" t="n">
-        <v>43.94</v>
+        <v>48.91</v>
       </c>
       <c r="F242" s="4" t="n">
-        <v>51.39</v>
+        <v>54.53</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>AXISCADES</t>
+          <t>ATLANTAELE</t>
         </is>
       </c>
       <c r="B243" s="3" t="inlineStr">
@@ -7586,22 +7720,22 @@
         </is>
       </c>
       <c r="C243" s="4" t="n">
-        <v>1691</v>
+        <v>1688.4</v>
       </c>
       <c r="D243" s="4" t="n">
-        <v>36.62</v>
+        <v>37.64</v>
       </c>
       <c r="E243" s="4" t="n">
-        <v>50</v>
+        <v>58.84</v>
       </c>
       <c r="F243" s="4" t="n">
-        <v>62.8</v>
+        <v/>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>IMFA</t>
+          <t>CELLO</t>
         </is>
       </c>
       <c r="B244" s="3" t="inlineStr">
@@ -7610,22 +7744,22 @@
         </is>
       </c>
       <c r="C244" s="4" t="n">
-        <v>1327</v>
+        <v>366.85</v>
       </c>
       <c r="D244" s="4" t="n">
-        <v>36.46</v>
+        <v>37.62</v>
       </c>
       <c r="E244" s="4" t="n">
-        <v>48.87</v>
+        <v>32.1</v>
       </c>
       <c r="F244" s="4" t="n">
-        <v>62.15</v>
+        <v>29.21</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>HAPPSTMNDS</t>
+          <t>PRSMJOHNSN</t>
         </is>
       </c>
       <c r="B245" s="3" t="inlineStr">
@@ -7634,22 +7768,22 @@
         </is>
       </c>
       <c r="C245" s="4" t="n">
-        <v>342.45</v>
+        <v>115.99</v>
       </c>
       <c r="D245" s="4" t="n">
-        <v>35.99</v>
+        <v>37.55</v>
       </c>
       <c r="E245" s="4" t="n">
-        <v>34.2</v>
+        <v>36.45</v>
       </c>
       <c r="F245" s="4" t="n">
-        <v>24.07</v>
+        <v>40.81</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>JAYNECOIND</t>
+          <t>JYOTHYLAB</t>
         </is>
       </c>
       <c r="B246" s="3" t="inlineStr">
@@ -7658,22 +7792,22 @@
         </is>
       </c>
       <c r="C246" s="4" t="n">
-        <v>85.76000000000001</v>
+        <v>192.13</v>
       </c>
       <c r="D246" s="4" t="n">
-        <v>34.93</v>
+        <v>36.03</v>
       </c>
       <c r="E246" s="4" t="n">
-        <v>49.14</v>
+        <v>31.65</v>
       </c>
       <c r="F246" s="4" t="n">
-        <v>59.2</v>
+        <v>36.05</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>PFOCUS</t>
+          <t>TDPOWERSYS</t>
         </is>
       </c>
       <c r="B247" s="3" t="inlineStr">
@@ -7682,22 +7816,22 @@
         </is>
       </c>
       <c r="C247" s="4" t="n">
-        <v>209.94</v>
+        <v>1091.8</v>
       </c>
       <c r="D247" s="4" t="n">
-        <v>33.5</v>
+        <v>35.54</v>
       </c>
       <c r="E247" s="4" t="n">
-        <v>38.64</v>
+        <v>54.2</v>
       </c>
       <c r="F247" s="4" t="n">
-        <v>54.56</v>
+        <v>68.34</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>MOIL</t>
+          <t>AXISCADES</t>
         </is>
       </c>
       <c r="B248" s="3" t="inlineStr">
@@ -7706,22 +7840,22 @@
         </is>
       </c>
       <c r="C248" s="4" t="n">
-        <v>279.55</v>
+        <v>1648.8</v>
       </c>
       <c r="D248" s="4" t="n">
-        <v>33.19</v>
+        <v>34.91</v>
       </c>
       <c r="E248" s="4" t="n">
-        <v>40.13</v>
+        <v>48.36</v>
       </c>
       <c r="F248" s="4" t="n">
-        <v>45</v>
+        <v>61.44</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>VIKRAMSOLR</t>
+          <t>AVANTIFEED</t>
         </is>
       </c>
       <c r="B249" s="3" t="inlineStr">
@@ -7730,22 +7864,22 @@
         </is>
       </c>
       <c r="C249" s="4" t="n">
-        <v>185.28</v>
+        <v>955.6</v>
       </c>
       <c r="D249" s="4" t="n">
-        <v>32.46</v>
+        <v>32.18</v>
       </c>
       <c r="E249" s="4" t="n">
-        <v>37.31</v>
+        <v>40.3</v>
       </c>
       <c r="F249" s="4" t="n">
-        <v/>
+        <v>54.56</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>CSBBANK</t>
+          <t>ADVENZYMES</t>
         </is>
       </c>
       <c r="B250" s="3" t="inlineStr">
@@ -7754,22 +7888,22 @@
         </is>
       </c>
       <c r="C250" s="4" t="n">
-        <v>324.6</v>
+        <v>317.6</v>
       </c>
       <c r="D250" s="4" t="n">
-        <v>29.47</v>
+        <v>31.38</v>
       </c>
       <c r="E250" s="4" t="n">
-        <v>36.51</v>
+        <v>46.85</v>
       </c>
       <c r="F250" s="4" t="n">
-        <v>45.34</v>
+        <v>49.26</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>AVANTIFEED</t>
+          <t>CMSINFO</t>
         </is>
       </c>
       <c r="B251" s="3" t="inlineStr">
@@ -7778,16 +7912,16 @@
         </is>
       </c>
       <c r="C251" s="4" t="n">
-        <v>962.2</v>
+        <v>274.55</v>
       </c>
       <c r="D251" s="4" t="n">
-        <v>28.72</v>
+        <v>29.05</v>
       </c>
       <c r="E251" s="4" t="n">
-        <v>40.57</v>
+        <v>34.06</v>
       </c>
       <c r="F251" s="4" t="n">
-        <v>54.84</v>
+        <v>36.13</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Micro250_stocks.xlsx
+++ b/reports/Micro250_stocks.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -551,7 +551,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CUPID</t>
+          <t>SKYGOLD</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -560,37 +560,37 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>198.84</v>
+        <v>623.85</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>89.06</v>
+        <v>74.36</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>87.23999999999999</v>
+        <v>72.77</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>89.59999999999999</v>
+        <v>75.75</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>56.61</v>
+        <v>21.43</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>110.43</v>
+        <v>431.63</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>98.90000000000001</v>
+        <v>411.76</v>
       </c>
       <c r="J2" s="4" t="n">
-        <v>19898789</v>
+        <v>1459124</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>26737</v>
+        <v>9775</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ASTRAMICRO</t>
+          <t>AZAD</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -599,37 +599,37 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>1848.5</v>
+        <v>2479.5</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>83.20999999999999</v>
+        <v>72.87</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>85.66</v>
+        <v>69.13</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>79.04000000000001</v>
+        <v>68.19</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>26.31</v>
+        <v>32.67</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>1180.89</v>
+        <v>1888.78</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>1133.01</v>
+        <v>1835.78</v>
       </c>
       <c r="J3" s="4" t="n">
-        <v>1627652</v>
+        <v>600518</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>17551</v>
+        <v>16013</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>MSTCLTD</t>
+          <t>DATAMATICS</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -638,37 +638,37 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>715.7</v>
+        <v>900.45</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>70.15000000000001</v>
+        <v>72.65000000000001</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>72.40000000000001</v>
+        <v>63.06</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>61.89</v>
+        <v>59.79</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>20.73</v>
+        <v>26.74</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>503.5</v>
+        <v>776.0700000000001</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>502.23</v>
+        <v>771.9299999999999</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>2435624</v>
+        <v>167470</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>5039</v>
+        <v>5330</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>AVALON</t>
+          <t>CUPID</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -677,37 +677,37 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1788.3</v>
+        <v>212.24</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>68.25</v>
+        <v>70.78</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>78.67</v>
+        <v>88.63</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>76.14</v>
+        <v>90.34999999999999</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>36.65</v>
+        <v>45.69</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>1240.32</v>
+        <v>116.89</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>1171.51</v>
+        <v>104.35</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>366801</v>
+        <v>32894881</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>11948</v>
+        <v>29837</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>ARVIND</t>
+          <t>WELENT</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -716,37 +716,37 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>569.05</v>
+        <v>614</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>68.05</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>83.51000000000001</v>
+        <v>72.62</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>73.56</v>
+        <v>62.27</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>20.38</v>
+        <v>24.85</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>415.47</v>
+        <v>518.22</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>399.9</v>
+        <v>514.23</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>981539</v>
+        <v>353028</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>14916</v>
+        <v>8449</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>SKIPPER</t>
+          <t>ASTRAMICRO</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>574.95</v>
+        <v>1803.7</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>67.06</v>
+        <v>69.17</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>70.16</v>
+        <v>81.44</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>63.3</v>
+        <v>78.41</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>60.23</v>
+        <v>35.97</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>466.39</v>
+        <v>1228.52</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>462.73</v>
+        <v>1171.64</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>1049438</v>
+        <v>1056343</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>6491</v>
+        <v>17125</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>PGIL</t>
+          <t>SPARC</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -794,37 +794,37 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>2016.3</v>
+        <v>264.6</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>66.41</v>
+        <v>67.63</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>67.09999999999999</v>
+        <v>78.29000000000001</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>69.87</v>
+        <v>64.56</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>29.26</v>
+        <v>21.05</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1598.27</v>
+        <v>176.05</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1557.03</v>
+        <v>169.99</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>174669</v>
+        <v>3630984</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>9312</v>
+        <v>8899</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>AKUMS</t>
+          <t>BALAMINES</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -833,37 +833,37 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>626.8</v>
+        <v>2414.9</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>65.47</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>69.93000000000001</v>
+        <v>80.29000000000001</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>54.57</v>
+        <v>64.12</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>35.68</v>
+        <v>23.56</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>520.58</v>
+        <v>1572.56</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>517.4299999999999</v>
+        <v>1530.21</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>324618</v>
+        <v>539783</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>9596</v>
+        <v>7825</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>SPARC</t>
+          <t>WABAG</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -872,37 +872,37 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>239.37</v>
+        <v>2221.2</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>65.08</v>
+        <v>67.03</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>74.23</v>
+        <v>80.52</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>61.34</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>29.26</v>
+        <v>21.02</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>169.71</v>
+        <v>1537.2</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>164.97</v>
+        <v>1502.07</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>6409404</v>
+        <v>929174</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>7768</v>
+        <v>13925</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AVL</t>
+          <t>TIPSMUSIC</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>638.55</v>
+        <v>711.15</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>64.27</v>
+        <v>66.15000000000001</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>66.73</v>
+        <v>65.09</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>66.77</v>
+        <v>62.36</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>20.36</v>
+        <v>27.79</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>527.86</v>
+        <v>604.54</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>517.49</v>
+        <v>598.74</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>336097</v>
+        <v>255263</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>8246</v>
+        <v>9089</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>APOLLO</t>
+          <t>KSB</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -950,37 +950,37 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>450.05</v>
+        <v>932.7</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>63.88</v>
+        <v>61.07</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>69.56</v>
+        <v>63.31</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>74.33</v>
+        <v>59.67</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>41.15</v>
+        <v>35.1</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>307.41</v>
+        <v>835.21</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>289.18</v>
+        <v>825.16</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>24916643</v>
+        <v>173886</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>16724</v>
+        <v>16364</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>SKYGOLD</t>
+          <t>PGIL</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -989,37 +989,37 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>560</v>
+        <v>1979.8</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>63.81</v>
+        <v>60.67</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>67.91</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>72.84999999999999</v>
+        <v>69.19</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>26.56</v>
+        <v>37.65</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>420.44</v>
+        <v>1623.44</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>402.14</v>
+        <v>1578</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>1457765</v>
+        <v>173073</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>8673</v>
+        <v>9228</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>KSB</t>
+          <t>NEOGEN</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1028,37 +1028,37 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>936.1</v>
+        <v>2026.7</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>63.59</v>
+        <v>60.31</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>62.9</v>
+        <v>68.69</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>59.39</v>
+        <v>61.2</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>28.92</v>
+        <v>22.02</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>828.61</v>
+        <v>1616.45</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>819.85</v>
+        <v>1583.75</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>177937</v>
+        <v>123492</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>16292</v>
+        <v>5549</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>TIPSMUSIC</t>
+          <t>VIYASH</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1067,37 +1067,37 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>684.65</v>
+        <v>281.05</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>63</v>
+        <v>59.44</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>62.13</v>
+        <v>67.34999999999999</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>60.73</v>
+        <v>66.87</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>28.15</v>
+        <v>20.32</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>599.9400000000001</v>
+        <v>227.35</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>594.84</v>
+        <v>220.3</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>231075</v>
+        <v>2617386</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>8752</v>
+        <v>12125</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>TMB</t>
+          <t>KTKBANK</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1106,37 +1106,37 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>778.65</v>
+        <v>276.35</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>62.96</v>
+        <v>58.98</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>65.94</v>
+        <v>66.22</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>72.62</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>28.08</v>
+        <v>34.19</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>640.2</v>
+        <v>237.43</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>612.01</v>
+        <v>229.45</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>322435</v>
+        <v>1968552</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>12330</v>
+        <v>10451</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>YATHARTH</t>
+          <t>EQUITASBNK</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1145,37 +1145,37 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>865.55</v>
+        <v>78.17</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>62.41</v>
+        <v>58.61</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>62.34</v>
+        <v>68.58</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>64.33</v>
+        <v>58.67</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>26.93</v>
+        <v>41.13</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>753.59</v>
+        <v>67.79000000000001</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>732.3</v>
+        <v>66.87</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>382214</v>
+        <v>4701897</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>8340</v>
+        <v>9407</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>BALAMINES</t>
+          <t>MSTCLTD</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1184,37 +1184,37 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>2194.2</v>
+        <v>676.3</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>61.07</v>
+        <v>57.79</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>76.66</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>61.06</v>
+        <v>58.96</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>24.25</v>
+        <v>36.05</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1526.68</v>
+        <v>512.89</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>1494.5</v>
+        <v>509.27</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>459830</v>
+        <v>2552355</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>7109</v>
+        <v>4721</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>DCBBANK</t>
+          <t>EPL</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1223,37 +1223,37 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>189.27</v>
+        <v>237.56</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>58.84</v>
+        <v>57.52</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>60.52</v>
+        <v>60.01</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>60.9</v>
+        <v>56.76</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>25.68</v>
+        <v>38.16</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>175.32</v>
+        <v>219.04</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>170.95</v>
+        <v>218.2</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>901270</v>
+        <v>573969</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>6096</v>
+        <v>7609</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>STAR</t>
+          <t>TMB</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1262,31 +1262,31 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1126.8</v>
+        <v>769.2</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>58.67</v>
+        <v>57.16</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>62.24</v>
+        <v>67.84</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>61.52</v>
+        <v>73.7</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>29.67</v>
+        <v>22.3</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>997.4299999999999</v>
+        <v>646.51</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>974.97</v>
+        <v>617.87</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>203699</v>
+        <v>338956</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>10386</v>
+        <v>12636</v>
       </c>
     </row>
     <row r="21">
@@ -1301,37 +1301,37 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>556</v>
+        <v>560.05</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>58.63</v>
+        <v>56.78</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>62.13</v>
+        <v>64.12</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>60.3</v>
+        <v>61.47</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>39.58</v>
+        <v>36.58</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>499.63</v>
+        <v>503.43</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>494.94</v>
+        <v>498.09</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>242645</v>
+        <v>255810</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>11528</v>
+        <v>11778</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>LLOYDSENT</t>
+          <t>AVALON</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1340,31 +1340,31 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>75.34999999999999</v>
+        <v>1728.6</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>58.31</v>
+        <v>56.24</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>60.78</v>
+        <v>76.89</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>59.81</v>
+        <v>75.20999999999999</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>50.2</v>
+        <v>41.44</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>64.73</v>
+        <v>1263.38</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>63.93</v>
+        <v>1191.61</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>3899130</v>
+        <v>367889</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>11503</v>
+        <v>11813</v>
       </c>
     </row>
     <row r="23">
@@ -1379,37 +1379,37 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>83.94</v>
+        <v>85.36</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>58.3</v>
+        <v>56.08</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>71.54000000000001</v>
+        <v>75.09</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>62.3</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>47.26</v>
+        <v>32.27</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>63.25</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>62.24</v>
+        <v>63.26</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>21539632</v>
+        <v>22676116</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>11964</v>
+        <v>12913</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>AZAD</t>
+          <t>LLOYDSENT</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1418,37 +1418,37 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2149.1</v>
+        <v>74.58</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>57.24</v>
+        <v>53.61</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>60.67</v>
+        <v>62.93</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>63.14</v>
+        <v>61.11</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>39.89</v>
+        <v>42.35</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1857.59</v>
+        <v>65.23999999999999</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1810.49</v>
+        <v>64.34999999999999</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>443110</v>
+        <v>4137249</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>13879</v>
+        <v>11935</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>NEOGEN</t>
+          <t>SKIPPER</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1457,37 +1457,37 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1968.3</v>
+        <v>548.05</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>56.8</v>
+        <v>53.41</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>65.48</v>
+        <v>63.24</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>58.77</v>
+        <v>61.39</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>30.71</v>
+        <v>54.02</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1596.14</v>
+        <v>470.67</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>1566.95</v>
+        <v>466.06</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>131169</v>
+        <v>881965</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>5390</v>
+        <v>6203</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>EQUITASBNK</t>
+          <t>ARVIND</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1496,37 +1496,37 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>76.3</v>
+        <v>533.1</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>56.07</v>
+        <v>53.17</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>62.99</v>
+        <v>69.72</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>55.67</v>
+        <v>67.56999999999999</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>50.82</v>
+        <v>24.81</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>67.13</v>
+        <v>421.74</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>66.34</v>
+        <v>405.26</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>4236095</v>
+        <v>1047276</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>8728</v>
+        <v>13806</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>BBOX</t>
+          <t>APOLLO</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1535,37 +1535,37 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>994.95</v>
+        <v>408.85</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>55.62</v>
+        <v>51.21</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>72.22</v>
+        <v>62.07</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>71.75</v>
+        <v>70.44</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>31.93</v>
+        <v>34.49</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>718.04</v>
+        <v>313.71</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>675.7</v>
+        <v>294.84</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>745017</v>
+        <v>21090881</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>17670</v>
+        <v>15193</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>SHAILY</t>
+          <t>KRN</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1574,31 +1574,31 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2901.6</v>
+        <v>1211.8</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>53.89</v>
+        <v>50.78</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>62.4</v>
+        <v>61.88</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>69.72</v>
+        <v>62.68</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>31.78</v>
+        <v>53.84</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>2447.84</v>
+        <v>1034.85</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>2353.56</v>
+        <v>990.9400000000001</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>345157</v>
+        <v>128517</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>13346</v>
+        <v>8057</v>
       </c>
     </row>
     <row r="29">
@@ -1613,37 +1613,37 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1825.9</v>
+        <v>1782.1</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>53.77</v>
+        <v>50.32</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>73.92</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>66.81</v>
+        <v>65.31</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>22.37</v>
+        <v>29.6</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1406.02</v>
+        <v>1425.71</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>1361.22</v>
+        <v>1378</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>255021</v>
+        <v>257088</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>11862</v>
+        <v>11587</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>RAIN</t>
+          <t>THYROCARE</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1652,37 +1652,37 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>187.74</v>
+        <v>515.7</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>52.81</v>
+        <v>46.66</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>66.19</v>
+        <v>61.06</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>57.91</v>
+        <v>63.55</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>27.7</v>
+        <v>29.9</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>153.44</v>
+        <v>453.05</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>150.22</v>
+        <v>438.17</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>6523813</v>
+        <v>387501</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>6315</v>
+        <v>8208</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>MIDHANI</t>
+          <t>MTARTECH</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1691,37 +1691,37 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>427.85</v>
+        <v>7101</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>52.34</v>
+        <v>45.61</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>61.48</v>
+        <v>64.01000000000001</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>56.72</v>
+        <v>78.15000000000001</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>34.39</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>382.37</v>
+        <v>5268.87</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>377.83</v>
+        <v>4719.47</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>1348920</v>
+        <v>1425331</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>8015</v>
+        <v>21842</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>KRN</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1730,109 +1730,31 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1214.8</v>
+        <v>543.05</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>51.89</v>
+        <v>45.53</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>61.04</v>
+        <v>70</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>61.94</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>59.39</v>
+        <v>80.38</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1024.66</v>
+        <v>344.94</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>981.5700000000001</v>
+        <v>301.85</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>135627</v>
+        <v>2936280</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>7952</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>STLTECH</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>576.8</v>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>51.11</v>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>75.43000000000001</v>
-      </c>
-      <c r="F33" s="4" t="n">
-        <v>84.48</v>
-      </c>
-      <c r="G33" s="4" t="n">
-        <v>68.89</v>
-      </c>
-      <c r="H33" s="4" t="n">
-        <v>330.6</v>
-      </c>
-      <c r="I33" s="4" t="n">
-        <v>289</v>
-      </c>
-      <c r="J33" s="4" t="n">
-        <v>2556221</v>
-      </c>
-      <c r="K33" s="4" t="n">
-        <v>29642</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>KTKBANK</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>Chart</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="n">
-        <v>263.4</v>
-      </c>
-      <c r="D34" s="4" t="n">
-        <v>45.53</v>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>61.92</v>
-      </c>
-      <c r="F34" s="4" t="n">
-        <v>64.91</v>
-      </c>
-      <c r="G34" s="4" t="n">
-        <v>34.21</v>
-      </c>
-      <c r="H34" s="4" t="n">
-        <v>235.37</v>
-      </c>
-      <c r="I34" s="4" t="n">
-        <v>227.54</v>
-      </c>
-      <c r="J34" s="4" t="n">
-        <v>2025654</v>
-      </c>
-      <c r="K34" s="4" t="n">
-        <v>9961</v>
+        <v>27781</v>
       </c>
     </row>
   </sheetData>
@@ -1868,8 +1790,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1927,7 +1847,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>CUPID</t>
+          <t>SHAREINDIA</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -1936,22 +1856,22 @@
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>198.84</v>
+        <v>179.03</v>
       </c>
       <c r="D2" s="4" t="n">
-        <v>89.06</v>
+        <v>83.67</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>87.23999999999999</v>
+        <v>66.66</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>89.59999999999999</v>
+        <v>49.01</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>QUESS</t>
+          <t>OPTIEMUS</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -1960,22 +1880,22 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>290.85</v>
+        <v>563.55</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>85.7</v>
+        <v>81.7</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>73.14</v>
+        <v>63.11</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>44.99</v>
+        <v>54.41</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ASTRAMICRO</t>
+          <t>GREAVESCOT</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -1984,22 +1904,22 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>1848.5</v>
+        <v>263.6</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>83.20999999999999</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>85.66</v>
+        <v>76.78</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>79.04000000000001</v>
+        <v>62.65</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>JLHL</t>
+          <t>STYL</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -2008,22 +1928,22 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1456.3</v>
+        <v>360.7</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>82.01000000000001</v>
+        <v>80.75</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>64.61</v>
+        <v>72.87</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>55.31</v>
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>WEWORK</t>
+          <t>TSFINV</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -2032,22 +1952,22 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>739.65</v>
+        <v>473.9</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>77.73999999999999</v>
+        <v>78.89</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>73.09</v>
+        <v>62.81</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v/>
+        <v>58.71</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>IXIGO</t>
+          <t>AETHER</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -2056,22 +1976,22 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>222.23</v>
+        <v>1500.8</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>76.59999999999999</v>
+        <v>76.94</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>60.53</v>
+        <v>76</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>57.33</v>
+        <v>76.48999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>STYL</t>
+          <t>JLHL</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -2080,22 +2000,22 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>325.65</v>
+        <v>1464.1</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>76.48999999999999</v>
+        <v>76.23</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>66.3</v>
+        <v>64.53</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v/>
+        <v>55.29</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>PICCADIL</t>
+          <t>IONEXCHANG</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -2104,22 +2024,22 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>647.35</v>
+        <v>468.3</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>75.93000000000001</v>
+        <v>74.88</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>61</v>
+        <v>66.8</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v/>
+        <v>53.02</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>VIYASH</t>
+          <t>SKYGOLD</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -2128,22 +2048,22 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>294.15</v>
+        <v>623.85</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>75.64</v>
+        <v>74.36</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>76.09999999999999</v>
+        <v>72.77</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>68.79000000000001</v>
+        <v>75.75</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>EMIL</t>
+          <t>AKUMS</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -2152,22 +2072,22 @@
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>140.68</v>
+        <v>658.2</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>75.62</v>
+        <v>73.33</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>66.23999999999999</v>
+        <v>76.89</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>52.22</v>
+        <v>60.45</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>OPTIEMUS</t>
+          <t>CCAVENUE</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2176,22 +2096,22 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>521.55</v>
+        <v>18.1</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>75.51000000000001</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>61.07</v>
+        <v>63.18</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>53.38</v>
+        <v>48.77</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>RATEGAIN</t>
+          <t>AZAD</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -2200,22 +2120,22 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>941.05</v>
+        <v>2479.5</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>75.09999999999999</v>
+        <v>72.87</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>78.31</v>
+        <v>69.13</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>66.59</v>
+        <v>68.19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>CCAVENUE</t>
+          <t>DATAMATICS</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -2224,22 +2144,22 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>17.08</v>
+        <v>900.45</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>74.48999999999999</v>
+        <v>72.65000000000001</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>59.15</v>
+        <v>63.06</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>46.52</v>
+        <v>59.79</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>PCJEWELLER</t>
+          <t>AEQUS</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -2248,22 +2168,22 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>10.3</v>
+        <v>258.07</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>74.08</v>
+        <v>71.13</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>55.17</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>50.81</v>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>TRIVENI</t>
+          <t>CUPID</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -2272,22 +2192,22 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>458.65</v>
+        <v>212.24</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>73.88</v>
+        <v>70.78</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>68.11</v>
+        <v>88.63</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>60.7</v>
+        <v>90.34999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>QUESS</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -2296,22 +2216,22 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2037.9</v>
+        <v>288.15</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>73.65000000000001</v>
+        <v>70.76000000000001</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>76.76000000000001</v>
+        <v>71.81</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v/>
+        <v>44.67</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>SFL</t>
+          <t>UTLSOLAR</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -2320,22 +2240,22 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>766.55</v>
+        <v>364.5</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>73.11</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>71.44</v>
+        <v>77.98</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>51.7</v>
+        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>SANSERA</t>
+          <t>SUDARSCHEM</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2344,22 +2264,22 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>3251.5</v>
+        <v>999.25</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>72.97</v>
+        <v>69.84</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>78.86</v>
+        <v>56.25</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>79.98</v>
+        <v>52.33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>TSFINV</t>
+          <t>WELENT</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -2368,22 +2288,22 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>455.5</v>
+        <v>614</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>72.81</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>58.77</v>
+        <v>72.62</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>57.02</v>
+        <v>62.27</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>SWSOLAR</t>
+          <t>VAIBHAVGBL</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -2392,22 +2312,22 @@
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>246.9</v>
+        <v>255.78</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>72.62</v>
+        <v>69.52</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>62.57</v>
+        <v>62.86</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>44.96</v>
+        <v>51.31</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>VARROC</t>
+          <t>TRIVENI</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -2416,22 +2336,22 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>667.55</v>
+        <v>462.4</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>72.42</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>69.23999999999999</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>60.66</v>
+        <v>61.06</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>SKFINDUS</t>
+          <t>RATEGAIN</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -2440,22 +2360,22 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2825.8</v>
+        <v>941.75</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>72.20999999999999</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>66.17</v>
+        <v>78.48</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v/>
+        <v>66.72</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>EIEL</t>
+          <t>ASTRAMICRO</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -2464,22 +2384,22 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>235.46</v>
+        <v>1803.7</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>71.72</v>
+        <v>69.17</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>63.28</v>
+        <v>81.44</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>49.78</v>
+        <v>78.41</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>INDIAGLYCO</t>
+          <t>BORORENEW</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -2488,22 +2408,22 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1075.75</v>
+        <v>651.65</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>71.06999999999999</v>
+        <v>69.17</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>59.95</v>
+        <v>66.53</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>62.4</v>
+        <v>58.61</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GREAVESCOT</t>
+          <t>UJJIVANSFB</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -2512,22 +2432,22 @@
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>226.57</v>
+        <v>65.27</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>70.76000000000001</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>69.61</v>
+        <v>63.09</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>57.79</v>
+        <v>63.38</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>WELENT</t>
+          <t>HAPPSTMNDS</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -2536,22 +2456,22 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>603.25</v>
+        <v>386.3</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>70.45999999999999</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>71.20999999999999</v>
+        <v>48.31</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>61.59</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>MSTCLTD</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -2560,22 +2480,22 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>715.7</v>
+        <v>244.49</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>70.15000000000001</v>
+        <v>68.41</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>72.40000000000001</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>61.89</v>
+        <v>51.44</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>AETHER</t>
+          <t>SANSERA</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -2584,22 +2504,22 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1359.6</v>
+        <v>3304</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>69.64</v>
+        <v>68.25</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>70.68000000000001</v>
+        <v>79.63</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>72.88</v>
+        <v>80.38</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>BORORENEW</t>
+          <t>THANGAMAYL</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -2608,22 +2528,22 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>621.7</v>
+        <v>6598.5</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>69.59</v>
+        <v>68.05</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>64.56</v>
+        <v>77.88</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>57.51</v>
+        <v>84.86</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>BLUESTONE</t>
+          <t>PNCINFRA</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -2632,22 +2552,22 @@
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>569.65</v>
+        <v>241.53</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>69.47</v>
+        <v>67.87</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>58.09</v>
+        <v>58.38</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v/>
+        <v>45.26</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>REFEX</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -2656,22 +2576,22 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>358.4</v>
+        <v>2022.8</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>69.34</v>
+        <v>67.75</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>69.25</v>
+        <v>76.92</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>55.86</v>
+        <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>PRICOLLTD</t>
+          <t>SPARC</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -2680,22 +2600,22 @@
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>621.7</v>
+        <v>264.6</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>69.3</v>
+        <v>67.63</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>58.2</v>
+        <v>78.29000000000001</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>61.29</v>
+        <v>64.56</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>APLLTD</t>
+          <t>PICCADIL</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -2704,22 +2624,22 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>823.7</v>
+        <v>649.45</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>69.26000000000001</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>58.32</v>
+        <v>64.25</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>48.66</v>
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>VMART</t>
+          <t>WEWORK</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -2728,22 +2648,22 @@
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>797.9</v>
+        <v>719.15</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>68.65000000000001</v>
+        <v>67.48</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>65.34</v>
+        <v>71.5</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>54.5</v>
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>SHRIPISTON</t>
+          <t>APLLTD</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -2752,22 +2672,22 @@
         </is>
  